--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -137,7 +137,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable" displayName="AveragesTable" ref="A1:EC19" headerRowCount="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AveragesTable_Germany_Bu" displayName="AveragesTable_Germany_Bu" ref="A1:EC19" headerRowCount="1">
   <autoFilter ref="A1:EC19"/>
   <tableColumns count="133">
     <tableColumn id="1" name="team_name"/>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C3" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>7</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>2.4</v>
+        <v>1.83</v>
       </c>
       <c r="H3" t="n">
-        <v>103.8</v>
+        <v>109.33</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>5.8</v>
+        <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="M3" t="n">
-        <v>61.2</v>
+        <v>64</v>
       </c>
       <c r="N3" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.4</v>
+        <v>2.67</v>
       </c>
       <c r="P3" t="n">
-        <v>18.4</v>
+        <v>15.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.4</v>
+        <v>10.17</v>
       </c>
       <c r="R3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>1.17</v>
       </c>
       <c r="T3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.2</v>
+        <v>48.83</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>18.2</v>
+        <v>19</v>
       </c>
       <c r="AA3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="n">
-        <v>18.8</v>
+        <v>19.67</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.95</v>
+        <v>2.01</v>
       </c>
       <c r="AE3" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0.14</v>
@@ -1953,70 +1953,70 @@
         <v>4</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BH3" t="n">
-        <v>12.5</v>
+        <v>13.15</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="BO3" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.83</v>
+        <v>5.31</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.67</v>
+        <v>6.08</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV3" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.39</v>
+        <v>2.33</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.64</v>
+        <v>3.66</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CC3" t="n">
         <v>2.94</v>
@@ -2028,7 +2028,7 @@
         <v>1.29</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CG3" t="n">
         <v>3.28</v>
@@ -2052,7 +2052,7 @@
         <v>2.99</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CO3" t="n">
         <v>1.19</v>
@@ -2061,7 +2061,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
@@ -2083,95 +2083,95 @@
       </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CZ3" t="inlineStr"/>
       <c r="DA3" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="DB3" t="n">
         <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DE3" t="n">
         <v>0.08</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="DH3" t="n">
-        <v>90.58</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>4.08</v>
+        <v>3.77</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.33</v>
+        <v>6.84</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5</v>
+        <v>0.39</v>
       </c>
       <c r="DM3" t="n">
-        <v>50.41</v>
+        <v>52.54</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.58</v>
+        <v>13.54</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.17</v>
+        <v>9.16</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.92</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.67</v>
+        <v>46.54</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.92</v>
+        <v>15.54</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.17</v>
+        <v>11.77</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.33</v>
+        <v>22.46</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="EC3" t="n">
-        <v>4.08</v>
+        <v>3.77</v>
       </c>
     </row>
     <row r="4">
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C5" t="n">
         <v>6</v>
       </c>
       <c r="D5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E5" t="n">
         <v>0.17</v>
@@ -2674,139 +2674,139 @@
         <v>1.83</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.17</v>
+        <v>2.57</v>
       </c>
       <c r="AI5" t="n">
-        <v>97</v>
+        <v>95.56999999999999</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.33</v>
+        <v>5.71</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.17</v>
+        <v>0</v>
       </c>
       <c r="AN5" t="n">
-        <v>53</v>
+        <v>51.14</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.17</v>
+        <v>1.71</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.5</v>
+        <v>12.14</v>
       </c>
       <c r="AR5" t="n">
-        <v>13.83</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.17</v>
+        <v>9.43</v>
       </c>
       <c r="AT5" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>48.57</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA5" t="n">
+        <v>14.71</v>
+      </c>
+      <c r="BB5" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="BC5" t="n">
+        <v>4.14</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>21.14</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BF5" t="n">
         <v>2</v>
       </c>
-      <c r="AU5" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY5" t="n">
-        <v>49.5</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="BB5" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="BC5" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BD5" t="n">
-        <v>22</v>
-      </c>
-      <c r="BE5" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>1.83</v>
-      </c>
       <c r="BG5" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.42</v>
+        <v>11.23</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.33</v>
+        <v>3.31</v>
       </c>
       <c r="BJ5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BO5" t="n">
         <v>2.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.17</v>
+        <v>3.77</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.25</v>
+        <v>5.69</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT5" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BU5" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW5" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX5" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BY5" t="n">
         <v>2.62</v>
@@ -2815,22 +2815,22 @@
         <v>2.72</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.22</v>
+        <v>3.26</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.74</v>
+        <v>3.77</v>
       </c>
       <c r="CE5" t="n">
         <v>1.3</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CG5" t="n">
         <v>3.3</v>
@@ -2851,13 +2851,13 @@
         <v>1.65</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP5" t="n">
         <v>1.63</v>
@@ -2878,7 +2878,7 @@
         <v>1.56</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CW5" t="n">
         <v>1.56</v>
@@ -2887,13 +2887,13 @@
         <v>1.46</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.6</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DB5" t="n">
         <v>1.2</v>
@@ -2902,49 +2902,49 @@
         <v>1.67</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.08</v>
+        <v>2.77</v>
       </c>
       <c r="DH5" t="n">
-        <v>93.25</v>
+        <v>92.77</v>
       </c>
       <c r="DI5" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.16</v>
+        <v>5.38</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.92</v>
+        <v>49.15</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.08</v>
+        <v>1.84</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.84</v>
+        <v>11.69</v>
       </c>
       <c r="DQ5" t="n">
-        <v>13.5</v>
+        <v>12.54</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.75</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="DS5" t="n">
         <v>0.08</v>
@@ -2956,28 +2956,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>50.08</v>
+        <v>49.54</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.25</v>
+        <v>13</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.75</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.58</v>
+        <v>22.08</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="6">
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C6" t="n">
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3080,49 +3080,49 @@
         <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AH6" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>102</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AN6" t="n">
-        <v>41.5</v>
+        <v>43</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.33</v>
+        <v>12.29</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.33</v>
+        <v>15.14</v>
       </c>
       <c r="AS6" t="n">
         <v>8</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AU6" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3134,82 +3134,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>44.83</v>
+        <v>45.29</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="BA6" t="n">
-        <v>11.67</v>
+        <v>12.14</v>
       </c>
       <c r="BB6" t="n">
-        <v>7.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.83</v>
+        <v>20.29</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="BG6" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.83</v>
+        <v>10.85</v>
       </c>
       <c r="BI6" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.58</v>
+        <v>4.77</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.25</v>
+        <v>6.08</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BT6" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV6" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY6" t="n">
         <v>3.16</v>
@@ -3218,46 +3218,46 @@
         <v>3.26</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.21</v>
+        <v>4.32</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.6</v>
+        <v>4.84</v>
       </c>
       <c r="CE6" t="n">
         <v>1.31</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CH6" t="n">
         <v>1.49</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK6" t="n">
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
@@ -3272,7 +3272,7 @@
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CT6" t="n">
         <v>3.27</v>
@@ -3281,73 +3281,73 @@
         <v>1.53</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.39</v>
+        <v>2.35</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DA6" t="n">
         <v>2.07</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="DH6" t="n">
-        <v>97.84</v>
+        <v>95.16</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.58</v>
+        <v>4.62</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DM6" t="n">
-        <v>36.42</v>
+        <v>37.61</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.42</v>
+        <v>12.39</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.08</v>
+        <v>14.07</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.17</v>
+        <v>8.15</v>
       </c>
       <c r="DS6" t="n">
         <v>0.08</v>
@@ -3359,28 +3359,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>43</v>
+        <v>43.39</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.42</v>
+        <v>11.69</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.58</v>
+        <v>7.92</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.58</v>
+        <v>20.77</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.26</v>
+        <v>1.28</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
     </row>
     <row r="7">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D8" t="n">
         <v>6</v>
@@ -3805,49 +3805,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.33</v>
+        <v>1.57</v>
       </c>
       <c r="G8" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="H8" t="n">
-        <v>98.17</v>
+        <v>86</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J8" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="L8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="M8" t="n">
-        <v>55.33</v>
+        <v>48.86</v>
       </c>
       <c r="N8" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="O8" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="P8" t="n">
-        <v>13</v>
+        <v>13.57</v>
       </c>
       <c r="Q8" t="n">
-        <v>12</v>
+        <v>11.71</v>
       </c>
       <c r="R8" t="n">
-        <v>5.67</v>
+        <v>6.14</v>
       </c>
       <c r="S8" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="T8" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>54</v>
+        <v>51.43</v>
       </c>
       <c r="Y8" t="n">
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.17</v>
+        <v>11.86</v>
       </c>
       <c r="AA8" t="n">
-        <v>9.17</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>3</v>
+        <v>3.14</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.5</v>
+        <v>21.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.32</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AF8" t="n">
         <v>0.17</v>
@@ -3964,64 +3964,64 @@
         <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.17</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL8" t="n">
         <v>0.92</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.33</v>
+        <v>4.15</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.75</v>
+        <v>5.31</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS8" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU8" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BV8" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW8" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY8" t="n">
         <v>2.28</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CA8" t="n">
         <v>3.64</v>
@@ -4039,19 +4039,19 @@
         <v>1.3</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CH8" t="n">
         <v>1.52</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.33</v>
+        <v>2.36</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK8" t="n">
         <v>1.4</v>
@@ -4060,37 +4060,37 @@
         <v>1.74</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN8" t="n">
         <v>2.05</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CR8" t="n">
         <v>1.38</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CT8" t="n">
         <v>3.15</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX8" t="n">
         <v>1.48</v>
@@ -4105,55 +4105,55 @@
         <v>2.07</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="DH8" t="n">
-        <v>95.34</v>
+        <v>89</v>
       </c>
       <c r="DI8" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.5</v>
+        <v>4.39</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM8" t="n">
-        <v>49.33</v>
+        <v>46.31</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.92</v>
+        <v>1.77</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.16</v>
+        <v>12.54</v>
       </c>
       <c r="DQ8" t="n">
-        <v>12.08</v>
+        <v>11.92</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.25</v>
+        <v>7.38</v>
       </c>
       <c r="DS8" t="n">
         <v>0.08</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.66</v>
+        <v>47.69</v>
       </c>
       <c r="DW8" t="n">
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.5</v>
+        <v>12.31</v>
       </c>
       <c r="DY8" t="n">
-        <v>9</v>
+        <v>8.77</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.5</v>
+        <v>3.54</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.5</v>
+        <v>20.69</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.5</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="9">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" t="n">
         <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,139 +4689,139 @@
         <v>1.83</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH10" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="AI10" t="n">
-        <v>110.5</v>
+        <v>104.86</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AL10" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN10" t="n">
-        <v>51.5</v>
+        <v>50.86</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AP10" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="AQ10" t="n">
-        <v>14.67</v>
+        <v>13.29</v>
       </c>
       <c r="AR10" t="n">
-        <v>14.17</v>
+        <v>13.86</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.17</v>
+        <v>6.57</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>60</v>
+        <v>57.86</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.83</v>
+        <v>14</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.33</v>
+        <v>5.86</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.17</v>
+        <v>19.43</v>
       </c>
       <c r="BE10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>9.92</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.23</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BN10" t="n">
         <v>1.62</v>
       </c>
-      <c r="BF10" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>9.5</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BM10" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BN10" t="n">
-        <v>1.75</v>
-      </c>
       <c r="BO10" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.08</v>
+        <v>4.23</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.42</v>
+        <v>5.69</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BT10" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BU10" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY10" t="n">
         <v>1.95</v>
@@ -4833,28 +4833,28 @@
         <v>3.57</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.43</v>
+        <v>2.56</v>
       </c>
       <c r="CE10" t="n">
         <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.56</v>
@@ -4863,34 +4863,34 @@
         <v>1.33</v>
       </c>
       <c r="CL10" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="CM10" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="CN10" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="CO10" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="CP10" t="n">
         <v>1.66</v>
       </c>
-      <c r="CM10" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="CN10" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="CO10" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="CP10" t="n">
-        <v>1.65</v>
-      </c>
       <c r="CQ10" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CR10" t="n">
         <v>1.37</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV10" t="n">
         <v>2.48</v>
@@ -4913,82 +4913,82 @@
         <v>1.69</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="DH10" t="n">
-        <v>109.75</v>
+        <v>106.77</v>
       </c>
       <c r="DI10" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="DK10" t="n">
-        <v>6</v>
+        <v>5.85</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.42</v>
+        <v>0.39</v>
       </c>
       <c r="DM10" t="n">
-        <v>57.08</v>
+        <v>56.31</v>
       </c>
       <c r="DN10" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DP10" t="n">
-        <v>14.58</v>
+        <v>13.85</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.17</v>
+        <v>14</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.5</v>
+        <v>6.69</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>59</v>
+        <v>57.92</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>15.66</v>
+        <v>15.62</v>
       </c>
       <c r="DY10" t="n">
-        <v>10.17</v>
+        <v>9.84</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.5</v>
+        <v>5.77</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.5</v>
+        <v>20.54</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="11">
@@ -4998,10 +4998,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D11" t="n">
         <v>6</v>
@@ -5010,82 +5010,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="G11" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="H11" t="n">
-        <v>97.33</v>
+        <v>92.86</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J11" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="K11" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="L11" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>41.17</v>
+        <v>43.71</v>
       </c>
       <c r="N11" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="P11" t="n">
-        <v>12.5</v>
+        <v>12.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.33</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>9.57</v>
       </c>
       <c r="S11" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="T11" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>46</v>
+        <v>46.86</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z11" t="n">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.17</v>
+        <v>7.57</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.33</v>
+        <v>18.86</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AF11" t="n">
         <v>0.17</v>
@@ -5169,70 +5169,70 @@
         <v>2.5</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.67</v>
+        <v>10.69</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN11" t="n">
         <v>1.08</v>
       </c>
       <c r="BO11" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.75</v>
+        <v>4.69</v>
       </c>
       <c r="BR11" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BT11" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV11" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.09</v>
+        <v>2.01</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.99</v>
+        <v>1.93</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.52</v>
+        <v>3.54</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="CC11" t="n">
         <v>2.92</v>
@@ -5241,153 +5241,157 @@
         <v>3.32</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CH11" t="n">
         <v>1.54</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.9</v>
+        <v>2.87</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CO11" t="n">
         <v>1.18</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="CT11" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="CU11" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CV11" t="n">
         <v>2.48</v>
       </c>
-      <c r="CT11" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="CU11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CV11" t="n">
-        <v>2.53</v>
-      </c>
       <c r="CW11" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="CX11" t="inlineStr"/>
+        <v>1.58</v>
+      </c>
+      <c r="CX11" t="n">
+        <v>1.44</v>
+      </c>
       <c r="CY11" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CZ11" t="inlineStr"/>
+        <v>1.67</v>
+      </c>
+      <c r="CZ11" t="n">
+        <v>2.63</v>
+      </c>
       <c r="DA11" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="DE11" t="n">
         <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DG11" t="n">
         <v>2.08</v>
       </c>
       <c r="DH11" t="n">
-        <v>92.75</v>
+        <v>90.7</v>
       </c>
       <c r="DI11" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.42</v>
+        <v>4.54</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DM11" t="n">
-        <v>43.42</v>
+        <v>44.61</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.84</v>
+        <v>0.77</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.84</v>
+        <v>2</v>
       </c>
       <c r="DP11" t="n">
         <v>13.92</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.33</v>
+        <v>11.38</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.42</v>
+        <v>9.23</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46</v>
+        <v>46.46</v>
       </c>
       <c r="DW11" t="n">
         <v>0.08</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.58</v>
+        <v>11.85</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.75</v>
+        <v>7.92</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.83</v>
+        <v>3.92</v>
       </c>
       <c r="EA11" t="n">
-        <v>21</v>
+        <v>20.62</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.5</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="12">
@@ -6602,13 +6606,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C15" t="n">
         <v>6</v>
       </c>
       <c r="D15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6695,49 +6699,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.5</v>
+        <v>3.43</v>
       </c>
       <c r="AI15" t="n">
-        <v>89.5</v>
+        <v>80</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="AL15" t="n">
-        <v>4.83</v>
+        <v>5.71</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AN15" t="n">
-        <v>42.33</v>
+        <v>38.57</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.83</v>
+        <v>11.57</v>
       </c>
       <c r="AR15" t="n">
-        <v>13</v>
+        <v>13.57</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.67</v>
+        <v>7.43</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6749,82 +6753,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>54.83</v>
+        <v>56.14</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>15</v>
+        <v>16.43</v>
       </c>
       <c r="BB15" t="n">
-        <v>10.17</v>
+        <v>11</v>
       </c>
       <c r="BC15" t="n">
-        <v>4.83</v>
+        <v>5.43</v>
       </c>
       <c r="BD15" t="n">
-        <v>19</v>
+        <v>18.71</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.59</v>
+        <v>1.69</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BH15" t="n">
-        <v>10</v>
+        <v>10.31</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.83</v>
+        <v>0.85</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BO15" t="n">
         <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.17</v>
+        <v>4.92</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.83</v>
+        <v>5.38</v>
       </c>
       <c r="BR15" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS15" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT15" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>23.08</v>
       </c>
       <c r="BV15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW15" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX15" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BY15" t="n">
         <v>2.22</v>
@@ -6839,10 +6843,10 @@
         <v>3.82</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.24</v>
+        <v>3.2</v>
       </c>
       <c r="CE15" t="n">
         <v>1.26</v>
@@ -6857,25 +6861,25 @@
         <v>1.61</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.49</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP15" t="n">
         <v>1.52</v>
@@ -6885,7 +6889,7 @@
       </c>
       <c r="CR15" t="inlineStr"/>
       <c r="CS15" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="n">
@@ -6901,64 +6905,64 @@
         <v>1.46</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.55</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB15" t="n">
         <v>1.17</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.42</v>
+        <v>2.92</v>
       </c>
       <c r="DH15" t="n">
-        <v>102.25</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="DI15" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
       <c r="DK15" t="n">
-        <v>4.83</v>
+        <v>5.3</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5</v>
+        <v>0.54</v>
       </c>
       <c r="DM15" t="n">
-        <v>48.42</v>
+        <v>45.92</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.42</v>
+        <v>2.39</v>
       </c>
       <c r="DP15" t="n">
-        <v>13</v>
+        <v>12.77</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.25</v>
+        <v>12.61</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.75</v>
+        <v>6.69</v>
       </c>
       <c r="DS15" t="n">
         <v>0.08</v>
@@ -6970,28 +6974,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>54.83</v>
+        <v>55.54</v>
       </c>
       <c r="DW15" t="n">
         <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>14.92</v>
+        <v>15.69</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.42</v>
+        <v>10.85</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.5</v>
+        <v>4.85</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.92</v>
+        <v>19.69</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.61</v>
+        <v>1.66</v>
       </c>
       <c r="EC15" t="n">
-        <v>3</v>
+        <v>2.85</v>
       </c>
     </row>
     <row r="16">
@@ -7400,10 +7404,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D17" t="n">
         <v>6</v>
@@ -7412,82 +7416,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="G17" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="H17" t="n">
+        <v>94.86</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>2</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.71</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="M17" t="n">
+        <v>49.71</v>
+      </c>
+      <c r="N17" t="n">
         <v>1</v>
       </c>
-      <c r="G17" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="H17" t="n">
-        <v>100.33</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="K17" t="n">
+      <c r="O17" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="P17" t="n">
+        <v>12.29</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>10.86</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>54.43</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>17.29</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>11.29</v>
+      </c>
+      <c r="AB17" t="n">
         <v>6</v>
       </c>
-      <c r="L17" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="M17" t="n">
-        <v>48.5</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="P17" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="R17" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="T17" t="n">
-        <v>2</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>54.33</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>6.33</v>
-      </c>
       <c r="AC17" t="n">
-        <v>19.83</v>
+        <v>21</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.9</v>
+        <v>1.87</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.71</v>
       </c>
       <c r="AF17" t="n">
         <v>0.33</v>
@@ -7571,70 +7575,70 @@
         <v>2.17</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.42</v>
+        <v>10.77</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.58</v>
+        <v>5.85</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.67</v>
+        <v>92.31</v>
       </c>
       <c r="BS17" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BU17" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX17" t="n">
-        <v>58.33</v>
+        <v>53.85</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.87</v>
+        <v>3.84</v>
       </c>
       <c r="CC17" t="n">
         <v>2.11</v>
@@ -7646,52 +7650,52 @@
         <v>1.3</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CH17" t="n">
         <v>1.53</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.58</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="CN17" t="n">
         <v>2.19</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP17" t="n">
         <v>1.63</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV17" t="n">
         <v>2.42</v>
@@ -7715,64 +7719,64 @@
         <v>1.21</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.83</v>
+        <v>3.23</v>
       </c>
       <c r="DH17" t="n">
-        <v>100</v>
+        <v>97.08</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.08</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.25</v>
+        <v>5.69</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DM17" t="n">
-        <v>46.66</v>
+        <v>47.46</v>
       </c>
       <c r="DN17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.58</v>
+        <v>12.54</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.08</v>
+        <v>7.77</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>51.92</v>
+        <v>52.15</v>
       </c>
       <c r="DW17" t="n">
         <v>0.08</v>
@@ -7781,19 +7785,19 @@
         <v>15.92</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.25</v>
+        <v>10.39</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.66</v>
+        <v>5.54</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.42</v>
+        <v>21</v>
       </c>
       <c r="EB17" t="n">
         <v>1.74</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="18">
@@ -7803,10 +7807,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D18" t="n">
         <v>6</v>
@@ -7815,82 +7819,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="G18" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="H18" t="n">
-        <v>86.5</v>
+        <v>89.14</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="J18" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="K18" t="n">
-        <v>4.17</v>
+        <v>4.14</v>
       </c>
       <c r="L18" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M18" t="n">
-        <v>35.17</v>
+        <v>37.86</v>
       </c>
       <c r="N18" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="P18" t="n">
-        <v>16.83</v>
+        <v>15.43</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.17</v>
+        <v>15</v>
       </c>
       <c r="R18" t="n">
-        <v>6.5</v>
+        <v>7</v>
       </c>
       <c r="S18" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="T18" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="U18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>55.5</v>
+        <v>55.43</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.83</v>
+        <v>11.71</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.33</v>
+        <v>7.57</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.5</v>
+        <v>4.14</v>
       </c>
       <c r="AC18" t="n">
-        <v>19.33</v>
+        <v>21.14</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.38</v>
+        <v>1.31</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7974,70 +7978,70 @@
         <v>3.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.17</v>
+        <v>9.23</v>
       </c>
       <c r="BI18" t="n">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="BL18" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.25</v>
+        <v>4.31</v>
       </c>
       <c r="BQ18" t="n">
         <v>4.92</v>
       </c>
       <c r="BR18" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BS18" t="n">
-        <v>91.67</v>
+        <v>84.62</v>
       </c>
       <c r="BT18" t="n">
-        <v>75</v>
+        <v>69.23</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BV18" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>83.33</v>
+        <v>76.92</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.44</v>
+        <v>2.57</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.67</v>
+        <v>2.76</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.51</v>
+        <v>3.49</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.57</v>
+        <v>3.54</v>
       </c>
       <c r="CC18" t="n">
         <v>3.3</v>
@@ -8046,43 +8050,43 @@
         <v>3.41</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.08</v>
+        <v>3.04</v>
       </c>
       <c r="CH18" t="n">
         <v>1.45</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL18" t="n">
         <v>1.87</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="CN18" t="n">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
@@ -8097,10 +8101,10 @@
         <v>1.47</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.29</v>
+        <v>2.27</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CX18" t="n">
         <v>1.51</v>
@@ -8115,13 +8119,13 @@
         <v>1.97</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.02</v>
+        <v>3.07</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
@@ -8130,40 +8134,40 @@
         <v>1.92</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>86.75</v>
+        <v>88.15000000000001</v>
       </c>
       <c r="DI18" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.17</v>
+        <v>4.15</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DM18" t="n">
-        <v>32.42</v>
+        <v>34.08</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.92</v>
+        <v>14.31</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15</v>
+        <v>15.38</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.08</v>
+        <v>7.31</v>
       </c>
       <c r="DS18" t="n">
         <v>0.08</v>
@@ -8175,28 +8179,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>59.25</v>
+        <v>58.92</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.16</v>
+        <v>11.61</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.92</v>
+        <v>7.54</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.25</v>
+        <v>4.08</v>
       </c>
       <c r="EA18" t="n">
-        <v>19.5</v>
+        <v>20.46</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="EC18" t="n">
-        <v>3.08</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="19">
@@ -8206,13 +8210,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C19" t="n">
         <v>6</v>
       </c>
       <c r="D19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E19" t="n">
         <v>0.33</v>
@@ -8296,127 +8300,127 @@
         <v>2.83</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG19" t="n">
         <v>2</v>
       </c>
       <c r="AH19" t="n">
-        <v>2</v>
+        <v>2.29</v>
       </c>
       <c r="AI19" t="n">
-        <v>87.83</v>
+        <v>103.57</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK19" t="n">
-        <v>3</v>
+        <v>3.29</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.5</v>
+        <v>4.71</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.17</v>
+        <v>0.43</v>
       </c>
       <c r="AN19" t="n">
-        <v>41.17</v>
+        <v>46.43</v>
       </c>
       <c r="AO19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>15.29</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>10.57</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>4.86</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>37.86</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>3.29</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BN19" t="n">
         <v>1</v>
       </c>
-      <c r="AP19" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>11.17</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>36.67</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>8.17</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>22.67</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>3</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>10.67</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1.08</v>
-      </c>
       <c r="BO19" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BP19" t="n">
         <v>4.92</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.67</v>
+        <v>5.62</v>
       </c>
       <c r="BR19" t="n">
-        <v>100</v>
+        <v>92.31</v>
       </c>
       <c r="BS19" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BT19" t="n">
-        <v>41.67</v>
+        <v>38.46</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8428,7 +8432,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>33.33</v>
+        <v>30.77</v>
       </c>
       <c r="BY19" t="n">
         <v>2.35</v>
@@ -8437,55 +8441,55 @@
         <v>2.35</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.48</v>
+        <v>3.46</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.6</v>
+        <v>3.57</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.99</v>
+        <v>2.9</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.14</v>
+        <v>3.1</v>
       </c>
       <c r="CH19" t="n">
         <v>1.46</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.74</v>
+        <v>2.79</v>
       </c>
       <c r="CR19" t="n">
         <v>1.36</v>
@@ -8500,106 +8504,106 @@
         <v>1.5</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.57</v>
+        <v>2.54</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.13</v>
+        <v>2.11</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.66</v>
+        <v>2.77</v>
       </c>
       <c r="DH19" t="n">
-        <v>96.83</v>
+        <v>104.61</v>
       </c>
       <c r="DI19" t="n">
         <v>0.16</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3</v>
+        <v>3.16</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.34</v>
+        <v>0.46</v>
       </c>
       <c r="DM19" t="n">
-        <v>46.5</v>
+        <v>48.92</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.84</v>
+        <v>1</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.16</v>
+        <v>14.62</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.5</v>
+        <v>11.15</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.25</v>
+        <v>5.16</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>40.67</v>
+        <v>41</v>
       </c>
       <c r="DW19" t="n">
         <v>0.08</v>
       </c>
       <c r="DX19" t="n">
-        <v>13</v>
+        <v>13.08</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.58</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.42</v>
+        <v>4.54</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.17</v>
+        <v>20.62</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C2" t="n">
         <v>7</v>
       </c>
       <c r="D2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
@@ -1472,115 +1472,115 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.2</v>
+        <v>4.83</v>
       </c>
       <c r="AI2" t="n">
-        <v>100.2</v>
+        <v>99.17</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="AL2" t="n">
-        <v>6</v>
+        <v>7.17</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.6</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>53</v>
+        <v>55.83</v>
       </c>
       <c r="AO2" t="n">
         <v>1</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.8</v>
+        <v>2.33</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.8</v>
+        <v>12.67</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.4</v>
+        <v>14.83</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AT2" t="n">
         <v>2</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.4</v>
+        <v>0.33</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>50.2</v>
+        <v>49</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.2</v>
+        <v>0.17</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.6</v>
+        <v>13.17</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.6</v>
+        <v>3.17</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.4</v>
+        <v>23.33</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.6</v>
+        <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.58</v>
+        <v>11.23</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.58</v>
+        <v>3.46</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="BN2" t="n">
         <v>2.08</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.42</v>
+        <v>4.23</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.08</v>
+        <v>6.92</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
@@ -1589,19 +1589,19 @@
         <v>100</v>
       </c>
       <c r="BT2" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BU2" t="n">
-        <v>50</v>
+        <v>46.15</v>
       </c>
       <c r="BV2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BW2" t="n">
-        <v>16.67</v>
+        <v>15.38</v>
       </c>
       <c r="BX2" t="n">
-        <v>66.67</v>
+        <v>61.54</v>
       </c>
       <c r="BY2" t="n">
         <v>2.21</v>
@@ -1610,16 +1610,16 @@
         <v>2.33</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CB2" t="n">
         <v>3.75</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.3</v>
+        <v>3.23</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.66</v>
+        <v>3.55</v>
       </c>
       <c r="CE2" t="n">
         <v>1.28</v>
@@ -1628,19 +1628,19 @@
         <v>2.37</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.53</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL2" t="n">
         <v>1.76</v>
@@ -1673,7 +1673,7 @@
         <v>1.58</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CW2" t="n">
         <v>1.55</v>
@@ -1694,85 +1694,85 @@
         <v>1.19</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DE2" t="n">
         <v>0</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.17</v>
+        <v>3.92</v>
       </c>
       <c r="DH2" t="n">
-        <v>102</v>
+        <v>101.39</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="DK2" t="n">
-        <v>5.42</v>
+        <v>6</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM2" t="n">
-        <v>47.5</v>
+        <v>49.23</v>
       </c>
       <c r="DN2" t="n">
         <v>1.08</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.5</v>
+        <v>12.47</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14.66</v>
+        <v>14.46</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.42</v>
+        <v>8.08</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.25</v>
+        <v>51.54</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.17</v>
+        <v>13.39</v>
       </c>
       <c r="DY2" t="n">
-        <v>8.92</v>
+        <v>9.390000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.75</v>
+        <v>23.69</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
     </row>
     <row r="3">
@@ -1797,7 +1797,7 @@
         <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>1.83</v>
+        <v>3.17</v>
       </c>
       <c r="H3" t="n">
         <v>109.33</v>
@@ -1812,7 +1812,7 @@
         <v>7</v>
       </c>
       <c r="L3" t="n">
-        <v>0.17</v>
+        <v>0.83</v>
       </c>
       <c r="M3" t="n">
         <v>64</v>
@@ -1821,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.67</v>
+        <v>3.83</v>
       </c>
       <c r="P3" t="n">
         <v>15.5</v>
@@ -1980,10 +1980,10 @@
         <v>1.08</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.31</v>
+        <v>6.15</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.08</v>
+        <v>7</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
@@ -2105,7 +2105,7 @@
         <v>2.54</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.77</v>
+        <v>3.39</v>
       </c>
       <c r="DH3" t="n">
         <v>94.15000000000001</v>
@@ -2120,7 +2120,7 @@
         <v>6.84</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.39</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM3" t="n">
         <v>52.54</v>
@@ -2129,7 +2129,7 @@
         <v>1.23</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.92</v>
+        <v>3.46</v>
       </c>
       <c r="DP3" t="n">
         <v>13.54</v>
@@ -2181,62 +2181,62 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D4" t="n">
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F4" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="H4" t="n">
-        <v>91.33</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J4" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="K4" t="n">
         <v>5</v>
       </c>
       <c r="L4" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="M4" t="n">
-        <v>54</v>
+        <v>51.14</v>
       </c>
       <c r="N4" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O4" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="P4" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>13</v>
+      </c>
+      <c r="R4" t="n">
+        <v>8.289999999999999</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="T4" t="n">
         <v>2</v>
       </c>
-      <c r="P4" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>13.67</v>
-      </c>
-      <c r="R4" t="n">
-        <v>9</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="T4" t="n">
-        <v>1.67</v>
-      </c>
       <c r="U4" t="n">
         <v>0</v>
       </c>
@@ -2247,28 +2247,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.5</v>
+        <v>49.86</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.17</v>
+        <v>14.71</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AC4" t="n">
-        <v>19.33</v>
+        <v>19.29</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="AE4" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="AF4" t="n">
         <v>0.17</v>
@@ -2352,70 +2352,70 @@
         <v>1.17</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.75</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.5</v>
+        <v>2.77</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.5</v>
+        <v>1.69</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5</v>
+        <v>4.77</v>
       </c>
       <c r="BR4" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU4" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV4" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW4" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.64</v>
+        <v>3.71</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.78</v>
+        <v>3.85</v>
       </c>
       <c r="CC4" t="n">
         <v>2.76</v>
@@ -2427,13 +2427,13 @@
         <v>1.29</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.27</v>
+        <v>3.32</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CI4" t="n">
         <v>2.36</v>
@@ -2445,10 +2445,10 @@
         <v>1.41</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CN4" t="n">
         <v>2.08</v>
@@ -2457,91 +2457,91 @@
         <v>1.17</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="CT4" t="n">
         <v>3.3</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW4" t="n">
         <v>1.57</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DB4" t="n">
         <v>1.2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.63</v>
+        <v>2.6</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.66</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.58</v>
+        <v>4.62</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="DM4" t="n">
-        <v>44.66</v>
+        <v>43.84</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.34</v>
+        <v>2.38</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.17</v>
+        <v>13.15</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.75</v>
+        <v>12.46</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.58</v>
+        <v>9.16</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2553,28 +2553,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.84</v>
+        <v>50.46</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.84</v>
+        <v>14.15</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.58</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.25</v>
+        <v>5.54</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.92</v>
+        <v>18.93</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
     </row>
     <row r="5">
@@ -2680,7 +2680,7 @@
         <v>1.29</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.57</v>
+        <v>3.29</v>
       </c>
       <c r="AI5" t="n">
         <v>95.56999999999999</v>
@@ -2695,7 +2695,7 @@
         <v>5.71</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>0.29</v>
       </c>
       <c r="AN5" t="n">
         <v>51.14</v>
@@ -2704,7 +2704,7 @@
         <v>0.86</v>
       </c>
       <c r="AP5" t="n">
-        <v>1.71</v>
+        <v>2.43</v>
       </c>
       <c r="AQ5" t="n">
         <v>12.14</v>
@@ -2782,10 +2782,10 @@
         <v>2.08</v>
       </c>
       <c r="BP5" t="n">
-        <v>3.77</v>
+        <v>4.62</v>
       </c>
       <c r="BQ5" t="n">
-        <v>5.69</v>
+        <v>6.62</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
@@ -2911,7 +2911,7 @@
         <v>1.47</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.77</v>
+        <v>3.16</v>
       </c>
       <c r="DH5" t="n">
         <v>92.77</v>
@@ -2926,7 +2926,7 @@
         <v>5.38</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.15</v>
+        <v>0.31</v>
       </c>
       <c r="DM5" t="n">
         <v>49.15</v>
@@ -2935,7 +2935,7 @@
         <v>0.62</v>
       </c>
       <c r="DO5" t="n">
-        <v>1.84</v>
+        <v>2.23</v>
       </c>
       <c r="DP5" t="n">
         <v>11.69</v>
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" t="n">
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E7" t="n">
         <v>0.17</v>
@@ -3480,52 +3480,52 @@
         <v>2.17</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.33</v>
+        <v>2.14</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.83</v>
+        <v>1.43</v>
       </c>
       <c r="AI7" t="n">
-        <v>94.17</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AK7" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.17</v>
+        <v>6.57</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.83</v>
+        <v>0.57</v>
       </c>
       <c r="AN7" t="n">
-        <v>45</v>
+        <v>45.14</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP7" t="n">
-        <v>4.17</v>
+        <v>3.43</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.5</v>
+        <v>10.86</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.67</v>
+        <v>15.57</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.17</v>
+        <v>6.86</v>
       </c>
       <c r="AT7" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3537,82 +3537,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>56.83</v>
+        <v>55.43</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA7" t="n">
-        <v>13.83</v>
+        <v>15.57</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.67</v>
+        <v>10.86</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.17</v>
+        <v>4.71</v>
       </c>
       <c r="BD7" t="n">
-        <v>22.67</v>
+        <v>23</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.49</v>
+        <v>1.64</v>
       </c>
       <c r="BF7" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.58</v>
+        <v>10.77</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.58</v>
+        <v>1.77</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.25</v>
+        <v>4.77</v>
       </c>
       <c r="BQ7" t="n">
-        <v>5.25</v>
+        <v>4.77</v>
       </c>
       <c r="BR7" t="n">
         <v>100</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU7" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BV7" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX7" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BY7" t="n">
         <v>2</v>
@@ -3621,16 +3621,16 @@
         <v>2.01</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="CE7" t="n">
         <v>1.3</v>
@@ -3639,7 +3639,7 @@
         <v>2.47</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.34</v>
+        <v>3.32</v>
       </c>
       <c r="CH7" t="n">
         <v>1.53</v>
@@ -3648,19 +3648,19 @@
         <v>2.37</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CO7" t="n">
         <v>1.19</v>
@@ -3675,19 +3675,19 @@
         <v>1.37</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.23</v>
+        <v>3.25</v>
       </c>
       <c r="CU7" t="n">
         <v>1.55</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
@@ -3699,58 +3699,58 @@
         <v>2.61</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.5</v>
+        <v>2.23</v>
       </c>
       <c r="DH7" t="n">
-        <v>93.42</v>
+        <v>94.69</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="DK7" t="n">
-        <v>5.84</v>
+        <v>6.08</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.42</v>
+        <v>0.31</v>
       </c>
       <c r="DM7" t="n">
-        <v>49.58</v>
+        <v>49.31</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.66</v>
+        <v>0.61</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.25</v>
+        <v>2.92</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.92</v>
+        <v>12</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.75</v>
+        <v>14.77</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.75</v>
+        <v>6.62</v>
       </c>
       <c r="DS7" t="n">
         <v>0.08</v>
@@ -3762,28 +3762,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55.66</v>
+        <v>55</v>
       </c>
       <c r="DW7" t="n">
         <v>0.08</v>
       </c>
       <c r="DX7" t="n">
-        <v>14.75</v>
+        <v>15.62</v>
       </c>
       <c r="DY7" t="n">
-        <v>9.75</v>
+        <v>10.38</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5</v>
+        <v>5.23</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.5</v>
+        <v>22.69</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
     </row>
     <row r="8">
@@ -3865,19 +3865,19 @@
         <v>0</v>
       </c>
       <c r="Z8" t="n">
-        <v>11.86</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
         <v>8.710000000000001</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.14</v>
+        <v>3.29</v>
       </c>
       <c r="AC8" t="n">
         <v>21.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
         <v>2.71</v>
@@ -4021,7 +4021,7 @@
         <v>2.28</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CA8" t="n">
         <v>3.64</v>
@@ -4078,13 +4078,13 @@
         <v>1.38</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CT8" t="n">
         <v>3.15</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV8" t="n">
         <v>2.5</v>
@@ -4096,13 +4096,13 @@
         <v>1.48</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.52</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB8" t="n">
         <v>1.2</v>
@@ -4111,7 +4111,7 @@
         <v>1.67</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="DE8" t="n">
         <v>0.08</v>
@@ -4171,19 +4171,19 @@
         <v>0.08</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.31</v>
+        <v>12.38</v>
       </c>
       <c r="DY8" t="n">
         <v>8.77</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.54</v>
+        <v>3.62</v>
       </c>
       <c r="EA8" t="n">
         <v>20.69</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC8" t="n">
         <v>2.61</v>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C9" t="n">
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E9" t="n">
         <v>0.33</v>
@@ -4289,136 +4289,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AH9" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>67.70999999999999</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>35.43</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11.86</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="AT9" t="n">
         <v>3</v>
       </c>
-      <c r="AI9" t="n">
-        <v>74.17</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>36.17</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>11.83</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.83</v>
-      </c>
       <c r="AU9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.83</v>
+        <v>46.14</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.5</v>
+        <v>13.57</v>
       </c>
       <c r="BB9" t="n">
-        <v>8.17</v>
+        <v>7.86</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.33</v>
+        <v>5.71</v>
       </c>
       <c r="BD9" t="n">
-        <v>24.83</v>
+        <v>24.43</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="BG9" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.58</v>
+        <v>10.31</v>
       </c>
       <c r="BI9" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.5</v>
+        <v>6.15</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BT9" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BU9" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BV9" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BW9" t="n">
-        <v>16.67</v>
+        <v>23.08</v>
       </c>
       <c r="BX9" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY9" t="n">
         <v>2.58</v>
@@ -4427,46 +4427,46 @@
         <v>3.1</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.77</v>
+        <v>3.82</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.97</v>
+        <v>4.02</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.14</v>
+        <v>4.29</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.13</v>
+        <v>5.23</v>
       </c>
       <c r="CE9" t="n">
         <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.41</v>
+        <v>3.45</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CI9" t="n">
         <v>2.41</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="CO9" t="n">
         <v>1.16</v>
@@ -4475,121 +4475,121 @@
         <v>1.59</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CT9" t="n">
         <v>3.28</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CW9" t="n">
         <v>1.56</v>
       </c>
       <c r="CX9" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="DB9" t="n">
         <v>1.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF9" t="n">
         <v>1</v>
       </c>
       <c r="DG9" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="DH9" t="n">
-        <v>82</v>
+        <v>77.92</v>
       </c>
       <c r="DI9" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.92</v>
+        <v>4.69</v>
       </c>
       <c r="DL9" t="n">
         <v>0.16</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.58</v>
+        <v>35.23</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.16</v>
+        <v>1.23</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.84</v>
+        <v>11.61</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.25</v>
+        <v>13.16</v>
       </c>
       <c r="DR9" t="n">
-        <v>8</v>
+        <v>7.84</v>
       </c>
       <c r="DS9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DT9" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.25</v>
+        <v>45</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.25</v>
+        <v>12.38</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.75</v>
+        <v>7.62</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.5</v>
+        <v>4.77</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.83</v>
+        <v>22.77</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="10">
@@ -4833,13 +4833,13 @@
         <v>3.57</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.71</v>
+        <v>3.72</v>
       </c>
       <c r="CC10" t="n">
         <v>2.48</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="CE10" t="n">
         <v>1.31</v>
@@ -4881,22 +4881,22 @@
         <v>2.61</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX10" t="inlineStr"/>
       <c r="CY10" t="n">
@@ -4910,10 +4910,10 @@
         <v>1.21</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="DE10" t="n">
         <v>0.08</v>
@@ -5401,13 +5401,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C12" t="n">
         <v>6</v>
       </c>
       <c r="D12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5491,139 +5491,139 @@
         <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AI12" t="n">
-        <v>83.67</v>
+        <v>82.29000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.33</v>
+        <v>3.57</v>
       </c>
       <c r="AL12" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>39.67</v>
+        <v>36.43</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.17</v>
+        <v>15.29</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.33</v>
+        <v>13.29</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.5</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>1.43</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AW12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.83</v>
+        <v>48.86</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BA12" t="n">
-        <v>12.33</v>
+        <v>11.71</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.67</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.67</v>
+        <v>3.43</v>
       </c>
       <c r="BD12" t="n">
-        <v>20</v>
+        <v>19.86</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.33</v>
+        <v>3.43</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.75</v>
+        <v>10</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.08</v>
+        <v>2.31</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.42</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="BO12" t="n">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="BP12" t="n">
-        <v>3.92</v>
+        <v>4.31</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.83</v>
+        <v>5.69</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BU12" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BV12" t="n">
-        <v>0</v>
+        <v>7.69</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY12" t="n">
         <v>2.14</v>
@@ -5635,40 +5635,40 @@
         <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CC12" t="n">
         <v>2.72</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CE12" t="n">
         <v>1.31</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CH12" t="n">
         <v>1.5</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL12" t="n">
         <v>1.67</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CN12" t="n">
         <v>2.22</v>
@@ -5677,10 +5677,10 @@
         <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5689,13 +5689,13 @@
         <v>2.55</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CU12" t="n">
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CW12" t="n">
         <v>1.59</v>
@@ -5704,13 +5704,13 @@
         <v>1.5</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.49</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DB12" t="n">
         <v>1.22</v>
@@ -5725,76 +5725,76 @@
         <v>0.08</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.75</v>
+        <v>1.84</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.92</v>
+        <v>85</v>
       </c>
       <c r="DI12" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.5</v>
+        <v>2.69</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="DM12" t="n">
-        <v>41.08</v>
+        <v>39.23</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.92</v>
+        <v>14.08</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.33</v>
+        <v>14.23</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.42</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS12" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DT12" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.92</v>
+        <v>50.77</v>
       </c>
       <c r="DW12" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.58</v>
+        <v>13.15</v>
       </c>
       <c r="DY12" t="n">
-        <v>9.08</v>
+        <v>8.85</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.84</v>
+        <v>19.77</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.47</v>
+        <v>1.42</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="13">
@@ -5804,94 +5804,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D13" t="n">
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="F13" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="G13" t="n">
-        <v>2.67</v>
+        <v>2.86</v>
       </c>
       <c r="H13" t="n">
-        <v>103.17</v>
+        <v>107.57</v>
       </c>
       <c r="I13" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J13" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="K13" t="n">
-        <v>5.67</v>
+        <v>6.29</v>
       </c>
       <c r="L13" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M13" t="n">
-        <v>48.5</v>
+        <v>52</v>
       </c>
       <c r="N13" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>1.5</v>
+        <v>2.14</v>
       </c>
       <c r="P13" t="n">
-        <v>11.83</v>
+        <v>12.14</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.33</v>
+        <v>13.71</v>
       </c>
       <c r="R13" t="n">
-        <v>8</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" t="n">
+        <v>51.71</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>17.57</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>10.29</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>7.29</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>22.14</v>
+      </c>
+      <c r="AD13" t="n">
         <v>2</v>
       </c>
-      <c r="U13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="V13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="W13" t="n">
-        <v>0</v>
-      </c>
-      <c r="X13" t="n">
-        <v>49.83</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>15.83</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>8.83</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>21.83</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.84</v>
-      </c>
       <c r="AE13" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5975,34 +5975,34 @@
         <v>2.83</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.25</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.5</v>
+        <v>0.77</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.83</v>
+        <v>0.77</v>
       </c>
       <c r="BN13" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BO13" t="n">
-        <v>0.83</v>
+        <v>1.15</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.17</v>
+        <v>4.54</v>
       </c>
       <c r="BQ13" t="n">
         <v>4</v>
@@ -6011,31 +6011,31 @@
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BU13" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>30.77</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.33</v>
+        <v>61.54</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB13" t="n">
         <v>3.65</v>
@@ -6050,40 +6050,40 @@
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.41</v>
+        <v>2.44</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CH13" t="n">
         <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL13" t="n">
         <v>1.72</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="CN13" t="n">
         <v>2.2</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP13" t="n">
         <v>1.68</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="CR13" t="n">
         <v>1.36</v>
@@ -6092,7 +6092,7 @@
         <v>2.57</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CU13" t="n">
         <v>1.54</v>
@@ -6113,7 +6113,7 @@
         <v>2.57</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DB13" t="n">
         <v>1.21</v>
@@ -6125,79 +6125,79 @@
         <v>2.69</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.16</v>
+        <v>0.23</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="DH13" t="n">
-        <v>100.25</v>
+        <v>102.84</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.92</v>
+        <v>2.85</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.92</v>
+        <v>5.31</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.92</v>
+        <v>46.15</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="DO13" t="n">
-        <v>1.92</v>
+        <v>2.23</v>
       </c>
       <c r="DP13" t="n">
-        <v>12</v>
+        <v>12.15</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.58</v>
+        <v>13.77</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.25</v>
+        <v>8.31</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.08</v>
+        <v>48.3</v>
       </c>
       <c r="DW13" t="n">
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.92</v>
+        <v>15</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.33</v>
+        <v>9.15</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.58</v>
+        <v>5.85</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.42</v>
+        <v>21.61</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.59</v>
+        <v>1.7</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="14">
@@ -6207,58 +6207,58 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D14" t="n">
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F14" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>2.67</v>
+        <v>2.14</v>
       </c>
       <c r="H14" t="n">
-        <v>85</v>
+        <v>82.70999999999999</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="K14" t="n">
-        <v>5.67</v>
+        <v>5.43</v>
       </c>
       <c r="L14" t="n">
-        <v>1</v>
+        <v>0.71</v>
       </c>
       <c r="M14" t="n">
-        <v>48</v>
+        <v>45.14</v>
       </c>
       <c r="N14" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="O14" t="n">
-        <v>3</v>
+        <v>2.43</v>
       </c>
       <c r="P14" t="n">
-        <v>14.83</v>
+        <v>14.86</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.5</v>
+        <v>13.43</v>
       </c>
       <c r="R14" t="n">
-        <v>7.5</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="S14" t="n">
-        <v>1.17</v>
+        <v>1.43</v>
       </c>
       <c r="T14" t="n">
         <v>2</v>
@@ -6273,28 +6273,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>48.83</v>
+        <v>49.43</v>
       </c>
       <c r="Y14" t="n">
         <v>0</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.5</v>
+        <v>12.29</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.67</v>
+        <v>6.71</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.83</v>
+        <v>5.57</v>
       </c>
       <c r="AC14" t="n">
-        <v>17.17</v>
+        <v>17</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.54</v>
+        <v>1.49</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.33</v>
+        <v>3.29</v>
       </c>
       <c r="AF14" t="n">
         <v>0.17</v>
@@ -6378,70 +6378,70 @@
         <v>2.17</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.5</v>
+        <v>10.69</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.08</v>
+        <v>3.23</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.58</v>
+        <v>0.62</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.58</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BP14" t="n">
-        <v>5.08</v>
+        <v>4.62</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.42</v>
+        <v>4.92</v>
       </c>
       <c r="BR14" t="n">
-        <v>83.33</v>
+        <v>84.62</v>
       </c>
       <c r="BS14" t="n">
-        <v>75</v>
+        <v>76.92</v>
       </c>
       <c r="BT14" t="n">
-        <v>66.67</v>
+        <v>69.23</v>
       </c>
       <c r="BU14" t="n">
-        <v>41.67</v>
+        <v>46.15</v>
       </c>
       <c r="BV14" t="n">
-        <v>33.33</v>
+        <v>38.46</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.33</v>
+        <v>7.69</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>53.85</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.19</v>
+        <v>2.33</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="CA14" t="n">
         <v>3.61</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CC14" t="n">
         <v>3.2</v>
@@ -6453,10 +6453,10 @@
         <v>1.29</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CH14" t="n">
         <v>1.55</v>
@@ -6492,78 +6492,78 @@
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="CT14" t="n">
         <v>3.31</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DB14" t="n">
         <v>1.2</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.83</v>
+        <v>2.54</v>
       </c>
       <c r="DH14" t="n">
-        <v>89.25</v>
+        <v>87.69</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.67</v>
+        <v>5.54</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.75</v>
+        <v>0.61</v>
       </c>
       <c r="DM14" t="n">
-        <v>44.42</v>
+        <v>43.15</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.83</v>
+        <v>2.54</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.83</v>
+        <v>13.92</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.42</v>
+        <v>11.54</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.08</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6575,28 +6575,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.25</v>
+        <v>49.54</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.42</v>
+        <v>13.23</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.42</v>
+        <v>17.31</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
     </row>
     <row r="15">
@@ -6840,13 +6840,13 @@
         <v>3.67</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC15" t="n">
         <v>2.96</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.2</v>
+        <v>3.24</v>
       </c>
       <c r="CE15" t="n">
         <v>1.26</v>
@@ -6889,14 +6889,14 @@
       </c>
       <c r="CR15" t="inlineStr"/>
       <c r="CS15" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="n">
         <v>1.63</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CW15" t="n">
         <v>1.5</v>
@@ -6905,13 +6905,13 @@
         <v>1.46</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.55</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DB15" t="n">
         <v>1.17</v>
@@ -7005,10 +7005,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" t="n">
         <v>6</v>
@@ -7017,82 +7017,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="G16" t="n">
-        <v>2.33</v>
+        <v>2.57</v>
       </c>
       <c r="H16" t="n">
-        <v>96.5</v>
+        <v>97.29000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="K16" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M16" t="n">
-        <v>45.67</v>
+        <v>43.43</v>
       </c>
       <c r="N16" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="O16" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="P16" t="n">
-        <v>10.83</v>
+        <v>11</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.67</v>
+        <v>14.14</v>
       </c>
       <c r="R16" t="n">
-        <v>9</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="S16" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="T16" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.5</v>
+        <v>51.43</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.83</v>
+        <v>12.57</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.67</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.5</v>
+        <v>19.86</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AF16" t="n">
         <v>0.17</v>
@@ -7176,70 +7176,70 @@
         <v>3</v>
       </c>
       <c r="BG16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>10.38</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BO16" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="BP16" t="n">
+        <v>4.62</v>
+      </c>
+      <c r="BQ16" t="n">
+        <v>5.77</v>
+      </c>
+      <c r="BR16" t="n">
+        <v>92.31</v>
+      </c>
+      <c r="BS16" t="n">
+        <v>76.92</v>
+      </c>
+      <c r="BT16" t="n">
+        <v>53.85</v>
+      </c>
+      <c r="BU16" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="BV16" t="n">
+        <v>7.69</v>
+      </c>
+      <c r="BW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX16" t="n">
+        <v>61.54</v>
+      </c>
+      <c r="BY16" t="n">
         <v>2.42</v>
       </c>
-      <c r="BH16" t="n">
-        <v>9.67</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BP16" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="BQ16" t="n">
-        <v>4.83</v>
-      </c>
-      <c r="BR16" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="BS16" t="n">
-        <v>75</v>
-      </c>
-      <c r="BT16" t="n">
-        <v>58.33</v>
-      </c>
-      <c r="BU16" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="BV16" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="BW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX16" t="n">
-        <v>66.67</v>
-      </c>
-      <c r="BY16" t="n">
-        <v>2.49</v>
-      </c>
       <c r="BZ16" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.7</v>
+        <v>3.71</v>
       </c>
       <c r="CC16" t="n">
         <v>2.97</v>
@@ -7251,28 +7251,28 @@
         <v>1.32</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CG16" t="n">
         <v>3.24</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK16" t="n">
         <v>1.35</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CN16" t="n">
         <v>2.22</v>
@@ -7281,28 +7281,28 @@
         <v>1.2</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX16" t="inlineStr"/>
       <c r="CY16" t="n">
@@ -7310,16 +7310,16 @@
       </c>
       <c r="CZ16" t="inlineStr"/>
       <c r="DA16" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DB16" t="n">
         <v>1.21</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="DE16" t="n">
         <v>0.08</v>
@@ -7328,73 +7328,73 @@
         <v>1.92</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>95.08</v>
+        <v>95.62</v>
       </c>
       <c r="DI16" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.42</v>
+        <v>5.46</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="DM16" t="n">
-        <v>48.08</v>
+        <v>46.69</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.66</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="DP16" t="n">
+        <v>12.92</v>
+      </c>
+      <c r="DQ16" t="n">
+        <v>14.08</v>
+      </c>
+      <c r="DR16" t="n">
+        <v>7.84</v>
+      </c>
+      <c r="DS16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DT16" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DU16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV16" t="n">
+        <v>50.23</v>
+      </c>
+      <c r="DW16" t="n">
+        <v>0</v>
+      </c>
+      <c r="DX16" t="n">
         <v>13</v>
       </c>
-      <c r="DQ16" t="n">
-        <v>14.34</v>
-      </c>
-      <c r="DR16" t="n">
-        <v>7.92</v>
-      </c>
-      <c r="DS16" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DT16" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DU16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV16" t="n">
-        <v>49.66</v>
-      </c>
-      <c r="DW16" t="n">
-        <v>0</v>
-      </c>
-      <c r="DX16" t="n">
-        <v>13.16</v>
-      </c>
       <c r="DY16" t="n">
-        <v>8.5</v>
+        <v>8.23</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.67</v>
+        <v>4.77</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.42</v>
+        <v>20.08</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="17">
@@ -7446,7 +7446,7 @@
         <v>2.86</v>
       </c>
       <c r="P17" t="n">
-        <v>12.29</v>
+        <v>12.43</v>
       </c>
       <c r="Q17" t="n">
         <v>10.86</v>
@@ -7638,7 +7638,7 @@
         <v>3.71</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.84</v>
+        <v>3.85</v>
       </c>
       <c r="CC17" t="n">
         <v>2.11</v>
@@ -7689,19 +7689,19 @@
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CX17" t="n">
         <v>1.46</v>
@@ -7719,10 +7719,10 @@
         <v>1.21</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="DE17" t="n">
         <v>0.15</v>
@@ -7758,7 +7758,7 @@
         <v>2.46</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.54</v>
+        <v>12.61</v>
       </c>
       <c r="DQ17" t="n">
         <v>11</v>
@@ -8041,7 +8041,7 @@
         <v>3.49</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.54</v>
+        <v>3.55</v>
       </c>
       <c r="CC18" t="n">
         <v>3.3</v>
@@ -8107,16 +8107,16 @@
         <v>1.68</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="DB18" t="n">
         <v>1.27</v>
@@ -8444,7 +8444,7 @@
         <v>3.46</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="CC19" t="n">
         <v>2.78</v>
@@ -8510,16 +8510,16 @@
         <v>1.65</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.54</v>
+        <v>2.46</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.11</v>
+        <v>2.08</v>
       </c>
       <c r="DB19" t="n">
         <v>1.25</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -2247,16 +2247,16 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.86</v>
+        <v>50</v>
       </c>
       <c r="Y4" t="n">
         <v>0.14</v>
       </c>
       <c r="Z4" t="n">
-        <v>14.71</v>
+        <v>14.57</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.710000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="AB4" t="n">
         <v>6</v>
@@ -2265,7 +2265,7 @@
         <v>19.29</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE4" t="n">
         <v>2.14</v>
@@ -2553,16 +2553,16 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.46</v>
+        <v>50.54</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.15</v>
+        <v>14.08</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.609999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ4" t="n">
         <v>5.54</v>
@@ -2571,7 +2571,7 @@
         <v>18.93</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="EC4" t="n">
         <v>1.69</v>
@@ -3868,16 +3868,16 @@
         <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.710000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.29</v>
+        <v>3.43</v>
       </c>
       <c r="AC8" t="n">
         <v>21.71</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE8" t="n">
         <v>2.71</v>
@@ -4174,16 +4174,16 @@
         <v>12.38</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.77</v>
+        <v>8.69</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.62</v>
+        <v>3.69</v>
       </c>
       <c r="EA8" t="n">
         <v>20.69</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
         <v>2.61</v>
@@ -4343,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46.14</v>
+        <v>46</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45</v>
+        <v>44.92</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
@@ -4725,7 +4725,7 @@
         <v>13.29</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.86</v>
+        <v>14</v>
       </c>
       <c r="AS10" t="n">
         <v>6.57</v>
@@ -4952,7 +4952,7 @@
         <v>13.85</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14</v>
+        <v>14.08</v>
       </c>
       <c r="DR10" t="n">
         <v>6.69</v>
@@ -6759,10 +6759,10 @@
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>16.43</v>
+        <v>16.57</v>
       </c>
       <c r="BB15" t="n">
-        <v>11</v>
+        <v>11.14</v>
       </c>
       <c r="BC15" t="n">
         <v>5.43</v>
@@ -6771,7 +6771,7 @@
         <v>18.71</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="BF15" t="n">
         <v>3</v>
@@ -6980,10 +6980,10 @@
         <v>0.08</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.69</v>
+        <v>15.77</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.85</v>
+        <v>10.92</v>
       </c>
       <c r="DZ15" t="n">
         <v>4.85</v>
@@ -6992,7 +6992,7 @@
         <v>19.69</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="EC15" t="n">
         <v>2.85</v>
@@ -7849,7 +7849,7 @@
         <v>2.57</v>
       </c>
       <c r="P18" t="n">
-        <v>15.43</v>
+        <v>15.57</v>
       </c>
       <c r="Q18" t="n">
         <v>15</v>
@@ -8161,7 +8161,7 @@
         <v>2.15</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.31</v>
+        <v>14.38</v>
       </c>
       <c r="DQ18" t="n">
         <v>15.38</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D10" t="n">
         <v>7</v>
@@ -4611,82 +4611,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="G10" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="H10" t="n">
-        <v>109</v>
+        <v>109.29</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>6.57</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M10" t="n">
-        <v>62.67</v>
+        <v>60.14</v>
       </c>
       <c r="N10" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O10" t="n">
-        <v>3.17</v>
+        <v>2.86</v>
       </c>
       <c r="P10" t="n">
-        <v>14.5</v>
+        <v>14.14</v>
       </c>
       <c r="Q10" t="n">
-        <v>14.17</v>
+        <v>13.29</v>
       </c>
       <c r="R10" t="n">
-        <v>6.83</v>
+        <v>6.71</v>
       </c>
       <c r="S10" t="n">
-        <v>1.83</v>
+        <v>1.57</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="U10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V10" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>58</v>
+        <v>57.86</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.5</v>
+        <v>17.57</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.83</v>
+        <v>11.71</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.67</v>
+        <v>5.86</v>
       </c>
       <c r="AC10" t="n">
-        <v>21.83</v>
+        <v>20</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AF10" t="n">
         <v>0.14</v>
@@ -4770,70 +4770,70 @@
         <v>2.43</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.92</v>
+        <v>9.57</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.54</v>
+        <v>0.71</v>
       </c>
       <c r="BM10" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.23</v>
+        <v>4.07</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.69</v>
+        <v>5.5</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT10" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.95</v>
+        <v>1.89</v>
       </c>
       <c r="BZ10" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.57</v>
+        <v>3.67</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.72</v>
+        <v>3.82</v>
       </c>
       <c r="CC10" t="n">
         <v>2.48</v>
@@ -4842,19 +4842,19 @@
         <v>2.55</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.24</v>
+        <v>3.28</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.56</v>
@@ -4866,31 +4866,31 @@
         <v>1.67</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.98</v>
+        <v>2.99</v>
       </c>
       <c r="CN10" t="n">
         <v>2.21</v>
       </c>
       <c r="CO10" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="CT10" t="n">
         <v>3.26</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="CV10" t="n">
         <v>2.49</v>
@@ -4900,95 +4900,95 @@
       </c>
       <c r="CX10" t="inlineStr"/>
       <c r="CY10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CZ10" t="inlineStr"/>
       <c r="DA10" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.66</v>
+        <v>2.61</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="DH10" t="n">
-        <v>106.77</v>
+        <v>107.08</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.85</v>
+        <v>5.72</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="DM10" t="n">
-        <v>56.31</v>
+        <v>55.5</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.62</v>
+        <v>2.5</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.85</v>
+        <v>13.72</v>
       </c>
       <c r="DQ10" t="n">
-        <v>14.08</v>
+        <v>13.64</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>57.92</v>
+        <v>57.86</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>15.62</v>
+        <v>15.78</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.84</v>
+        <v>9.92</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.77</v>
+        <v>5.86</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.54</v>
+        <v>19.72</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="11">
@@ -6207,13 +6207,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E14" t="n">
         <v>0.14</v>
@@ -6297,52 +6297,52 @@
         <v>3.29</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH14" t="n">
-        <v>3</v>
+        <v>2.57</v>
       </c>
       <c r="AI14" t="n">
-        <v>93.5</v>
+        <v>89.14</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.67</v>
+        <v>5</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN14" t="n">
-        <v>40.83</v>
+        <v>38.86</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.67</v>
+        <v>2.43</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.83</v>
+        <v>12.14</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.33</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AT14" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6354,82 +6354,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.67</v>
+        <v>48.71</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>14.33</v>
+        <v>13.57</v>
       </c>
       <c r="BB14" t="n">
-        <v>10.33</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>4</v>
+        <v>3.71</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.67</v>
+        <v>17.57</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BF14" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.69</v>
+        <v>10.29</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN14" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.62</v>
+        <v>4.43</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.92</v>
+        <v>4.79</v>
       </c>
       <c r="BR14" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV14" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX14" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
         <v>2.33</v>
@@ -6438,28 +6438,28 @@
         <v>2.52</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.61</v>
+        <v>3.71</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.74</v>
+        <v>3.84</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.27</v>
+        <v>3.76</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.28</v>
+        <v>3.32</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="CI14" t="n">
         <v>2.39</v>
@@ -6474,31 +6474,31 @@
         <v>1.68</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CO14" t="n">
         <v>1.16</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.51</v>
+        <v>2.47</v>
       </c>
       <c r="CT14" t="n">
         <v>3.31</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="CV14" t="n">
         <v>2.53</v>
@@ -6512,58 +6512,58 @@
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="DH14" t="n">
-        <v>87.69</v>
+        <v>85.92</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.54</v>
+        <v>5.21</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DM14" t="n">
-        <v>43.15</v>
+        <v>42</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.54</v>
+        <v>2.43</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.92</v>
+        <v>13.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.54</v>
+        <v>11.57</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6575,28 +6575,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.54</v>
+        <v>49.07</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>13.23</v>
+        <v>12.93</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.380000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.85</v>
+        <v>4.64</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.31</v>
+        <v>17.28</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="15">
@@ -7404,13 +7404,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C17" t="n">
         <v>7</v>
       </c>
       <c r="D17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7494,139 +7494,139 @@
         <v>1.71</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AI17" t="n">
-        <v>99.67</v>
+        <v>99.14</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.5</v>
+        <v>4.29</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AN17" t="n">
-        <v>44.83</v>
+        <v>42.71</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AP17" t="n">
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.83</v>
+        <v>13</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.17</v>
+        <v>10.57</v>
       </c>
       <c r="AS17" t="n">
-        <v>7</v>
+        <v>7.86</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.5</v>
+        <v>0.71</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>49.5</v>
+        <v>51.29</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>14.33</v>
+        <v>13.43</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.33</v>
+        <v>9</v>
       </c>
       <c r="BC17" t="n">
-        <v>5</v>
+        <v>4.43</v>
       </c>
       <c r="BD17" t="n">
         <v>21</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.58</v>
+        <v>1.47</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.77</v>
+        <v>10.43</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.92</v>
+        <v>4.79</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.85</v>
+        <v>5.64</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS17" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BU17" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV17" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX17" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY17" t="n">
         <v>1.85</v>
@@ -7635,169 +7635,169 @@
         <v>1.89</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.71</v>
+        <v>3.68</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="CD17" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="CE17" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="CF17" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="CG17" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CH17" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CI17" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="CJ17" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CK17" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CL17" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="CM17" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="CN17" t="n">
         <v>2.17</v>
-      </c>
-      <c r="CE17" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="CF17" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="CG17" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CH17" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CI17" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="CJ17" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CK17" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CL17" t="n">
-        <v>1.69</v>
-      </c>
-      <c r="CM17" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="CN17" t="n">
-        <v>2.19</v>
       </c>
       <c r="CO17" t="n">
         <v>1.19</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.54</v>
+        <v>2.59</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.28</v>
+        <v>3.22</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CX17" t="n">
         <v>1.46</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DB17" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.08</v>
+        <v>1.14</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.23</v>
+        <v>3.08</v>
       </c>
       <c r="DH17" t="n">
-        <v>97.08</v>
+        <v>97</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.08</v>
+        <v>2.14</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.69</v>
+        <v>5.5</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DM17" t="n">
-        <v>47.46</v>
+        <v>46.21</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.61</v>
+        <v>12.72</v>
       </c>
       <c r="DQ17" t="n">
-        <v>11</v>
+        <v>10.72</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.77</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>52.15</v>
+        <v>52.86</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.92</v>
+        <v>15.36</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.39</v>
+        <v>10.14</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.54</v>
+        <v>5.21</v>
       </c>
       <c r="EA17" t="n">
         <v>21</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="EC17" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -8210,61 +8210,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C19" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" t="n">
         <v>7</v>
       </c>
       <c r="E19" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F19" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="G19" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="H19" t="n">
-        <v>105.83</v>
+        <v>102.14</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="K19" t="n">
-        <v>6.33</v>
+        <v>5.86</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="M19" t="n">
-        <v>51.83</v>
+        <v>52.14</v>
       </c>
       <c r="N19" t="n">
-        <v>0.67</v>
+        <v>0.57</v>
       </c>
       <c r="O19" t="n">
-        <v>3</v>
+        <v>2.71</v>
       </c>
       <c r="P19" t="n">
-        <v>13.83</v>
+        <v>12.86</v>
       </c>
       <c r="Q19" t="n">
-        <v>11.83</v>
+        <v>12.14</v>
       </c>
       <c r="R19" t="n">
-        <v>5.5</v>
+        <v>5.43</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="T19" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8276,28 +8276,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>44.67</v>
+        <v>43.71</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.83</v>
+        <v>13.86</v>
       </c>
       <c r="AA19" t="n">
         <v>9</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.83</v>
+        <v>4.86</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.67</v>
+        <v>20.57</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AF19" t="n">
         <v>0.29</v>
@@ -8381,46 +8381,46 @@
         <v>3.29</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.62</v>
+        <v>10.29</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.77</v>
+        <v>1.86</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BN19" t="n">
         <v>1</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.92</v>
+        <v>4.79</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.62</v>
+        <v>5.43</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS19" t="n">
-        <v>46.15</v>
+        <v>50</v>
       </c>
       <c r="BT19" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8432,19 +8432,19 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>30.77</v>
+        <v>35.71</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CC19" t="n">
         <v>2.78</v>
@@ -8456,67 +8456,67 @@
         <v>1.33</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.1</v>
+        <v>3.08</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO19" t="n">
         <v>1.23</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.79</v>
+        <v>2.82</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.69</v>
+        <v>2.73</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CU19" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="CV19" t="n">
+        <v>2.31</v>
+      </c>
+      <c r="CW19" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CX19" t="n">
         <v>1.5</v>
-      </c>
-      <c r="CV19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="CW19" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CX19" t="n">
-        <v>1.52</v>
       </c>
       <c r="CY19" t="n">
         <v>1.75</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="DA19" t="n">
         <v>2.08</v>
@@ -8525,85 +8525,85 @@
         <v>1.25</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.94</v>
+        <v>2.98</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
       <c r="DH19" t="n">
-        <v>104.61</v>
+        <v>102.86</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.16</v>
+        <v>3.08</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.46</v>
+        <v>5.29</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DM19" t="n">
-        <v>48.92</v>
+        <v>49.28</v>
       </c>
       <c r="DN19" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.69</v>
+        <v>2.57</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.62</v>
+        <v>14.08</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.15</v>
+        <v>11.36</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.16</v>
+        <v>5.14</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>41</v>
+        <v>40.79</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.08</v>
+        <v>13.14</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.539999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.54</v>
+        <v>4.58</v>
       </c>
       <c r="EA19" t="n">
-        <v>20.62</v>
+        <v>21</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="EC19" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C3" t="n">
         <v>6</v>
       </c>
       <c r="D3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>3.5</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.57</v>
+        <v>3.38</v>
       </c>
       <c r="AI3" t="n">
-        <v>81.14</v>
+        <v>82.5</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="AL3" t="n">
-        <v>6.71</v>
+        <v>7</v>
       </c>
       <c r="AM3" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>43</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>8.880000000000001</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="AT3" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AU3" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>44.62</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA3" t="n">
+        <v>12.75</v>
+      </c>
+      <c r="BB3" t="n">
+        <v>9.619999999999999</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>3.12</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>23.88</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="BF3" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="BG3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BH3" t="n">
+        <v>13.29</v>
+      </c>
+      <c r="BI3" t="n">
+        <v>2.86</v>
+      </c>
+      <c r="BJ3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BK3" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="BM3" t="n">
         <v>0.57</v>
       </c>
-      <c r="AN3" t="n">
-        <v>42.71</v>
-      </c>
-      <c r="AO3" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AP3" t="n">
-        <v>3.14</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>11.86</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>8.289999999999999</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>10.43</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>44.57</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>12.57</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>9.859999999999999</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>24.86</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>4</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BH3" t="n">
-        <v>13.15</v>
-      </c>
-      <c r="BI3" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="BJ3" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BK3" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BL3" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="BM3" t="n">
-        <v>0.62</v>
-      </c>
       <c r="BN3" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.08</v>
+        <v>1.21</v>
       </c>
       <c r="BP3" t="n">
-        <v>6.15</v>
+        <v>6.43</v>
       </c>
       <c r="BQ3" t="n">
-        <v>7</v>
+        <v>6.86</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT3" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV3" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
         <v>2.2</v>
@@ -2013,40 +2013,40 @@
         <v>2.33</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="CE3" t="n">
         <v>1.29</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CK3" t="n">
         <v>1.33</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CM3" t="n">
         <v>2.99</v>
@@ -2058,120 +2058,120 @@
         <v>1.19</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.53</v>
+        <v>2.51</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CT3" t="n">
         <v>3.29</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CZ3" t="inlineStr"/>
       <c r="DA3" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.08</v>
+        <v>0.14</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.39</v>
+        <v>3.29</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.15000000000001</v>
+        <v>94</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.84</v>
+        <v>7</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.78</v>
       </c>
       <c r="DM3" t="n">
-        <v>52.54</v>
+        <v>52</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.46</v>
+        <v>3.71</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.54</v>
+        <v>13.5</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.16</v>
+        <v>9.43</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.539999999999999</v>
+        <v>9.07</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.54</v>
+        <v>46.42</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.54</v>
+        <v>15.43</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.77</v>
+        <v>11.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.46</v>
+        <v>22.08</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.77</v>
+        <v>3.5</v>
       </c>
     </row>
     <row r="4">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -2999,82 +2999,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="G6" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="H6" t="n">
-        <v>93.67</v>
+        <v>94.86</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3.17</v>
+        <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.33</v>
+        <v>4.43</v>
       </c>
       <c r="L6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="M6" t="n">
-        <v>31.33</v>
+        <v>32.57</v>
       </c>
       <c r="N6" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="O6" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="P6" t="n">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.83</v>
+        <v>13.57</v>
       </c>
       <c r="R6" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="S6" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="U6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V6" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>41.17</v>
+        <v>40</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.17</v>
+        <v>11.86</v>
       </c>
       <c r="AA6" t="n">
-        <v>7.67</v>
+        <v>8</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.33</v>
+        <v>20</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.18</v>
+        <v>1.26</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3158,70 +3158,70 @@
         <v>2.43</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.85</v>
+        <v>10.86</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.85</v>
+        <v>2.79</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.85</v>
+        <v>0.79</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BU6" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC6" t="n">
         <v>4.32</v>
@@ -3230,19 +3230,19 @@
         <v>4.84</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF6" t="n">
         <v>2.47</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.15</v>
+        <v>3.14</v>
       </c>
       <c r="CH6" t="n">
         <v>1.49</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.62</v>
@@ -3251,7 +3251,7 @@
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM6" t="n">
         <v>2.71</v>
@@ -3263,7 +3263,7 @@
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ6" t="n">
         <v>2.65</v>
@@ -3281,22 +3281,22 @@
         <v>1.53</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CX6" t="n">
         <v>1.47</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.56</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB6" t="n">
         <v>1.22</v>
@@ -3311,76 +3311,76 @@
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.77</v>
+        <v>2.64</v>
       </c>
       <c r="DH6" t="n">
-        <v>95.16</v>
+        <v>95.64</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.23</v>
+        <v>3.14</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.61</v>
+        <v>37.79</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.39</v>
+        <v>12.64</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.07</v>
+        <v>14.36</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.15</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>43.39</v>
+        <v>42.64</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DX6" t="n">
-        <v>11.69</v>
+        <v>12</v>
       </c>
       <c r="DY6" t="n">
-        <v>7.92</v>
+        <v>8.07</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.77</v>
+        <v>3.93</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.77</v>
+        <v>20.14</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -4196,61 +4196,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C9" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D9" t="n">
         <v>7</v>
       </c>
       <c r="E9" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="F9" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="G9" t="n">
-        <v>3.5</v>
+        <v>3.43</v>
       </c>
       <c r="H9" t="n">
-        <v>89.83</v>
+        <v>91.86</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="J9" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="M9" t="n">
-        <v>35</v>
+        <v>36.57</v>
       </c>
       <c r="N9" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="O9" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="P9" t="n">
-        <v>9.17</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.67</v>
+        <v>14.43</v>
       </c>
       <c r="R9" t="n">
-        <v>7.5</v>
+        <v>7.57</v>
       </c>
       <c r="S9" t="n">
-        <v>2.17</v>
+        <v>2.29</v>
       </c>
       <c r="T9" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4262,28 +4262,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>43.67</v>
+        <v>45.29</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z9" t="n">
-        <v>11</v>
+        <v>10.86</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.33</v>
+        <v>7.57</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.67</v>
+        <v>3.29</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.83</v>
+        <v>21.57</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,70 +4367,70 @@
         <v>2.71</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.31</v>
+        <v>10.64</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.15</v>
+        <v>4.07</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.77</v>
+        <v>0.93</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.46</v>
+        <v>1.36</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.69</v>
+        <v>2.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.46</v>
+        <v>1.57</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.15</v>
+        <v>4.57</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.15</v>
+        <v>6.07</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BV9" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BW9" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BX9" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.58</v>
+        <v>2.63</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.02</v>
+        <v>4.01</v>
       </c>
       <c r="CC9" t="n">
         <v>4.29</v>
@@ -4442,46 +4442,46 @@
         <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="CH9" t="n">
         <v>1.57</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CK9" t="n">
         <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CO9" t="n">
         <v>1.16</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CT9" t="n">
         <v>3.28</v>
@@ -4490,7 +4490,7 @@
         <v>1.6</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CW9" t="n">
         <v>1.56</v>
@@ -4499,25 +4499,25 @@
         <v>1.47</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.58</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
         <v>1</v>
@@ -4526,70 +4526,70 @@
         <v>3</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.92</v>
+        <v>79.78</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.69</v>
+        <v>4.78</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.16</v>
+        <v>0.22</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.23</v>
+        <v>36</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.23</v>
+        <v>1.21</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.69</v>
+        <v>1.78</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.61</v>
+        <v>11.71</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.16</v>
+        <v>13.14</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.84</v>
+        <v>7.86</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>44.92</v>
+        <v>45.64</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.38</v>
+        <v>12.22</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.62</v>
+        <v>7.72</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.77</v>
+        <v>4.5</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.77</v>
+        <v>23</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="10">
@@ -4998,13 +4998,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C11" t="n">
         <v>7</v>
       </c>
       <c r="D11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5088,139 +5088,139 @@
         <v>2.29</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG11" t="n">
-        <v>1.83</v>
+        <v>2.14</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AI11" t="n">
-        <v>88.17</v>
+        <v>90.29000000000001</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.83</v>
+        <v>3.71</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.67</v>
+        <v>45.29</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.67</v>
+        <v>0.86</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.17</v>
+        <v>1.29</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.33</v>
+        <v>15.14</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.33</v>
+        <v>14.14</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.83</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>46</v>
+        <v>46.29</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.67</v>
+        <v>11.43</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.33</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.33</v>
+        <v>3.14</v>
       </c>
       <c r="BD11" t="n">
-        <v>22.67</v>
+        <v>23.29</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.69</v>
+        <v>10.71</v>
       </c>
       <c r="BI11" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BP11" t="n">
-        <v>5</v>
+        <v>4.93</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.69</v>
+        <v>4.86</v>
       </c>
       <c r="BR11" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BT11" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BY11" t="n">
         <v>2.01</v>
@@ -5229,22 +5229,22 @@
         <v>1.93</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.54</v>
+        <v>3.53</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.92</v>
+        <v>2.87</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.32</v>
+        <v>3.24</v>
       </c>
       <c r="CE11" t="n">
         <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG11" t="n">
         <v>3.26</v>
@@ -5253,7 +5253,7 @@
         <v>1.54</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.54</v>
@@ -5265,10 +5265,10 @@
         <v>1.67</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CO11" t="n">
         <v>1.18</v>
@@ -5283,10 +5283,10 @@
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CU11" t="n">
         <v>1.56</v>
@@ -5307,7 +5307,7 @@
         <v>2.63</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB11" t="n">
         <v>1.2</v>
@@ -5319,34 +5319,34 @@
         <v>2.58</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.69</v>
+        <v>1.86</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>90.7</v>
+        <v>91.58</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0.08</v>
+        <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.54</v>
+        <v>4.42</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.61</v>
+        <v>44.5</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.77</v>
+        <v>0.86</v>
       </c>
       <c r="DO11" t="n">
         <v>2</v>
@@ -5355,43 +5355,43 @@
         <v>13.92</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.38</v>
+        <v>11.5</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.23</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.46</v>
+        <v>46.58</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.85</v>
+        <v>11.72</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.92</v>
+        <v>7.93</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.92</v>
+        <v>3.78</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.62</v>
+        <v>21.07</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.39</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="12">
@@ -5401,10 +5401,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D12" t="n">
         <v>7</v>
@@ -5413,49 +5413,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.83</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.67</v>
+        <v>3.14</v>
       </c>
       <c r="H12" t="n">
-        <v>88.17</v>
+        <v>90</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="K12" t="n">
-        <v>5.17</v>
+        <v>5.57</v>
       </c>
       <c r="L12" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="M12" t="n">
-        <v>42.5</v>
+        <v>41.86</v>
       </c>
       <c r="N12" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.43</v>
       </c>
       <c r="P12" t="n">
-        <v>12.67</v>
+        <v>12.71</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.33</v>
+        <v>15.14</v>
       </c>
       <c r="R12" t="n">
-        <v>8.33</v>
+        <v>8.43</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5467,28 +5467,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>53</v>
+        <v>52.86</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>14.83</v>
+        <v>14</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="AB12" t="n">
-        <v>5.33</v>
+        <v>4.57</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.67</v>
+        <v>19.14</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.62</v>
+        <v>1.51</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="AF12" t="n">
         <v>0.14</v>
@@ -5572,67 +5572,67 @@
         <v>3.43</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BH12" t="n">
-        <v>10</v>
+        <v>10.07</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.31</v>
+        <v>2.21</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.69</v>
+        <v>5.79</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT12" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BU12" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV12" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.14</v>
+        <v>2.19</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.15</v>
+        <v>2.2</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.58</v>
+        <v>3.56</v>
       </c>
       <c r="CB12" t="n">
         <v>3.67</v>
@@ -5644,13 +5644,13 @@
         <v>2.86</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF12" t="n">
         <v>2.49</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CH12" t="n">
         <v>1.5</v>
@@ -5659,7 +5659,7 @@
         <v>2.35</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK12" t="n">
         <v>1.34</v>
@@ -5668,7 +5668,7 @@
         <v>1.67</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CN12" t="n">
         <v>2.22</v>
@@ -5680,7 +5680,7 @@
         <v>1.68</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CR12" t="n">
         <v>1.35</v>
@@ -5710,7 +5710,7 @@
         <v>2.49</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB12" t="n">
         <v>1.22</v>
@@ -5722,79 +5722,79 @@
         <v>2.73</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.54</v>
+        <v>2.78</v>
       </c>
       <c r="DH12" t="n">
-        <v>85</v>
+        <v>86.15000000000001</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.46</v>
+        <v>4.72</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.23</v>
+        <v>39.14</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.85</v>
+        <v>0.78</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.08</v>
+        <v>14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.23</v>
+        <v>14.22</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.619999999999999</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.77</v>
+        <v>50.86</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX12" t="n">
-        <v>13.15</v>
+        <v>12.86</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.85</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4.31</v>
+        <v>4</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.77</v>
+        <v>19.5</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="13">
@@ -5804,13 +5804,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C13" t="n">
         <v>7</v>
       </c>
       <c r="D13" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E13" t="n">
         <v>0.43</v>
@@ -5897,136 +5897,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.83</v>
+        <v>2.29</v>
       </c>
       <c r="AI13" t="n">
-        <v>97.33</v>
+        <v>98.86</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.17</v>
+        <v>3.43</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.17</v>
+        <v>4.43</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="AN13" t="n">
-        <v>39.33</v>
+        <v>39.71</v>
       </c>
       <c r="AO13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AP13" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AQ13" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR13" t="n">
+        <v>14.14</v>
+      </c>
+      <c r="AS13" t="n">
+        <v>9</v>
+      </c>
+      <c r="AT13" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AU13" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>47.57</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>11.71</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>21.43</v>
+      </c>
+      <c r="BE13" t="n">
         <v>1.33</v>
       </c>
-      <c r="AP13" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AQ13" t="n">
-        <v>12.17</v>
-      </c>
-      <c r="AR13" t="n">
-        <v>13.83</v>
-      </c>
-      <c r="AS13" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="AT13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU13" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AV13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>44.33</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>7.83</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>21</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.34</v>
-      </c>
       <c r="BF13" t="n">
-        <v>2.83</v>
+        <v>3.14</v>
       </c>
       <c r="BG13" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.539999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>3</v>
+        <v>2.93</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.85</v>
+        <v>1.79</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.54</v>
+        <v>4.57</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4</v>
+        <v>4.14</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV13" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY13" t="n">
         <v>2.35</v>
@@ -6035,16 +6035,16 @@
         <v>2.47</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB13" t="n">
         <v>3.65</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.92</v>
+        <v>2.8</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
@@ -6053,10 +6053,10 @@
         <v>2.44</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI13" t="n">
         <v>2.36</v>
@@ -6065,22 +6065,22 @@
         <v>1.56</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CO13" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ13" t="n">
         <v>2.62</v>
@@ -6089,13 +6089,13 @@
         <v>1.36</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CT13" t="n">
         <v>3.3</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV13" t="n">
         <v>2.5</v>
@@ -6107,7 +6107,7 @@
         <v>1.46</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.57</v>
@@ -6125,79 +6125,79 @@
         <v>2.69</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.62</v>
+        <v>1.72</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.38</v>
+        <v>2.58</v>
       </c>
       <c r="DH13" t="n">
-        <v>102.84</v>
+        <v>103.22</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.85</v>
+        <v>3</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.31</v>
+        <v>5.36</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>46.15</v>
+        <v>45.86</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.15</v>
+        <v>1.21</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.15</v>
+        <v>12.57</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.77</v>
+        <v>13.92</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.31</v>
+        <v>8.57</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.3</v>
+        <v>49.64</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX13" t="n">
-        <v>15</v>
+        <v>14.64</v>
       </c>
       <c r="DY13" t="n">
-        <v>9.15</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.85</v>
+        <v>5.79</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.61</v>
+        <v>21.78</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.69</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="14">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="F2" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="G2" t="n">
-        <v>3.14</v>
+        <v>3.88</v>
       </c>
       <c r="H2" t="n">
-        <v>103.29</v>
+        <v>101.75</v>
       </c>
       <c r="I2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="J2" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="K2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L2" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="M2" t="n">
-        <v>43.57</v>
+        <v>46.88</v>
       </c>
       <c r="N2" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="O2" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="P2" t="n">
-        <v>12.29</v>
+        <v>12.75</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.14</v>
+        <v>14.5</v>
       </c>
       <c r="R2" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="S2" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="U2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53.71</v>
+        <v>53.38</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z2" t="n">
-        <v>13.57</v>
+        <v>14</v>
       </c>
       <c r="AA2" t="n">
-        <v>8.859999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.71</v>
+        <v>4.38</v>
       </c>
       <c r="AC2" t="n">
-        <v>24</v>
+        <v>24.62</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.14</v>
+        <v>2.25</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,37 +1550,37 @@
         <v>2.67</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.23</v>
+        <v>11.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.46</v>
+        <v>3.43</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.62</v>
+        <v>1.5</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.46</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.23</v>
+        <v>4.29</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.92</v>
+        <v>7.14</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
@@ -1589,31 +1589,31 @@
         <v>100</v>
       </c>
       <c r="BT2" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BU2" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW2" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BX2" t="n">
-        <v>61.54</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.21</v>
+        <v>2.17</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="CC2" t="n">
         <v>3.23</v>
@@ -1622,13 +1622,13 @@
         <v>3.55</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF2" t="n">
         <v>2.37</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CH2" t="n">
         <v>1.55</v>
@@ -1637,16 +1637,16 @@
         <v>2.39</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CK2" t="n">
         <v>1.36</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="CN2" t="n">
         <v>2.15</v>
@@ -1655,28 +1655,28 @@
         <v>1.17</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CT2" t="n">
         <v>3.26</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CX2" t="n">
         <v>1.48</v>
@@ -1694,85 +1694,85 @@
         <v>1.19</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="DE2" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.92</v>
+        <v>4.29</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.39</v>
+        <v>100.64</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.16</v>
+        <v>0.14</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="DK2" t="n">
-        <v>6</v>
+        <v>6.5</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.23</v>
+        <v>50.72</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.08</v>
+        <v>2.21</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.47</v>
+        <v>12.72</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14.46</v>
+        <v>14.64</v>
       </c>
       <c r="DR2" t="n">
-        <v>8.08</v>
+        <v>8</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.54</v>
+        <v>51.5</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.39</v>
+        <v>13.64</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.390000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4</v>
+        <v>3.86</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.69</v>
+        <v>24.07</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
     </row>
     <row r="3">
@@ -2016,13 +2016,13 @@
         <v>3.65</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.73</v>
+        <v>3.71</v>
       </c>
       <c r="CC3" t="n">
         <v>2.84</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CE3" t="n">
         <v>1.29</v>
@@ -2067,16 +2067,16 @@
         <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CT3" t="n">
         <v>3.29</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CW3" t="n">
         <v>1.56</v>
@@ -2087,16 +2087,16 @@
       </c>
       <c r="CZ3" t="inlineStr"/>
       <c r="DA3" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC3" t="n">
         <v>1.67</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="DE3" t="n">
         <v>0.14</v>
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C4" t="n">
         <v>7</v>
       </c>
       <c r="D4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E4" t="n">
         <v>0.29</v>
@@ -2271,52 +2271,52 @@
         <v>2.14</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.83</v>
+        <v>0.86</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AI4" t="n">
-        <v>88</v>
+        <v>89.86</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.17</v>
+        <v>-0.14</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.17</v>
+        <v>4.29</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN4" t="n">
-        <v>35.33</v>
+        <v>36.86</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13.17</v>
+        <v>13</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.83</v>
+        <v>11.29</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.17</v>
+        <v>10.29</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.17</v>
+        <v>1</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2328,82 +2328,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>51.17</v>
+        <v>51.43</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>13.5</v>
+        <v>13.14</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.5</v>
+        <v>8.57</v>
       </c>
       <c r="BC4" t="n">
-        <v>5</v>
+        <v>4.57</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.5</v>
+        <v>19.29</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.17</v>
+        <v>1.14</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.539999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.77</v>
+        <v>2.57</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.92</v>
+        <v>0.86</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.69</v>
+        <v>1.57</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.77</v>
+        <v>4.86</v>
       </c>
       <c r="BR4" t="n">
-        <v>84.62</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>69.23</v>
+        <v>64.29000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV4" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX4" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
         <v>1.88</v>
@@ -2412,31 +2412,31 @@
         <v>1.86</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CB4" t="n">
         <v>3.85</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.76</v>
+        <v>2.87</v>
       </c>
       <c r="CD4" t="n">
-        <v>2.96</v>
+        <v>3.12</v>
       </c>
       <c r="CE4" t="n">
         <v>1.29</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CH4" t="n">
         <v>1.55</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.56</v>
@@ -2445,10 +2445,10 @@
         <v>1.41</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CN4" t="n">
         <v>2.08</v>
@@ -2460,7 +2460,7 @@
         <v>1.6</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
@@ -2502,46 +2502,46 @@
         <v>2.6</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.15000000000001</v>
+        <v>87.22</v>
       </c>
       <c r="DI4" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.62</v>
+        <v>4.65</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.84</v>
+        <v>44</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.15</v>
+        <v>13.07</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.46</v>
+        <v>12.14</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.16</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2553,28 +2553,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.54</v>
+        <v>50.72</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.08</v>
+        <v>13.86</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.539999999999999</v>
+        <v>8.57</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.54</v>
+        <v>5.29</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.93</v>
+        <v>19.29</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="5">
@@ -2584,94 +2584,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C5" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D5" t="n">
         <v>7</v>
       </c>
       <c r="E5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F5" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="H5" t="n">
-        <v>89.5</v>
+        <v>87.14</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="K5" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="L5" t="n">
-        <v>0.33</v>
+        <v>0.43</v>
       </c>
       <c r="M5" t="n">
-        <v>46.83</v>
+        <v>45.14</v>
       </c>
       <c r="N5" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>11.17</v>
+        <v>11.29</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.17</v>
+        <v>13.14</v>
       </c>
       <c r="R5" t="n">
-        <v>7.33</v>
+        <v>7.57</v>
       </c>
       <c r="S5" t="n">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="T5" t="n">
-        <v>1.33</v>
+        <v>1.43</v>
       </c>
       <c r="U5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>50.67</v>
+        <v>49.57</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>11</v>
+        <v>11.71</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.17</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.83</v>
+        <v>3</v>
       </c>
       <c r="AC5" t="n">
-        <v>23.17</v>
+        <v>22.43</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="AF5" t="n">
         <v>0.14</v>
@@ -2755,70 +2755,70 @@
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.23</v>
+        <v>10.71</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.15</v>
+        <v>1.07</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BO5" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.62</v>
+        <v>4.43</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.62</v>
+        <v>6.29</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BT5" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX5" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="CA5" t="n">
         <v>3.64</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CC5" t="n">
         <v>3.26</v>
@@ -2830,16 +2830,16 @@
         <v>1.3</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH5" t="n">
         <v>1.53</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.55</v>
@@ -2851,25 +2851,25 @@
         <v>1.65</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CR5" t="n">
         <v>1.35</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT5" t="n">
         <v>3.33</v>
@@ -2881,103 +2881,103 @@
         <v>2.5</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX5" t="n">
         <v>1.46</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.6</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.47</v>
+        <v>1.43</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.16</v>
+        <v>3.08</v>
       </c>
       <c r="DH5" t="n">
-        <v>92.77</v>
+        <v>91.36</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.23</v>
+        <v>2.14</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.38</v>
+        <v>5.29</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.31</v>
+        <v>0.36</v>
       </c>
       <c r="DM5" t="n">
-        <v>49.15</v>
+        <v>48.14</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.69</v>
+        <v>11.72</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.54</v>
+        <v>12.57</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.460000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.54</v>
+        <v>49.07</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX5" t="n">
-        <v>13</v>
+        <v>13.21</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.460000000000001</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.54</v>
+        <v>3.57</v>
       </c>
       <c r="EA5" t="n">
-        <v>22.08</v>
+        <v>21.78</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.92</v>
+        <v>1.86</v>
       </c>
     </row>
     <row r="6">
@@ -3215,7 +3215,7 @@
         <v>3.13</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CA6" t="n">
         <v>3.66</v>
@@ -3272,19 +3272,19 @@
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CU6" t="n">
         <v>1.53</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX6" t="n">
         <v>1.47</v>
@@ -3302,10 +3302,10 @@
         <v>1.22</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
@@ -3390,94 +3390,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C7" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D7" t="n">
         <v>7</v>
       </c>
       <c r="E7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="F7" t="n">
-        <v>1.67</v>
+        <v>1.43</v>
       </c>
       <c r="G7" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="H7" t="n">
-        <v>92.67</v>
+        <v>94.14</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="K7" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>54.17</v>
+        <v>53.71</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="O7" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="P7" t="n">
-        <v>13.33</v>
+        <v>12.57</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.83</v>
+        <v>13.57</v>
       </c>
       <c r="R7" t="n">
-        <v>6.33</v>
+        <v>6.71</v>
       </c>
       <c r="S7" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="T7" t="n">
-        <v>2.33</v>
+        <v>2</v>
       </c>
       <c r="U7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V7" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>54.5</v>
+        <v>53.43</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.67</v>
+        <v>15.43</v>
       </c>
       <c r="AA7" t="n">
-        <v>9.83</v>
+        <v>10</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.83</v>
+        <v>5.43</v>
       </c>
       <c r="AC7" t="n">
-        <v>22.33</v>
+        <v>22.71</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="AE7" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="AF7" t="n">
         <v>0.14</v>
@@ -3561,70 +3561,70 @@
         <v>2.71</v>
       </c>
       <c r="BG7" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.77</v>
+        <v>10.79</v>
       </c>
       <c r="BI7" t="n">
-        <v>3.08</v>
+        <v>2.86</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.31</v>
+        <v>1.21</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.77</v>
+        <v>4.79</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.77</v>
+        <v>4.86</v>
       </c>
       <c r="BR7" t="n">
-        <v>100</v>
+        <v>92.86</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.92</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>53.85</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>46.15</v>
+        <v>42.86</v>
       </c>
       <c r="BV7" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX7" t="n">
-        <v>38.46</v>
+        <v>35.71</v>
       </c>
       <c r="BY7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BZ7" t="n">
         <v>2</v>
-      </c>
-      <c r="BZ7" t="n">
-        <v>2.01</v>
       </c>
       <c r="CA7" t="n">
         <v>3.55</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.74</v>
+        <v>3.75</v>
       </c>
       <c r="CC7" t="n">
         <v>2.12</v>
@@ -3636,7 +3636,7 @@
         <v>1.3</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CG7" t="n">
         <v>3.32</v>
@@ -3645,19 +3645,19 @@
         <v>1.53</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.54</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL7" t="n">
         <v>1.67</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CN7" t="n">
         <v>2.16</v>
@@ -3666,7 +3666,7 @@
         <v>1.19</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ7" t="n">
         <v>2.57</v>
@@ -3693,7 +3693,7 @@
         <v>1.44</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.61</v>
@@ -3705,85 +3705,85 @@
         <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.92</v>
+        <v>1.78</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DH7" t="n">
-        <v>94.69</v>
+        <v>95.28</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.08</v>
+        <v>6.07</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.31</v>
+        <v>0.28</v>
       </c>
       <c r="DM7" t="n">
-        <v>49.31</v>
+        <v>49.42</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.61</v>
+        <v>0.57</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="DP7" t="n">
-        <v>12</v>
+        <v>11.72</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.77</v>
+        <v>14.57</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.62</v>
+        <v>6.79</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>55</v>
+        <v>54.43</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.62</v>
+        <v>15.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.38</v>
+        <v>10.43</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.23</v>
+        <v>5.07</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.69</v>
+        <v>22.86</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.46</v>
+        <v>2.28</v>
       </c>
     </row>
     <row r="8">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C8" t="n">
         <v>7</v>
       </c>
       <c r="D8" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3883,139 +3883,139 @@
         <v>2.71</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.83</v>
+        <v>2.43</v>
       </c>
       <c r="AI8" t="n">
-        <v>92.5</v>
+        <v>97.70999999999999</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.67</v>
+        <v>2.57</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.5</v>
+        <v>3.86</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AN8" t="n">
-        <v>43.33</v>
+        <v>43.29</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.5</v>
+        <v>1.29</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.33</v>
+        <v>11.57</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.17</v>
+        <v>12.14</v>
       </c>
       <c r="AS8" t="n">
-        <v>8.83</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>43.33</v>
+        <v>45.29</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.83</v>
+        <v>12.86</v>
       </c>
       <c r="BB8" t="n">
-        <v>8.83</v>
+        <v>9.140000000000001</v>
       </c>
       <c r="BC8" t="n">
+        <v>3.71</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>20.29</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>1.39</v>
+      </c>
+      <c r="BF8" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BG8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BP8" t="n">
         <v>4</v>
       </c>
-      <c r="BD8" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BE8" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BH8" t="n">
-        <v>9.539999999999999</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.92</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.85</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>4.15</v>
-      </c>
       <c r="BQ8" t="n">
-        <v>5.31</v>
+        <v>5.07</v>
       </c>
       <c r="BR8" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS8" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU8" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BV8" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX8" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BY8" t="n">
         <v>2.28</v>
@@ -4027,13 +4027,13 @@
         <v>3.64</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.31</v>
+        <v>3.21</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="CE8" t="n">
         <v>1.3</v>
@@ -4048,7 +4048,7 @@
         <v>1.52</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.56</v>
@@ -4060,10 +4060,10 @@
         <v>1.74</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="CO8" t="n">
         <v>1.18</v>
@@ -4072,7 +4072,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CR8" t="n">
         <v>1.38</v>
@@ -4096,97 +4096,97 @@
         <v>1.48</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.52</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="DH8" t="n">
-        <v>89</v>
+        <v>91.84999999999999</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.69</v>
+        <v>2.64</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.39</v>
+        <v>4.08</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.31</v>
+        <v>46.08</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.54</v>
+        <v>12.57</v>
       </c>
       <c r="DQ8" t="n">
         <v>11.92</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.38</v>
+        <v>7.71</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.69</v>
+        <v>48.36</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.38</v>
+        <v>12.43</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.69</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.69</v>
+        <v>3.57</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.69</v>
+        <v>21</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.61</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="9">
@@ -4430,7 +4430,7 @@
         <v>3.8</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.01</v>
+        <v>4</v>
       </c>
       <c r="CC9" t="n">
         <v>4.29</v>
@@ -4481,7 +4481,7 @@
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CT9" t="n">
         <v>3.28</v>
@@ -4490,7 +4490,7 @@
         <v>1.6</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CW9" t="n">
         <v>1.56</v>
@@ -4508,13 +4508,13 @@
         <v>2.18</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="DE9" t="n">
         <v>0.14</v>
@@ -5238,7 +5238,7 @@
         <v>2.87</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="CE11" t="n">
         <v>1.3</v>
@@ -5292,7 +5292,7 @@
         <v>1.56</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CW11" t="n">
         <v>1.58</v>
@@ -5629,7 +5629,7 @@
         <v>2.19</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CA12" t="n">
         <v>3.56</v>
@@ -5695,10 +5695,10 @@
         <v>1.54</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CX12" t="n">
         <v>1.5</v>
@@ -6044,7 +6044,7 @@
         <v>2.8</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
@@ -6092,13 +6092,13 @@
         <v>2.58</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CU13" t="n">
         <v>1.53</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CW13" t="n">
         <v>1.57</v>
@@ -6119,10 +6119,10 @@
         <v>1.21</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="DE13" t="n">
         <v>0.22</v>
@@ -6606,10 +6606,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D15" t="n">
         <v>7</v>
@@ -6618,82 +6618,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="G15" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="H15" t="n">
-        <v>115</v>
+        <v>114.14</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="K15" t="n">
-        <v>4.83</v>
+        <v>5</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="M15" t="n">
-        <v>54.5</v>
+        <v>56.14</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.71</v>
       </c>
       <c r="O15" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="P15" t="n">
-        <v>14.17</v>
+        <v>13.86</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.5</v>
+        <v>10.86</v>
       </c>
       <c r="R15" t="n">
-        <v>5.83</v>
+        <v>5.86</v>
       </c>
       <c r="S15" t="n">
-        <v>2.17</v>
+        <v>1.86</v>
       </c>
       <c r="T15" t="n">
-        <v>1</v>
+        <v>1.29</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>54.83</v>
+        <v>55.43</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="Z15" t="n">
-        <v>14.83</v>
+        <v>15.43</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.67</v>
+        <v>10.71</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.17</v>
+        <v>4.71</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.63</v>
+        <v>1.71</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6777,70 +6777,70 @@
         <v>3</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.31</v>
+        <v>10.36</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.85</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.77</v>
+        <v>0.71</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.92</v>
+        <v>5.14</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.38</v>
+        <v>5.21</v>
       </c>
       <c r="BR15" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS15" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT15" t="n">
-        <v>38.46</v>
+        <v>42.86</v>
       </c>
       <c r="BU15" t="n">
-        <v>23.08</v>
+        <v>21.43</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BX15" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BY15" t="n">
         <v>2.22</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC15" t="n">
         <v>2.96</v>
@@ -6852,28 +6852,28 @@
         <v>1.26</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="CH15" t="n">
         <v>1.61</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.49</v>
       </c>
       <c r="CK15" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CL15" t="n">
         <v>1.75</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CN15" t="n">
         <v>2.15</v>
@@ -6893,13 +6893,13 @@
       </c>
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CX15" t="n">
         <v>1.46</v>
@@ -6926,76 +6926,76 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="DH15" t="n">
-        <v>96.15000000000001</v>
+        <v>97.06999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="DM15" t="n">
-        <v>45.92</v>
+        <v>47.36</v>
       </c>
       <c r="DN15" t="n">
         <v>0.85</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.39</v>
+        <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.77</v>
+        <v>12.72</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.61</v>
+        <v>12.22</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.69</v>
+        <v>6.64</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.54</v>
+        <v>55.78</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>15.77</v>
+        <v>16</v>
       </c>
       <c r="DY15" t="n">
         <v>10.92</v>
       </c>
       <c r="DZ15" t="n">
-        <v>4.85</v>
+        <v>5.07</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.69</v>
+        <v>19.36</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="16">
@@ -7005,13 +7005,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C16" t="n">
         <v>7</v>
       </c>
       <c r="D16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7095,139 +7095,139 @@
         <v>2.29</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AG16" t="n">
         <v>2</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.5</v>
+        <v>3.14</v>
       </c>
       <c r="AI16" t="n">
-        <v>93.67</v>
+        <v>90.70999999999999</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="AK16" t="n">
         <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>6</v>
+        <v>5.86</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="AN16" t="n">
-        <v>50.5</v>
+        <v>47.57</v>
       </c>
       <c r="AO16" t="n">
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.5</v>
+        <v>2.71</v>
       </c>
       <c r="AQ16" t="n">
-        <v>15.17</v>
+        <v>14</v>
       </c>
       <c r="AR16" t="n">
-        <v>14</v>
+        <v>13.71</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.83</v>
+        <v>8</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.5</v>
+        <v>1.71</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.33</v>
+        <v>1.14</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>48.83</v>
+        <v>47.71</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0</v>
+        <v>0.14</v>
       </c>
       <c r="BA16" t="n">
-        <v>13.5</v>
+        <v>12.57</v>
       </c>
       <c r="BB16" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>5.17</v>
+        <v>4.57</v>
       </c>
       <c r="BD16" t="n">
-        <v>20.33</v>
+        <v>20</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="BF16" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.38</v>
+        <v>10.43</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.62</v>
+        <v>0.79</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.31</v>
+        <v>1.43</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.62</v>
+        <v>4.86</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.77</v>
+        <v>5.57</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS16" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>53.85</v>
+        <v>57.14</v>
       </c>
       <c r="BU16" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BV16" t="n">
-        <v>7.69</v>
+        <v>7.14</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.54</v>
+        <v>57.14</v>
       </c>
       <c r="BY16" t="n">
         <v>2.42</v>
@@ -7236,31 +7236,31 @@
         <v>2.46</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CC16" t="n">
-        <v>2.97</v>
+        <v>3</v>
       </c>
       <c r="CD16" t="n">
         <v>3.14</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF16" t="n">
         <v>2.43</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.24</v>
+        <v>3.27</v>
       </c>
       <c r="CH16" t="n">
         <v>1.51</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.29</v>
+        <v>2.31</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.57</v>
@@ -7269,37 +7269,37 @@
         <v>1.35</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.95</v>
+        <v>2.94</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="CT16" t="n">
         <v>3.27</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.48</v>
+        <v>2.51</v>
       </c>
       <c r="CW16" t="n">
         <v>1.57</v>
@@ -7316,85 +7316,85 @@
         <v>1.21</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
       <c r="DH16" t="n">
-        <v>95.62</v>
+        <v>94</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.46</v>
+        <v>5.43</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.15</v>
+        <v>0.22</v>
       </c>
       <c r="DM16" t="n">
-        <v>46.69</v>
+        <v>45.5</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.46</v>
+        <v>2.57</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.92</v>
+        <v>12.5</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.08</v>
+        <v>13.92</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.84</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.23</v>
+        <v>49.57</v>
       </c>
       <c r="DW16" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DX16" t="n">
-        <v>13</v>
+        <v>12.57</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.23</v>
+        <v>8.07</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.77</v>
+        <v>4.5</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.08</v>
+        <v>19.93</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.49</v>
+        <v>1.44</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="17">
@@ -7497,7 +7497,7 @@
         <v>0.29</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.43</v>
+        <v>1.57</v>
       </c>
       <c r="AH17" t="n">
         <v>2.29</v>
@@ -7509,7 +7509,7 @@
         <v>-0.14</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="AL17" t="n">
         <v>4.29</v>
@@ -7572,7 +7572,7 @@
         <v>1.47</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.29</v>
+        <v>2.43</v>
       </c>
       <c r="BG17" t="n">
         <v>2.5</v>
@@ -7728,7 +7728,7 @@
         <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.14</v>
+        <v>1.21</v>
       </c>
       <c r="DG17" t="n">
         <v>3.08</v>
@@ -7740,7 +7740,7 @@
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="DK17" t="n">
         <v>5.5</v>
@@ -7797,7 +7797,7 @@
         <v>1.67</v>
       </c>
       <c r="EC17" t="n">
-        <v>2</v>
+        <v>2.07</v>
       </c>
     </row>
     <row r="18">
@@ -7807,13 +7807,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C18" t="n">
         <v>7</v>
       </c>
       <c r="D18" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7900,49 +7900,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.33</v>
+        <v>2.29</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.5</v>
+        <v>2.29</v>
       </c>
       <c r="AI18" t="n">
-        <v>87</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.33</v>
+        <v>0.29</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.83</v>
+        <v>4.14</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.17</v>
+        <v>3.86</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>29.67</v>
+        <v>30.57</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.33</v>
+        <v>1.71</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.67</v>
+        <v>1.57</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>13.71</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.83</v>
+        <v>15.86</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.67</v>
+        <v>7.86</v>
       </c>
       <c r="AT18" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AU18" t="n">
-        <v>1</v>
+        <v>1.14</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7954,82 +7954,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.17</v>
+        <v>0.14</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.5</v>
+        <v>11.57</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.5</v>
+        <v>7.29</v>
       </c>
       <c r="BC18" t="n">
-        <v>4</v>
+        <v>4.29</v>
       </c>
       <c r="BD18" t="n">
-        <v>19.67</v>
+        <v>20.86</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.5</v>
+        <v>3.86</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.23</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.31</v>
+        <v>4.36</v>
       </c>
       <c r="BQ18" t="n">
-        <v>4.92</v>
+        <v>5.29</v>
       </c>
       <c r="BR18" t="n">
-        <v>92.31</v>
+        <v>92.86</v>
       </c>
       <c r="BS18" t="n">
-        <v>84.62</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>69.23</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BU18" t="n">
-        <v>30.77</v>
+        <v>28.57</v>
       </c>
       <c r="BV18" t="n">
-        <v>15.38</v>
+        <v>14.29</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>76.92</v>
+        <v>78.56999999999999</v>
       </c>
       <c r="BY18" t="n">
         <v>2.57</v>
@@ -8038,22 +8038,22 @@
         <v>2.76</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.49</v>
+        <v>3.5</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.3</v>
+        <v>3.37</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.41</v>
+        <v>3.65</v>
       </c>
       <c r="CE18" t="n">
         <v>1.35</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CG18" t="n">
         <v>3.04</v>
@@ -8065,19 +8065,19 @@
         <v>2.19</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL18" t="n">
         <v>1.87</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CO18" t="n">
         <v>1.23</v>
@@ -8086,121 +8086,121 @@
         <v>1.78</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CT18" t="n">
         <v>3.16</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CV18" t="n">
         <v>2.27</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX18" t="n">
         <v>1.53</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.43</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="DG18" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.15000000000001</v>
+        <v>86.42</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.23</v>
+        <v>3.42</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.15</v>
+        <v>4</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM18" t="n">
-        <v>34.08</v>
+        <v>34.21</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.15</v>
+        <v>2.07</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.38</v>
+        <v>14.64</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.38</v>
+        <v>15.43</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.31</v>
+        <v>7.43</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>58.92</v>
+        <v>58.22</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.61</v>
+        <v>11.64</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.54</v>
+        <v>7.43</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.08</v>
+        <v>4.22</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.46</v>
+        <v>21</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.92</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1944,7 +1944,7 @@
         <v>3.12</v>
       </c>
       <c r="BD3" t="n">
-        <v>23.88</v>
+        <v>24</v>
       </c>
       <c r="BE3" t="n">
         <v>1.34</v>
@@ -2165,7 +2165,7 @@
         <v>3.93</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.08</v>
+        <v>22.14</v>
       </c>
       <c r="EB3" t="n">
         <v>1.63</v>
@@ -2328,7 +2328,7 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>51.43</v>
+        <v>51.57</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
@@ -2553,7 +2553,7 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.72</v>
+        <v>50.78</v>
       </c>
       <c r="DW4" t="n">
         <v>0.07000000000000001</v>
@@ -2650,16 +2650,16 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49.57</v>
+        <v>49.43</v>
       </c>
       <c r="Y5" t="n">
         <v>0.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.71</v>
+        <v>12</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.710000000000001</v>
+        <v>9</v>
       </c>
       <c r="AB5" t="n">
         <v>3</v>
@@ -2668,7 +2668,7 @@
         <v>22.43</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AE5" t="n">
         <v>1.71</v>
@@ -2956,16 +2956,16 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.07</v>
+        <v>49</v>
       </c>
       <c r="DW5" t="n">
         <v>0.14</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.21</v>
+        <v>13.36</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.640000000000001</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="DZ5" t="n">
         <v>3.57</v>
@@ -3456,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>53.43</v>
+        <v>53.29</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.43</v>
+        <v>54.36</v>
       </c>
       <c r="DW7" t="n">
         <v>0.07000000000000001</v>
@@ -3940,16 +3940,16 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.29</v>
+        <v>45.43</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.14</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.86</v>
+        <v>13</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.140000000000001</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="BC8" t="n">
         <v>3.71</v>
@@ -3958,7 +3958,7 @@
         <v>20.29</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BF8" t="n">
         <v>2.43</v>
@@ -4165,16 +4165,16 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.36</v>
+        <v>48.43</v>
       </c>
       <c r="DW8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.859999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.57</v>
@@ -4183,7 +4183,7 @@
         <v>21</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
         <v>2.57</v>
@@ -5151,10 +5151,10 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.43</v>
+        <v>11.29</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.289999999999999</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="BC11" t="n">
         <v>3.14</v>
@@ -5376,10 +5376,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.72</v>
+        <v>11.64</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.93</v>
+        <v>7.86</v>
       </c>
       <c r="DZ11" t="n">
         <v>3.78</v>
@@ -6672,7 +6672,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.43</v>
+        <v>55.29</v>
       </c>
       <c r="Y15" t="n">
         <v>0.14</v>
@@ -6974,7 +6974,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.78</v>
+        <v>55.72</v>
       </c>
       <c r="DW15" t="n">
         <v>0.07000000000000001</v>
@@ -7152,7 +7152,7 @@
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>47.71</v>
+        <v>47.86</v>
       </c>
       <c r="AZ16" t="n">
         <v>0.14</v>
@@ -7373,7 +7373,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.57</v>
+        <v>49.64</v>
       </c>
       <c r="DW16" t="n">
         <v>0.07000000000000001</v>
@@ -7960,10 +7960,10 @@
         <v>0.14</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.57</v>
+        <v>11.71</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.29</v>
+        <v>7.43</v>
       </c>
       <c r="BC18" t="n">
         <v>4.29</v>
@@ -7972,7 +7972,7 @@
         <v>20.86</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="BF18" t="n">
         <v>3.86</v>
@@ -8185,10 +8185,10 @@
         <v>0.14</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.64</v>
+        <v>11.71</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.43</v>
+        <v>7.5</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.22</v>
@@ -8197,7 +8197,7 @@
         <v>21</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="EC18" t="n">
         <v>3.14</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D8" t="n">
         <v>7</v>
@@ -3805,49 +3805,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.57</v>
+        <v>1.88</v>
       </c>
       <c r="G8" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="H8" t="n">
-        <v>86</v>
+        <v>87.12</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J8" t="n">
-        <v>2.71</v>
+        <v>3.25</v>
       </c>
       <c r="K8" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="L8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="M8" t="n">
-        <v>48.86</v>
+        <v>48.38</v>
       </c>
       <c r="N8" t="n">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="O8" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="P8" t="n">
-        <v>13.57</v>
+        <v>13.75</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.71</v>
+        <v>11.25</v>
       </c>
       <c r="R8" t="n">
-        <v>6.14</v>
+        <v>7</v>
       </c>
       <c r="S8" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="T8" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.43</v>
+        <v>51.88</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>12.25</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.57</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.71</v>
+        <v>21</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.71</v>
+        <v>3.12</v>
       </c>
       <c r="AF8" t="n">
         <v>0.14</v>
@@ -3964,70 +3964,70 @@
         <v>2.43</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.140000000000001</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.79</v>
+        <v>1.73</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>3.87</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.07</v>
+        <v>4.93</v>
       </c>
       <c r="BR8" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS8" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT8" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU8" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BV8" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW8" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX8" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.28</v>
+        <v>2.37</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.36</v>
+        <v>2.49</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CC8" t="n">
         <v>3.21</v>
@@ -4039,40 +4039,40 @@
         <v>1.3</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.22</v>
+        <v>3.19</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK8" t="n">
         <v>1.4</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.07</v>
+        <v>2.05</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="CR8" t="n">
         <v>1.38</v>
@@ -4087,73 +4087,73 @@
         <v>1.55</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.52</v>
+        <v>2.49</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.09</v>
+        <v>2.07</v>
       </c>
       <c r="DB8" t="n">
         <v>1.21</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="DE8" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="DH8" t="n">
-        <v>91.84999999999999</v>
+        <v>92.06</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.64</v>
+        <v>2.93</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.08</v>
+        <v>3.87</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.08</v>
+        <v>46</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.22</v>
+        <v>1.34</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.57</v>
+        <v>12.73</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.92</v>
+        <v>11.67</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.71</v>
+        <v>8.07</v>
       </c>
       <c r="DS8" t="n">
         <v>0.07000000000000001</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.43</v>
+        <v>48.87</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.93</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.57</v>
+        <v>3.4</v>
       </c>
       <c r="EA8" t="n">
-        <v>21</v>
+        <v>20.67</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.57</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="9">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C10" t="n">
         <v>7</v>
       </c>
       <c r="D10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,139 +4689,139 @@
         <v>1.86</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AI10" t="n">
-        <v>104.86</v>
+        <v>103.25</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.86</v>
+        <v>4.5</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN10" t="n">
-        <v>50.86</v>
+        <v>47.25</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.29</v>
+        <v>13.75</v>
       </c>
       <c r="AR10" t="n">
-        <v>14</v>
+        <v>13.88</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.57</v>
+        <v>6.88</v>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>57.86</v>
+        <v>56.12</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>14</v>
+        <v>12.75</v>
       </c>
       <c r="BB10" t="n">
-        <v>8.140000000000001</v>
+        <v>7.38</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.86</v>
+        <v>5.38</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.43</v>
+        <v>19.38</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.67</v>
+        <v>1.53</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.57</v>
+        <v>9.4</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.21</v>
+        <v>3.27</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BM10" t="n">
         <v>1</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.07</v>
+        <v>4.13</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.5</v>
+        <v>5.27</v>
       </c>
       <c r="BR10" t="n">
         <v>100</v>
       </c>
       <c r="BS10" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BU10" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY10" t="n">
         <v>1.89</v>
@@ -4833,19 +4833,19 @@
         <v>3.67</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.48</v>
+        <v>2.38</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.55</v>
+        <v>2.45</v>
       </c>
       <c r="CE10" t="n">
         <v>1.3</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CG10" t="n">
         <v>3.28</v>
@@ -4860,16 +4860,16 @@
         <v>1.56</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.99</v>
+        <v>2.96</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
@@ -4878,7 +4878,7 @@
         <v>1.64</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
@@ -4887,108 +4887,112 @@
         <v>2.49</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CU10" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="CV10" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="CW10" t="n">
         <v>1.58</v>
       </c>
-      <c r="CV10" t="n">
-        <v>2.49</v>
-      </c>
-      <c r="CW10" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CX10" t="inlineStr"/>
+      <c r="CX10" t="n">
+        <v>1.51</v>
+      </c>
       <c r="CY10" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CZ10" t="inlineStr"/>
+        <v>1.67</v>
+      </c>
+      <c r="CZ10" t="n">
+        <v>2.47</v>
+      </c>
       <c r="DA10" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="DB10" t="n">
         <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="DH10" t="n">
-        <v>107.08</v>
+        <v>106.07</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.72</v>
+        <v>5.47</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM10" t="n">
-        <v>55.5</v>
+        <v>53.27</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.72</v>
+        <v>13.93</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.64</v>
+        <v>13.6</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.64</v>
+        <v>6.8</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>57.86</v>
+        <v>56.93</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>15.78</v>
+        <v>15</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.92</v>
+        <v>9.4</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.86</v>
+        <v>5.6</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.72</v>
+        <v>19.67</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.81</v>
+        <v>1.73</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="11">
@@ -7807,10 +7811,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D18" t="n">
         <v>7</v>
@@ -7819,82 +7823,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="H18" t="n">
-        <v>89.14</v>
+        <v>89.25</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J18" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="K18" t="n">
-        <v>4.14</v>
+        <v>4.25</v>
       </c>
       <c r="L18" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M18" t="n">
-        <v>37.86</v>
+        <v>37.62</v>
       </c>
       <c r="N18" t="n">
         <v>1</v>
       </c>
       <c r="O18" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="P18" t="n">
-        <v>15.57</v>
+        <v>15.25</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>15.12</v>
       </c>
       <c r="R18" t="n">
-        <v>7</v>
+        <v>6.75</v>
       </c>
       <c r="S18" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="T18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="U18" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V18" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>55.43</v>
+        <v>55.5</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>11.71</v>
+        <v>12.38</v>
       </c>
       <c r="AA18" t="n">
-        <v>7.57</v>
+        <v>8.25</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.14</v>
+        <v>4.12</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.14</v>
+        <v>21.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7978,70 +7982,70 @@
         <v>3.86</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.640000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.64</v>
+        <v>1.73</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.36</v>
+        <v>4.4</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.29</v>
+        <v>5.07</v>
       </c>
       <c r="BR18" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS18" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT18" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>28.57</v>
+        <v>33.33</v>
       </c>
       <c r="BV18" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.57</v>
+        <v>2.68</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.76</v>
+        <v>2.97</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.5</v>
+        <v>3.52</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CC18" t="n">
         <v>3.37</v>
@@ -8053,64 +8057,64 @@
         <v>1.35</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.04</v>
+        <v>3.06</v>
       </c>
       <c r="CH18" t="n">
         <v>1.45</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.63</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CN18" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.77</v>
+        <v>2.75</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.16</v>
+        <v>3.18</v>
       </c>
       <c r="CU18" t="n">
         <v>1.48</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CW18" t="n">
         <v>1.67</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.43</v>
@@ -8122,85 +8126,85 @@
         <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DG18" t="n">
         <v>1.93</v>
       </c>
       <c r="DH18" t="n">
-        <v>86.42</v>
+        <v>86.66</v>
       </c>
       <c r="DI18" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.42</v>
+        <v>3.47</v>
       </c>
       <c r="DK18" t="n">
-        <v>4</v>
+        <v>4.07</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM18" t="n">
-        <v>34.21</v>
+        <v>34.33</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.64</v>
+        <v>14.53</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.43</v>
+        <v>15.47</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.43</v>
+        <v>7.27</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>58.22</v>
+        <v>58.07</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX18" t="n">
-        <v>11.71</v>
+        <v>12.07</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.5</v>
+        <v>7.87</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.22</v>
+        <v>4.2</v>
       </c>
       <c r="EA18" t="n">
-        <v>21</v>
+        <v>21.07</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="EC18" t="n">
-        <v>3.14</v>
+        <v>3.2</v>
       </c>
     </row>
     <row r="19">
@@ -8210,13 +8214,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C19" t="n">
         <v>7</v>
       </c>
       <c r="D19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E19" t="n">
         <v>0.29</v>
@@ -8300,127 +8304,127 @@
         <v>2.71</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG19" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AI19" t="n">
-        <v>103.57</v>
+        <v>104.62</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK19" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.71</v>
+        <v>4.62</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN19" t="n">
-        <v>46.43</v>
+        <v>46.25</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AQ19" t="n">
-        <v>15.29</v>
+        <v>14.38</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.57</v>
+        <v>11</v>
       </c>
       <c r="AS19" t="n">
-        <v>4.86</v>
+        <v>5.25</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>37.86</v>
+        <v>38.75</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.140000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.29</v>
+        <v>4.62</v>
       </c>
       <c r="BD19" t="n">
-        <v>21.43</v>
+        <v>22.12</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="BF19" t="n">
-        <v>3.29</v>
+        <v>3</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BH19" t="n">
-        <v>10.29</v>
+        <v>9.93</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BN19" t="n">
         <v>1</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.79</v>
+        <v>4.6</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.43</v>
+        <v>5.27</v>
       </c>
       <c r="BR19" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS19" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BT19" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8432,7 +8436,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BY19" t="n">
         <v>2.38</v>
@@ -8447,19 +8451,19 @@
         <v>3.56</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.78</v>
+        <v>2.71</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF19" t="n">
         <v>2.6</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CH19" t="n">
         <v>1.45</v>
@@ -8471,16 +8475,16 @@
         <v>1.62</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO19" t="n">
         <v>1.23</v>
@@ -8489,7 +8493,7 @@
         <v>1.74</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
@@ -8504,106 +8508,106 @@
         <v>1.49</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="DB19" t="n">
         <v>1.25</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD19" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.72</v>
+        <v>2.67</v>
       </c>
       <c r="DH19" t="n">
-        <v>102.86</v>
+        <v>103.46</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ19" t="n">
-        <v>3.08</v>
+        <v>2.93</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.29</v>
+        <v>5.2</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM19" t="n">
-        <v>49.28</v>
+        <v>49</v>
       </c>
       <c r="DN19" t="n">
         <v>0.93</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="DP19" t="n">
-        <v>14.08</v>
+        <v>13.67</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.36</v>
+        <v>11.53</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.14</v>
+        <v>5.33</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.22</v>
+        <v>0.27</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>40.79</v>
+        <v>41.06</v>
       </c>
       <c r="DW19" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.14</v>
+        <v>13.13</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.57</v>
+        <v>8.4</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.58</v>
+        <v>4.73</v>
       </c>
       <c r="EA19" t="n">
-        <v>21</v>
+        <v>21.4</v>
       </c>
       <c r="EB19" t="n">
         <v>1.52</v>
       </c>
       <c r="EC19" t="n">
-        <v>3</v>
+        <v>2.86</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C2" t="n">
         <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E2" t="n">
         <v>0.12</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.83</v>
+        <v>4.43</v>
       </c>
       <c r="AI2" t="n">
-        <v>99.17</v>
+        <v>96.14</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="AL2" t="n">
-        <v>7.17</v>
+        <v>6.86</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="AN2" t="n">
-        <v>55.83</v>
+        <v>52.57</v>
       </c>
       <c r="AO2" t="n">
-        <v>1</v>
+        <v>0.86</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.33</v>
+        <v>2.43</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.67</v>
+        <v>12.57</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.83</v>
+        <v>15.86</v>
       </c>
       <c r="AS2" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>50.43</v>
+      </c>
+      <c r="AZ2" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="BA2" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="BB2" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="BC2" t="n">
+        <v>3.57</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>23.57</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="BF2" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BG2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BH2" t="n">
+        <v>11.33</v>
+      </c>
+      <c r="BI2" t="n">
+        <v>3.27</v>
+      </c>
+      <c r="BJ2" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="BK2" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>4.27</v>
+      </c>
+      <c r="BQ2" t="n">
         <v>7</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>2</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>49</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="BA2" t="n">
-        <v>13.17</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>10</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="BD2" t="n">
-        <v>23.33</v>
-      </c>
-      <c r="BE2" t="n">
-        <v>1.46</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="BH2" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BI2" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="BJ2" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="BK2" t="n">
-        <v>0.86</v>
-      </c>
-      <c r="BL2" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="BM2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="BN2" t="n">
-        <v>2</v>
-      </c>
-      <c r="BO2" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="BP2" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="BQ2" t="n">
-        <v>7.14</v>
       </c>
       <c r="BR2" t="n">
         <v>100</v>
       </c>
       <c r="BS2" t="n">
-        <v>100</v>
+        <v>93.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BU2" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW2" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>64.29000000000001</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
         <v>2.17</v>
@@ -1610,16 +1610,16 @@
         <v>2.26</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.76</v>
+        <v>3.73</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.55</v>
+        <v>3.43</v>
       </c>
       <c r="CE2" t="n">
         <v>1.29</v>
@@ -1631,7 +1631,7 @@
         <v>3.28</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI2" t="n">
         <v>2.39</v>
@@ -1643,13 +1643,13 @@
         <v>1.36</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.73</v>
+        <v>2.77</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
       <c r="CO2" t="n">
         <v>1.17</v>
@@ -1658,7 +1658,7 @@
         <v>1.61</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1676,103 +1676,103 @@
         <v>2.54</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CX2" t="n">
         <v>1.48</v>
       </c>
       <c r="CY2" t="n">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="CZ2" t="n">
         <v>2.52</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.17</v>
+        <v>2.2</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.29</v>
+        <v>4.14</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.64</v>
+        <v>99.13</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.72</v>
+        <v>49.54</v>
       </c>
       <c r="DN2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.72</v>
+        <v>12.67</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14.64</v>
+        <v>15.13</v>
       </c>
       <c r="DR2" t="n">
-        <v>8</v>
+        <v>7.67</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.36</v>
+        <v>0.34</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.5</v>
+        <v>52</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.64</v>
+        <v>13.73</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.779999999999999</v>
+        <v>9.73</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.86</v>
+        <v>4</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.07</v>
+        <v>24.13</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C3" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D3" t="n">
         <v>8</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>2.57</v>
       </c>
       <c r="G3" t="n">
-        <v>3.17</v>
+        <v>3.14</v>
       </c>
       <c r="H3" t="n">
-        <v>109.33</v>
+        <v>108</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="K3" t="n">
-        <v>7</v>
+        <v>6.57</v>
       </c>
       <c r="L3" t="n">
-        <v>0.83</v>
+        <v>0.71</v>
       </c>
       <c r="M3" t="n">
-        <v>64</v>
+        <v>60.14</v>
       </c>
       <c r="N3" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="O3" t="n">
+        <v>3.43</v>
+      </c>
+      <c r="P3" t="n">
+        <v>16.43</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>10.43</v>
+      </c>
+      <c r="R3" t="n">
+        <v>8.57</v>
+      </c>
+      <c r="S3" t="n">
         <v>1</v>
       </c>
-      <c r="O3" t="n">
-        <v>3.83</v>
-      </c>
-      <c r="P3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>10.17</v>
-      </c>
-      <c r="R3" t="n">
-        <v>8.5</v>
-      </c>
-      <c r="S3" t="n">
-        <v>1.17</v>
-      </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>48.83</v>
+        <v>47.71</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>19</v>
+        <v>17.86</v>
       </c>
       <c r="AA3" t="n">
-        <v>14</v>
+        <v>12.86</v>
       </c>
       <c r="AB3" t="n">
         <v>5</v>
       </c>
       <c r="AC3" t="n">
-        <v>19.67</v>
+        <v>21.43</v>
       </c>
       <c r="AD3" t="n">
-        <v>2.01</v>
+        <v>1.91</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.5</v>
+        <v>3.71</v>
       </c>
       <c r="AF3" t="n">
         <v>0.25</v>
@@ -1953,70 +1953,70 @@
         <v>3.5</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="BH3" t="n">
-        <v>13.29</v>
+        <v>13</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
         <v>1.07</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.21</v>
+        <v>1.13</v>
       </c>
       <c r="BP3" t="n">
-        <v>6.43</v>
+        <v>6.27</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.86</v>
+        <v>6.73</v>
       </c>
       <c r="BR3" t="n">
         <v>100</v>
       </c>
       <c r="BS3" t="n">
-        <v>85.70999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV3" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CC3" t="n">
         <v>2.84</v>
@@ -2037,22 +2037,22 @@
         <v>1.53</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.53</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="CL3" t="n">
         <v>1.64</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CO3" t="n">
         <v>1.19</v>
@@ -2061,7 +2061,7 @@
         <v>1.62</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
@@ -2083,95 +2083,95 @@
       </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CZ3" t="inlineStr"/>
       <c r="DA3" t="n">
-        <v>2.25</v>
+        <v>2.28</v>
       </c>
       <c r="DB3" t="n">
         <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.36</v>
+        <v>2.4</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="DH3" t="n">
-        <v>94</v>
+        <v>94.40000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="DK3" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DM3" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.71</v>
+        <v>3.53</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.5</v>
+        <v>14.07</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.43</v>
+        <v>9.6</v>
       </c>
       <c r="DR3" t="n">
         <v>9.07</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.42</v>
+        <v>46.06</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.43</v>
+        <v>15.13</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.5</v>
+        <v>11.13</v>
       </c>
       <c r="DZ3" t="n">
-        <v>3.93</v>
+        <v>4</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.14</v>
+        <v>22.8</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
     </row>
     <row r="4">
@@ -2181,94 +2181,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F4" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="G4" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H4" t="n">
-        <v>84.56999999999999</v>
+        <v>85.88</v>
       </c>
       <c r="I4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="J4" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="K4" t="n">
-        <v>5</v>
+        <v>5.38</v>
       </c>
       <c r="L4" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>51.14</v>
+        <v>49.75</v>
       </c>
       <c r="N4" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.14</v>
+        <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>13.14</v>
+        <v>12.25</v>
       </c>
       <c r="Q4" t="n">
-        <v>13</v>
+        <v>12.62</v>
       </c>
       <c r="R4" t="n">
-        <v>8.289999999999999</v>
+        <v>7.88</v>
       </c>
       <c r="S4" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="T4" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>51</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>15.88</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>9.380000000000001</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>18.75</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AE4" t="n">
         <v>2</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>50</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>14.57</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>2.14</v>
       </c>
       <c r="AF4" t="n">
         <v>0.14</v>
@@ -2352,70 +2352,70 @@
         <v>1.14</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="BH4" t="n">
-        <v>9.640000000000001</v>
+        <v>10.13</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.86</v>
+        <v>0.93</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.57</v>
+        <v>1.67</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.79</v>
+        <v>4.87</v>
       </c>
       <c r="BQ4" t="n">
-        <v>4.86</v>
+        <v>5.27</v>
       </c>
       <c r="BR4" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BS4" t="n">
-        <v>64.29000000000001</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU4" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV4" t="n">
-        <v>21.43</v>
+        <v>26.67</v>
       </c>
       <c r="BW4" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.85</v>
+        <v>3.87</v>
       </c>
       <c r="CC4" t="n">
         <v>2.87</v>
@@ -2430,13 +2430,13 @@
         <v>2.36</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CH4" t="n">
         <v>1.55</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.56</v>
@@ -2451,7 +2451,7 @@
         <v>2.68</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO4" t="n">
         <v>1.17</v>
@@ -2460,7 +2460,7 @@
         <v>1.6</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
@@ -2478,7 +2478,7 @@
         <v>2.48</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX4" t="n">
         <v>1.46</v>
@@ -2502,46 +2502,46 @@
         <v>2.6</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.36</v>
+        <v>1.27</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="DH4" t="n">
-        <v>87.22</v>
+        <v>87.73999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.65</v>
+        <v>4.87</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="DM4" t="n">
-        <v>44</v>
+        <v>43.73</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.36</v>
+        <v>2.53</v>
       </c>
       <c r="DP4" t="n">
-        <v>13.07</v>
+        <v>12.6</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.289999999999999</v>
+        <v>9</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2553,28 +2553,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.78</v>
+        <v>51.27</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.86</v>
+        <v>14.6</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.57</v>
+        <v>9</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.29</v>
+        <v>5.6</v>
       </c>
       <c r="EA4" t="n">
-        <v>19.29</v>
+        <v>19</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.56</v>
+        <v>1.63</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.64</v>
+        <v>1.6</v>
       </c>
     </row>
     <row r="5">
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" t="n">
         <v>7</v>
       </c>
       <c r="D5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E5" t="n">
         <v>0.14</v>
@@ -2674,52 +2674,52 @@
         <v>1.71</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.29</v>
+        <v>3.12</v>
       </c>
       <c r="AI5" t="n">
-        <v>95.56999999999999</v>
+        <v>95.62</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.71</v>
+        <v>5.38</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>51.14</v>
+        <v>49</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ5" t="n">
-        <v>12.14</v>
+        <v>11.75</v>
       </c>
       <c r="AR5" t="n">
-        <v>12</v>
+        <v>11.88</v>
       </c>
       <c r="AS5" t="n">
-        <v>9.43</v>
+        <v>8.75</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2731,82 +2731,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.57</v>
+        <v>49.88</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.71</v>
+        <v>14</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.57</v>
+        <v>10.12</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.14</v>
+        <v>21.25</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.59</v>
+        <v>1.51</v>
       </c>
       <c r="BF5" t="n">
-        <v>2</v>
+        <v>2.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.71</v>
+        <v>10.67</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.29</v>
+        <v>3.33</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.93</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.29</v>
+        <v>1.4</v>
       </c>
       <c r="BO5" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.43</v>
+        <v>4.6</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.29</v>
+        <v>6.07</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BT5" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BU5" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW5" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX5" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BY5" t="n">
         <v>2.59</v>
@@ -2815,22 +2815,22 @@
         <v>2.66</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CB5" t="n">
         <v>3.72</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="CE5" t="n">
         <v>1.3</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="CG5" t="n">
         <v>3.29</v>
@@ -2845,25 +2845,25 @@
         <v>1.55</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="CN5" t="n">
         <v>2.18</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="CP5" t="n">
         <v>1.64</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CR5" t="n">
         <v>1.35</v>
@@ -2902,49 +2902,49 @@
         <v>1.68</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.43</v>
+        <v>1.53</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.08</v>
+        <v>3</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.36</v>
+        <v>91.66</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.29</v>
+        <v>5.14</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.36</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>48.14</v>
+        <v>47.2</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.22</v>
+        <v>2.13</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.72</v>
+        <v>11.54</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.57</v>
+        <v>12.47</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS5" t="n">
         <v>0.07000000000000001</v>
@@ -2956,28 +2956,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49</v>
+        <v>49.67</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.36</v>
+        <v>13.07</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.779999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.57</v>
+        <v>3.47</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.78</v>
+        <v>21.8</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D6" t="n">
         <v>7</v>
@@ -2999,13 +2999,13 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="G6" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="H6" t="n">
-        <v>94.86</v>
+        <v>92.88</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
@@ -3014,67 +3014,67 @@
         <v>3</v>
       </c>
       <c r="K6" t="n">
-        <v>4.43</v>
+        <v>4.12</v>
       </c>
       <c r="L6" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M6" t="n">
-        <v>32.57</v>
+        <v>34.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="O6" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
         <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.57</v>
+        <v>13.88</v>
       </c>
       <c r="R6" t="n">
-        <v>8.43</v>
+        <v>8.5</v>
       </c>
       <c r="S6" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="T6" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="U6" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>40</v>
+        <v>39.62</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="Z6" t="n">
-        <v>11.86</v>
+        <v>12.88</v>
       </c>
       <c r="AA6" t="n">
-        <v>8</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.86</v>
+        <v>3.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>20</v>
+        <v>20.38</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.26</v>
+        <v>1.33</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.57</v>
+        <v>2.38</v>
       </c>
       <c r="AF6" t="n">
         <v>0</v>
@@ -3158,70 +3158,70 @@
         <v>2.43</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.86</v>
+        <v>10.53</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.79</v>
+        <v>2.73</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.79</v>
+        <v>0.73</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.43</v>
+        <v>1.33</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.79</v>
+        <v>4.6</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6.07</v>
+        <v>5.93</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.14</v>
+        <v>53.33</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>14.29</v>
+        <v>13.33</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.13</v>
+        <v>3.07</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.26</v>
+        <v>3.19</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.81</v>
+        <v>3.78</v>
       </c>
       <c r="CC6" t="n">
         <v>4.32</v>
@@ -3233,16 +3233,16 @@
         <v>1.32</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CH6" t="n">
         <v>1.49</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.62</v>
@@ -3251,37 +3251,37 @@
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO6" t="n">
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CR6" t="n">
         <v>1.36</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CW6" t="n">
         <v>1.64</v>
@@ -3296,28 +3296,28 @@
         <v>2.56</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB6" t="n">
         <v>1.22</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="DE6" t="n">
         <v>0</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.14</v>
+        <v>2.06</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.64</v>
+        <v>2.53</v>
       </c>
       <c r="DH6" t="n">
-        <v>95.64</v>
+        <v>94.54000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
@@ -3326,61 +3326,61 @@
         <v>3.14</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.65</v>
+        <v>4.47</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM6" t="n">
-        <v>37.79</v>
+        <v>38.6</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO6" t="n">
-        <v>2</v>
+        <v>1.93</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.64</v>
+        <v>12.67</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.36</v>
+        <v>14.47</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.220000000000001</v>
+        <v>8.27</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.64</v>
+        <v>42.27</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DX6" t="n">
-        <v>12</v>
+        <v>12.53</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.07</v>
+        <v>8.66</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.93</v>
+        <v>3.87</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.14</v>
+        <v>20.34</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
     </row>
     <row r="7">
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="n">
         <v>7</v>
       </c>
       <c r="D7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E7" t="n">
         <v>0.14</v>
@@ -3480,52 +3480,52 @@
         <v>1.86</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="AI7" t="n">
-        <v>96.43000000000001</v>
+        <v>95.88</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.57</v>
+        <v>7</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AN7" t="n">
-        <v>45.14</v>
+        <v>44.88</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.43</v>
+        <v>3.75</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.86</v>
+        <v>10.12</v>
       </c>
       <c r="AR7" t="n">
-        <v>15.57</v>
+        <v>16</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.86</v>
+        <v>6.5</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AV7" t="n">
         <v>0</v>
@@ -3537,82 +3537,82 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>55.43</v>
+        <v>54.88</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA7" t="n">
-        <v>15.57</v>
+        <v>15.62</v>
       </c>
       <c r="BB7" t="n">
-        <v>10.86</v>
+        <v>10.88</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.71</v>
+        <v>4.75</v>
       </c>
       <c r="BD7" t="n">
-        <v>23</v>
+        <v>22.25</v>
       </c>
       <c r="BE7" t="n">
         <v>1.64</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.79</v>
+        <v>10.93</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BL7" t="n">
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP7" t="n">
-        <v>4.79</v>
+        <v>5.07</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.86</v>
+        <v>4.8</v>
       </c>
       <c r="BR7" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS7" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU7" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BV7" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BW7" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX7" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BY7" t="n">
         <v>1.98</v>
@@ -3624,10 +3624,10 @@
         <v>3.55</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.12</v>
+        <v>2.21</v>
       </c>
       <c r="CD7" t="n">
         <v>2.66</v>
@@ -3639,7 +3639,7 @@
         <v>2.45</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CH7" t="n">
         <v>1.53</v>
@@ -3654,19 +3654,19 @@
         <v>1.36</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.81</v>
+        <v>2.83</v>
       </c>
       <c r="CN7" t="n">
         <v>2.16</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ7" t="n">
         <v>2.57</v>
@@ -3699,7 +3699,7 @@
         <v>2.61</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DB7" t="n">
         <v>1.22</v>
@@ -3708,49 +3708,49 @@
         <v>1.71</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.78</v>
+        <v>1.73</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.28</v>
+        <v>2.4</v>
       </c>
       <c r="DH7" t="n">
-        <v>95.28</v>
+        <v>95.06999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.36</v>
+        <v>2.27</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.07</v>
+        <v>6.33</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.28</v>
+        <v>0.33</v>
       </c>
       <c r="DM7" t="n">
-        <v>49.42</v>
+        <v>49</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.93</v>
+        <v>3.13</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.72</v>
+        <v>11.26</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.57</v>
+        <v>14.87</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.79</v>
+        <v>6.6</v>
       </c>
       <c r="DS7" t="n">
         <v>0.07000000000000001</v>
@@ -3762,28 +3762,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.36</v>
+        <v>54.14</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.5</v>
+        <v>15.53</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.43</v>
+        <v>10.47</v>
       </c>
       <c r="DZ7" t="n">
         <v>5.07</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.86</v>
+        <v>22.46</v>
       </c>
       <c r="EB7" t="n">
         <v>1.69</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="8">
@@ -4075,16 +4075,16 @@
         <v>2.54</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.15</v>
+        <v>3.11</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV8" t="n">
         <v>2.47</v>
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C9" t="n">
         <v>7</v>
       </c>
       <c r="D9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E9" t="n">
         <v>0.29</v>
@@ -4289,136 +4289,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.14</v>
+        <v>1.25</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.57</v>
+        <v>2.25</v>
       </c>
       <c r="AI9" t="n">
-        <v>67.70999999999999</v>
+        <v>66.25</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN9" t="n">
-        <v>35.43</v>
+        <v>32.88</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.71</v>
+        <v>14.12</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.86</v>
+        <v>11.88</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.140000000000001</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT9" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.57</v>
+        <v>13</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.86</v>
+        <v>7.38</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>24.43</v>
+        <v>23.88</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.51</v>
+        <v>1.45</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="BG9" t="n">
         <v>4.07</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.64</v>
+        <v>10.47</v>
       </c>
       <c r="BI9" t="n">
         <v>4.07</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.64</v>
+        <v>0.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.57</v>
+        <v>1.47</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.57</v>
+        <v>4.47</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6.07</v>
+        <v>6</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BT9" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BU9" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BV9" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BW9" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BX9" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
         <v>2.63</v>
@@ -4427,16 +4427,16 @@
         <v>3.11</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="CB9" t="n">
         <v>4</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.23</v>
+        <v>5.16</v>
       </c>
       <c r="CE9" t="n">
         <v>1.28</v>
@@ -4445,67 +4445,67 @@
         <v>2.3</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="CH9" t="n">
         <v>1.57</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.54</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP9" t="n">
         <v>1.58</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CT9" t="n">
         <v>3.28</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX9" t="n">
         <v>1.47</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.58</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="DB9" t="n">
         <v>1.19</v>
@@ -4514,82 +4514,82 @@
         <v>1.62</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DE9" t="n">
         <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1</v>
+        <v>1.07</v>
       </c>
       <c r="DG9" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.78</v>
+        <v>78.2</v>
       </c>
       <c r="DI9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.28</v>
+        <v>2.33</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.78</v>
+        <v>4.67</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM9" t="n">
-        <v>36</v>
+        <v>34.6</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.78</v>
+        <v>1.86</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.71</v>
+        <v>12.06</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.14</v>
+        <v>13.07</v>
       </c>
       <c r="DR9" t="n">
-        <v>7.86</v>
+        <v>8.27</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.64</v>
+        <v>45.14</v>
       </c>
       <c r="DW9" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.22</v>
+        <v>12</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.72</v>
+        <v>7.47</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.5</v>
+        <v>4.53</v>
       </c>
       <c r="EA9" t="n">
-        <v>23</v>
+        <v>22.8</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D11" t="n">
         <v>7</v>
@@ -5014,82 +5014,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="G11" t="n">
-        <v>2.43</v>
+        <v>2.88</v>
       </c>
       <c r="H11" t="n">
-        <v>92.86</v>
+        <v>93.75</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="J11" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="K11" t="n">
-        <v>5.14</v>
+        <v>5.38</v>
       </c>
       <c r="L11" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M11" t="n">
-        <v>43.71</v>
+        <v>44.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.71</v>
+        <v>2.5</v>
       </c>
       <c r="P11" t="n">
-        <v>12.71</v>
+        <v>13.12</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.859999999999999</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="R11" t="n">
-        <v>9.57</v>
+        <v>10</v>
       </c>
       <c r="S11" t="n">
-        <v>0.71</v>
+        <v>0.88</v>
       </c>
       <c r="T11" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="U11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>46.86</v>
+        <v>47.12</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z11" t="n">
-        <v>12</v>
+        <v>12.88</v>
       </c>
       <c r="AA11" t="n">
-        <v>7.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.86</v>
+        <v>18.62</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.39</v>
+        <v>1.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.29</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
         <v>0.14</v>
@@ -5176,67 +5176,67 @@
         <v>1.93</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.71</v>
+        <v>10.8</v>
       </c>
       <c r="BI11" t="n">
         <v>1.93</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="BP11" t="n">
         <v>4.93</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS11" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BT11" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV11" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW11" t="n">
         <v>0</v>
       </c>
       <c r="BX11" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BY11" t="n">
-        <v>2.01</v>
+        <v>1.99</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.93</v>
+        <v>1.91</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.82</v>
+        <v>3.83</v>
       </c>
       <c r="CC11" t="n">
         <v>2.87</v>
@@ -5251,13 +5251,13 @@
         <v>2.38</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.26</v>
+        <v>3.29</v>
       </c>
       <c r="CH11" t="n">
         <v>1.54</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.54</v>
@@ -5266,10 +5266,10 @@
         <v>1.36</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CN11" t="n">
         <v>2.19</v>
@@ -5281,25 +5281,25 @@
         <v>1.63</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CT11" t="n">
         <v>3.33</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX11" t="n">
         <v>1.44</v>
@@ -5311,91 +5311,91 @@
         <v>2.63</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="DE11" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.86</v>
+        <v>1.73</v>
       </c>
       <c r="DG11" t="n">
-        <v>2</v>
+        <v>2.27</v>
       </c>
       <c r="DH11" t="n">
-        <v>91.58</v>
+        <v>92.14</v>
       </c>
       <c r="DI11" t="n">
         <v>0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.72</v>
+        <v>2.53</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.42</v>
+        <v>4.6</v>
       </c>
       <c r="DL11" t="n">
         <v>0.14</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.5</v>
+        <v>44.87</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.86</v>
+        <v>0.8</v>
       </c>
       <c r="DO11" t="n">
-        <v>2</v>
+        <v>1.94</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.92</v>
+        <v>14.06</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.5</v>
+        <v>11.2</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.220000000000001</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.58</v>
+        <v>46.73</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>11.64</v>
+        <v>12.14</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.86</v>
+        <v>8.27</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.78</v>
+        <v>3.87</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.07</v>
+        <v>20.8</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.64</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="12">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5495,139 +5495,139 @@
         <v>1.71</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="AI12" t="n">
-        <v>82.29000000000001</v>
+        <v>83.88</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.57</v>
+        <v>3.75</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>36.43</v>
+        <v>36</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.29</v>
+        <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.29</v>
+        <v>13.25</v>
       </c>
       <c r="AS12" t="n">
-        <v>8.859999999999999</v>
+        <v>9</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>48.86</v>
+        <v>50.62</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.71</v>
+        <v>11.88</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.289999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.43</v>
+        <v>3.38</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.86</v>
+        <v>19</v>
       </c>
       <c r="BE12" t="n">
         <v>1.25</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.43</v>
+        <v>3.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.07</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.14</v>
+        <v>1.07</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.29</v>
+        <v>4.13</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.79</v>
+        <v>5.67</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>35.71</v>
+        <v>33.33</v>
       </c>
       <c r="BU12" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV12" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW12" t="n">
         <v>0</v>
       </c>
       <c r="BX12" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY12" t="n">
         <v>2.19</v>
@@ -5639,31 +5639,31 @@
         <v>3.56</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.72</v>
+        <v>2.7</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="CE12" t="n">
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CH12" t="n">
         <v>1.5</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK12" t="n">
         <v>1.34</v>
@@ -5675,34 +5675,34 @@
         <v>2.87</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO12" t="n">
         <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.61</v>
+        <v>2.65</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.55</v>
+        <v>2.59</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.35</v>
+        <v>3.31</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="CX12" t="n">
         <v>1.5</v>
@@ -5717,88 +5717,88 @@
         <v>2.16</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.73</v>
+        <v>2.78</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.86</v>
+        <v>1.93</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DH12" t="n">
-        <v>86.15000000000001</v>
+        <v>86.73999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.64</v>
+        <v>2.8</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.72</v>
+        <v>4.67</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="DM12" t="n">
-        <v>39.14</v>
+        <v>38.73</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.78</v>
+        <v>0.86</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DP12" t="n">
-        <v>14</v>
+        <v>14.2</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.22</v>
+        <v>14.13</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.640000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.86</v>
+        <v>51.67</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.86</v>
+        <v>12.87</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.859999999999999</v>
+        <v>8.93</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.5</v>
+        <v>19.07</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.57</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="13">
@@ -5808,94 +5808,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D13" t="n">
         <v>7</v>
       </c>
       <c r="E13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="F13" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="G13" t="n">
-        <v>2.86</v>
+        <v>2.62</v>
       </c>
       <c r="H13" t="n">
-        <v>107.57</v>
+        <v>105.88</v>
       </c>
       <c r="I13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J13" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="K13" t="n">
-        <v>6.29</v>
+        <v>6.38</v>
       </c>
       <c r="L13" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M13" t="n">
-        <v>52</v>
+        <v>49.62</v>
       </c>
       <c r="N13" t="n">
         <v>1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.14</v>
+        <v>2.62</v>
       </c>
       <c r="P13" t="n">
-        <v>12.14</v>
+        <v>12</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.71</v>
+        <v>13.12</v>
       </c>
       <c r="R13" t="n">
-        <v>8.140000000000001</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
       </c>
       <c r="T13" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="U13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>51.71</v>
+        <v>50.38</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>17.57</v>
+        <v>16.88</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.29</v>
+        <v>10.12</v>
       </c>
       <c r="AB13" t="n">
-        <v>7.29</v>
+        <v>6.75</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.14</v>
+        <v>22</v>
       </c>
       <c r="AD13" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,67 +5979,67 @@
         <v>3.14</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.640000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.93</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.07</v>
+        <v>1.13</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.79</v>
+        <v>1.87</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.57</v>
+        <v>4.73</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.14</v>
+        <v>4.07</v>
       </c>
       <c r="BR13" t="n">
         <v>100</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU13" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BV13" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.35</v>
+        <v>2.31</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CB13" t="n">
         <v>3.65</v>
@@ -6054,28 +6054,28 @@
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.56</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CN13" t="n">
         <v>2.19</v>
@@ -6087,7 +6087,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CR13" t="n">
         <v>1.36</v>
@@ -6111,7 +6111,7 @@
         <v>1.46</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.57</v>
@@ -6129,76 +6129,76 @@
         <v>2.7</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.58</v>
+        <v>2.47</v>
       </c>
       <c r="DH13" t="n">
-        <v>103.22</v>
+        <v>102.6</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DJ13" t="n">
         <v>3</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.36</v>
+        <v>5.47</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM13" t="n">
-        <v>45.86</v>
+        <v>45</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.14</v>
+        <v>2.4</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.57</v>
+        <v>12.47</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.92</v>
+        <v>13.6</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.57</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.64</v>
+        <v>49.07</v>
       </c>
       <c r="DW13" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.64</v>
+        <v>14.47</v>
       </c>
       <c r="DY13" t="n">
         <v>8.859999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.79</v>
+        <v>5.6</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.78</v>
+        <v>21.73</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="EC13" t="n">
         <v>2.86</v>
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C14" t="n">
         <v>7</v>
       </c>
       <c r="D14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E14" t="n">
         <v>0.14</v>
@@ -6301,16 +6301,16 @@
         <v>3.29</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH14" t="n">
-        <v>2.57</v>
+        <v>3.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>89.14</v>
+        <v>86.38</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
@@ -6319,34 +6319,34 @@
         <v>2</v>
       </c>
       <c r="AL14" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="AN14" t="n">
-        <v>38.86</v>
+        <v>39.38</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ14" t="n">
-        <v>12.14</v>
+        <v>11.88</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.710000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AS14" t="n">
-        <v>8.710000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="AU14" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6358,82 +6358,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>48.71</v>
+        <v>47.88</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>13.57</v>
+        <v>13.12</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.859999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.71</v>
+        <v>3.62</v>
       </c>
       <c r="BD14" t="n">
-        <v>17.57</v>
+        <v>18.25</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="BF14" t="n">
         <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.21</v>
+        <v>3.33</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.29</v>
+        <v>10.73</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.21</v>
+        <v>3.33</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.57</v>
+        <v>0.6</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.14</v>
+        <v>1.2</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.43</v>
+        <v>4.53</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.79</v>
+        <v>5.2</v>
       </c>
       <c r="BR14" t="n">
-        <v>85.70999999999999</v>
+        <v>86.67</v>
       </c>
       <c r="BS14" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT14" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BU14" t="n">
-        <v>42.86</v>
+        <v>46.67</v>
       </c>
       <c r="BV14" t="n">
-        <v>35.71</v>
+        <v>40</v>
       </c>
       <c r="BW14" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BY14" t="n">
         <v>2.33</v>
@@ -6442,22 +6442,22 @@
         <v>2.52</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.71</v>
+        <v>3.73</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.84</v>
+        <v>3.87</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.6</v>
+        <v>3.69</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.76</v>
+        <v>3.88</v>
       </c>
       <c r="CE14" t="n">
         <v>1.28</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CG14" t="n">
         <v>3.32</v>
@@ -6478,16 +6478,16 @@
         <v>1.68</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.19</v>
+        <v>2.17</v>
       </c>
       <c r="CO14" t="n">
         <v>1.16</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CQ14" t="n">
         <v>2.43</v>
@@ -6496,16 +6496,16 @@
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CT14" t="n">
         <v>3.31</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CW14" t="n">
         <v>1.56</v>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DB14" t="n">
         <v>1.19</v>
@@ -6528,46 +6528,46 @@
         <v>2.56</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.36</v>
+        <v>2.73</v>
       </c>
       <c r="DH14" t="n">
-        <v>85.92</v>
+        <v>84.67</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.21</v>
+        <v>5.47</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DM14" t="n">
-        <v>42</v>
+        <v>42.07</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.43</v>
+        <v>2.33</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.5</v>
+        <v>13.27</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.57</v>
+        <v>11.2</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.43</v>
+        <v>8.6</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>49.07</v>
+        <v>48.6</v>
       </c>
       <c r="DW14" t="n">
         <v>0</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.93</v>
+        <v>12.73</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.279999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.64</v>
+        <v>4.53</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.28</v>
+        <v>17.67</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C15" t="n">
         <v>7</v>
       </c>
       <c r="D15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6703,49 +6703,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="AI15" t="n">
-        <v>80</v>
+        <v>81.12</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.14</v>
+        <v>0.38</v>
       </c>
       <c r="AK15" t="n">
         <v>3</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.71</v>
+        <v>5.62</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AN15" t="n">
-        <v>38.57</v>
+        <v>39.75</v>
       </c>
       <c r="AO15" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.57</v>
+        <v>11</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.57</v>
+        <v>13.88</v>
       </c>
       <c r="AS15" t="n">
-        <v>7.43</v>
+        <v>8</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.57</v>
+        <v>0.75</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6757,82 +6757,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>56.14</v>
+        <v>55.5</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>16.57</v>
+        <v>16.75</v>
       </c>
       <c r="BB15" t="n">
-        <v>11.14</v>
+        <v>11.38</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.43</v>
+        <v>5.38</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.71</v>
+        <v>18</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="BF15" t="n">
         <v>3</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.36</v>
+        <v>10.47</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL15" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.71</v>
+        <v>0.8</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.14</v>
+        <v>5.13</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.21</v>
+        <v>5.33</v>
       </c>
       <c r="BR15" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS15" t="n">
-        <v>71.43000000000001</v>
+        <v>73.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>42.86</v>
+        <v>40</v>
       </c>
       <c r="BU15" t="n">
-        <v>21.43</v>
+        <v>20</v>
       </c>
       <c r="BV15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>28.57</v>
+        <v>26.67</v>
       </c>
       <c r="BY15" t="n">
         <v>2.22</v>
@@ -6841,16 +6841,16 @@
         <v>2.43</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.96</v>
+        <v>3.09</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.24</v>
+        <v>3.42</v>
       </c>
       <c r="CE15" t="n">
         <v>1.26</v>
@@ -6859,7 +6859,7 @@
         <v>2.27</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.41</v>
+        <v>3.43</v>
       </c>
       <c r="CH15" t="n">
         <v>1.61</v>
@@ -6874,10 +6874,10 @@
         <v>1.37</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CN15" t="n">
         <v>2.15</v>
@@ -6893,17 +6893,17 @@
       </c>
       <c r="CR15" t="inlineStr"/>
       <c r="CS15" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="n">
         <v>1.64</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CX15" t="n">
         <v>1.46</v>
@@ -6924,49 +6924,49 @@
         <v>1.56</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.86</v>
+        <v>2.73</v>
       </c>
       <c r="DH15" t="n">
-        <v>97.06999999999999</v>
+        <v>96.53</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="DJ15" t="n">
         <v>2.93</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.36</v>
+        <v>5.33</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.36</v>
+        <v>47.4</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.85</v>
+        <v>0.93</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.72</v>
+        <v>12.33</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.22</v>
+        <v>12.47</v>
       </c>
       <c r="DR15" t="n">
-        <v>6.64</v>
+        <v>7</v>
       </c>
       <c r="DS15" t="n">
         <v>0.07000000000000001</v>
@@ -6978,25 +6978,25 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.72</v>
+        <v>55.4</v>
       </c>
       <c r="DW15" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX15" t="n">
-        <v>16</v>
+        <v>16.13</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.92</v>
+        <v>11.07</v>
       </c>
       <c r="DZ15" t="n">
         <v>5.07</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.36</v>
+        <v>18.93</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="EC15" t="n">
         <v>2.86</v>
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D16" t="n">
         <v>7</v>
@@ -7021,82 +7021,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="G16" t="n">
-        <v>2.57</v>
+        <v>2.88</v>
       </c>
       <c r="H16" t="n">
-        <v>97.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="K16" t="n">
         <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M16" t="n">
-        <v>43.43</v>
+        <v>45.25</v>
       </c>
       <c r="N16" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O16" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="P16" t="n">
-        <v>11</v>
+        <v>11.12</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.14</v>
+        <v>14.5</v>
       </c>
       <c r="R16" t="n">
-        <v>8.710000000000001</v>
+        <v>7.88</v>
       </c>
       <c r="S16" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="T16" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="U16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>51.43</v>
+        <v>52.75</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.57</v>
+        <v>12.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.140000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.86</v>
+        <v>20.75</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="AF16" t="n">
         <v>0.14</v>
@@ -7180,70 +7180,70 @@
         <v>2.86</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.43</v>
+        <v>10.27</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.43</v>
+        <v>2.53</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.79</v>
+        <v>0.87</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.64</v>
+        <v>0.73</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.43</v>
+        <v>1.6</v>
       </c>
       <c r="BO16" t="n">
-        <v>1</v>
+        <v>0.93</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.86</v>
+        <v>4.73</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.57</v>
+        <v>5.53</v>
       </c>
       <c r="BR16" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS16" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BU16" t="n">
-        <v>7.14</v>
+        <v>13.33</v>
       </c>
       <c r="BV16" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.42</v>
+        <v>2.34</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.46</v>
+        <v>2.37</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.7</v>
+        <v>3.73</v>
       </c>
       <c r="CC16" t="n">
         <v>3</v>
@@ -7255,7 +7255,7 @@
         <v>1.31</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.43</v>
+        <v>2.41</v>
       </c>
       <c r="CG16" t="n">
         <v>3.27</v>
@@ -7276,16 +7276,16 @@
         <v>1.68</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CO16" t="n">
         <v>1.19</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ16" t="n">
         <v>2.6</v>
@@ -7303,7 +7303,7 @@
         <v>1.55</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CW16" t="n">
         <v>1.57</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="CZ16" t="inlineStr"/>
       <c r="DA16" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="DB16" t="n">
         <v>1.21</v>
@@ -7329,76 +7329,76 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.93</v>
+        <v>1.87</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>94</v>
+        <v>95.66</v>
       </c>
       <c r="DI16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DM16" t="n">
-        <v>45.5</v>
+        <v>46.33</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.57</v>
+        <v>2.4</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.5</v>
+        <v>12.46</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.92</v>
+        <v>14.13</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.359999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.64</v>
+        <v>50.47</v>
       </c>
       <c r="DW16" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.57</v>
+        <v>12.6</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.07</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="EA16" t="n">
-        <v>19.93</v>
+        <v>20.4</v>
       </c>
       <c r="EB16" t="n">
         <v>1.44</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.58</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="17">
@@ -7408,10 +7408,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D17" t="n">
         <v>7</v>
@@ -7420,82 +7420,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.86</v>
+        <v>1.38</v>
       </c>
       <c r="G17" t="n">
-        <v>3.86</v>
+        <v>3.38</v>
       </c>
       <c r="H17" t="n">
-        <v>94.86</v>
+        <v>93.88</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="K17" t="n">
+        <v>6.25</v>
+      </c>
+      <c r="L17" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="M17" t="n">
+        <v>48.88</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="O17" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="P17" t="n">
+        <v>13.25</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>10.12</v>
+      </c>
+      <c r="R17" t="n">
+        <v>8.5</v>
+      </c>
+      <c r="S17" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="V17" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="W17" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" t="n">
+        <v>53.75</v>
+      </c>
+      <c r="Y17" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="Z17" t="n">
+        <v>16.25</v>
+      </c>
+      <c r="AA17" t="n">
+        <v>10.62</v>
+      </c>
+      <c r="AB17" t="n">
+        <v>5.62</v>
+      </c>
+      <c r="AC17" t="n">
+        <v>21.62</v>
+      </c>
+      <c r="AD17" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AE17" t="n">
         <v>2</v>
-      </c>
-      <c r="K17" t="n">
-        <v>6.71</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="M17" t="n">
-        <v>49.71</v>
-      </c>
-      <c r="N17" t="n">
-        <v>1</v>
-      </c>
-      <c r="O17" t="n">
-        <v>2.86</v>
-      </c>
-      <c r="P17" t="n">
-        <v>12.43</v>
-      </c>
-      <c r="Q17" t="n">
-        <v>10.86</v>
-      </c>
-      <c r="R17" t="n">
-        <v>8.43</v>
-      </c>
-      <c r="S17" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="T17" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="V17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="W17" t="n">
-        <v>0</v>
-      </c>
-      <c r="X17" t="n">
-        <v>54.43</v>
-      </c>
-      <c r="Y17" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="Z17" t="n">
-        <v>17.29</v>
-      </c>
-      <c r="AA17" t="n">
-        <v>11.29</v>
-      </c>
-      <c r="AB17" t="n">
-        <v>6</v>
-      </c>
-      <c r="AC17" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD17" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="AE17" t="n">
-        <v>1.71</v>
       </c>
       <c r="AF17" t="n">
         <v>0.29</v>
@@ -7579,70 +7579,70 @@
         <v>2.43</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.43</v>
+        <v>10.6</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.79</v>
+        <v>5.07</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.64</v>
+        <v>5.53</v>
       </c>
       <c r="BR17" t="n">
-        <v>92.86</v>
+        <v>93.33</v>
       </c>
       <c r="BS17" t="n">
-        <v>78.56999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT17" t="n">
-        <v>50</v>
+        <v>53.33</v>
       </c>
       <c r="BU17" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BV17" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BW17" t="n">
-        <v>7.14</v>
+        <v>6.67</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.14</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.85</v>
+        <v>1.89</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.89</v>
+        <v>1.98</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC17" t="n">
         <v>2.2</v>
@@ -7651,7 +7651,7 @@
         <v>2.27</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF17" t="n">
         <v>2.43</v>
@@ -7663,7 +7663,7 @@
         <v>1.52</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.59</v>
@@ -7672,16 +7672,16 @@
         <v>1.36</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP17" t="n">
         <v>1.66</v>
@@ -7699,10 +7699,10 @@
         <v>3.22</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CW17" t="n">
         <v>1.61</v>
@@ -7717,7 +7717,7 @@
         <v>2.58</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB17" t="n">
         <v>1.22</v>
@@ -7726,82 +7726,82 @@
         <v>1.71</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DE17" t="n">
         <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.21</v>
+        <v>1.47</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.08</v>
+        <v>2.87</v>
       </c>
       <c r="DH17" t="n">
-        <v>97</v>
+        <v>96.33</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.07000000000000001</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.22</v>
+        <v>2.47</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.5</v>
+        <v>5.34</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.78</v>
+        <v>0.73</v>
       </c>
       <c r="DM17" t="n">
-        <v>46.21</v>
+        <v>46</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.72</v>
+        <v>13.13</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.72</v>
+        <v>10.33</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.140000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>52.86</v>
+        <v>52.6</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.36</v>
+        <v>14.93</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.14</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.21</v>
+        <v>5.06</v>
       </c>
       <c r="EA17" t="n">
-        <v>21</v>
+        <v>21.33</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.67</v>
+        <v>1.63</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="18">
@@ -7883,10 +7883,10 @@
         <v>0.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.38</v>
+        <v>12.62</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.25</v>
+        <v>8.5</v>
       </c>
       <c r="AB18" t="n">
         <v>4.12</v>
@@ -7895,7 +7895,7 @@
         <v>21.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="AE18" t="n">
         <v>2.62</v>
@@ -8189,10 +8189,10 @@
         <v>0.13</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.07</v>
+        <v>12.2</v>
       </c>
       <c r="DY18" t="n">
-        <v>7.87</v>
+        <v>8</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.2</v>
@@ -8201,7 +8201,7 @@
         <v>21.07</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC18" t="n">
         <v>3.2</v>
@@ -8499,13 +8499,13 @@
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV19" t="n">
         <v>2.3</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1854,19 +1854,19 @@
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.86</v>
+        <v>18</v>
       </c>
       <c r="AA3" t="n">
         <v>12.86</v>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>5.14</v>
       </c>
       <c r="AC3" t="n">
         <v>21.43</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AE3" t="n">
         <v>3.71</v>
@@ -2156,19 +2156,19 @@
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.13</v>
+        <v>15.2</v>
       </c>
       <c r="DY3" t="n">
         <v>11.13</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="EA3" t="n">
         <v>22.8</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="EC3" t="n">
         <v>3.6</v>
@@ -2253,10 +2253,10 @@
         <v>0.12</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.88</v>
+        <v>15.75</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.380000000000001</v>
+        <v>9.25</v>
       </c>
       <c r="AB4" t="n">
         <v>6.5</v>
@@ -2559,10 +2559,10 @@
         <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.6</v>
+        <v>14.53</v>
       </c>
       <c r="DY4" t="n">
-        <v>9</v>
+        <v>8.93</v>
       </c>
       <c r="DZ4" t="n">
         <v>5.6</v>
@@ -3035,7 +3035,7 @@
         <v>13.88</v>
       </c>
       <c r="R6" t="n">
-        <v>8.5</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="S6" t="n">
         <v>1.88</v>
@@ -3347,7 +3347,7 @@
         <v>14.47</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.27</v>
+        <v>8.33</v>
       </c>
       <c r="DS6" t="n">
         <v>0.13</v>
@@ -4349,19 +4349,19 @@
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>13</v>
+        <v>13.12</v>
       </c>
       <c r="BB9" t="n">
         <v>7.38</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.62</v>
+        <v>5.75</v>
       </c>
       <c r="BD9" t="n">
         <v>23.88</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="BF9" t="n">
         <v>2.75</v>
@@ -4574,13 +4574,13 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="DX9" t="n">
-        <v>12</v>
+        <v>12.07</v>
       </c>
       <c r="DY9" t="n">
         <v>7.47</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.53</v>
+        <v>4.6</v>
       </c>
       <c r="EA9" t="n">
         <v>22.8</v>
@@ -5558,19 +5558,19 @@
         <v>0.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.88</v>
+        <v>11.62</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.5</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.38</v>
+        <v>3.25</v>
       </c>
       <c r="BD12" t="n">
         <v>19</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="BF12" t="n">
         <v>3.5</v>
@@ -5783,19 +5783,19 @@
         <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.87</v>
+        <v>12.73</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.93</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.94</v>
+        <v>3.87</v>
       </c>
       <c r="EA12" t="n">
         <v>19.07</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC12" t="n">
         <v>2.66</v>
@@ -7883,10 +7883,10 @@
         <v>0.12</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.62</v>
+        <v>12.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.5</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB18" t="n">
         <v>4.12</v>
@@ -7895,7 +7895,7 @@
         <v>21.25</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="AE18" t="n">
         <v>2.62</v>
@@ -8189,10 +8189,10 @@
         <v>0.13</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.2</v>
+        <v>12.26</v>
       </c>
       <c r="DY18" t="n">
-        <v>8</v>
+        <v>8.06</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.2</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -2584,94 +2584,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D5" t="n">
         <v>8</v>
       </c>
       <c r="E5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F5" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="G5" t="n">
-        <v>2.86</v>
+        <v>3.12</v>
       </c>
       <c r="H5" t="n">
-        <v>87.14</v>
+        <v>85</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="K5" t="n">
-        <v>4.86</v>
+        <v>5.12</v>
       </c>
       <c r="L5" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M5" t="n">
-        <v>45.14</v>
+        <v>43.62</v>
       </c>
       <c r="N5" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="O5" t="n">
         <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>11.29</v>
+        <v>10.88</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.14</v>
+        <v>13.12</v>
       </c>
       <c r="R5" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="S5" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="T5" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49.43</v>
+        <v>49.62</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z5" t="n">
-        <v>12</v>
+        <v>11.75</v>
       </c>
       <c r="AA5" t="n">
-        <v>9</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AB5" t="n">
-        <v>3</v>
+        <v>3.62</v>
       </c>
       <c r="AC5" t="n">
-        <v>22.43</v>
+        <v>21.62</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="AF5" t="n">
         <v>0.12</v>
@@ -2755,70 +2755,70 @@
         <v>2.25</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.67</v>
+        <v>10.94</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.33</v>
+        <v>3.44</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.4</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.6</v>
+        <v>4.81</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.07</v>
+        <v>6.12</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BT5" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BU5" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX5" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.59</v>
+        <v>2.54</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.65</v>
+        <v>3.63</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.72</v>
+        <v>3.69</v>
       </c>
       <c r="CC5" t="n">
         <v>3.28</v>
@@ -2827,22 +2827,22 @@
         <v>3.74</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.29</v>
+        <v>3.26</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK5" t="n">
         <v>1.35</v>
@@ -2857,31 +2857,31 @@
         <v>2.18</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CQ5" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="CR5" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CS5" t="n">
         <v>2.56</v>
       </c>
-      <c r="CR5" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="CS5" t="n">
-        <v>2.51</v>
-      </c>
       <c r="CT5" t="n">
-        <v>3.33</v>
+        <v>3.26</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX5" t="n">
         <v>1.46</v>
@@ -2896,88 +2896,88 @@
         <v>2.21</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.68</v>
+        <v>1.71</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="DG5" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.66</v>
+        <v>90.31</v>
       </c>
       <c r="DI5" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.27</v>
+        <v>2.31</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.14</v>
+        <v>5.25</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>47.2</v>
+        <v>46.31</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.54</v>
+        <v>11.32</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.199999999999999</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.67</v>
+        <v>49.75</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.07</v>
+        <v>12.88</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.6</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.47</v>
+        <v>3.75</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.8</v>
+        <v>21.44</v>
       </c>
       <c r="EB5" t="n">
         <v>1.41</v>
       </c>
       <c r="EC5" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="6">
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C6" t="n">
         <v>8</v>
       </c>
       <c r="D6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3077,52 +3077,52 @@
         <v>2.38</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="AI6" t="n">
-        <v>96.43000000000001</v>
+        <v>96.12</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.29</v>
+        <v>3.38</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.86</v>
+        <v>5.25</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>43</v>
+        <v>43.12</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.29</v>
+        <v>0.38</v>
       </c>
       <c r="AP6" t="n">
-        <v>1.86</v>
+        <v>2.38</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.29</v>
+        <v>12.38</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.14</v>
+        <v>14.25</v>
       </c>
       <c r="AS6" t="n">
-        <v>8</v>
+        <v>7.75</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.86</v>
+        <v>1.12</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3134,82 +3134,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>45.29</v>
+        <v>45.75</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.14</v>
+        <v>12.75</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.140000000000001</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="BC6" t="n">
-        <v>4</v>
+        <v>4.12</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.29</v>
+        <v>19.62</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.43</v>
+        <v>2.62</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.53</v>
+        <v>10.81</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.73</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.73</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.6</v>
+        <v>4.81</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.93</v>
+        <v>6</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT6" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV6" t="n">
-        <v>13.33</v>
+        <v>18.75</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY6" t="n">
         <v>3.07</v>
@@ -3218,25 +3218,25 @@
         <v>3.19</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.65</v>
+        <v>3.62</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.78</v>
+        <v>3.74</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.84</v>
+        <v>4.66</v>
       </c>
       <c r="CE6" t="n">
         <v>1.32</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.12</v>
+        <v>3.1</v>
       </c>
       <c r="CH6" t="n">
         <v>1.49</v>
@@ -3245,16 +3245,16 @@
         <v>2.18</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CN6" t="n">
         <v>2.08</v>
@@ -3263,124 +3263,124 @@
         <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.63</v>
+        <v>2.66</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.25</v>
+        <v>3.21</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CX6" t="n">
         <v>1.47</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.56</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.09</v>
+        <v>2.1</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="DE6" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DF6" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.53</v>
+        <v>2.5</v>
       </c>
       <c r="DH6" t="n">
-        <v>94.54000000000001</v>
+        <v>94.5</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3.14</v>
+        <v>3.19</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.47</v>
+        <v>4.69</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.13</v>
+        <v>0.18</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.6</v>
+        <v>38.94</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO6" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.67</v>
+        <v>12.69</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.47</v>
+        <v>14.07</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.33</v>
+        <v>8.18</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.27</v>
+        <v>42.68</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.53</v>
+        <v>12.82</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.66</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.87</v>
+        <v>3.94</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.34</v>
+        <v>20</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="7">
@@ -4196,61 +4196,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C9" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D9" t="n">
         <v>8</v>
       </c>
       <c r="E9" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F9" t="n">
-        <v>0.86</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="H9" t="n">
-        <v>91.86</v>
+        <v>88.75</v>
       </c>
       <c r="I9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="J9" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="K9" t="n">
-        <v>5.14</v>
+        <v>4.75</v>
       </c>
       <c r="L9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="M9" t="n">
-        <v>36.57</v>
+        <v>36</v>
       </c>
       <c r="N9" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="O9" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="P9" t="n">
-        <v>9.710000000000001</v>
+        <v>10.12</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.43</v>
+        <v>14.12</v>
       </c>
       <c r="R9" t="n">
-        <v>7.57</v>
+        <v>7.75</v>
       </c>
       <c r="S9" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>1.25</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4262,28 +4262,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.29</v>
+        <v>45.88</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.86</v>
+        <v>11.25</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.57</v>
+        <v>7.62</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.29</v>
+        <v>3.62</v>
       </c>
       <c r="AC9" t="n">
-        <v>21.57</v>
+        <v>20.25</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,70 +4367,70 @@
         <v>2.75</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.07</v>
+        <v>4.19</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.47</v>
+        <v>10.19</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.07</v>
+        <v>4.19</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.47</v>
+        <v>1.56</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.47</v>
+        <v>4.31</v>
       </c>
       <c r="BQ9" t="n">
-        <v>6</v>
+        <v>5.88</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BT9" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BU9" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BV9" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BW9" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.63</v>
+        <v>2.82</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.11</v>
+        <v>3.23</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.81</v>
+        <v>3.79</v>
       </c>
       <c r="CB9" t="n">
-        <v>4</v>
+        <v>3.99</v>
       </c>
       <c r="CC9" t="n">
         <v>4.28</v>
@@ -4445,13 +4445,13 @@
         <v>2.3</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.45</v>
+        <v>3.42</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.54</v>
@@ -4463,34 +4463,34 @@
         <v>1.72</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP9" t="n">
         <v>1.58</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="CU9" t="n">
         <v>1.59</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CW9" t="n">
         <v>1.57</v>
@@ -4499,7 +4499,7 @@
         <v>1.47</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.58</v>
@@ -4511,52 +4511,52 @@
         <v>1.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.07</v>
+        <v>1.12</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.8</v>
+        <v>2.68</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.2</v>
+        <v>77.5</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.6</v>
+        <v>34.44</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.86</v>
+        <v>1.81</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.06</v>
+        <v>12.12</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.07</v>
+        <v>13</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.27</v>
+        <v>8.32</v>
       </c>
       <c r="DS9" t="n">
         <v>0.06</v>
@@ -4568,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.14</v>
+        <v>45.44</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.07</v>
+        <v>12.18</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.6</v>
+        <v>4.69</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.8</v>
+        <v>22.06</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="10">
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C11" t="n">
         <v>8</v>
       </c>
       <c r="D11" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5092,139 +5092,139 @@
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AI11" t="n">
-        <v>90.29000000000001</v>
+        <v>88.75</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK11" t="n">
         <v>3</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AN11" t="n">
-        <v>45.29</v>
+        <v>46.38</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>15.14</v>
+        <v>14.75</v>
       </c>
       <c r="AR11" t="n">
-        <v>14.14</v>
+        <v>14</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.859999999999999</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.71</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.57</v>
+        <v>1.75</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>46.29</v>
+        <v>46.75</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.29</v>
+        <v>11.88</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.140000000000001</v>
+        <v>8.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.14</v>
+        <v>3.62</v>
       </c>
       <c r="BD11" t="n">
-        <v>23.29</v>
+        <v>22.88</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="BF11" t="n">
         <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.8</v>
+        <v>10.5</v>
       </c>
       <c r="BI11" t="n">
-        <v>1.93</v>
+        <v>2.19</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.33</v>
+        <v>0.44</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.27</v>
+        <v>0.38</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.8</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.93</v>
+        <v>4.75</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="BR11" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>60</v>
+        <v>62.5</v>
       </c>
       <c r="BT11" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU11" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BV11" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW11" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BX11" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BY11" t="n">
         <v>1.99</v>
@@ -5239,19 +5239,19 @@
         <v>3.83</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.27</v>
+        <v>3.1</v>
       </c>
       <c r="CE11" t="n">
         <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.29</v>
+        <v>3.28</v>
       </c>
       <c r="CH11" t="n">
         <v>1.54</v>
@@ -5269,7 +5269,7 @@
         <v>1.68</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="CN11" t="n">
         <v>2.19</v>
@@ -5281,7 +5281,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5290,16 +5290,16 @@
         <v>2.49</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="CU11" t="n">
         <v>1.57</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX11" t="n">
         <v>1.44</v>
@@ -5311,91 +5311,91 @@
         <v>2.63</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC11" t="n">
         <v>1.64</v>
       </c>
       <c r="DD11" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="DE11" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DF11" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG11" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="DH11" t="n">
+        <v>91.25</v>
+      </c>
+      <c r="DI11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ11" t="n">
         <v>2.56</v>
       </c>
-      <c r="DE11" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DF11" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="DG11" t="n">
-        <v>2.27</v>
-      </c>
-      <c r="DH11" t="n">
-        <v>92.14</v>
-      </c>
-      <c r="DI11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ11" t="n">
-        <v>2.53</v>
-      </c>
       <c r="DK11" t="n">
-        <v>4.6</v>
+        <v>4.56</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.87</v>
+        <v>45.44</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.94</v>
+        <v>1.88</v>
       </c>
       <c r="DP11" t="n">
-        <v>14.06</v>
+        <v>13.93</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.2</v>
+        <v>11.31</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.470000000000001</v>
+        <v>9.44</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>46.73</v>
+        <v>46.94</v>
       </c>
       <c r="DW11" t="n">
         <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.14</v>
+        <v>12.38</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.27</v>
+        <v>8.32</v>
       </c>
       <c r="DZ11" t="n">
-        <v>3.87</v>
+        <v>4.06</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.8</v>
+        <v>20.75</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D2" t="n">
         <v>7</v>
       </c>
       <c r="E2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F2" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="G2" t="n">
-        <v>3.88</v>
+        <v>4.22</v>
       </c>
       <c r="H2" t="n">
-        <v>101.75</v>
+        <v>97.56</v>
       </c>
       <c r="I2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J2" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="K2" t="n">
-        <v>6</v>
+        <v>6.44</v>
       </c>
       <c r="L2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M2" t="n">
-        <v>46.88</v>
+        <v>45.56</v>
       </c>
       <c r="N2" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="O2" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="P2" t="n">
-        <v>12.75</v>
+        <v>13.44</v>
       </c>
       <c r="Q2" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="R2" t="n">
-        <v>8.75</v>
+        <v>8.33</v>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="T2" t="n">
-        <v>2.12</v>
+        <v>1.89</v>
       </c>
       <c r="U2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>53.38</v>
+        <v>55.44</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>14</v>
+        <v>14.22</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.38</v>
+        <v>4.22</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.62</v>
+        <v>24.22</v>
       </c>
       <c r="AD2" t="n">
         <v>1.53</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.57</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.33</v>
+        <v>11.5</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.33</v>
+        <v>1.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.27</v>
+        <v>4.25</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7</v>
+        <v>7.19</v>
       </c>
       <c r="BR2" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS2" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BT2" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU2" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.17</v>
+        <v>2.14</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CC2" t="n">
         <v>3.2</v>
@@ -1625,13 +1625,13 @@
         <v>1.29</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CI2" t="n">
         <v>2.39</v>
@@ -1643,7 +1643,7 @@
         <v>1.36</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM2" t="n">
         <v>2.77</v>
@@ -1655,10 +1655,10 @@
         <v>1.17</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CR2" t="n">
         <v>1.36</v>
@@ -1688,7 +1688,7 @@
         <v>2.52</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DB2" t="n">
         <v>1.2</v>
@@ -1697,82 +1697,82 @@
         <v>1.65</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="DE2" t="n">
         <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.14</v>
+        <v>4.31</v>
       </c>
       <c r="DH2" t="n">
-        <v>99.13</v>
+        <v>96.94</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.4</v>
+        <v>6.62</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.54</v>
+        <v>48.63</v>
       </c>
       <c r="DN2" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="DP2" t="n">
-        <v>12.67</v>
+        <v>13.06</v>
       </c>
       <c r="DQ2" t="n">
-        <v>15.13</v>
+        <v>14.81</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.67</v>
+        <v>7.5</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52</v>
+        <v>53.25</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.73</v>
+        <v>13.87</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.73</v>
+        <v>9.94</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.13</v>
+        <v>23.94</v>
       </c>
       <c r="EB2" t="n">
         <v>1.51</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C3" t="n">
         <v>7</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>3.71</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AH3" t="n">
-        <v>3.38</v>
+        <v>3</v>
       </c>
       <c r="AI3" t="n">
-        <v>82.5</v>
+        <v>83.44</v>
       </c>
       <c r="AJ3" t="n">
         <v>0</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="AL3" t="n">
-        <v>7</v>
+        <v>6.22</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AN3" t="n">
-        <v>43</v>
+        <v>41.78</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>12.56</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.880000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.5</v>
+        <v>9.44</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.62</v>
+        <v>43.67</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.75</v>
+        <v>12.22</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.619999999999999</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="BD3" t="n">
-        <v>24</v>
+        <v>23.67</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.34</v>
+        <v>1.29</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.5</v>
+        <v>3.56</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="BH3" t="n">
-        <v>13</v>
+        <v>12.62</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.73</v>
+        <v>2.56</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.6</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BP3" t="n">
-        <v>6.27</v>
+        <v>6.06</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.73</v>
+        <v>6.56</v>
       </c>
       <c r="BR3" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT3" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY3" t="n">
         <v>2.22</v>
@@ -2013,34 +2013,34 @@
         <v>2.37</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.63</v>
+        <v>3.65</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.84</v>
+        <v>2.99</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.21</v>
+        <v>3.34</v>
       </c>
       <c r="CE3" t="n">
         <v>1.29</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH3" t="n">
         <v>1.53</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CK3" t="n">
         <v>1.32</v>
@@ -2049,45 +2049,45 @@
         <v>1.64</v>
       </c>
       <c r="CM3" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CT3" t="n">
         <v>3.29</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CZ3" t="inlineStr"/>
       <c r="DA3" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="DB3" t="n">
         <v>1.21</v>
@@ -2096,82 +2096,82 @@
         <v>1.68</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.40000000000001</v>
+        <v>94.18000000000001</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.8</v>
+        <v>6.37</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DM3" t="n">
-        <v>51</v>
+        <v>49.81</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.53</v>
+        <v>3.31</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.07</v>
+        <v>14.25</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.6</v>
+        <v>9.25</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.07</v>
+        <v>9.06</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.06</v>
+        <v>45.44</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>15.2</v>
+        <v>14.75</v>
       </c>
       <c r="DY3" t="n">
-        <v>11.13</v>
+        <v>10.75</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.8</v>
+        <v>22.69</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.62</v>
+        <v>1.57</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.6</v>
+        <v>3.63</v>
       </c>
     </row>
     <row r="4">
@@ -2181,61 +2181,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D4" t="n">
         <v>7</v>
       </c>
       <c r="E4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F4" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="G4" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="H4" t="n">
-        <v>85.88</v>
+        <v>84.56</v>
       </c>
       <c r="I4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="J4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="K4" t="n">
-        <v>5.38</v>
+        <v>5.56</v>
       </c>
       <c r="L4" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="M4" t="n">
-        <v>49.75</v>
+        <v>48.33</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O4" t="n">
-        <v>2.5</v>
+        <v>2.89</v>
       </c>
       <c r="P4" t="n">
-        <v>12.25</v>
+        <v>12</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.62</v>
+        <v>12.22</v>
       </c>
       <c r="R4" t="n">
-        <v>7.88</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T4" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="U4" t="n">
         <v>0</v>
@@ -2247,25 +2247,25 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>51</v>
+        <v>48.89</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.75</v>
+        <v>15.67</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.25</v>
+        <v>9.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.5</v>
+        <v>6.22</v>
       </c>
       <c r="AC4" t="n">
-        <v>18.75</v>
+        <v>17.89</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -2352,70 +2352,70 @@
         <v>1.14</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.13</v>
+        <v>10.19</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.87</v>
+        <v>4.94</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="BR4" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>62.5</v>
       </c>
       <c r="BT4" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU4" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV4" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX4" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.87</v>
+        <v>3.85</v>
       </c>
       <c r="CC4" t="n">
         <v>2.87</v>
@@ -2427,25 +2427,25 @@
         <v>1.29</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.32</v>
+        <v>3.3</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ4" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK4" t="n">
         <v>1.41</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM4" t="n">
         <v>2.68</v>
@@ -2460,7 +2460,7 @@
         <v>1.6</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
@@ -2475,7 +2475,7 @@
         <v>1.57</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CW4" t="n">
         <v>1.58</v>
@@ -2484,13 +2484,13 @@
         <v>1.46</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CZ4" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DB4" t="n">
         <v>1.2</v>
@@ -2499,49 +2499,49 @@
         <v>1.66</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.33</v>
+        <v>2.25</v>
       </c>
       <c r="DH4" t="n">
-        <v>87.73999999999999</v>
+        <v>86.88</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.66</v>
+        <v>1.69</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.87</v>
+        <v>5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.54</v>
+        <v>0.57</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.73</v>
+        <v>43.31</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.4</v>
+        <v>0.44</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.53</v>
+        <v>2.75</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.6</v>
+        <v>12.44</v>
       </c>
       <c r="DQ4" t="n">
-        <v>12</v>
+        <v>11.81</v>
       </c>
       <c r="DR4" t="n">
-        <v>9</v>
+        <v>9.130000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2553,28 +2553,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>51.27</v>
+        <v>50.06</v>
       </c>
       <c r="DW4" t="n">
         <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.53</v>
+        <v>14.56</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.93</v>
+        <v>9.06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="EA4" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="5">
@@ -3390,94 +3390,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D7" t="n">
         <v>8</v>
       </c>
       <c r="E7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F7" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="G7" t="n">
-        <v>3.14</v>
+        <v>3.38</v>
       </c>
       <c r="H7" t="n">
-        <v>94.14</v>
+        <v>95.25</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="K7" t="n">
-        <v>5.57</v>
+        <v>5.88</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>53.71</v>
+        <v>53.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="P7" t="n">
-        <v>12.57</v>
+        <v>11.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.57</v>
+        <v>14.5</v>
       </c>
       <c r="R7" t="n">
-        <v>6.71</v>
+        <v>6.88</v>
       </c>
       <c r="S7" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="T7" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V7" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>53.29</v>
+        <v>53.75</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.43</v>
+        <v>15.38</v>
       </c>
       <c r="AA7" t="n">
-        <v>10</v>
+        <v>10.25</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.43</v>
+        <v>5.12</v>
       </c>
       <c r="AC7" t="n">
-        <v>22.71</v>
+        <v>23.25</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AF7" t="n">
         <v>0.12</v>
@@ -3561,70 +3561,70 @@
         <v>2.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.93</v>
+        <v>11.12</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.87</v>
+        <v>2.75</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BL7" t="n">
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.07</v>
+        <v>5.19</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.8</v>
+        <v>4.94</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS7" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT7" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>18.75</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX7" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.98</v>
+        <v>1.93</v>
       </c>
       <c r="BZ7" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.55</v>
+        <v>3.61</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="CC7" t="n">
         <v>2.21</v>
@@ -3636,7 +3636,7 @@
         <v>1.3</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG7" t="n">
         <v>3.31</v>
@@ -3645,10 +3645,10 @@
         <v>1.53</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CK7" t="n">
         <v>1.36</v>
@@ -3660,16 +3660,16 @@
         <v>2.83</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CR7" t="n">
         <v>1.37</v>
@@ -3684,7 +3684,7 @@
         <v>1.55</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CW7" t="n">
         <v>1.59</v>
@@ -3702,88 +3702,88 @@
         <v>2.14</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.73</v>
+        <v>1.62</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.4</v>
+        <v>2.56</v>
       </c>
       <c r="DH7" t="n">
-        <v>95.06999999999999</v>
+        <v>95.56</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.27</v>
+        <v>2.18</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.33</v>
+        <v>6.44</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.33</v>
+        <v>0.37</v>
       </c>
       <c r="DM7" t="n">
-        <v>49</v>
+        <v>49.19</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.26</v>
+        <v>11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.87</v>
+        <v>15.25</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.6</v>
+        <v>6.69</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.14</v>
+        <v>54.32</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.53</v>
+        <v>15.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.47</v>
+        <v>10.57</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.07</v>
+        <v>4.94</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.46</v>
+        <v>22.75</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.69</v>
+        <v>1.67</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.2</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="8">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C8" t="n">
         <v>8</v>
       </c>
       <c r="D8" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3883,139 +3883,139 @@
         <v>3.12</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AI8" t="n">
-        <v>97.70999999999999</v>
+        <v>94.62</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.57</v>
+        <v>2.62</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.86</v>
+        <v>4.12</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN8" t="n">
-        <v>43.29</v>
+        <v>42.38</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AQ8" t="n">
-        <v>11.57</v>
+        <v>12.62</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.14</v>
+        <v>11.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.289999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.43</v>
+        <v>45.12</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.289999999999999</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.71</v>
+        <v>3.88</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.29</v>
+        <v>20.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.869999999999999</v>
+        <v>9.19</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.87</v>
+        <v>4.06</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.93</v>
+        <v>5.06</v>
       </c>
       <c r="BR8" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS8" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BT8" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV8" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX8" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
         <v>2.37</v>
@@ -4024,31 +4024,31 @@
         <v>2.49</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.63</v>
+        <v>3.68</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.72</v>
+        <v>3.77</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.21</v>
+        <v>3.51</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="CE8" t="n">
         <v>1.3</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.57</v>
@@ -4057,7 +4057,7 @@
         <v>1.4</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM8" t="n">
         <v>2.68</v>
@@ -4066,13 +4066,13 @@
         <v>2.05</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP8" t="n">
         <v>1.64</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CR8" t="n">
         <v>1.39</v>
@@ -4090,103 +4090,103 @@
         <v>2.47</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX8" t="n">
         <v>1.49</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ8" t="n">
         <v>2.49</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="DB8" t="n">
         <v>1.21</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.69</v>
+        <v>2.66</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.06</v>
+        <v>90.87</v>
       </c>
       <c r="DI8" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DM8" t="n">
-        <v>46</v>
+        <v>45.38</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.54</v>
+        <v>1.68</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.73</v>
+        <v>13.18</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.67</v>
+        <v>11.38</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.07</v>
+        <v>8.06</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.87</v>
+        <v>48.5</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.6</v>
+        <v>12.88</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.67</v>
+        <v>20.81</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="9">
@@ -4599,10 +4599,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C10" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D10" t="n">
         <v>8</v>
@@ -4611,82 +4611,82 @@
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>1.29</v>
+        <v>1.12</v>
       </c>
       <c r="G10" t="n">
-        <v>3.71</v>
+        <v>3.75</v>
       </c>
       <c r="H10" t="n">
-        <v>109.29</v>
+        <v>113.12</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="K10" t="n">
-        <v>6.57</v>
+        <v>6.62</v>
       </c>
       <c r="L10" t="n">
-        <v>0.43</v>
+        <v>0.38</v>
       </c>
       <c r="M10" t="n">
-        <v>60.14</v>
+        <v>59.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="P10" t="n">
-        <v>14.14</v>
+        <v>12.88</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.29</v>
+        <v>13.62</v>
       </c>
       <c r="R10" t="n">
-        <v>6.71</v>
+        <v>6.5</v>
       </c>
       <c r="S10" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="T10" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="V10" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.86</v>
+        <v>58.62</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.57</v>
+        <v>17.88</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.71</v>
+        <v>11.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>20</v>
+        <v>20.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.86</v>
+        <v>1.62</v>
       </c>
       <c r="AF10" t="n">
         <v>0.12</v>
@@ -4770,70 +4770,70 @@
         <v>2.5</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.4</v>
+        <v>9.25</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.27</v>
+        <v>3.06</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BM10" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.8</v>
+        <v>1.69</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.27</v>
+        <v>5.19</v>
       </c>
       <c r="BR10" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS10" t="n">
-        <v>93.33</v>
+        <v>87.5</v>
       </c>
       <c r="BT10" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BU10" t="n">
-        <v>46.67</v>
+        <v>43.75</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.83</v>
+        <v>3.81</v>
       </c>
       <c r="CC10" t="n">
         <v>2.38</v>
@@ -4845,7 +4845,7 @@
         <v>1.3</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG10" t="n">
         <v>3.28</v>
@@ -4854,37 +4854,37 @@
         <v>1.55</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK10" t="n">
         <v>1.34</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.96</v>
+        <v>2.97</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CR10" t="n">
         <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CT10" t="n">
         <v>3.27</v>
@@ -4893,7 +4893,7 @@
         <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CW10" t="n">
         <v>1.58</v>
@@ -4902,13 +4902,13 @@
         <v>1.51</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.47</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="DB10" t="n">
         <v>1.2</v>
@@ -4917,82 +4917,82 @@
         <v>1.67</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="DG10" t="n">
-        <v>3</v>
+        <v>3.06</v>
       </c>
       <c r="DH10" t="n">
-        <v>106.07</v>
+        <v>108.18</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.47</v>
+        <v>5.56</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM10" t="n">
-        <v>53.27</v>
+        <v>53.25</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.93</v>
+        <v>13.32</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.6</v>
+        <v>13.75</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.8</v>
+        <v>6.69</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.93</v>
+        <v>57.37</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>15</v>
+        <v>15.32</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.4</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.6</v>
+        <v>5.69</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.67</v>
+        <v>19.81</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
     </row>
     <row r="11">
@@ -5155,19 +5155,19 @@
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.88</v>
+        <v>12</v>
       </c>
       <c r="BB11" t="n">
         <v>8.25</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.62</v>
+        <v>3.75</v>
       </c>
       <c r="BD11" t="n">
         <v>22.88</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="BF11" t="n">
         <v>3</v>
@@ -5380,13 +5380,13 @@
         <v>0.06</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.38</v>
+        <v>12.44</v>
       </c>
       <c r="DY11" t="n">
         <v>8.32</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="EA11" t="n">
         <v>20.75</v>
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C12" t="n">
         <v>7</v>
       </c>
       <c r="D12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5495,139 +5495,139 @@
         <v>1.71</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.5</v>
+        <v>2.67</v>
       </c>
       <c r="AI12" t="n">
-        <v>83.88</v>
+        <v>78.78</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.75</v>
+        <v>3.67</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.88</v>
+        <v>3.89</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>36</v>
+        <v>34.89</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.5</v>
+        <v>15.33</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.25</v>
+        <v>12.78</v>
       </c>
       <c r="AS12" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AU12" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.12</v>
+        <v>0.33</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.62</v>
+        <v>49.78</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.62</v>
+        <v>11.89</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.380000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.25</v>
+        <v>3.56</v>
       </c>
       <c r="BD12" t="n">
-        <v>19</v>
+        <v>19.33</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.800000000000001</v>
+        <v>9.81</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.2</v>
+        <v>2.44</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.67</v>
+        <v>0.75</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.07</v>
+        <v>1.19</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.13</v>
+        <v>1.25</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.13</v>
+        <v>4.06</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.67</v>
+        <v>5.75</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT12" t="n">
-        <v>33.33</v>
+        <v>37.5</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BV12" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW12" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="BX12" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BY12" t="n">
         <v>2.19</v>
@@ -5636,34 +5636,34 @@
         <v>2.18</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.56</v>
+        <v>3.57</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.84</v>
+        <v>2.91</v>
       </c>
       <c r="CE12" t="n">
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CH12" t="n">
         <v>1.5</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK12" t="n">
         <v>1.34</v>
@@ -5672,25 +5672,25 @@
         <v>1.67</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.87</v>
+        <v>2.9</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CO12" t="n">
         <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.65</v>
+        <v>2.63</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT12" t="n">
         <v>3.31</v>
@@ -5714,91 +5714,91 @@
         <v>2.49</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC12" t="n">
         <v>1.74</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="DE12" t="n">
         <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.93</v>
+        <v>2</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.8</v>
+        <v>2.88</v>
       </c>
       <c r="DH12" t="n">
-        <v>86.73999999999999</v>
+        <v>83.69</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.67</v>
+        <v>4.62</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.73</v>
+        <v>37.94</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.86</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.2</v>
+        <v>14.18</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14.13</v>
+        <v>13.81</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.73</v>
+        <v>8.81</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.06</v>
+        <v>0.19</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.67</v>
+        <v>51.13</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.73</v>
+        <v>12.81</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.869999999999999</v>
+        <v>8.81</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.87</v>
+        <v>4</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.07</v>
+        <v>19.25</v>
       </c>
       <c r="EB12" t="n">
         <v>1.36</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="13">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C13" t="n">
         <v>8</v>
       </c>
       <c r="D13" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E13" t="n">
         <v>0.38</v>
@@ -5901,136 +5901,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="AI13" t="n">
-        <v>98.86</v>
+        <v>91.12</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.43</v>
+        <v>4.38</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.57</v>
+        <v>0.62</v>
       </c>
       <c r="AN13" t="n">
-        <v>39.71</v>
+        <v>35.62</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.14</v>
+        <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>12.62</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.14</v>
+        <v>14.75</v>
       </c>
       <c r="AS13" t="n">
-        <v>9</v>
+        <v>9.619999999999999</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.43</v>
+        <v>1.25</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>47.57</v>
+        <v>45.12</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.71</v>
+        <v>10.75</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.43</v>
+        <v>6.88</v>
       </c>
       <c r="BC13" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="BD13" t="n">
-        <v>21.43</v>
+        <v>20.88</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.33</v>
+        <v>1.21</v>
       </c>
       <c r="BF13" t="n">
-        <v>3.14</v>
+        <v>2.88</v>
       </c>
       <c r="BG13" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.67</v>
+        <v>9.94</v>
       </c>
       <c r="BI13" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.87</v>
+        <v>1.75</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.13</v>
+        <v>1.06</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.73</v>
+        <v>4.69</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.07</v>
+        <v>4.44</v>
       </c>
       <c r="BR13" t="n">
-        <v>100</v>
+        <v>93.75</v>
       </c>
       <c r="BS13" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT13" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BU13" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BV13" t="n">
-        <v>26.67</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY13" t="n">
         <v>2.31</v>
@@ -6045,10 +6045,10 @@
         <v>3.65</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CD13" t="n">
-        <v>2.93</v>
+        <v>3.01</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
@@ -6057,13 +6057,13 @@
         <v>2.45</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH13" t="n">
         <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.56</v>
@@ -6072,10 +6072,10 @@
         <v>1.34</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CN13" t="n">
         <v>2.19</v>
@@ -6093,16 +6093,16 @@
         <v>1.36</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CT13" t="n">
         <v>3.31</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CW13" t="n">
         <v>1.57</v>
@@ -6111,7 +6111,7 @@
         <v>1.46</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.57</v>
@@ -6123,85 +6123,85 @@
         <v>1.21</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.73</v>
+        <v>1.68</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
       <c r="DH13" t="n">
-        <v>102.6</v>
+        <v>98.5</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.47</v>
+        <v>5.38</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="DM13" t="n">
-        <v>45</v>
+        <v>42.62</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.4</v>
+        <v>2.31</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.47</v>
+        <v>12.31</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.6</v>
+        <v>13.93</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.529999999999999</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>49.07</v>
+        <v>47.75</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>14.47</v>
+        <v>13.82</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.859999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.6</v>
+        <v>5.32</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.73</v>
+        <v>21.44</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.63</v>
+        <v>1.56</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="14">
@@ -6211,61 +6211,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C14" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D14" t="n">
         <v>8</v>
       </c>
       <c r="E14" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="F14" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G14" t="n">
         <v>2</v>
       </c>
-      <c r="G14" t="n">
-        <v>2.14</v>
-      </c>
       <c r="H14" t="n">
-        <v>82.70999999999999</v>
+        <v>76.25</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.29</v>
+        <v>3.5</v>
       </c>
       <c r="K14" t="n">
-        <v>5.43</v>
+        <v>4.88</v>
       </c>
       <c r="L14" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M14" t="n">
-        <v>45.14</v>
+        <v>42.12</v>
       </c>
       <c r="N14" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="O14" t="n">
-        <v>2.43</v>
+        <v>2.12</v>
       </c>
       <c r="P14" t="n">
-        <v>14.86</v>
+        <v>14.75</v>
       </c>
       <c r="Q14" t="n">
-        <v>13.43</v>
+        <v>12.75</v>
       </c>
       <c r="R14" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="S14" t="n">
-        <v>1.43</v>
+        <v>1.75</v>
       </c>
       <c r="T14" t="n">
-        <v>2</v>
+        <v>1.75</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6277,28 +6277,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>49.43</v>
+        <v>46.88</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="Z14" t="n">
-        <v>12.29</v>
+        <v>11.25</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.71</v>
+        <v>6.38</v>
       </c>
       <c r="AB14" t="n">
-        <v>5.57</v>
+        <v>4.88</v>
       </c>
       <c r="AC14" t="n">
-        <v>17</v>
+        <v>16.38</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.49</v>
+        <v>1.36</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="AF14" t="n">
         <v>0.12</v>
@@ -6382,70 +6382,70 @@
         <v>2</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.73</v>
+        <v>10.5</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.33</v>
+        <v>3.38</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.6</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.47</v>
+        <v>1.38</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.67</v>
+        <v>0.88</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.13</v>
+        <v>2.25</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.53</v>
+        <v>4.38</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="BR14" t="n">
-        <v>86.67</v>
+        <v>87.5</v>
       </c>
       <c r="BS14" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT14" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BU14" t="n">
-        <v>46.67</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX14" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.33</v>
+        <v>2.48</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.52</v>
+        <v>2.64</v>
       </c>
       <c r="CA14" t="n">
         <v>3.73</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.87</v>
+        <v>3.86</v>
       </c>
       <c r="CC14" t="n">
         <v>3.69</v>
@@ -6454,43 +6454,43 @@
         <v>3.88</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF14" t="n">
         <v>2.31</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CJ14" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CK14" t="n">
         <v>1.35</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM14" t="n">
         <v>2.91</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CO14" t="n">
         <v>1.16</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
@@ -6502,10 +6502,10 @@
         <v>3.31</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CW14" t="n">
         <v>1.56</v>
@@ -6516,58 +6516,58 @@
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC14" t="n">
         <v>1.64</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.67</v>
+        <v>1.75</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.73</v>
+        <v>2.62</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.67</v>
+        <v>81.31999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.6</v>
+        <v>2.75</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.47</v>
+        <v>5.19</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>42.07</v>
+        <v>40.75</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.33</v>
+        <v>2.18</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.27</v>
+        <v>13.32</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11.2</v>
+        <v>11</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.6</v>
+        <v>47.38</v>
       </c>
       <c r="DW14" t="n">
-        <v>0</v>
+        <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.73</v>
+        <v>12.18</v>
       </c>
       <c r="DY14" t="n">
-        <v>8.199999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.53</v>
+        <v>4.25</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.67</v>
+        <v>17.31</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="15">
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C15" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D15" t="n">
         <v>8</v>
@@ -6622,82 +6622,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G15" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="H15" t="n">
-        <v>114.14</v>
+        <v>106</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.86</v>
+        <v>2.75</v>
       </c>
       <c r="K15" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="L15" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="M15" t="n">
-        <v>56.14</v>
+        <v>53.88</v>
       </c>
       <c r="N15" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O15" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="P15" t="n">
-        <v>13.86</v>
+        <v>13.5</v>
       </c>
       <c r="Q15" t="n">
-        <v>10.86</v>
+        <v>11.12</v>
       </c>
       <c r="R15" t="n">
-        <v>5.86</v>
+        <v>6.12</v>
       </c>
       <c r="S15" t="n">
-        <v>1.86</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.29</v>
+        <v>1.5</v>
       </c>
       <c r="U15" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="V15" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.29</v>
+        <v>55.5</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.43</v>
+        <v>15.75</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.71</v>
+        <v>10.62</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.71</v>
+        <v>5.12</v>
       </c>
       <c r="AC15" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,70 +6781,70 @@
         <v>3</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.47</v>
+        <v>10.44</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.93</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.8</v>
+        <v>0.88</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="BO15" t="n">
-        <v>0.87</v>
+        <v>1</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.13</v>
+        <v>5</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.33</v>
+        <v>5.44</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS15" t="n">
-        <v>73.33</v>
+        <v>75</v>
       </c>
       <c r="BT15" t="n">
-        <v>40</v>
+        <v>43.75</v>
       </c>
       <c r="BU15" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BW15" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BX15" t="n">
-        <v>26.67</v>
+        <v>31.25</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.43</v>
+        <v>2.39</v>
       </c>
       <c r="CA15" t="n">
         <v>3.66</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC15" t="n">
         <v>3.09</v>
@@ -6859,10 +6859,10 @@
         <v>2.27</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.43</v>
+        <v>3.42</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CI15" t="n">
         <v>2.55</v>
@@ -6877,10 +6877,10 @@
         <v>1.76</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.8</v>
+        <v>2.83</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="CO15" t="n">
         <v>1.15</v>
@@ -6893,14 +6893,14 @@
       </c>
       <c r="CR15" t="inlineStr"/>
       <c r="CS15" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CW15" t="n">
         <v>1.5</v>
@@ -6915,7 +6915,7 @@
         <v>2.55</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DB15" t="n">
         <v>1.17</v>
@@ -6924,7 +6924,7 @@
         <v>1.56</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
@@ -6933,73 +6933,73 @@
         <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.73</v>
+        <v>2.75</v>
       </c>
       <c r="DH15" t="n">
-        <v>96.53</v>
+        <v>93.56</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.93</v>
+        <v>2.88</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.33</v>
+        <v>5.37</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.4</v>
+        <v>46.82</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.93</v>
+        <v>0.87</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.33</v>
+        <v>12.25</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.47</v>
+        <v>12.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>7</v>
+        <v>7.06</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.12</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.4</v>
+        <v>55.5</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.13</v>
+        <v>16.25</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.07</v>
+        <v>11</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.07</v>
+        <v>5.25</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.93</v>
+        <v>18.75</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.86</v>
+        <v>2.81</v>
       </c>
     </row>
     <row r="16">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C16" t="n">
         <v>8</v>
       </c>
       <c r="D16" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7099,139 +7099,139 @@
         <v>2.25</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AG16" t="n">
         <v>2</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.14</v>
+        <v>3.62</v>
       </c>
       <c r="AI16" t="n">
-        <v>90.70999999999999</v>
+        <v>94.12</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="AK16" t="n">
         <v>3</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.86</v>
+        <v>6</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN16" t="n">
-        <v>47.57</v>
+        <v>48</v>
       </c>
       <c r="AO16" t="n">
         <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14</v>
+        <v>14.25</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.71</v>
+        <v>14.25</v>
       </c>
       <c r="AS16" t="n">
-        <v>8</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AU16" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>47.86</v>
+        <v>50</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.57</v>
+        <v>11.62</v>
       </c>
       <c r="BB16" t="n">
-        <v>8</v>
+        <v>7.25</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.57</v>
+        <v>4.38</v>
       </c>
       <c r="BD16" t="n">
-        <v>20</v>
+        <v>21.62</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.27</v>
+        <v>10.06</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.53</v>
+        <v>2.44</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.6</v>
+        <v>1.56</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.73</v>
+        <v>4.44</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.53</v>
+        <v>5.62</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS16" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BT16" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BU16" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BV16" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY16" t="n">
         <v>2.34</v>
@@ -7240,165 +7240,169 @@
         <v>2.37</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CC16" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.14</v>
+        <v>3.27</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK16" t="n">
         <v>1.35</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.95</v>
+        <v>2.92</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="CO16" t="n">
         <v>1.19</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="CX16" t="inlineStr"/>
+        <v>1.58</v>
+      </c>
+      <c r="CX16" t="n">
+        <v>1.45</v>
+      </c>
       <c r="CY16" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CZ16" t="inlineStr"/>
+        <v>1.64</v>
+      </c>
+      <c r="CZ16" t="n">
+        <v>2.61</v>
+      </c>
       <c r="DA16" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="DB16" t="n">
         <v>1.21</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="DH16" t="n">
-        <v>95.66</v>
+        <v>97.06</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DM16" t="n">
-        <v>46.33</v>
+        <v>46.62</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.4</v>
+        <v>2.25</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.46</v>
+        <v>12.68</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.13</v>
+        <v>14.38</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.94</v>
+        <v>8</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.47</v>
+        <v>51.38</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.6</v>
+        <v>12.12</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.199999999999999</v>
+        <v>7.82</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.4</v>
+        <v>4.31</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.4</v>
+        <v>21.18</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.53</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="17">
@@ -7408,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C17" t="n">
         <v>8</v>
       </c>
       <c r="D17" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7498,139 +7502,139 @@
         <v>2</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>99.14</v>
+        <v>94.88</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.29</v>
+        <v>4.5</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AN17" t="n">
-        <v>42.71</v>
+        <v>41.88</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AP17" t="n">
         <v>2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>12.38</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.57</v>
+        <v>11</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.86</v>
+        <v>7.38</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.29</v>
+        <v>1.62</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>51.29</v>
+        <v>53.75</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.43</v>
+        <v>15.12</v>
       </c>
       <c r="BB17" t="n">
-        <v>9</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.43</v>
+        <v>5.25</v>
       </c>
       <c r="BD17" t="n">
-        <v>21</v>
+        <v>19.88</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.47</v>
+        <v>1.63</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.43</v>
+        <v>2.38</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.6</v>
+        <v>10.38</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.53</v>
+        <v>2.62</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.47</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.2</v>
+        <v>1.12</v>
       </c>
       <c r="BP17" t="n">
-        <v>5.07</v>
+        <v>4.88</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.53</v>
+        <v>5.5</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS17" t="n">
-        <v>80</v>
+        <v>81.25</v>
       </c>
       <c r="BT17" t="n">
-        <v>53.33</v>
+        <v>56.25</v>
       </c>
       <c r="BU17" t="n">
-        <v>6.67</v>
+        <v>12.5</v>
       </c>
       <c r="BV17" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.67</v>
+        <v>6.25</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>56.25</v>
       </c>
       <c r="BY17" t="n">
         <v>1.89</v>
@@ -7645,19 +7649,19 @@
         <v>3.8</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="CE17" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CH17" t="n">
         <v>1.52</v>
@@ -7672,22 +7676,22 @@
         <v>1.36</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="CP17" t="n">
         <v>1.66</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
@@ -7699,10 +7703,10 @@
         <v>3.22</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CW17" t="n">
         <v>1.61</v>
@@ -7717,7 +7721,7 @@
         <v>2.58</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DB17" t="n">
         <v>1.22</v>
@@ -7729,79 +7733,79 @@
         <v>2.73</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.87</v>
+        <v>2.94</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.33</v>
+        <v>94.38</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.07000000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.34</v>
+        <v>5.38</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="DM17" t="n">
-        <v>46</v>
+        <v>45.38</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.13</v>
+        <v>12.82</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.33</v>
+        <v>10.56</v>
       </c>
       <c r="DR17" t="n">
-        <v>8.199999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>52.6</v>
+        <v>53.75</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>14.93</v>
+        <v>15.68</v>
       </c>
       <c r="DY17" t="n">
-        <v>9.859999999999999</v>
+        <v>10.25</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.06</v>
+        <v>5.44</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.33</v>
+        <v>20.75</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.63</v>
+        <v>1.7</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
     </row>
     <row r="18">
@@ -7811,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C18" t="n">
         <v>8</v>
       </c>
       <c r="D18" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7904,49 +7908,49 @@
         <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.29</v>
+        <v>2.12</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.29</v>
+        <v>2.5</v>
       </c>
       <c r="AI18" t="n">
-        <v>83.70999999999999</v>
+        <v>88.5</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>4.14</v>
+        <v>3.88</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.86</v>
+        <v>3.88</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>30.57</v>
+        <v>33.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.57</v>
+        <v>1.38</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13.71</v>
+        <v>13.12</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.86</v>
+        <v>15.12</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.86</v>
+        <v>7.75</v>
       </c>
       <c r="AT18" t="n">
-        <v>2</v>
+        <v>1.88</v>
       </c>
       <c r="AU18" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7958,82 +7962,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>61</v>
+        <v>61.88</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.71</v>
+        <v>12.12</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.43</v>
+        <v>8.25</v>
       </c>
       <c r="BC18" t="n">
-        <v>4.29</v>
+        <v>3.88</v>
       </c>
       <c r="BD18" t="n">
-        <v>20.86</v>
+        <v>20.12</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.86</v>
+        <v>3.62</v>
       </c>
       <c r="BG18" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.470000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="BI18" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.8</v>
+        <v>0.75</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL18" t="n">
         <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.73</v>
+        <v>1.69</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.27</v>
+        <v>1.19</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.07</v>
+        <v>5.06</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS18" t="n">
-        <v>86.67</v>
+        <v>81.25</v>
       </c>
       <c r="BT18" t="n">
-        <v>73.33</v>
+        <v>68.75</v>
       </c>
       <c r="BU18" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BV18" t="n">
-        <v>13.33</v>
+        <v>12.5</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="BY18" t="n">
         <v>2.68</v>
@@ -8042,22 +8046,22 @@
         <v>2.97</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CB18" t="n">
         <v>3.6</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.37</v>
+        <v>3.51</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.65</v>
+        <v>3.74</v>
       </c>
       <c r="CE18" t="n">
         <v>1.35</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG18" t="n">
         <v>3.06</v>
@@ -8072,37 +8076,37 @@
         <v>1.63</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL18" t="n">
         <v>1.86</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CN18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="CO18" t="n">
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CT18" t="n">
         <v>3.18</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV18" t="n">
         <v>2.28</v>
@@ -8117,7 +8121,7 @@
         <v>1.85</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="DA18" t="n">
         <v>1.97</v>
@@ -8126,85 +8130,85 @@
         <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.03</v>
+        <v>3.01</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="DG18" t="n">
+        <v>2.06</v>
+      </c>
+      <c r="DH18" t="n">
+        <v>88.88</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>4.06</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>35.56</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="DO18" t="n">
         <v>2</v>
       </c>
-      <c r="DG18" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="DH18" t="n">
-        <v>86.66</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="DJ18" t="n">
-        <v>3.47</v>
-      </c>
-      <c r="DK18" t="n">
-        <v>4.07</v>
-      </c>
-      <c r="DL18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DM18" t="n">
-        <v>34.33</v>
-      </c>
-      <c r="DN18" t="n">
+      <c r="DP18" t="n">
+        <v>14.18</v>
+      </c>
+      <c r="DQ18" t="n">
+        <v>15.12</v>
+      </c>
+      <c r="DR18" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="DS18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DT18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DU18" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV18" t="n">
+        <v>58.69</v>
+      </c>
+      <c r="DW18" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="DX18" t="n">
+        <v>12.43</v>
+      </c>
+      <c r="DY18" t="n">
+        <v>8.43</v>
+      </c>
+      <c r="DZ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="EA18" t="n">
+        <v>20.68</v>
+      </c>
+      <c r="EB18" t="n">
         <v>1.33</v>
       </c>
-      <c r="DO18" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="DP18" t="n">
-        <v>14.53</v>
-      </c>
-      <c r="DQ18" t="n">
-        <v>15.47</v>
-      </c>
-      <c r="DR18" t="n">
-        <v>7.27</v>
-      </c>
-      <c r="DS18" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DT18" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DU18" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV18" t="n">
-        <v>58.07</v>
-      </c>
-      <c r="DW18" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="DX18" t="n">
-        <v>12.26</v>
-      </c>
-      <c r="DY18" t="n">
-        <v>8.06</v>
-      </c>
-      <c r="DZ18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="EA18" t="n">
-        <v>21.07</v>
-      </c>
-      <c r="EB18" t="n">
-        <v>1.32</v>
-      </c>
       <c r="EC18" t="n">
-        <v>3.2</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="19">
@@ -8214,61 +8218,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D19" t="n">
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="F19" t="n">
-        <v>2.29</v>
+        <v>2.38</v>
       </c>
       <c r="G19" t="n">
-        <v>3.14</v>
+        <v>2.75</v>
       </c>
       <c r="H19" t="n">
-        <v>102.14</v>
+        <v>99.5</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="K19" t="n">
-        <v>5.86</v>
+        <v>5.12</v>
       </c>
       <c r="L19" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="M19" t="n">
-        <v>52.14</v>
+        <v>51.12</v>
       </c>
       <c r="N19" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.71</v>
+        <v>2.38</v>
       </c>
       <c r="P19" t="n">
-        <v>12.86</v>
+        <v>13.5</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.14</v>
+        <v>12.62</v>
       </c>
       <c r="R19" t="n">
-        <v>5.43</v>
+        <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="T19" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8280,28 +8284,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>43.71</v>
+        <v>42.62</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.86</v>
+        <v>13</v>
       </c>
       <c r="AA19" t="n">
-        <v>9</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.86</v>
+        <v>4.62</v>
       </c>
       <c r="AC19" t="n">
-        <v>20.57</v>
+        <v>19.88</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.6</v>
+        <v>1.52</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="AF19" t="n">
         <v>0.25</v>
@@ -8385,46 +8389,46 @@
         <v>3</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.93</v>
+        <v>9.75</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN19" t="n">
         <v>1</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.87</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.6</v>
+        <v>4.31</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.27</v>
+        <v>5.38</v>
       </c>
       <c r="BR19" t="n">
-        <v>93.33</v>
+        <v>93.75</v>
       </c>
       <c r="BS19" t="n">
-        <v>53.33</v>
+        <v>50</v>
       </c>
       <c r="BT19" t="n">
-        <v>40</v>
+        <v>37.5</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8436,13 +8440,13 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>33.33</v>
+        <v>31.25</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="CA19" t="n">
         <v>3.44</v>
@@ -8460,46 +8464,46 @@
         <v>1.34</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CH19" t="n">
         <v>1.45</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK19" t="n">
         <v>1.41</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO19" t="n">
         <v>1.23</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT19" t="n">
         <v>3.21</v>
@@ -8508,19 +8512,19 @@
         <v>1.48</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW19" t="n">
         <v>1.67</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY19" t="n">
         <v>1.77</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="DA19" t="n">
         <v>2.05</v>
@@ -8532,82 +8536,82 @@
         <v>1.84</v>
       </c>
       <c r="DD19" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DF19" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="DH19" t="n">
-        <v>103.46</v>
+        <v>102.06</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.2</v>
+        <v>4.87</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM19" t="n">
-        <v>49</v>
+        <v>48.68</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.93</v>
+        <v>0.88</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.53</v>
+        <v>2.38</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.67</v>
+        <v>13.94</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.53</v>
+        <v>11.81</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.33</v>
+        <v>5.12</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>41.06</v>
+        <v>40.68</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.13</v>
+        <v>12.75</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.4</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.73</v>
+        <v>4.62</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.4</v>
+        <v>21</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1938,16 +1938,16 @@
         <v>12.22</v>
       </c>
       <c r="BB3" t="n">
-        <v>9.109999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.11</v>
+        <v>3.22</v>
       </c>
       <c r="BD3" t="n">
         <v>23.67</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="BF3" t="n">
         <v>3.56</v>
@@ -2159,16 +2159,16 @@
         <v>14.75</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.75</v>
+        <v>10.69</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="EA3" t="n">
         <v>22.69</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="EC3" t="n">
         <v>3.63</v>
@@ -3435,7 +3435,7 @@
         <v>11.88</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.5</v>
+        <v>14.38</v>
       </c>
       <c r="R7" t="n">
         <v>6.88</v>
@@ -3747,7 +3747,7 @@
         <v>11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.25</v>
+        <v>15.19</v>
       </c>
       <c r="DR7" t="n">
         <v>6.69</v>
@@ -5552,16 +5552,16 @@
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>49.78</v>
+        <v>49.67</v>
       </c>
       <c r="AZ12" t="n">
         <v>0.22</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.89</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.33</v>
+        <v>8.44</v>
       </c>
       <c r="BC12" t="n">
         <v>3.56</v>
@@ -5570,7 +5570,7 @@
         <v>19.33</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="BF12" t="n">
         <v>3.44</v>
@@ -5777,16 +5777,16 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.13</v>
+        <v>51.07</v>
       </c>
       <c r="DW12" t="n">
         <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.81</v>
+        <v>12.88</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.81</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="DZ12" t="n">
         <v>4</v>
@@ -5795,7 +5795,7 @@
         <v>19.25</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="EC12" t="n">
         <v>2.68</v>
@@ -6277,7 +6277,7 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.88</v>
+        <v>47</v>
       </c>
       <c r="Y14" t="n">
         <v>0.25</v>
@@ -6579,7 +6579,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.38</v>
+        <v>47.44</v>
       </c>
       <c r="DW14" t="n">
         <v>0.12</v>
@@ -6676,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.5</v>
+        <v>55.62</v>
       </c>
       <c r="Y15" t="n">
         <v>0.12</v>
@@ -6978,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.5</v>
+        <v>55.56</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
@@ -7559,7 +7559,7 @@
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>53.75</v>
+        <v>53.62</v>
       </c>
       <c r="AZ17" t="n">
         <v>0</v>
@@ -7784,7 +7784,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>53.75</v>
+        <v>53.68</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -2253,19 +2253,19 @@
         <v>0.11</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.67</v>
+        <v>15.78</v>
       </c>
       <c r="AA4" t="n">
         <v>9.44</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.22</v>
+        <v>6.33</v>
       </c>
       <c r="AC4" t="n">
         <v>17.89</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="AE4" t="n">
         <v>2</v>
@@ -2559,19 +2559,19 @@
         <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.56</v>
+        <v>14.62</v>
       </c>
       <c r="DY4" t="n">
         <v>9.06</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.5</v>
+        <v>5.56</v>
       </c>
       <c r="EA4" t="n">
         <v>18.5</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="EC4" t="n">
         <v>1.62</v>
@@ -3456,7 +3456,7 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>53.75</v>
+        <v>53.62</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -3762,7 +3762,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.32</v>
+        <v>54.25</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
@@ -3940,7 +3940,7 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.12</v>
+        <v>45.25</v>
       </c>
       <c r="AZ8" t="n">
         <v>0.12</v>
@@ -3949,16 +3949,16 @@
         <v>13.5</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.619999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.88</v>
+        <v>3.75</v>
       </c>
       <c r="BD8" t="n">
         <v>20.62</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BF8" t="n">
         <v>2.5</v>
@@ -4165,7 +4165,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.5</v>
+        <v>48.56</v>
       </c>
       <c r="DW8" t="n">
         <v>0.12</v>
@@ -4174,16 +4174,16 @@
         <v>12.88</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.369999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="EA8" t="n">
         <v>20.81</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
         <v>2.81</v>
@@ -4671,10 +4671,10 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.88</v>
+        <v>18.12</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.88</v>
+        <v>12.12</v>
       </c>
       <c r="AB10" t="n">
         <v>6</v>
@@ -4683,7 +4683,7 @@
         <v>20.25</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="AE10" t="n">
         <v>1.62</v>
@@ -4977,10 +4977,10 @@
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>15.32</v>
+        <v>15.44</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.630000000000001</v>
+        <v>9.75</v>
       </c>
       <c r="DZ10" t="n">
         <v>5.69</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E2" t="n">
         <v>0.11</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.43</v>
+        <v>4.25</v>
       </c>
       <c r="AI2" t="n">
-        <v>96.14</v>
+        <v>95.38</v>
       </c>
       <c r="AJ2" t="n">
         <v>0</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.71</v>
+        <v>2.62</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.86</v>
+        <v>6.5</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.43</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>52.57</v>
+        <v>52.38</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.43</v>
+        <v>2.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>12.57</v>
+        <v>13</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.86</v>
+        <v>15.38</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.43</v>
+        <v>6.5</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.86</v>
+        <v>1.75</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>50.43</v>
+        <v>49.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.14</v>
+        <v>0.12</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.43</v>
+        <v>13.12</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.859999999999999</v>
+        <v>9.25</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.57</v>
+        <v>3.88</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.57</v>
+        <v>24.25</v>
       </c>
       <c r="BE2" t="n">
         <v>1.48</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="BG2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.5</v>
+        <v>11.24</v>
       </c>
       <c r="BI2" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.25</v>
+        <v>1.18</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.25</v>
+        <v>4.12</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.19</v>
+        <v>7.06</v>
       </c>
       <c r="BR2" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS2" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>56.25</v>
+        <v>52.94</v>
       </c>
       <c r="BU2" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW2" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX2" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY2" t="n">
         <v>2.14</v>
@@ -1610,28 +1610,28 @@
         <v>2.24</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.2</v>
+        <v>3.29</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.43</v>
+        <v>3.52</v>
       </c>
       <c r="CE2" t="n">
         <v>1.29</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI2" t="n">
         <v>2.39</v>
@@ -1640,16 +1640,16 @@
         <v>1.54</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.77</v>
+        <v>2.79</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CO2" t="n">
         <v>1.17</v>
@@ -1661,22 +1661,22 @@
         <v>2.49</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.26</v>
+        <v>3.21</v>
       </c>
       <c r="CU2" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>2.52</v>
+      </c>
+      <c r="CW2" t="n">
         <v>1.57</v>
-      </c>
-      <c r="CV2" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="CW2" t="n">
-        <v>1.55</v>
       </c>
       <c r="CX2" t="n">
         <v>1.48</v>
@@ -1694,85 +1694,85 @@
         <v>1.2</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
       <c r="DE2" t="n">
         <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.31</v>
+        <v>4.23</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.94</v>
+        <v>96.53</v>
       </c>
       <c r="DI2" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.62</v>
+        <v>6.47</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DM2" t="n">
-        <v>48.63</v>
+        <v>48.77</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.06</v>
+        <v>13.23</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14.81</v>
+        <v>14.65</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.5</v>
+        <v>7.47</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>53.25</v>
+        <v>52.64</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.87</v>
+        <v>13.7</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.94</v>
+        <v>9.65</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.94</v>
+        <v>4.06</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.94</v>
+        <v>24.23</v>
       </c>
       <c r="EB2" t="n">
         <v>1.51</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="3">
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C3" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="G3" t="n">
-        <v>3.14</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="K3" t="n">
-        <v>6.57</v>
+        <v>6.12</v>
       </c>
       <c r="L3" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="M3" t="n">
-        <v>60.14</v>
+        <v>56</v>
       </c>
       <c r="N3" t="n">
-        <v>1.14</v>
+        <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.43</v>
+        <v>3.12</v>
       </c>
       <c r="P3" t="n">
-        <v>16.43</v>
+        <v>15.25</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.43</v>
+        <v>10.38</v>
       </c>
       <c r="R3" t="n">
-        <v>8.57</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="T3" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.71</v>
+        <v>46.38</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>18</v>
+        <v>17.12</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.86</v>
+        <v>12.12</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.14</v>
+        <v>5</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.43</v>
+        <v>21.12</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.93</v>
+        <v>1.84</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.71</v>
+        <v>3.5</v>
       </c>
       <c r="AF3" t="n">
         <v>0.22</v>
@@ -1953,70 +1953,70 @@
         <v>3.56</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="BH3" t="n">
-        <v>12.62</v>
+        <v>12.24</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL3" t="n">
         <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.59</v>
       </c>
       <c r="BO3" t="n">
         <v>1.06</v>
       </c>
       <c r="BP3" t="n">
-        <v>6.06</v>
+        <v>5.82</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.56</v>
+        <v>6.41</v>
       </c>
       <c r="BR3" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS3" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU3" t="n">
-        <v>18.75</v>
+        <v>23.53</v>
       </c>
       <c r="BV3" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW3" t="n">
         <v>0</v>
       </c>
       <c r="BX3" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.22</v>
+        <v>2.15</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.37</v>
+        <v>2.27</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.65</v>
+        <v>3.67</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.68</v>
+        <v>3.74</v>
       </c>
       <c r="CC3" t="n">
         <v>2.99</v>
@@ -2028,10 +2028,10 @@
         <v>1.29</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CH3" t="n">
         <v>1.53</v>
@@ -2046,7 +2046,7 @@
         <v>1.32</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CM3" t="n">
         <v>3.02</v>
@@ -2061,33 +2061,33 @@
         <v>1.63</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.55</v>
+        <v>2.53</v>
       </c>
       <c r="CT3" t="n">
         <v>3.29</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX3" t="inlineStr"/>
       <c r="CY3" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CZ3" t="inlineStr"/>
       <c r="DA3" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="DB3" t="n">
         <v>1.21</v>
@@ -2096,49 +2096,49 @@
         <v>1.68</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="DE3" t="n">
         <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.06</v>
+        <v>3</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.18000000000001</v>
+        <v>94.53</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.63</v>
+        <v>3.53</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.37</v>
+        <v>6.17</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="DM3" t="n">
-        <v>49.81</v>
+        <v>48.47</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.31</v>
+        <v>3.17</v>
       </c>
       <c r="DP3" t="n">
-        <v>14.25</v>
+        <v>13.83</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.25</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DR3" t="n">
-        <v>9.06</v>
+        <v>8.82</v>
       </c>
       <c r="DS3" t="n">
         <v>0.12</v>
@@ -2150,28 +2150,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.44</v>
+        <v>44.95</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.75</v>
+        <v>14.53</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.69</v>
+        <v>10.47</v>
       </c>
       <c r="DZ3" t="n">
         <v>4.06</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.69</v>
+        <v>22.47</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.63</v>
+        <v>3.53</v>
       </c>
     </row>
     <row r="4">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="E4" t="n">
         <v>0.22</v>
@@ -2271,139 +2271,139 @@
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.14</v>
+        <v>0.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.86</v>
+        <v>0.88</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.71</v>
+        <v>1.62</v>
       </c>
       <c r="AI4" t="n">
-        <v>89.86</v>
+        <v>86.75</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.14</v>
+        <v>-0.12</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.29</v>
+        <v>4.12</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.86</v>
+        <v>35.12</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.29</v>
+        <v>0.25</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.29</v>
+        <v>11.62</v>
       </c>
       <c r="AS4" t="n">
-        <v>10.29</v>
+        <v>9.75</v>
       </c>
       <c r="AT4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>12.62</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.380000000000001</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>18.38</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.71</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="BL4" t="n">
         <v>1</v>
       </c>
-      <c r="AU4" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>51.57</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>13.14</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8.57</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>19.29</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>0.9399999999999999</v>
-      </c>
       <c r="BM4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="BO4" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.94</v>
+        <v>4.82</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.25</v>
+        <v>5.35</v>
       </c>
       <c r="BR4" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT4" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU4" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BW4" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX4" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY4" t="n">
         <v>1.83</v>
@@ -2418,19 +2418,19 @@
         <v>3.85</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.87</v>
+        <v>2.93</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="CE4" t="n">
         <v>1.29</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH4" t="n">
         <v>1.54</v>
@@ -2448,19 +2448,19 @@
         <v>1.75</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO4" t="n">
         <v>1.17</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
@@ -2484,7 +2484,7 @@
         <v>1.46</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.58</v>
@@ -2502,46 +2502,46 @@
         <v>2.61</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.88</v>
+        <v>85.59</v>
       </c>
       <c r="DI4" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.69</v>
+        <v>1.64</v>
       </c>
       <c r="DK4" t="n">
-        <v>5</v>
+        <v>4.88</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.57</v>
+        <v>0.53</v>
       </c>
       <c r="DM4" t="n">
-        <v>43.31</v>
+        <v>42.11</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.44</v>
+        <v>12.24</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.81</v>
+        <v>11.94</v>
       </c>
       <c r="DR4" t="n">
-        <v>9.130000000000001</v>
+        <v>8.94</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2553,28 +2553,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.06</v>
+        <v>49.18</v>
       </c>
       <c r="DW4" t="n">
         <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.62</v>
+        <v>14.29</v>
       </c>
       <c r="DY4" t="n">
-        <v>9.06</v>
+        <v>8.94</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.56</v>
+        <v>5.35</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.5</v>
+        <v>18.12</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="5">
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C5" t="n">
         <v>8</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E5" t="n">
         <v>0.12</v>
@@ -2674,52 +2674,52 @@
         <v>1.88</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.12</v>
+        <v>3.56</v>
       </c>
       <c r="AI5" t="n">
-        <v>95.62</v>
+        <v>98.44</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.38</v>
+        <v>5.78</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>49</v>
+        <v>49.33</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.75</v>
+        <v>11.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.88</v>
+        <v>11.33</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.75</v>
+        <v>8.33</v>
       </c>
       <c r="AT5" t="n">
         <v>2</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2731,37 +2731,37 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>49.88</v>
+        <v>50</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA5" t="n">
-        <v>14</v>
+        <v>14.56</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.12</v>
+        <v>10.22</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.88</v>
+        <v>4.33</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.25</v>
+        <v>21.22</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.51</v>
+        <v>1.58</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.94</v>
+        <v>11.24</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.44</v>
+        <v>3.41</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.88</v>
@@ -2773,40 +2773,40 @@
         <v>0.88</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="BO5" t="n">
         <v>1.94</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.12</v>
+        <v>6.41</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BT5" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BU5" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV5" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW5" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX5" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BY5" t="n">
         <v>2.54</v>
@@ -2815,43 +2815,43 @@
         <v>2.62</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.74</v>
+        <v>3.71</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CH5" t="n">
         <v>1.52</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK5" t="n">
         <v>1.35</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CN5" t="n">
         <v>2.18</v>
@@ -2863,88 +2863,88 @@
         <v>1.66</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CU5" t="n">
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX5" t="n">
         <v>1.46</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.6</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DB5" t="n">
         <v>1.22</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="DE5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DF5" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="DG5" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="DH5" t="n">
+        <v>92.12</v>
+      </c>
+      <c r="DI5" t="n">
         <v>0.12</v>
       </c>
-      <c r="DF5" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="DG5" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="DH5" t="n">
-        <v>90.31</v>
-      </c>
-      <c r="DI5" t="n">
-        <v>0.06</v>
-      </c>
       <c r="DJ5" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.25</v>
+        <v>5.47</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.31</v>
+        <v>46.64</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DO5" t="n">
         <v>2.12</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.32</v>
+        <v>11.12</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.5</v>
+        <v>12.17</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.119999999999999</v>
+        <v>7.94</v>
       </c>
       <c r="DS5" t="n">
         <v>0.06</v>
@@ -2956,28 +2956,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.75</v>
+        <v>49.82</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.88</v>
+        <v>13.24</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.119999999999999</v>
+        <v>9.23</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.44</v>
+        <v>21.41</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.06</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -2999,82 +2999,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="G6" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="H6" t="n">
-        <v>92.88</v>
+        <v>90.89</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="K6" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="M6" t="n">
-        <v>34.75</v>
+        <v>34.33</v>
       </c>
       <c r="N6" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="O6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="P6" t="n">
         <v>13</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.88</v>
+        <v>13.78</v>
       </c>
       <c r="R6" t="n">
-        <v>8.619999999999999</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="T6" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="U6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>39.62</v>
+        <v>39.78</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.88</v>
+        <v>12.89</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.119999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="AC6" t="n">
-        <v>20.38</v>
+        <v>21.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3161,31 +3161,31 @@
         <v>2.88</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.81</v>
+        <v>10.59</v>
       </c>
       <c r="BI6" t="n">
         <v>2.88</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK6" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="BL6" t="n">
         <v>0.88</v>
       </c>
-      <c r="BL6" t="n">
-        <v>0.8100000000000001</v>
-      </c>
       <c r="BM6" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.44</v>
+        <v>1.35</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.81</v>
+        <v>4.59</v>
       </c>
       <c r="BQ6" t="n">
         <v>6</v>
@@ -3194,34 +3194,34 @@
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU6" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BV6" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.07</v>
+        <v>3.1</v>
       </c>
       <c r="BZ6" t="n">
         <v>3.19</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CC6" t="n">
         <v>4.2</v>
@@ -3230,58 +3230,58 @@
         <v>4.66</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CN6" t="n">
         <v>2.08</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CW6" t="n">
         <v>1.66</v>
@@ -3299,55 +3299,55 @@
         <v>2.1</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.83</v>
+        <v>2.86</v>
       </c>
       <c r="DE6" t="n">
         <v>0.06</v>
       </c>
       <c r="DF6" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG6" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="DH6" t="n">
+        <v>93.34999999999999</v>
+      </c>
+      <c r="DI6" t="n">
+        <v>0</v>
+      </c>
+      <c r="DJ6" t="n">
+        <v>3</v>
+      </c>
+      <c r="DK6" t="n">
+        <v>4.59</v>
+      </c>
+      <c r="DL6" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="DM6" t="n">
+        <v>38.47</v>
+      </c>
+      <c r="DN6" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="DO6" t="n">
         <v>2.12</v>
       </c>
-      <c r="DG6" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DH6" t="n">
-        <v>94.5</v>
-      </c>
-      <c r="DI6" t="n">
-        <v>0</v>
-      </c>
-      <c r="DJ6" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="DK6" t="n">
-        <v>4.69</v>
-      </c>
-      <c r="DL6" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DM6" t="n">
-        <v>38.94</v>
-      </c>
-      <c r="DN6" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="DO6" t="n">
-        <v>2.19</v>
-      </c>
       <c r="DP6" t="n">
-        <v>12.69</v>
+        <v>12.71</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14.07</v>
+        <v>14</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.18</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DS6" t="n">
         <v>0.12</v>
@@ -3359,28 +3359,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.68</v>
+        <v>42.59</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DX6" t="n">
         <v>12.82</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.869999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.94</v>
+        <v>4</v>
       </c>
       <c r="EA6" t="n">
-        <v>20</v>
+        <v>20.71</v>
       </c>
       <c r="EB6" t="n">
         <v>1.37</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.5</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="7">
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E7" t="n">
         <v>0.12</v>
@@ -3480,139 +3480,139 @@
         <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG7" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AH7" t="n">
         <v>2</v>
       </c>
-      <c r="AH7" t="n">
-        <v>1.75</v>
-      </c>
       <c r="AI7" t="n">
-        <v>95.88</v>
+        <v>94.44</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="AL7" t="n">
-        <v>7</v>
+        <v>6.89</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN7" t="n">
-        <v>44.88</v>
+        <v>45.22</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.62</v>
+        <v>0.78</v>
       </c>
       <c r="AP7" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.12</v>
+        <v>10.22</v>
       </c>
       <c r="AR7" t="n">
-        <v>16</v>
+        <v>16.22</v>
       </c>
       <c r="AS7" t="n">
-        <v>6.5</v>
+        <v>6.89</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>54.88</v>
+        <v>53.22</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>15.62</v>
+        <v>15</v>
       </c>
       <c r="BB7" t="n">
-        <v>10.88</v>
+        <v>10.22</v>
       </c>
       <c r="BC7" t="n">
-        <v>4.75</v>
+        <v>4.78</v>
       </c>
       <c r="BD7" t="n">
-        <v>22.25</v>
+        <v>22.44</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BH7" t="n">
         <v>11.12</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BL7" t="n">
         <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="BO7" t="n">
         <v>1.12</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.19</v>
+        <v>5.29</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.94</v>
+        <v>4.88</v>
       </c>
       <c r="BR7" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS7" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>47.06</v>
       </c>
       <c r="BU7" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BV7" t="n">
-        <v>18.75</v>
+        <v>17.65</v>
       </c>
       <c r="BW7" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX7" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BY7" t="n">
         <v>1.93</v>
@@ -3621,16 +3621,16 @@
         <v>1.95</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.21</v>
+        <v>2.18</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.66</v>
+        <v>2.6</v>
       </c>
       <c r="CE7" t="n">
         <v>1.3</v>
@@ -3639,13 +3639,13 @@
         <v>2.44</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH7" t="n">
         <v>1.53</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.55</v>
@@ -3657,7 +3657,7 @@
         <v>1.66</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CN7" t="n">
         <v>2.15</v>
@@ -3666,28 +3666,28 @@
         <v>1.19</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CR7" t="n">
         <v>1.37</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CT7" t="n">
         <v>3.25</v>
       </c>
       <c r="CU7" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
@@ -3702,88 +3702,88 @@
         <v>2.14</v>
       </c>
       <c r="DB7" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
       <c r="DH7" t="n">
-        <v>95.56</v>
+        <v>94.81999999999999</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.18</v>
+        <v>2.24</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.44</v>
+        <v>6.41</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM7" t="n">
-        <v>49.19</v>
+        <v>49.12</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
       <c r="DP7" t="n">
         <v>11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.19</v>
+        <v>15.35</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.69</v>
+        <v>6.89</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.06</v>
+        <v>0.11</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.25</v>
+        <v>53.41</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.5</v>
+        <v>15.18</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.57</v>
+        <v>10.23</v>
       </c>
       <c r="DZ7" t="n">
         <v>4.94</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.75</v>
+        <v>22.82</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="8">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3805,82 +3805,82 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="G8" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="H8" t="n">
-        <v>87.12</v>
+        <v>85.89</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J8" t="n">
-        <v>3.25</v>
+        <v>3.33</v>
       </c>
       <c r="K8" t="n">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="L8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="M8" t="n">
-        <v>48.38</v>
+        <v>47.22</v>
       </c>
       <c r="N8" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="O8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="P8" t="n">
+        <v>13.44</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>10.56</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6.78</v>
+      </c>
+      <c r="S8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="T8" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" t="n">
+        <v>49.89</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>12.56</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>20.11</v>
+      </c>
+      <c r="AD8" t="n">
         <v>1.38</v>
       </c>
-      <c r="O8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="P8" t="n">
-        <v>13.75</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="R8" t="n">
-        <v>7</v>
-      </c>
-      <c r="S8" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T8" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="U8" t="n">
-        <v>0</v>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
-      </c>
-      <c r="W8" t="n">
-        <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>51.88</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>12.25</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>9.119999999999999</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>3.12</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AE8" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3964,70 +3964,70 @@
         <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.19</v>
+        <v>9.24</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.25</v>
+        <v>0.29</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL8" t="n">
         <v>0.88</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP8" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.06</v>
+        <v>5.18</v>
       </c>
       <c r="BR8" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS8" t="n">
-        <v>68.75</v>
+        <v>70.59</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV8" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW8" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.37</v>
+        <v>2.31</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.49</v>
+        <v>2.41</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.77</v>
+        <v>3.79</v>
       </c>
       <c r="CC8" t="n">
         <v>3.51</v>
@@ -4057,7 +4057,7 @@
         <v>1.4</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="CM8" t="n">
         <v>2.68</v>
@@ -4072,25 +4072,25 @@
         <v>1.64</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CR8" t="n">
         <v>1.39</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="CT8" t="n">
         <v>3.11</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV8" t="n">
         <v>2.47</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CX8" t="n">
         <v>1.49</v>
@@ -4111,49 +4111,49 @@
         <v>1.68</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="DE8" t="n">
         <v>0.06</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.25</v>
+        <v>2.41</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.87</v>
+        <v>90</v>
       </c>
       <c r="DI8" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="DK8" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DM8" t="n">
-        <v>45.38</v>
+        <v>44.94</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.32</v>
+        <v>1.41</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.18</v>
+        <v>13.05</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.38</v>
+        <v>11</v>
       </c>
       <c r="DR8" t="n">
-        <v>8.06</v>
+        <v>7.88</v>
       </c>
       <c r="DS8" t="n">
         <v>0.06</v>
@@ -4165,28 +4165,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.56</v>
+        <v>47.71</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.88</v>
+        <v>13</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.43</v>
+        <v>9.35</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.44</v>
+        <v>3.65</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.81</v>
+        <v>20.35</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.81</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E9" t="n">
         <v>0.25</v>
@@ -4289,136 +4289,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.25</v>
+        <v>2.22</v>
       </c>
       <c r="AI9" t="n">
-        <v>66.25</v>
+        <v>70.89</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.25</v>
+        <v>4.22</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN9" t="n">
-        <v>32.88</v>
+        <v>34.44</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="AP9" t="n">
         <v>2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>14.12</v>
+        <v>13.11</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.88</v>
+        <v>11.67</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.880000000000001</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>45</v>
+        <v>47.33</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>13.12</v>
+        <v>12.78</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.75</v>
+        <v>5.44</v>
       </c>
       <c r="BD9" t="n">
-        <v>23.88</v>
+        <v>22.89</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.19</v>
+        <v>10.18</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.19</v>
+        <v>4.12</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.62</v>
+        <v>0.65</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.31</v>
+        <v>4.24</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.88</v>
+        <v>5.94</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BU9" t="n">
-        <v>62.5</v>
+        <v>58.82</v>
       </c>
       <c r="BV9" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BW9" t="n">
-        <v>25</v>
+        <v>23.53</v>
       </c>
       <c r="BX9" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BY9" t="n">
         <v>2.82</v>
@@ -4427,16 +4427,16 @@
         <v>3.23</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.99</v>
+        <v>4</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.28</v>
+        <v>4.21</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.16</v>
+        <v>5.05</v>
       </c>
       <c r="CE9" t="n">
         <v>1.28</v>
@@ -4445,7 +4445,7 @@
         <v>2.3</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CH9" t="n">
         <v>1.56</v>
@@ -4457,31 +4457,31 @@
         <v>1.54</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO9" t="n">
         <v>1.16</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CT9" t="n">
         <v>3.31</v>
@@ -4490,7 +4490,7 @@
         <v>1.59</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CW9" t="n">
         <v>1.57</v>
@@ -4499,7 +4499,7 @@
         <v>1.47</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.58</v>
@@ -4511,79 +4511,79 @@
         <v>1.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="DE9" t="n">
         <v>0.12</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.5</v>
+        <v>79.29000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.5</v>
+        <v>4.47</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.44</v>
+        <v>35.17</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.12</v>
+        <v>11.7</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13</v>
+        <v>12.82</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.32</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.06</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.44</v>
+        <v>46.65</v>
       </c>
       <c r="DW9" t="n">
         <v>0.06</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.18</v>
+        <v>12.06</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.5</v>
+        <v>7.47</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.69</v>
+        <v>4.58</v>
       </c>
       <c r="EA9" t="n">
-        <v>22.06</v>
+        <v>21.65</v>
       </c>
       <c r="EB9" t="n">
         <v>1.34</v>
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,139 +4689,139 @@
         <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="AI10" t="n">
-        <v>103.25</v>
+        <v>105.78</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.25</v>
+        <v>0.44</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.25</v>
+        <v>47.22</v>
       </c>
       <c r="AO10" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.75</v>
+        <v>13.22</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.88</v>
+        <v>13.89</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.88</v>
+        <v>6.67</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AU10" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>56.12</v>
+        <v>57.33</v>
       </c>
       <c r="AZ10" t="n">
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.75</v>
+        <v>13</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.38</v>
+        <v>7.33</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.38</v>
+        <v>5.67</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.38</v>
+        <v>19.89</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.53</v>
+        <v>1.57</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="BG10" t="n">
         <v>3.06</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.25</v>
+        <v>9.24</v>
       </c>
       <c r="BI10" t="n">
         <v>3.06</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.19</v>
+        <v>5.24</v>
       </c>
       <c r="BR10" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS10" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BT10" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BU10" t="n">
-        <v>43.75</v>
+        <v>41.18</v>
       </c>
       <c r="BV10" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY10" t="n">
         <v>1.87</v>
@@ -4830,16 +4830,16 @@
         <v>1.95</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.38</v>
+        <v>2.35</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.45</v>
+        <v>2.41</v>
       </c>
       <c r="CE10" t="n">
         <v>1.3</v>
@@ -4857,16 +4857,16 @@
         <v>2.31</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CN10" t="n">
         <v>2.21</v>
@@ -4884,7 +4884,7 @@
         <v>1.36</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT10" t="n">
         <v>3.27</v>
@@ -4893,10 +4893,10 @@
         <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX10" t="n">
         <v>1.51</v>
@@ -4914,85 +4914,85 @@
         <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.06</v>
+        <v>3.12</v>
       </c>
       <c r="DH10" t="n">
-        <v>108.18</v>
+        <v>109.23</v>
       </c>
       <c r="DI10" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.56</v>
+        <v>5.59</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.32</v>
+        <v>0.41</v>
       </c>
       <c r="DM10" t="n">
-        <v>53.25</v>
+        <v>52.88</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.32</v>
+        <v>13.06</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.75</v>
+        <v>13.76</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.69</v>
+        <v>6.59</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>57.37</v>
+        <v>57.94</v>
       </c>
       <c r="DW10" t="n">
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>15.44</v>
+        <v>15.41</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.75</v>
+        <v>9.58</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.69</v>
+        <v>5.83</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.81</v>
+        <v>20.06</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="11">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
@@ -5014,82 +5014,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="G11" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="H11" t="n">
-        <v>93.75</v>
+        <v>95.33</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J11" t="n">
-        <v>2.12</v>
+        <v>2.44</v>
       </c>
       <c r="K11" t="n">
-        <v>5.38</v>
+        <v>5.11</v>
       </c>
       <c r="L11" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M11" t="n">
-        <v>44.5</v>
+        <v>43.56</v>
       </c>
       <c r="N11" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="O11" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="P11" t="n">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="Q11" t="n">
-        <v>8.619999999999999</v>
+        <v>9.44</v>
       </c>
       <c r="R11" t="n">
-        <v>10</v>
+        <v>10.22</v>
       </c>
       <c r="S11" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="T11" t="n">
-        <v>0.75</v>
+        <v>0.78</v>
       </c>
       <c r="U11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>47.12</v>
+        <v>48.22</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.88</v>
+        <v>12.56</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.380000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.5</v>
+        <v>4.22</v>
       </c>
       <c r="AC11" t="n">
-        <v>18.62</v>
+        <v>19.33</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.45</v>
+        <v>1.41</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5173,70 +5173,70 @@
         <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.5</v>
+        <v>10.29</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BM11" t="n">
         <v>0.88</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.88</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.75</v>
+        <v>4.59</v>
       </c>
       <c r="BQ11" t="n">
         <v>4.94</v>
       </c>
       <c r="BR11" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>62.5</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BU11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV11" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW11" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX11" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.55</v>
+        <v>3.54</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.83</v>
+        <v>3.8</v>
       </c>
       <c r="CC11" t="n">
         <v>2.75</v>
@@ -5248,16 +5248,16 @@
         <v>1.3</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.28</v>
+        <v>3.26</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.54</v>
@@ -5266,46 +5266,46 @@
         <v>1.36</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="CO11" t="n">
         <v>1.18</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.49</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.34</v>
+        <v>3.3</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.49</v>
+        <v>2.46</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX11" t="n">
         <v>1.44</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ11" t="n">
         <v>2.63</v>
@@ -5317,85 +5317,85 @@
         <v>1.2</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.57</v>
+        <v>2.6</v>
       </c>
       <c r="DE11" t="n">
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DH11" t="n">
-        <v>91.25</v>
+        <v>92.23</v>
       </c>
       <c r="DI11" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.56</v>
+        <v>4.47</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.44</v>
+        <v>44.89</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.88</v>
+        <v>1.82</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.93</v>
+        <v>13.82</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.31</v>
+        <v>11.59</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.44</v>
+        <v>9.59</v>
       </c>
       <c r="DS11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DT11" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="DU11" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV11" t="n">
+        <v>47.53</v>
+      </c>
+      <c r="DW11" t="n">
         <v>0.12</v>
       </c>
-      <c r="DT11" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="DU11" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV11" t="n">
-        <v>46.94</v>
-      </c>
-      <c r="DW11" t="n">
-        <v>0.06</v>
-      </c>
       <c r="DX11" t="n">
-        <v>12.44</v>
+        <v>12.3</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.32</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.75</v>
+        <v>21</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="12">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C12" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
@@ -5417,49 +5417,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>0.88</v>
       </c>
       <c r="G12" t="n">
-        <v>3.14</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
-        <v>90</v>
+        <v>89.25</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="K12" t="n">
-        <v>5.57</v>
+        <v>5.75</v>
       </c>
       <c r="L12" t="n">
-        <v>0.86</v>
+        <v>0.75</v>
       </c>
       <c r="M12" t="n">
-        <v>41.86</v>
+        <v>40.88</v>
       </c>
       <c r="N12" t="n">
-        <v>0.71</v>
+        <v>0.62</v>
       </c>
       <c r="O12" t="n">
-        <v>2.43</v>
+        <v>2.5</v>
       </c>
       <c r="P12" t="n">
-        <v>12.71</v>
+        <v>12</v>
       </c>
       <c r="Q12" t="n">
-        <v>15.14</v>
+        <v>14.25</v>
       </c>
       <c r="R12" t="n">
-        <v>8.43</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5471,28 +5471,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.86</v>
+        <v>52.38</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>14</v>
+        <v>13.75</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.43</v>
+        <v>9.25</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.57</v>
+        <v>4.5</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.14</v>
+        <v>18.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.71</v>
+        <v>1.5</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5576,61 +5576,61 @@
         <v>3.44</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BH12" t="n">
-        <v>9.81</v>
+        <v>10.18</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.75</v>
+        <v>6.06</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT12" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU12" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV12" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW12" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX12" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="BZ12" t="n">
         <v>2.18</v>
@@ -5651,46 +5651,46 @@
         <v>1.32</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CH12" t="n">
         <v>1.5</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK12" t="n">
         <v>1.34</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CN12" t="n">
         <v>2.22</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="CP12" t="n">
         <v>1.68</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CT12" t="n">
         <v>3.31</v>
@@ -5699,7 +5699,7 @@
         <v>1.53</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW12" t="n">
         <v>1.6</v>
@@ -5717,88 +5717,88 @@
         <v>2.17</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC12" t="n">
         <v>1.74</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DE12" t="n">
         <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.88</v>
+        <v>2.94</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.69</v>
+        <v>83.70999999999999</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.81</v>
+        <v>2.65</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.62</v>
+        <v>4.77</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.38</v>
+        <v>0.35</v>
       </c>
       <c r="DM12" t="n">
-        <v>37.94</v>
+        <v>37.71</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.18</v>
+        <v>13.76</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.81</v>
+        <v>13.47</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.81</v>
+        <v>8.77</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.07</v>
+        <v>50.95</v>
       </c>
       <c r="DW12" t="n">
         <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.88</v>
+        <v>12.82</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.869999999999999</v>
+        <v>8.82</v>
       </c>
       <c r="DZ12" t="n">
         <v>4</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.25</v>
+        <v>19.12</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.68</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="13">
@@ -5808,94 +5808,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="F13" t="n">
-        <v>1.62</v>
+        <v>1.89</v>
       </c>
       <c r="G13" t="n">
-        <v>2.62</v>
+        <v>2.67</v>
       </c>
       <c r="H13" t="n">
-        <v>105.88</v>
+        <v>106.44</v>
       </c>
       <c r="I13" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="J13" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="K13" t="n">
-        <v>6.38</v>
+        <v>6.11</v>
       </c>
       <c r="L13" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>49.62</v>
+        <v>49.78</v>
       </c>
       <c r="N13" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="O13" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="P13" t="n">
-        <v>12</v>
+        <v>11.67</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.12</v>
+        <v>13.33</v>
       </c>
       <c r="R13" t="n">
-        <v>8.119999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="S13" t="n">
-        <v>1</v>
+        <v>1.22</v>
       </c>
       <c r="T13" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="U13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V13" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.38</v>
+        <v>50.67</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>16.88</v>
+        <v>16.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.12</v>
+        <v>10.22</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.75</v>
+        <v>6.44</v>
       </c>
       <c r="AC13" t="n">
-        <v>22</v>
+        <v>23.11</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.62</v>
+        <v>3</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,70 +5979,70 @@
         <v>2.88</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.94</v>
+        <v>9.82</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.31</v>
+        <v>0.41</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.75</v>
+        <v>1.82</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.06</v>
+        <v>1.12</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.69</v>
+        <v>4.65</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.44</v>
+        <v>4.41</v>
       </c>
       <c r="BR13" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS13" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT13" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BU13" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="BZ13" t="n">
         <v>2.42</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CC13" t="n">
         <v>2.82</v>
@@ -6054,10 +6054,10 @@
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CH13" t="n">
         <v>1.52</v>
@@ -6066,13 +6066,13 @@
         <v>2.36</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK13" t="n">
         <v>1.34</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CM13" t="n">
         <v>2.91</v>
@@ -6084,16 +6084,16 @@
         <v>1.19</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="CR13" t="n">
         <v>1.36</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.57</v>
+        <v>2.55</v>
       </c>
       <c r="CT13" t="n">
         <v>3.31</v>
@@ -6102,7 +6102,7 @@
         <v>1.54</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CW13" t="n">
         <v>1.57</v>
@@ -6123,85 +6123,85 @@
         <v>1.21</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.68</v>
+        <v>1.82</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="DH13" t="n">
-        <v>98.5</v>
+        <v>99.23</v>
       </c>
       <c r="DI13" t="n">
         <v>0.18</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.87</v>
+        <v>3.06</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.38</v>
+        <v>5.3</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM13" t="n">
-        <v>42.62</v>
+        <v>43.12</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.31</v>
+        <v>2.23</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.31</v>
+        <v>12.12</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.93</v>
+        <v>14</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.869999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.75</v>
+        <v>48.06</v>
       </c>
       <c r="DW13" t="n">
         <v>0.06</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.82</v>
+        <v>13.88</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.5</v>
+        <v>8.65</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.32</v>
+        <v>5.24</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.44</v>
+        <v>22.06</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.75</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E14" t="n">
         <v>0.12</v>
@@ -6301,52 +6301,52 @@
         <v>3.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.38</v>
+        <v>1.22</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.25</v>
+        <v>3.11</v>
       </c>
       <c r="AI14" t="n">
-        <v>86.38</v>
+        <v>90.67</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.5</v>
+        <v>5.22</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN14" t="n">
-        <v>39.38</v>
+        <v>40.44</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.88</v>
+        <v>11.78</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="AS14" t="n">
         <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AV14" t="n">
         <v>0</v>
@@ -6358,82 +6358,82 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>47.88</v>
+        <v>49.56</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>13.12</v>
+        <v>12.89</v>
       </c>
       <c r="BB14" t="n">
-        <v>9.5</v>
+        <v>9</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.62</v>
+        <v>3.89</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.25</v>
+        <v>18.89</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="BF14" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.5</v>
+        <v>10.24</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BO14" t="n">
         <v>1.12</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.38</v>
+        <v>4.24</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.19</v>
+        <v>5.12</v>
       </c>
       <c r="BR14" t="n">
-        <v>87.5</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="BS14" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BV14" t="n">
-        <v>37.5</v>
+        <v>35.29</v>
       </c>
       <c r="BW14" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BY14" t="n">
         <v>2.48</v>
@@ -6442,19 +6442,19 @@
         <v>2.64</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.86</v>
+        <v>3.9</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.69</v>
+        <v>3.75</v>
       </c>
       <c r="CD14" t="n">
-        <v>3.88</v>
+        <v>4.07</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="CF14" t="n">
         <v>2.31</v>
@@ -6466,7 +6466,7 @@
         <v>1.56</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.54</v>
@@ -6475,13 +6475,13 @@
         <v>1.35</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CO14" t="n">
         <v>1.16</v>
@@ -6502,21 +6502,21 @@
         <v>3.31</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DB14" t="n">
         <v>1.2</v>
@@ -6525,49 +6525,49 @@
         <v>1.64</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.75</v>
+        <v>1.64</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DH14" t="n">
-        <v>81.31999999999999</v>
+        <v>83.88</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.75</v>
+        <v>2.59</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.19</v>
+        <v>5.06</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM14" t="n">
-        <v>40.75</v>
+        <v>41.23</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.32</v>
+        <v>13.18</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11</v>
+        <v>10.76</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.5</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0</v>
@@ -6579,28 +6579,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.44</v>
+        <v>48.36</v>
       </c>
       <c r="DW14" t="n">
         <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.18</v>
+        <v>12.12</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.94</v>
+        <v>7.77</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.25</v>
+        <v>4.36</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.31</v>
+        <v>17.71</v>
       </c>
       <c r="EB14" t="n">
         <v>1.37</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.62</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="15">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6703,49 +6703,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.88</v>
+        <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AI15" t="n">
-        <v>81.12</v>
+        <v>79.67</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AK15" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.62</v>
+        <v>5.44</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="AN15" t="n">
-        <v>39.75</v>
+        <v>39.11</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11</v>
+        <v>11.56</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.88</v>
+        <v>13.33</v>
       </c>
       <c r="AS15" t="n">
-        <v>8</v>
+        <v>8.44</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AU15" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6757,82 +6757,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>55.5</v>
+        <v>54.56</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>16.75</v>
+        <v>17.11</v>
       </c>
       <c r="BB15" t="n">
-        <v>11.38</v>
+        <v>11.22</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.38</v>
+        <v>5.89</v>
       </c>
       <c r="BD15" t="n">
-        <v>18</v>
+        <v>17.67</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.72</v>
+        <v>1.77</v>
       </c>
       <c r="BF15" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.44</v>
+        <v>10.29</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.5</v>
+        <v>0.59</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM15" t="n">
         <v>0.88</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="BO15" t="n">
-        <v>1</v>
+        <v>1.06</v>
       </c>
       <c r="BP15" t="n">
-        <v>5</v>
+        <v>4.94</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.44</v>
+        <v>5.35</v>
       </c>
       <c r="BR15" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS15" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT15" t="n">
-        <v>43.75</v>
+        <v>47.06</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>29.41</v>
       </c>
       <c r="BV15" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BW15" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BX15" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY15" t="n">
         <v>2.2</v>
@@ -6841,16 +6841,16 @@
         <v>2.39</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CB15" t="n">
         <v>3.8</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.09</v>
+        <v>3.06</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.42</v>
+        <v>3.34</v>
       </c>
       <c r="CE15" t="n">
         <v>1.26</v>
@@ -6865,7 +6865,7 @@
         <v>1.6</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.55</v>
+        <v>2.54</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.49</v>
@@ -6874,7 +6874,7 @@
         <v>1.37</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM15" t="n">
         <v>2.83</v>
@@ -6909,7 +6909,7 @@
         <v>1.46</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.55</v>
@@ -6930,43 +6930,43 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.75</v>
+        <v>2.65</v>
       </c>
       <c r="DH15" t="n">
-        <v>93.56</v>
+        <v>92.06</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.19</v>
+        <v>0.17</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.37</v>
+        <v>5.29</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.59</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.82</v>
+        <v>46.06</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.87</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.25</v>
+        <v>12.47</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.5</v>
+        <v>12.29</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.06</v>
+        <v>7.35</v>
       </c>
       <c r="DS15" t="n">
         <v>0.12</v>
@@ -6978,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.56</v>
+        <v>55.06</v>
       </c>
       <c r="DW15" t="n">
         <v>0.06</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.25</v>
+        <v>16.47</v>
       </c>
       <c r="DY15" t="n">
-        <v>11</v>
+        <v>10.94</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.25</v>
+        <v>5.53</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.75</v>
+        <v>18.53</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
     </row>
     <row r="16">
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -7021,82 +7021,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.75</v>
+        <v>1.89</v>
       </c>
       <c r="G16" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="H16" t="n">
-        <v>100</v>
+        <v>95.56</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>4.78</v>
       </c>
       <c r="L16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M16" t="n">
-        <v>45.25</v>
+        <v>43.11</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="P16" t="n">
-        <v>11.12</v>
+        <v>11.44</v>
       </c>
       <c r="Q16" t="n">
-        <v>14.5</v>
+        <v>13.89</v>
       </c>
       <c r="R16" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="S16" t="n">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="T16" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="U16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>52.75</v>
+        <v>50.56</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.62</v>
+        <v>12.33</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.380000000000001</v>
+        <v>8</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.75</v>
+        <v>20.22</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AF16" t="n">
         <v>0.12</v>
@@ -7180,67 +7180,67 @@
         <v>2.88</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BH16" t="n">
-        <v>10.06</v>
+        <v>10</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.44</v>
+        <v>2.47</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="BL16" t="n">
         <v>0.88</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.44</v>
+        <v>4.35</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.62</v>
+        <v>5.65</v>
       </c>
       <c r="BR16" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS16" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BT16" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU16" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BV16" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.37</v>
+        <v>2.52</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB16" t="n">
         <v>3.72</v>
@@ -7252,7 +7252,7 @@
         <v>3.27</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF16" t="n">
         <v>2.45</v>
@@ -7261,10 +7261,10 @@
         <v>3.24</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.58</v>
@@ -7273,10 +7273,10 @@
         <v>1.35</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CN16" t="n">
         <v>2.2</v>
@@ -7303,10 +7303,10 @@
         <v>1.54</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX16" t="n">
         <v>1.45</v>
@@ -7327,49 +7327,49 @@
         <v>1.7</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.88</v>
+        <v>1.94</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.25</v>
+        <v>3.18</v>
       </c>
       <c r="DH16" t="n">
-        <v>97.06</v>
+        <v>94.88</v>
       </c>
       <c r="DI16" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.5</v>
+        <v>5.35</v>
       </c>
       <c r="DL16" t="n">
         <v>0.18</v>
       </c>
       <c r="DM16" t="n">
-        <v>46.62</v>
+        <v>45.41</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.25</v>
+        <v>2.18</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.68</v>
+        <v>12.76</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.38</v>
+        <v>14.06</v>
       </c>
       <c r="DR16" t="n">
-        <v>8</v>
+        <v>7.94</v>
       </c>
       <c r="DS16" t="n">
         <v>0.18</v>
@@ -7381,28 +7381,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>51.38</v>
+        <v>50.3</v>
       </c>
       <c r="DW16" t="n">
         <v>0.06</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.12</v>
+        <v>12</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.82</v>
+        <v>7.65</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.31</v>
+        <v>4.35</v>
       </c>
       <c r="EA16" t="n">
-        <v>21.18</v>
+        <v>20.88</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.56</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="17">
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D17" t="n">
         <v>8</v>
@@ -7424,82 +7424,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="G17" t="n">
-        <v>3.38</v>
+        <v>3.67</v>
       </c>
       <c r="H17" t="n">
-        <v>93.88</v>
+        <v>97.11</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.5</v>
+        <v>2.33</v>
       </c>
       <c r="K17" t="n">
-        <v>6.25</v>
+        <v>6.33</v>
       </c>
       <c r="L17" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="M17" t="n">
-        <v>48.88</v>
+        <v>52.22</v>
       </c>
       <c r="N17" t="n">
-        <v>0.88</v>
+        <v>0.78</v>
       </c>
       <c r="O17" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="P17" t="n">
-        <v>13.25</v>
+        <v>13.33</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.12</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="R17" t="n">
-        <v>8.5</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S17" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="T17" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="U17" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="V17" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>53.75</v>
+        <v>55</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.25</v>
+        <v>16.44</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.62</v>
+        <v>10.67</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.62</v>
+        <v>5.78</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.62</v>
+        <v>21.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="AE17" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="AF17" t="n">
         <v>0.25</v>
@@ -7583,70 +7583,70 @@
         <v>2.38</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.38</v>
+        <v>10.35</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.62</v>
+        <v>2.71</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.88</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.12</v>
+        <v>1.18</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.88</v>
+        <v>4.76</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.5</v>
+        <v>5.59</v>
       </c>
       <c r="BR17" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BU17" t="n">
-        <v>12.5</v>
+        <v>17.65</v>
       </c>
       <c r="BV17" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BW17" t="n">
-        <v>6.25</v>
+        <v>5.88</v>
       </c>
       <c r="BX17" t="n">
-        <v>56.25</v>
+        <v>58.82</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="CA17" t="n">
         <v>3.67</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC17" t="n">
         <v>2.18</v>
@@ -7661,7 +7661,7 @@
         <v>2.42</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH17" t="n">
         <v>1.52</v>
@@ -7673,22 +7673,22 @@
         <v>1.59</v>
       </c>
       <c r="CK17" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL17" t="n">
         <v>1.69</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="CO17" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CQ17" t="n">
         <v>2.63</v>
@@ -7730,82 +7730,82 @@
         <v>1.71</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="DE17" t="n">
         <v>0.12</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.44</v>
+        <v>1.41</v>
       </c>
       <c r="DG17" t="n">
-        <v>2.94</v>
+        <v>3.12</v>
       </c>
       <c r="DH17" t="n">
-        <v>94.38</v>
+        <v>96.06</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.38</v>
+        <v>5.47</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="DM17" t="n">
-        <v>45.38</v>
+        <v>47.35</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.44</v>
+        <v>2.35</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.82</v>
+        <v>12.88</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.56</v>
+        <v>10.41</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.94</v>
+        <v>7.77</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.18</v>
+        <v>0.23</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>53.68</v>
+        <v>54.35</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.68</v>
+        <v>15.82</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.25</v>
+        <v>10.3</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.44</v>
+        <v>5.53</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.75</v>
+        <v>20.71</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.19</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="18">
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -7827,82 +7827,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G18" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="H18" t="n">
-        <v>89.25</v>
+        <v>92</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="J18" t="n">
-        <v>2.88</v>
+        <v>2.78</v>
       </c>
       <c r="K18" t="n">
-        <v>4.25</v>
+        <v>4.33</v>
       </c>
       <c r="L18" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M18" t="n">
-        <v>37.62</v>
+        <v>39.22</v>
       </c>
       <c r="N18" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="O18" t="n">
-        <v>2.62</v>
+        <v>2.89</v>
       </c>
       <c r="P18" t="n">
-        <v>15.25</v>
+        <v>15.67</v>
       </c>
       <c r="Q18" t="n">
-        <v>15.12</v>
+        <v>14.56</v>
       </c>
       <c r="R18" t="n">
-        <v>6.75</v>
+        <v>6.89</v>
       </c>
       <c r="S18" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="T18" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="U18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>55.5</v>
+        <v>56</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z18" t="n">
-        <v>12.75</v>
+        <v>13.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.619999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.12</v>
+        <v>4.44</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.25</v>
+        <v>21.56</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.37</v>
+        <v>1.45</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7986,64 +7986,64 @@
         <v>3.62</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.56</v>
+        <v>9.65</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.88</v>
+        <v>2.82</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL18" t="n">
         <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.65</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.5</v>
+        <v>4.65</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BR18" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS18" t="n">
-        <v>81.25</v>
+        <v>82.34999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>68.75</v>
+        <v>64.70999999999999</v>
       </c>
       <c r="BU18" t="n">
-        <v>31.25</v>
+        <v>29.41</v>
       </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>11.76</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>75</v>
+        <v>76.47</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.97</v>
+        <v>3.02</v>
       </c>
       <c r="CA18" t="n">
         <v>3.53</v>
@@ -8058,7 +8058,7 @@
         <v>3.74</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="CF18" t="n">
         <v>2.52</v>
@@ -8073,13 +8073,13 @@
         <v>2.2</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CK18" t="n">
         <v>1.43</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM18" t="n">
         <v>2.58</v>
@@ -8094,10 +8094,10 @@
         <v>1.76</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS18" t="n">
         <v>2.74</v>
@@ -8118,13 +8118,13 @@
         <v>1.52</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.45</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="DB18" t="n">
         <v>1.26</v>
@@ -8142,40 +8142,40 @@
         <v>1.94</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.88</v>
+        <v>90.34999999999999</v>
       </c>
       <c r="DI18" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.38</v>
+        <v>3.3</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.06</v>
+        <v>4.12</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.19</v>
+        <v>0.3</v>
       </c>
       <c r="DM18" t="n">
-        <v>35.56</v>
+        <v>36.53</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.31</v>
+        <v>1.23</v>
       </c>
       <c r="DO18" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.18</v>
+        <v>14.47</v>
       </c>
       <c r="DQ18" t="n">
-        <v>15.12</v>
+        <v>14.82</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.25</v>
+        <v>7.29</v>
       </c>
       <c r="DS18" t="n">
         <v>0.12</v>
@@ -8187,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>58.69</v>
+        <v>58.77</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.43</v>
+        <v>12.82</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.43</v>
+        <v>8.65</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4</v>
+        <v>4.18</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.68</v>
+        <v>20.88</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="EC18" t="n">
-        <v>3.12</v>
+        <v>3.06</v>
       </c>
     </row>
     <row r="19">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" t="n">
         <v>0.25</v>
@@ -8308,127 +8308,127 @@
         <v>2.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.25</v>
+        <v>2.44</v>
       </c>
       <c r="AI19" t="n">
-        <v>104.62</v>
+        <v>104</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK19" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.62</v>
+        <v>4.56</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="AN19" t="n">
-        <v>46.25</v>
+        <v>45.89</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.38</v>
+        <v>14.22</v>
       </c>
       <c r="AR19" t="n">
-        <v>11</v>
+        <v>11.22</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.25</v>
+        <v>5.89</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>38.75</v>
+        <v>41</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.5</v>
+        <v>12.22</v>
       </c>
       <c r="BB19" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.62</v>
+        <v>4.44</v>
       </c>
       <c r="BD19" t="n">
-        <v>22.12</v>
+        <v>22.89</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BF19" t="n">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.75</v>
+        <v>9.59</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.81</v>
+        <v>1.88</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.65</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BN19" t="n">
-        <v>1</v>
+        <v>1.12</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.76</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.31</v>
+        <v>4.12</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.38</v>
+        <v>5.41</v>
       </c>
       <c r="BR19" t="n">
-        <v>93.75</v>
+        <v>94.12</v>
       </c>
       <c r="BS19" t="n">
-        <v>50</v>
+        <v>52.94</v>
       </c>
       <c r="BT19" t="n">
-        <v>37.5</v>
+        <v>41.18</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>31.25</v>
+        <v>35.29</v>
       </c>
       <c r="BY19" t="n">
         <v>2.31</v>
@@ -8449,73 +8449,73 @@
         <v>2.32</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.44</v>
+        <v>3.43</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.71</v>
+        <v>2.65</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.81</v>
+        <v>2.76</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.05</v>
+        <v>3.02</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="CL19" t="n">
         <v>1.81</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CN19" t="n">
         <v>2.05</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CU19" t="n">
         <v>1.48</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX19" t="n">
         <v>1.5</v>
@@ -8530,88 +8530,88 @@
         <v>2.05</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DF19" t="n">
-        <v>2.06</v>
+        <v>1.95</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="DH19" t="n">
-        <v>102.06</v>
+        <v>101.88</v>
       </c>
       <c r="DI19" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.94</v>
+        <v>2.83</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.87</v>
+        <v>4.82</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.44</v>
+        <v>0.41</v>
       </c>
       <c r="DM19" t="n">
-        <v>48.68</v>
+        <v>48.35</v>
       </c>
       <c r="DN19" t="n">
         <v>0.88</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.38</v>
+        <v>2.24</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.94</v>
+        <v>13.88</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.81</v>
+        <v>11.88</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.12</v>
+        <v>5.47</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>40.68</v>
+        <v>41.76</v>
       </c>
       <c r="DW19" t="n">
         <v>0.06</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.75</v>
+        <v>12.59</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.130000000000001</v>
+        <v>8.06</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.62</v>
+        <v>4.52</v>
       </c>
       <c r="EA19" t="n">
-        <v>21</v>
+        <v>21.47</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.88</v>
+        <v>2.77</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -3215,13 +3215,13 @@
         <v>3.1</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CA6" t="n">
         <v>3.6</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CC6" t="n">
         <v>4.2</v>
@@ -3269,10 +3269,10 @@
         <v>2.76</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CT6" t="n">
         <v>3.19</v>
@@ -3281,7 +3281,7 @@
         <v>1.5</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CW6" t="n">
         <v>1.66</v>
@@ -3290,13 +3290,13 @@
         <v>1.47</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="DB6" t="n">
         <v>1.24</v>
@@ -3624,13 +3624,13 @@
         <v>3.6</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC7" t="n">
         <v>2.18</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="CE7" t="n">
         <v>1.3</v>
@@ -3675,16 +3675,16 @@
         <v>1.37</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CU7" t="n">
         <v>1.54</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CW7" t="n">
         <v>1.6</v>
@@ -3705,10 +3705,10 @@
         <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DE7" t="n">
         <v>0.11</v>
@@ -3859,7 +3859,7 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>49.89</v>
+        <v>50</v>
       </c>
       <c r="Y8" t="n">
         <v>0.11</v>
@@ -4165,7 +4165,7 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.71</v>
+        <v>47.76</v>
       </c>
       <c r="DW8" t="n">
         <v>0.11</v>
@@ -4343,7 +4343,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>47.33</v>
+        <v>47.22</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -4568,7 +4568,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.65</v>
+        <v>46.59</v>
       </c>
       <c r="DW9" t="n">
         <v>0.06</v>
@@ -4833,7 +4833,7 @@
         <v>3.67</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="CC10" t="n">
         <v>2.35</v>
@@ -4881,19 +4881,19 @@
         <v>2.57</v>
       </c>
       <c r="CR10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS10" t="n">
         <v>2.51</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CU10" t="n">
         <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CW10" t="n">
         <v>1.59</v>
@@ -4908,16 +4908,16 @@
         <v>2.47</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DB10" t="n">
         <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="DE10" t="n">
         <v>0.06</v>
@@ -6334,7 +6334,7 @@
         <v>2.11</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.78</v>
+        <v>11.67</v>
       </c>
       <c r="AR14" t="n">
         <v>9</v>
@@ -6364,10 +6364,10 @@
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.89</v>
+        <v>12.78</v>
       </c>
       <c r="BB14" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="BC14" t="n">
         <v>3.89</v>
@@ -6376,7 +6376,7 @@
         <v>18.89</v>
       </c>
       <c r="BE14" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="BF14" t="n">
         <v>1.78</v>
@@ -6561,7 +6561,7 @@
         <v>2.11</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.18</v>
+        <v>13.12</v>
       </c>
       <c r="DQ14" t="n">
         <v>10.76</v>
@@ -6585,10 +6585,10 @@
         <v>0.12</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.12</v>
+        <v>12.06</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.77</v>
+        <v>7.71</v>
       </c>
       <c r="DZ14" t="n">
         <v>4.36</v>
@@ -7297,7 +7297,7 @@
         <v>2.56</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CU16" t="n">
         <v>1.54</v>
@@ -7312,13 +7312,13 @@
         <v>1.45</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.61</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DB16" t="n">
         <v>1.21</v>
@@ -7327,7 +7327,7 @@
         <v>1.7</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="DE16" t="n">
         <v>0.06</v>
@@ -7484,10 +7484,10 @@
         <v>0.22</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.44</v>
+        <v>16.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.67</v>
+        <v>10.89</v>
       </c>
       <c r="AB17" t="n">
         <v>5.78</v>
@@ -7496,7 +7496,7 @@
         <v>21.44</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AE17" t="n">
         <v>1.89</v>
@@ -7790,10 +7790,10 @@
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.82</v>
+        <v>15.94</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.3</v>
+        <v>10.41</v>
       </c>
       <c r="DZ17" t="n">
         <v>5.53</v>
@@ -7802,7 +7802,7 @@
         <v>20.71</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="EC17" t="n">
         <v>2.12</v>
@@ -8043,13 +8043,13 @@
         <v>2.78</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CA18" t="n">
         <v>3.53</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CC18" t="n">
         <v>3.51</v>
@@ -8097,19 +8097,19 @@
         <v>2.78</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CW18" t="n">
         <v>1.67</v>
@@ -8130,10 +8130,10 @@
         <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
@@ -8500,10 +8500,10 @@
         <v>2.91</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="CT19" t="n">
         <v>3.19</v>
@@ -8521,13 +8521,13 @@
         <v>1.5</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CZ19" t="n">
         <v>2.49</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="DB19" t="n">
         <v>1.26</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -3543,10 +3543,10 @@
         <v>0.11</v>
       </c>
       <c r="BA7" t="n">
-        <v>15</v>
+        <v>15.11</v>
       </c>
       <c r="BB7" t="n">
-        <v>10.22</v>
+        <v>10.33</v>
       </c>
       <c r="BC7" t="n">
         <v>4.78</v>
@@ -3555,7 +3555,7 @@
         <v>22.44</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BF7" t="n">
         <v>2.56</v>
@@ -3768,10 +3768,10 @@
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.18</v>
+        <v>15.24</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.23</v>
+        <v>10.29</v>
       </c>
       <c r="DZ7" t="n">
         <v>4.94</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1445,16 +1445,16 @@
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>55.44</v>
+        <v>55.56</v>
       </c>
       <c r="Y2" t="n">
         <v>0.11</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.22</v>
+        <v>14.11</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="AB2" t="n">
         <v>4.22</v>
@@ -1463,7 +1463,7 @@
         <v>24.22</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="AE2" t="n">
         <v>2.11</v>
@@ -1751,16 +1751,16 @@
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.64</v>
+        <v>52.71</v>
       </c>
       <c r="DW2" t="n">
         <v>0.11</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.7</v>
+        <v>13.64</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.65</v>
+        <v>9.59</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.06</v>
@@ -1769,7 +1769,7 @@
         <v>24.23</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC2" t="n">
         <v>2.29</v>
@@ -2307,7 +2307,7 @@
         <v>12.5</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.62</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
         <v>9.75</v>
@@ -2538,7 +2538,7 @@
         <v>12.24</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.94</v>
+        <v>11.88</v>
       </c>
       <c r="DR4" t="n">
         <v>8.94</v>
@@ -3053,16 +3053,16 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>39.78</v>
+        <v>39.89</v>
       </c>
       <c r="Y6" t="n">
         <v>0.33</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.89</v>
+        <v>13</v>
       </c>
       <c r="AA6" t="n">
-        <v>9</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AB6" t="n">
         <v>3.89</v>
@@ -3071,7 +3071,7 @@
         <v>21.67</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="AE6" t="n">
         <v>2.11</v>
@@ -3140,10 +3140,10 @@
         <v>0.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.75</v>
+        <v>12.62</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.619999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="BC6" t="n">
         <v>4.12</v>
@@ -3152,7 +3152,7 @@
         <v>19.62</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="BF6" t="n">
         <v>2.62</v>
@@ -3359,7 +3359,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.59</v>
+        <v>42.65</v>
       </c>
       <c r="DW6" t="n">
         <v>0.41</v>
@@ -3865,10 +3865,10 @@
         <v>0.11</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.56</v>
+        <v>12.44</v>
       </c>
       <c r="AA8" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AB8" t="n">
         <v>3.56</v>
@@ -4171,10 +4171,10 @@
         <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>13</v>
+        <v>12.94</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.35</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.65</v>
@@ -4752,10 +4752,10 @@
         <v>0</v>
       </c>
       <c r="BA10" t="n">
-        <v>13</v>
+        <v>13.11</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.33</v>
+        <v>7.44</v>
       </c>
       <c r="BC10" t="n">
         <v>5.67</v>
@@ -4977,10 +4977,10 @@
         <v>0</v>
       </c>
       <c r="DX10" t="n">
-        <v>15.41</v>
+        <v>15.47</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.58</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DZ10" t="n">
         <v>5.83</v>
@@ -5095,7 +5095,7 @@
         <v>0.12</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.12</v>
+        <v>2.25</v>
       </c>
       <c r="AH11" t="n">
         <v>1.75</v>
@@ -5107,7 +5107,7 @@
         <v>0.12</v>
       </c>
       <c r="AK11" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="AL11" t="n">
         <v>3.75</v>
@@ -5170,7 +5170,7 @@
         <v>1.36</v>
       </c>
       <c r="BF11" t="n">
-        <v>3</v>
+        <v>3.12</v>
       </c>
       <c r="BG11" t="n">
         <v>2.18</v>
@@ -5326,7 +5326,7 @@
         <v>0.06</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.82</v>
+        <v>1.88</v>
       </c>
       <c r="DG11" t="n">
         <v>2.3</v>
@@ -5338,7 +5338,7 @@
         <v>-0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="DK11" t="n">
         <v>4.47</v>
@@ -5395,7 +5395,7 @@
         <v>1.39</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="12">
@@ -5477,10 +5477,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.75</v>
+        <v>13.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.25</v>
+        <v>9</v>
       </c>
       <c r="AB12" t="n">
         <v>4.5</v>
@@ -5489,7 +5489,7 @@
         <v>18.88</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
         <v>1.5</v>
@@ -5498,7 +5498,7 @@
         <v>0.11</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.78</v>
+        <v>2.89</v>
       </c>
       <c r="AH12" t="n">
         <v>2.67</v>
@@ -5510,7 +5510,7 @@
         <v>0.11</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="AL12" t="n">
         <v>3.89</v>
@@ -5573,7 +5573,7 @@
         <v>1.26</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.44</v>
+        <v>3.56</v>
       </c>
       <c r="BG12" t="n">
         <v>2.47</v>
@@ -5729,7 +5729,7 @@
         <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.89</v>
+        <v>1.94</v>
       </c>
       <c r="DG12" t="n">
         <v>2.94</v>
@@ -5741,7 +5741,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="DK12" t="n">
         <v>4.77</v>
@@ -5783,10 +5783,10 @@
         <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.82</v>
+        <v>12.71</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.82</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ12" t="n">
         <v>4</v>
@@ -5795,10 +5795,10 @@
         <v>19.12</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.53</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="13">
@@ -5883,16 +5883,16 @@
         <v>16.67</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.22</v>
+        <v>10.11</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.44</v>
+        <v>6.56</v>
       </c>
       <c r="AC13" t="n">
         <v>23.11</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="AE13" t="n">
         <v>3</v>
@@ -5955,7 +5955,7 @@
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.12</v>
+        <v>44.88</v>
       </c>
       <c r="AZ13" t="n">
         <v>0.12</v>
@@ -6180,7 +6180,7 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48.06</v>
+        <v>47.95</v>
       </c>
       <c r="DW13" t="n">
         <v>0.06</v>
@@ -6189,16 +6189,16 @@
         <v>13.88</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.65</v>
+        <v>8.59</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.24</v>
+        <v>5.3</v>
       </c>
       <c r="EA13" t="n">
         <v>22.06</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC13" t="n">
         <v>2.94</v>
@@ -7021,7 +7021,7 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
         <v>2.78</v>
@@ -7033,7 +7033,7 @@
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="K16" t="n">
         <v>4.78</v>
@@ -7096,7 +7096,7 @@
         <v>1.4</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="AF16" t="n">
         <v>0.12</v>
@@ -7333,7 +7333,7 @@
         <v>0.06</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DG16" t="n">
         <v>3.18</v>
@@ -7345,7 +7345,7 @@
         <v>0.06</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.7</v>
+        <v>2.77</v>
       </c>
       <c r="DK16" t="n">
         <v>5.35</v>
@@ -7402,7 +7402,7 @@
         <v>1.4</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="17">
@@ -7890,16 +7890,16 @@
         <v>13.44</v>
       </c>
       <c r="AA18" t="n">
-        <v>9</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.44</v>
+        <v>4.56</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.56</v>
+        <v>21.44</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="AE18" t="n">
         <v>2.56</v>
@@ -7968,10 +7968,10 @@
         <v>0.12</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.12</v>
+        <v>12.25</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.25</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BC18" t="n">
         <v>3.88</v>
@@ -7980,7 +7980,7 @@
         <v>20.12</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="BF18" t="n">
         <v>3.62</v>
@@ -8193,19 +8193,19 @@
         <v>0.11</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.82</v>
+        <v>12.88</v>
       </c>
       <c r="DY18" t="n">
         <v>8.65</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.18</v>
+        <v>4.24</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.88</v>
+        <v>20.82</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC18" t="n">
         <v>3.06</v>
@@ -8260,7 +8260,7 @@
         <v>2.38</v>
       </c>
       <c r="P19" t="n">
-        <v>13.5</v>
+        <v>13.38</v>
       </c>
       <c r="Q19" t="n">
         <v>12.62</v>
@@ -8344,7 +8344,7 @@
         <v>14.22</v>
       </c>
       <c r="AR19" t="n">
-        <v>11.22</v>
+        <v>11.33</v>
       </c>
       <c r="AS19" t="n">
         <v>5.89</v>
@@ -8572,10 +8572,10 @@
         <v>2.24</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.88</v>
+        <v>13.82</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.88</v>
+        <v>11.94</v>
       </c>
       <c r="DR19" t="n">
         <v>5.47</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" t="n">
         <v>9</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E2" t="n">
         <v>0.11</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.88</v>
+        <v>1.67</v>
       </c>
       <c r="AH2" t="n">
-        <v>4.25</v>
+        <v>4</v>
       </c>
       <c r="AI2" t="n">
-        <v>95.38</v>
+        <v>95.78</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.5</v>
+        <v>6</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="AN2" t="n">
-        <v>52.38</v>
+        <v>50.78</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.25</v>
+        <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13</v>
+        <v>13.44</v>
       </c>
       <c r="AR2" t="n">
-        <v>15.38</v>
+        <v>15</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.5</v>
+        <v>6.67</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.5</v>
+        <v>49.11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.12</v>
+        <v>12.33</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.25</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.88</v>
+        <v>3.56</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.25</v>
+        <v>24.22</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.48</v>
+        <v>1.4</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BH2" t="n">
-        <v>11.24</v>
+        <v>10.83</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.89</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.12</v>
+        <v>3.94</v>
       </c>
       <c r="BQ2" t="n">
-        <v>7.06</v>
+        <v>6.83</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS2" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX2" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY2" t="n">
         <v>2.14</v>
@@ -1610,22 +1610,22 @@
         <v>2.24</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.29</v>
+        <v>3.22</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.52</v>
+        <v>3.44</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.39</v>
+        <v>2.41</v>
       </c>
       <c r="CG2" t="n">
         <v>3.26</v>
@@ -1634,10 +1634,10 @@
         <v>1.54</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CK2" t="n">
         <v>1.35</v>
@@ -1649,16 +1649,16 @@
         <v>2.79</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CO2" t="n">
         <v>1.17</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.49</v>
+        <v>2.52</v>
       </c>
       <c r="CR2" t="n">
         <v>1.37</v>
@@ -1673,7 +1673,7 @@
         <v>1.56</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CW2" t="n">
         <v>1.57</v>
@@ -1694,85 +1694,85 @@
         <v>1.2</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="DE2" t="n">
         <v>0.06</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.23</v>
+        <v>4.11</v>
       </c>
       <c r="DH2" t="n">
-        <v>96.53</v>
+        <v>96.67</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.12</v>
+        <v>0.06</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.47</v>
+        <v>6.22</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM2" t="n">
-        <v>48.77</v>
+        <v>48.17</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.88</v>
+        <v>0.84</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.23</v>
+        <v>2.11</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.23</v>
+        <v>13.44</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14.65</v>
+        <v>14.5</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.47</v>
+        <v>7.5</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.71</v>
+        <v>52.34</v>
       </c>
       <c r="DW2" t="n">
         <v>0.11</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.64</v>
+        <v>13.22</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.59</v>
+        <v>9.34</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.06</v>
+        <v>3.89</v>
       </c>
       <c r="EA2" t="n">
-        <v>24.23</v>
+        <v>24.22</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.29</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="3">
@@ -2987,10 +2987,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D6" t="n">
         <v>8</v>
@@ -2999,82 +2999,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="G6" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="H6" t="n">
-        <v>90.89</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>3.7</v>
       </c>
       <c r="L6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M6" t="n">
-        <v>34.33</v>
+        <v>34.6</v>
       </c>
       <c r="N6" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O6" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="P6" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.78</v>
+        <v>13.6</v>
       </c>
       <c r="R6" t="n">
-        <v>8.779999999999999</v>
+        <v>8.9</v>
       </c>
       <c r="S6" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="T6" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V6" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>39.89</v>
+        <v>40.3</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="Z6" t="n">
-        <v>13</v>
+        <v>12.3</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.109999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.67</v>
+        <v>21.6</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.35</v>
+        <v>1.29</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.11</v>
+        <v>2.2</v>
       </c>
       <c r="AF6" t="n">
         <v>0.12</v>
@@ -3158,67 +3158,67 @@
         <v>2.62</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.59</v>
+        <v>10.56</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.59</v>
+        <v>4.61</v>
       </c>
       <c r="BQ6" t="n">
-        <v>6</v>
+        <v>5.94</v>
       </c>
       <c r="BR6" t="n">
         <v>100</v>
       </c>
       <c r="BS6" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT6" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU6" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BV6" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.1</v>
+        <v>3.06</v>
       </c>
       <c r="BZ6" t="n">
         <v>3.18</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CB6" t="n">
         <v>3.72</v>
@@ -3233,19 +3233,19 @@
         <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CH6" t="n">
         <v>1.48</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK6" t="n">
         <v>1.41</v>
@@ -3260,31 +3260,31 @@
         <v>2.08</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CT6" t="n">
         <v>3.19</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CX6" t="n">
         <v>1.47</v>
@@ -3296,28 +3296,28 @@
         <v>2.55</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF6" t="n">
         <v>2</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.47</v>
+        <v>2.34</v>
       </c>
       <c r="DH6" t="n">
-        <v>93.34999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
@@ -3326,61 +3326,61 @@
         <v>3</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.59</v>
+        <v>4.39</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.47</v>
+        <v>38.39</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.12</v>
+        <v>2.06</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.71</v>
+        <v>12.67</v>
       </c>
       <c r="DQ6" t="n">
-        <v>14</v>
+        <v>13.89</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.300000000000001</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.65</v>
+        <v>42.72</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.82</v>
+        <v>12.44</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.82</v>
+        <v>8.56</v>
       </c>
       <c r="DZ6" t="n">
-        <v>4</v>
+        <v>3.89</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.71</v>
+        <v>20.72</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.37</v>
+        <v>1.34</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.35</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="7">
@@ -3793,10 +3793,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D8" t="n">
         <v>8</v>
@@ -3805,49 +3805,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="G8" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="H8" t="n">
-        <v>85.89</v>
+        <v>88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.11</v>
+        <v>-0.2</v>
       </c>
       <c r="J8" t="n">
-        <v>3.33</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M8" t="n">
-        <v>47.22</v>
+        <v>48.3</v>
       </c>
       <c r="N8" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="O8" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="P8" t="n">
-        <v>13.44</v>
+        <v>13.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>10.56</v>
+        <v>11.2</v>
       </c>
       <c r="R8" t="n">
-        <v>6.78</v>
+        <v>6.7</v>
       </c>
       <c r="S8" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3859,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50</v>
+        <v>50.4</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.44</v>
+        <v>12.4</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.890000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>20.11</v>
+        <v>19.9</v>
       </c>
       <c r="AD8" t="n">
         <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="AF8" t="n">
         <v>0.12</v>
@@ -3964,70 +3964,70 @@
         <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BH8" t="n">
-        <v>9.24</v>
+        <v>8.94</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BP8" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.18</v>
+        <v>5.06</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS8" t="n">
-        <v>70.59</v>
+        <v>66.67</v>
       </c>
       <c r="BT8" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX8" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.31</v>
+        <v>2.34</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.67</v>
+        <v>3.64</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CC8" t="n">
         <v>3.51</v>
@@ -4039,7 +4039,7 @@
         <v>1.3</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CG8" t="n">
         <v>3.2</v>
@@ -4048,7 +4048,7 @@
         <v>1.52</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.57</v>
@@ -4060,19 +4060,19 @@
         <v>1.76</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO8" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="CR8" t="n">
         <v>1.39</v>
@@ -4087,10 +4087,10 @@
         <v>1.55</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX8" t="n">
         <v>1.49</v>
@@ -4102,7 +4102,7 @@
         <v>2.49</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB8" t="n">
         <v>1.21</v>
@@ -4111,82 +4111,82 @@
         <v>1.68</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="DH8" t="n">
-        <v>90</v>
+        <v>90.94</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.06</v>
+        <v>-0.11</v>
       </c>
       <c r="DJ8" t="n">
-        <v>3</v>
+        <v>2.83</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.11</v>
+        <v>4</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM8" t="n">
-        <v>44.94</v>
+        <v>45.67</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.65</v>
+        <v>1.61</v>
       </c>
       <c r="DP8" t="n">
-        <v>13.05</v>
+        <v>13</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11</v>
+        <v>11.33</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.88</v>
+        <v>7.78</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>47.76</v>
+        <v>48.11</v>
       </c>
       <c r="DW8" t="n">
         <v>0.11</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.94</v>
+        <v>12.89</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.289999999999999</v>
+        <v>9.279999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.65</v>
+        <v>3.61</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.35</v>
+        <v>20.22</v>
       </c>
       <c r="EB8" t="n">
         <v>1.4</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.88</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="9">
@@ -6610,13 +6610,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C15" t="n">
         <v>8</v>
       </c>
       <c r="D15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6706,46 +6706,46 @@
         <v>2</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.89</v>
+        <v>3.1</v>
       </c>
       <c r="AI15" t="n">
-        <v>79.67</v>
+        <v>80.5</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.44</v>
+        <v>5.8</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AN15" t="n">
-        <v>39.11</v>
+        <v>40.3</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.56</v>
+        <v>2.7</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.56</v>
+        <v>11.6</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.33</v>
+        <v>13.2</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.44</v>
+        <v>8.5</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AU15" t="n">
-        <v>1</v>
+        <v>1.2</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6757,52 +6757,52 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>54.56</v>
+        <v>54.7</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>17.11</v>
+        <v>17.5</v>
       </c>
       <c r="BB15" t="n">
-        <v>11.22</v>
+        <v>11.4</v>
       </c>
       <c r="BC15" t="n">
-        <v>5.89</v>
+        <v>6.1</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.67</v>
+        <v>17.7</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.77</v>
+        <v>1.82</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="BG15" t="n">
         <v>2.94</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.29</v>
+        <v>10.28</v>
       </c>
       <c r="BI15" t="n">
         <v>2.94</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL15" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.88</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="BO15" t="n">
         <v>1.06</v>
@@ -6811,28 +6811,28 @@
         <v>4.94</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.35</v>
+        <v>5.33</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS15" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT15" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU15" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV15" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BX15" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY15" t="n">
         <v>2.2</v>
@@ -6841,16 +6841,16 @@
         <v>2.39</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB15" t="n">
         <v>3.8</v>
       </c>
       <c r="CC15" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.34</v>
+        <v>3.23</v>
       </c>
       <c r="CE15" t="n">
         <v>1.26</v>
@@ -6859,7 +6859,7 @@
         <v>2.27</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.42</v>
+        <v>3.41</v>
       </c>
       <c r="CH15" t="n">
         <v>1.6</v>
@@ -6868,13 +6868,13 @@
         <v>2.54</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CK15" t="n">
         <v>1.37</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM15" t="n">
         <v>2.83</v>
@@ -6886,10 +6886,10 @@
         <v>1.15</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.33</v>
+        <v>2.35</v>
       </c>
       <c r="CR15" t="inlineStr"/>
       <c r="CS15" t="n">
@@ -6900,7 +6900,7 @@
         <v>1.63</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CW15" t="n">
         <v>1.5</v>
@@ -6909,34 +6909,34 @@
         <v>1.46</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.55</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DB15" t="n">
         <v>1.17</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.65</v>
+        <v>2.78</v>
       </c>
       <c r="DH15" t="n">
-        <v>92.06</v>
+        <v>91.83</v>
       </c>
       <c r="DI15" t="n">
         <v>0.17</v>
@@ -6945,58 +6945,58 @@
         <v>3</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.29</v>
+        <v>5.5</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.06</v>
+        <v>46.34</v>
       </c>
       <c r="DN15" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.65</v>
+        <v>2.72</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.47</v>
+        <v>12.44</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.29</v>
+        <v>12.28</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.35</v>
+        <v>7.44</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.06</v>
+        <v>55.11</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.47</v>
+        <v>16.72</v>
       </c>
       <c r="DY15" t="n">
-        <v>10.94</v>
+        <v>11.05</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.53</v>
+        <v>5.66</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.53</v>
+        <v>18.5</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="EC15" t="n">
         <v>2.94</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1782,10 +1782,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D3" t="n">
         <v>9</v>
@@ -1794,49 +1794,49 @@
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>3.22</v>
       </c>
       <c r="H3" t="n">
-        <v>107</v>
+        <v>109.33</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="J3" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="K3" t="n">
-        <v>6.12</v>
+        <v>6.33</v>
       </c>
       <c r="L3" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>56</v>
+        <v>57.56</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="P3" t="n">
-        <v>15.25</v>
+        <v>14.67</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.38</v>
+        <v>10.11</v>
       </c>
       <c r="R3" t="n">
-        <v>8.119999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="S3" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.38</v>
+        <v>47.56</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.12</v>
+        <v>17.44</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.12</v>
+        <v>12.33</v>
       </c>
       <c r="AB3" t="n">
-        <v>5</v>
+        <v>5.11</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.12</v>
+        <v>22</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.5</v>
+        <v>3.22</v>
       </c>
       <c r="AF3" t="n">
         <v>0.22</v>
@@ -1953,70 +1953,70 @@
         <v>3.56</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="BH3" t="n">
-        <v>12.24</v>
+        <v>12.33</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.65</v>
+        <v>2.83</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BL3" t="n">
         <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.82</v>
+        <v>5.94</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.41</v>
+        <v>6.39</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS3" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BV3" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BW3" t="n">
-        <v>0</v>
+        <v>5.56</v>
       </c>
       <c r="BX3" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.27</v>
+        <v>2.3</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CC3" t="n">
         <v>2.99</v>
@@ -2031,13 +2031,13 @@
         <v>2.33</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.31</v>
+        <v>3.29</v>
       </c>
       <c r="CH3" t="n">
         <v>1.53</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.54</v>
@@ -2049,13 +2049,13 @@
         <v>1.63</v>
       </c>
       <c r="CM3" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CN3" t="n">
         <v>2.28</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP3" t="n">
         <v>1.63</v>
@@ -2067,16 +2067,16 @@
         <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CW3" t="n">
         <v>1.58</v>
@@ -2093,85 +2093,85 @@
         <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.47</v>
+        <v>2.33</v>
       </c>
       <c r="DG3" t="n">
-        <v>3</v>
+        <v>3.11</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.53</v>
+        <v>96.38</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.53</v>
+        <v>3.39</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.17</v>
+        <v>6.28</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DM3" t="n">
-        <v>48.47</v>
+        <v>49.67</v>
       </c>
       <c r="DN3" t="n">
         <v>1.06</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.83</v>
+        <v>13.62</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.289999999999999</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.82</v>
+        <v>8.77</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.95</v>
+        <v>45.62</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.53</v>
+        <v>14.83</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.47</v>
+        <v>10.66</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.06</v>
+        <v>4.16</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.47</v>
+        <v>22.84</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.53</v>
+        <v>3.39</v>
       </c>
     </row>
     <row r="4">
@@ -2181,13 +2181,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C4" t="n">
         <v>9</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E4" t="n">
         <v>0.22</v>
@@ -2271,52 +2271,52 @@
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AI4" t="n">
-        <v>86.75</v>
+        <v>84.22</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.12</v>
+        <v>-0.11</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.12</v>
+        <v>4.33</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN4" t="n">
-        <v>35.12</v>
+        <v>35</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.5</v>
+        <v>2.78</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.5</v>
+        <v>11.33</v>
       </c>
       <c r="AS4" t="n">
-        <v>9.75</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.12</v>
+        <v>1.33</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AV4" t="n">
         <v>0</v>
@@ -2328,82 +2328,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>49.5</v>
+        <v>48.78</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.62</v>
+        <v>12.11</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.380000000000001</v>
+        <v>8</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.25</v>
+        <v>4.11</v>
       </c>
       <c r="BD4" t="n">
-        <v>18.38</v>
+        <v>18.56</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.71</v>
+        <v>2.89</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.18</v>
+        <v>10.39</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.71</v>
+        <v>2.89</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.59</v>
+        <v>0.67</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.47</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BL4" t="n">
         <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.06</v>
+        <v>1.22</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.82</v>
+        <v>5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.35</v>
+        <v>5.39</v>
       </c>
       <c r="BR4" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS4" t="n">
-        <v>64.70999999999999</v>
+        <v>66.67</v>
       </c>
       <c r="BT4" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU4" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV4" t="n">
-        <v>23.53</v>
+        <v>27.78</v>
       </c>
       <c r="BW4" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY4" t="n">
         <v>1.83</v>
@@ -2412,70 +2412,70 @@
         <v>1.85</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.93</v>
+        <v>2.91</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.17</v>
+        <v>3.15</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.57</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="CO4" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP4" t="n">
         <v>1.61</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CW4" t="n">
         <v>1.58</v>
@@ -2484,64 +2484,64 @@
         <v>1.46</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.58</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.11</v>
+        <v>2.13</v>
       </c>
       <c r="DB4" t="n">
         <v>1.2</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.23</v>
+        <v>0.28</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.59</v>
+        <v>84.39</v>
       </c>
       <c r="DI4" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.88</v>
+        <v>4.94</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.53</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.11</v>
+        <v>41.66</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
       <c r="DP4" t="n">
-        <v>12.24</v>
+        <v>12</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.88</v>
+        <v>11.77</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.94</v>
+        <v>8.66</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2553,28 +2553,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.18</v>
+        <v>48.84</v>
       </c>
       <c r="DW4" t="n">
         <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.29</v>
+        <v>13.94</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.94</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.35</v>
+        <v>5.22</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.12</v>
+        <v>18.22</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
     </row>
     <row r="5">
@@ -2584,94 +2584,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D5" t="n">
         <v>9</v>
       </c>
       <c r="E5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F5" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="G5" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="H5" t="n">
-        <v>85</v>
+        <v>85.44</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="K5" t="n">
-        <v>5.12</v>
+        <v>5.33</v>
       </c>
       <c r="L5" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="M5" t="n">
-        <v>43.62</v>
+        <v>43.78</v>
       </c>
       <c r="N5" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="O5" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="P5" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>13.22</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7.56</v>
+      </c>
+      <c r="S5" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>49.78</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>11.78</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>3.67</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>21.56</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AE5" t="n">
         <v>2</v>
-      </c>
-      <c r="P5" t="n">
-        <v>10.88</v>
-      </c>
-      <c r="Q5" t="n">
-        <v>13.12</v>
-      </c>
-      <c r="R5" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="S5" t="n">
-        <v>2</v>
-      </c>
-      <c r="T5" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="V5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="W5" t="n">
-        <v>0</v>
-      </c>
-      <c r="X5" t="n">
-        <v>49.62</v>
-      </c>
-      <c r="Y5" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="Z5" t="n">
-        <v>11.75</v>
-      </c>
-      <c r="AA5" t="n">
-        <v>8.119999999999999</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>3.62</v>
-      </c>
-      <c r="AC5" t="n">
-        <v>21.62</v>
-      </c>
-      <c r="AD5" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AE5" t="n">
-        <v>1.88</v>
       </c>
       <c r="AF5" t="n">
         <v>0.11</v>
@@ -2755,67 +2755,67 @@
         <v>2.11</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.24</v>
+        <v>11.17</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.82</v>
+        <v>4.89</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.41</v>
+        <v>6.28</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BT5" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BU5" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BV5" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX5" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BY5" t="n">
+        <v>2.47</v>
+      </c>
+      <c r="BZ5" t="n">
         <v>2.54</v>
       </c>
-      <c r="BZ5" t="n">
-        <v>2.62</v>
-      </c>
       <c r="CA5" t="n">
-        <v>3.62</v>
+        <v>3.63</v>
       </c>
       <c r="CB5" t="n">
         <v>3.68</v>
@@ -2830,16 +2830,16 @@
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH5" t="n">
         <v>1.52</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.57</v>
@@ -2854,7 +2854,7 @@
         <v>2.88</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CO5" t="n">
         <v>1.18</v>
@@ -2872,13 +2872,13 @@
         <v>2.57</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.27</v>
+        <v>3.28</v>
       </c>
       <c r="CU5" t="n">
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CW5" t="n">
         <v>1.59</v>
@@ -2887,13 +2887,13 @@
         <v>1.46</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.6</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="DB5" t="n">
         <v>1.22</v>
@@ -2908,40 +2908,40 @@
         <v>0.11</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="DH5" t="n">
-        <v>92.12</v>
+        <v>91.94</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.23</v>
+        <v>2.28</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.47</v>
+        <v>5.56</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.64</v>
+        <v>46.56</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.12</v>
+        <v>11.11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.17</v>
+        <v>12.27</v>
       </c>
       <c r="DR5" t="n">
         <v>7.94</v>
@@ -2956,28 +2956,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.82</v>
+        <v>49.89</v>
       </c>
       <c r="DW5" t="n">
         <v>0.11</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.24</v>
+        <v>13.17</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.23</v>
+        <v>9.16</v>
       </c>
       <c r="DZ5" t="n">
         <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.41</v>
+        <v>21.39</v>
       </c>
       <c r="EB5" t="n">
         <v>1.45</v>
       </c>
       <c r="EC5" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="6">
@@ -3390,13 +3390,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" t="n">
         <v>8</v>
       </c>
       <c r="D7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
         <v>0.12</v>
@@ -3480,139 +3480,139 @@
         <v>1.75</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AH7" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="AI7" t="n">
+        <v>93.5</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>43.9</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>52.9</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>14.9</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>22.1</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>11.06</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="BK7" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>4.83</v>
+      </c>
+      <c r="BR7" t="n">
         <v>94.44</v>
       </c>
-      <c r="AJ7" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>0.5600000000000001</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>45.22</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10.22</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>6.89</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>53.22</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>22.44</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>11.12</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.59</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>5.29</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>94.12</v>
-      </c>
       <c r="BS7" t="n">
-        <v>70.59</v>
+        <v>72.22</v>
       </c>
       <c r="BT7" t="n">
-        <v>47.06</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>35.29</v>
+        <v>38.89</v>
       </c>
       <c r="BV7" t="n">
-        <v>17.65</v>
+        <v>22.22</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX7" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BY7" t="n">
         <v>1.93</v>
@@ -3621,73 +3621,73 @@
         <v>1.95</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.6</v>
+        <v>3.41</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.3</v>
+        <v>1.23</v>
       </c>
       <c r="CF7" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CG7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="CH7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="CI7" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="CJ7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CK7" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CM7" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CN7" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="CO7" t="n">
+        <v>1.13</v>
+      </c>
+      <c r="CP7" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="CQ7" t="n">
         <v>2.44</v>
       </c>
-      <c r="CG7" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CH7" t="n">
+      <c r="CR7" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="CS7" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="CT7" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="CU7" t="n">
         <v>1.53</v>
       </c>
-      <c r="CI7" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="CJ7" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="CK7" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CL7" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="CM7" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="CN7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="CO7" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="CP7" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="CQ7" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="CR7" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CS7" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="CT7" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="CU7" t="n">
-        <v>1.54</v>
-      </c>
       <c r="CV7" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
@@ -3705,52 +3705,52 @@
         <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="DE7" t="n">
         <v>0.11</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.59</v>
+        <v>1.56</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
       <c r="DH7" t="n">
-        <v>94.81999999999999</v>
+        <v>94.28</v>
       </c>
       <c r="DI7" t="n">
         <v>0.17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.24</v>
+        <v>2.17</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.41</v>
+        <v>6.22</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DM7" t="n">
-        <v>49.12</v>
+        <v>48.17</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.65</v>
+        <v>0.61</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
       <c r="DP7" t="n">
-        <v>11</v>
+        <v>11.11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15.35</v>
+        <v>15</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.89</v>
+        <v>7.06</v>
       </c>
       <c r="DS7" t="n">
         <v>0.11</v>
@@ -3762,28 +3762,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.41</v>
+        <v>53.22</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.24</v>
+        <v>15.11</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.29</v>
+        <v>10.06</v>
       </c>
       <c r="DZ7" t="n">
-        <v>4.94</v>
+        <v>5.05</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.82</v>
+        <v>22.61</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.18</v>
+        <v>2.11</v>
       </c>
     </row>
     <row r="8">
@@ -4196,13 +4196,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C9" t="n">
         <v>8</v>
       </c>
       <c r="D9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
         <v>0.25</v>
@@ -4289,136 +4289,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="AI9" t="n">
-        <v>70.89</v>
+        <v>72.40000000000001</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.22</v>
+        <v>4.1</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN9" t="n">
-        <v>34.44</v>
+        <v>34</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AP9" t="n">
         <v>2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.11</v>
+        <v>13.2</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.67</v>
+        <v>11.6</v>
       </c>
       <c r="AS9" t="n">
-        <v>9.109999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>47.22</v>
+        <v>47.4</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>12.78</v>
+        <v>12.4</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.33</v>
+        <v>7.5</v>
       </c>
       <c r="BC9" t="n">
-        <v>5.44</v>
+        <v>4.9</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.89</v>
+        <v>22.4</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.43</v>
+        <v>1.37</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.18</v>
+        <v>10.17</v>
       </c>
       <c r="BI9" t="n">
-        <v>4.12</v>
+        <v>4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.59</v>
+        <v>2.5</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.24</v>
+        <v>4.33</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.94</v>
+        <v>5.83</v>
       </c>
       <c r="BR9" t="n">
         <v>100</v>
       </c>
       <c r="BS9" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT9" t="n">
-        <v>82.34999999999999</v>
+        <v>77.78</v>
       </c>
       <c r="BU9" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BV9" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BW9" t="n">
-        <v>23.53</v>
+        <v>22.22</v>
       </c>
       <c r="BX9" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BY9" t="n">
         <v>2.82</v>
@@ -4430,43 +4430,43 @@
         <v>3.77</v>
       </c>
       <c r="CB9" t="n">
-        <v>4</v>
+        <v>3.98</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.21</v>
+        <v>4.13</v>
       </c>
       <c r="CD9" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="CE9" t="n">
         <v>1.28</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CH9" t="n">
         <v>1.56</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="CO9" t="n">
         <v>1.16</v>
@@ -4475,22 +4475,22 @@
         <v>1.59</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CT9" t="n">
         <v>3.31</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CW9" t="n">
         <v>1.57</v>
@@ -4499,7 +4499,7 @@
         <v>1.47</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.58</v>
@@ -4511,85 +4511,85 @@
         <v>1.19</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF9" t="n">
         <v>1.17</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.64</v>
+        <v>2.55</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.29000000000001</v>
+        <v>79.67</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.47</v>
+        <v>4.39</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DM9" t="n">
-        <v>35.17</v>
+        <v>34.89</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.7</v>
+        <v>11.83</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.82</v>
+        <v>12.72</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.470000000000001</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.59</v>
+        <v>46.72</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX9" t="n">
-        <v>12.06</v>
+        <v>11.89</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.47</v>
+        <v>7.55</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.58</v>
+        <v>4.33</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.65</v>
+        <v>21.44</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.34</v>
+        <v>1.31</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
     </row>
     <row r="10">
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C10" t="n">
         <v>8</v>
       </c>
       <c r="D10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
@@ -4689,139 +4689,139 @@
         <v>1.62</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AI10" t="n">
-        <v>105.78</v>
+        <v>104.1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.67</v>
+        <v>4.8</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN10" t="n">
-        <v>47.22</v>
+        <v>46.1</v>
       </c>
       <c r="AO10" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.22</v>
+        <v>13.3</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.89</v>
+        <v>13.7</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.67</v>
+        <v>6.6</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AU10" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>57.33</v>
+        <v>56.8</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA10" t="n">
-        <v>13.11</v>
+        <v>12.9</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.44</v>
+        <v>7.6</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.67</v>
+        <v>5.3</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.89</v>
+        <v>19.8</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.24</v>
+        <v>9.33</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.06</v>
+        <v>3.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.76</v>
+        <v>0.89</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.24</v>
+        <v>5.28</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BT10" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BU10" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BY10" t="n">
         <v>1.87</v>
@@ -4833,13 +4833,13 @@
         <v>3.67</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.35</v>
+        <v>2.32</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CE10" t="n">
         <v>1.3</v>
@@ -4848,7 +4848,7 @@
         <v>2.44</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.28</v>
+        <v>3.27</v>
       </c>
       <c r="CH10" t="n">
         <v>1.55</v>
@@ -4860,16 +4860,16 @@
         <v>1.56</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL10" t="n">
         <v>1.68</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.21</v>
+        <v>2.19</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
@@ -4890,25 +4890,25 @@
         <v>3.28</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CW10" t="n">
         <v>1.59</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.47</v>
+        <v>2.52</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DB10" t="n">
         <v>1.2</v>
@@ -4923,76 +4923,76 @@
         <v>0.06</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.29</v>
+        <v>1.33</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="DH10" t="n">
-        <v>109.23</v>
+        <v>108.11</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ10" t="n">
         <v>2.05</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.59</v>
+        <v>5.61</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM10" t="n">
-        <v>52.88</v>
+        <v>51.94</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.47</v>
+        <v>2.39</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.06</v>
+        <v>13.11</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.76</v>
+        <v>13.66</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.59</v>
+        <v>6.56</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>57.94</v>
+        <v>57.61</v>
       </c>
       <c r="DW10" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DX10" t="n">
-        <v>15.47</v>
+        <v>15.22</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.640000000000001</v>
+        <v>9.609999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.83</v>
+        <v>5.61</v>
       </c>
       <c r="EA10" t="n">
-        <v>20.06</v>
+        <v>20</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5002,10 +5002,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D11" t="n">
         <v>8</v>
@@ -5014,82 +5014,82 @@
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="G11" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H11" t="n">
-        <v>95.33</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="K11" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="L11" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="M11" t="n">
-        <v>43.56</v>
+        <v>44.9</v>
       </c>
       <c r="N11" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="O11" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="P11" t="n">
-        <v>13</v>
+        <v>12.7</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.44</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="R11" t="n">
-        <v>10.22</v>
+        <v>9.4</v>
       </c>
       <c r="S11" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T11" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="U11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>48.22</v>
+        <v>49.5</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.56</v>
+        <v>12.4</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.22</v>
+        <v>4.4</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.33</v>
+        <v>20.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="AF11" t="n">
         <v>0.12</v>
@@ -5173,70 +5173,70 @@
         <v>3.12</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.29</v>
+        <v>10.22</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.18</v>
+        <v>2.06</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.59</v>
+        <v>4.5</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.94</v>
+        <v>5</v>
       </c>
       <c r="BR11" t="n">
-        <v>88.23999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BS11" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BT11" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BU11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV11" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX11" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.96</v>
+        <v>1.79</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.92</v>
+        <v>1.99</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.54</v>
+        <v>3.34</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.8</v>
+        <v>3.77</v>
       </c>
       <c r="CC11" t="n">
         <v>2.75</v>
@@ -5245,43 +5245,43 @@
         <v>3.1</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.3</v>
+        <v>1.24</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.38</v>
+        <v>2.27</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.26</v>
+        <v>3.05</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.53</v>
+        <v>1.44</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.54</v>
+        <v>1.47</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.36</v>
+        <v>1.29</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.87</v>
+        <v>2.69</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.2</v>
+        <v>2.06</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.18</v>
+        <v>1.12</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.64</v>
+        <v>1.57</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.49</v>
+        <v>2.42</v>
       </c>
       <c r="CR11" t="n">
         <v>1.36</v>
@@ -5296,73 +5296,73 @@
         <v>1.56</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CW11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.3</v>
+        <v>2.33</v>
       </c>
       <c r="DH11" t="n">
-        <v>92.23</v>
+        <v>93.94</v>
       </c>
       <c r="DI11" t="n">
         <v>-0</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.47</v>
+        <v>4.56</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.12</v>
+        <v>0.17</v>
       </c>
       <c r="DM11" t="n">
-        <v>44.89</v>
+        <v>45.56</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.83</v>
+        <v>0.89</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.82</v>
+        <v>1.89</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.82</v>
+        <v>13.61</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.59</v>
+        <v>11.67</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.59</v>
+        <v>9.17</v>
       </c>
       <c r="DS11" t="n">
         <v>0.11</v>
@@ -5374,28 +5374,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>47.53</v>
+        <v>48.28</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.3</v>
+        <v>12.22</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.289999999999999</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="EA11" t="n">
-        <v>21</v>
+        <v>21.45</v>
       </c>
       <c r="EB11" t="n">
         <v>1.39</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.59</v>
+        <v>2.66</v>
       </c>
     </row>
     <row r="12">
@@ -5405,10 +5405,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C12" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D12" t="n">
         <v>9</v>
@@ -5417,49 +5417,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="G12" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>89.25</v>
+        <v>85.22</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="K12" t="n">
-        <v>5.75</v>
+        <v>5.22</v>
       </c>
       <c r="L12" t="n">
-        <v>0.75</v>
+        <v>0.67</v>
       </c>
       <c r="M12" t="n">
-        <v>40.88</v>
+        <v>38.33</v>
       </c>
       <c r="N12" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O12" t="n">
-        <v>2.5</v>
+        <v>2.22</v>
       </c>
       <c r="P12" t="n">
         <v>12</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.25</v>
+        <v>14.67</v>
       </c>
       <c r="R12" t="n">
-        <v>8.380000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="T12" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5471,28 +5471,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.38</v>
+        <v>50.78</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>13.5</v>
+        <v>12.78</v>
       </c>
       <c r="AA12" t="n">
-        <v>9</v>
+        <v>8.44</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.88</v>
+        <v>18.44</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.5</v>
+        <v>1.67</v>
       </c>
       <c r="AF12" t="n">
         <v>0.11</v>
@@ -5576,34 +5576,34 @@
         <v>3.56</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.18</v>
+        <v>10.28</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.47</v>
+        <v>2.44</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.12</v>
+        <v>4.17</v>
       </c>
       <c r="BQ12" t="n">
         <v>6.06</v>
@@ -5612,34 +5612,34 @@
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT12" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU12" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BV12" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX12" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.15</v>
+        <v>2.22</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC12" t="n">
         <v>2.76</v>
@@ -5654,13 +5654,13 @@
         <v>2.5</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CH12" t="n">
         <v>1.5</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.56</v>
@@ -5675,31 +5675,31 @@
         <v>2.89</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.22</v>
+        <v>2.21</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP12" t="n">
         <v>1.68</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CW12" t="n">
         <v>1.6</v>
@@ -5714,91 +5714,91 @@
         <v>2.49</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB12" t="n">
         <v>1.23</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="DE12" t="n">
         <v>0.06</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.70999999999999</v>
+        <v>82</v>
       </c>
       <c r="DI12" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.77</v>
+        <v>4.56</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="DM12" t="n">
-        <v>37.71</v>
+        <v>36.61</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.76</v>
+        <v>0.78</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.76</v>
+        <v>13.66</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.47</v>
+        <v>13.73</v>
       </c>
       <c r="DR12" t="n">
         <v>8.77</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.95</v>
+        <v>50.22</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.71</v>
+        <v>12.39</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.44</v>
       </c>
       <c r="DZ12" t="n">
-        <v>4</v>
+        <v>3.94</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.12</v>
+        <v>18.88</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.59</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="13">
@@ -5808,94 +5808,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D13" t="n">
         <v>8</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="F13" t="n">
-        <v>1.89</v>
+        <v>1.7</v>
       </c>
       <c r="G13" t="n">
-        <v>2.67</v>
+        <v>2.5</v>
       </c>
       <c r="H13" t="n">
-        <v>106.44</v>
+        <v>106.1</v>
       </c>
       <c r="I13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J13" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="K13" t="n">
-        <v>6.11</v>
+        <v>6</v>
       </c>
       <c r="L13" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="M13" t="n">
-        <v>49.78</v>
+        <v>49.8</v>
       </c>
       <c r="N13" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="O13" t="n">
-        <v>2.44</v>
+        <v>2.6</v>
       </c>
       <c r="P13" t="n">
-        <v>11.67</v>
+        <v>11.7</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.33</v>
+        <v>13.4</v>
       </c>
       <c r="R13" t="n">
-        <v>8.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="S13" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="T13" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="U13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V13" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.67</v>
+        <v>50.4</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>16.67</v>
+        <v>16.6</v>
       </c>
       <c r="AA13" t="n">
-        <v>10.11</v>
+        <v>9.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.56</v>
+        <v>6.7</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.11</v>
+        <v>23.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="AE13" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,67 +5979,67 @@
         <v>2.88</v>
       </c>
       <c r="BG13" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.82</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI13" t="n">
-        <v>2.94</v>
+        <v>3</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.82</v>
+        <v>1.94</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.65</v>
+        <v>4.67</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.41</v>
+        <v>4.5</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS13" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT13" t="n">
-        <v>52.94</v>
+        <v>55.56</v>
       </c>
       <c r="BU13" t="n">
-        <v>41.18</v>
+        <v>44.44</v>
       </c>
       <c r="BV13" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.32</v>
+        <v>2.41</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.58</v>
+        <v>3.59</v>
       </c>
       <c r="CB13" t="n">
         <v>3.66</v>
@@ -6069,16 +6069,16 @@
         <v>1.55</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CO13" t="n">
         <v>1.19</v>
@@ -6099,25 +6099,25 @@
         <v>3.31</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV13" t="n">
         <v>2.51</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CX13" t="n">
         <v>1.46</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.23</v>
+        <v>2.22</v>
       </c>
       <c r="DB13" t="n">
         <v>1.21</v>
@@ -6132,49 +6132,49 @@
         <v>0.17</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.82</v>
+        <v>1.72</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.53</v>
+        <v>2.45</v>
       </c>
       <c r="DH13" t="n">
-        <v>99.23</v>
+        <v>99.44</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ13" t="n">
-        <v>3.06</v>
+        <v>2.94</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.3</v>
+        <v>5.28</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.12</v>
+        <v>43.5</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.23</v>
+        <v>2.33</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.12</v>
+        <v>12.11</v>
       </c>
       <c r="DQ13" t="n">
         <v>14</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.94</v>
+        <v>9.16</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
@@ -6183,25 +6183,25 @@
         <v>47.95</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.88</v>
+        <v>14</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.59</v>
+        <v>8.56</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.3</v>
+        <v>5.45</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.06</v>
+        <v>22.34</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6211,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C14" t="n">
         <v>8</v>
       </c>
       <c r="D14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
         <v>0.12</v>
@@ -6301,139 +6301,139 @@
         <v>3.25</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.11</v>
+        <v>3.1</v>
       </c>
       <c r="AI14" t="n">
-        <v>90.67</v>
+        <v>90</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.22</v>
+        <v>5.6</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="AN14" t="n">
-        <v>40.44</v>
+        <v>40.9</v>
       </c>
       <c r="AO14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.7</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.11</v>
+        <v>2.5</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.67</v>
+        <v>11.6</v>
       </c>
       <c r="AR14" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="AS14" t="n">
         <v>9</v>
       </c>
       <c r="AT14" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AU14" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AV14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AW14" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AX14" t="n">
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>49.56</v>
+        <v>48.2</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
       </c>
       <c r="BA14" t="n">
-        <v>12.78</v>
+        <v>12.9</v>
       </c>
       <c r="BB14" t="n">
-        <v>8.890000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC14" t="n">
-        <v>3.89</v>
+        <v>3.7</v>
       </c>
       <c r="BD14" t="n">
-        <v>18.89</v>
+        <v>18.6</v>
       </c>
       <c r="BE14" t="n">
         <v>1.37</v>
       </c>
       <c r="BF14" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.24</v>
+        <v>10.56</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.41</v>
+        <v>3.33</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.24</v>
+        <v>4.56</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.12</v>
+        <v>5.17</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.23999999999999</v>
+        <v>88.89</v>
       </c>
       <c r="BS14" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT14" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BU14" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX14" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
         <v>2.48</v>
@@ -6442,31 +6442,31 @@
         <v>2.64</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CB14" t="n">
         <v>3.9</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.75</v>
+        <v>3.78</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.07</v>
+        <v>4.1</v>
       </c>
       <c r="CE14" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF14" t="n">
         <v>2.31</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CH14" t="n">
         <v>1.56</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.37</v>
+        <v>2.36</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.54</v>
@@ -6475,13 +6475,13 @@
         <v>1.35</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CO14" t="n">
         <v>1.16</v>
@@ -6490,7 +6490,7 @@
         <v>1.61</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
@@ -6502,7 +6502,7 @@
         <v>3.31</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV14" t="n">
         <v>2.5</v>
@@ -6512,11 +6512,11 @@
       </c>
       <c r="CX14" t="inlineStr"/>
       <c r="CY14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ14" t="inlineStr"/>
       <c r="DA14" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DB14" t="n">
         <v>1.2</v>
@@ -6525,82 +6525,82 @@
         <v>1.64</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="DE14" t="n">
         <v>0.11</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DH14" t="n">
-        <v>83.88</v>
+        <v>83.89</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.06</v>
+        <v>5.28</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.47</v>
+        <v>0.55</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.23</v>
+        <v>41.44</v>
       </c>
       <c r="DN14" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.11</v>
+        <v>2.33</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.12</v>
+        <v>13</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.76</v>
+        <v>10.72</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.529999999999999</v>
+        <v>8.56</v>
       </c>
       <c r="DS14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DT14" t="n">
-        <v>0</v>
+        <v>0.06</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.36</v>
+        <v>47.67</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.06</v>
+        <v>12.17</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.71</v>
+        <v>7.95</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.36</v>
+        <v>4.22</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.71</v>
+        <v>17.61</v>
       </c>
       <c r="EB14" t="n">
         <v>1.37</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.47</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="15">
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D16" t="n">
         <v>8</v>
@@ -7021,82 +7021,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.78</v>
+        <v>2.6</v>
       </c>
       <c r="H16" t="n">
-        <v>95.56</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="K16" t="n">
-        <v>4.78</v>
+        <v>5</v>
       </c>
       <c r="L16" t="n">
-        <v>0.11</v>
+        <v>0.4</v>
       </c>
       <c r="M16" t="n">
-        <v>43.11</v>
+        <v>43.5</v>
       </c>
       <c r="N16" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="O16" t="n">
-        <v>2</v>
+        <v>2.4</v>
       </c>
       <c r="P16" t="n">
-        <v>11.44</v>
+        <v>11.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.89</v>
+        <v>13.8</v>
       </c>
       <c r="R16" t="n">
-        <v>7.78</v>
+        <v>7.7</v>
       </c>
       <c r="S16" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T16" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="U16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.56</v>
+        <v>50.5</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>12.33</v>
+        <v>13.8</v>
       </c>
       <c r="AA16" t="n">
-        <v>8</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AB16" t="n">
-        <v>4.33</v>
+        <v>5.1</v>
       </c>
       <c r="AC16" t="n">
-        <v>20.22</v>
+        <v>19.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.4</v>
+        <v>1.54</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="AF16" t="n">
         <v>0.12</v>
@@ -7180,70 +7180,70 @@
         <v>2.88</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="BH16" t="n">
         <v>10</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.47</v>
+        <v>2.61</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.41</v>
+        <v>0.44</v>
       </c>
       <c r="BL16" t="n">
-        <v>0.88</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.53</v>
+        <v>1.67</v>
       </c>
       <c r="BO16" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.35</v>
+        <v>4.44</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.65</v>
+        <v>5.56</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS16" t="n">
-        <v>76.47</v>
+        <v>77.78</v>
       </c>
       <c r="BT16" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BU16" t="n">
-        <v>11.76</v>
+        <v>16.67</v>
       </c>
       <c r="BV16" t="n">
-        <v>5.88</v>
+        <v>11.11</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>58.82</v>
+        <v>61.11</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="BZ16" t="n">
         <v>2.52</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CC16" t="n">
         <v>3.12</v>
@@ -7252,19 +7252,19 @@
         <v>3.27</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CH16" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.58</v>
@@ -7276,37 +7276,37 @@
         <v>1.71</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.91</v>
+        <v>2.9</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CO16" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP16" t="n">
         <v>1.7</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX16" t="n">
         <v>1.45</v>
@@ -7321,88 +7321,88 @@
         <v>2.2</v>
       </c>
       <c r="DB16" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>2</v>
+        <v>2.11</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.18</v>
+        <v>3.05</v>
       </c>
       <c r="DH16" t="n">
-        <v>94.88</v>
+        <v>95.39</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.77</v>
+        <v>2.89</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.35</v>
+        <v>5.44</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="DM16" t="n">
-        <v>45.41</v>
+        <v>45.5</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.18</v>
+        <v>2.39</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.76</v>
+        <v>12.61</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14.06</v>
+        <v>14</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.94</v>
+        <v>7.89</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.3</v>
+        <v>50.28</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX16" t="n">
-        <v>12</v>
+        <v>12.83</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.65</v>
+        <v>8.06</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.35</v>
+        <v>4.78</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.88</v>
+        <v>20.44</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.71</v>
+        <v>2.84</v>
       </c>
     </row>
     <row r="17">
@@ -7412,13 +7412,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C17" t="n">
         <v>9</v>
       </c>
       <c r="D17" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7502,139 +7502,139 @@
         <v>1.89</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AG17" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AH17" t="n">
+        <v>2.78</v>
+      </c>
+      <c r="AI17" t="n">
+        <v>99.22</v>
+      </c>
+      <c r="AJ17" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="AK17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AL17" t="n">
+        <v>5.22</v>
+      </c>
+      <c r="AM17" t="n">
+        <v>1</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>43.44</v>
+      </c>
+      <c r="AO17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="AP17" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ17" t="n">
+        <v>13</v>
+      </c>
+      <c r="AR17" t="n">
+        <v>11.11</v>
+      </c>
+      <c r="AS17" t="n">
+        <v>6.89</v>
+      </c>
+      <c r="AT17" t="n">
+        <v>0.78</v>
+      </c>
+      <c r="AU17" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AV17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AW17" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>54.56</v>
+      </c>
+      <c r="AZ17" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA17" t="n">
+        <v>15.44</v>
+      </c>
+      <c r="BB17" t="n">
+        <v>10.11</v>
+      </c>
+      <c r="BC17" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="BD17" t="n">
+        <v>20.67</v>
+      </c>
+      <c r="BE17" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF17" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="BG17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BH17" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="BI17" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BJ17" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BK17" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="BL17" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="BM17" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BN17" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH17" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AI17" t="n">
-        <v>94.88</v>
-      </c>
-      <c r="AJ17" t="n">
-        <v>-0.12</v>
-      </c>
-      <c r="AK17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AL17" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AM17" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>41.88</v>
-      </c>
-      <c r="AO17" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="AP17" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>12.38</v>
-      </c>
-      <c r="AR17" t="n">
-        <v>11</v>
-      </c>
-      <c r="AS17" t="n">
-        <v>7.38</v>
-      </c>
-      <c r="AT17" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="AU17" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AV17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AW17" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="AX17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY17" t="n">
-        <v>53.62</v>
-      </c>
-      <c r="AZ17" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA17" t="n">
-        <v>15.12</v>
-      </c>
-      <c r="BB17" t="n">
-        <v>9.880000000000001</v>
-      </c>
-      <c r="BC17" t="n">
-        <v>5.25</v>
-      </c>
-      <c r="BD17" t="n">
-        <v>19.88</v>
-      </c>
-      <c r="BE17" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="BF17" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="BG17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BH17" t="n">
-        <v>10.35</v>
-      </c>
-      <c r="BI17" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BJ17" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BK17" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BL17" t="n">
-        <v>0.88</v>
-      </c>
-      <c r="BM17" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN17" t="n">
-        <v>1.53</v>
-      </c>
       <c r="BO17" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.76</v>
+        <v>4.78</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.59</v>
+        <v>5.61</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS17" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BU17" t="n">
-        <v>17.65</v>
+        <v>16.67</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.88</v>
+        <v>5.56</v>
       </c>
       <c r="BX17" t="n">
-        <v>58.82</v>
+        <v>55.56</v>
       </c>
       <c r="BY17" t="n">
         <v>1.91</v>
@@ -7643,31 +7643,31 @@
         <v>2</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.67</v>
+        <v>3.65</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.25</v>
+        <v>2.27</v>
       </c>
       <c r="CE17" t="n">
         <v>1.31</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CH17" t="n">
         <v>1.52</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.59</v>
@@ -7688,22 +7688,22 @@
         <v>1.2</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT17" t="n">
         <v>3.22</v>
       </c>
       <c r="CU17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV17" t="n">
         <v>2.41</v>
@@ -7727,85 +7727,85 @@
         <v>1.22</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.12</v>
+        <v>3.22</v>
       </c>
       <c r="DH17" t="n">
-        <v>96.06</v>
+        <v>98.16</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.06</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.35</v>
+        <v>2.38</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.47</v>
+        <v>5.78</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.77</v>
+        <v>0.84</v>
       </c>
       <c r="DM17" t="n">
-        <v>47.35</v>
+        <v>47.83</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.35</v>
+        <v>2.5</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.88</v>
+        <v>13.16</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.41</v>
+        <v>10.5</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.77</v>
+        <v>7.5</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.35</v>
+        <v>54.78</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.94</v>
+        <v>16.06</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.41</v>
+        <v>10.5</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.53</v>
+        <v>5.56</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.71</v>
+        <v>21.06</v>
       </c>
       <c r="EB17" t="n">
         <v>1.74</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="18">
@@ -7815,10 +7815,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D18" t="n">
         <v>8</v>
@@ -7827,82 +7827,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="G18" t="n">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="H18" t="n">
-        <v>92</v>
+        <v>90.90000000000001</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="J18" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="K18" t="n">
-        <v>4.33</v>
+        <v>4.6</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>39.22</v>
+        <v>38.9</v>
       </c>
       <c r="N18" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="O18" t="n">
-        <v>2.89</v>
+        <v>3</v>
       </c>
       <c r="P18" t="n">
-        <v>15.67</v>
+        <v>15.2</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.56</v>
+        <v>14.2</v>
       </c>
       <c r="R18" t="n">
-        <v>6.89</v>
+        <v>6.5</v>
       </c>
       <c r="S18" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="T18" t="n">
-        <v>1.56</v>
+        <v>1.4</v>
       </c>
       <c r="U18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>56</v>
+        <v>56.8</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.44</v>
+        <v>13.7</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.890000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.56</v>
+        <v>4.8</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.44</v>
+        <v>21.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AF18" t="n">
         <v>0</v>
@@ -7986,70 +7986,70 @@
         <v>3.62</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.65</v>
+        <v>10</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.82</v>
+        <v>2.78</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.71</v>
+        <v>0.67</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.47</v>
+        <v>0.44</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.18</v>
+        <v>1.11</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.65</v>
+        <v>4.94</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5</v>
+        <v>5.06</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.12</v>
+        <v>94.44</v>
       </c>
       <c r="BS18" t="n">
-        <v>82.34999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>64.70999999999999</v>
+        <v>61.11</v>
       </c>
       <c r="BU18" t="n">
-        <v>29.41</v>
+        <v>27.78</v>
       </c>
       <c r="BV18" t="n">
-        <v>11.76</v>
+        <v>11.11</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>76.47</v>
+        <v>72.22</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="BZ18" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="CA18" t="n">
         <v>3.53</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.59</v>
+        <v>3.6</v>
       </c>
       <c r="CC18" t="n">
         <v>3.51</v>
@@ -8061,13 +8061,13 @@
         <v>1.34</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CG18" t="n">
         <v>3.06</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI18" t="n">
         <v>2.2</v>
@@ -8079,7 +8079,7 @@
         <v>1.43</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM18" t="n">
         <v>2.58</v>
@@ -8100,16 +8100,16 @@
         <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.75</v>
+        <v>2.74</v>
       </c>
       <c r="CT18" t="n">
         <v>3.17</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CW18" t="n">
         <v>1.67</v>
@@ -8118,7 +8118,7 @@
         <v>1.52</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.45</v>
@@ -8130,85 +8130,85 @@
         <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="DE18" t="n">
         <v>0</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.94</v>
+        <v>1.89</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>90.34999999999999</v>
+        <v>89.83</v>
       </c>
       <c r="DI18" t="n">
         <v>0.06</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.3</v>
+        <v>3.22</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.12</v>
+        <v>4.28</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM18" t="n">
-        <v>36.53</v>
+        <v>36.5</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.23</v>
+        <v>1.16</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.18</v>
+        <v>2.28</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.47</v>
+        <v>14.28</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.82</v>
+        <v>14.61</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.29</v>
+        <v>7.06</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>58.77</v>
+        <v>59.06</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.88</v>
+        <v>13.06</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.65</v>
+        <v>8.67</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.24</v>
+        <v>4.39</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.82</v>
+        <v>20.78</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="EC18" t="n">
-        <v>3.06</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="19">
@@ -8218,13 +8218,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C19" t="n">
         <v>8</v>
       </c>
       <c r="D19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E19" t="n">
         <v>0.25</v>
@@ -8308,127 +8308,127 @@
         <v>2.75</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AI19" t="n">
-        <v>104</v>
+        <v>101.9</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.56</v>
+        <v>4.4</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN19" t="n">
-        <v>45.89</v>
+        <v>43.3</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14.22</v>
+        <v>14.1</v>
       </c>
       <c r="AR19" t="n">
-        <v>11.33</v>
+        <v>11.2</v>
       </c>
       <c r="AS19" t="n">
-        <v>5.89</v>
+        <v>6.3</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AU19" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>40.8</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>23.1</v>
+      </c>
+      <c r="BE19" t="n">
         <v>1.33</v>
       </c>
-      <c r="AV19" t="n">
+      <c r="BF19" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>9.56</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="BK19" t="n">
         <v>0.44</v>
       </c>
-      <c r="AW19" t="n">
+      <c r="BL19" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BM19" t="n">
         <v>0.44</v>
       </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>41</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>12.22</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.78</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>4.44</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>22.89</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>9.59</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.29</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0.47</v>
-      </c>
       <c r="BN19" t="n">
-        <v>1.12</v>
+        <v>1.06</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.76</v>
+        <v>0.72</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.12</v>
+        <v>4.06</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.41</v>
+        <v>5.44</v>
       </c>
       <c r="BR19" t="n">
-        <v>94.12</v>
+        <v>88.89</v>
       </c>
       <c r="BS19" t="n">
-        <v>52.94</v>
+        <v>50</v>
       </c>
       <c r="BT19" t="n">
-        <v>41.18</v>
+        <v>38.89</v>
       </c>
       <c r="BU19" t="n">
         <v>0</v>
@@ -8440,7 +8440,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>35.29</v>
+        <v>33.33</v>
       </c>
       <c r="BY19" t="n">
         <v>2.31</v>
@@ -8449,34 +8449,34 @@
         <v>2.32</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.43</v>
+        <v>3.41</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.65</v>
+        <v>2.68</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CE19" t="n">
         <v>1.35</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CG19" t="n">
-        <v>3.02</v>
+        <v>3</v>
       </c>
       <c r="CH19" t="n">
         <v>1.44</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK19" t="n">
         <v>1.42</v>
@@ -8485,19 +8485,19 @@
         <v>1.81</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO19" t="n">
         <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
@@ -8512,106 +8512,106 @@
         <v>1.48</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CW19" t="n">
         <v>1.68</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="DB19" t="n">
         <v>1.26</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.03</v>
+        <v>3.07</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DF19" t="n">
         <v>1.95</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="DH19" t="n">
-        <v>101.88</v>
+        <v>100.83</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.82</v>
+        <v>4.72</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM19" t="n">
-        <v>48.35</v>
+        <v>46.78</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.88</v>
+        <v>0.83</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.24</v>
+        <v>2.11</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.82</v>
+        <v>13.78</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.94</v>
+        <v>11.83</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.47</v>
+        <v>5.72</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.23</v>
+        <v>0.22</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>41.76</v>
+        <v>41.61</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.59</v>
+        <v>12.17</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.06</v>
+        <v>7.89</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.52</v>
+        <v>4.28</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.47</v>
+        <v>21.67</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.47</v>
+        <v>1.41</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.77</v>
+        <v>2.72</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1532,19 +1532,19 @@
         <v>0.11</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.33</v>
+        <v>12.44</v>
       </c>
       <c r="BB2" t="n">
         <v>8.779999999999999</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.56</v>
+        <v>3.67</v>
       </c>
       <c r="BD2" t="n">
         <v>24.22</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="BF2" t="n">
         <v>2.22</v>
@@ -1757,13 +1757,13 @@
         <v>0.11</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.22</v>
+        <v>13.27</v>
       </c>
       <c r="DY2" t="n">
         <v>9.34</v>
       </c>
       <c r="DZ2" t="n">
-        <v>3.89</v>
+        <v>3.94</v>
       </c>
       <c r="EA2" t="n">
         <v>24.22</v>
@@ -2334,19 +2334,19 @@
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.11</v>
+        <v>12.33</v>
       </c>
       <c r="BB4" t="n">
         <v>8</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.11</v>
+        <v>4.33</v>
       </c>
       <c r="BD4" t="n">
         <v>18.56</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="BF4" t="n">
         <v>1.22</v>
@@ -2559,19 +2559,19 @@
         <v>0.06</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.94</v>
+        <v>14.06</v>
       </c>
       <c r="DY4" t="n">
         <v>8.720000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.22</v>
+        <v>5.33</v>
       </c>
       <c r="EA4" t="n">
         <v>18.22</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="EC4" t="n">
         <v>1.61</v>
@@ -2659,16 +2659,16 @@
         <v>11.78</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.109999999999999</v>
+        <v>8</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.67</v>
+        <v>3.78</v>
       </c>
       <c r="AC5" t="n">
         <v>21.56</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -2965,16 +2965,16 @@
         <v>13.17</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.16</v>
+        <v>9.109999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4</v>
+        <v>4.06</v>
       </c>
       <c r="EA5" t="n">
         <v>21.39</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="EC5" t="n">
         <v>2.05</v>
@@ -3537,16 +3537,16 @@
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>52.9</v>
+        <v>52.8</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.1</v>
       </c>
       <c r="BA7" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC7" t="n">
         <v>5</v>
@@ -3555,7 +3555,7 @@
         <v>22.1</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="BF7" t="n">
         <v>2.4</v>
@@ -3762,16 +3762,16 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.22</v>
+        <v>53.16</v>
       </c>
       <c r="DW7" t="n">
         <v>0.06</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.11</v>
+        <v>15.06</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.06</v>
+        <v>10</v>
       </c>
       <c r="DZ7" t="n">
         <v>5.05</v>
@@ -4746,7 +4746,7 @@
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>56.8</v>
+        <v>56.7</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.1</v>
@@ -4971,7 +4971,7 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>57.61</v>
+        <v>57.55</v>
       </c>
       <c r="DW10" t="n">
         <v>0.06</v>
@@ -5074,19 +5074,19 @@
         <v>0.2</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.4</v>
+        <v>12.6</v>
       </c>
       <c r="AA11" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AC11" t="n">
         <v>20.3</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="AE11" t="n">
         <v>2.3</v>
@@ -5380,19 +5380,19 @@
         <v>0.11</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.22</v>
+        <v>12.33</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.109999999999999</v>
+        <v>8.17</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.11</v>
+        <v>4.17</v>
       </c>
       <c r="EA11" t="n">
         <v>21.45</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="EC11" t="n">
         <v>2.66</v>
@@ -5477,10 +5477,10 @@
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.78</v>
+        <v>12.89</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.44</v>
+        <v>8.56</v>
       </c>
       <c r="AB12" t="n">
         <v>4.33</v>
@@ -5489,7 +5489,7 @@
         <v>18.44</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE12" t="n">
         <v>1.67</v>
@@ -5783,10 +5783,10 @@
         <v>0.11</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.39</v>
+        <v>12.44</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.44</v>
+        <v>8.5</v>
       </c>
       <c r="DZ12" t="n">
         <v>3.94</v>
@@ -5874,16 +5874,16 @@
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.4</v>
+        <v>50.5</v>
       </c>
       <c r="Y13" t="n">
         <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>16.6</v>
+        <v>16.5</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB13" t="n">
         <v>6.7</v>
@@ -5892,7 +5892,7 @@
         <v>23.5</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="AE13" t="n">
         <v>2.8</v>
@@ -6180,16 +6180,16 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.95</v>
+        <v>48</v>
       </c>
       <c r="DW13" t="n">
         <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>14</v>
+        <v>13.94</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.56</v>
+        <v>8.5</v>
       </c>
       <c r="DZ13" t="n">
         <v>5.45</v>
@@ -7057,7 +7057,7 @@
         <v>13.8</v>
       </c>
       <c r="R16" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="S16" t="n">
         <v>1.2</v>
@@ -7075,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.5</v>
+        <v>50.6</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
@@ -7369,7 +7369,7 @@
         <v>14</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.89</v>
+        <v>7.83</v>
       </c>
       <c r="DS16" t="n">
         <v>0.17</v>
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.28</v>
+        <v>50.33</v>
       </c>
       <c r="DW16" t="n">
         <v>0.05</v>
@@ -7565,19 +7565,19 @@
         <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>15.44</v>
+        <v>15.22</v>
       </c>
       <c r="BB17" t="n">
         <v>10.11</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.33</v>
+        <v>5.11</v>
       </c>
       <c r="BD17" t="n">
         <v>20.67</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="BF17" t="n">
         <v>2.44</v>
@@ -7790,19 +7790,19 @@
         <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.06</v>
+        <v>15.95</v>
       </c>
       <c r="DY17" t="n">
         <v>10.5</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.56</v>
+        <v>5.44</v>
       </c>
       <c r="EA17" t="n">
         <v>21.06</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="EC17" t="n">
         <v>2.16</v>
@@ -7887,10 +7887,10 @@
         <v>0.2</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.7</v>
+        <v>13.6</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB18" t="n">
         <v>4.8</v>
@@ -7899,7 +7899,7 @@
         <v>21.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="n">
         <v>2.3</v>
@@ -8193,10 +8193,10 @@
         <v>0.16</v>
       </c>
       <c r="DX18" t="n">
-        <v>13.06</v>
+        <v>13</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.67</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.39</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D2" t="n">
         <v>9</v>
       </c>
       <c r="E2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F2" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="G2" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="H2" t="n">
-        <v>97.56</v>
+        <v>102.9</v>
       </c>
       <c r="I2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J2" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="K2" t="n">
-        <v>6.44</v>
+        <v>6.3</v>
       </c>
       <c r="L2" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="M2" t="n">
-        <v>45.56</v>
+        <v>49.2</v>
       </c>
       <c r="N2" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="O2" t="n">
-        <v>2.22</v>
+        <v>2</v>
       </c>
       <c r="P2" t="n">
-        <v>13.44</v>
+        <v>13.1</v>
       </c>
       <c r="Q2" t="n">
-        <v>14</v>
+        <v>14.1</v>
       </c>
       <c r="R2" t="n">
-        <v>8.33</v>
+        <v>7.9</v>
       </c>
       <c r="S2" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="T2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="U2" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="V2" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>55.56</v>
+        <v>56.2</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.11</v>
+        <v>14.1</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.890000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.22</v>
+        <v>4.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>24.22</v>
+        <v>23.6</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AE2" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,70 +1550,70 @@
         <v>2.22</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.83</v>
+        <v>10.84</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.89</v>
+        <v>2.95</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.67</v>
+        <v>0.74</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.11</v>
+        <v>1.16</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.94</v>
+        <v>3.89</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.83</v>
+        <v>6.89</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU2" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BV2" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW2" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX2" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY2" t="n">
         <v>2.14</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC2" t="n">
         <v>3.22</v>
@@ -1625,25 +1625,25 @@
         <v>1.3</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.26</v>
+        <v>3.24</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM2" t="n">
         <v>2.79</v>
@@ -1652,127 +1652,127 @@
         <v>2.18</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.21</v>
+        <v>3.16</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX2" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="CY2" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CZ2" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DA2" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DB2" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DC2" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="DD2" t="n">
+        <v>2.69</v>
+      </c>
+      <c r="DE2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DF2" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="DG2" t="n">
+        <v>4.16</v>
+      </c>
+      <c r="DH2" t="n">
+        <v>99.53</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DK2" t="n">
+        <v>6.16</v>
+      </c>
+      <c r="DL2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="DM2" t="n">
+        <v>49.95</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>2</v>
+      </c>
+      <c r="DP2" t="n">
+        <v>13.26</v>
+      </c>
+      <c r="DQ2" t="n">
+        <v>14.53</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>7.32</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>52.84</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DX2" t="n">
+        <v>13.31</v>
+      </c>
+      <c r="DY2" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>4</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>23.89</v>
+      </c>
+      <c r="EB2" t="n">
         <v>1.48</v>
       </c>
-      <c r="CY2" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="CZ2" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="DA2" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="DB2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DC2" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DD2" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DF2" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DG2" t="n">
-        <v>4.11</v>
-      </c>
-      <c r="DH2" t="n">
-        <v>96.67</v>
-      </c>
-      <c r="DI2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="DK2" t="n">
-        <v>6.22</v>
-      </c>
-      <c r="DL2" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>48.17</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0.84</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>13.44</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.28</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>52.34</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>13.27</v>
-      </c>
-      <c r="DY2" t="n">
-        <v>9.34</v>
-      </c>
-      <c r="DZ2" t="n">
-        <v>3.94</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>24.22</v>
-      </c>
-      <c r="EB2" t="n">
-        <v>1.46</v>
-      </c>
       <c r="EC2" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
@@ -2181,58 +2181,58 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D4" t="n">
         <v>9</v>
       </c>
       <c r="E4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F4" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.67</v>
+        <v>2.3</v>
       </c>
       <c r="H4" t="n">
-        <v>84.56</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J4" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>5.56</v>
+        <v>5.2</v>
       </c>
       <c r="L4" t="n">
-        <v>0.78</v>
+        <v>0.6</v>
       </c>
       <c r="M4" t="n">
-        <v>48.33</v>
+        <v>47.6</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="P4" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.22</v>
+        <v>11.7</v>
       </c>
       <c r="R4" t="n">
-        <v>8.220000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="T4" t="n">
         <v>2</v>
@@ -2247,28 +2247,28 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.89</v>
+        <v>48.9</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.78</v>
+        <v>15.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>9.44</v>
+        <v>9</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.33</v>
+        <v>6.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.89</v>
+        <v>18.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.79</v>
+        <v>1.74</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF4" t="n">
         <v>0.33</v>
@@ -2352,70 +2352,70 @@
         <v>1.22</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.39</v>
+        <v>10.26</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.89</v>
+        <v>2.84</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="BP4" t="n">
-        <v>5</v>
+        <v>4.68</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.39</v>
+        <v>5.05</v>
       </c>
       <c r="BR4" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT4" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU4" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV4" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW4" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX4" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.82</v>
+        <v>3.8</v>
       </c>
       <c r="CC4" t="n">
         <v>2.91</v>
@@ -2427,10 +2427,10 @@
         <v>1.3</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CH4" t="n">
         <v>1.53</v>
@@ -2445,28 +2445,28 @@
         <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="CO4" t="n">
         <v>1.18</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CT4" t="n">
         <v>3.28</v>
@@ -2475,22 +2475,22 @@
         <v>1.56</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX4" t="n">
         <v>1.46</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.58</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="DB4" t="n">
         <v>1.2</v>
@@ -2502,46 +2502,46 @@
         <v>2.64</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.28</v>
+        <v>1.26</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.12</v>
+        <v>1.95</v>
       </c>
       <c r="DH4" t="n">
-        <v>84.39</v>
+        <v>85.20999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.94</v>
+        <v>4.79</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.47</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.66</v>
+        <v>41.63</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.84</v>
+        <v>2.63</v>
       </c>
       <c r="DP4" t="n">
-        <v>12</v>
+        <v>11.79</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.77</v>
+        <v>11.52</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.66</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0</v>
@@ -2556,25 +2556,25 @@
         <v>48.84</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX4" t="n">
-        <v>14.06</v>
+        <v>13.84</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.720000000000001</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.33</v>
+        <v>5.31</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.22</v>
+        <v>18.32</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
     </row>
     <row r="5">
@@ -5405,13 +5405,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="n">
         <v>9</v>
       </c>
       <c r="D12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5495,139 +5495,139 @@
         <v>1.67</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="AI12" t="n">
-        <v>78.78</v>
+        <v>77.40000000000001</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.78</v>
+        <v>3.7</v>
       </c>
       <c r="AL12" t="n">
-        <v>3.89</v>
+        <v>4.1</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>34.89</v>
+        <v>33.8</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.22</v>
+        <v>1.4</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.33</v>
+        <v>15.4</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.78</v>
+        <v>12.5</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.109999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.22</v>
+        <v>1.3</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>49.67</v>
+        <v>48.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="BA12" t="n">
-        <v>12</v>
+        <v>11.6</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.44</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.56</v>
+        <v>3.3</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.33</v>
+        <v>19.1</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.28</v>
+        <v>10.32</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.5</v>
+        <v>0.58</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.17</v>
+        <v>4.11</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.06</v>
+        <v>6.16</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT12" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU12" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BV12" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX12" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY12" t="n">
         <v>2.22</v>
@@ -5636,97 +5636,97 @@
         <v>2.28</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.76</v>
+        <v>2.83</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK12" t="n">
         <v>1.34</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.89</v>
+        <v>2.87</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CO12" t="n">
         <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.6</v>
+        <v>2.63</v>
       </c>
       <c r="CT12" t="n">
-        <v>3.3</v>
+        <v>3.28</v>
       </c>
       <c r="CU12" t="n">
         <v>1.52</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB12" t="n">
         <v>1.23</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DF12" t="n">
         <v>1.95</v>
@@ -5735,37 +5735,37 @@
         <v>2.84</v>
       </c>
       <c r="DH12" t="n">
-        <v>82</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="DM12" t="n">
-        <v>36.61</v>
+        <v>35.95</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.66</v>
+        <v>13.79</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.73</v>
+        <v>13.53</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.77</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
@@ -5777,28 +5777,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.22</v>
+        <v>49.58</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.44</v>
+        <v>12.21</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.5</v>
+        <v>8.42</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.94</v>
+        <v>3.79</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.88</v>
+        <v>18.79</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.62</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="13">
@@ -7009,13 +7009,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C16" t="n">
         <v>10</v>
       </c>
       <c r="D16" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7099,139 +7099,139 @@
         <v>2.8</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG16" t="n">
-        <v>2</v>
+        <v>1.78</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.62</v>
+        <v>3.11</v>
       </c>
       <c r="AI16" t="n">
-        <v>94.12</v>
+        <v>94.33</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AK16" t="n">
-        <v>3</v>
+        <v>2.67</v>
       </c>
       <c r="AL16" t="n">
         <v>6</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.25</v>
+        <v>0.11</v>
       </c>
       <c r="AN16" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.38</v>
+        <v>2</v>
       </c>
       <c r="AQ16" t="n">
-        <v>14.25</v>
+        <v>13.44</v>
       </c>
       <c r="AR16" t="n">
-        <v>14.25</v>
+        <v>13.56</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.119999999999999</v>
+        <v>7.89</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AU16" t="n">
-        <v>1</v>
+        <v>0.89</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>50</v>
+        <v>50.11</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.62</v>
+        <v>12.44</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.25</v>
+        <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.38</v>
+        <v>4.44</v>
       </c>
       <c r="BD16" t="n">
-        <v>21.62</v>
+        <v>21.22</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.88</v>
+        <v>2.56</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BH16" t="n">
-        <v>10</v>
+        <v>9.890000000000001</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL16" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.44</v>
+        <v>4.16</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.56</v>
+        <v>5.21</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT16" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU16" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV16" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY16" t="n">
         <v>2.5</v>
@@ -7246,10 +7246,10 @@
         <v>3.7</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.12</v>
+        <v>3.17</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.27</v>
+        <v>3.34</v>
       </c>
       <c r="CE16" t="n">
         <v>1.32</v>
@@ -7258,13 +7258,13 @@
         <v>2.46</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH16" t="n">
         <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.58</v>
@@ -7273,37 +7273,37 @@
         <v>1.35</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CO16" t="n">
         <v>1.2</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU16" t="n">
         <v>1.53</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CW16" t="n">
         <v>1.6</v>
@@ -7312,13 +7312,13 @@
         <v>1.45</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.61</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DB16" t="n">
         <v>1.22</v>
@@ -7333,76 +7333,76 @@
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="DH16" t="n">
-        <v>95.39</v>
+        <v>95.42</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.44</v>
+        <v>5.47</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.33</v>
+        <v>0.26</v>
       </c>
       <c r="DM16" t="n">
-        <v>45.5</v>
+        <v>46.58</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.39</v>
+        <v>2.21</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.61</v>
+        <v>12.31</v>
       </c>
       <c r="DQ16" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.83</v>
+        <v>7.74</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.33</v>
+        <v>50.37</v>
       </c>
       <c r="DW16" t="n">
         <v>0.05</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.83</v>
+        <v>13.16</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.06</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.44</v>
+        <v>20.31</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.84</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="17">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="n">
         <v>9</v>
       </c>
       <c r="D3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
@@ -1872,139 +1872,139 @@
         <v>3.22</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.44</v>
+        <v>2.2</v>
       </c>
       <c r="AH3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AI3" t="n">
-        <v>83.44</v>
+        <v>83.8</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="AL3" t="n">
-        <v>6.22</v>
+        <v>5.8</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>41.78</v>
+        <v>40.3</v>
       </c>
       <c r="AO3" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AP3" t="n">
-        <v>3.22</v>
+        <v>2.9</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.56</v>
+        <v>12.5</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.33</v>
+        <v>8.4</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.44</v>
+        <v>9.6</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>43.67</v>
+        <v>43</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>12.22</v>
+        <v>11.7</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="BD3" t="n">
-        <v>23.67</v>
+        <v>22.9</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.56</v>
+        <v>3.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BH3" t="n">
-        <v>12.33</v>
+        <v>12.26</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL3" t="n">
         <v>1</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.94</v>
+        <v>6.05</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.39</v>
+        <v>6.21</v>
       </c>
       <c r="BR3" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT3" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BU3" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV3" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX3" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY3" t="n">
         <v>2.17</v>
@@ -2013,25 +2013,25 @@
         <v>2.3</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CC3" t="n">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="CE3" t="n">
         <v>1.29</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CH3" t="n">
         <v>1.53</v>
@@ -2040,19 +2040,19 @@
         <v>2.36</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CM3" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="CO3" t="n">
         <v>1.19</v>
@@ -2061,7 +2061,7 @@
         <v>1.63</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
@@ -2070,7 +2070,7 @@
         <v>2.55</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.27</v>
+        <v>3.29</v>
       </c>
       <c r="CU3" t="n">
         <v>1.54</v>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="CZ3" t="inlineStr"/>
       <c r="DA3" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="DB3" t="n">
         <v>1.21</v>
@@ -2102,43 +2102,43 @@
         <v>0.11</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.33</v>
+        <v>2.21</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.11</v>
+        <v>3.05</v>
       </c>
       <c r="DH3" t="n">
-        <v>96.38</v>
+        <v>95.89</v>
       </c>
       <c r="DI3" t="n">
-        <v>0.06</v>
+        <v>-0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.28</v>
+        <v>6.05</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.62</v>
+        <v>0.58</v>
       </c>
       <c r="DM3" t="n">
-        <v>49.67</v>
+        <v>48.48</v>
       </c>
       <c r="DN3" t="n">
-        <v>1.06</v>
+        <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.62</v>
+        <v>13.53</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.220000000000001</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.77</v>
+        <v>8.890000000000001</v>
       </c>
       <c r="DS3" t="n">
         <v>0.11</v>
@@ -2150,28 +2150,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.62</v>
+        <v>45.16</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.83</v>
+        <v>14.42</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.66</v>
+        <v>10.31</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.84</v>
+        <v>22.47</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.39</v>
+        <v>3.21</v>
       </c>
     </row>
     <row r="4">
@@ -2196,7 +2196,7 @@
         <v>1.5</v>
       </c>
       <c r="G4" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="H4" t="n">
         <v>86.09999999999999</v>
@@ -2208,10 +2208,10 @@
         <v>2</v>
       </c>
       <c r="K4" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="M4" t="n">
         <v>47.6</v>
@@ -2220,7 +2220,7 @@
         <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>2.5</v>
+        <v>2.8</v>
       </c>
       <c r="P4" t="n">
         <v>11.6</v>
@@ -2253,10 +2253,10 @@
         <v>0.1</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.2</v>
+        <v>15.1</v>
       </c>
       <c r="AA4" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="AB4" t="n">
         <v>6.2</v>
@@ -2265,7 +2265,7 @@
         <v>18.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="AE4" t="n">
         <v>1.9</v>
@@ -2355,7 +2355,7 @@
         <v>2.84</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.26</v>
+        <v>10.32</v>
       </c>
       <c r="BI4" t="n">
         <v>2.84</v>
@@ -2379,10 +2379,10 @@
         <v>1.16</v>
       </c>
       <c r="BP4" t="n">
-        <v>4.68</v>
+        <v>5.05</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.05</v>
+        <v>5.26</v>
       </c>
       <c r="BR4" t="n">
         <v>84.20999999999999</v>
@@ -2466,7 +2466,7 @@
         <v>1.36</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CT4" t="n">
         <v>3.28</v>
@@ -2493,13 +2493,13 @@
         <v>2.12</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="DE4" t="n">
         <v>0.26</v>
@@ -2508,7 +2508,7 @@
         <v>1.26</v>
       </c>
       <c r="DG4" t="n">
-        <v>1.95</v>
+        <v>2.05</v>
       </c>
       <c r="DH4" t="n">
         <v>85.20999999999999</v>
@@ -2520,10 +2520,10 @@
         <v>1.63</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.79</v>
+        <v>4.84</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.47</v>
+        <v>0.58</v>
       </c>
       <c r="DM4" t="n">
         <v>41.63</v>
@@ -2532,7 +2532,7 @@
         <v>0.37</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.63</v>
+        <v>2.79</v>
       </c>
       <c r="DP4" t="n">
         <v>11.79</v>
@@ -2559,10 +2559,10 @@
         <v>0.05</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.84</v>
+        <v>13.79</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.529999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ4" t="n">
         <v>5.31</v>
@@ -2584,13 +2584,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
         <v>9</v>
       </c>
       <c r="D5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
         <v>0.11</v>
@@ -2674,52 +2674,52 @@
         <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.56</v>
+        <v>3.4</v>
       </c>
       <c r="AI5" t="n">
-        <v>98.44</v>
+        <v>97.2</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.33</v>
+        <v>2.1</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.78</v>
+        <v>5.7</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN5" t="n">
-        <v>49.33</v>
+        <v>47.6</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.33</v>
+        <v>11.1</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.33</v>
+        <v>11.1</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.33</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2731,82 +2731,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>50</v>
+        <v>48.7</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.56</v>
+        <v>14.4</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.22</v>
+        <v>10.2</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="BD5" t="n">
-        <v>21.22</v>
+        <v>20.8</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="BF5" t="n">
-        <v>2.11</v>
+        <v>1.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.17</v>
+        <v>11.37</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.89</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.89</v>
+        <v>0.84</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.53</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.44</v>
+        <v>1.37</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.89</v>
+        <v>5.05</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.28</v>
+        <v>6.26</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BU5" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV5" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX5" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BY5" t="n">
         <v>2.47</v>
@@ -2818,19 +2818,19 @@
         <v>3.63</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.68</v>
+        <v>3.7</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.36</v>
+        <v>3.48</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.71</v>
+        <v>3.84</v>
       </c>
       <c r="CE5" t="n">
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CG5" t="n">
         <v>3.24</v>
@@ -2848,13 +2848,13 @@
         <v>1.35</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CO5" t="n">
         <v>1.18</v>
@@ -2878,7 +2878,7 @@
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CW5" t="n">
         <v>1.59</v>
@@ -2887,7 +2887,7 @@
         <v>1.46</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.6</v>
@@ -2899,85 +2899,85 @@
         <v>1.22</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.34</v>
+        <v>3.26</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.94</v>
+        <v>91.63</v>
       </c>
       <c r="DI5" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.56</v>
+        <v>5.52</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.37</v>
       </c>
       <c r="DM5" t="n">
-        <v>46.56</v>
+        <v>45.79</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.27</v>
+        <v>12.1</v>
       </c>
       <c r="DR5" t="n">
-        <v>7.94</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.89</v>
+        <v>49.21</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.17</v>
+        <v>13.16</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.109999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.39</v>
+        <v>21.16</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="EC5" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="6">
@@ -2987,13 +2987,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="n">
         <v>10</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3077,52 +3077,52 @@
         <v>2.2</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.75</v>
+        <v>2.44</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.88</v>
+        <v>3</v>
       </c>
       <c r="AI6" t="n">
-        <v>96.12</v>
+        <v>103.78</v>
       </c>
       <c r="AJ6" t="n">
         <v>0</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.25</v>
+        <v>5.78</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.25</v>
+        <v>0.33</v>
       </c>
       <c r="AN6" t="n">
-        <v>43.12</v>
+        <v>48</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.38</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.38</v>
+        <v>2.78</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.38</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>14.25</v>
+        <v>13.89</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.75</v>
+        <v>7.22</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.12</v>
+        <v>1</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3134,82 +3134,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>45.75</v>
+        <v>48.56</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.62</v>
+        <v>13.33</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.5</v>
+        <v>9.44</v>
       </c>
       <c r="BC6" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="BD6" t="n">
-        <v>19.62</v>
+        <v>20.67</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.4</v>
+        <v>1.47</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.56</v>
+        <v>10.63</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.89</v>
+        <v>2.74</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.33</v>
+        <v>1.26</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.61</v>
+        <v>4.74</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.94</v>
+        <v>5.89</v>
       </c>
       <c r="BR6" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BU6" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BV6" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY6" t="n">
         <v>3.06</v>
@@ -3218,31 +3218,31 @@
         <v>3.18</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.2</v>
+        <v>4.03</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.66</v>
+        <v>4.42</v>
       </c>
       <c r="CE6" t="n">
         <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.08</v>
+        <v>3.07</v>
       </c>
       <c r="CH6" t="n">
         <v>1.48</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CJ6" t="n">
         <v>1.63</v>
@@ -3251,22 +3251,22 @@
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="CN6" t="n">
         <v>2.08</v>
       </c>
       <c r="CO6" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3284,70 +3284,70 @@
         <v>2.32</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CX6" t="n">
         <v>1.47</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.55</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB6" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.34</v>
+        <v>2.42</v>
       </c>
       <c r="DH6" t="n">
-        <v>93.5</v>
+        <v>97.26000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.39</v>
+        <v>4.69</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DM6" t="n">
-        <v>38.39</v>
+        <v>40.95</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.78</v>
+        <v>0.84</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.06</v>
+        <v>2.26</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.67</v>
+        <v>12.95</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.89</v>
+        <v>13.74</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.390000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="DS6" t="n">
         <v>0.11</v>
@@ -3359,28 +3359,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>42.72</v>
+        <v>44.21</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.44</v>
+        <v>12.79</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.56</v>
+        <v>9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.89</v>
+        <v>3.79</v>
       </c>
       <c r="EA6" t="n">
-        <v>20.72</v>
+        <v>21.16</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.34</v>
+        <v>1.38</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.39</v>
+        <v>2.37</v>
       </c>
     </row>
     <row r="7">
@@ -3390,94 +3390,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D7" t="n">
         <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="F7" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="G7" t="n">
-        <v>3.38</v>
+        <v>3.11</v>
       </c>
       <c r="H7" t="n">
-        <v>95.25</v>
+        <v>103.22</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>-0.11</v>
       </c>
       <c r="J7" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="K7" t="n">
-        <v>5.88</v>
+        <v>6.22</v>
       </c>
       <c r="L7" t="n">
-        <v>0.12</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M7" t="n">
-        <v>53.5</v>
+        <v>57.44</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O7" t="n">
-        <v>2.5</v>
+        <v>3.11</v>
       </c>
       <c r="P7" t="n">
-        <v>11.88</v>
+        <v>11.56</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.38</v>
+        <v>14.11</v>
       </c>
       <c r="R7" t="n">
-        <v>6.88</v>
+        <v>7</v>
       </c>
       <c r="S7" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>1.78</v>
       </c>
       <c r="U7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>53.62</v>
+        <v>54.67</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>15.38</v>
+        <v>16.11</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.25</v>
+        <v>10.89</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.12</v>
+        <v>5.22</v>
       </c>
       <c r="AC7" t="n">
-        <v>23.25</v>
+        <v>23.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.75</v>
+        <v>1.56</v>
       </c>
       <c r="AF7" t="n">
         <v>0.1</v>
@@ -3561,58 +3561,58 @@
         <v>2.4</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BH7" t="n">
-        <v>11.06</v>
+        <v>11.05</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BL7" t="n">
         <v>1.11</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="BO7" t="n">
         <v>1.11</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.33</v>
+        <v>5.47</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.83</v>
+        <v>4.74</v>
       </c>
       <c r="BR7" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>47.37</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BV7" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BW7" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX7" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BY7" t="n">
         <v>1.93</v>
@@ -3621,10 +3621,10 @@
         <v>1.95</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CC7" t="n">
         <v>2.2</v>
@@ -3636,10 +3636,10 @@
         <v>1.23</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.1</v>
+        <v>3.11</v>
       </c>
       <c r="CH7" t="n">
         <v>1.44</v>
@@ -3648,7 +3648,7 @@
         <v>2.22</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CK7" t="n">
         <v>1.29</v>
@@ -3657,28 +3657,28 @@
         <v>1.58</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.65</v>
+        <v>2.69</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="CR7" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS7" t="n">
         <v>2.6</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="CU7" t="n">
         <v>1.53</v>
@@ -3693,13 +3693,13 @@
         <v>1.44</v>
       </c>
       <c r="CY7" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CZ7" t="n">
         <v>2.61</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.14</v>
+        <v>2.17</v>
       </c>
       <c r="DB7" t="n">
         <v>1.22</v>
@@ -3711,79 +3711,79 @@
         <v>2.76</v>
       </c>
       <c r="DE7" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DF7" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="DG7" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="DH7" t="n">
+        <v>98.09999999999999</v>
+      </c>
+      <c r="DI7" t="n">
         <v>0.11</v>
       </c>
-      <c r="DF7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="DG7" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="DH7" t="n">
-        <v>94.28</v>
-      </c>
-      <c r="DI7" t="n">
-        <v>0.17</v>
-      </c>
       <c r="DJ7" t="n">
-        <v>2.17</v>
+        <v>2.05</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.22</v>
+        <v>6.37</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.33</v>
+        <v>0.53</v>
       </c>
       <c r="DM7" t="n">
-        <v>48.17</v>
+        <v>50.31</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.89</v>
+        <v>3.16</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="DQ7" t="n">
-        <v>15</v>
+        <v>14.84</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.06</v>
+        <v>7.11</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.16</v>
+        <v>53.69</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.06</v>
+        <v>15.42</v>
       </c>
       <c r="DY7" t="n">
-        <v>10</v>
+        <v>10.32</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.61</v>
+        <v>22.95</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3793,13 +3793,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="n">
         <v>10</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3883,139 +3883,139 @@
         <v>2.9</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.38</v>
+        <v>1.44</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="AI8" t="n">
-        <v>94.62</v>
+        <v>95.11</v>
       </c>
       <c r="AJ8" t="n">
         <v>0</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.62</v>
+        <v>2.78</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.12</v>
+        <v>3.89</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AN8" t="n">
-        <v>42.38</v>
+        <v>41.78</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.62</v>
+        <v>1.44</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.62</v>
+        <v>12.33</v>
       </c>
       <c r="AR8" t="n">
-        <v>11.5</v>
+        <v>12.11</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.119999999999999</v>
+        <v>9.33</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.25</v>
+        <v>45.56</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.5</v>
+        <v>12.78</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.75</v>
+        <v>9.220000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.62</v>
+        <v>20.56</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.94</v>
+        <v>8.84</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.28</v>
+        <v>0.32</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL8" t="n">
         <v>0.89</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.72</v>
+        <v>0.74</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.83</v>
+        <v>3.79</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5.06</v>
+        <v>5</v>
       </c>
       <c r="BR8" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>66.67</v>
+        <v>68.42</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BV8" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW8" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX8" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY8" t="n">
         <v>2.34</v>
@@ -4024,16 +4024,16 @@
         <v>2.43</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.78</v>
+        <v>3.79</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.51</v>
+        <v>3.59</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.9</v>
+        <v>3.98</v>
       </c>
       <c r="CE8" t="n">
         <v>1.3</v>
@@ -4045,13 +4045,13 @@
         <v>3.2</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI8" t="n">
         <v>2.33</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK8" t="n">
         <v>1.4</v>
@@ -4072,22 +4072,22 @@
         <v>1.65</v>
       </c>
       <c r="CQ8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="CR8" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS8" t="n">
         <v>2.55</v>
       </c>
-      <c r="CR8" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="CS8" t="n">
-        <v>2.56</v>
-      </c>
       <c r="CT8" t="n">
-        <v>3.11</v>
+        <v>3.16</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CW8" t="n">
         <v>1.59</v>
@@ -4117,43 +4117,43 @@
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.34</v>
+        <v>2.31</v>
       </c>
       <c r="DH8" t="n">
-        <v>90.94</v>
+        <v>91.37</v>
       </c>
       <c r="DI8" t="n">
         <v>-0.11</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.83</v>
+        <v>2.9</v>
       </c>
       <c r="DK8" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM8" t="n">
-        <v>45.67</v>
+        <v>45.21</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.61</v>
+        <v>1.52</v>
       </c>
       <c r="DP8" t="n">
-        <v>13</v>
+        <v>12.84</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.33</v>
+        <v>11.63</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.78</v>
+        <v>7.95</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4168,25 +4168,25 @@
         <v>48.11</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.89</v>
+        <v>12.58</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.279999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.61</v>
+        <v>3.53</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.22</v>
+        <v>20.21</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="9">
@@ -4196,61 +4196,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D9" t="n">
         <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="H9" t="n">
-        <v>88.75</v>
+        <v>83.11</v>
       </c>
       <c r="I9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="J9" t="n">
-        <v>1.88</v>
+        <v>2.22</v>
       </c>
       <c r="K9" t="n">
-        <v>4.75</v>
+        <v>4.44</v>
       </c>
       <c r="L9" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="M9" t="n">
-        <v>36</v>
+        <v>33.89</v>
       </c>
       <c r="N9" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="P9" t="n">
-        <v>10.12</v>
+        <v>10.22</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.12</v>
+        <v>14.56</v>
       </c>
       <c r="R9" t="n">
-        <v>7.75</v>
+        <v>9</v>
       </c>
       <c r="S9" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="T9" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4262,28 +4262,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.88</v>
+        <v>44</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="Z9" t="n">
-        <v>11.25</v>
+        <v>10.44</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.62</v>
+        <v>7.22</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.62</v>
+        <v>3.22</v>
       </c>
       <c r="AC9" t="n">
-        <v>20.25</v>
+        <v>19.56</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.23</v>
+        <v>1.14</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.62</v>
+        <v>1.78</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4367,70 +4367,70 @@
         <v>2.7</v>
       </c>
       <c r="BG9" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.17</v>
+        <v>10.26</v>
       </c>
       <c r="BI9" t="n">
-        <v>4</v>
+        <v>3.79</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.39</v>
+        <v>1.32</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.5</v>
+        <v>2.37</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.33</v>
+        <v>4.47</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.83</v>
+        <v>5.79</v>
       </c>
       <c r="BR9" t="n">
-        <v>100</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>88.89</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>77.78</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BU9" t="n">
-        <v>55.56</v>
+        <v>52.63</v>
       </c>
       <c r="BV9" t="n">
-        <v>38.89</v>
+        <v>36.84</v>
       </c>
       <c r="BW9" t="n">
-        <v>22.22</v>
+        <v>21.05</v>
       </c>
       <c r="BX9" t="n">
-        <v>61.11</v>
+        <v>57.89</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.23</v>
+        <v>3.2</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.77</v>
+        <v>3.74</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.98</v>
+        <v>3.95</v>
       </c>
       <c r="CC9" t="n">
         <v>4.13</v>
@@ -4439,43 +4439,43 @@
         <v>4.95</v>
       </c>
       <c r="CE9" t="n">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.39</v>
+        <v>3.36</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.55</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO9" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.44</v>
+        <v>2.49</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
@@ -4490,73 +4490,73 @@
         <v>1.58</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX9" t="n">
         <v>1.47</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.58</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DB9" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.53</v>
+        <v>2.57</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.55</v>
+        <v>2.47</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.67</v>
+        <v>77.47</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.34</v>
+        <v>2.47</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.89</v>
+        <v>33.95</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.83</v>
+        <v>11.79</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.72</v>
+        <v>13</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.279999999999999</v>
+        <v>8.84</v>
       </c>
       <c r="DS9" t="n">
         <v>0.11</v>
@@ -4568,28 +4568,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.72</v>
+        <v>45.79</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.89</v>
+        <v>11.47</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.55</v>
+        <v>7.37</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.33</v>
+        <v>4.1</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.44</v>
+        <v>21.05</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="10">
@@ -4599,94 +4599,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D10" t="n">
         <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="F10" t="n">
-        <v>1.12</v>
+        <v>1.22</v>
       </c>
       <c r="G10" t="n">
-        <v>3.75</v>
+        <v>3.56</v>
       </c>
       <c r="H10" t="n">
-        <v>113.12</v>
+        <v>112.78</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="K10" t="n">
-        <v>6.62</v>
+        <v>6.44</v>
       </c>
       <c r="L10" t="n">
-        <v>0.38</v>
+        <v>0.33</v>
       </c>
       <c r="M10" t="n">
-        <v>59.25</v>
+        <v>58</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="O10" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="P10" t="n">
-        <v>12.88</v>
+        <v>13.33</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.62</v>
+        <v>13.11</v>
       </c>
       <c r="R10" t="n">
-        <v>6.5</v>
+        <v>6.44</v>
       </c>
       <c r="S10" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="T10" t="n">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="U10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="V10" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>58.62</v>
+        <v>57.89</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>18.12</v>
+        <v>17.22</v>
       </c>
       <c r="AA10" t="n">
-        <v>12.12</v>
+        <v>11.44</v>
       </c>
       <c r="AB10" t="n">
-        <v>6</v>
+        <v>5.78</v>
       </c>
       <c r="AC10" t="n">
-        <v>20.25</v>
+        <v>19.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.99</v>
+        <v>1.91</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="AF10" t="n">
         <v>0.1</v>
@@ -4773,16 +4773,16 @@
         <v>3.11</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.33</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="BI10" t="n">
         <v>3.11</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.78</v>
+        <v>0.74</v>
       </c>
       <c r="BL10" t="n">
         <v>0.89</v>
@@ -4791,46 +4791,46 @@
         <v>0.89</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.06</v>
+        <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.28</v>
+        <v>5.21</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BT10" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BU10" t="n">
-        <v>44.44</v>
+        <v>42.11</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CB10" t="n">
         <v>3.8</v>
@@ -4848,25 +4848,25 @@
         <v>2.44</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.27</v>
+        <v>3.26</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI10" t="n">
         <v>2.31</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK10" t="n">
         <v>1.34</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.94</v>
+        <v>2.93</v>
       </c>
       <c r="CN10" t="n">
         <v>2.19</v>
@@ -4878,7 +4878,7 @@
         <v>1.65</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4887,13 +4887,13 @@
         <v>2.51</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.28</v>
+        <v>3.29</v>
       </c>
       <c r="CU10" t="n">
         <v>1.56</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CW10" t="n">
         <v>1.59</v>
@@ -4902,13 +4902,13 @@
         <v>1.48</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.52</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB10" t="n">
         <v>1.2</v>
@@ -4920,16 +4920,16 @@
         <v>2.64</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.33</v>
+        <v>1.37</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="DH10" t="n">
-        <v>108.11</v>
+        <v>108.21</v>
       </c>
       <c r="DI10" t="n">
         <v>0.11</v>
@@ -4938,28 +4938,28 @@
         <v>2.05</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.61</v>
+        <v>5.58</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.94</v>
+        <v>51.74</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.39</v>
+        <v>2.42</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.11</v>
+        <v>13.31</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.66</v>
+        <v>13.42</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.56</v>
+        <v>6.52</v>
       </c>
       <c r="DS10" t="n">
         <v>0.16</v>
@@ -4971,25 +4971,25 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>57.55</v>
+        <v>57.26</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>15.22</v>
+        <v>14.95</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.609999999999999</v>
+        <v>9.42</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.61</v>
+        <v>5.53</v>
       </c>
       <c r="EA10" t="n">
-        <v>20</v>
+        <v>19.84</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="EC10" t="n">
         <v>2</v>
@@ -5002,13 +5002,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C11" t="n">
         <v>10</v>
       </c>
       <c r="D11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
@@ -5092,139 +5092,139 @@
         <v>2.3</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.25</v>
+        <v>2.11</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AI11" t="n">
-        <v>88.75</v>
+        <v>93.56</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="AK11" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.75</v>
+        <v>3.89</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.12</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>46.38</v>
+        <v>48.67</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.25</v>
+        <v>1.56</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.75</v>
+        <v>14.56</v>
       </c>
       <c r="AR11" t="n">
-        <v>14</v>
+        <v>13.22</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.880000000000001</v>
+        <v>8.44</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>1.11</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>46.75</v>
+        <v>48.56</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>12</v>
+        <v>12.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.25</v>
+        <v>8.67</v>
       </c>
       <c r="BC11" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BD11" t="n">
-        <v>22.88</v>
+        <v>22.67</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.36</v>
+        <v>1.44</v>
       </c>
       <c r="BF11" t="n">
-        <v>3.12</v>
+        <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.22</v>
+        <v>10.11</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.83</v>
+        <v>0.95</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.5</v>
+        <v>4.58</v>
       </c>
       <c r="BQ11" t="n">
-        <v>5</v>
+        <v>4.84</v>
       </c>
       <c r="BR11" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BT11" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BU11" t="n">
-        <v>11.11</v>
+        <v>15.79</v>
       </c>
       <c r="BV11" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX11" t="n">
-        <v>27.78</v>
+        <v>31.58</v>
       </c>
       <c r="BY11" t="n">
         <v>1.79</v>
@@ -5236,13 +5236,13 @@
         <v>3.34</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.75</v>
+        <v>2.66</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.1</v>
+        <v>2.98</v>
       </c>
       <c r="CE11" t="n">
         <v>1.24</v>
@@ -5251,7 +5251,7 @@
         <v>2.27</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.05</v>
+        <v>3.06</v>
       </c>
       <c r="CH11" t="n">
         <v>1.44</v>
@@ -5269,10 +5269,10 @@
         <v>1.59</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO11" t="n">
         <v>1.12</v>
@@ -5287,7 +5287,7 @@
         <v>1.36</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CT11" t="n">
         <v>3.3</v>
@@ -5296,7 +5296,7 @@
         <v>1.56</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CW11" t="n">
         <v>1.6</v>
@@ -5314,88 +5314,88 @@
         <v>2.16</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC11" t="n">
         <v>1.68</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="DE11" t="n">
         <v>0.05</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.33</v>
+        <v>2.26</v>
       </c>
       <c r="DH11" t="n">
-        <v>93.94</v>
+        <v>95.95</v>
       </c>
       <c r="DI11" t="n">
-        <v>-0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.56</v>
+        <v>4.58</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.56</v>
+        <v>46.69</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.61</v>
+        <v>13.58</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.67</v>
+        <v>11.42</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.17</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.28</v>
+        <v>49.05</v>
       </c>
       <c r="DW11" t="n">
         <v>0.11</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.33</v>
+        <v>12.63</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.17</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.17</v>
+        <v>4.26</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.45</v>
+        <v>21.42</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.66</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="12">
@@ -5808,13 +5808,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="n">
         <v>10</v>
       </c>
       <c r="D13" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E13" t="n">
         <v>0.3</v>
@@ -5901,136 +5901,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.75</v>
+        <v>1.67</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="AI13" t="n">
-        <v>91.12</v>
+        <v>89.22</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK13" t="n">
-        <v>3.12</v>
+        <v>2.89</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.38</v>
+        <v>4.11</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="AN13" t="n">
-        <v>35.62</v>
+        <v>35.33</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.25</v>
+        <v>1.11</v>
       </c>
       <c r="AP13" t="n">
         <v>2</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.62</v>
+        <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.75</v>
+        <v>14.44</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.619999999999999</v>
+        <v>10</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="AU13" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>44.33</v>
+      </c>
+      <c r="AZ13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="BA13" t="n">
+        <v>10.44</v>
+      </c>
+      <c r="BB13" t="n">
+        <v>6.67</v>
+      </c>
+      <c r="BC13" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="BD13" t="n">
+        <v>20.56</v>
+      </c>
+      <c r="BE13" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BL13" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BM13" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BN13" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BO13" t="n">
         <v>1</v>
       </c>
-      <c r="AV13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AW13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="n">
-        <v>44.88</v>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="BA13" t="n">
-        <v>10.75</v>
-      </c>
-      <c r="BB13" t="n">
-        <v>6.88</v>
-      </c>
-      <c r="BC13" t="n">
-        <v>3.88</v>
-      </c>
-      <c r="BD13" t="n">
-        <v>20.88</v>
-      </c>
-      <c r="BE13" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BF13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.890000000000001</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BM13" t="n">
-        <v>0.72</v>
-      </c>
-      <c r="BN13" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BO13" t="n">
-        <v>1.06</v>
-      </c>
       <c r="BP13" t="n">
-        <v>4.67</v>
+        <v>4.63</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.5</v>
+        <v>4.68</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT13" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU13" t="n">
-        <v>44.44</v>
+        <v>47.37</v>
       </c>
       <c r="BV13" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BY13" t="n">
         <v>2.41</v>
@@ -6039,136 +6039,136 @@
         <v>2.49</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.59</v>
+        <v>3.56</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.82</v>
+        <v>2.97</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.01</v>
+        <v>3.13</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.21</v>
+        <v>3.17</v>
       </c>
       <c r="CH13" t="n">
         <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ13" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.89</v>
+        <v>2.86</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="CO13" t="n">
         <v>1.19</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CR13" t="n">
         <v>1.36</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.31</v>
+        <v>3.28</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CX13" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.22</v>
+        <v>2.19</v>
       </c>
       <c r="DB13" t="n">
         <v>1.21</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.45</v>
+        <v>2.32</v>
       </c>
       <c r="DH13" t="n">
-        <v>99.44</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.94</v>
+        <v>2.84</v>
       </c>
       <c r="DK13" t="n">
-        <v>5.28</v>
+        <v>5.1</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM13" t="n">
-        <v>43.5</v>
+        <v>42.95</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.17</v>
+        <v>1.1</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.11</v>
+        <v>12.32</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14</v>
+        <v>13.89</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.16</v>
+        <v>9.369999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0.16</v>
@@ -6180,28 +6180,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>48</v>
+        <v>47.58</v>
       </c>
       <c r="DW13" t="n">
         <v>0.05</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.94</v>
+        <v>13.63</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.5</v>
+        <v>8.32</v>
       </c>
       <c r="DZ13" t="n">
-        <v>5.45</v>
+        <v>5.32</v>
       </c>
       <c r="EA13" t="n">
-        <v>22.34</v>
+        <v>22.11</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.84</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="14">
@@ -6211,94 +6211,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C14" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D14" t="n">
         <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="F14" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1.89</v>
       </c>
       <c r="H14" t="n">
-        <v>76.25</v>
+        <v>75.44</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.5</v>
+        <v>3.44</v>
       </c>
       <c r="K14" t="n">
-        <v>4.88</v>
+        <v>4.67</v>
       </c>
       <c r="L14" t="n">
-        <v>0.62</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="M14" t="n">
-        <v>42.12</v>
+        <v>41.78</v>
       </c>
       <c r="N14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="P14" t="n">
+        <v>13.89</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>12.78</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8.44</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>45.89</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>11.56</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>6.56</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>5</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>16.33</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.38</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.12</v>
-      </c>
-      <c r="P14" t="n">
-        <v>14.75</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>12.75</v>
-      </c>
-      <c r="R14" t="n">
-        <v>8</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>47</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>11.25</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>6.38</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>4.88</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>16.38</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.36</v>
-      </c>
       <c r="AE14" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="AF14" t="n">
         <v>0.1</v>
@@ -6382,67 +6382,67 @@
         <v>1.9</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.56</v>
+        <v>10.42</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.33</v>
+        <v>3.37</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.53</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.28</v>
+        <v>1.21</v>
       </c>
       <c r="BM14" t="n">
         <v>1</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.28</v>
+        <v>2.21</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.56</v>
+        <v>4.63</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.17</v>
+        <v>5</v>
       </c>
       <c r="BR14" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS14" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BV14" t="n">
-        <v>33.33</v>
+        <v>31.58</v>
       </c>
       <c r="BW14" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CB14" t="n">
         <v>3.9</v>
@@ -6460,7 +6460,7 @@
         <v>2.31</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.3</v>
+        <v>3.29</v>
       </c>
       <c r="CH14" t="n">
         <v>1.56</v>
@@ -6475,7 +6475,7 @@
         <v>1.35</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM14" t="n">
         <v>2.9</v>
@@ -6490,7 +6490,7 @@
         <v>1.61</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
@@ -6502,7 +6502,7 @@
         <v>3.31</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CV14" t="n">
         <v>2.5</v>
@@ -6519,88 +6519,88 @@
         <v>2.2</v>
       </c>
       <c r="DB14" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DC14" t="n">
         <v>1.64</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.11</v>
+        <v>0.16</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.61</v>
+        <v>2.53</v>
       </c>
       <c r="DH14" t="n">
-        <v>83.89</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.61</v>
+        <v>2.63</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.28</v>
+        <v>5.16</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.44</v>
+        <v>41.32</v>
       </c>
       <c r="DN14" t="n">
         <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="DP14" t="n">
-        <v>13</v>
+        <v>12.68</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.72</v>
+        <v>10.84</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.56</v>
+        <v>8.73</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.67</v>
+        <v>47.11</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.17</v>
+        <v>12.27</v>
       </c>
       <c r="DY14" t="n">
         <v>7.95</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.22</v>
+        <v>4.32</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.61</v>
+        <v>17.52</v>
       </c>
       <c r="EB14" t="n">
         <v>1.37</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
     </row>
     <row r="15">
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
@@ -6622,82 +6622,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2.12</v>
+        <v>2</v>
       </c>
       <c r="G15" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="H15" t="n">
-        <v>106</v>
+        <v>107.78</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="K15" t="n">
-        <v>5.12</v>
+        <v>5.67</v>
       </c>
       <c r="L15" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M15" t="n">
-        <v>53.88</v>
+        <v>55.56</v>
       </c>
       <c r="N15" t="n">
-        <v>0.62</v>
+        <v>0.67</v>
       </c>
       <c r="O15" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="P15" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.12</v>
+        <v>10.89</v>
       </c>
       <c r="R15" t="n">
-        <v>6.12</v>
+        <v>6.22</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="U15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="V15" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>55.62</v>
+        <v>56.44</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z15" t="n">
-        <v>15.75</v>
+        <v>16.33</v>
       </c>
       <c r="AA15" t="n">
-        <v>10.62</v>
+        <v>11.22</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.12</v>
+        <v>5.11</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.5</v>
+        <v>20.67</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.62</v>
+        <v>2.56</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6781,70 +6781,70 @@
         <v>3.2</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.28</v>
+        <v>10.53</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.94</v>
+        <v>2.95</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.89</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.89</v>
+        <v>1.79</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.06</v>
+        <v>1.16</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.94</v>
+        <v>5.11</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.33</v>
+        <v>5.37</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>77.78</v>
+        <v>78.95</v>
       </c>
       <c r="BT15" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV15" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BW15" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BX15" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.39</v>
+        <v>2.31</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.8</v>
+        <v>3.81</v>
       </c>
       <c r="CC15" t="n">
         <v>2.98</v>
@@ -6856,31 +6856,31 @@
         <v>1.26</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.41</v>
+        <v>3.4</v>
       </c>
       <c r="CH15" t="n">
         <v>1.6</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CK15" t="n">
         <v>1.37</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO15" t="n">
         <v>1.15</v>
@@ -6889,7 +6889,7 @@
         <v>1.53</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CR15" t="inlineStr"/>
       <c r="CS15" t="n">
@@ -6900,10 +6900,10 @@
         <v>1.63</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CX15" t="n">
         <v>1.46</v>
@@ -6924,82 +6924,82 @@
         <v>1.57</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.78</v>
+        <v>2.84</v>
       </c>
       <c r="DH15" t="n">
-        <v>91.83</v>
+        <v>93.42</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ15" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.5</v>
+        <v>5.74</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.34</v>
+        <v>47.53</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.72</v>
+        <v>2.84</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.44</v>
+        <v>12.26</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.28</v>
+        <v>12.11</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.44</v>
+        <v>7.42</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.11</v>
+        <v>55.52</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.72</v>
+        <v>16.95</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.05</v>
+        <v>11.31</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.66</v>
+        <v>5.63</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.5</v>
+        <v>19.11</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.78</v>
+        <v>1.81</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.94</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="16">
@@ -7105,7 +7105,7 @@
         <v>1.78</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.11</v>
+        <v>3.44</v>
       </c>
       <c r="AI16" t="n">
         <v>94.33</v>
@@ -7120,7 +7120,7 @@
         <v>6</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.11</v>
+        <v>0.44</v>
       </c>
       <c r="AN16" t="n">
         <v>50</v>
@@ -7129,7 +7129,7 @@
         <v>0.89</v>
       </c>
       <c r="AP16" t="n">
-        <v>2</v>
+        <v>2.56</v>
       </c>
       <c r="AQ16" t="n">
         <v>13.44</v>
@@ -7162,19 +7162,19 @@
         <v>0.11</v>
       </c>
       <c r="BA16" t="n">
-        <v>12.44</v>
+        <v>12.56</v>
       </c>
       <c r="BB16" t="n">
         <v>8</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.44</v>
+        <v>4.56</v>
       </c>
       <c r="BD16" t="n">
         <v>21.22</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BF16" t="n">
         <v>2.56</v>
@@ -7183,7 +7183,7 @@
         <v>2.58</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.890000000000001</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="BI16" t="n">
         <v>2.58</v>
@@ -7207,10 +7207,10 @@
         <v>0.89</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.16</v>
+        <v>4.53</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.21</v>
+        <v>5.42</v>
       </c>
       <c r="BR16" t="n">
         <v>94.73999999999999</v>
@@ -7294,10 +7294,10 @@
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CU16" t="n">
         <v>1.53</v>
@@ -7324,10 +7324,10 @@
         <v>1.22</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
@@ -7336,7 +7336,7 @@
         <v>2</v>
       </c>
       <c r="DG16" t="n">
-        <v>2.84</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
         <v>95.42</v>
@@ -7351,7 +7351,7 @@
         <v>5.47</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.26</v>
+        <v>0.42</v>
       </c>
       <c r="DM16" t="n">
         <v>46.58</v>
@@ -7360,7 +7360,7 @@
         <v>0.74</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.21</v>
+        <v>2.48</v>
       </c>
       <c r="DP16" t="n">
         <v>12.31</v>
@@ -7387,19 +7387,19 @@
         <v>0.05</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.16</v>
+        <v>13.21</v>
       </c>
       <c r="DY16" t="n">
         <v>8.369999999999999</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.79</v>
+        <v>4.84</v>
       </c>
       <c r="EA16" t="n">
         <v>20.31</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="EC16" t="n">
         <v>2.69</v>
@@ -7412,10 +7412,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D17" t="n">
         <v>9</v>
@@ -7424,82 +7424,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="G17" t="n">
-        <v>3.67</v>
+        <v>3.8</v>
       </c>
       <c r="H17" t="n">
-        <v>97.11</v>
+        <v>102.2</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="K17" t="n">
-        <v>6.33</v>
+        <v>6.4</v>
       </c>
       <c r="L17" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M17" t="n">
-        <v>52.22</v>
+        <v>56.1</v>
       </c>
       <c r="N17" t="n">
-        <v>0.78</v>
+        <v>0.7</v>
       </c>
       <c r="O17" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="P17" t="n">
-        <v>13.33</v>
+        <v>12.9</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.890000000000001</v>
+        <v>9.9</v>
       </c>
       <c r="R17" t="n">
-        <v>8.109999999999999</v>
+        <v>7.5</v>
       </c>
       <c r="S17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T17" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>55</v>
+        <v>56.1</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>16.67</v>
+        <v>17.8</v>
       </c>
       <c r="AA17" t="n">
-        <v>10.89</v>
+        <v>11.8</v>
       </c>
       <c r="AB17" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.44</v>
+        <v>21.6</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.83</v>
+        <v>1.95</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AF17" t="n">
         <v>0.22</v>
@@ -7583,67 +7583,67 @@
         <v>2.44</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.44</v>
+        <v>10.58</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.5</v>
+        <v>1.53</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.78</v>
+        <v>4.79</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.61</v>
+        <v>5.74</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BU17" t="n">
-        <v>16.67</v>
+        <v>15.79</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.56</v>
+        <v>5.26</v>
       </c>
       <c r="BX17" t="n">
-        <v>55.56</v>
+        <v>57.89</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB17" t="n">
         <v>3.77</v>
@@ -7658,19 +7658,19 @@
         <v>1.31</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CH17" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CK17" t="n">
         <v>1.37</v>
@@ -7679,7 +7679,7 @@
         <v>1.69</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CN17" t="n">
         <v>2.15</v>
@@ -7691,7 +7691,7 @@
         <v>1.68</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CR17" t="n">
         <v>1.37</v>
@@ -7700,13 +7700,13 @@
         <v>2.6</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CU17" t="n">
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CW17" t="n">
         <v>1.61</v>
@@ -7721,7 +7721,7 @@
         <v>2.58</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB17" t="n">
         <v>1.22</v>
@@ -7733,79 +7733,79 @@
         <v>2.75</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="DH17" t="n">
-        <v>98.16</v>
+        <v>100.79</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.06</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.38</v>
+        <v>2.31</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.78</v>
+        <v>5.84</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DM17" t="n">
-        <v>47.83</v>
+        <v>50.1</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.84</v>
+        <v>0.79</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
       <c r="DP17" t="n">
-        <v>13.16</v>
+        <v>12.95</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.5</v>
+        <v>10.47</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.5</v>
+        <v>7.21</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.78</v>
+        <v>55.37</v>
       </c>
       <c r="DW17" t="n">
         <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.95</v>
+        <v>16.58</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.44</v>
+        <v>5.58</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.06</v>
+        <v>21.16</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="18">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7905,49 +7905,49 @@
         <v>2.3</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>0.11</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.12</v>
+        <v>2.22</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="AI18" t="n">
-        <v>88.5</v>
+        <v>83.44</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="AK18" t="n">
-        <v>3.88</v>
+        <v>4</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.88</v>
+        <v>4.11</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>33.5</v>
+        <v>32.89</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.38</v>
+        <v>1.56</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13.12</v>
+        <v>12.78</v>
       </c>
       <c r="AR18" t="n">
-        <v>15.12</v>
+        <v>14.44</v>
       </c>
       <c r="AS18" t="n">
-        <v>7.75</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="AU18" t="n">
         <v>1</v>
@@ -7962,82 +7962,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>61.88</v>
+        <v>58.78</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.12</v>
+        <v>0.22</v>
       </c>
       <c r="BA18" t="n">
-        <v>12.25</v>
+        <v>11.78</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.380000000000001</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.88</v>
+        <v>3.67</v>
       </c>
       <c r="BD18" t="n">
-        <v>20.12</v>
+        <v>20</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.62</v>
+        <v>3.56</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BH18" t="n">
-        <v>10</v>
+        <v>10.16</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.67</v>
+        <v>0.63</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.44</v>
+        <v>0.47</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.9399999999999999</v>
+        <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="BO18" t="n">
         <v>1.11</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.94</v>
+        <v>4.95</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.06</v>
+        <v>5.21</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.44</v>
+        <v>94.73999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>83.33</v>
+        <v>84.20999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>61.11</v>
+        <v>63.16</v>
       </c>
       <c r="BU18" t="n">
-        <v>27.78</v>
+        <v>26.32</v>
       </c>
       <c r="BV18" t="n">
-        <v>11.11</v>
+        <v>10.53</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>72.22</v>
+        <v>73.68000000000001</v>
       </c>
       <c r="BY18" t="n">
         <v>2.7</v>
@@ -8046,16 +8046,16 @@
         <v>2.88</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.53</v>
+        <v>3.54</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.6</v>
+        <v>3.61</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.51</v>
+        <v>3.74</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.74</v>
+        <v>3.92</v>
       </c>
       <c r="CE18" t="n">
         <v>1.34</v>
@@ -8064,7 +8064,7 @@
         <v>2.51</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.06</v>
+        <v>3.07</v>
       </c>
       <c r="CH18" t="n">
         <v>1.46</v>
@@ -8073,19 +8073,19 @@
         <v>2.2</v>
       </c>
       <c r="CJ18" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CK18" t="n">
         <v>1.43</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM18" t="n">
         <v>2.58</v>
       </c>
       <c r="CN18" t="n">
-        <v>2</v>
+        <v>2.01</v>
       </c>
       <c r="CO18" t="n">
         <v>1.22</v>
@@ -8097,13 +8097,13 @@
         <v>2.78</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CU18" t="n">
         <v>1.49</v>
@@ -8115,67 +8115,67 @@
         <v>1.67</v>
       </c>
       <c r="CX18" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="DD18" t="n">
-        <v>3</v>
+        <v>2.99</v>
       </c>
       <c r="DE18" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="DG18" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
       <c r="DH18" t="n">
-        <v>89.83</v>
+        <v>87.37</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.22</v>
+        <v>3.32</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.28</v>
+        <v>4.37</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM18" t="n">
-        <v>36.5</v>
+        <v>36.05</v>
       </c>
       <c r="DN18" t="n">
         <v>1.16</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.28</v>
+        <v>14.05</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.61</v>
+        <v>14.31</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.06</v>
+        <v>7.58</v>
       </c>
       <c r="DS18" t="n">
         <v>0.11</v>
@@ -8187,28 +8187,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>59.06</v>
+        <v>57.74</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.16</v>
+        <v>0.21</v>
       </c>
       <c r="DX18" t="n">
-        <v>13</v>
+        <v>12.74</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.609999999999999</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.39</v>
+        <v>4.26</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.78</v>
+        <v>20.68</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.4</v>
+        <v>1.37</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="19">
@@ -8218,61 +8218,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C19" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D19" t="n">
         <v>10</v>
       </c>
       <c r="E19" t="n">
-        <v>0.25</v>
+        <v>0.22</v>
       </c>
       <c r="F19" t="n">
-        <v>2.38</v>
+        <v>2.11</v>
       </c>
       <c r="G19" t="n">
-        <v>2.75</v>
+        <v>3.33</v>
       </c>
       <c r="H19" t="n">
-        <v>99.5</v>
+        <v>102.44</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.88</v>
+        <v>2.67</v>
       </c>
       <c r="K19" t="n">
-        <v>5.12</v>
+        <v>5.67</v>
       </c>
       <c r="L19" t="n">
-        <v>0.5</v>
+        <v>0.44</v>
       </c>
       <c r="M19" t="n">
-        <v>51.12</v>
+        <v>50.78</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="O19" t="n">
-        <v>2.38</v>
+        <v>2.33</v>
       </c>
       <c r="P19" t="n">
-        <v>13.38</v>
+        <v>13.22</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.62</v>
+        <v>13</v>
       </c>
       <c r="R19" t="n">
         <v>5</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="T19" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8284,28 +8284,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>42.62</v>
+        <v>44.56</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="Z19" t="n">
-        <v>13</v>
+        <v>13.44</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.380000000000001</v>
+        <v>8.779999999999999</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.62</v>
+        <v>4.67</v>
       </c>
       <c r="AC19" t="n">
-        <v>19.88</v>
+        <v>20.78</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.75</v>
+        <v>2.56</v>
       </c>
       <c r="AF19" t="n">
         <v>0.2</v>
@@ -8389,49 +8389,49 @@
         <v>2.7</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.56</v>
+        <v>9.68</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.61</v>
+        <v>0.68</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.44</v>
+        <v>0.53</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.06</v>
+        <v>1.21</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.72</v>
+        <v>0.68</v>
       </c>
       <c r="BP19" t="n">
-        <v>4.06</v>
+        <v>4.05</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.44</v>
+        <v>5.58</v>
       </c>
       <c r="BR19" t="n">
-        <v>88.89</v>
+        <v>89.47</v>
       </c>
       <c r="BS19" t="n">
-        <v>50</v>
+        <v>52.63</v>
       </c>
       <c r="BT19" t="n">
-        <v>38.89</v>
+        <v>42.11</v>
       </c>
       <c r="BU19" t="n">
-        <v>0</v>
+        <v>5.26</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8440,19 +8440,19 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>33.33</v>
+        <v>36.84</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.32</v>
+        <v>2.29</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.41</v>
+        <v>3.39</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CC19" t="n">
         <v>2.68</v>
@@ -8464,13 +8464,13 @@
         <v>1.35</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="CG19" t="n">
-        <v>3</v>
+        <v>2.97</v>
       </c>
       <c r="CH19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CI19" t="n">
         <v>2.17</v>
@@ -8479,139 +8479,139 @@
         <v>1.65</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="CO19" t="n">
         <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CQ19" t="n">
         <v>2.95</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CU19" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX19" t="n">
         <v>1.51</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.03</v>
+        <v>2.01</v>
       </c>
       <c r="DB19" t="n">
         <v>1.26</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.61</v>
+        <v>2.89</v>
       </c>
       <c r="DH19" t="n">
-        <v>100.83</v>
+        <v>102.16</v>
       </c>
       <c r="DI19" t="n">
         <v>0.11</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.72</v>
+        <v>5</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM19" t="n">
-        <v>46.78</v>
+        <v>46.84</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.78</v>
+        <v>13.68</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.83</v>
+        <v>12.05</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.72</v>
+        <v>5.68</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>41.61</v>
+        <v>42.58</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.17</v>
+        <v>12.42</v>
       </c>
       <c r="DY19" t="n">
-        <v>7.89</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.28</v>
+        <v>4.32</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.67</v>
+        <v>22</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.72</v>
+        <v>2.63</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -2731,7 +2731,7 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.1</v>
@@ -2956,7 +2956,7 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.21</v>
+        <v>49.16</v>
       </c>
       <c r="DW5" t="n">
         <v>0.1</v>
@@ -3462,10 +3462,10 @@
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.11</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.89</v>
+        <v>10.78</v>
       </c>
       <c r="AB7" t="n">
         <v>5.22</v>
@@ -3474,7 +3474,7 @@
         <v>23.89</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="AE7" t="n">
         <v>1.56</v>
@@ -3768,10 +3768,10 @@
         <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.42</v>
+        <v>15.37</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.32</v>
+        <v>10.26</v>
       </c>
       <c r="DZ7" t="n">
         <v>5.1</v>
@@ -4671,10 +4671,10 @@
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.22</v>
+        <v>17.33</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.44</v>
+        <v>11.56</v>
       </c>
       <c r="AB10" t="n">
         <v>5.78</v>
@@ -4683,7 +4683,7 @@
         <v>19.89</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AE10" t="n">
         <v>1.67</v>
@@ -4977,10 +4977,10 @@
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.95</v>
+        <v>15</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.42</v>
+        <v>9.48</v>
       </c>
       <c r="DZ10" t="n">
         <v>5.53</v>
@@ -4989,7 +4989,7 @@
         <v>19.84</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="EC10" t="n">
         <v>2</v>
@@ -5158,10 +5158,10 @@
         <v>12.67</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.67</v>
+        <v>8.56</v>
       </c>
       <c r="BC11" t="n">
-        <v>4</v>
+        <v>4.11</v>
       </c>
       <c r="BD11" t="n">
         <v>22.67</v>
@@ -5383,10 +5383,10 @@
         <v>12.63</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.369999999999999</v>
+        <v>8.32</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.26</v>
+        <v>4.32</v>
       </c>
       <c r="EA11" t="n">
         <v>21.42</v>
@@ -6259,7 +6259,7 @@
         <v>12.78</v>
       </c>
       <c r="R14" t="n">
-        <v>8.44</v>
+        <v>8.56</v>
       </c>
       <c r="S14" t="n">
         <v>1.78</v>
@@ -6292,7 +6292,7 @@
         <v>5</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.33</v>
+        <v>16.22</v>
       </c>
       <c r="AD14" t="n">
         <v>1.38</v>
@@ -6567,7 +6567,7 @@
         <v>10.84</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.73</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.05</v>
@@ -6594,7 +6594,7 @@
         <v>4.32</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.52</v>
+        <v>17.47</v>
       </c>
       <c r="EB14" t="n">
         <v>1.37</v>
@@ -6676,7 +6676,7 @@
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56.44</v>
+        <v>56.56</v>
       </c>
       <c r="Y15" t="n">
         <v>0.11</v>
@@ -6978,7 +6978,7 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.52</v>
+        <v>55.58</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
@@ -7484,10 +7484,10 @@
         <v>0.2</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.8</v>
+        <v>17.9</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.8</v>
+        <v>11.9</v>
       </c>
       <c r="AB17" t="n">
         <v>6</v>
@@ -7790,10 +7790,10 @@
         <v>0.11</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.58</v>
+        <v>16.63</v>
       </c>
       <c r="DY17" t="n">
-        <v>11</v>
+        <v>11.05</v>
       </c>
       <c r="DZ17" t="n">
         <v>5.58</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -4599,13 +4599,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="n">
         <v>9</v>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E10" t="n">
         <v>0.11</v>
@@ -4689,139 +4689,139 @@
         <v>1.67</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>101.18</v>
+      </c>
+      <c r="AJ10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AK10" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AL10" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="AM10" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>45.18</v>
+      </c>
+      <c r="AO10" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2.09</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13.73</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>13.45</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.36</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>55.45</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12.82</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5.09</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>19.18</v>
+      </c>
+      <c r="BE10" t="n">
         <v>1.5</v>
       </c>
-      <c r="AH10" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>104.1</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>46.1</v>
-      </c>
-      <c r="AO10" t="n">
+      <c r="BF10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BK10" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BL10" t="n">
         <v>0.9</v>
       </c>
-      <c r="AP10" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>56.7</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>19.8</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>9.210000000000001</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3.11</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BL10" t="n">
-        <v>0.89</v>
-      </c>
       <c r="BM10" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP10" t="n">
         <v>4</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.21</v>
+        <v>5.2</v>
       </c>
       <c r="BR10" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS10" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BT10" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BU10" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BV10" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY10" t="n">
         <v>1.85</v>
@@ -4830,22 +4830,22 @@
         <v>1.93</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB10" t="n">
         <v>3.8</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CE10" t="n">
         <v>1.3</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CG10" t="n">
         <v>3.26</v>
@@ -4857,19 +4857,19 @@
         <v>2.31</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="CK10" t="n">
         <v>1.34</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CM10" t="n">
         <v>2.93</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
@@ -4878,7 +4878,7 @@
         <v>1.65</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4923,76 +4923,76 @@
         <v>0.1</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.37</v>
+        <v>1.5</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="DH10" t="n">
-        <v>108.21</v>
+        <v>106.4</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.58</v>
+        <v>5.45</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.74</v>
+        <v>50.95</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.31</v>
+        <v>13.55</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.42</v>
+        <v>13.3</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.52</v>
+        <v>6.4</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>57.26</v>
+        <v>56.55</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>15</v>
+        <v>14.85</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.48</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.53</v>
+        <v>5.4</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.84</v>
+        <v>19.5</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="11">
@@ -6610,10 +6610,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D15" t="n">
         <v>10</v>
@@ -6622,82 +6622,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>2</v>
+        <v>1.8</v>
       </c>
       <c r="G15" t="n">
-        <v>2.56</v>
+        <v>2.8</v>
       </c>
       <c r="H15" t="n">
-        <v>107.78</v>
+        <v>108</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.67</v>
+        <v>2.4</v>
       </c>
       <c r="K15" t="n">
-        <v>5.67</v>
+        <v>5.7</v>
       </c>
       <c r="L15" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M15" t="n">
-        <v>55.56</v>
+        <v>55.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="O15" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="P15" t="n">
-        <v>13</v>
+        <v>12.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>10.89</v>
+        <v>11.6</v>
       </c>
       <c r="R15" t="n">
-        <v>6.22</v>
+        <v>6.4</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="U15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="V15" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56.56</v>
+        <v>56.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.33</v>
+        <v>16</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.22</v>
+        <v>11</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="AC15" t="n">
-        <v>20.67</v>
+        <v>19.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.56</v>
+        <v>2.3</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6784,67 +6784,67 @@
         <v>2.95</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.53</v>
+        <v>10.45</v>
       </c>
       <c r="BI15" t="n">
         <v>2.95</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP15" t="n">
-        <v>5.11</v>
+        <v>5.05</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.37</v>
+        <v>5.35</v>
       </c>
       <c r="BR15" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS15" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT15" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU15" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV15" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW15" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX15" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.15</v>
+        <v>2.17</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.81</v>
+        <v>3.8</v>
       </c>
       <c r="CC15" t="n">
         <v>2.98</v>
@@ -6859,10 +6859,10 @@
         <v>2.28</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CI15" t="n">
         <v>2.52</v>
@@ -6877,7 +6877,7 @@
         <v>1.75</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="CN15" t="n">
         <v>2.16</v>
@@ -6893,14 +6893,14 @@
       </c>
       <c r="CR15" t="inlineStr"/>
       <c r="CS15" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="n">
         <v>1.63</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CW15" t="n">
         <v>1.51</v>
@@ -6921,52 +6921,52 @@
         <v>1.17</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.84</v>
+        <v>2.95</v>
       </c>
       <c r="DH15" t="n">
-        <v>93.42</v>
+        <v>94.25</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.95</v>
+        <v>2.8</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.74</v>
+        <v>5.75</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.53</v>
+        <v>47.8</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.84</v>
+        <v>2.75</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.26</v>
+        <v>12.2</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.11</v>
+        <v>12.4</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.42</v>
+        <v>7.45</v>
       </c>
       <c r="DS15" t="n">
         <v>0.1</v>
@@ -6978,28 +6978,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.58</v>
+        <v>55.65</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.95</v>
+        <v>16.75</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.31</v>
+        <v>11.2</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.63</v>
+        <v>5.55</v>
       </c>
       <c r="EA15" t="n">
-        <v>19.11</v>
+        <v>18.65</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.9</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="16">
@@ -7009,10 +7009,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D16" t="n">
         <v>9</v>
@@ -7021,82 +7021,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="G16" t="n">
-        <v>2.6</v>
+        <v>2.82</v>
       </c>
       <c r="H16" t="n">
-        <v>96.40000000000001</v>
+        <v>97.55</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="K16" t="n">
-        <v>5</v>
+        <v>5.18</v>
       </c>
       <c r="L16" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="M16" t="n">
-        <v>43.5</v>
+        <v>45.55</v>
       </c>
       <c r="N16" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O16" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="P16" t="n">
-        <v>11.3</v>
+        <v>10.91</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.8</v>
+        <v>13.91</v>
       </c>
       <c r="R16" t="n">
-        <v>7.6</v>
+        <v>7.64</v>
       </c>
       <c r="S16" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="T16" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.6</v>
+        <v>50.91</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.8</v>
+        <v>14.09</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.699999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.5</v>
+        <v>19.91</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.8</v>
+        <v>2.73</v>
       </c>
       <c r="AF16" t="n">
         <v>0.11</v>
@@ -7180,70 +7180,70 @@
         <v>2.56</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.949999999999999</v>
+        <v>9.9</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL16" t="n">
         <v>1.05</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BO16" t="n">
-        <v>0.89</v>
+        <v>0.85</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.53</v>
+        <v>4.45</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.42</v>
+        <v>5.45</v>
       </c>
       <c r="BR16" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS16" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU16" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV16" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY16" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="BZ16" t="n">
         <v>2.5</v>
       </c>
-      <c r="BZ16" t="n">
-        <v>2.52</v>
-      </c>
       <c r="CA16" t="n">
-        <v>3.55</v>
+        <v>3.53</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CC16" t="n">
         <v>3.17</v>
@@ -7255,28 +7255,28 @@
         <v>1.32</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.46</v>
+        <v>2.49</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.21</v>
+        <v>3.19</v>
       </c>
       <c r="CH16" t="n">
         <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CJ16" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CK16" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.89</v>
+        <v>2.88</v>
       </c>
       <c r="CN16" t="n">
         <v>2.18</v>
@@ -7285,124 +7285,124 @@
         <v>1.2</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CU16" t="n">
         <v>1.53</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW16" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX16" t="n">
         <v>1.45</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DB16" t="n">
         <v>1.22</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.74</v>
+        <v>2.77</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="DH16" t="n">
-        <v>95.42</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.47</v>
+        <v>5.55</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="DM16" t="n">
-        <v>46.58</v>
+        <v>47.55</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.48</v>
+        <v>2.45</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.31</v>
+        <v>12.05</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.69</v>
+        <v>13.75</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.74</v>
+        <v>7.75</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.37</v>
+        <v>50.55</v>
       </c>
       <c r="DW16" t="n">
         <v>0.05</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.21</v>
+        <v>13.4</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.369999999999999</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.84</v>
+        <v>4.85</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.31</v>
+        <v>20.5</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.51</v>
+        <v>1.54</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.69</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="17">
@@ -7815,13 +7815,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C18" t="n">
         <v>10</v>
       </c>
       <c r="D18" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7905,49 +7905,49 @@
         <v>2.3</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.56</v>
+        <v>2.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>83.44</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AK18" t="n">
         <v>4</v>
       </c>
       <c r="AL18" t="n">
-        <v>4.11</v>
+        <v>3.9</v>
       </c>
       <c r="AM18" t="n">
         <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>32.89</v>
+        <v>32.3</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.78</v>
+        <v>13</v>
       </c>
       <c r="AR18" t="n">
-        <v>14.44</v>
+        <v>13.7</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.779999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="AU18" t="n">
         <v>1</v>
@@ -7962,82 +7962,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>58.78</v>
+        <v>57.5</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.78</v>
+        <v>11.6</v>
       </c>
       <c r="BB18" t="n">
-        <v>8.109999999999999</v>
+        <v>7.9</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="BD18" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.56</v>
+        <v>3.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.16</v>
+        <v>10.1</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="BL18" t="n">
         <v>1</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.95</v>
+        <v>4.85</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.21</v>
+        <v>5.25</v>
       </c>
       <c r="BR18" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS18" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT18" t="n">
-        <v>63.16</v>
+        <v>60</v>
       </c>
       <c r="BU18" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV18" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BY18" t="n">
         <v>2.7</v>
@@ -8046,43 +8046,43 @@
         <v>2.88</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.54</v>
+        <v>3.52</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CC18" t="n">
         <v>3.74</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.92</v>
+        <v>3.87</v>
       </c>
       <c r="CE18" t="n">
         <v>1.34</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.07</v>
+        <v>3.06</v>
       </c>
       <c r="CH18" t="n">
         <v>1.46</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.63</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL18" t="n">
         <v>1.85</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CN18" t="n">
         <v>2.01</v>
@@ -8091,16 +8091,16 @@
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CR18" t="n">
         <v>1.37</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="CT18" t="n">
         <v>3.18</v>
@@ -8121,7 +8121,7 @@
         <v>1.82</v>
       </c>
       <c r="CZ18" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="DA18" t="n">
         <v>1.99</v>
@@ -8130,10 +8130,10 @@
         <v>1.25</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="DD18" t="n">
-        <v>2.99</v>
+        <v>3</v>
       </c>
       <c r="DE18" t="n">
         <v>0.05</v>
@@ -8142,73 +8142,73 @@
         <v>1.95</v>
       </c>
       <c r="DG18" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>87.37</v>
+        <v>87.90000000000001</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.37</v>
+        <v>4.25</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM18" t="n">
-        <v>36.05</v>
+        <v>35.6</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.05</v>
+        <v>14.1</v>
       </c>
       <c r="DQ18" t="n">
-        <v>14.31</v>
+        <v>13.95</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.58</v>
+        <v>7.65</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>57.74</v>
+        <v>57.15</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.74</v>
+        <v>12.6</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.470000000000001</v>
+        <v>8.35</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.26</v>
+        <v>4.25</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.68</v>
+        <v>20.75</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
         <v>10</v>
       </c>
       <c r="D2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
         <v>0.1</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="AH2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AI2" t="n">
-        <v>95.78</v>
+        <v>98.7</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.33</v>
+        <v>2.4</v>
       </c>
       <c r="AL2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>50.78</v>
+        <v>51</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AP2" t="n">
         <v>2</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.44</v>
+        <v>13.3</v>
       </c>
       <c r="AR2" t="n">
-        <v>15</v>
+        <v>14.7</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.67</v>
+        <v>6.8</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.67</v>
+        <v>1.6</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.11</v>
+        <v>49.5</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.44</v>
+        <v>12.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>8.779999999999999</v>
+        <v>9</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.67</v>
+        <v>3.9</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.22</v>
+        <v>23.7</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.41</v>
+        <v>1.46</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.84</v>
+        <v>10.7</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.89</v>
+        <v>3.9</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.89</v>
+        <v>6.75</v>
       </c>
       <c r="BR2" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS2" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV2" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW2" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX2" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY2" t="n">
         <v>2.14</v>
@@ -1610,28 +1610,28 @@
         <v>2.25</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.57</v>
+        <v>3.55</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.68</v>
+        <v>3.66</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.22</v>
+        <v>3.16</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.44</v>
+        <v>3.36</v>
       </c>
       <c r="CE2" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI2" t="n">
         <v>2.35</v>
@@ -1646,37 +1646,37 @@
         <v>1.75</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CN2" t="n">
         <v>2.18</v>
       </c>
       <c r="CO2" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.54</v>
+        <v>2.58</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.16</v>
+        <v>3.13</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX2" t="n">
         <v>1.46</v>
@@ -1688,91 +1688,91 @@
         <v>2.58</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DB2" t="n">
         <v>1.21</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="DE2" t="n">
         <v>0.05</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.16</v>
+        <v>4.1</v>
       </c>
       <c r="DH2" t="n">
-        <v>99.53</v>
+        <v>100.8</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.16</v>
+        <v>6.1</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="DM2" t="n">
-        <v>49.95</v>
+        <v>50.1</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO2" t="n">
         <v>2</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.26</v>
+        <v>13.2</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14.53</v>
+        <v>14.4</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.32</v>
+        <v>7.35</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.31</v>
+        <v>0.35</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.84</v>
+        <v>52.85</v>
       </c>
       <c r="DW2" t="n">
         <v>0.1</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.31</v>
+        <v>13.5</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.32</v>
+        <v>9.4</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.89</v>
+        <v>23.65</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.1</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D3" t="n">
         <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="F3" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="G3" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="H3" t="n">
-        <v>109.33</v>
+        <v>104.4</v>
       </c>
       <c r="I3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="J3" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="K3" t="n">
-        <v>6.33</v>
+        <v>5.9</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M3" t="n">
-        <v>57.56</v>
+        <v>54.3</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="P3" t="n">
-        <v>14.67</v>
+        <v>14.7</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.11</v>
+        <v>10.4</v>
       </c>
       <c r="R3" t="n">
-        <v>8.109999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="S3" t="n">
-        <v>1.33</v>
+        <v>1.2</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.56</v>
+        <v>46.6</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.44</v>
+        <v>16.7</v>
       </c>
       <c r="AA3" t="n">
-        <v>12.33</v>
+        <v>11.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.11</v>
+        <v>5.2</v>
       </c>
       <c r="AC3" t="n">
-        <v>22</v>
+        <v>21.5</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.87</v>
+        <v>1.81</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.22</v>
+        <v>3.3</v>
       </c>
       <c r="AF3" t="n">
         <v>0.2</v>
@@ -1953,70 +1953,70 @@
         <v>3.2</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BH3" t="n">
-        <v>12.26</v>
+        <v>11.95</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BL3" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.58</v>
+        <v>1.5</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.21</v>
+        <v>1.25</v>
       </c>
       <c r="BP3" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="BQ3" t="n">
         <v>6.05</v>
       </c>
-      <c r="BQ3" t="n">
-        <v>6.21</v>
-      </c>
       <c r="BR3" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BU3" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BV3" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.17</v>
+        <v>2.19</v>
       </c>
       <c r="BZ3" t="n">
         <v>2.3</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CC3" t="n">
         <v>3.07</v>
@@ -2025,153 +2025,157 @@
         <v>3.39</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CF3" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="CG3" t="n">
+        <v>3.26</v>
+      </c>
+      <c r="CH3" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="CI3" t="n">
         <v>2.34</v>
       </c>
-      <c r="CG3" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="CH3" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>2.36</v>
-      </c>
       <c r="CJ3" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="CM3" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CO3" t="n">
         <v>1.19</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.29</v>
+        <v>3.25</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="CX3" t="inlineStr"/>
+        <v>1.59</v>
+      </c>
+      <c r="CX3" t="n">
+        <v>1.45</v>
+      </c>
       <c r="CY3" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="CZ3" t="inlineStr"/>
+        <v>1.6</v>
+      </c>
+      <c r="CZ3" t="n">
+        <v>2.59</v>
+      </c>
       <c r="DA3" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="DB3" t="n">
         <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="DG3" t="n">
-        <v>3.05</v>
+        <v>2.95</v>
       </c>
       <c r="DH3" t="n">
-        <v>95.89</v>
+        <v>94.09999999999999</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
       <c r="DK3" t="n">
-        <v>6.05</v>
+        <v>5.85</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM3" t="n">
-        <v>48.48</v>
+        <v>47.3</v>
       </c>
       <c r="DN3" t="n">
         <v>1</v>
       </c>
       <c r="DO3" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.53</v>
+        <v>13.6</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.210000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.890000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.16</v>
+        <v>44.8</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.42</v>
+        <v>14.2</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.31</v>
+        <v>10</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.47</v>
+        <v>22.2</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.21</v>
+        <v>3.25</v>
       </c>
     </row>
     <row r="4">
@@ -2181,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>10</v>
       </c>
       <c r="D4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
         <v>0.2</v>
@@ -2271,139 +2275,139 @@
         <v>1.9</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AG4" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>87.8</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO4" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AP4" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AQ4" t="n">
+        <v>12.3</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AT4" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU4" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="AZ4" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA4" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="BB4" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="BC4" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>17.9</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="BF4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="BG4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BH4" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="BI4" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="BJ4" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="BK4" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="BL4" t="n">
         <v>1</v>
       </c>
-      <c r="AH4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>84.22</v>
-      </c>
-      <c r="AJ4" t="n">
-        <v>-0.11</v>
-      </c>
-      <c r="AK4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="AM4" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>35</v>
-      </c>
-      <c r="AO4" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AP4" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AQ4" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>11.33</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>9.109999999999999</v>
-      </c>
-      <c r="AT4" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AU4" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AV4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY4" t="n">
-        <v>48.78</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA4" t="n">
-        <v>12.33</v>
-      </c>
-      <c r="BB4" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="BD4" t="n">
-        <v>18.56</v>
-      </c>
-      <c r="BE4" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BH4" t="n">
-        <v>10.32</v>
-      </c>
-      <c r="BI4" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="BJ4" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BK4" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BL4" t="n">
-        <v>1.05</v>
-      </c>
       <c r="BM4" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.16</v>
+        <v>1.25</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.05</v>
+        <v>5.1</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.26</v>
+        <v>5.2</v>
       </c>
       <c r="BR4" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS4" t="n">
-        <v>68.42</v>
+        <v>70</v>
       </c>
       <c r="BT4" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BU4" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BV4" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW4" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY4" t="n">
         <v>1.84</v>
@@ -2412,40 +2416,40 @@
         <v>1.86</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.91</v>
+        <v>2.95</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.15</v>
+        <v>3.17</v>
       </c>
       <c r="CE4" t="n">
         <v>1.3</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CH4" t="n">
         <v>1.53</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.57</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="CM4" t="n">
         <v>2.7</v>
@@ -2457,10 +2461,10 @@
         <v>1.18</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
@@ -2469,7 +2473,7 @@
         <v>2.5</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.28</v>
+        <v>3.3</v>
       </c>
       <c r="CU4" t="n">
         <v>1.56</v>
@@ -2481,16 +2485,16 @@
         <v>1.59</v>
       </c>
       <c r="CX4" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.58</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.12</v>
+        <v>2.11</v>
       </c>
       <c r="DB4" t="n">
         <v>1.21</v>
@@ -2502,79 +2506,79 @@
         <v>2.67</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.05</v>
+        <v>2.15</v>
       </c>
       <c r="DH4" t="n">
-        <v>85.20999999999999</v>
+        <v>86.95</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.63</v>
+        <v>1.75</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.84</v>
+        <v>4.9</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.63</v>
+        <v>41.8</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.79</v>
+        <v>11.95</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.52</v>
+        <v>11.35</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.630000000000001</v>
+        <v>8.5</v>
       </c>
       <c r="DS4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DT4" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>48.84</v>
+        <v>49.2</v>
       </c>
       <c r="DW4" t="n">
         <v>0.05</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.79</v>
+        <v>13.85</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.470000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.31</v>
+        <v>5.25</v>
       </c>
       <c r="EA4" t="n">
-        <v>18.32</v>
+        <v>18</v>
       </c>
       <c r="EB4" t="n">
         <v>1.55</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.58</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="5">
@@ -2584,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D5" t="n">
         <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="G5" t="n">
-        <v>3.11</v>
+        <v>2.9</v>
       </c>
       <c r="H5" t="n">
-        <v>85.44</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="K5" t="n">
-        <v>5.33</v>
+        <v>5.1</v>
       </c>
       <c r="L5" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="M5" t="n">
-        <v>43.78</v>
+        <v>41.8</v>
       </c>
       <c r="N5" t="n">
-        <v>0.33</v>
+        <v>0.4</v>
       </c>
       <c r="O5" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="P5" t="n">
-        <v>10.89</v>
+        <v>11.1</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.22</v>
+        <v>13.1</v>
       </c>
       <c r="R5" t="n">
-        <v>7.56</v>
+        <v>7.4</v>
       </c>
       <c r="S5" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="T5" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="U5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49.78</v>
+        <v>49.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.78</v>
+        <v>11.8</v>
       </c>
       <c r="AA5" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.78</v>
+        <v>3.9</v>
       </c>
       <c r="AC5" t="n">
-        <v>21.56</v>
+        <v>20.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>1.9</v>
       </c>
       <c r="AF5" t="n">
         <v>0.1</v>
@@ -2755,70 +2759,70 @@
         <v>1.9</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.37</v>
+        <v>11.2</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.32</v>
+        <v>3.25</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="BK5" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.53</v>
+        <v>0.55</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="BP5" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.26</v>
+        <v>6.15</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BT5" t="n">
-        <v>78.95</v>
+        <v>75</v>
       </c>
       <c r="BU5" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BV5" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW5" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX5" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.63</v>
+        <v>3.61</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.7</v>
+        <v>3.69</v>
       </c>
       <c r="CC5" t="n">
         <v>3.48</v>
@@ -2830,28 +2834,28 @@
         <v>1.31</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.24</v>
+        <v>3.23</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI5" t="n">
         <v>2.31</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK5" t="n">
         <v>1.35</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="CN5" t="n">
         <v>2.18</v>
@@ -2860,34 +2864,34 @@
         <v>1.18</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX5" t="n">
         <v>1.46</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.6</v>
@@ -2899,52 +2903,52 @@
         <v>1.22</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.72</v>
+        <v>2.75</v>
       </c>
       <c r="DE5" t="n">
         <v>0.1</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.26</v>
+        <v>3.15</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.63</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.52</v>
+        <v>5.4</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.79</v>
+        <v>44.7</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DP5" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="DQ5" t="n">
         <v>12.1</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.210000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="DS5" t="n">
         <v>0.05</v>
@@ -2956,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.16</v>
+        <v>49.05</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.16</v>
+        <v>13.1</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.16</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.16</v>
+        <v>20.75</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
     </row>
     <row r="6">
@@ -2987,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D6" t="n">
         <v>9</v>
@@ -2999,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.4</v>
+        <v>1.55</v>
       </c>
       <c r="G6" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="H6" t="n">
-        <v>91.40000000000001</v>
+        <v>93.45</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="K6" t="n">
-        <v>3.7</v>
+        <v>3.91</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M6" t="n">
-        <v>34.6</v>
+        <v>34.27</v>
       </c>
       <c r="N6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="O6" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="P6" t="n">
-        <v>12.9</v>
+        <v>12.64</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.6</v>
+        <v>13.18</v>
       </c>
       <c r="R6" t="n">
-        <v>8.9</v>
+        <v>8.91</v>
       </c>
       <c r="S6" t="n">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="T6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="U6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>40.3</v>
+        <v>40.73</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.3</v>
+        <v>12.45</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.6</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.7</v>
+        <v>3.82</v>
       </c>
       <c r="AC6" t="n">
-        <v>21.6</v>
+        <v>22.27</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AF6" t="n">
         <v>0.11</v>
@@ -3158,70 +3162,70 @@
         <v>2.56</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.63</v>
+        <v>10.6</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.74</v>
+        <v>2.65</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.74</v>
+        <v>4.7</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.89</v>
+        <v>5.9</v>
       </c>
       <c r="BR6" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS6" t="n">
-        <v>84.20999999999999</v>
+        <v>80</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BU6" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BV6" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>57.89</v>
+        <v>55</v>
       </c>
       <c r="BY6" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.18</v>
+        <v>3.09</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.57</v>
+        <v>3.56</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CC6" t="n">
         <v>4.03</v>
@@ -3236,7 +3240,7 @@
         <v>2.53</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.07</v>
+        <v>3.05</v>
       </c>
       <c r="CH6" t="n">
         <v>1.48</v>
@@ -3254,7 +3258,7 @@
         <v>1.78</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN6" t="n">
         <v>2.08</v>
@@ -3263,10 +3267,10 @@
         <v>1.21</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CR6" t="n">
         <v>1.37</v>
@@ -3275,7 +3279,7 @@
         <v>2.67</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CU6" t="n">
         <v>1.51</v>
@@ -3293,7 +3297,7 @@
         <v>1.75</v>
       </c>
       <c r="CZ6" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DA6" t="n">
         <v>2.08</v>
@@ -3302,85 +3306,85 @@
         <v>1.24</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="DE6" t="n">
         <v>0.05</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="DH6" t="n">
-        <v>97.26000000000001</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="DI6" t="n">
         <v>0</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.69</v>
+        <v>4.75</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.26</v>
+        <v>0.25</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.95</v>
+        <v>40.45</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.95</v>
+        <v>12.8</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.74</v>
+        <v>13.5</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.1</v>
+        <v>8.15</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.21</v>
+        <v>44.25</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.79</v>
+        <v>12.85</v>
       </c>
       <c r="DY6" t="n">
         <v>9</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.79</v>
+        <v>3.85</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.16</v>
+        <v>21.55</v>
       </c>
       <c r="EB6" t="n">
         <v>1.38</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.37</v>
+        <v>2.45</v>
       </c>
     </row>
     <row r="7">
@@ -3390,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="n">
         <v>9</v>
       </c>
       <c r="D7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E7" t="n">
         <v>0.11</v>
@@ -3480,139 +3484,139 @@
         <v>1.56</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AI7" t="n">
-        <v>93.5</v>
+        <v>95.36</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.5</v>
+        <v>6.09</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN7" t="n">
-        <v>43.9</v>
+        <v>46</v>
       </c>
       <c r="AO7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>2.91</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>10.91</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>14.91</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>7.18</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>53.73</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>15.09</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>9.73</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>22</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="BF7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BH7" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="BI7" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="BJ7" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BK7" t="n">
         <v>0.7</v>
       </c>
-      <c r="AP7" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>52.8</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>14.8</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC7" t="n">
+      <c r="BL7" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BQ7" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BR7" t="n">
+        <v>95</v>
+      </c>
+      <c r="BS7" t="n">
+        <v>75</v>
+      </c>
+      <c r="BT7" t="n">
+        <v>50</v>
+      </c>
+      <c r="BU7" t="n">
+        <v>40</v>
+      </c>
+      <c r="BV7" t="n">
+        <v>20</v>
+      </c>
+      <c r="BW7" t="n">
         <v>5</v>
       </c>
-      <c r="BD7" t="n">
-        <v>22.1</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BH7" t="n">
-        <v>11.05</v>
-      </c>
-      <c r="BI7" t="n">
-        <v>2.79</v>
-      </c>
-      <c r="BJ7" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BK7" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BL7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BM7" t="n">
-        <v>0.58</v>
-      </c>
-      <c r="BN7" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="BO7" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="BP7" t="n">
-        <v>5.47</v>
-      </c>
-      <c r="BQ7" t="n">
-        <v>4.74</v>
-      </c>
-      <c r="BR7" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="BS7" t="n">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="BT7" t="n">
-        <v>47.37</v>
-      </c>
-      <c r="BU7" t="n">
-        <v>36.84</v>
-      </c>
-      <c r="BV7" t="n">
-        <v>21.05</v>
-      </c>
-      <c r="BW7" t="n">
-        <v>5.26</v>
-      </c>
       <c r="BX7" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>1.93</v>
@@ -3627,40 +3631,40 @@
         <v>3.74</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.64</v>
+        <v>2.61</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.33</v>
+        <v>2.34</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="CH7" t="n">
         <v>1.44</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.48</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CM7" t="n">
         <v>2.69</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.05</v>
+        <v>2.06</v>
       </c>
       <c r="CO7" t="n">
         <v>1.14</v>
@@ -3669,7 +3673,7 @@
         <v>1.57</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR7" t="n">
         <v>1.37</v>
@@ -3684,10 +3688,10 @@
         <v>1.53</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
@@ -3699,91 +3703,91 @@
         <v>2.61</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB7" t="n">
         <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="DE7" t="n">
         <v>0.1</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.47</v>
+        <v>1.55</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="DH7" t="n">
-        <v>98.09999999999999</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.05</v>
+        <v>2.1</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.37</v>
+        <v>6.15</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>50.31</v>
+        <v>51.15</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.16</v>
+        <v>3</v>
       </c>
       <c r="DP7" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.84</v>
+        <v>14.55</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.11</v>
+        <v>7.1</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>53.69</v>
+        <v>54.15</v>
       </c>
       <c r="DW7" t="n">
         <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.37</v>
+        <v>15.5</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.26</v>
+        <v>10.2</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.95</v>
+        <v>22.85</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="8">
@@ -3793,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D8" t="n">
         <v>9</v>
@@ -3805,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="G8" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="H8" t="n">
-        <v>88</v>
+        <v>91.45</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.2</v>
+        <v>-0.18</v>
       </c>
       <c r="J8" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>4.18</v>
       </c>
       <c r="L8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M8" t="n">
-        <v>48.3</v>
+        <v>50.64</v>
       </c>
       <c r="N8" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="O8" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="P8" t="n">
-        <v>13.3</v>
+        <v>13</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.2</v>
+        <v>11.27</v>
       </c>
       <c r="R8" t="n">
-        <v>6.7</v>
+        <v>6.36</v>
       </c>
       <c r="S8" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="T8" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3859,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>50.4</v>
+        <v>51.55</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.4</v>
+        <v>12</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.9</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.9</v>
+        <v>19.82</v>
       </c>
       <c r="AD8" t="n">
         <v>1.38</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="AF8" t="n">
         <v>0.11</v>
@@ -3964,70 +3968,70 @@
         <v>2.56</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.84</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.89</v>
+        <v>0.95</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.79</v>
+        <v>3.8</v>
       </c>
       <c r="BQ8" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>95</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>70</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>55</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>10</v>
+      </c>
+      <c r="BW8" t="n">
         <v>5</v>
       </c>
-      <c r="BR8" t="n">
-        <v>94.73999999999999</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>68.42</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>52.63</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>10.53</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>5.26</v>
-      </c>
       <c r="BX8" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.34</v>
+        <v>2.39</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.43</v>
+        <v>2.47</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.79</v>
+        <v>3.78</v>
       </c>
       <c r="CC8" t="n">
         <v>3.59</v>
@@ -4039,10 +4043,10 @@
         <v>1.3</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CH8" t="n">
         <v>1.51</v>
@@ -4057,13 +4061,13 @@
         <v>1.4</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.06</v>
+        <v>2.05</v>
       </c>
       <c r="CO8" t="n">
         <v>1.19</v>
@@ -4072,16 +4076,16 @@
         <v>1.65</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.56</v>
+        <v>2.57</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="CU8" t="n">
         <v>1.54</v>
@@ -4102,58 +4106,58 @@
         <v>2.49</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB8" t="n">
         <v>1.21</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="DE8" t="n">
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.52</v>
+        <v>1.55</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.31</v>
+        <v>2.4</v>
       </c>
       <c r="DH8" t="n">
-        <v>91.37</v>
+        <v>93.09999999999999</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.9</v>
+        <v>2.85</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM8" t="n">
-        <v>45.21</v>
+        <v>46.65</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.37</v>
+        <v>1.3</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.52</v>
+        <v>1.6</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.84</v>
+        <v>12.7</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.63</v>
+        <v>11.65</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.95</v>
+        <v>7.7</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4165,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.11</v>
+        <v>48.85</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.58</v>
+        <v>12.35</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.050000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.53</v>
+        <v>3.6</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.21</v>
+        <v>20.15</v>
       </c>
       <c r="EB8" t="n">
         <v>1.37</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="9">
@@ -4196,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="n">
         <v>9</v>
       </c>
       <c r="D9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E9" t="n">
         <v>0.22</v>
@@ -4289,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>2</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>72.55</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>33.36</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>13.55</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>11.64</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>45.91</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.64</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>22.27</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.3</v>
       </c>
-      <c r="AH9" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>72.40000000000001</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>34</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>13.2</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>47.4</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>12.4</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>22.4</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.37</v>
-      </c>
       <c r="BF9" t="n">
-        <v>2.7</v>
+        <v>2.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.26</v>
+        <v>10.15</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.63</v>
+        <v>0.6</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.79</v>
+        <v>0.75</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.05</v>
+        <v>1.1</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.37</v>
+        <v>2.4</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.42</v>
+        <v>1.35</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.47</v>
+        <v>4.45</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.79</v>
+        <v>5.7</v>
       </c>
       <c r="BR9" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS9" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT9" t="n">
-        <v>73.68000000000001</v>
+        <v>75</v>
       </c>
       <c r="BU9" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BV9" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BW9" t="n">
-        <v>21.05</v>
+        <v>20</v>
       </c>
       <c r="BX9" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY9" t="n">
         <v>2.8</v>
@@ -4427,22 +4431,22 @@
         <v>3.2</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.13</v>
+        <v>4.16</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.95</v>
+        <v>4.96</v>
       </c>
       <c r="CE9" t="n">
         <v>1.29</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CG9" t="n">
         <v>3.36</v>
@@ -4451,16 +4455,16 @@
         <v>1.55</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK9" t="n">
         <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM9" t="n">
         <v>2.79</v>
@@ -4475,37 +4479,37 @@
         <v>1.61</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CU9" t="n">
         <v>1.58</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CX9" t="n">
         <v>1.47</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.58</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DB9" t="n">
         <v>1.2</v>
@@ -4514,82 +4518,82 @@
         <v>1.65</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DE9" t="n">
         <v>0.1</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.47</v>
+        <v>77.3</v>
       </c>
       <c r="DI9" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.26</v>
+        <v>4.15</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.95</v>
+        <v>33.6</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.21</v>
+        <v>1.15</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.79</v>
+        <v>12.05</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13</v>
+        <v>12.95</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.84</v>
+        <v>8.85</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.79</v>
+        <v>45.05</v>
       </c>
       <c r="DW9" t="n">
         <v>0.1</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.47</v>
+        <v>11.15</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.37</v>
+        <v>7.15</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="EA9" t="n">
         <v>21.05</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.26</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="10">
@@ -5002,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D11" t="n">
         <v>9</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="F11" t="n">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="G11" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="H11" t="n">
-        <v>98.09999999999999</v>
+        <v>95.18000000000001</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J11" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="K11" t="n">
-        <v>5.2</v>
+        <v>5.09</v>
       </c>
       <c r="L11" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M11" t="n">
-        <v>44.9</v>
+        <v>44.55</v>
       </c>
       <c r="N11" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O11" t="n">
-        <v>2.4</v>
+        <v>2.55</v>
       </c>
       <c r="P11" t="n">
-        <v>12.7</v>
+        <v>12.36</v>
       </c>
       <c r="Q11" t="n">
-        <v>9.800000000000001</v>
+        <v>10.27</v>
       </c>
       <c r="R11" t="n">
-        <v>9.4</v>
+        <v>9.18</v>
       </c>
       <c r="S11" t="n">
-        <v>0.8</v>
+        <v>0.91</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="U11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.6</v>
+        <v>12.64</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.1</v>
+        <v>8</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.5</v>
+        <v>4.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>20.3</v>
+        <v>19.55</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AF11" t="n">
         <v>0.11</v>
@@ -5173,70 +5177,70 @@
         <v>3</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.11</v>
+        <v>10.1</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.16</v>
+        <v>2.25</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.42</v>
+        <v>0.45</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="BO11" t="n">
-        <v>0.95</v>
+        <v>1.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.58</v>
+        <v>4.65</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.84</v>
+        <v>4.8</v>
       </c>
       <c r="BR11" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BS11" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BT11" t="n">
-        <v>36.84</v>
+        <v>40</v>
       </c>
       <c r="BU11" t="n">
-        <v>15.79</v>
+        <v>20</v>
       </c>
       <c r="BV11" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW11" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX11" t="n">
-        <v>31.58</v>
+        <v>35</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="BZ11" t="n">
-        <v>1.99</v>
+        <v>2.01</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CC11" t="n">
         <v>2.66</v>
@@ -5245,52 +5249,52 @@
         <v>2.98</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.59</v>
+        <v>1.61</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CR11" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CS11" t="n">
         <v>2.51</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CU11" t="n">
         <v>1.56</v>
@@ -5302,19 +5306,19 @@
         <v>1.6</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CY11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB11" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC11" t="n">
         <v>1.68</v>
@@ -5323,46 +5327,46 @@
         <v>2.65</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.84</v>
+        <v>1.8</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.26</v>
+        <v>2.15</v>
       </c>
       <c r="DH11" t="n">
-        <v>95.95</v>
+        <v>94.45</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.79</v>
+        <v>2.75</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.58</v>
+        <v>4.55</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.69</v>
+        <v>46.4</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.9</v>
+        <v>0.85</v>
       </c>
       <c r="DO11" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.58</v>
+        <v>13.35</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.42</v>
+        <v>11.6</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.949999999999999</v>
+        <v>8.85</v>
       </c>
       <c r="DS11" t="n">
         <v>0.1</v>
@@ -5374,28 +5378,28 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.05</v>
+        <v>48.8</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.63</v>
+        <v>12.65</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.32</v>
+        <v>8.25</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.32</v>
+        <v>4.4</v>
       </c>
       <c r="EA11" t="n">
-        <v>21.42</v>
+        <v>20.95</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="12">
@@ -5405,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D12" t="n">
         <v>10</v>
@@ -5417,49 +5421,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="G12" t="n">
         <v>3</v>
       </c>
       <c r="H12" t="n">
-        <v>85.22</v>
+        <v>90.40000000000001</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="K12" t="n">
-        <v>5.22</v>
+        <v>5.3</v>
       </c>
       <c r="L12" t="n">
-        <v>0.67</v>
+        <v>0.6</v>
       </c>
       <c r="M12" t="n">
-        <v>38.33</v>
+        <v>41.6</v>
       </c>
       <c r="N12" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="O12" t="n">
-        <v>2.22</v>
+        <v>2.3</v>
       </c>
       <c r="P12" t="n">
-        <v>12</v>
+        <v>12.1</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.67</v>
+        <v>14.9</v>
       </c>
       <c r="R12" t="n">
-        <v>8.44</v>
+        <v>7.6</v>
       </c>
       <c r="S12" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="T12" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="U12" t="n">
         <v>0</v>
@@ -5471,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>50.78</v>
+        <v>52.6</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.89</v>
+        <v>12.9</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.56</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.33</v>
+        <v>4.2</v>
       </c>
       <c r="AC12" t="n">
-        <v>18.44</v>
+        <v>19.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.67</v>
+        <v>1.8</v>
       </c>
       <c r="AF12" t="n">
         <v>0.1</v>
@@ -5576,70 +5580,70 @@
         <v>3.4</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.32</v>
+        <v>10.2</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.53</v>
+        <v>0.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.21</v>
+        <v>1.3</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.11</v>
+        <v>4.1</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.16</v>
+        <v>6.05</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT12" t="n">
-        <v>42.11</v>
+        <v>45</v>
       </c>
       <c r="BU12" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV12" t="n">
-        <v>10.53</v>
+        <v>10</v>
       </c>
       <c r="BW12" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX12" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY12" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="BZ12" t="n">
         <v>2.22</v>
       </c>
-      <c r="BZ12" t="n">
-        <v>2.28</v>
-      </c>
       <c r="CA12" t="n">
-        <v>3.55</v>
+        <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.61</v>
+        <v>3.63</v>
       </c>
       <c r="CC12" t="n">
         <v>2.83</v>
@@ -5654,19 +5658,19 @@
         <v>2.51</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CH12" t="n">
         <v>1.49</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL12" t="n">
         <v>1.69</v>
@@ -5690,7 +5694,7 @@
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CT12" t="n">
         <v>3.28</v>
@@ -5699,22 +5703,22 @@
         <v>1.52</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX12" t="n">
         <v>1.48</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DB12" t="n">
         <v>1.23</v>
@@ -5732,73 +5736,73 @@
         <v>1.95</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="DH12" t="n">
-        <v>81.09999999999999</v>
+        <v>83.90000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.63</v>
+        <v>4.7</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM12" t="n">
-        <v>35.95</v>
+        <v>37.7</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.79</v>
+        <v>13.75</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.53</v>
+        <v>13.7</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.949999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>49.58</v>
+        <v>50.55</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.21</v>
+        <v>12.25</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.42</v>
+        <v>8.5</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.79</v>
+        <v>3.75</v>
       </c>
       <c r="EA12" t="n">
-        <v>18.79</v>
+        <v>19.2</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
     </row>
     <row r="13">
@@ -5808,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D13" t="n">
         <v>9</v>
       </c>
       <c r="E13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="G13" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="H13" t="n">
-        <v>106.1</v>
+        <v>103.36</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J13" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="K13" t="n">
-        <v>6</v>
+        <v>5.64</v>
       </c>
       <c r="L13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="M13" t="n">
-        <v>49.8</v>
+        <v>48.27</v>
       </c>
       <c r="N13" t="n">
-        <v>1.1</v>
+        <v>1.27</v>
       </c>
       <c r="O13" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P13" t="n">
-        <v>11.7</v>
+        <v>11.55</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.4</v>
+        <v>13.55</v>
       </c>
       <c r="R13" t="n">
-        <v>8.800000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="S13" t="n">
-        <v>1.2</v>
+        <v>1.36</v>
       </c>
       <c r="T13" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V13" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>50.5</v>
+        <v>49.27</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>16.5</v>
+        <v>15.45</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.800000000000001</v>
+        <v>9.27</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.7</v>
+        <v>6.18</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.5</v>
+        <v>22.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.87</v>
+        <v>1.76</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5979,67 +5983,67 @@
         <v>2.67</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BH13" t="n">
-        <v>10</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.63</v>
+        <v>0.65</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.26</v>
+        <v>1.2</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="BN13" t="n">
         <v>2.05</v>
       </c>
       <c r="BO13" t="n">
-        <v>1</v>
+        <v>1.05</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.63</v>
+        <v>4.5</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.68</v>
+        <v>4.55</v>
       </c>
       <c r="BR13" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.95</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU13" t="n">
-        <v>47.37</v>
+        <v>50</v>
       </c>
       <c r="BV13" t="n">
-        <v>26.32</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>63.16</v>
+        <v>65</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.41</v>
+        <v>2.45</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB13" t="n">
         <v>3.64</v>
@@ -6054,16 +6058,16 @@
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CH13" t="n">
         <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.56</v>
@@ -6072,13 +6076,13 @@
         <v>1.36</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CO13" t="n">
         <v>1.19</v>
@@ -6087,7 +6091,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CR13" t="n">
         <v>1.36</v>
@@ -6102,7 +6106,7 @@
         <v>1.54</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CW13" t="n">
         <v>1.57</v>
@@ -6129,79 +6133,79 @@
         <v>2.7</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.32</v>
+        <v>2.2</v>
       </c>
       <c r="DH13" t="n">
-        <v>98.09999999999999</v>
+        <v>97</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="DK13" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>42.45</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>13.95</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>47.05</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>13.2</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="DZ13" t="n">
         <v>5.1</v>
       </c>
-      <c r="DL13" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="DM13" t="n">
-        <v>42.95</v>
-      </c>
-      <c r="DN13" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="DO13" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="DP13" t="n">
-        <v>12.32</v>
-      </c>
-      <c r="DQ13" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="DR13" t="n">
-        <v>9.369999999999999</v>
-      </c>
-      <c r="DS13" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DT13" t="n">
-        <v>0.16</v>
-      </c>
-      <c r="DU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV13" t="n">
-        <v>47.58</v>
-      </c>
-      <c r="DW13" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="DX13" t="n">
-        <v>13.63</v>
-      </c>
-      <c r="DY13" t="n">
-        <v>8.32</v>
-      </c>
-      <c r="DZ13" t="n">
-        <v>5.32</v>
-      </c>
       <c r="EA13" t="n">
-        <v>22.11</v>
+        <v>21.75</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="14">
@@ -6211,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="n">
         <v>9</v>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E14" t="n">
         <v>0.22</v>
@@ -6301,139 +6305,139 @@
         <v>3.22</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.2</v>
+        <v>1.27</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.1</v>
+        <v>3.09</v>
       </c>
       <c r="AI14" t="n">
+        <v>89.73</v>
+      </c>
+      <c r="AJ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AL14" t="n">
+        <v>5.45</v>
+      </c>
+      <c r="AM14" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>41.55</v>
+      </c>
+      <c r="AO14" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8.73</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>48.82</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>12.55</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9.18</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>19.09</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>5.05</v>
+      </c>
+      <c r="BR14" t="n">
         <v>90</v>
       </c>
-      <c r="AJ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AL14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AM14" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>40.9</v>
-      </c>
-      <c r="AO14" t="n">
-        <v>0.7</v>
-      </c>
-      <c r="AP14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>9.1</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>9</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>48.2</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>12.9</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>18.6</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>10.42</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.37</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>1</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>2.21</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>4.63</v>
-      </c>
-      <c r="BQ14" t="n">
+      <c r="BS14" t="n">
+        <v>80</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>70</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>50</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>30</v>
+      </c>
+      <c r="BW14" t="n">
         <v>5</v>
       </c>
-      <c r="BR14" t="n">
-        <v>89.47</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>84.20999999999999</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>73.68000000000001</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>52.63</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>31.58</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>5.26</v>
-      </c>
       <c r="BX14" t="n">
-        <v>52.63</v>
+        <v>50</v>
       </c>
       <c r="BY14" t="n">
         <v>2.56</v>
@@ -6442,132 +6446,136 @@
         <v>2.74</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.9</v>
+        <v>3.87</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.78</v>
+        <v>3.73</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.1</v>
+        <v>4.05</v>
       </c>
       <c r="CE14" t="n">
         <v>1.29</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="CH14" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.54</v>
       </c>
       <c r="CK14" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO14" t="n">
         <v>1.16</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.31</v>
+        <v>3.3</v>
       </c>
       <c r="CU14" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CW14" t="n">
         <v>1.57</v>
       </c>
-      <c r="CX14" t="inlineStr"/>
+      <c r="CX14" t="n">
+        <v>1.46</v>
+      </c>
       <c r="CY14" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="CZ14" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="DA14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="DB14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="DC14" t="n">
         <v>1.65</v>
       </c>
-      <c r="CZ14" t="inlineStr"/>
-      <c r="DA14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="DB14" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="DC14" t="n">
-        <v>1.64</v>
-      </c>
       <c r="DD14" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.63</v>
+        <v>1.65</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="DH14" t="n">
-        <v>83.09999999999999</v>
+        <v>83.3</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.63</v>
+        <v>2.75</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.16</v>
+        <v>5.1</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.32</v>
+        <v>41.65</v>
       </c>
       <c r="DN14" t="n">
-        <v>1</v>
+        <v>1.1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.32</v>
+        <v>2.25</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.68</v>
+        <v>12.5</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.84</v>
+        <v>10.8</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.789999999999999</v>
+        <v>8.65</v>
       </c>
       <c r="DS14" t="n">
         <v>0.05</v>
@@ -6579,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.11</v>
+        <v>47.5</v>
       </c>
       <c r="DW14" t="n">
         <v>0.1</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.27</v>
+        <v>12.1</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.95</v>
+        <v>8</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.32</v>
+        <v>4.1</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.47</v>
+        <v>17.8</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.53</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="15">
@@ -6622,7 +6630,7 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="G15" t="n">
         <v>2.8</v>
@@ -6634,7 +6642,7 @@
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="K15" t="n">
         <v>5.7</v>
@@ -6685,19 +6693,19 @@
         <v>16</v>
       </c>
       <c r="AA15" t="n">
-        <v>11</v>
+        <v>11.1</v>
       </c>
       <c r="AB15" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="AC15" t="n">
         <v>19.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6930,7 +6938,7 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="DG15" t="n">
         <v>2.95</v>
@@ -6942,7 +6950,7 @@
         <v>0.15</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="DK15" t="n">
         <v>5.75</v>
@@ -6987,19 +6995,19 @@
         <v>16.75</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.2</v>
+        <v>11.25</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.55</v>
+        <v>5.5</v>
       </c>
       <c r="EA15" t="n">
         <v>18.65</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
     </row>
     <row r="16">
@@ -7090,7 +7098,7 @@
         <v>5.09</v>
       </c>
       <c r="AC16" t="n">
-        <v>19.91</v>
+        <v>20</v>
       </c>
       <c r="AD16" t="n">
         <v>1.58</v>
@@ -7396,7 +7404,7 @@
         <v>4.85</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.5</v>
+        <v>20.55</v>
       </c>
       <c r="EB16" t="n">
         <v>1.54</v>
@@ -7412,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C17" t="n">
         <v>10</v>
       </c>
       <c r="D17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7502,139 +7510,139 @@
         <v>1.8</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>99.22</v>
+        <v>98.2</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.11</v>
+        <v>-0.1</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>5.22</v>
+        <v>4.8</v>
       </c>
       <c r="AM17" t="n">
         <v>1</v>
       </c>
       <c r="AN17" t="n">
-        <v>43.44</v>
+        <v>42.1</v>
       </c>
       <c r="AO17" t="n">
-        <v>0.89</v>
+        <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.33</v>
+        <v>2.2</v>
       </c>
       <c r="AQ17" t="n">
-        <v>13</v>
+        <v>12.9</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.11</v>
+        <v>11</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.89</v>
+        <v>6.9</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.78</v>
+        <v>0.9</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>54.56</v>
+        <v>52.8</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="BA17" t="n">
-        <v>15.22</v>
+        <v>14.7</v>
       </c>
       <c r="BB17" t="n">
-        <v>10.11</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BC17" t="n">
-        <v>5.11</v>
+        <v>5</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.67</v>
+        <v>21.1</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.63</v>
+        <v>1.58</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.58</v>
+        <v>10.45</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.95</v>
+        <v>1</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.58</v>
+        <v>0.55</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.79</v>
+        <v>4.75</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.74</v>
+        <v>5.65</v>
       </c>
       <c r="BR17" t="n">
-        <v>94.73999999999999</v>
+        <v>95</v>
       </c>
       <c r="BS17" t="n">
-        <v>84.20999999999999</v>
+        <v>85</v>
       </c>
       <c r="BT17" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BU17" t="n">
-        <v>15.79</v>
+        <v>15</v>
       </c>
       <c r="BV17" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BW17" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BX17" t="n">
-        <v>57.89</v>
+        <v>60</v>
       </c>
       <c r="BY17" t="n">
         <v>1.89</v>
@@ -7643,31 +7651,31 @@
         <v>1.97</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.19</v>
+        <v>2.21</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="CE17" t="n">
         <v>1.31</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG17" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CH17" t="n">
         <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.6</v>
@@ -7676,13 +7684,13 @@
         <v>1.37</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CO17" t="n">
         <v>1.2</v>
@@ -7694,22 +7702,22 @@
         <v>2.66</v>
       </c>
       <c r="CR17" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU17" t="n">
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX17" t="n">
         <v>1.46</v>
@@ -7730,79 +7738,79 @@
         <v>1.72</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.1</v>
+        <v>0.15</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.32</v>
+        <v>3.15</v>
       </c>
       <c r="DH17" t="n">
-        <v>100.79</v>
+        <v>100.2</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.31</v>
+        <v>2.35</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.84</v>
+        <v>5.6</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.1</v>
+        <v>49.1</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.79</v>
+        <v>0.85</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.47</v>
+        <v>2.4</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.95</v>
+        <v>12.9</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.47</v>
+        <v>10.45</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.21</v>
+        <v>7.2</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>55.37</v>
+        <v>54.45</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.11</v>
+        <v>0.15</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.63</v>
+        <v>16.3</v>
       </c>
       <c r="DY17" t="n">
-        <v>11.05</v>
+        <v>10.8</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.58</v>
+        <v>5.5</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.16</v>
+        <v>21.35</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="EC17" t="n">
         <v>2.1</v>
@@ -8218,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C19" t="n">
         <v>9</v>
       </c>
       <c r="D19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E19" t="n">
         <v>0.22</v>
@@ -8308,130 +8316,130 @@
         <v>2.56</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AI19" t="n">
-        <v>101.9</v>
+        <v>105.18</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.7</v>
+        <v>2.45</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.4</v>
+        <v>4.36</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="AN19" t="n">
-        <v>43.3</v>
+        <v>43.73</v>
       </c>
       <c r="AO19" t="n">
-        <v>1.1</v>
+        <v>1</v>
       </c>
       <c r="AP19" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>6</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>42.73</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>11.55</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>22.73</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="BG19" t="n">
         <v>1.9</v>
       </c>
-      <c r="AQ19" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>11.2</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>6.3</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>0.6</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AV19" t="n">
+      <c r="BH19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="BK19" t="n">
         <v>0.4</v>
       </c>
-      <c r="AW19" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>40.8</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="BC19" t="n">
+      <c r="BL19" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BN19" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BO19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="BP19" t="n">
         <v>4</v>
       </c>
-      <c r="BD19" t="n">
-        <v>23.1</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>9.68</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.42</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="BO19" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BP19" t="n">
-        <v>4.05</v>
-      </c>
       <c r="BQ19" t="n">
-        <v>5.58</v>
+        <v>5.45</v>
       </c>
       <c r="BR19" t="n">
-        <v>89.47</v>
+        <v>90</v>
       </c>
       <c r="BS19" t="n">
-        <v>52.63</v>
+        <v>55</v>
       </c>
       <c r="BT19" t="n">
-        <v>42.11</v>
+        <v>40</v>
       </c>
       <c r="BU19" t="n">
-        <v>5.26</v>
+        <v>5</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8440,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>36.84</v>
+        <v>35</v>
       </c>
       <c r="BY19" t="n">
         <v>2.28</v>
@@ -8449,40 +8457,40 @@
         <v>2.29</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CB19" t="n">
         <v>3.52</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="CE19" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CF19" t="n">
         <v>2.66</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.97</v>
+        <v>2.95</v>
       </c>
       <c r="CH19" t="n">
         <v>1.43</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CK19" t="n">
         <v>1.43</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="CM19" t="n">
         <v>2.62</v>
@@ -8494,19 +8502,19 @@
         <v>1.24</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.95</v>
+        <v>2.99</v>
       </c>
       <c r="CR19" t="n">
         <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CU19" t="n">
         <v>1.47</v>
@@ -8515,16 +8523,16 @@
         <v>2.26</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CX19" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CY19" t="n">
         <v>1.81</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="DA19" t="n">
         <v>2.01</v>
@@ -8539,79 +8547,79 @@
         <v>3.08</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.84</v>
+        <v>1.75</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.89</v>
+        <v>2.85</v>
       </c>
       <c r="DH19" t="n">
-        <v>102.16</v>
+        <v>103.95</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.69</v>
+        <v>2.55</v>
       </c>
       <c r="DK19" t="n">
-        <v>5</v>
+        <v>4.95</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM19" t="n">
-        <v>46.84</v>
+        <v>46.9</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.84</v>
+        <v>0.8</v>
       </c>
       <c r="DO19" t="n">
         <v>2.1</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.68</v>
+        <v>13.65</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.05</v>
+        <v>12.2</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.68</v>
+        <v>5.55</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>42.58</v>
+        <v>43.55</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.42</v>
+        <v>12.4</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.109999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.32</v>
+        <v>4.2</v>
       </c>
       <c r="EA19" t="n">
-        <v>22</v>
+        <v>21.85</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.63</v>
+        <v>2.5</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -3057,7 +3057,7 @@
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>40.73</v>
+        <v>40.64</v>
       </c>
       <c r="Y6" t="n">
         <v>0.27</v>
@@ -3363,7 +3363,7 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.25</v>
+        <v>44.2</v>
       </c>
       <c r="DW6" t="n">
         <v>0.35</v>
@@ -4347,7 +4347,7 @@
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>45.91</v>
+        <v>46</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
@@ -4572,7 +4572,7 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.05</v>
+        <v>45.1</v>
       </c>
       <c r="DW9" t="n">
         <v>0.1</v>
@@ -5475,16 +5475,16 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.6</v>
+        <v>52.5</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.9</v>
+        <v>13</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AB12" t="n">
         <v>4.2</v>
@@ -5493,7 +5493,7 @@
         <v>19.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="AE12" t="n">
         <v>1.8</v>
@@ -5781,16 +5781,16 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.55</v>
+        <v>50.5</v>
       </c>
       <c r="DW12" t="n">
         <v>0.15</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.25</v>
+        <v>12.3</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.5</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ12" t="n">
         <v>3.75</v>
@@ -5799,7 +5799,7 @@
         <v>19.2</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
         <v>2.6</v>
@@ -5884,10 +5884,10 @@
         <v>0.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.45</v>
+        <v>15.55</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.27</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AB13" t="n">
         <v>6.18</v>
@@ -5896,7 +5896,7 @@
         <v>22.73</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="AE13" t="n">
         <v>2.82</v>
@@ -6190,10 +6190,10 @@
         <v>0.1</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.2</v>
+        <v>13.25</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.1</v>
+        <v>8.15</v>
       </c>
       <c r="DZ13" t="n">
         <v>5.1</v>
@@ -6202,7 +6202,7 @@
         <v>21.75</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="EC13" t="n">
         <v>2.75</v>
@@ -6362,7 +6362,7 @@
         <v>0</v>
       </c>
       <c r="AY14" t="n">
-        <v>48.82</v>
+        <v>48.91</v>
       </c>
       <c r="AZ14" t="n">
         <v>0</v>
@@ -6587,7 +6587,7 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.5</v>
+        <v>47.55</v>
       </c>
       <c r="DW14" t="n">
         <v>0.1</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -2332,16 +2332,16 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>49.5</v>
+        <v>49.6</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.6</v>
+        <v>12.5</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC4" t="n">
         <v>4.3</v>
@@ -2350,7 +2350,7 @@
         <v>17.9</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="BF4" t="n">
         <v>1.5</v>
@@ -2557,16 +2557,16 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.2</v>
+        <v>49.25</v>
       </c>
       <c r="DW4" t="n">
         <v>0.05</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.85</v>
+        <v>13.8</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.6</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ4" t="n">
         <v>5.25</v>
@@ -2575,7 +2575,7 @@
         <v>18</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="EC4" t="n">
         <v>1.7</v>
@@ -3547,19 +3547,19 @@
         <v>0.09</v>
       </c>
       <c r="BA7" t="n">
-        <v>15.09</v>
+        <v>15</v>
       </c>
       <c r="BB7" t="n">
         <v>9.73</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.36</v>
+        <v>5.27</v>
       </c>
       <c r="BD7" t="n">
         <v>22</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="BF7" t="n">
         <v>2.45</v>
@@ -3772,19 +3772,19 @@
         <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.5</v>
+        <v>15.45</v>
       </c>
       <c r="DY7" t="n">
         <v>10.2</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="EA7" t="n">
         <v>22.85</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="EC7" t="n">
         <v>2.05</v>
@@ -3869,10 +3869,10 @@
         <v>0.09</v>
       </c>
       <c r="Z8" t="n">
-        <v>12</v>
+        <v>12.09</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.359999999999999</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="AB8" t="n">
         <v>3.64</v>
@@ -3881,7 +3881,7 @@
         <v>19.82</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="AE8" t="n">
         <v>2.82</v>
@@ -4175,10 +4175,10 @@
         <v>0.15</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.35</v>
+        <v>12.4</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.75</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.6</v>
@@ -4187,7 +4187,7 @@
         <v>20.15</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC8" t="n">
         <v>2.7</v>
@@ -5072,16 +5072,16 @@
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49</v>
+        <v>48.91</v>
       </c>
       <c r="Y11" t="n">
         <v>0.27</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.64</v>
+        <v>12.73</v>
       </c>
       <c r="AA11" t="n">
-        <v>8</v>
+        <v>8.09</v>
       </c>
       <c r="AB11" t="n">
         <v>4.64</v>
@@ -5378,16 +5378,16 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.8</v>
+        <v>48.75</v>
       </c>
       <c r="DW11" t="n">
         <v>0.15</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.65</v>
+        <v>12.7</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.25</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ11" t="n">
         <v>4.4</v>
@@ -5884,10 +5884,10 @@
         <v>0.09</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.55</v>
+        <v>15.64</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.359999999999999</v>
+        <v>9.449999999999999</v>
       </c>
       <c r="AB13" t="n">
         <v>6.18</v>
@@ -6190,10 +6190,10 @@
         <v>0.1</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.25</v>
+        <v>13.3</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.15</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ13" t="n">
         <v>5.1</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="n">
         <v>10</v>
       </c>
       <c r="D3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E3" t="n">
         <v>0.1</v>
@@ -1872,139 +1872,139 @@
         <v>3.3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AI3" t="n">
-        <v>83.8</v>
+        <v>83.81999999999999</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.8</v>
+        <v>5.82</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AN3" t="n">
-        <v>40.3</v>
+        <v>39.09</v>
       </c>
       <c r="AO3" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.5</v>
+        <v>12.82</v>
       </c>
       <c r="AR3" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.6</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>43</v>
+        <v>44.55</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.7</v>
+        <v>12</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.5</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="BD3" t="n">
-        <v>22.9</v>
+        <v>23.18</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.95</v>
+        <v>11.81</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.9</v>
+        <v>5.81</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT3" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BU3" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW3" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX3" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY3" t="n">
         <v>2.19</v>
@@ -2013,31 +2013,31 @@
         <v>2.3</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.62</v>
+        <v>3.6</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.7</v>
+        <v>3.68</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.07</v>
+        <v>3.01</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.39</v>
+        <v>3.34</v>
       </c>
       <c r="CE3" t="n">
         <v>1.3</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CH3" t="n">
         <v>1.52</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.56</v>
@@ -2046,10 +2046,10 @@
         <v>1.32</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CM3" t="n">
-        <v>3.02</v>
+        <v>3.01</v>
       </c>
       <c r="CN3" t="n">
         <v>2.28</v>
@@ -2058,25 +2058,25 @@
         <v>1.19</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ3" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="CS3" t="n">
         <v>2.6</v>
       </c>
-      <c r="CR3" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>2.58</v>
-      </c>
       <c r="CT3" t="n">
-        <v>3.25</v>
+        <v>3.22</v>
       </c>
       <c r="CU3" t="n">
         <v>1.53</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CW3" t="n">
         <v>1.59</v>
@@ -2103,79 +2103,79 @@
         <v>2.71</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DG3" t="n">
         <v>2.95</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.09999999999999</v>
+        <v>93.62</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.85</v>
+        <v>5.86</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.55</v>
+        <v>0.53</v>
       </c>
       <c r="DM3" t="n">
-        <v>47.3</v>
+        <v>46.33</v>
       </c>
       <c r="DN3" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.6</v>
+        <v>13.72</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.4</v>
+        <v>9.67</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.949999999999999</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>44.8</v>
+        <v>45.53</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.2</v>
+        <v>14.24</v>
       </c>
       <c r="DY3" t="n">
-        <v>10</v>
+        <v>9.9</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.2</v>
+        <v>4.34</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.2</v>
+        <v>22.38</v>
       </c>
       <c r="EB3" t="n">
         <v>1.54</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D4" t="n">
         <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="F4" t="n">
-        <v>1.5</v>
+        <v>1.36</v>
       </c>
       <c r="G4" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="H4" t="n">
-        <v>86.09999999999999</v>
+        <v>87.27</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="K4" t="n">
-        <v>5.3</v>
+        <v>5.36</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="M4" t="n">
-        <v>47.6</v>
+        <v>46.36</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.55</v>
       </c>
       <c r="O4" t="n">
-        <v>2.8</v>
+        <v>2.91</v>
       </c>
       <c r="P4" t="n">
-        <v>11.6</v>
+        <v>10.91</v>
       </c>
       <c r="Q4" t="n">
-        <v>11.7</v>
+        <v>12.09</v>
       </c>
       <c r="R4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="S4" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="T4" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.9</v>
+        <v>48.73</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.1</v>
+        <v>15.09</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.9</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.2</v>
+        <v>6.45</v>
       </c>
       <c r="AC4" t="n">
-        <v>18.1</v>
+        <v>17.45</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AF4" t="n">
         <v>0.3</v>
@@ -2356,70 +2356,70 @@
         <v>1.5</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.3</v>
+        <v>10.38</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.7</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
         <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.1</v>
+        <v>5.24</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.2</v>
+        <v>5.14</v>
       </c>
       <c r="BR4" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT4" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU4" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BV4" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW4" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX4" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BY4" t="n">
         <v>1.84</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.79</v>
+        <v>3.77</v>
       </c>
       <c r="CC4" t="n">
         <v>2.95</v>
@@ -2434,7 +2434,7 @@
         <v>2.39</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH4" t="n">
         <v>1.53</v>
@@ -2464,13 +2464,13 @@
         <v>1.63</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CT4" t="n">
         <v>3.3</v>
@@ -2506,79 +2506,79 @@
         <v>2.67</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.25</v>
+        <v>0.28</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.35</v>
+        <v>1.28</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DH4" t="n">
-        <v>86.95</v>
+        <v>87.52</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.9</v>
+        <v>4.95</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.8</v>
+        <v>41.43</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.4</v>
+        <v>0.43</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.75</v>
+        <v>2.81</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.95</v>
+        <v>11.57</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.35</v>
+        <v>11.57</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.5</v>
+        <v>8.57</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.25</v>
+        <v>49.14</v>
       </c>
       <c r="DW4" t="n">
         <v>0.05</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.8</v>
+        <v>13.86</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.550000000000001</v>
+        <v>8.43</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.25</v>
+        <v>5.43</v>
       </c>
       <c r="EA4" t="n">
-        <v>18</v>
+        <v>17.66</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="n">
         <v>10</v>
       </c>
       <c r="D5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E5" t="n">
         <v>0.1</v>
@@ -2678,52 +2678,52 @@
         <v>1.9</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.4</v>
+        <v>3.18</v>
       </c>
       <c r="AI5" t="n">
-        <v>97.2</v>
+        <v>97.45</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.7</v>
+        <v>5.27</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.6</v>
+        <v>47.55</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.8</v>
+        <v>0.82</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.3</v>
+        <v>2.09</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.1</v>
+        <v>11.45</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.800000000000001</v>
+        <v>8.82</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.6</v>
+        <v>49.27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA5" t="n">
-        <v>14.4</v>
+        <v>13.91</v>
       </c>
       <c r="BB5" t="n">
-        <v>10.2</v>
+        <v>9.91</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="BD5" t="n">
-        <v>20.8</v>
+        <v>22.36</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.2</v>
+        <v>11.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.25</v>
+        <v>3.29</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BK5" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.35</v>
+        <v>1.48</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.9</v>
+        <v>1.81</v>
       </c>
       <c r="BP5" t="n">
-        <v>5</v>
+        <v>4.86</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
       <c r="BR5" t="n">
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BT5" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BU5" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV5" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BW5" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX5" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BY5" t="n">
         <v>2.49</v>
@@ -2819,40 +2819,40 @@
         <v>2.56</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.61</v>
+        <v>3.62</v>
       </c>
       <c r="CB5" t="n">
         <v>3.69</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.48</v>
+        <v>3.6</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.84</v>
+        <v>3.9</v>
       </c>
       <c r="CE5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CH5" t="n">
         <v>1.51</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.31</v>
+        <v>2.28</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CK5" t="n">
         <v>1.35</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM5" t="n">
         <v>2.88</v>
@@ -2861,13 +2861,13 @@
         <v>2.18</v>
       </c>
       <c r="CO5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.64</v>
+        <v>2.69</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
@@ -2882,10 +2882,10 @@
         <v>1.53</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX5" t="n">
         <v>1.46</v>
@@ -2900,55 +2900,55 @@
         <v>2.21</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.75</v>
+        <v>2.78</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.40000000000001</v>
+        <v>91.81</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.4</v>
+        <v>5.19</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>44.7</v>
+        <v>44.81</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.25</v>
+        <v>2.14</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.1</v>
+        <v>11.09</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.1</v>
+        <v>12.24</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.1</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="DS5" t="n">
         <v>0.05</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.05</v>
+        <v>49.38</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX5" t="n">
-        <v>13.1</v>
+        <v>12.91</v>
       </c>
       <c r="DY5" t="n">
-        <v>9.050000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.05</v>
+        <v>3.95</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.75</v>
+        <v>21.57</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="6">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D7" t="n">
         <v>11</v>
       </c>
       <c r="E7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="F7" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="H7" t="n">
-        <v>103.22</v>
+        <v>104.1</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.11</v>
+        <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="K7" t="n">
-        <v>6.22</v>
+        <v>6.3</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.4</v>
       </c>
       <c r="M7" t="n">
-        <v>57.44</v>
+        <v>58.8</v>
       </c>
       <c r="N7" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>3.11</v>
+        <v>2.7</v>
       </c>
       <c r="P7" t="n">
-        <v>11.56</v>
+        <v>11.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>14.11</v>
+        <v>14</v>
       </c>
       <c r="R7" t="n">
-        <v>7</v>
+        <v>6.4</v>
       </c>
       <c r="S7" t="n">
-        <v>0.67</v>
+        <v>0.9</v>
       </c>
       <c r="T7" t="n">
-        <v>1.78</v>
+        <v>1.6</v>
       </c>
       <c r="U7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V7" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>54.67</v>
+        <v>55.1</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>16</v>
+        <v>16.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>10.78</v>
+        <v>11.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.22</v>
+        <v>5.1</v>
       </c>
       <c r="AC7" t="n">
-        <v>23.89</v>
+        <v>23.9</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AF7" t="n">
         <v>0.09</v>
@@ -3565,70 +3565,70 @@
         <v>2.45</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.7</v>
+        <v>10.76</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.85</v>
+        <v>2.86</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BL7" t="n">
-        <v>1.05</v>
+        <v>1</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.6</v>
+        <v>4.33</v>
       </c>
       <c r="BR7" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS7" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BT7" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU7" t="n">
-        <v>40</v>
+        <v>38.1</v>
       </c>
       <c r="BV7" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BW7" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="CA7" t="n">
         <v>3.42</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CC7" t="n">
         <v>2.21</v>
@@ -3643,13 +3643,13 @@
         <v>2.34</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.48</v>
@@ -3658,13 +3658,13 @@
         <v>1.3</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CM7" t="n">
         <v>2.69</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO7" t="n">
         <v>1.14</v>
@@ -3673,7 +3673,7 @@
         <v>1.57</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CR7" t="n">
         <v>1.37</v>
@@ -3715,79 +3715,79 @@
         <v>2.75</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.55</v>
+        <v>1.48</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.55</v>
+        <v>2.38</v>
       </c>
       <c r="DH7" t="n">
-        <v>98.90000000000001</v>
+        <v>99.52</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.15</v>
+        <v>6.19</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.5</v>
+        <v>0.43</v>
       </c>
       <c r="DM7" t="n">
-        <v>51.15</v>
+        <v>52.1</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="DO7" t="n">
-        <v>3</v>
+        <v>2.81</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.2</v>
+        <v>11.05</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.55</v>
+        <v>14.48</v>
       </c>
       <c r="DR7" t="n">
-        <v>7.1</v>
+        <v>6.81</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.15</v>
+        <v>54.38</v>
       </c>
       <c r="DW7" t="n">
         <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.45</v>
+        <v>15.67</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.2</v>
+        <v>10.48</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.25</v>
+        <v>5.19</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.85</v>
+        <v>22.9</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C9" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D9" t="n">
         <v>11</v>
       </c>
       <c r="E9" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="F9" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="G9" t="n">
-        <v>2.89</v>
+        <v>2.5</v>
       </c>
       <c r="H9" t="n">
-        <v>83.11</v>
+        <v>85.59999999999999</v>
       </c>
       <c r="I9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="J9" t="n">
-        <v>2.22</v>
+        <v>2.1</v>
       </c>
       <c r="K9" t="n">
-        <v>4.44</v>
+        <v>5</v>
       </c>
       <c r="L9" t="n">
-        <v>0.11</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>33.89</v>
+        <v>34.2</v>
       </c>
       <c r="N9" t="n">
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="P9" t="n">
-        <v>10.22</v>
+        <v>10.5</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.56</v>
+        <v>14.9</v>
       </c>
       <c r="R9" t="n">
-        <v>9</v>
+        <v>8.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.11</v>
+        <v>2.4</v>
       </c>
       <c r="T9" t="n">
-        <v>1.11</v>
+        <v>1.4</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>44</v>
+        <v>45.2</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.44</v>
+        <v>10.8</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.22</v>
+        <v>7.4</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.22</v>
+        <v>3.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.56</v>
+        <v>19.4</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.78</v>
+        <v>1.7</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>2.55</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.15</v>
+        <v>10.19</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.6</v>
+        <v>0.71</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.75</v>
+        <v>0.95</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.4</v>
+        <v>2.33</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.35</v>
+        <v>1.67</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.45</v>
+        <v>4.19</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.7</v>
+        <v>5.38</v>
       </c>
       <c r="BR9" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS9" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BU9" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BV9" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BW9" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BX9" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.8</v>
+        <v>2.9</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.2</v>
+        <v>3.34</v>
       </c>
       <c r="CA9" t="n">
         <v>3.76</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.96</v>
+        <v>3.97</v>
       </c>
       <c r="CC9" t="n">
         <v>4.16</v>
@@ -4467,10 +4467,10 @@
         <v>1.73</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="CO9" t="n">
         <v>1.17</v>
@@ -4479,7 +4479,7 @@
         <v>1.61</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
@@ -4518,82 +4518,82 @@
         <v>1.65</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.15</v>
+        <v>1.09</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.4</v>
+        <v>2.24</v>
       </c>
       <c r="DH9" t="n">
-        <v>77.3</v>
+        <v>78.76000000000001</v>
       </c>
       <c r="DI9" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.4</v>
+        <v>2.34</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.15</v>
+        <v>4.43</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.6</v>
+        <v>33.76</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.05</v>
+        <v>12.1</v>
       </c>
       <c r="DQ9" t="n">
-        <v>12.95</v>
+        <v>13.19</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.85</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.1</v>
+        <v>45.62</v>
       </c>
       <c r="DW9" t="n">
         <v>0.1</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.15</v>
+        <v>11.29</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.15</v>
+        <v>7.24</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4</v>
+        <v>4.05</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.05</v>
+        <v>20.9</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.2</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="10">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="n">
         <v>11</v>
       </c>
       <c r="D11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E11" t="n">
         <v>0.09</v>
@@ -5096,139 +5096,139 @@
         <v>2.09</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.67</v>
+        <v>1.4</v>
       </c>
       <c r="AI11" t="n">
-        <v>93.56</v>
+        <v>93.5</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="AL11" t="n">
-        <v>3.89</v>
+        <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-0.1</v>
       </c>
       <c r="AN11" t="n">
-        <v>48.67</v>
+        <v>47</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.89</v>
+        <v>0.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.56</v>
+        <v>1.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.56</v>
+        <v>14.4</v>
       </c>
       <c r="AR11" t="n">
-        <v>13.22</v>
+        <v>12.8</v>
       </c>
       <c r="AS11" t="n">
-        <v>8.44</v>
+        <v>9</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>48.56</v>
+        <v>47.8</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>12.67</v>
+        <v>12</v>
       </c>
       <c r="BB11" t="n">
-        <v>8.56</v>
+        <v>7.8</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.11</v>
+        <v>4.2</v>
       </c>
       <c r="BD11" t="n">
-        <v>22.67</v>
+        <v>21.8</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="BF11" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.1</v>
+        <v>10.19</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.25</v>
+        <v>2.29</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.6</v>
+        <v>0.57</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="BO11" t="n">
         <v>1.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.65</v>
+        <v>4.38</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.8</v>
+        <v>4.52</v>
       </c>
       <c r="BR11" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>65</v>
+        <v>66.67</v>
       </c>
       <c r="BT11" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU11" t="n">
-        <v>20</v>
+        <v>19.05</v>
       </c>
       <c r="BV11" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW11" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX11" t="n">
-        <v>35</v>
+        <v>33.33</v>
       </c>
       <c r="BY11" t="n">
         <v>1.82</v>
@@ -5237,16 +5237,16 @@
         <v>2.01</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="CB11" t="n">
         <v>3.76</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.66</v>
+        <v>2.69</v>
       </c>
       <c r="CD11" t="n">
-        <v>2.98</v>
+        <v>3.01</v>
       </c>
       <c r="CE11" t="n">
         <v>1.25</v>
@@ -5255,13 +5255,13 @@
         <v>2.29</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.05</v>
+        <v>3.07</v>
       </c>
       <c r="CH11" t="n">
         <v>1.45</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.21</v>
+        <v>2.22</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.48</v>
@@ -5270,13 +5270,13 @@
         <v>1.3</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CM11" t="n">
         <v>2.69</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO11" t="n">
         <v>1.13</v>
@@ -5291,7 +5291,7 @@
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CT11" t="n">
         <v>3.31</v>
@@ -5300,7 +5300,7 @@
         <v>1.56</v>
       </c>
       <c r="CV11" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CW11" t="n">
         <v>1.6</v>
@@ -5324,82 +5324,82 @@
         <v>1.68</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.15</v>
+        <v>2</v>
       </c>
       <c r="DH11" t="n">
-        <v>94.45</v>
+        <v>94.38</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.55</v>
+        <v>4.57</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.2</v>
+        <v>0.14</v>
       </c>
       <c r="DM11" t="n">
-        <v>46.4</v>
+        <v>45.72</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.1</v>
+        <v>1.95</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.35</v>
+        <v>13.33</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.6</v>
+        <v>11.47</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.85</v>
+        <v>9.09</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.75</v>
+        <v>48.38</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.7</v>
+        <v>12.38</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.300000000000001</v>
+        <v>7.95</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.4</v>
+        <v>4.43</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.95</v>
+        <v>20.62</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="12">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="n">
         <v>11</v>
       </c>
       <c r="D13" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E13" t="n">
         <v>0.27</v>
@@ -5905,136 +5905,136 @@
         <v>0</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="AI13" t="n">
-        <v>89.22</v>
+        <v>88.8</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.22</v>
+        <v>0.3</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.89</v>
+        <v>2.8</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.11</v>
+        <v>4.3</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>35.33</v>
+        <v>36.6</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.11</v>
+        <v>1.2</v>
       </c>
       <c r="AP13" t="n">
-        <v>2</v>
+        <v>2.2</v>
       </c>
       <c r="AQ13" t="n">
         <v>13</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.44</v>
+        <v>13.8</v>
       </c>
       <c r="AS13" t="n">
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.11</v>
+        <v>1</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>44.33</v>
+        <v>45.2</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="BA13" t="n">
-        <v>10.44</v>
+        <v>11</v>
       </c>
       <c r="BB13" t="n">
-        <v>6.67</v>
+        <v>7.4</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.78</v>
+        <v>3.6</v>
       </c>
       <c r="BD13" t="n">
-        <v>20.56</v>
+        <v>19.7</v>
       </c>
       <c r="BE13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="BF13" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BH13" t="n">
+        <v>9.81</v>
+      </c>
+      <c r="BI13" t="n">
+        <v>3.14</v>
+      </c>
+      <c r="BJ13" t="n">
+        <v>0.76</v>
+      </c>
+      <c r="BK13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL13" t="n">
         <v>1.19</v>
       </c>
-      <c r="BF13" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="BG13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BH13" t="n">
-        <v>9.699999999999999</v>
-      </c>
-      <c r="BI13" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="BJ13" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BK13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL13" t="n">
-        <v>1.2</v>
-      </c>
       <c r="BM13" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BN13" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.5</v>
+        <v>4.67</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.55</v>
+        <v>4.52</v>
       </c>
       <c r="BR13" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS13" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT13" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>65</v>
+        <v>61.9</v>
       </c>
       <c r="BY13" t="n">
         <v>2.45</v>
@@ -6043,31 +6043,31 @@
         <v>2.54</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC13" t="n">
-        <v>2.97</v>
+        <v>3.06</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.13</v>
+        <v>3.18</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.56</v>
@@ -6076,10 +6076,10 @@
         <v>1.36</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CN13" t="n">
         <v>2.17</v>
@@ -6091,7 +6091,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CR13" t="n">
         <v>1.36</v>
@@ -6133,79 +6133,79 @@
         <v>2.7</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.65</v>
+        <v>1.57</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DH13" t="n">
-        <v>97</v>
+        <v>96.43000000000001</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.15</v>
+        <v>0.19</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="DK13" t="n">
+        <v>5</v>
+      </c>
+      <c r="DL13" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="DM13" t="n">
+        <v>42.71</v>
+      </c>
+      <c r="DN13" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="DO13" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="DP13" t="n">
+        <v>12.24</v>
+      </c>
+      <c r="DQ13" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="DR13" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="DS13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DT13" t="n">
+        <v>0.14</v>
+      </c>
+      <c r="DU13" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV13" t="n">
+        <v>47.33</v>
+      </c>
+      <c r="DW13" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="DX13" t="n">
+        <v>13.43</v>
+      </c>
+      <c r="DY13" t="n">
+        <v>8.470000000000001</v>
+      </c>
+      <c r="DZ13" t="n">
         <v>4.95</v>
       </c>
-      <c r="DL13" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="DM13" t="n">
-        <v>42.45</v>
-      </c>
-      <c r="DN13" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="DO13" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="DP13" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="DQ13" t="n">
-        <v>13.95</v>
-      </c>
-      <c r="DR13" t="n">
-        <v>9.300000000000001</v>
-      </c>
-      <c r="DS13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DT13" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="DU13" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV13" t="n">
-        <v>47.05</v>
-      </c>
-      <c r="DW13" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="DX13" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="DY13" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="DZ13" t="n">
-        <v>5.1</v>
-      </c>
       <c r="EA13" t="n">
-        <v>21.75</v>
+        <v>21.29</v>
       </c>
       <c r="EB13" t="n">
         <v>1.51</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="14">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="n">
         <v>10</v>
       </c>
       <c r="D15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AH15" t="n">
-        <v>3.1</v>
+        <v>2.73</v>
       </c>
       <c r="AI15" t="n">
-        <v>80.5</v>
+        <v>80.36</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.8</v>
+        <v>5.36</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.7</v>
+        <v>0.55</v>
       </c>
       <c r="AN15" t="n">
-        <v>40.3</v>
+        <v>39.55</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.7</v>
+        <v>2.36</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.6</v>
+        <v>12.27</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.2</v>
+        <v>13.18</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.3</v>
+        <v>1.55</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.2</v>
+        <v>1.55</v>
       </c>
       <c r="AV15" t="n">
         <v>0</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>54.7</v>
+        <v>53.73</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>17.5</v>
+        <v>17.09</v>
       </c>
       <c r="BB15" t="n">
-        <v>11.4</v>
+        <v>10.91</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.1</v>
+        <v>6.18</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.7</v>
+        <v>17.64</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.2</v>
+        <v>3.09</v>
       </c>
       <c r="BG15" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="BI15" t="n">
-        <v>2.95</v>
+        <v>3.24</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.45</v>
+        <v>0.57</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.7</v>
+        <v>0.9</v>
       </c>
       <c r="BL15" t="n">
         <v>0.9</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.15</v>
+        <v>1.48</v>
       </c>
       <c r="BP15" t="n">
+        <v>4.76</v>
+      </c>
+      <c r="BQ15" t="n">
         <v>5.05</v>
       </c>
-      <c r="BQ15" t="n">
-        <v>5.35</v>
-      </c>
       <c r="BR15" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS15" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT15" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU15" t="n">
-        <v>25</v>
+        <v>28.57</v>
       </c>
       <c r="BV15" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BW15" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BX15" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BY15" t="n">
         <v>2.17</v>
@@ -6852,13 +6852,13 @@
         <v>3.65</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.98</v>
+        <v>2.86</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.23</v>
+        <v>3.1</v>
       </c>
       <c r="CE15" t="n">
         <v>1.26</v>
@@ -6873,7 +6873,7 @@
         <v>1.59</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.52</v>
+        <v>2.51</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.49</v>
@@ -6882,19 +6882,19 @@
         <v>1.37</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM15" t="n">
         <v>2.83</v>
       </c>
       <c r="CN15" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CO15" t="n">
         <v>1.15</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CQ15" t="n">
         <v>2.36</v>
@@ -6908,22 +6908,22 @@
         <v>1.63</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CW15" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CX15" t="n">
         <v>1.46</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.55</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="DB15" t="n">
         <v>1.17</v>
@@ -6938,43 +6938,43 @@
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.95</v>
+        <v>2.76</v>
       </c>
       <c r="DH15" t="n">
-        <v>94.25</v>
+        <v>93.52</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.75</v>
+        <v>5.52</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.55</v>
+        <v>0.48</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.8</v>
+        <v>47.05</v>
       </c>
       <c r="DN15" t="n">
         <v>0.9</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.75</v>
+        <v>2.57</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.2</v>
+        <v>12.52</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.4</v>
+        <v>12.43</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.45</v>
+        <v>7.57</v>
       </c>
       <c r="DS15" t="n">
         <v>0.1</v>
@@ -6986,28 +6986,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.65</v>
+        <v>55.1</v>
       </c>
       <c r="DW15" t="n">
         <v>0.05</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.75</v>
+        <v>16.57</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.25</v>
+        <v>11</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.65</v>
+        <v>18.57</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7017,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C16" t="n">
         <v>11</v>
       </c>
       <c r="D16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7107,139 +7107,139 @@
         <v>2.73</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.78</v>
+        <v>1.9</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.44</v>
+        <v>3.3</v>
       </c>
       <c r="AI16" t="n">
-        <v>94.33</v>
+        <v>92.3</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.67</v>
+        <v>2.9</v>
       </c>
       <c r="AL16" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="AN16" t="n">
-        <v>50</v>
+        <v>48.6</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.44</v>
+        <v>13.1</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.56</v>
+        <v>13.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.89</v>
+        <v>8.1</v>
       </c>
       <c r="AT16" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.9</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>49.6</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>12</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>21.8</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.949999999999999</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BN16" t="n">
         <v>1.67</v>
       </c>
-      <c r="AU16" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>50.11</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.11</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>12.56</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>8</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.56</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>21.22</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.56</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>9.9</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.45</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.7</v>
-      </c>
       <c r="BO16" t="n">
-        <v>0.85</v>
+        <v>0.9</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.45</v>
+        <v>4.48</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.45</v>
+        <v>5.48</v>
       </c>
       <c r="BR16" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS16" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT16" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU16" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV16" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW16" t="n">
         <v>0</v>
       </c>
       <c r="BX16" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY16" t="n">
         <v>2.43</v>
@@ -7254,10 +7254,10 @@
         <v>3.69</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.34</v>
+        <v>3.39</v>
       </c>
       <c r="CE16" t="n">
         <v>1.32</v>
@@ -7266,7 +7266,7 @@
         <v>2.49</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.19</v>
+        <v>3.2</v>
       </c>
       <c r="CH16" t="n">
         <v>1.5</v>
@@ -7281,13 +7281,13 @@
         <v>1.36</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.88</v>
+        <v>2.87</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO16" t="n">
         <v>1.2</v>
@@ -7299,13 +7299,13 @@
         <v>2.68</v>
       </c>
       <c r="CR16" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS16" t="n">
         <v>2.6</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CU16" t="n">
         <v>1.53</v>
@@ -7332,85 +7332,85 @@
         <v>1.22</v>
       </c>
       <c r="DC16" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.77</v>
+        <v>2.76</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="DH16" t="n">
-        <v>96.09999999999999</v>
+        <v>95.05</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.7</v>
+        <v>2.81</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.55</v>
+        <v>5.52</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.45</v>
+        <v>0.47</v>
       </c>
       <c r="DM16" t="n">
-        <v>47.55</v>
+        <v>47</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
       <c r="DP16" t="n">
-        <v>12.05</v>
+        <v>11.95</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.75</v>
+        <v>13.86</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.75</v>
+        <v>7.86</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.55</v>
+        <v>50.29</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.4</v>
+        <v>13.09</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.550000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.85</v>
+        <v>4.76</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.55</v>
+        <v>20.86</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.65</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="17">
@@ -7420,10 +7420,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D17" t="n">
         <v>10</v>
@@ -7432,82 +7432,82 @@
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="G17" t="n">
-        <v>3.8</v>
+        <v>3.82</v>
       </c>
       <c r="H17" t="n">
-        <v>102.2</v>
+        <v>102.36</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="K17" t="n">
-        <v>6.4</v>
+        <v>6.36</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="M17" t="n">
-        <v>56.1</v>
+        <v>58.91</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7</v>
+        <v>0.64</v>
       </c>
       <c r="O17" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="P17" t="n">
-        <v>12.9</v>
+        <v>12.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>9.9</v>
+        <v>10.18</v>
       </c>
       <c r="R17" t="n">
-        <v>7.5</v>
+        <v>7.27</v>
       </c>
       <c r="S17" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="T17" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="U17" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>56.1</v>
+        <v>56</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.9</v>
+        <v>17.64</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.9</v>
+        <v>11.55</v>
       </c>
       <c r="AB17" t="n">
-        <v>6</v>
+        <v>6.09</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.6</v>
+        <v>21.64</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AF17" t="n">
         <v>0.3</v>
@@ -7591,58 +7591,58 @@
         <v>2.4</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.3</v>
+        <v>0.38</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL17" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.55</v>
+        <v>1.52</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.75</v>
+        <v>4.76</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.65</v>
+        <v>5.67</v>
       </c>
       <c r="BR17" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS17" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BU17" t="n">
-        <v>15</v>
+        <v>14.29</v>
       </c>
       <c r="BV17" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW17" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX17" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY17" t="n">
         <v>1.89</v>
@@ -7675,7 +7675,7 @@
         <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.6</v>
@@ -7705,7 +7705,7 @@
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CT17" t="n">
         <v>3.25</v>
@@ -7714,10 +7714,10 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CX17" t="n">
         <v>1.46</v>
@@ -7738,79 +7738,79 @@
         <v>1.72</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.15</v>
+        <v>3.19</v>
       </c>
       <c r="DH17" t="n">
-        <v>100.2</v>
+        <v>100.38</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.6</v>
+        <v>5.62</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM17" t="n">
-        <v>49.1</v>
+        <v>50.91</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.85</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.9</v>
+        <v>12.81</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.45</v>
+        <v>10.57</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.2</v>
+        <v>7.09</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.45</v>
+        <v>54.48</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.3</v>
+        <v>16.24</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.8</v>
+        <v>10.67</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.5</v>
+        <v>5.57</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.35</v>
+        <v>21.38</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="EC17" t="n">
         <v>2.1</v>
@@ -7823,10 +7823,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D18" t="n">
         <v>10</v>
@@ -7835,82 +7835,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="G18" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="H18" t="n">
-        <v>90.90000000000001</v>
+        <v>91.27</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="J18" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="K18" t="n">
-        <v>4.6</v>
+        <v>4.45</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M18" t="n">
-        <v>38.9</v>
+        <v>38.09</v>
       </c>
       <c r="N18" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="O18" t="n">
-        <v>3</v>
+        <v>2.82</v>
       </c>
       <c r="P18" t="n">
-        <v>15.2</v>
+        <v>14.91</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.2</v>
+        <v>14.18</v>
       </c>
       <c r="R18" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="S18" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>56.8</v>
+        <v>55.27</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.6</v>
+        <v>13.18</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.800000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.8</v>
+        <v>4.64</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.3</v>
+        <v>21.45</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.44</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="AF18" t="n">
         <v>0.1</v>
@@ -7994,70 +7994,70 @@
         <v>3.6</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BH18" t="n">
-        <v>10.1</v>
+        <v>10.05</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.75</v>
+        <v>2.71</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BL18" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BO18" t="n">
         <v>1.05</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.85</v>
+        <v>4.81</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.25</v>
+        <v>5.24</v>
       </c>
       <c r="BR18" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS18" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>60</v>
+        <v>57.14</v>
       </c>
       <c r="BU18" t="n">
-        <v>25</v>
+        <v>23.81</v>
       </c>
       <c r="BV18" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>75</v>
+        <v>76.19</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.52</v>
+        <v>3.51</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.6</v>
+        <v>3.59</v>
       </c>
       <c r="CC18" t="n">
         <v>3.74</v>
@@ -8078,22 +8078,22 @@
         <v>1.46</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.63</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="CL18" t="n">
         <v>1.85</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="CO18" t="n">
         <v>1.22</v>
@@ -8105,19 +8105,19 @@
         <v>2.79</v>
       </c>
       <c r="CR18" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.74</v>
+        <v>2.75</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CW18" t="n">
         <v>1.67</v>
@@ -8126,13 +8126,13 @@
         <v>1.51</v>
       </c>
       <c r="CY18" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="CZ18" t="n">
         <v>2.48</v>
       </c>
       <c r="DA18" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="DB18" t="n">
         <v>1.25</v>
@@ -8153,70 +8153,70 @@
         <v>2</v>
       </c>
       <c r="DH18" t="n">
-        <v>87.90000000000001</v>
+        <v>88.23999999999999</v>
       </c>
       <c r="DI18" t="n">
         <v>0.1</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.35</v>
+        <v>3.29</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM18" t="n">
-        <v>35.6</v>
+        <v>35.33</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.2</v>
+        <v>1.14</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.25</v>
+        <v>2.19</v>
       </c>
       <c r="DP18" t="n">
-        <v>14.1</v>
+        <v>14</v>
       </c>
       <c r="DQ18" t="n">
         <v>13.95</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.65</v>
+        <v>7.62</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>57.15</v>
+        <v>56.33</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.6</v>
+        <v>12.43</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.35</v>
+        <v>8.24</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.25</v>
+        <v>4.19</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.75</v>
+        <v>20.85</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.95</v>
+        <v>2.9</v>
       </c>
     </row>
     <row r="19">
@@ -8226,61 +8226,61 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C19" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D19" t="n">
         <v>11</v>
       </c>
       <c r="E19" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F19" t="n">
-        <v>2.11</v>
+        <v>2.1</v>
       </c>
       <c r="G19" t="n">
-        <v>3.33</v>
+        <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>102.44</v>
+        <v>103.1</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="K19" t="n">
-        <v>5.67</v>
+        <v>5.8</v>
       </c>
       <c r="L19" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="M19" t="n">
-        <v>50.78</v>
+        <v>50.4</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="O19" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="P19" t="n">
-        <v>13.22</v>
+        <v>13.6</v>
       </c>
       <c r="Q19" t="n">
-        <v>13</v>
+        <v>12.6</v>
       </c>
       <c r="R19" t="n">
-        <v>5</v>
+        <v>5.5</v>
       </c>
       <c r="S19" t="n">
-        <v>0.67</v>
+        <v>0.8</v>
       </c>
       <c r="T19" t="n">
-        <v>1.33</v>
+        <v>1.4</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
@@ -8292,28 +8292,28 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>44.56</v>
+        <v>44.5</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.44</v>
+        <v>13.7</v>
       </c>
       <c r="AA19" t="n">
-        <v>8.779999999999999</v>
+        <v>9</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.67</v>
+        <v>4.7</v>
       </c>
       <c r="AC19" t="n">
-        <v>20.78</v>
+        <v>21</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="AF19" t="n">
         <v>0.18</v>
@@ -8397,49 +8397,49 @@
         <v>2.45</v>
       </c>
       <c r="BG19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.5</v>
+        <v>9.43</v>
       </c>
       <c r="BI19" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BP19" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.45</v>
+        <v>5.48</v>
       </c>
       <c r="BR19" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS19" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BT19" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BU19" t="n">
-        <v>5</v>
+        <v>9.52</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8448,19 +8448,19 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.29</v>
+        <v>2.25</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.38</v>
+        <v>3.4</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CC19" t="n">
         <v>2.69</v>
@@ -8472,19 +8472,19 @@
         <v>1.36</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CH19" t="n">
         <v>1.43</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ19" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CK19" t="n">
         <v>1.43</v>
@@ -8493,19 +8493,19 @@
         <v>1.84</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.02</v>
+        <v>2.03</v>
       </c>
       <c r="CO19" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CQ19" t="n">
-        <v>2.99</v>
+        <v>3.01</v>
       </c>
       <c r="CR19" t="n">
         <v>1.38</v>
@@ -8523,19 +8523,19 @@
         <v>2.26</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CX19" t="n">
         <v>1.5</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.01</v>
+        <v>2.02</v>
       </c>
       <c r="DB19" t="n">
         <v>1.26</v>
@@ -8544,82 +8544,82 @@
         <v>1.87</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.08</v>
+        <v>3.1</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.85</v>
+        <v>2.95</v>
       </c>
       <c r="DH19" t="n">
-        <v>103.95</v>
+        <v>104.19</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.55</v>
+        <v>2.52</v>
       </c>
       <c r="DK19" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.4</v>
+        <v>0.38</v>
       </c>
       <c r="DM19" t="n">
-        <v>46.9</v>
+        <v>46.91</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO19" t="n">
         <v>2.1</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.65</v>
+        <v>13.81</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.2</v>
+        <v>12.05</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.55</v>
+        <v>5.76</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>43.55</v>
+        <v>43.57</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.4</v>
+        <v>12.57</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.199999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.85</v>
+        <v>21.91</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.5</v>
+        <v>2.47</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="n">
         <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F2" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="G2" t="n">
-        <v>4.3</v>
+        <v>4.27</v>
       </c>
       <c r="H2" t="n">
-        <v>102.9</v>
+        <v>102.36</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J2" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="K2" t="n">
-        <v>6.3</v>
+        <v>6.55</v>
       </c>
       <c r="L2" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="M2" t="n">
-        <v>49.2</v>
+        <v>49.55</v>
       </c>
       <c r="N2" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="O2" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="P2" t="n">
+        <v>13.18</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>13.82</v>
+      </c>
+      <c r="R2" t="n">
+        <v>7.73</v>
+      </c>
+      <c r="S2" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="T2" t="n">
         <v>2</v>
       </c>
-      <c r="P2" t="n">
-        <v>13.1</v>
-      </c>
-      <c r="Q2" t="n">
-        <v>14.1</v>
-      </c>
-      <c r="R2" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="S2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="T2" t="n">
-        <v>1.9</v>
-      </c>
       <c r="U2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="V2" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>56.2</v>
+        <v>55.36</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.1</v>
+        <v>14.64</v>
       </c>
       <c r="AA2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.3</v>
+        <v>4.64</v>
       </c>
       <c r="AC2" t="n">
-        <v>23.6</v>
+        <v>23</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="AE2" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,64 +1550,64 @@
         <v>2.3</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.7</v>
+        <v>10.67</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.15</v>
+        <v>1.29</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.75</v>
+        <v>6.67</v>
       </c>
       <c r="BR2" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS2" t="n">
-        <v>85</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BU2" t="n">
-        <v>35</v>
+        <v>38.1</v>
       </c>
       <c r="BV2" t="n">
-        <v>10</v>
+        <v>14.29</v>
       </c>
       <c r="BW2" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BX2" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.14</v>
+        <v>2.11</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.25</v>
+        <v>2.21</v>
       </c>
       <c r="CA2" t="n">
         <v>3.55</v>
@@ -1625,19 +1625,19 @@
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.23</v>
+        <v>3.21</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK2" t="n">
         <v>1.36</v>
@@ -1649,22 +1649,22 @@
         <v>2.8</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO2" t="n">
         <v>1.19</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CT2" t="n">
         <v>3.13</v>
@@ -1673,7 +1673,7 @@
         <v>1.54</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="CW2" t="n">
         <v>1.59</v>
@@ -1685,94 +1685,94 @@
         <v>1.66</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DB2" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.8</v>
+        <v>100.62</v>
       </c>
       <c r="DI2" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.3</v>
+        <v>2.24</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.1</v>
+        <v>6.24</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.3</v>
+        <v>0.28</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.1</v>
+        <v>50.24</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.8</v>
+        <v>0.76</v>
       </c>
       <c r="DO2" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.2</v>
+        <v>13.24</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14.4</v>
+        <v>14.24</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.35</v>
+        <v>7.29</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.85</v>
+        <v>52.57</v>
       </c>
       <c r="DW2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.5</v>
+        <v>13.81</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.4</v>
+        <v>9.52</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.1</v>
+        <v>4.29</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.65</v>
+        <v>23.33</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.15</v>
+        <v>2.1</v>
       </c>
     </row>
     <row r="3">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="n">
         <v>11</v>
       </c>
       <c r="D6" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,139 +3081,139 @@
         <v>2.36</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="AH6" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="AI6" t="n">
-        <v>103.78</v>
+        <v>105.4</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.78</v>
+        <v>5.3</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.33</v>
+        <v>0.3</v>
       </c>
       <c r="AN6" t="n">
-        <v>48</v>
+        <v>47.7</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.6</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.78</v>
+        <v>2.5</v>
       </c>
       <c r="AQ6" t="n">
+        <v>12.7</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>13.8</v>
+      </c>
+      <c r="AS6" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AT6" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AU6" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>49</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="BA6" t="n">
         <v>13</v>
       </c>
-      <c r="AR6" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="AS6" t="n">
-        <v>7.22</v>
-      </c>
-      <c r="AT6" t="n">
+      <c r="BB6" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>20.8</v>
+      </c>
+      <c r="BE6" t="n">
         <v>1.44</v>
       </c>
-      <c r="AU6" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>48.56</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.44</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>13.33</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>9.44</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>3.89</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>20.67</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>1.47</v>
-      </c>
       <c r="BF6" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.6</v>
+        <v>10.57</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.65</v>
+        <v>2.76</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.5</v>
+        <v>0.57</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.75</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.25</v>
+        <v>1.38</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.7</v>
+        <v>4.71</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.9</v>
+        <v>5.86</v>
       </c>
       <c r="BR6" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS6" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT6" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BU6" t="n">
-        <v>20</v>
+        <v>23.81</v>
       </c>
       <c r="BV6" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY6" t="n">
         <v>2.98</v>
@@ -3228,37 +3228,37 @@
         <v>3.69</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.03</v>
+        <v>4</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.42</v>
+        <v>4.45</v>
       </c>
       <c r="CE6" t="n">
         <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.05</v>
+        <v>3.03</v>
       </c>
       <c r="CH6" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK6" t="n">
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN6" t="n">
         <v>2.08</v>
@@ -3267,25 +3267,25 @@
         <v>1.21</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.77</v>
+        <v>2.8</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CU6" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CW6" t="n">
         <v>1.66</v>
@@ -3309,82 +3309,82 @@
         <v>1.78</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="DF6" t="n">
         <v>1.95</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="DH6" t="n">
-        <v>98.09999999999999</v>
+        <v>99.14</v>
       </c>
       <c r="DI6" t="n">
-        <v>0</v>
+        <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
         <v>3</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.75</v>
+        <v>4.57</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.25</v>
+        <v>0.24</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.45</v>
+        <v>40.67</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.8</v>
+        <v>12.67</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.5</v>
+        <v>13.48</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.15</v>
+        <v>8.24</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.2</v>
+        <v>44.62</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.35</v>
+        <v>0.33</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.85</v>
+        <v>12.71</v>
       </c>
       <c r="DY6" t="n">
-        <v>9</v>
+        <v>8.859999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.85</v>
+        <v>3.86</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.55</v>
+        <v>21.57</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.45</v>
+        <v>2.47</v>
       </c>
     </row>
     <row r="7">
@@ -3409,7 +3409,7 @@
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>2.7</v>
+        <v>3.2</v>
       </c>
       <c r="H7" t="n">
         <v>104.1</v>
@@ -3424,7 +3424,7 @@
         <v>6.3</v>
       </c>
       <c r="L7" t="n">
-        <v>0.4</v>
+        <v>0.5</v>
       </c>
       <c r="M7" t="n">
         <v>58.8</v>
@@ -3433,7 +3433,7 @@
         <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>2.7</v>
+        <v>3.1</v>
       </c>
       <c r="P7" t="n">
         <v>11.2</v>
@@ -3442,7 +3442,7 @@
         <v>14</v>
       </c>
       <c r="R7" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="S7" t="n">
         <v>0.9</v>
@@ -3460,16 +3460,16 @@
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.1</v>
+        <v>55.2</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.4</v>
+        <v>16.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.3</v>
+        <v>11.4</v>
       </c>
       <c r="AB7" t="n">
         <v>5.1</v>
@@ -3592,10 +3592,10 @@
         <v>1.14</v>
       </c>
       <c r="BP7" t="n">
-        <v>5</v>
+        <v>5.38</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.33</v>
+        <v>4.62</v>
       </c>
       <c r="BR7" t="n">
         <v>95.23999999999999</v>
@@ -3721,7 +3721,7 @@
         <v>1.48</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="DH7" t="n">
         <v>99.52</v>
@@ -3736,7 +3736,7 @@
         <v>6.19</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="DM7" t="n">
         <v>52.1</v>
@@ -3745,7 +3745,7 @@
         <v>0.57</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="DP7" t="n">
         <v>11.05</v>
@@ -3754,7 +3754,7 @@
         <v>14.48</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.81</v>
+        <v>6.86</v>
       </c>
       <c r="DS7" t="n">
         <v>0.14</v>
@@ -3766,16 +3766,16 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.38</v>
+        <v>54.43</v>
       </c>
       <c r="DW7" t="n">
         <v>0.05</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.67</v>
+        <v>15.71</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.48</v>
+        <v>10.53</v>
       </c>
       <c r="DZ7" t="n">
         <v>5.19</v>
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C8" t="n">
         <v>11</v>
       </c>
       <c r="D8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,139 +3887,139 @@
         <v>2.82</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.33</v>
+        <v>2.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>95.11</v>
+        <v>94.59999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.89</v>
+        <v>3.8</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="AN8" t="n">
-        <v>41.78</v>
+        <v>41.1</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.33</v>
+        <v>12.6</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.11</v>
+        <v>12.2</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.33</v>
+        <v>9.5</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.56</v>
+        <v>1.5</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.56</v>
+        <v>45.4</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="BA8" t="n">
-        <v>12.78</v>
+        <v>13.4</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.220000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="BD8" t="n">
-        <v>20.56</v>
+        <v>20</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.36</v>
+        <v>1.41</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL8" t="n">
         <v>0.95</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.8</v>
+        <v>3.76</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.95</v>
+        <v>4.86</v>
       </c>
       <c r="BR8" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS8" t="n">
-        <v>70</v>
+        <v>71.43000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>55</v>
+        <v>52.38</v>
       </c>
       <c r="BU8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BV8" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW8" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX8" t="n">
-        <v>55</v>
+        <v>57.14</v>
       </c>
       <c r="BY8" t="n">
         <v>2.39</v>
@@ -4034,19 +4034,19 @@
         <v>3.78</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.59</v>
+        <v>3.45</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.98</v>
+        <v>3.79</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF8" t="n">
         <v>2.43</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH8" t="n">
         <v>1.51</v>
@@ -4055,7 +4055,7 @@
         <v>2.33</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CK8" t="n">
         <v>1.4</v>
@@ -4064,7 +4064,7 @@
         <v>1.77</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CN8" t="n">
         <v>2.05</v>
@@ -4076,13 +4076,13 @@
         <v>1.65</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CT8" t="n">
         <v>3.19</v>
@@ -4115,49 +4115,49 @@
         <v>1.69</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="DE8" t="n">
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.09999999999999</v>
+        <v>92.95</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.1</v>
+        <v>-0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.05</v>
+        <v>4</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.2</v>
+        <v>0.19</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.65</v>
+        <v>46.1</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.7</v>
+        <v>12.81</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.65</v>
+        <v>11.71</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.7</v>
+        <v>7.86</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.85</v>
+        <v>48.62</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.4</v>
+        <v>12.71</v>
       </c>
       <c r="DY8" t="n">
-        <v>8.800000000000001</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.6</v>
+        <v>3.67</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.15</v>
+        <v>19.91</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
     </row>
     <row r="9">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D10" t="n">
         <v>11</v>
       </c>
       <c r="E10" t="n">
-        <v>0.11</v>
+        <v>0.2</v>
       </c>
       <c r="F10" t="n">
-        <v>1.22</v>
+        <v>1.1</v>
       </c>
       <c r="G10" t="n">
-        <v>3.56</v>
+        <v>3.5</v>
       </c>
       <c r="H10" t="n">
-        <v>112.78</v>
+        <v>111.8</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="K10" t="n">
-        <v>6.44</v>
+        <v>6.8</v>
       </c>
       <c r="L10" t="n">
-        <v>0.33</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>58</v>
+        <v>58.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0.44</v>
+        <v>0.4</v>
       </c>
       <c r="O10" t="n">
-        <v>2.89</v>
+        <v>3.3</v>
       </c>
       <c r="P10" t="n">
-        <v>13.33</v>
+        <v>13.1</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.11</v>
+        <v>13.6</v>
       </c>
       <c r="R10" t="n">
-        <v>6.44</v>
+        <v>6</v>
       </c>
       <c r="S10" t="n">
-        <v>1.33</v>
+        <v>1.3</v>
       </c>
       <c r="T10" t="n">
-        <v>1.56</v>
+        <v>1.7</v>
       </c>
       <c r="U10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="V10" t="n">
-        <v>0.11</v>
+        <v>0.1</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.89</v>
+        <v>57.3</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.33</v>
+        <v>17.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.56</v>
+        <v>11.6</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.78</v>
+        <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.89</v>
+        <v>19.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.67</v>
+        <v>1.5</v>
       </c>
       <c r="AF10" t="n">
         <v>0.09</v>
@@ -4774,19 +4774,19 @@
         <v>2.45</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.199999999999999</v>
+        <v>9.43</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.1</v>
+        <v>3.14</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.55</v>
+        <v>0.62</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.75</v>
+        <v>0.71</v>
       </c>
       <c r="BL10" t="n">
         <v>0.9</v>
@@ -4795,49 +4795,49 @@
         <v>0.9</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BP10" t="n">
-        <v>4</v>
+        <v>4.24</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="BR10" t="n">
-        <v>95</v>
+        <v>95.23999999999999</v>
       </c>
       <c r="BS10" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BT10" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BU10" t="n">
-        <v>40</v>
+        <v>42.86</v>
       </c>
       <c r="BV10" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY10" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="BZ10" t="n">
-        <v>1.93</v>
+        <v>1.9</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.8</v>
+        <v>3.79</v>
       </c>
       <c r="CC10" t="n">
         <v>2.36</v>
@@ -4846,31 +4846,31 @@
         <v>2.42</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.26</v>
+        <v>3.23</v>
       </c>
       <c r="CH10" t="n">
         <v>1.54</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK10" t="n">
         <v>1.34</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.93</v>
+        <v>2.92</v>
       </c>
       <c r="CN10" t="n">
         <v>2.18</v>
@@ -4879,16 +4879,16 @@
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CT10" t="n">
         <v>3.29</v>
@@ -4897,10 +4897,10 @@
         <v>1.56</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX10" t="n">
         <v>1.48</v>
@@ -4909,94 +4909,94 @@
         <v>1.68</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.52</v>
+        <v>2.55</v>
       </c>
       <c r="DA10" t="n">
         <v>2.16</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.1</v>
+        <v>0.14</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG10" t="n">
         <v>3</v>
       </c>
       <c r="DH10" t="n">
-        <v>106.4</v>
+        <v>106.24</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.15</v>
+        <v>2.05</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.45</v>
+        <v>5.67</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.35</v>
+        <v>0.43</v>
       </c>
       <c r="DM10" t="n">
-        <v>50.95</v>
+        <v>51.52</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.45</v>
+        <v>2.67</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.55</v>
+        <v>13.43</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.3</v>
+        <v>13.52</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.4</v>
+        <v>6.19</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.55</v>
+        <v>56.33</v>
       </c>
       <c r="DW10" t="n">
         <v>0.05</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.85</v>
+        <v>15.1</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.449999999999999</v>
+        <v>9.57</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.4</v>
+        <v>5.52</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.5</v>
+        <v>19.48</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.69</v>
+        <v>1.72</v>
       </c>
       <c r="EC10" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -5102,7 +5102,7 @@
         <v>2.1</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="AI11" t="n">
         <v>93.5</v>
@@ -5117,7 +5117,7 @@
         <v>4</v>
       </c>
       <c r="AM11" t="n">
-        <v>-0.1</v>
+        <v>0</v>
       </c>
       <c r="AN11" t="n">
         <v>47</v>
@@ -5126,7 +5126,7 @@
         <v>0.8</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.3</v>
+        <v>1.8</v>
       </c>
       <c r="AQ11" t="n">
         <v>14.4</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.8</v>
+        <v>47.7</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -5204,10 +5204,10 @@
         <v>1.05</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.38</v>
+        <v>4.76</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.52</v>
+        <v>4.81</v>
       </c>
       <c r="BR11" t="n">
         <v>85.70999999999999</v>
@@ -5333,7 +5333,7 @@
         <v>1.81</v>
       </c>
       <c r="DG11" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DH11" t="n">
         <v>94.38</v>
@@ -5348,7 +5348,7 @@
         <v>4.57</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.14</v>
+        <v>0.19</v>
       </c>
       <c r="DM11" t="n">
         <v>45.72</v>
@@ -5357,7 +5357,7 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="DO11" t="n">
-        <v>1.95</v>
+        <v>2.19</v>
       </c>
       <c r="DP11" t="n">
         <v>13.33</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.38</v>
+        <v>48.33</v>
       </c>
       <c r="DW11" t="n">
         <v>0.14</v>
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C12" t="n">
         <v>10</v>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,139 +5499,139 @@
         <v>1.8</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AI12" t="n">
-        <v>77.40000000000001</v>
+        <v>78</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.7</v>
+        <v>3.64</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.1</v>
+        <v>4.09</v>
       </c>
       <c r="AM12" t="n">
         <v>0</v>
       </c>
       <c r="AN12" t="n">
-        <v>33.8</v>
+        <v>33.36</v>
       </c>
       <c r="AO12" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.4</v>
+        <v>15.73</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.5</v>
+        <v>12.45</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.4</v>
+        <v>9.82</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.3</v>
+        <v>1.27</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>48.5</v>
+        <v>48.45</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.6</v>
+        <v>11.27</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.300000000000001</v>
+        <v>7.91</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.1</v>
+        <v>19.36</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.2</v>
+        <v>10.38</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.55</v>
+        <v>2.62</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.7</v>
+        <v>0.76</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.7</v>
+        <v>0.71</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.25</v>
+        <v>1.29</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.1</v>
+        <v>4.33</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.05</v>
+        <v>6</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT12" t="n">
-        <v>45</v>
+        <v>47.62</v>
       </c>
       <c r="BU12" t="n">
-        <v>15</v>
+        <v>19.05</v>
       </c>
       <c r="BV12" t="n">
-        <v>10</v>
+        <v>9.52</v>
       </c>
       <c r="BW12" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX12" t="n">
-        <v>60</v>
+        <v>61.9</v>
       </c>
       <c r="BY12" t="n">
         <v>2.15</v>
@@ -5640,52 +5640,52 @@
         <v>2.22</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.63</v>
+        <v>3.64</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.83</v>
+        <v>3.05</v>
       </c>
       <c r="CD12" t="n">
-        <v>2.95</v>
+        <v>3.27</v>
       </c>
       <c r="CE12" t="n">
         <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.16</v>
+        <v>3.14</v>
       </c>
       <c r="CH12" t="n">
         <v>1.49</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="CJ12" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CK12" t="n">
         <v>1.35</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CO12" t="n">
         <v>1.19</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CQ12" t="n">
         <v>2.68</v>
@@ -5694,7 +5694,7 @@
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CT12" t="n">
         <v>3.28</v>
@@ -5703,40 +5703,40 @@
         <v>1.52</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CY12" t="n">
         <v>1.7</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DB12" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="DC12" t="n">
         <v>1.77</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="DE12" t="n">
         <v>0.05</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="DH12" t="n">
         <v>83.90000000000001</v>
@@ -5745,64 +5745,64 @@
         <v>0.05</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.7</v>
+        <v>4.67</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DM12" t="n">
-        <v>37.7</v>
+        <v>37.28</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.8</v>
+        <v>0.86</v>
       </c>
       <c r="DO12" t="n">
         <v>1.85</v>
       </c>
       <c r="DP12" t="n">
-        <v>13.75</v>
+        <v>14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.7</v>
+        <v>13.62</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.5</v>
+        <v>8.76</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.5</v>
+        <v>50.38</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.3</v>
+        <v>12.09</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.550000000000001</v>
+        <v>8.33</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.75</v>
+        <v>3.76</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.2</v>
+        <v>19.33</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
     </row>
     <row r="13">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C14" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D14" t="n">
         <v>11</v>
       </c>
       <c r="E14" t="n">
-        <v>0.22</v>
+        <v>0.2</v>
       </c>
       <c r="F14" t="n">
-        <v>2.11</v>
+        <v>2</v>
       </c>
       <c r="G14" t="n">
-        <v>1.89</v>
+        <v>1.8</v>
       </c>
       <c r="H14" t="n">
-        <v>75.44</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.44</v>
+        <v>3.2</v>
       </c>
       <c r="K14" t="n">
-        <v>4.67</v>
+        <v>4.5</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="M14" t="n">
-        <v>41.78</v>
+        <v>42.8</v>
       </c>
       <c r="N14" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="P14" t="n">
+        <v>14</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>13</v>
+      </c>
+      <c r="R14" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="S14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" t="n">
+        <v>46.9</v>
+      </c>
+      <c r="Y14" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>11</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>6.3</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="AD14" t="n">
         <v>1.33</v>
       </c>
-      <c r="O14" t="n">
-        <v>2.11</v>
-      </c>
-      <c r="P14" t="n">
-        <v>13.89</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>12.78</v>
-      </c>
-      <c r="R14" t="n">
-        <v>8.56</v>
-      </c>
-      <c r="S14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="T14" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="U14" t="n">
-        <v>0</v>
-      </c>
-      <c r="V14" t="n">
-        <v>0</v>
-      </c>
-      <c r="W14" t="n">
-        <v>0</v>
-      </c>
-      <c r="X14" t="n">
-        <v>45.89</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>11.56</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>6.56</v>
-      </c>
-      <c r="AB14" t="n">
-        <v>5</v>
-      </c>
-      <c r="AC14" t="n">
-        <v>16.22</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>1.38</v>
-      </c>
       <c r="AE14" t="n">
-        <v>3.22</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>0.09</v>
@@ -6386,67 +6386,67 @@
         <v>2.18</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.4</v>
+        <v>10.19</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.25</v>
+        <v>3.19</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.95</v>
+        <v>0.9</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.6</v>
+        <v>4.52</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="BR14" t="n">
-        <v>90</v>
+        <v>90.48</v>
       </c>
       <c r="BS14" t="n">
-        <v>80</v>
+        <v>80.95</v>
       </c>
       <c r="BT14" t="n">
-        <v>70</v>
+        <v>66.67</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>47.62</v>
       </c>
       <c r="BV14" t="n">
-        <v>30</v>
+        <v>28.57</v>
       </c>
       <c r="BW14" t="n">
-        <v>5</v>
+        <v>4.76</v>
       </c>
       <c r="BX14" t="n">
-        <v>50</v>
+        <v>52.38</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.56</v>
+        <v>2.55</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.74</v>
+        <v>2.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CB14" t="n">
         <v>3.87</v>
@@ -6461,10 +6461,10 @@
         <v>1.29</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.27</v>
+        <v>3.25</v>
       </c>
       <c r="CH14" t="n">
         <v>1.55</v>
@@ -6482,25 +6482,25 @@
         <v>1.68</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CN14" t="n">
         <v>2.17</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CT14" t="n">
         <v>3.3</v>
@@ -6524,7 +6524,7 @@
         <v>2.6</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DB14" t="n">
         <v>1.2</v>
@@ -6536,46 +6536,46 @@
         <v>2.59</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.55</v>
+        <v>2.48</v>
       </c>
       <c r="DH14" t="n">
-        <v>83.3</v>
+        <v>84.56999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.75</v>
+        <v>2.67</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.5</v>
+        <v>0.47</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.65</v>
+        <v>42.15</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.1</v>
+        <v>1.05</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.5</v>
+        <v>12.62</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.65</v>
+        <v>8.67</v>
       </c>
       <c r="DS14" t="n">
         <v>0.05</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.55</v>
+        <v>47.95</v>
       </c>
       <c r="DW14" t="n">
         <v>0.1</v>
       </c>
       <c r="DX14" t="n">
-        <v>12.1</v>
+        <v>11.81</v>
       </c>
       <c r="DY14" t="n">
-        <v>8</v>
+        <v>7.81</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.8</v>
+        <v>17.95</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.65</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="15">
@@ -7492,10 +7492,10 @@
         <v>0.18</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.64</v>
+        <v>17.73</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.55</v>
+        <v>11.64</v>
       </c>
       <c r="AB17" t="n">
         <v>6.09</v>
@@ -7504,7 +7504,7 @@
         <v>21.64</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="AE17" t="n">
         <v>1.82</v>
@@ -7798,10 +7798,10 @@
         <v>0.14</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.24</v>
+        <v>16.29</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.67</v>
+        <v>10.72</v>
       </c>
       <c r="DZ17" t="n">
         <v>5.57</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1451,10 +1451,10 @@
         <v>0.09</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.64</v>
+        <v>14.73</v>
       </c>
       <c r="AA2" t="n">
-        <v>10</v>
+        <v>10.09</v>
       </c>
       <c r="AB2" t="n">
         <v>4.64</v>
@@ -1757,10 +1757,10 @@
         <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.81</v>
+        <v>13.86</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.52</v>
+        <v>9.57</v>
       </c>
       <c r="DZ2" t="n">
         <v>4.29</v>
@@ -3144,10 +3144,10 @@
         <v>0.4</v>
       </c>
       <c r="BA6" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.1</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="BC6" t="n">
         <v>3.9</v>
@@ -3156,7 +3156,7 @@
         <v>20.8</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="BF6" t="n">
         <v>2.6</v>
@@ -3369,10 +3369,10 @@
         <v>0.33</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.71</v>
+        <v>12.81</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.859999999999999</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DZ6" t="n">
         <v>3.86</v>
@@ -3381,7 +3381,7 @@
         <v>21.57</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="EC6" t="n">
         <v>2.47</v>
@@ -6287,10 +6287,10 @@
         <v>0.2</v>
       </c>
       <c r="Z14" t="n">
-        <v>11</v>
+        <v>11.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.3</v>
+        <v>6.5</v>
       </c>
       <c r="AB14" t="n">
         <v>4.7</v>
@@ -6299,7 +6299,7 @@
         <v>16.7</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AE14" t="n">
         <v>3</v>
@@ -6593,10 +6593,10 @@
         <v>0.1</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.81</v>
+        <v>11.91</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.81</v>
+        <v>7.9</v>
       </c>
       <c r="DZ14" t="n">
         <v>4</v>
@@ -6605,7 +6605,7 @@
         <v>17.95</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC14" t="n">
         <v>2.57</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="n">
         <v>11</v>
       </c>
       <c r="D4" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E4" t="n">
         <v>0.27</v>
@@ -2275,139 +2275,139 @@
         <v>1.82</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.8</v>
+        <v>2.09</v>
       </c>
       <c r="AI4" t="n">
-        <v>87.8</v>
+        <v>89.27</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.5</v>
+        <v>4.73</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN4" t="n">
-        <v>36</v>
+        <v>36.73</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AQ4" t="n">
-        <v>12.3</v>
+        <v>11.64</v>
       </c>
       <c r="AR4" t="n">
-        <v>11</v>
+        <v>10.91</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.800000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>49.6</v>
+        <v>50.82</v>
       </c>
       <c r="AZ4" t="n">
         <v>0</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.5</v>
+        <v>12.45</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.199999999999999</v>
+        <v>8.09</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.9</v>
+        <v>17.82</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BG4" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.38</v>
+        <v>10.5</v>
       </c>
       <c r="BI4" t="n">
-        <v>2.95</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.86</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.24</v>
+        <v>5.23</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.14</v>
+        <v>5.27</v>
       </c>
       <c r="BR4" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS4" t="n">
-        <v>71.43000000000001</v>
+        <v>72.73</v>
       </c>
       <c r="BT4" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU4" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BV4" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX4" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY4" t="n">
         <v>1.84</v>
@@ -2416,16 +2416,16 @@
         <v>1.89</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.95</v>
+        <v>2.88</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.17</v>
+        <v>3.09</v>
       </c>
       <c r="CE4" t="n">
         <v>1.3</v>
@@ -2434,10 +2434,10 @@
         <v>2.39</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CH4" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CI4" t="n">
         <v>2.33</v>
@@ -2446,10 +2446,10 @@
         <v>1.57</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM4" t="n">
         <v>2.7</v>
@@ -2461,28 +2461,28 @@
         <v>1.18</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.51</v>
+        <v>2.53</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.3</v>
+        <v>3.26</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CW4" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX4" t="n">
         <v>1.47</v>
@@ -2500,52 +2500,52 @@
         <v>1.21</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.67</v>
+        <v>2.71</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.14</v>
+        <v>2.27</v>
       </c>
       <c r="DH4" t="n">
-        <v>87.52</v>
+        <v>88.27</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.43</v>
+        <v>41.54</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.81</v>
+        <v>2.78</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.57</v>
+        <v>11.28</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.57</v>
+        <v>11.5</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.57</v>
+        <v>8.5</v>
       </c>
       <c r="DS4" t="n">
         <v>0.09</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.14</v>
+        <v>49.78</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.86</v>
+        <v>13.77</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.43</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.43</v>
+        <v>5.4</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.66</v>
+        <v>17.64</v>
       </c>
       <c r="EB4" t="n">
         <v>1.55</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="5">
@@ -2588,94 +2588,94 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C5" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D5" t="n">
         <v>11</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F5" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="G5" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="H5" t="n">
-        <v>85.59999999999999</v>
+        <v>85.45</v>
       </c>
       <c r="I5" t="n">
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="K5" t="n">
-        <v>5.1</v>
+        <v>5.09</v>
       </c>
       <c r="L5" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M5" t="n">
-        <v>41.8</v>
+        <v>43.27</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="O5" t="n">
-        <v>2.2</v>
+        <v>2.09</v>
       </c>
       <c r="P5" t="n">
-        <v>11.1</v>
+        <v>10.45</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.1</v>
+        <v>13.09</v>
       </c>
       <c r="R5" t="n">
-        <v>7.4</v>
+        <v>7.18</v>
       </c>
       <c r="S5" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="T5" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49.5</v>
+        <v>49</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.8</v>
+        <v>11.91</v>
       </c>
       <c r="AA5" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.7</v>
+        <v>20.64</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="AF5" t="n">
         <v>0.09</v>
@@ -2759,31 +2759,31 @@
         <v>1.91</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="BH5" t="n">
         <v>11.05</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.29</v>
+        <v>3.27</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.86</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.86</v>
+        <v>0.82</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="BP5" t="n">
         <v>4.86</v>
@@ -2795,34 +2795,34 @@
         <v>100</v>
       </c>
       <c r="BS5" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BT5" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BU5" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV5" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX5" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.49</v>
+        <v>2.54</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="CA5" t="n">
         <v>3.62</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CC5" t="n">
         <v>3.6</v>
@@ -2834,16 +2834,16 @@
         <v>1.32</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.59</v>
@@ -2852,13 +2852,13 @@
         <v>1.35</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.88</v>
+        <v>2.86</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO5" t="n">
         <v>1.19</v>
@@ -2891,13 +2891,13 @@
         <v>1.46</v>
       </c>
       <c r="CY5" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CZ5" t="n">
         <v>2.6</v>
       </c>
       <c r="DA5" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DB5" t="n">
         <v>1.23</v>
@@ -2912,76 +2912,76 @@
         <v>0.09</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.05</v>
+        <v>3.09</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.81</v>
+        <v>91.45</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM5" t="n">
-        <v>44.81</v>
+        <v>45.41</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.14</v>
+        <v>2.09</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.09</v>
+        <v>10.77</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.24</v>
+        <v>12.27</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.140000000000001</v>
+        <v>8</v>
       </c>
       <c r="DS5" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT5" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU5" t="n">
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.38</v>
+        <v>49.14</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX5" t="n">
         <v>12.91</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.57</v>
+        <v>21.5</v>
       </c>
       <c r="EB5" t="n">
         <v>1.42</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D6" t="n">
         <v>10</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="G6" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="H6" t="n">
+        <v>92.83</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.67</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M6" t="n">
+        <v>35.75</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="H6" t="n">
-        <v>93.45</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K6" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="M6" t="n">
-        <v>34.27</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.91</v>
-      </c>
       <c r="P6" t="n">
-        <v>12.64</v>
+        <v>12</v>
       </c>
       <c r="Q6" t="n">
-        <v>13.18</v>
+        <v>12.58</v>
       </c>
       <c r="R6" t="n">
-        <v>8.91</v>
+        <v>8.58</v>
       </c>
       <c r="S6" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="T6" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="U6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="V6" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>40.64</v>
+        <v>40.33</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.45</v>
+        <v>12.67</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.640000000000001</v>
+        <v>8.67</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.82</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.27</v>
+        <v>22.42</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.31</v>
+        <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AF6" t="n">
         <v>0.2</v>
@@ -3162,70 +3162,70 @@
         <v>2.6</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.57</v>
+        <v>10.68</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.76</v>
+        <v>2.82</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.57</v>
+        <v>0.64</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.62</v>
+        <v>0.68</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.71</v>
+        <v>4.73</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.86</v>
+        <v>5.95</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS6" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT6" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU6" t="n">
-        <v>23.81</v>
+        <v>27.27</v>
       </c>
       <c r="BV6" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CA6" t="n">
         <v>3.56</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.69</v>
+        <v>3.67</v>
       </c>
       <c r="CC6" t="n">
         <v>4</v>
@@ -3246,10 +3246,10 @@
         <v>1.47</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="CK6" t="n">
         <v>1.41</v>
@@ -3258,7 +3258,7 @@
         <v>1.79</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CN6" t="n">
         <v>2.08</v>
@@ -3270,25 +3270,25 @@
         <v>1.76</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CU6" t="n">
         <v>1.5</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CX6" t="n">
         <v>1.47</v>
@@ -3306,85 +3306,85 @@
         <v>1.24</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.88</v>
+        <v>2.91</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.95</v>
+        <v>1.87</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.38</v>
+        <v>2.41</v>
       </c>
       <c r="DH6" t="n">
-        <v>99.14</v>
+        <v>98.54000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ6" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.57</v>
+        <v>4.63</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="DM6" t="n">
-        <v>40.67</v>
+        <v>41.18</v>
       </c>
       <c r="DN6" t="n">
         <v>0.86</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.19</v>
+        <v>2.23</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.67</v>
+        <v>12.32</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.48</v>
+        <v>13.13</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.24</v>
+        <v>8.09</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.62</v>
+        <v>44.27</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.81</v>
+        <v>12.91</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.949999999999999</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.86</v>
+        <v>3.95</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.57</v>
+        <v>21.68</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="7">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C7" t="n">
         <v>10</v>
       </c>
       <c r="D7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E7" t="n">
         <v>0.1</v>
@@ -3484,139 +3484,139 @@
         <v>1.5</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AI7" t="n">
-        <v>95.36</v>
+        <v>96.42</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.09</v>
+        <v>6.08</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN7" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.64</v>
+        <v>0.67</v>
       </c>
       <c r="AP7" t="n">
-        <v>2.91</v>
+        <v>3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.91</v>
+        <v>10.25</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.91</v>
+        <v>14.83</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.73</v>
+        <v>53.92</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>15</v>
+        <v>14.75</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.73</v>
+        <v>9.5</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.27</v>
+        <v>5.25</v>
       </c>
       <c r="BD7" t="n">
-        <v>22</v>
+        <v>21.67</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="BG7" t="n">
         <v>2.86</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.76</v>
+        <v>10.77</v>
       </c>
       <c r="BI7" t="n">
         <v>2.86</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BL7" t="n">
-        <v>1</v>
+        <v>0.95</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="BO7" t="n">
         <v>1.14</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.38</v>
+        <v>5.36</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.62</v>
+        <v>4.68</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS7" t="n">
-        <v>76.19</v>
+        <v>77.27</v>
       </c>
       <c r="BT7" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BU7" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV7" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX7" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>1.95</v>
@@ -3628,37 +3628,37 @@
         <v>3.42</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="CE7" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CH7" t="n">
         <v>1.45</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CK7" t="n">
         <v>1.3</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="CM7" t="n">
         <v>2.69</v>
@@ -3670,10 +3670,10 @@
         <v>1.14</v>
       </c>
       <c r="CP7" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR7" t="n">
         <v>1.37</v>
@@ -3688,7 +3688,7 @@
         <v>1.53</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW7" t="n">
         <v>1.6</v>
@@ -3700,7 +3700,7 @@
         <v>1.68</v>
       </c>
       <c r="CZ7" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="DA7" t="n">
         <v>2.16</v>
@@ -3718,43 +3718,43 @@
         <v>0.09</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.62</v>
+        <v>2.59</v>
       </c>
       <c r="DH7" t="n">
-        <v>99.52</v>
+        <v>99.91</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.19</v>
+        <v>6.18</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.1</v>
+        <v>52.36</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.57</v>
+        <v>0.59</v>
       </c>
       <c r="DO7" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="DP7" t="n">
-        <v>11.05</v>
+        <v>10.68</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.48</v>
+        <v>14.45</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.86</v>
+        <v>6.87</v>
       </c>
       <c r="DS7" t="n">
         <v>0.14</v>
@@ -3766,28 +3766,28 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.43</v>
+        <v>54.5</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.71</v>
+        <v>15.55</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.53</v>
+        <v>10.36</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.19</v>
+        <v>5.18</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.9</v>
+        <v>22.68</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>2.05</v>
       </c>
     </row>
     <row r="8">
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D8" t="n">
         <v>10</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G8" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="H8" t="n">
-        <v>91.45</v>
+        <v>92.67</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.18</v>
+        <v>-0.17</v>
       </c>
       <c r="J8" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="K8" t="n">
-        <v>4.18</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="M8" t="n">
-        <v>50.64</v>
+        <v>51.75</v>
       </c>
       <c r="N8" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="O8" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="P8" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.27</v>
+        <v>11.33</v>
       </c>
       <c r="R8" t="n">
-        <v>6.36</v>
+        <v>6.17</v>
       </c>
       <c r="S8" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.55</v>
+        <v>51.33</v>
       </c>
       <c r="Y8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.09</v>
+        <v>12.08</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.449999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.64</v>
+        <v>3.58</v>
       </c>
       <c r="AC8" t="n">
-        <v>19.82</v>
+        <v>21.92</v>
       </c>
       <c r="AD8" t="n">
         <v>1.39</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="AF8" t="n">
         <v>0.1</v>
@@ -3968,70 +3968,70 @@
         <v>2.5</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.67</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.43</v>
+        <v>2.32</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.29</v>
+        <v>0.27</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.48</v>
+        <v>0.45</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.67</v>
+        <v>1.59</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.76</v>
+        <v>3.64</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.86</v>
+        <v>4.77</v>
       </c>
       <c r="BR8" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS8" t="n">
-        <v>71.43000000000001</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT8" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX8" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY8" t="n">
-        <v>2.39</v>
+        <v>2.36</v>
       </c>
       <c r="BZ8" t="n">
-        <v>2.47</v>
+        <v>2.42</v>
       </c>
       <c r="CA8" t="n">
         <v>3.64</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CC8" t="n">
         <v>3.45</v>
@@ -4043,31 +4043,31 @@
         <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.43</v>
+        <v>2.45</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.2</v>
+        <v>3.18</v>
       </c>
       <c r="CH8" t="n">
         <v>1.51</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CJ8" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK8" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.05</v>
+        <v>2.04</v>
       </c>
       <c r="CO8" t="n">
         <v>1.19</v>
@@ -4076,25 +4076,25 @@
         <v>1.65</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CR8" t="n">
         <v>1.37</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CU8" t="n">
         <v>1.54</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CW8" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX8" t="n">
         <v>1.49</v>
@@ -4112,52 +4112,52 @@
         <v>1.21</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="DE8" t="n">
         <v>0.05</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.53</v>
+        <v>1.5</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DH8" t="n">
-        <v>92.95</v>
+        <v>93.55</v>
       </c>
       <c r="DI8" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.81</v>
+        <v>2.82</v>
       </c>
       <c r="DK8" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.1</v>
+        <v>46.91</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.81</v>
+        <v>12.55</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.71</v>
+        <v>11.73</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.86</v>
+        <v>7.68</v>
       </c>
       <c r="DS8" t="n">
         <v>0.05</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.62</v>
+        <v>48.63</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.71</v>
+        <v>12.68</v>
       </c>
       <c r="DY8" t="n">
         <v>9.050000000000001</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.67</v>
+        <v>3.63</v>
       </c>
       <c r="EA8" t="n">
-        <v>19.91</v>
+        <v>21.05</v>
       </c>
       <c r="EB8" t="n">
         <v>1.4</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="9">
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" t="n">
         <v>10</v>
       </c>
       <c r="D9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E9" t="n">
         <v>0.3</v>
@@ -4293,136 +4293,136 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH9" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>75.92</v>
+      </c>
+      <c r="AJ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>4.08</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>34.67</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AP9" t="n">
         <v>2</v>
       </c>
-      <c r="AI9" t="n">
-        <v>72.55</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>3.91</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>33.36</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>1.91</v>
-      </c>
       <c r="AQ9" t="n">
-        <v>13.55</v>
+        <v>13.58</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.64</v>
+        <v>11.83</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.73</v>
+        <v>8.92</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="AU9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>47.5</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>11.92</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>22.67</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF9" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="BG9" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BH9" t="n">
+        <v>10.05</v>
+      </c>
+      <c r="BI9" t="n">
+        <v>3.86</v>
+      </c>
+      <c r="BJ9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BK9" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>1</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="BO9" t="n">
         <v>1.64</v>
       </c>
-      <c r="AV9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>0.27</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>46</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>11.73</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>7.09</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>4.64</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>22.27</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BH9" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="BI9" t="n">
-        <v>4</v>
-      </c>
-      <c r="BJ9" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BK9" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BL9" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="BM9" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BN9" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BO9" t="n">
-        <v>1.67</v>
-      </c>
       <c r="BP9" t="n">
-        <v>4.19</v>
+        <v>4.18</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.38</v>
+        <v>5.27</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS9" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT9" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BU9" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV9" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BW9" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BX9" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY9" t="n">
         <v>2.9</v>
@@ -4431,16 +4431,16 @@
         <v>3.34</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.76</v>
+        <v>3.78</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.97</v>
+        <v>3.98</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.16</v>
+        <v>4.2</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.96</v>
+        <v>4.95</v>
       </c>
       <c r="CE9" t="n">
         <v>1.29</v>
@@ -4458,7 +4458,7 @@
         <v>2.35</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CK9" t="n">
         <v>1.37</v>
@@ -4479,7 +4479,7 @@
         <v>1.61</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
@@ -4524,43 +4524,43 @@
         <v>0.14</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.09</v>
+        <v>1.13</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.24</v>
+        <v>2.27</v>
       </c>
       <c r="DH9" t="n">
-        <v>78.76000000000001</v>
+        <v>80.31999999999999</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.43</v>
+        <v>4.5</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.76</v>
+        <v>34.46</v>
       </c>
       <c r="DN9" t="n">
         <v>1.14</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.1</v>
+        <v>12.18</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.19</v>
+        <v>13.23</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.619999999999999</v>
+        <v>8.73</v>
       </c>
       <c r="DS9" t="n">
         <v>0.14</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.62</v>
+        <v>46.45</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.29</v>
+        <v>11.41</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.24</v>
+        <v>7.45</v>
       </c>
       <c r="DZ9" t="n">
-        <v>4.05</v>
+        <v>3.96</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.9</v>
+        <v>21.18</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.15</v>
+        <v>2.18</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C10" t="n">
         <v>10</v>
       </c>
       <c r="D10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E10" t="n">
         <v>0.2</v>
@@ -4693,139 +4693,139 @@
         <v>1.5</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AI10" t="n">
-        <v>101.18</v>
+        <v>100.67</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.64</v>
+        <v>4.75</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN10" t="n">
-        <v>45.18</v>
+        <v>45.17</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.73</v>
+        <v>13.33</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.45</v>
+        <v>13.5</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.36</v>
+        <v>6.33</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AU10" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>55.45</v>
+        <v>54.58</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.82</v>
+        <v>12.75</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.73</v>
+        <v>7.5</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.09</v>
+        <v>5.25</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.18</v>
+        <v>19.25</v>
       </c>
       <c r="BE10" t="n">
         <v>1.5</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.43</v>
+        <v>9.5</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.14</v>
+        <v>3.23</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.9</v>
+        <v>0.95</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.24</v>
+        <v>4.23</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.19</v>
+        <v>5.27</v>
       </c>
       <c r="BR10" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS10" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BT10" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BU10" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BV10" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY10" t="n">
         <v>1.81</v>
@@ -4834,13 +4834,13 @@
         <v>1.9</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB10" t="n">
         <v>3.79</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CD10" t="n">
         <v>2.42</v>
@@ -4849,13 +4849,13 @@
         <v>1.31</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI10" t="n">
         <v>2.29</v>
@@ -4867,13 +4867,13 @@
         <v>1.34</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.92</v>
+        <v>2.91</v>
       </c>
       <c r="CN10" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO10" t="n">
         <v>1.18</v>
@@ -4882,7 +4882,7 @@
         <v>1.66</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4891,7 +4891,7 @@
         <v>2.53</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.29</v>
+        <v>3.3</v>
       </c>
       <c r="CU10" t="n">
         <v>1.56</v>
@@ -4903,16 +4903,16 @@
         <v>1.6</v>
       </c>
       <c r="CX10" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ10" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB10" t="n">
         <v>1.21</v>
@@ -4924,46 +4924,46 @@
         <v>2.66</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.43</v>
+        <v>1.36</v>
       </c>
       <c r="DG10" t="n">
         <v>3</v>
       </c>
       <c r="DH10" t="n">
-        <v>106.24</v>
+        <v>105.73</v>
       </c>
       <c r="DI10" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>2.05</v>
+        <v>1.95</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.43</v>
+        <v>0.41</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.52</v>
+        <v>51.23</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.43</v>
+        <v>13.23</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.52</v>
+        <v>13.55</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.19</v>
+        <v>6.18</v>
       </c>
       <c r="DS10" t="n">
         <v>0.14</v>
@@ -4975,28 +4975,28 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.33</v>
+        <v>55.82</v>
       </c>
       <c r="DW10" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>15.1</v>
+        <v>14.95</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.57</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.52</v>
+        <v>5.59</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.48</v>
+        <v>19.5</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="EC10" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
     </row>
     <row r="11">
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D11" t="n">
         <v>10</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="G11" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="H11" t="n">
-        <v>95.18000000000001</v>
+        <v>96</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="K11" t="n">
-        <v>5.09</v>
+        <v>5.08</v>
       </c>
       <c r="L11" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="M11" t="n">
-        <v>44.55</v>
+        <v>44.75</v>
       </c>
       <c r="N11" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O11" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="P11" t="n">
-        <v>12.36</v>
+        <v>12.42</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.27</v>
+        <v>10.25</v>
       </c>
       <c r="R11" t="n">
-        <v>9.18</v>
+        <v>8.92</v>
       </c>
       <c r="S11" t="n">
-        <v>0.91</v>
+        <v>1.08</v>
       </c>
       <c r="T11" t="n">
-        <v>0.82</v>
+        <v>0.92</v>
       </c>
       <c r="U11" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="V11" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>48.91</v>
+        <v>49.42</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.73</v>
+        <v>12.92</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.09</v>
+        <v>8.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.64</v>
+        <v>4.83</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.55</v>
+        <v>20</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="AE11" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="AF11" t="n">
         <v>0.1</v>
@@ -5177,70 +5177,70 @@
         <v>2.9</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.19</v>
+        <v>10.23</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.29</v>
+        <v>2.41</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.48</v>
+        <v>0.55</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.33</v>
+        <v>0.41</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.81</v>
+        <v>4.91</v>
       </c>
       <c r="BR11" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BS11" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BT11" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU11" t="n">
-        <v>19.05</v>
+        <v>22.73</v>
       </c>
       <c r="BV11" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX11" t="n">
-        <v>33.33</v>
+        <v>36.36</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.82</v>
+        <v>1.91</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.01</v>
+        <v>2.08</v>
       </c>
       <c r="CA11" t="n">
         <v>3.36</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CC11" t="n">
         <v>2.69</v>
@@ -5252,10 +5252,10 @@
         <v>1.25</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.29</v>
+        <v>2.3</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.07</v>
+        <v>3.08</v>
       </c>
       <c r="CH11" t="n">
         <v>1.45</v>
@@ -5267,22 +5267,22 @@
         <v>1.48</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CM11" t="n">
         <v>2.69</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="CO11" t="n">
         <v>1.13</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CQ11" t="n">
         <v>2.44</v>
@@ -5294,7 +5294,7 @@
         <v>2.52</v>
       </c>
       <c r="CT11" t="n">
-        <v>3.31</v>
+        <v>3.32</v>
       </c>
       <c r="CU11" t="n">
         <v>1.56</v>
@@ -5306,13 +5306,13 @@
         <v>1.6</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CY11" t="n">
         <v>1.69</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="DA11" t="n">
         <v>2.15</v>
@@ -5324,82 +5324,82 @@
         <v>1.68</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="DE11" t="n">
         <v>0.09</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.81</v>
+        <v>1.77</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DH11" t="n">
-        <v>94.38</v>
+        <v>94.86</v>
       </c>
       <c r="DI11" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.72</v>
+        <v>2.64</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.57</v>
+        <v>4.59</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.72</v>
+        <v>45.77</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.19</v>
+        <v>2.14</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.33</v>
+        <v>13.32</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.47</v>
+        <v>11.41</v>
       </c>
       <c r="DR11" t="n">
-        <v>9.09</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.09</v>
+        <v>0.14</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.33</v>
+        <v>48.64</v>
       </c>
       <c r="DW11" t="n">
         <v>0.14</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.38</v>
+        <v>12.5</v>
       </c>
       <c r="DY11" t="n">
         <v>7.95</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.43</v>
+        <v>4.54</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.62</v>
+        <v>20.82</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="12">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D13" t="n">
         <v>10</v>
       </c>
       <c r="E13" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="F13" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="G13" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="H13" t="n">
-        <v>103.36</v>
+        <v>101.5</v>
       </c>
       <c r="I13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="K13" t="n">
-        <v>5.64</v>
+        <v>5.25</v>
       </c>
       <c r="L13" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="M13" t="n">
-        <v>48.27</v>
+        <v>47.92</v>
       </c>
       <c r="N13" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="O13" t="n">
-        <v>2.55</v>
+        <v>2.42</v>
       </c>
       <c r="P13" t="n">
-        <v>11.55</v>
+        <v>11.75</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.55</v>
+        <v>13.58</v>
       </c>
       <c r="R13" t="n">
-        <v>8.73</v>
+        <v>8.5</v>
       </c>
       <c r="S13" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="T13" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="U13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>49.27</v>
+        <v>48.17</v>
       </c>
       <c r="Y13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.64</v>
+        <v>15.42</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.449999999999999</v>
+        <v>9.5</v>
       </c>
       <c r="AB13" t="n">
-        <v>6.18</v>
+        <v>5.92</v>
       </c>
       <c r="AC13" t="n">
-        <v>22.73</v>
+        <v>23.67</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="AF13" t="n">
         <v>0</v>
@@ -5983,70 +5983,70 @@
         <v>2.6</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.81</v>
+        <v>9.68</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.14</v>
+        <v>3.05</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BN13" t="n">
-        <v>2</v>
+        <v>1.91</v>
       </c>
       <c r="BO13" t="n">
         <v>1.14</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.67</v>
+        <v>4.64</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS13" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BT13" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU13" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BV13" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.45</v>
+        <v>2.38</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.54</v>
+        <v>2.47</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="CC13" t="n">
         <v>3.06</v>
@@ -6061,10 +6061,10 @@
         <v>2.45</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CH13" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI13" t="n">
         <v>2.35</v>
@@ -6076,7 +6076,7 @@
         <v>1.36</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM13" t="n">
         <v>2.84</v>
@@ -6088,16 +6088,16 @@
         <v>1.19</v>
       </c>
       <c r="CP13" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CR13" t="n">
         <v>1.36</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.57</v>
+        <v>2.56</v>
       </c>
       <c r="CT13" t="n">
         <v>3.28</v>
@@ -6106,10 +6106,10 @@
         <v>1.54</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.5</v>
+        <v>2.49</v>
       </c>
       <c r="CW13" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX13" t="n">
         <v>1.49</v>
@@ -6127,52 +6127,52 @@
         <v>1.21</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.19</v>
+        <v>2.09</v>
       </c>
       <c r="DH13" t="n">
-        <v>96.43000000000001</v>
+        <v>95.73</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.86</v>
+        <v>2.82</v>
       </c>
       <c r="DK13" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.38</v>
+        <v>0.41</v>
       </c>
       <c r="DM13" t="n">
-        <v>42.71</v>
+        <v>42.77</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.24</v>
+        <v>12.32</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.67</v>
+        <v>13.68</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.1</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0.14</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>47.33</v>
+        <v>46.82</v>
       </c>
       <c r="DW13" t="n">
         <v>0.09</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.43</v>
+        <v>13.41</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.470000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.95</v>
+        <v>4.87</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.29</v>
+        <v>21.87</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C14" t="n">
         <v>10</v>
       </c>
       <c r="D14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E14" t="n">
         <v>0.2</v>
@@ -6305,139 +6305,139 @@
         <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.09</v>
+        <v>3.17</v>
       </c>
       <c r="AI14" t="n">
-        <v>89.73</v>
+        <v>91.25</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.18</v>
+        <v>2.25</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.45</v>
+        <v>5.5</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN14" t="n">
-        <v>41.55</v>
+        <v>42.17</v>
       </c>
       <c r="AO14" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="AP14" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="AQ14" t="n">
+        <v>11.58</v>
+      </c>
+      <c r="AR14" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="AS14" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>49.58</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>12.42</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>9.17</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>19.25</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>10.18</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.32</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="BM14" t="n">
         <v>0.91</v>
       </c>
-      <c r="AP14" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="AQ14" t="n">
-        <v>11.36</v>
-      </c>
-      <c r="AR14" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="AS14" t="n">
-        <v>8.73</v>
-      </c>
-      <c r="AT14" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>48.91</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>12.55</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>9.18</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>19.09</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>10.19</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.9</v>
-      </c>
       <c r="BN14" t="n">
-        <v>2.05</v>
+        <v>2.09</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.14</v>
+        <v>1.23</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.52</v>
+        <v>4.45</v>
       </c>
       <c r="BQ14" t="n">
-        <v>4.95</v>
+        <v>5.05</v>
       </c>
       <c r="BR14" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS14" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT14" t="n">
-        <v>66.67</v>
+        <v>68.18000000000001</v>
       </c>
       <c r="BU14" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BV14" t="n">
-        <v>28.57</v>
+        <v>31.82</v>
       </c>
       <c r="BW14" t="n">
-        <v>4.76</v>
+        <v>9.09</v>
       </c>
       <c r="BX14" t="n">
-        <v>52.38</v>
+        <v>54.55</v>
       </c>
       <c r="BY14" t="n">
         <v>2.55</v>
@@ -6446,31 +6446,31 @@
         <v>2.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.7</v>
+        <v>3.72</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.87</v>
+        <v>3.88</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.73</v>
+        <v>3.75</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.05</v>
+        <v>4.08</v>
       </c>
       <c r="CE14" t="n">
         <v>1.29</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CH14" t="n">
         <v>1.55</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.54</v>
@@ -6479,10 +6479,10 @@
         <v>1.36</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CN14" t="n">
         <v>2.17</v>
@@ -6491,10 +6491,10 @@
         <v>1.17</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.47</v>
+        <v>2.46</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
@@ -6509,10 +6509,10 @@
         <v>1.58</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CX14" t="n">
         <v>1.46</v>
@@ -6536,79 +6536,79 @@
         <v>2.59</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.48</v>
+        <v>2.55</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.56999999999999</v>
+        <v>85.64</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DK14" t="n">
-        <v>5</v>
+        <v>5.05</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM14" t="n">
-        <v>42.15</v>
+        <v>42.46</v>
       </c>
       <c r="DN14" t="n">
         <v>1.05</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.62</v>
+        <v>12.68</v>
       </c>
       <c r="DQ14" t="n">
-        <v>11</v>
+        <v>10.95</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.67</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.95</v>
+        <v>48.36</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.91</v>
+        <v>11.87</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.9</v>
+        <v>7.96</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.95</v>
+        <v>18.09</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.57</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="15">
@@ -7017,10 +7017,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D16" t="n">
         <v>10</v>
@@ -7029,82 +7029,82 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="G16" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="H16" t="n">
-        <v>97.55</v>
+        <v>95.42</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="K16" t="n">
-        <v>5.18</v>
+        <v>5.08</v>
       </c>
       <c r="L16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M16" t="n">
-        <v>45.55</v>
+        <v>44.33</v>
       </c>
       <c r="N16" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O16" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="P16" t="n">
-        <v>10.91</v>
+        <v>10.83</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.91</v>
+        <v>13.92</v>
       </c>
       <c r="R16" t="n">
-        <v>7.64</v>
+        <v>7.92</v>
       </c>
       <c r="S16" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="T16" t="n">
-        <v>1.36</v>
+        <v>1.67</v>
       </c>
       <c r="U16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.91</v>
+        <v>50.25</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>14.09</v>
+        <v>13.92</v>
       </c>
       <c r="AA16" t="n">
-        <v>9</v>
+        <v>8.58</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.09</v>
+        <v>5.33</v>
       </c>
       <c r="AC16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AF16" t="n">
         <v>0.1</v>
@@ -7188,70 +7188,70 @@
         <v>2.6</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="BH16" t="n">
         <v>9.949999999999999</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.57</v>
+        <v>2.73</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.52</v>
+        <v>0.64</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BL16" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BN16" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BO16" t="n">
         <v>1</v>
       </c>
-      <c r="BM16" t="n">
-        <v>0.67</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BO16" t="n">
-        <v>0.9</v>
-      </c>
       <c r="BP16" t="n">
-        <v>4.48</v>
+        <v>4.41</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.48</v>
+        <v>5.55</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS16" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT16" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BU16" t="n">
-        <v>14.29</v>
+        <v>18.18</v>
       </c>
       <c r="BV16" t="n">
-        <v>9.52</v>
+        <v>13.64</v>
       </c>
       <c r="BW16" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BX16" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY16" t="n">
+        <v>2.37</v>
+      </c>
+      <c r="BZ16" t="n">
         <v>2.43</v>
       </c>
-      <c r="BZ16" t="n">
-        <v>2.5</v>
-      </c>
       <c r="CA16" t="n">
-        <v>3.53</v>
+        <v>3.56</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.69</v>
+        <v>3.71</v>
       </c>
       <c r="CC16" t="n">
         <v>3.22</v>
@@ -7263,16 +7263,16 @@
         <v>1.32</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="CH16" t="n">
         <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.59</v>
@@ -7281,22 +7281,22 @@
         <v>1.36</v>
       </c>
       <c r="CL16" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM16" t="n">
         <v>2.87</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CO16" t="n">
         <v>1.2</v>
       </c>
       <c r="CP16" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7335,82 +7335,82 @@
         <v>1.72</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="DE16" t="n">
         <v>0.05</v>
       </c>
       <c r="DF16" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="DH16" t="n">
-        <v>95.05</v>
+        <v>94</v>
       </c>
       <c r="DI16" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.81</v>
+        <v>2.73</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.52</v>
+        <v>5.45</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.47</v>
+        <v>0.46</v>
       </c>
       <c r="DM16" t="n">
-        <v>47</v>
+        <v>46.27</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.95</v>
+        <v>11.86</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.86</v>
+        <v>13.87</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.86</v>
+        <v>8</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>50.29</v>
+        <v>49.95</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.09</v>
+        <v>13.05</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.33</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.76</v>
+        <v>4.91</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.86</v>
+        <v>20.27</v>
       </c>
       <c r="EB16" t="n">
         <v>1.5</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="17">
@@ -7823,13 +7823,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C18" t="n">
         <v>11</v>
       </c>
       <c r="D18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7913,139 +7913,139 @@
         <v>2.27</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AI18" t="n">
-        <v>84.90000000000001</v>
+        <v>84.73</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK18" t="n">
         <v>4</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.9</v>
+        <v>3.73</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AN18" t="n">
-        <v>32.3</v>
+        <v>32.18</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AQ18" t="n">
-        <v>13</v>
+        <v>12.64</v>
       </c>
       <c r="AR18" t="n">
-        <v>13.7</v>
+        <v>13.27</v>
       </c>
       <c r="AS18" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="AU18" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>56.91</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>11.09</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>7.55</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BD18" t="n">
+        <v>21.09</v>
+      </c>
+      <c r="BE18" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="BF18" t="n">
+        <v>3.64</v>
+      </c>
+      <c r="BG18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BH18" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="BI18" t="n">
+        <v>2.59</v>
+      </c>
+      <c r="BJ18" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="BK18" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="BL18" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="BM18" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="BN18" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="BO18" t="n">
         <v>1</v>
       </c>
-      <c r="AV18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>57.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>11.6</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>7.9</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>20.2</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="BG18" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BH18" t="n">
-        <v>10.05</v>
-      </c>
-      <c r="BI18" t="n">
-        <v>2.71</v>
-      </c>
-      <c r="BJ18" t="n">
-        <v>0.62</v>
-      </c>
-      <c r="BK18" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="BL18" t="n">
-        <v>0.95</v>
-      </c>
-      <c r="BM18" t="n">
-        <v>0.71</v>
-      </c>
-      <c r="BN18" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="BO18" t="n">
-        <v>1.05</v>
-      </c>
       <c r="BP18" t="n">
-        <v>4.81</v>
+        <v>4.64</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.24</v>
+        <v>5.14</v>
       </c>
       <c r="BR18" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS18" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT18" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU18" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV18" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>76.19</v>
+        <v>72.73</v>
       </c>
       <c r="BY18" t="n">
         <v>2.68</v>
@@ -8060,55 +8060,55 @@
         <v>3.59</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.87</v>
+        <v>3.9</v>
       </c>
       <c r="CE18" t="n">
         <v>1.34</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.53</v>
+        <v>2.55</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.06</v>
+        <v>3.05</v>
       </c>
       <c r="CH18" t="n">
         <v>1.46</v>
       </c>
       <c r="CI18" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CJ18" t="n">
         <v>1.63</v>
       </c>
       <c r="CK18" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="CN18" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="CO18" t="n">
         <v>1.22</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.79</v>
+        <v>2.81</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="CT18" t="n">
         <v>3.17</v>
@@ -8120,7 +8120,7 @@
         <v>2.27</v>
       </c>
       <c r="CW18" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX18" t="n">
         <v>1.51</v>
@@ -8135,55 +8135,55 @@
         <v>2</v>
       </c>
       <c r="DB18" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="DC18" t="n">
         <v>1.83</v>
       </c>
       <c r="DD18" t="n">
-        <v>3</v>
+        <v>3.01</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF18" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="DG18" t="n">
         <v>1.95</v>
       </c>
-      <c r="DG18" t="n">
-        <v>2</v>
-      </c>
       <c r="DH18" t="n">
-        <v>88.23999999999999</v>
+        <v>88</v>
       </c>
       <c r="DI18" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.19</v>
+        <v>4.09</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.24</v>
+        <v>0.27</v>
       </c>
       <c r="DM18" t="n">
-        <v>35.33</v>
+        <v>35.14</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.19</v>
+        <v>2.13</v>
       </c>
       <c r="DP18" t="n">
-        <v>14</v>
+        <v>13.78</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.95</v>
+        <v>13.72</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.62</v>
+        <v>7.78</v>
       </c>
       <c r="DS18" t="n">
         <v>0.09</v>
@@ -8195,28 +8195,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>56.33</v>
+        <v>56.09</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.43</v>
+        <v>12.13</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.24</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.19</v>
+        <v>4.1</v>
       </c>
       <c r="EA18" t="n">
-        <v>20.85</v>
+        <v>21.27</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.9</v>
+        <v>2.95</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E2" t="n">
         <v>0.18</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.9</v>
+        <v>3.64</v>
       </c>
       <c r="AI2" t="n">
-        <v>98.7</v>
+        <v>99.91</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.9</v>
+        <v>5.73</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.4</v>
+        <v>0.55</v>
       </c>
       <c r="AN2" t="n">
         <v>51</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="AP2" t="n">
-        <v>2</v>
+        <v>2.09</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.3</v>
+        <v>13.64</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.7</v>
+        <v>14.09</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.8</v>
+        <v>7.36</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.6</v>
+        <v>1.45</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.5</v>
+        <v>48.64</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA2" t="n">
-        <v>12.9</v>
+        <v>13.09</v>
       </c>
       <c r="BB2" t="n">
-        <v>9</v>
+        <v>9.18</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.7</v>
+        <v>23.55</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="BG2" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.67</v>
+        <v>10.55</v>
       </c>
       <c r="BI2" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.43</v>
+        <v>0.45</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BP2" t="n">
         <v>3.95</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.67</v>
+        <v>6.55</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS2" t="n">
-        <v>85.70999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.38</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>38.1</v>
+        <v>36.36</v>
       </c>
       <c r="BV2" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BX2" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY2" t="n">
         <v>2.11</v>
@@ -1610,7 +1610,7 @@
         <v>2.21</v>
       </c>
       <c r="CA2" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CB2" t="n">
         <v>3.66</v>
@@ -1619,19 +1619,19 @@
         <v>3.16</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CE2" t="n">
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="CI2" t="n">
         <v>2.33</v>
@@ -1640,16 +1640,16 @@
         <v>1.57</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CO2" t="n">
         <v>1.19</v>
@@ -1658,13 +1658,13 @@
         <v>1.68</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CR2" t="n">
         <v>1.39</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT2" t="n">
         <v>3.13</v>
@@ -1694,7 +1694,7 @@
         <v>1.22</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD2" t="n">
         <v>2.74</v>
@@ -1703,76 +1703,76 @@
         <v>0.09</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.09</v>
+        <v>3.95</v>
       </c>
       <c r="DH2" t="n">
-        <v>100.62</v>
+        <v>101.14</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.24</v>
+        <v>6.14</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.28</v>
+        <v>0.37</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.24</v>
+        <v>50.28</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.24</v>
+        <v>13.41</v>
       </c>
       <c r="DQ2" t="n">
-        <v>14.24</v>
+        <v>13.96</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.29</v>
+        <v>7.55</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.57</v>
+        <v>52</v>
       </c>
       <c r="DW2" t="n">
         <v>0.09</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.86</v>
+        <v>13.91</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.57</v>
+        <v>9.630000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.29</v>
+        <v>4.28</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.33</v>
+        <v>23.28</v>
       </c>
       <c r="EB2" t="n">
         <v>1.54</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
     </row>
     <row r="3">
@@ -1782,61 +1782,61 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>3</v>
+        <v>2.91</v>
       </c>
       <c r="H3" t="n">
-        <v>104.4</v>
+        <v>103.91</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="J3" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="K3" t="n">
-        <v>5.9</v>
+        <v>5.73</v>
       </c>
       <c r="L3" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M3" t="n">
-        <v>54.3</v>
+        <v>54.18</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.9</v>
+        <v>2.82</v>
       </c>
       <c r="P3" t="n">
-        <v>14.7</v>
+        <v>14.82</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.4</v>
+        <v>10.27</v>
       </c>
       <c r="R3" t="n">
-        <v>8.300000000000001</v>
+        <v>8.09</v>
       </c>
       <c r="S3" t="n">
-        <v>1.2</v>
+        <v>1.09</v>
       </c>
       <c r="T3" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -1848,28 +1848,28 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.6</v>
+        <v>46.64</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.7</v>
+        <v>17.18</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.5</v>
+        <v>11.64</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.2</v>
+        <v>5.55</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.5</v>
+        <v>21.64</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.81</v>
+        <v>1.86</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AF3" t="n">
         <v>0.18</v>
@@ -1953,70 +1953,70 @@
         <v>3.09</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.81</v>
+        <v>11.73</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.48</v>
+        <v>1.41</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.24</v>
+        <v>1.18</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.81</v>
+        <v>5.73</v>
       </c>
       <c r="BQ3" t="n">
         <v>6</v>
       </c>
       <c r="BR3" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS3" t="n">
-        <v>80.95</v>
+        <v>77.27</v>
       </c>
       <c r="BT3" t="n">
-        <v>47.62</v>
+        <v>45.45</v>
       </c>
       <c r="BU3" t="n">
-        <v>23.81</v>
+        <v>22.73</v>
       </c>
       <c r="BV3" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX3" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.19</v>
+        <v>2.22</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.3</v>
+        <v>2.35</v>
       </c>
       <c r="CA3" t="n">
         <v>3.6</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CC3" t="n">
         <v>3.01</v>
@@ -2061,88 +2061,88 @@
         <v>1.66</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CT3" t="n">
         <v>3.22</v>
       </c>
       <c r="CU3" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV3" t="n">
         <v>2.44</v>
       </c>
       <c r="CW3" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX3" t="n">
         <v>1.45</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CZ3" t="n">
         <v>2.59</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.24</v>
+        <v>2.18</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.62</v>
+        <v>93.86</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.86</v>
+        <v>5.78</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.53</v>
+        <v>0.5</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.33</v>
+        <v>46.64</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.91</v>
+        <v>2.86</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.72</v>
+        <v>13.82</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.67</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.859999999999999</v>
+        <v>8.720000000000001</v>
       </c>
       <c r="DS3" t="n">
         <v>0.09</v>
@@ -2154,28 +2154,28 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.53</v>
+        <v>45.6</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.24</v>
+        <v>14.59</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.9</v>
+        <v>10.04</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.34</v>
+        <v>4.55</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.38</v>
+        <v>22.41</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.19</v>
+        <v>3.14</v>
       </c>
     </row>
     <row r="4">
@@ -3869,10 +3869,10 @@
         <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.08</v>
+        <v>12.17</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.5</v>
+        <v>8.58</v>
       </c>
       <c r="AB8" t="n">
         <v>3.58</v>
@@ -3881,7 +3881,7 @@
         <v>21.92</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="AE8" t="n">
         <v>2.83</v>
@@ -4175,10 +4175,10 @@
         <v>0.13</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.68</v>
+        <v>12.73</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.050000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="DZ8" t="n">
         <v>3.63</v>
@@ -5078,10 +5078,10 @@
         <v>0.25</v>
       </c>
       <c r="Z11" t="n">
-        <v>12.92</v>
+        <v>13.08</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.08</v>
+        <v>8.25</v>
       </c>
       <c r="AB11" t="n">
         <v>4.83</v>
@@ -5090,7 +5090,7 @@
         <v>20</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="AE11" t="n">
         <v>2</v>
@@ -5384,10 +5384,10 @@
         <v>0.14</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.5</v>
+        <v>12.59</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.95</v>
+        <v>8.050000000000001</v>
       </c>
       <c r="DZ11" t="n">
         <v>4.54</v>
@@ -5396,7 +5396,7 @@
         <v>20.82</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="EC11" t="n">
         <v>2.41</v>
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D12" t="n">
         <v>11</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.1</v>
+        <v>1.18</v>
       </c>
       <c r="G12" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="H12" t="n">
-        <v>90.40000000000001</v>
+        <v>88.81999999999999</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="K12" t="n">
-        <v>5.3</v>
+        <v>5.64</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="M12" t="n">
-        <v>41.6</v>
+        <v>42.55</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7</v>
+        <v>0.73</v>
       </c>
       <c r="O12" t="n">
-        <v>2.3</v>
+        <v>2.27</v>
       </c>
       <c r="P12" t="n">
-        <v>12.1</v>
+        <v>12.55</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.9</v>
+        <v>14.55</v>
       </c>
       <c r="R12" t="n">
-        <v>7.6</v>
+        <v>7.55</v>
       </c>
       <c r="S12" t="n">
-        <v>1</v>
+        <v>1.09</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.5</v>
+        <v>52.64</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>13</v>
+        <v>12.73</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.800000000000001</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.2</v>
+        <v>4.18</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.3</v>
+        <v>20.09</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="AF12" t="n">
         <v>0.09</v>
@@ -5580,70 +5580,70 @@
         <v>3.36</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.38</v>
+        <v>10.59</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.52</v>
+        <v>0.59</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.59</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.33</v>
+        <v>4.41</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6</v>
+        <v>6.14</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT12" t="n">
-        <v>47.62</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX12" t="n">
-        <v>61.9</v>
+        <v>63.64</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.15</v>
+        <v>2.23</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.22</v>
+        <v>2.29</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.64</v>
+        <v>3.62</v>
       </c>
       <c r="CC12" t="n">
         <v>3.05</v>
@@ -5655,40 +5655,40 @@
         <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.14</v>
+        <v>3.12</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.59</v>
       </c>
       <c r="CK12" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL12" t="n">
         <v>1.7</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="CO12" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.71</v>
+        <v>1.73</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.68</v>
+        <v>2.71</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
@@ -5703,19 +5703,19 @@
         <v>1.52</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CX12" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CZ12" t="n">
-        <v>2.56</v>
+        <v>2.54</v>
       </c>
       <c r="DA12" t="n">
         <v>2.13</v>
@@ -5724,85 +5724,85 @@
         <v>1.24</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.77</v>
+        <v>1.79</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.85</v>
+        <v>2.9</v>
       </c>
       <c r="DE12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF12" t="n">
         <v>1.91</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.81</v>
+        <v>3</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.90000000000001</v>
+        <v>83.41</v>
       </c>
       <c r="DI12" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.67</v>
+        <v>4.86</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM12" t="n">
-        <v>37.28</v>
+        <v>37.96</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="DP12" t="n">
-        <v>14</v>
+        <v>14.14</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.62</v>
+        <v>13.5</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.76</v>
+        <v>8.68</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.14</v>
+        <v>0.18</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.38</v>
+        <v>50.54</v>
       </c>
       <c r="DW12" t="n">
         <v>0.14</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.09</v>
+        <v>12</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.33</v>
+        <v>8.23</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.76</v>
+        <v>3.77</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.33</v>
+        <v>19.72</v>
       </c>
       <c r="EB12" t="n">
         <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="13">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D15" t="n">
         <v>11</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="G15" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="H15" t="n">
-        <v>108</v>
+        <v>107.36</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="K15" t="n">
-        <v>5.7</v>
+        <v>5.55</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="M15" t="n">
-        <v>55.3</v>
+        <v>55.82</v>
       </c>
       <c r="N15" t="n">
-        <v>0.6</v>
+        <v>0.64</v>
       </c>
       <c r="O15" t="n">
-        <v>2.8</v>
+        <v>2.64</v>
       </c>
       <c r="P15" t="n">
-        <v>12.8</v>
+        <v>12.36</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.6</v>
+        <v>11.82</v>
       </c>
       <c r="R15" t="n">
-        <v>6.4</v>
+        <v>6.36</v>
       </c>
       <c r="S15" t="n">
         <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="U15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>56.6</v>
+        <v>56.91</v>
       </c>
       <c r="Y15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z15" t="n">
-        <v>16</v>
+        <v>16.27</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.1</v>
+        <v>11.55</v>
       </c>
       <c r="AB15" t="n">
-        <v>4.9</v>
+        <v>4.73</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.6</v>
+        <v>19.27</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.4</v>
+        <v>2.36</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,67 +6789,67 @@
         <v>3.09</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.48</v>
+        <v>10.36</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.24</v>
+        <v>3.18</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.9</v>
+        <v>0.86</v>
       </c>
       <c r="BM15" t="n">
         <v>0.86</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.23999999999999</v>
+        <v>95.45</v>
       </c>
       <c r="BS15" t="n">
-        <v>80.95</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT15" t="n">
-        <v>57.14</v>
+        <v>54.55</v>
       </c>
       <c r="BU15" t="n">
-        <v>28.57</v>
+        <v>27.27</v>
       </c>
       <c r="BV15" t="n">
-        <v>19.05</v>
+        <v>18.18</v>
       </c>
       <c r="BW15" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BX15" t="n">
-        <v>42.86</v>
+        <v>40.91</v>
       </c>
       <c r="BY15" t="n">
         <v>2.17</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CB15" t="n">
         <v>3.82</v>
@@ -6861,7 +6861,7 @@
         <v>3.1</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="CF15" t="n">
         <v>2.28</v>
@@ -6885,7 +6885,7 @@
         <v>1.74</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CN15" t="n">
         <v>2.17</v>
@@ -6901,14 +6901,14 @@
       </c>
       <c r="CR15" t="inlineStr"/>
       <c r="CS15" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CT15" t="inlineStr"/>
       <c r="CU15" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CW15" t="n">
         <v>1.52</v>
@@ -6932,82 +6932,82 @@
         <v>1.58</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.91</v>
+        <v>1.86</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="DH15" t="n">
-        <v>93.52</v>
+        <v>93.86</v>
       </c>
       <c r="DI15" t="n">
         <v>0.14</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.81</v>
+        <v>2.77</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.52</v>
+        <v>5.45</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.05</v>
+        <v>47.68</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.52</v>
+        <v>12.31</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.43</v>
+        <v>12.5</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.57</v>
+        <v>7.5</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.1</v>
+        <v>55.32</v>
       </c>
       <c r="DW15" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.57</v>
+        <v>16.68</v>
       </c>
       <c r="DY15" t="n">
-        <v>11</v>
+        <v>11.23</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.57</v>
+        <v>5.45</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.57</v>
+        <v>18.45</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.76</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="16">
@@ -7420,13 +7420,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C17" t="n">
         <v>11</v>
       </c>
       <c r="D17" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
@@ -7510,139 +7510,139 @@
         <v>1.82</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="AI17" t="n">
-        <v>98.2</v>
+        <v>98.73</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.5</v>
+        <v>2.55</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.8</v>
+        <v>4.91</v>
       </c>
       <c r="AM17" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="AN17" t="n">
-        <v>42.1</v>
+        <v>40.91</v>
       </c>
       <c r="AO17" t="n">
         <v>1</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.9</v>
+        <v>12.55</v>
       </c>
       <c r="AR17" t="n">
-        <v>11</v>
+        <v>11.36</v>
       </c>
       <c r="AS17" t="n">
-        <v>6.9</v>
+        <v>7.36</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52.8</v>
+        <v>52.82</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA17" t="n">
-        <v>14.7</v>
+        <v>14</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.699999999999999</v>
+        <v>9.18</v>
       </c>
       <c r="BC17" t="n">
-        <v>5</v>
+        <v>4.82</v>
       </c>
       <c r="BD17" t="n">
-        <v>21.1</v>
+        <v>20.73</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.58</v>
+        <v>1.52</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.4</v>
+        <v>2.45</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.48</v>
+        <v>10.45</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.71</v>
+        <v>2.59</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.77</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.52</v>
+        <v>1.45</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.19</v>
+        <v>1.14</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.76</v>
+        <v>4.73</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.67</v>
+        <v>5.68</v>
       </c>
       <c r="BR17" t="n">
-        <v>95.23999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="BS17" t="n">
-        <v>85.70999999999999</v>
+        <v>81.81999999999999</v>
       </c>
       <c r="BT17" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BU17" t="n">
-        <v>14.29</v>
+        <v>13.64</v>
       </c>
       <c r="BV17" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.76</v>
+        <v>4.55</v>
       </c>
       <c r="BX17" t="n">
-        <v>61.9</v>
+        <v>59.09</v>
       </c>
       <c r="BY17" t="n">
         <v>1.89</v>
@@ -7651,16 +7651,16 @@
         <v>1.97</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.21</v>
+        <v>2.25</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.29</v>
+        <v>2.32</v>
       </c>
       <c r="CE17" t="n">
         <v>1.31</v>
@@ -7687,37 +7687,37 @@
         <v>1.7</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.14</v>
+        <v>2.15</v>
       </c>
       <c r="CO17" t="n">
         <v>1.2</v>
       </c>
       <c r="CP17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CT17" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU17" t="n">
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX17" t="n">
         <v>1.46</v>
@@ -7735,85 +7735,85 @@
         <v>1.22</v>
       </c>
       <c r="DC17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD17" t="n">
-        <v>2.75</v>
+        <v>2.77</v>
       </c>
       <c r="DE17" t="n">
         <v>0.14</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.19</v>
+        <v>3.23</v>
       </c>
       <c r="DH17" t="n">
-        <v>100.38</v>
+        <v>100.54</v>
       </c>
       <c r="DI17" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.33</v>
+        <v>2.37</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.62</v>
+        <v>5.64</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.78</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.91</v>
+        <v>49.91</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.8100000000000001</v>
+        <v>0.82</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.38</v>
+        <v>2.37</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.81</v>
+        <v>12.64</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.57</v>
+        <v>10.77</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.09</v>
+        <v>7.32</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.24</v>
+        <v>0.22</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.48</v>
+        <v>54.41</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>16.29</v>
+        <v>15.86</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.72</v>
+        <v>10.41</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.57</v>
+        <v>5.45</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.38</v>
+        <v>21.18</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.78</v>
+        <v>1.74</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="18">
@@ -8226,13 +8226,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C19" t="n">
         <v>10</v>
       </c>
       <c r="D19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E19" t="n">
         <v>0.2</v>
@@ -8316,130 +8316,130 @@
         <v>2.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AI19" t="n">
-        <v>105.18</v>
+        <v>106.83</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.45</v>
+        <v>2.33</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.36</v>
+        <v>4.5</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="AN19" t="n">
-        <v>43.73</v>
+        <v>45.17</v>
       </c>
       <c r="AO19" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP19" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="AQ19" t="n">
-        <v>14</v>
+        <v>13.67</v>
       </c>
       <c r="AR19" t="n">
-        <v>11.55</v>
+        <v>12.17</v>
       </c>
       <c r="AS19" t="n">
-        <v>6</v>
+        <v>6.08</v>
       </c>
       <c r="AT19" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>43</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>12.33</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>8.17</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>23</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>9.68</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.45</v>
+      </c>
+      <c r="BL19" t="n">
         <v>0.73</v>
       </c>
-      <c r="AU19" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>42.73</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>7.73</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>22.73</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>9.43</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.38</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.71</v>
-      </c>
       <c r="BM19" t="n">
-        <v>0.57</v>
+        <v>0.55</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.71</v>
+        <v>0.77</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.48</v>
+        <v>5.64</v>
       </c>
       <c r="BR19" t="n">
-        <v>90.48</v>
+        <v>90.91</v>
       </c>
       <c r="BS19" t="n">
-        <v>57.14</v>
+        <v>59.09</v>
       </c>
       <c r="BT19" t="n">
-        <v>42.86</v>
+        <v>45.45</v>
       </c>
       <c r="BU19" t="n">
-        <v>9.52</v>
+        <v>9.09</v>
       </c>
       <c r="BV19" t="n">
         <v>0</v>
@@ -8448,7 +8448,7 @@
         <v>0</v>
       </c>
       <c r="BX19" t="n">
-        <v>38.1</v>
+        <v>40.91</v>
       </c>
       <c r="BY19" t="n">
         <v>2.23</v>
@@ -8457,31 +8457,31 @@
         <v>2.25</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.4</v>
+        <v>3.39</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.53</v>
+        <v>3.52</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.69</v>
+        <v>2.67</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="CE19" t="n">
         <v>1.36</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.96</v>
+        <v>2.95</v>
       </c>
       <c r="CH19" t="n">
         <v>1.43</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.67</v>
@@ -8496,16 +8496,16 @@
         <v>2.63</v>
       </c>
       <c r="CN19" t="n">
-        <v>2.03</v>
+        <v>2.02</v>
       </c>
       <c r="CO19" t="n">
         <v>1.25</v>
       </c>
       <c r="CP19" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="CR19" t="n">
         <v>1.38</v>
@@ -8520,10 +8520,10 @@
         <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX19" t="n">
         <v>1.5</v>
@@ -8538,88 +8538,88 @@
         <v>2.02</v>
       </c>
       <c r="DB19" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.1</v>
+        <v>3.13</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.95</v>
+        <v>2.91</v>
       </c>
       <c r="DH19" t="n">
-        <v>104.19</v>
+        <v>105.13</v>
       </c>
       <c r="DI19" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.05</v>
+        <v>5.09</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="DM19" t="n">
-        <v>46.91</v>
+        <v>47.55</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.81</v>
+        <v>13.64</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.05</v>
+        <v>12.37</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.76</v>
+        <v>5.82</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>43.57</v>
+        <v>43.68</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.57</v>
+        <v>12.95</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.33</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.24</v>
+        <v>4.41</v>
       </c>
       <c r="EA19" t="n">
-        <v>21.91</v>
+        <v>22.09</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.47</v>
+        <v>2.41</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -5475,7 +5475,7 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.64</v>
+        <v>52.73</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
@@ -5781,7 +5781,7 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.54</v>
+        <v>50.59</v>
       </c>
       <c r="DW12" t="n">
         <v>0.14</v>
@@ -7573,10 +7573,10 @@
         <v>0.09</v>
       </c>
       <c r="BA17" t="n">
-        <v>14</v>
+        <v>13.91</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.18</v>
+        <v>9.09</v>
       </c>
       <c r="BC17" t="n">
         <v>4.82</v>
@@ -7798,10 +7798,10 @@
         <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.86</v>
+        <v>15.82</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.41</v>
+        <v>10.37</v>
       </c>
       <c r="DZ17" t="n">
         <v>5.45</v>
@@ -8373,25 +8373,25 @@
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>43</v>
+        <v>42.92</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.33</v>
+        <v>12.42</v>
       </c>
       <c r="BB19" t="n">
         <v>8.17</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="BD19" t="n">
         <v>23</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="BF19" t="n">
         <v>2.33</v>
@@ -8598,25 +8598,25 @@
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>43.68</v>
+        <v>43.64</v>
       </c>
       <c r="DW19" t="n">
         <v>0.05</v>
       </c>
       <c r="DX19" t="n">
-        <v>12.95</v>
+        <v>13</v>
       </c>
       <c r="DY19" t="n">
         <v>8.550000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.41</v>
+        <v>4.45</v>
       </c>
       <c r="EA19" t="n">
         <v>22.09</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="EC19" t="n">
         <v>2.41</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="n">
         <v>11</v>
       </c>
       <c r="D2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="n">
         <v>0.18</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.64</v>
+        <v>3.83</v>
       </c>
       <c r="AI2" t="n">
-        <v>99.91</v>
+        <v>102.67</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="AL2" t="n">
-        <v>5.73</v>
+        <v>6.08</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.73</v>
+        <v>0.67</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.09</v>
+        <v>2.25</v>
       </c>
       <c r="AQ2" t="n">
-        <v>13.64</v>
+        <v>14</v>
       </c>
       <c r="AR2" t="n">
-        <v>14.09</v>
+        <v>13.83</v>
       </c>
       <c r="AS2" t="n">
-        <v>7.36</v>
+        <v>6.83</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>48.64</v>
+        <v>49.17</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.09</v>
+        <v>13.25</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.18</v>
+        <v>9.42</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="BD2" t="n">
-        <v>23.55</v>
+        <v>24.75</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.55</v>
+        <v>10.52</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.45</v>
+        <v>0.43</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.27</v>
+        <v>1.3</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.55</v>
+        <v>6.52</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU2" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW2" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX2" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY2" t="n">
         <v>2.11</v>
@@ -1613,22 +1613,22 @@
         <v>3.56</v>
       </c>
       <c r="CB2" t="n">
-        <v>3.66</v>
+        <v>3.67</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.16</v>
+        <v>3.06</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.37</v>
+        <v>3.24</v>
       </c>
       <c r="CE2" t="n">
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CH2" t="n">
         <v>1.52</v>
@@ -1640,7 +1640,7 @@
         <v>1.57</v>
       </c>
       <c r="CK2" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL2" t="n">
         <v>1.74</v>
@@ -1649,7 +1649,7 @@
         <v>2.81</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO2" t="n">
         <v>1.19</v>
@@ -1658,25 +1658,25 @@
         <v>1.68</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.13</v>
+        <v>3.16</v>
       </c>
       <c r="CU2" t="n">
         <v>1.54</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CW2" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX2" t="n">
         <v>1.46</v>
@@ -1694,7 +1694,7 @@
         <v>1.22</v>
       </c>
       <c r="DC2" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD2" t="n">
         <v>2.74</v>
@@ -1703,76 +1703,76 @@
         <v>0.09</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.95</v>
+        <v>4.04</v>
       </c>
       <c r="DH2" t="n">
-        <v>101.14</v>
+        <v>102.52</v>
       </c>
       <c r="DI2" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.14</v>
+        <v>6.3</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.28</v>
+        <v>50.83</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.18</v>
+        <v>2.26</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.41</v>
+        <v>13.61</v>
       </c>
       <c r="DQ2" t="n">
+        <v>13.83</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>7.26</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>52.13</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DX2" t="n">
         <v>13.96</v>
       </c>
-      <c r="DR2" t="n">
-        <v>7.55</v>
-      </c>
-      <c r="DS2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="DT2" t="n">
-        <v>0.32</v>
-      </c>
-      <c r="DU2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>52</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>13.91</v>
-      </c>
       <c r="DY2" t="n">
-        <v>9.630000000000001</v>
+        <v>9.74</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.28</v>
+        <v>4.22</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.28</v>
+        <v>23.91</v>
       </c>
       <c r="EB2" t="n">
         <v>1.54</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="3">
@@ -1782,94 +1782,94 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D3" t="n">
         <v>11</v>
       </c>
       <c r="E3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="H3" t="n">
-        <v>103.91</v>
+        <v>103.92</v>
       </c>
       <c r="I3" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="J3" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.73</v>
+        <v>5.5</v>
       </c>
       <c r="L3" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M3" t="n">
-        <v>54.18</v>
+        <v>54.17</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.82</v>
+        <v>2.67</v>
       </c>
       <c r="P3" t="n">
-        <v>14.82</v>
+        <v>14.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.27</v>
+        <v>10.08</v>
       </c>
       <c r="R3" t="n">
-        <v>8.09</v>
+        <v>8.08</v>
       </c>
       <c r="S3" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T3" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>46.64</v>
+        <v>47.17</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.18</v>
+        <v>16.42</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.64</v>
+        <v>11.08</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.55</v>
+        <v>5.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.64</v>
+        <v>21.33</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="AE3" t="n">
-        <v>3.18</v>
+        <v>3</v>
       </c>
       <c r="AF3" t="n">
         <v>0.18</v>
@@ -1953,64 +1953,64 @@
         <v>3.09</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.73</v>
+        <v>11.48</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.73</v>
+        <v>5.57</v>
       </c>
       <c r="BQ3" t="n">
-        <v>6</v>
+        <v>5.91</v>
       </c>
       <c r="BR3" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS3" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT3" t="n">
-        <v>45.45</v>
+        <v>43.48</v>
       </c>
       <c r="BU3" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BV3" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX3" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CA3" t="n">
         <v>3.6</v>
@@ -2028,31 +2028,31 @@
         <v>1.3</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CG3" t="n">
         <v>3.25</v>
       </c>
       <c r="CH3" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.56</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CM3" t="n">
-        <v>3.01</v>
+        <v>3</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CO3" t="n">
         <v>1.19</v>
@@ -2061,22 +2061,22 @@
         <v>1.66</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CR3" t="n">
         <v>1.37</v>
       </c>
       <c r="CS3" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="CU3" t="n">
         <v>1.52</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CW3" t="n">
         <v>1.6</v>
@@ -2091,7 +2091,7 @@
         <v>2.59</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="DB3" t="n">
         <v>1.22</v>
@@ -2106,76 +2106,76 @@
         <v>0.13</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.18</v>
+        <v>2.09</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.86</v>
+        <v>94.31</v>
       </c>
       <c r="DI3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.78</v>
+        <v>5.65</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.64</v>
+        <v>46.96</v>
       </c>
       <c r="DN3" t="n">
         <v>0.96</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.82</v>
+        <v>13.7</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.56</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.720000000000001</v>
+        <v>8.69</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.6</v>
+        <v>45.92</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.59</v>
+        <v>14.31</v>
       </c>
       <c r="DY3" t="n">
-        <v>10.04</v>
+        <v>9.82</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.55</v>
+        <v>4.48</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.41</v>
+        <v>22.21</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.14</v>
+        <v>3.04</v>
       </c>
     </row>
     <row r="4">
@@ -2185,94 +2185,94 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" t="n">
         <v>11</v>
       </c>
       <c r="E4" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="F4" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="G4" t="n">
-        <v>2.45</v>
+        <v>2.58</v>
       </c>
       <c r="H4" t="n">
-        <v>87.27</v>
+        <v>87.58</v>
       </c>
       <c r="I4" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J4" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="K4" t="n">
-        <v>5.36</v>
+        <v>5.25</v>
       </c>
       <c r="L4" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="M4" t="n">
-        <v>46.36</v>
+        <v>46.92</v>
       </c>
       <c r="N4" t="n">
-        <v>0.55</v>
+        <v>0.75</v>
       </c>
       <c r="O4" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
       <c r="P4" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.09</v>
+        <v>12.25</v>
       </c>
       <c r="R4" t="n">
-        <v>8.359999999999999</v>
+        <v>8.25</v>
       </c>
       <c r="S4" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="T4" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="U4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>48.73</v>
+        <v>49.17</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z4" t="n">
-        <v>15.09</v>
+        <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.75</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.45</v>
+        <v>6.25</v>
       </c>
       <c r="AC4" t="n">
-        <v>17.45</v>
+        <v>16.75</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="AE4" t="n">
-        <v>1.82</v>
+        <v>2</v>
       </c>
       <c r="AF4" t="n">
         <v>0.27</v>
@@ -2359,67 +2359,67 @@
         <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.5</v>
+        <v>10.7</v>
       </c>
       <c r="BI4" t="n">
         <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.23</v>
+        <v>5.17</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.27</v>
+        <v>5.52</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BT4" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU4" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV4" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BW4" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX4" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY4" t="n">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="BZ4" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.68</v>
+        <v>3.67</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.76</v>
+        <v>3.74</v>
       </c>
       <c r="CC4" t="n">
         <v>2.88</v>
@@ -2428,19 +2428,19 @@
         <v>3.09</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CH4" t="n">
         <v>1.52</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.57</v>
@@ -2449,7 +2449,7 @@
         <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM4" t="n">
         <v>2.7</v>
@@ -2470,16 +2470,16 @@
         <v>1.36</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CT4" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CU4" t="n">
         <v>1.55</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW4" t="n">
         <v>1.6</v>
@@ -2506,79 +2506,79 @@
         <v>2.71</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.27</v>
+        <v>2.35</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.27</v>
+        <v>88.39</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.68</v>
+        <v>1.78</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.05</v>
+        <v>5</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.55</v>
+        <v>0.52</v>
       </c>
       <c r="DM4" t="n">
-        <v>41.54</v>
+        <v>42.05</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.41</v>
+        <v>0.52</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.78</v>
+        <v>2.66</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.28</v>
+        <v>11.26</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.5</v>
+        <v>11.61</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.5</v>
+        <v>8.44</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU4" t="n">
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.78</v>
+        <v>49.96</v>
       </c>
       <c r="DW4" t="n">
         <v>0.04</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.77</v>
+        <v>13.78</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.359999999999999</v>
+        <v>8.43</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.4</v>
+        <v>5.35</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.64</v>
+        <v>17.26</v>
       </c>
       <c r="EB4" t="n">
         <v>1.55</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.64</v>
+        <v>1.74</v>
       </c>
     </row>
     <row r="5">
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C5" t="n">
         <v>11</v>
       </c>
       <c r="D5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E5" t="n">
         <v>0.09</v>
@@ -2678,52 +2678,52 @@
         <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AH5" t="n">
-        <v>3.18</v>
+        <v>2.92</v>
       </c>
       <c r="AI5" t="n">
-        <v>97.45</v>
+        <v>96.5</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.09</v>
+        <v>2.17</v>
       </c>
       <c r="AL5" t="n">
-        <v>5.27</v>
+        <v>5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AN5" t="n">
-        <v>47.55</v>
+        <v>46.25</v>
       </c>
       <c r="AO5" t="n">
-        <v>0.82</v>
+        <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.09</v>
+        <v>11.33</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.45</v>
+        <v>11.75</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.82</v>
+        <v>8.92</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>49.27</v>
+        <v>48.75</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.91</v>
+        <v>13.25</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.91</v>
+        <v>9.42</v>
       </c>
       <c r="BC5" t="n">
-        <v>4</v>
+        <v>3.83</v>
       </c>
       <c r="BD5" t="n">
-        <v>22.36</v>
+        <v>22.17</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.51</v>
+        <v>1.44</v>
       </c>
       <c r="BF5" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.27</v>
+        <v>3.13</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.05</v>
+        <v>11.04</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.27</v>
+        <v>3.13</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.82</v>
+        <v>0.78</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.77</v>
+        <v>1.7</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.86</v>
+        <v>4.91</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.14</v>
+        <v>6.09</v>
       </c>
       <c r="BR5" t="n">
-        <v>100</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>95.45</v>
+        <v>91.3</v>
       </c>
       <c r="BT5" t="n">
-        <v>77.27</v>
+        <v>73.91</v>
       </c>
       <c r="BU5" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX5" t="n">
-        <v>81.81999999999999</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BY5" t="n">
         <v>2.54</v>
@@ -2819,16 +2819,16 @@
         <v>2.62</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.62</v>
+        <v>3.66</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.68</v>
+        <v>3.73</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="CD5" t="n">
-        <v>3.9</v>
+        <v>4.09</v>
       </c>
       <c r="CE5" t="n">
         <v>1.32</v>
@@ -2840,10 +2840,10 @@
         <v>3.23</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.59</v>
@@ -2855,10 +2855,10 @@
         <v>1.69</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.86</v>
+        <v>2.87</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CO5" t="n">
         <v>1.19</v>
@@ -2867,22 +2867,22 @@
         <v>1.69</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT5" t="n">
         <v>3.25</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CW5" t="n">
         <v>1.61</v>
@@ -2900,55 +2900,55 @@
         <v>2.2</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.5</v>
+        <v>1.43</v>
       </c>
       <c r="DG5" t="n">
-        <v>3.09</v>
+        <v>2.96</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.45</v>
+        <v>91.22</v>
       </c>
       <c r="DI5" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.18</v>
+        <v>5.04</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM5" t="n">
-        <v>45.41</v>
+        <v>44.82</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.59</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.77</v>
+        <v>10.91</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.27</v>
+        <v>12.39</v>
       </c>
       <c r="DR5" t="n">
-        <v>8</v>
+        <v>8.09</v>
       </c>
       <c r="DS5" t="n">
         <v>0.04</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49.14</v>
+        <v>48.87</v>
       </c>
       <c r="DW5" t="n">
         <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.91</v>
+        <v>12.61</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.960000000000001</v>
+        <v>8.74</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.96</v>
+        <v>3.87</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.5</v>
+        <v>21.44</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.95</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C6" t="n">
         <v>12</v>
       </c>
       <c r="D6" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,52 +3081,52 @@
         <v>2.25</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.8</v>
+        <v>2.55</v>
       </c>
       <c r="AI6" t="n">
-        <v>105.4</v>
+        <v>103.91</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK6" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="AL6" t="n">
-        <v>5.3</v>
+        <v>4.82</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.7</v>
+        <v>47.09</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.6</v>
+        <v>0.55</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.7</v>
+        <v>12.82</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.8</v>
+        <v>13.18</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.5</v>
+        <v>7.64</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>49</v>
+        <v>48.27</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.4</v>
+        <v>0.36</v>
       </c>
       <c r="BA6" t="n">
-        <v>13.2</v>
+        <v>12.64</v>
       </c>
       <c r="BB6" t="n">
-        <v>9.300000000000001</v>
+        <v>8.73</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.9</v>
+        <v>3.91</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.8</v>
+        <v>20.91</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.68</v>
+        <v>10.39</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.82</v>
+        <v>2.87</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.7</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.73</v>
+        <v>4.52</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.95</v>
+        <v>5.87</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT6" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU6" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BV6" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY6" t="n">
         <v>3</v>
@@ -3222,46 +3222,46 @@
         <v>3.1</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.67</v>
+        <v>3.71</v>
       </c>
       <c r="CC6" t="n">
-        <v>4</v>
+        <v>4.15</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.45</v>
+        <v>4.57</v>
       </c>
       <c r="CE6" t="n">
         <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CH6" t="n">
         <v>1.47</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CK6" t="n">
         <v>1.41</v>
       </c>
       <c r="CL6" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO6" t="n">
         <v>1.21</v>
@@ -3270,22 +3270,22 @@
         <v>1.76</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.18</v>
+        <v>3.19</v>
       </c>
       <c r="CU6" t="n">
         <v>1.5</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.3</v>
+        <v>2.29</v>
       </c>
       <c r="CW6" t="n">
         <v>1.67</v>
@@ -3294,7 +3294,7 @@
         <v>1.47</v>
       </c>
       <c r="CY6" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CZ6" t="n">
         <v>2.56</v>
@@ -3315,76 +3315,76 @@
         <v>0.09</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.87</v>
+        <v>1.83</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.41</v>
+        <v>2.3</v>
       </c>
       <c r="DH6" t="n">
-        <v>98.54000000000001</v>
+        <v>98.13</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.63</v>
+        <v>4.43</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.18</v>
+        <v>41.17</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.86</v>
+        <v>0.83</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.32</v>
+        <v>12.39</v>
       </c>
       <c r="DQ6" t="n">
-        <v>13.13</v>
+        <v>12.87</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.09</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.27</v>
+        <v>44.13</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.32</v>
+        <v>0.3</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.91</v>
+        <v>12.66</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.960000000000001</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.95</v>
+        <v>3.96</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.68</v>
+        <v>21.7</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C7" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D7" t="n">
         <v>12</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="F7" t="n">
         <v>1</v>
       </c>
       <c r="G7" t="n">
-        <v>3.2</v>
+        <v>3.27</v>
       </c>
       <c r="H7" t="n">
-        <v>104.1</v>
+        <v>102.27</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="K7" t="n">
-        <v>6.3</v>
+        <v>6.09</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M7" t="n">
-        <v>58.8</v>
+        <v>56.91</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O7" t="n">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="P7" t="n">
-        <v>11.2</v>
+        <v>10.82</v>
       </c>
       <c r="Q7" t="n">
-        <v>14</v>
+        <v>13.73</v>
       </c>
       <c r="R7" t="n">
-        <v>6.5</v>
+        <v>6.45</v>
       </c>
       <c r="S7" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="T7" t="n">
-        <v>1.6</v>
+        <v>1.73</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V7" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.2</v>
+        <v>55.55</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.5</v>
+        <v>16.09</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.4</v>
+        <v>11.09</v>
       </c>
       <c r="AB7" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="AC7" t="n">
-        <v>23.9</v>
+        <v>24.36</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.82</v>
+        <v>1.78</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="AF7" t="n">
         <v>0.08</v>
@@ -3565,70 +3565,70 @@
         <v>2.5</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.77</v>
+        <v>10.48</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.86</v>
+        <v>2.91</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.45</v>
+        <v>0.52</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.95</v>
+        <v>0.96</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.14</v>
+        <v>1.22</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.36</v>
+        <v>5.13</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.68</v>
+        <v>4.65</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT7" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU7" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BV7" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX7" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BY7" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="BZ7" t="n">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.42</v>
+        <v>3.46</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.72</v>
+        <v>3.75</v>
       </c>
       <c r="CC7" t="n">
         <v>2.2</v>
@@ -3640,19 +3640,19 @@
         <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.14</v>
+        <v>3.15</v>
       </c>
       <c r="CH7" t="n">
         <v>1.45</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="CJ7" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CK7" t="n">
         <v>1.3</v>
@@ -3661,19 +3661,19 @@
         <v>1.62</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN7" t="n">
         <v>2.07</v>
       </c>
       <c r="CO7" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="CP7" t="n">
         <v>1.58</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CR7" t="n">
         <v>1.37</v>
@@ -3682,16 +3682,16 @@
         <v>2.6</v>
       </c>
       <c r="CT7" t="n">
-        <v>3.22</v>
+        <v>3.23</v>
       </c>
       <c r="CU7" t="n">
         <v>1.53</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CW7" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX7" t="n">
         <v>1.44</v>
@@ -3715,79 +3715,79 @@
         <v>2.75</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.59</v>
+        <v>2.65</v>
       </c>
       <c r="DH7" t="n">
-        <v>99.91</v>
+        <v>99.22</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.18</v>
+        <v>6.08</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.36</v>
+        <v>51.74</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.59</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO7" t="n">
-        <v>3.05</v>
+        <v>2.91</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.68</v>
+        <v>10.52</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.45</v>
+        <v>14.3</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.87</v>
+        <v>6.83</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.5</v>
+        <v>54.7</v>
       </c>
       <c r="DW7" t="n">
         <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.55</v>
+        <v>15.39</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.36</v>
+        <v>10.26</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.18</v>
+        <v>5.13</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.68</v>
+        <v>22.96</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="EC7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C8" t="n">
         <v>12</v>
       </c>
       <c r="D8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,139 +3887,139 @@
         <v>2.83</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.3</v>
+        <v>2.73</v>
       </c>
       <c r="AI8" t="n">
-        <v>94.59999999999999</v>
+        <v>93.81999999999999</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="AL8" t="n">
-        <v>3.8</v>
+        <v>4.45</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AN8" t="n">
-        <v>41.1</v>
+        <v>41.91</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.4</v>
+        <v>1.64</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.6</v>
+        <v>12.73</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.2</v>
+        <v>12.18</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.5</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.4</v>
+        <v>45.45</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.4</v>
+        <v>13.82</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.699999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>3.7</v>
+        <v>4.18</v>
       </c>
       <c r="BD8" t="n">
-        <v>20</v>
+        <v>19.27</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.41</v>
+        <v>1.47</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.449999999999999</v>
+        <v>8.74</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL8" t="n">
         <v>0.91</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.77</v>
+        <v>5.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS8" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT8" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BV8" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX8" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY8" t="n">
         <v>2.36</v>
@@ -4028,16 +4028,16 @@
         <v>2.42</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.77</v>
+        <v>3.76</v>
       </c>
       <c r="CC8" t="n">
         <v>3.45</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.79</v>
+        <v>3.81</v>
       </c>
       <c r="CE8" t="n">
         <v>1.31</v>
@@ -4046,13 +4046,13 @@
         <v>2.45</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CH8" t="n">
         <v>1.51</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.58</v>
@@ -4064,7 +4064,7 @@
         <v>1.78</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CN8" t="n">
         <v>2.04</v>
@@ -4073,7 +4073,7 @@
         <v>1.19</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ8" t="n">
         <v>2.58</v>
@@ -4085,13 +4085,13 @@
         <v>2.58</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="CU8" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="CW8" t="n">
         <v>1.6</v>
@@ -4118,79 +4118,79 @@
         <v>2.71</v>
       </c>
       <c r="DE8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.37</v>
+        <v>2.57</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.55</v>
+        <v>93.22</v>
       </c>
       <c r="DI8" t="n">
         <v>-0.05</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.82</v>
+        <v>2.79</v>
       </c>
       <c r="DK8" t="n">
-        <v>3.91</v>
+        <v>4.22</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM8" t="n">
-        <v>46.91</v>
+        <v>47.04</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.32</v>
+        <v>1.26</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.5</v>
+        <v>1.61</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.55</v>
+        <v>12.61</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.73</v>
+        <v>11.74</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.68</v>
+        <v>7.83</v>
       </c>
       <c r="DS8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DT8" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DU8" t="n">
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.63</v>
+        <v>48.52</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.73</v>
+        <v>12.96</v>
       </c>
       <c r="DY8" t="n">
         <v>9.09</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.63</v>
+        <v>3.87</v>
       </c>
       <c r="EA8" t="n">
-        <v>21.05</v>
+        <v>20.65</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.68</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3</v>
+        <v>0.36</v>
       </c>
       <c r="F9" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.5</v>
+        <v>2.27</v>
       </c>
       <c r="H9" t="n">
-        <v>85.59999999999999</v>
+        <v>86.36</v>
       </c>
       <c r="I9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J9" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="K9" t="n">
-        <v>5</v>
+        <v>4.55</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>34.2</v>
+        <v>33</v>
       </c>
       <c r="N9" t="n">
-        <v>1</v>
+        <v>0.91</v>
       </c>
       <c r="O9" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="P9" t="n">
-        <v>10.5</v>
+        <v>10.64</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.9</v>
+        <v>15.18</v>
       </c>
       <c r="R9" t="n">
-        <v>8.5</v>
+        <v>8.09</v>
       </c>
       <c r="S9" t="n">
-        <v>2.4</v>
+        <v>2.27</v>
       </c>
       <c r="T9" t="n">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.2</v>
+        <v>45.18</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.8</v>
+        <v>10.27</v>
       </c>
       <c r="AA9" t="n">
-        <v>7.4</v>
+        <v>6.91</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.4</v>
+        <v>3.36</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.4</v>
+        <v>19.27</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.17</v>
+        <v>1.13</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,67 +4371,67 @@
         <v>2.58</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.05</v>
+        <v>10.04</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.86</v>
+        <v>3.83</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK9" t="n">
         <v>0.91</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BM9" t="n">
-        <v>1</v>
+        <v>0.96</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.23</v>
+        <v>2.17</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.18</v>
+        <v>4.17</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.27</v>
+        <v>5.3</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT9" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BU9" t="n">
-        <v>50</v>
+        <v>47.83</v>
       </c>
       <c r="BV9" t="n">
-        <v>36.36</v>
+        <v>34.78</v>
       </c>
       <c r="BW9" t="n">
-        <v>22.73</v>
+        <v>21.74</v>
       </c>
       <c r="BX9" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.34</v>
+        <v>3.42</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.78</v>
+        <v>3.77</v>
       </c>
       <c r="CB9" t="n">
         <v>3.98</v>
@@ -4446,31 +4446,31 @@
         <v>1.29</v>
       </c>
       <c r="CF9" t="n">
-        <v>2.36</v>
+        <v>2.37</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="CH9" t="n">
         <v>1.55</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="CK9" t="n">
         <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM9" t="n">
         <v>2.8</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CO9" t="n">
         <v>1.17</v>
@@ -4479,22 +4479,22 @@
         <v>1.61</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.32</v>
+        <v>3.33</v>
       </c>
       <c r="CU9" t="n">
         <v>1.58</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.46</v>
+        <v>2.45</v>
       </c>
       <c r="CW9" t="n">
         <v>1.59</v>
@@ -4518,82 +4518,82 @@
         <v>1.65</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.31999999999999</v>
+        <v>80.91</v>
       </c>
       <c r="DI9" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM9" t="n">
-        <v>34.46</v>
+        <v>33.87</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.68</v>
+        <v>1.61</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.18</v>
+        <v>12.17</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.23</v>
+        <v>13.43</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.73</v>
+        <v>8.52</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.45</v>
+        <v>46.39</v>
       </c>
       <c r="DW9" t="n">
         <v>0.09</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.41</v>
+        <v>11.13</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.45</v>
+        <v>7.22</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.96</v>
+        <v>3.91</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.18</v>
+        <v>21.04</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C10" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D10" t="n">
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F10" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="G10" t="n">
-        <v>3.5</v>
+        <v>3.64</v>
       </c>
       <c r="H10" t="n">
-        <v>111.8</v>
+        <v>111.27</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="K10" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="L10" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M10" t="n">
-        <v>58.5</v>
+        <v>57.27</v>
       </c>
       <c r="N10" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="O10" t="n">
-        <v>3.3</v>
+        <v>3.36</v>
       </c>
       <c r="P10" t="n">
-        <v>13.1</v>
+        <v>13.45</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.6</v>
+        <v>13.55</v>
       </c>
       <c r="R10" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="S10" t="n">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="T10" t="n">
-        <v>1.7</v>
+        <v>1.55</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="V10" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.3</v>
+        <v>57.27</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.6</v>
+        <v>17.09</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.6</v>
+        <v>11.36</v>
       </c>
       <c r="AB10" t="n">
-        <v>6</v>
+        <v>5.73</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.8</v>
+        <v>19.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.96</v>
+        <v>1.9</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AF10" t="n">
         <v>0.17</v>
@@ -4774,70 +4774,70 @@
         <v>2.25</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.5</v>
+        <v>9.57</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.95</v>
+        <v>0.91</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="BN10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>91.3</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>86.95999999999999</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>78.26000000000001</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>43.48</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>8.699999999999999</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>60.87</v>
+      </c>
+      <c r="BY10" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="BZ10" t="n">
         <v>1.86</v>
       </c>
-      <c r="BO10" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>4.23</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>5.27</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>95.45</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>90.91</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>81.81999999999999</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>45.45</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>9.09</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>63.64</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="BZ10" t="n">
-        <v>1.9</v>
-      </c>
       <c r="CA10" t="n">
-        <v>3.67</v>
+        <v>3.7</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.79</v>
+        <v>3.83</v>
       </c>
       <c r="CC10" t="n">
         <v>2.35</v>
@@ -4852,16 +4852,16 @@
         <v>2.45</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CJ10" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK10" t="n">
         <v>1.34</v>
@@ -4888,7 +4888,7 @@
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CT10" t="n">
         <v>3.3</v>
@@ -4921,82 +4921,82 @@
         <v>1.68</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.66</v>
+        <v>2.65</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DG10" t="n">
-        <v>3</v>
+        <v>3.09</v>
       </c>
       <c r="DH10" t="n">
-        <v>105.73</v>
+        <v>105.74</v>
       </c>
       <c r="DI10" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ10" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.68</v>
+        <v>5.83</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.23</v>
+        <v>50.96</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.23</v>
+        <v>13.39</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.55</v>
+        <v>13.52</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.18</v>
+        <v>6.04</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.82</v>
+        <v>55.87</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.95</v>
+        <v>14.83</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.359999999999999</v>
+        <v>9.35</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.59</v>
+        <v>5.48</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.5</v>
+        <v>19.48</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="11">
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C11" t="n">
         <v>12</v>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E11" t="n">
         <v>0.08</v>
@@ -5096,139 +5096,139 @@
         <v>2</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG11" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.6</v>
+        <v>1.91</v>
       </c>
       <c r="AI11" t="n">
-        <v>93.5</v>
+        <v>92.73</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="AL11" t="n">
-        <v>4</v>
+        <v>4.27</v>
       </c>
       <c r="AM11" t="n">
         <v>0</v>
       </c>
       <c r="AN11" t="n">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.8</v>
+        <v>0.73</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AQ11" t="n">
-        <v>14.4</v>
+        <v>13.45</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.8</v>
+        <v>12.45</v>
       </c>
       <c r="AS11" t="n">
-        <v>9</v>
+        <v>9.09</v>
       </c>
       <c r="AT11" t="n">
-        <v>1</v>
+        <v>1.36</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.7</v>
+        <v>47.45</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>12</v>
+        <v>11.64</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.8</v>
+        <v>7.55</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.2</v>
+        <v>4.09</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.8</v>
+        <v>21.27</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.9</v>
+        <v>2.73</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.23</v>
+        <v>10.26</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.41</v>
+        <v>2.61</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.55</v>
+        <v>0.65</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.41</v>
+        <v>0.48</v>
       </c>
       <c r="BM11" t="n">
         <v>0.91</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.09</v>
+        <v>1.22</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.73</v>
+        <v>4.78</v>
       </c>
       <c r="BQ11" t="n">
         <v>4.91</v>
       </c>
       <c r="BR11" t="n">
-        <v>86.36</v>
+        <v>86.95999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BT11" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU11" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV11" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BW11" t="n">
-        <v>4.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX11" t="n">
-        <v>36.36</v>
+        <v>39.13</v>
       </c>
       <c r="BY11" t="n">
         <v>1.91</v>
@@ -5237,22 +5237,22 @@
         <v>2.08</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.36</v>
+        <v>3.37</v>
       </c>
       <c r="CB11" t="n">
         <v>3.75</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.69</v>
+        <v>2.71</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CE11" t="n">
         <v>1.25</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.3</v>
+        <v>2.31</v>
       </c>
       <c r="CG11" t="n">
         <v>3.08</v>
@@ -5264,19 +5264,19 @@
         <v>2.22</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CK11" t="n">
         <v>1.31</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CN11" t="n">
-        <v>2.06</v>
+        <v>2.07</v>
       </c>
       <c r="CO11" t="n">
         <v>1.13</v>
@@ -5285,7 +5285,7 @@
         <v>1.59</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
@@ -5327,79 +5327,79 @@
         <v>2.67</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.18</v>
+        <v>2.31</v>
       </c>
       <c r="DH11" t="n">
-        <v>94.86</v>
+        <v>94.44</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.64</v>
+        <v>2.57</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.59</v>
+        <v>4.69</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.77</v>
+        <v>45.35</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="DP11" t="n">
-        <v>13.32</v>
+        <v>12.91</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.41</v>
+        <v>11.3</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.960000000000001</v>
+        <v>9</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.64</v>
+        <v>48.48</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.59</v>
+        <v>12.39</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.050000000000001</v>
+        <v>7.92</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.54</v>
+        <v>4.48</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.82</v>
+        <v>20.61</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
     </row>
     <row r="12">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" t="n">
         <v>11</v>
       </c>
       <c r="D12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5499,139 +5499,139 @@
         <v>1.91</v>
       </c>
       <c r="AF12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.64</v>
+        <v>2.42</v>
       </c>
       <c r="AI12" t="n">
-        <v>78</v>
+        <v>82.25</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.64</v>
+        <v>3.75</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.09</v>
+        <v>4.08</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="AN12" t="n">
-        <v>33.36</v>
+        <v>35.17</v>
       </c>
       <c r="AO12" t="n">
-        <v>1</v>
+        <v>1.08</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.45</v>
+        <v>1.67</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.73</v>
+        <v>15.5</v>
       </c>
       <c r="AR12" t="n">
-        <v>12.45</v>
+        <v>13.33</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.82</v>
+        <v>9.5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.73</v>
+        <v>1.83</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>48.45</v>
+        <v>50.08</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.27</v>
+        <v>11.58</v>
       </c>
       <c r="BB12" t="n">
-        <v>7.91</v>
+        <v>8.17</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.36</v>
+        <v>19.42</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.19</v>
+        <v>1.23</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.36</v>
+        <v>3.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.59</v>
+        <v>10.43</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.59</v>
+        <v>0.57</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.41</v>
+        <v>4.39</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6.14</v>
+        <v>6</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BU12" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BV12" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX12" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY12" t="n">
         <v>2.23</v>
@@ -5646,10 +5646,10 @@
         <v>3.62</v>
       </c>
       <c r="CC12" t="n">
-        <v>3.05</v>
+        <v>2.99</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.27</v>
+        <v>3.2</v>
       </c>
       <c r="CE12" t="n">
         <v>1.33</v>
@@ -5658,13 +5658,13 @@
         <v>2.53</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CH12" t="n">
         <v>1.48</v>
       </c>
       <c r="CI12" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CJ12" t="n">
         <v>1.59</v>
@@ -5676,10 +5676,10 @@
         <v>1.7</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO12" t="n">
         <v>1.2</v>
@@ -5688,13 +5688,13 @@
         <v>1.73</v>
       </c>
       <c r="CQ12" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CR12" t="n">
         <v>1.36</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CT12" t="n">
         <v>3.28</v>
@@ -5703,7 +5703,7 @@
         <v>1.52</v>
       </c>
       <c r="CV12" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CW12" t="n">
         <v>1.64</v>
@@ -5733,76 +5733,76 @@
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.91</v>
+        <v>1.96</v>
       </c>
       <c r="DG12" t="n">
-        <v>3</v>
+        <v>2.87</v>
       </c>
       <c r="DH12" t="n">
-        <v>83.41</v>
+        <v>85.39</v>
       </c>
       <c r="DI12" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.78</v>
+        <v>2.87</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.86</v>
+        <v>4.83</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.28</v>
+        <v>0.35</v>
       </c>
       <c r="DM12" t="n">
-        <v>37.96</v>
+        <v>38.7</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.87</v>
+        <v>0.91</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.86</v>
+        <v>1.96</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.14</v>
+        <v>14.09</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.5</v>
+        <v>13.91</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.68</v>
+        <v>8.57</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>50.59</v>
+        <v>51.35</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DX12" t="n">
-        <v>12</v>
+        <v>12.13</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.23</v>
+        <v>8.35</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.72</v>
+        <v>19.74</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
     </row>
     <row r="13">
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C13" t="n">
         <v>12</v>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E13" t="n">
         <v>0.33</v>
@@ -5902,139 +5902,139 @@
         <v>2.75</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="AI13" t="n">
-        <v>88.8</v>
+        <v>87.81999999999999</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.3</v>
+        <v>0.27</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.3</v>
+        <v>4.36</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN13" t="n">
-        <v>36.6</v>
+        <v>35.91</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="AQ13" t="n">
-        <v>13</v>
+        <v>12.91</v>
       </c>
       <c r="AR13" t="n">
-        <v>13.8</v>
+        <v>14.09</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.5</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="AU13" t="n">
-        <v>1</v>
+        <v>1.18</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.1</v>
+        <v>0.18</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.2</v>
+        <v>45.18</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>11.55</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.4</v>
+        <v>7.64</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.6</v>
+        <v>3.91</v>
       </c>
       <c r="BD13" t="n">
-        <v>19.7</v>
+        <v>20</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.68</v>
+        <v>9.74</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.05</v>
+        <v>3.13</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.77</v>
+        <v>0.74</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.91</v>
+        <v>1.87</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.45</v>
+        <v>4.52</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS13" t="n">
-        <v>77.27</v>
+        <v>78.26000000000001</v>
       </c>
       <c r="BT13" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BV13" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY13" t="n">
         <v>2.38</v>
@@ -6043,46 +6043,46 @@
         <v>2.47</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.06</v>
+        <v>3.02</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.18</v>
+        <v>3.16</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.18</v>
+        <v>3.17</v>
       </c>
       <c r="CH13" t="n">
         <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.56</v>
       </c>
       <c r="CK13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO13" t="n">
         <v>1.19</v>
@@ -6091,22 +6091,22 @@
         <v>1.68</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CR13" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="CT13" t="n">
-        <v>3.28</v>
+        <v>3.25</v>
       </c>
       <c r="CU13" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="CW13" t="n">
         <v>1.58</v>
@@ -6115,97 +6115,97 @@
         <v>1.49</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CZ13" t="n">
         <v>2.5</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DB13" t="n">
         <v>1.21</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.69</v>
+        <v>2.72</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DH13" t="n">
-        <v>95.73</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.82</v>
+        <v>2.83</v>
       </c>
       <c r="DK13" t="n">
         <v>4.82</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.41</v>
+        <v>0.39</v>
       </c>
       <c r="DM13" t="n">
-        <v>42.77</v>
+        <v>42.18</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.32</v>
+        <v>2.35</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.32</v>
+        <v>12.3</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.68</v>
+        <v>13.82</v>
       </c>
       <c r="DR13" t="n">
-        <v>8.949999999999999</v>
+        <v>9.050000000000001</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.82</v>
+        <v>46.74</v>
       </c>
       <c r="DW13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.41</v>
+        <v>13.57</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.550000000000001</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.87</v>
+        <v>4.96</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.87</v>
+        <v>21.91</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="14">
@@ -6215,61 +6215,61 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D14" t="n">
         <v>12</v>
       </c>
       <c r="E14" t="n">
-        <v>0.2</v>
+        <v>0.27</v>
       </c>
       <c r="F14" t="n">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="G14" t="n">
-        <v>1.8</v>
+        <v>1.91</v>
       </c>
       <c r="H14" t="n">
-        <v>78.90000000000001</v>
+        <v>77.55</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.2</v>
+        <v>3.36</v>
       </c>
       <c r="K14" t="n">
-        <v>4.5</v>
+        <v>4.36</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="M14" t="n">
-        <v>42.8</v>
+        <v>41.82</v>
       </c>
       <c r="N14" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="O14" t="n">
-        <v>2.1</v>
+        <v>1.91</v>
       </c>
       <c r="P14" t="n">
-        <v>14</v>
+        <v>14.91</v>
       </c>
       <c r="Q14" t="n">
-        <v>13</v>
+        <v>12.82</v>
       </c>
       <c r="R14" t="n">
-        <v>8.6</v>
+        <v>8.91</v>
       </c>
       <c r="S14" t="n">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="T14" t="n">
-        <v>1.7</v>
+        <v>1.82</v>
       </c>
       <c r="U14" t="n">
         <v>0</v>
@@ -6281,28 +6281,28 @@
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>46.9</v>
+        <v>45.55</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.2</v>
+        <v>11.45</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.5</v>
+        <v>6.55</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.7</v>
+        <v>4.91</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.7</v>
+        <v>16.55</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="AF14" t="n">
         <v>0.08</v>
@@ -6386,70 +6386,70 @@
         <v>2.25</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="BH14" t="n">
-        <v>10.18</v>
+        <v>10.04</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.32</v>
+        <v>3.35</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="BM14" t="n">
         <v>0.91</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.09</v>
+        <v>2.13</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.45</v>
+        <v>4.43</v>
       </c>
       <c r="BQ14" t="n">
-        <v>5.05</v>
+        <v>4.96</v>
       </c>
       <c r="BR14" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS14" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT14" t="n">
-        <v>68.18000000000001</v>
+        <v>69.56999999999999</v>
       </c>
       <c r="BU14" t="n">
-        <v>50</v>
+        <v>52.17</v>
       </c>
       <c r="BV14" t="n">
-        <v>31.82</v>
+        <v>30.43</v>
       </c>
       <c r="BW14" t="n">
-        <v>9.09</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX14" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="BZ14" t="n">
         <v>2.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.88</v>
+        <v>3.87</v>
       </c>
       <c r="CC14" t="n">
         <v>3.75</v>
@@ -6461,7 +6461,7 @@
         <v>1.29</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="CG14" t="n">
         <v>3.26</v>
@@ -6470,7 +6470,7 @@
         <v>1.55</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.54</v>
@@ -6494,7 +6494,7 @@
         <v>1.62</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
@@ -6536,46 +6536,46 @@
         <v>2.59</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.63</v>
+        <v>1.74</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.55</v>
+        <v>2.57</v>
       </c>
       <c r="DH14" t="n">
-        <v>85.64</v>
+        <v>84.7</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.68</v>
+        <v>2.78</v>
       </c>
       <c r="DK14" t="n">
-        <v>5.05</v>
+        <v>4.95</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM14" t="n">
-        <v>42.46</v>
+        <v>42</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.23</v>
+        <v>2.13</v>
       </c>
       <c r="DP14" t="n">
-        <v>12.68</v>
+        <v>13.17</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.95</v>
+        <v>10.96</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.449999999999999</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="DS14" t="n">
         <v>0.09</v>
@@ -6587,28 +6587,28 @@
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>48.36</v>
+        <v>47.65</v>
       </c>
       <c r="DW14" t="n">
         <v>0.09</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.87</v>
+        <v>11.96</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.96</v>
+        <v>7.92</v>
       </c>
       <c r="DZ14" t="n">
-        <v>3.91</v>
+        <v>4.04</v>
       </c>
       <c r="EA14" t="n">
-        <v>18.09</v>
+        <v>17.96</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.59</v>
+        <v>2.69</v>
       </c>
     </row>
     <row r="15">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="n">
         <v>11</v>
       </c>
       <c r="D15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,136 +6711,136 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.91</v>
+        <v>1.75</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.73</v>
+        <v>2.58</v>
       </c>
       <c r="AI15" t="n">
-        <v>80.36</v>
+        <v>81.17</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AK15" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="AL15" t="n">
-        <v>5.36</v>
+        <v>5.08</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="AN15" t="n">
-        <v>39.55</v>
+        <v>37.67</v>
       </c>
       <c r="AO15" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.36</v>
+        <v>2.25</v>
       </c>
       <c r="AQ15" t="n">
-        <v>12.27</v>
+        <v>11.83</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.18</v>
+        <v>13.58</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.640000000000001</v>
+        <v>8.58</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.55</v>
+        <v>1.83</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.55</v>
+        <v>1.67</v>
       </c>
       <c r="AV15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AW15" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="AX15" t="n">
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>53.73</v>
+        <v>53.58</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>17.09</v>
+        <v>16.92</v>
       </c>
       <c r="BB15" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="BC15" t="n">
-        <v>6.18</v>
+        <v>6</v>
       </c>
       <c r="BD15" t="n">
-        <v>17.64</v>
+        <v>18.42</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="BF15" t="n">
-        <v>3.09</v>
+        <v>2.83</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.18</v>
+        <v>3.39</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.36</v>
+        <v>10.17</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.18</v>
+        <v>3.39</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BK15" t="n">
         <v>0.91</v>
       </c>
       <c r="BL15" t="n">
-        <v>0.86</v>
+        <v>0.96</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.86</v>
+        <v>0.91</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.73</v>
+        <v>4.61</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS15" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT15" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU15" t="n">
-        <v>27.27</v>
+        <v>30.43</v>
       </c>
       <c r="BV15" t="n">
-        <v>18.18</v>
+        <v>21.74</v>
       </c>
       <c r="BW15" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BX15" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY15" t="n">
         <v>2.17</v>
@@ -6849,34 +6849,34 @@
         <v>2.33</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.66</v>
+        <v>3.64</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.82</v>
+        <v>3.81</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.1</v>
+        <v>3.12</v>
       </c>
       <c r="CE15" t="n">
         <v>1.27</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.39</v>
+        <v>3.37</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.51</v>
+        <v>2.49</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CK15" t="n">
         <v>1.37</v>
@@ -6891,24 +6891,28 @@
         <v>2.17</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CQ15" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="CR15" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="CS15" t="n">
         <v>2.36</v>
       </c>
-      <c r="CR15" t="inlineStr"/>
-      <c r="CS15" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="CT15" t="inlineStr"/>
+      <c r="CT15" t="n">
+        <v>3.38</v>
+      </c>
       <c r="CU15" t="n">
         <v>1.62</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CW15" t="n">
         <v>1.52</v>
@@ -6926,88 +6930,88 @@
         <v>2.18</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.86</v>
+        <v>1.78</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.78</v>
+        <v>2.69</v>
       </c>
       <c r="DH15" t="n">
-        <v>93.86</v>
+        <v>93.7</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.77</v>
+        <v>2.65</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.45</v>
+        <v>5.3</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="DM15" t="n">
-        <v>47.68</v>
+        <v>46.35</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.91</v>
+        <v>0.87</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.5</v>
+        <v>2.44</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.31</v>
+        <v>12.08</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.5</v>
+        <v>12.74</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.5</v>
+        <v>7.52</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.09</v>
+        <v>0.13</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.32</v>
+        <v>55.17</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.68</v>
+        <v>16.61</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.23</v>
+        <v>11.22</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.45</v>
+        <v>5.39</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.45</v>
+        <v>18.83</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.78</v>
+        <v>1.76</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.72</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="16">
@@ -7017,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7107,139 +7111,139 @@
         <v>2.58</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.9</v>
+        <v>1.82</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.3</v>
+        <v>3.18</v>
       </c>
       <c r="AI16" t="n">
-        <v>92.3</v>
+        <v>93.64</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.9</v>
+        <v>5.64</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="AN16" t="n">
-        <v>48.6</v>
+        <v>48.64</v>
       </c>
       <c r="AO16" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.6</v>
+        <v>2.45</v>
       </c>
       <c r="AQ16" t="n">
-        <v>13.1</v>
+        <v>12.82</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.8</v>
+        <v>13.73</v>
       </c>
       <c r="AS16" t="n">
-        <v>8.1</v>
+        <v>7.91</v>
       </c>
       <c r="AT16" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AU16" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="AV16" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AW16" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>49.36</v>
+      </c>
+      <c r="AZ16" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="BA16" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="BB16" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="BC16" t="n">
+        <v>4.36</v>
+      </c>
+      <c r="BD16" t="n">
+        <v>22.36</v>
+      </c>
+      <c r="BE16" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="BF16" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="BG16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BH16" t="n">
+        <v>9.779999999999999</v>
+      </c>
+      <c r="BI16" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="BJ16" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="BK16" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="BL16" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="BM16" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="BN16" t="n">
         <v>1.7</v>
-      </c>
-      <c r="AU16" t="n">
-        <v>0.9</v>
-      </c>
-      <c r="AV16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AW16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="AX16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY16" t="n">
-        <v>49.6</v>
-      </c>
-      <c r="AZ16" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="BA16" t="n">
-        <v>12</v>
-      </c>
-      <c r="BB16" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC16" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BD16" t="n">
-        <v>21.8</v>
-      </c>
-      <c r="BE16" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="BF16" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BG16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BH16" t="n">
-        <v>9.949999999999999</v>
-      </c>
-      <c r="BI16" t="n">
-        <v>2.73</v>
-      </c>
-      <c r="BJ16" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="BK16" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="BL16" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="BM16" t="n">
-        <v>0.68</v>
-      </c>
-      <c r="BN16" t="n">
-        <v>1.73</v>
       </c>
       <c r="BO16" t="n">
         <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.41</v>
+        <v>4.3</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.55</v>
+        <v>5.48</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.45</v>
+        <v>95.65000000000001</v>
       </c>
       <c r="BS16" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT16" t="n">
-        <v>59.09</v>
+        <v>56.52</v>
       </c>
       <c r="BU16" t="n">
-        <v>18.18</v>
+        <v>17.39</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.64</v>
+        <v>13.04</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.55</v>
+        <v>4.35</v>
       </c>
       <c r="BX16" t="n">
-        <v>63.64</v>
+        <v>65.22</v>
       </c>
       <c r="BY16" t="n">
         <v>2.37</v>
@@ -7248,16 +7252,16 @@
         <v>2.43</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB16" t="n">
-        <v>3.71</v>
+        <v>3.7</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.22</v>
+        <v>3.21</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="CE16" t="n">
         <v>1.32</v>
@@ -7284,10 +7288,10 @@
         <v>1.74</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO16" t="n">
         <v>1.2</v>
@@ -7296,7 +7300,7 @@
         <v>1.71</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7305,7 +7309,7 @@
         <v>2.6</v>
       </c>
       <c r="CT16" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU16" t="n">
         <v>1.53</v>
@@ -7326,7 +7330,7 @@
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DB16" t="n">
         <v>1.22</v>
@@ -7335,49 +7339,49 @@
         <v>1.72</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DE16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.95</v>
+        <v>1.91</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>94</v>
+        <v>94.56999999999999</v>
       </c>
       <c r="DI16" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.73</v>
+        <v>2.74</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.45</v>
+        <v>5.35</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="DM16" t="n">
-        <v>46.27</v>
+        <v>46.39</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.41</v>
+        <v>2.35</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.86</v>
+        <v>11.78</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.87</v>
+        <v>13.83</v>
       </c>
       <c r="DR16" t="n">
-        <v>8</v>
+        <v>7.92</v>
       </c>
       <c r="DS16" t="n">
         <v>0.13</v>
@@ -7389,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.95</v>
+        <v>49.82</v>
       </c>
       <c r="DW16" t="n">
         <v>0.09</v>
       </c>
       <c r="DX16" t="n">
-        <v>13.05</v>
+        <v>12.87</v>
       </c>
       <c r="DY16" t="n">
-        <v>8.130000000000001</v>
+        <v>8</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.91</v>
+        <v>4.87</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.27</v>
+        <v>20.61</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
     </row>
     <row r="17">
@@ -7420,94 +7424,94 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D17" t="n">
         <v>11</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="F17" t="n">
-        <v>1.36</v>
+        <v>1.25</v>
       </c>
       <c r="G17" t="n">
-        <v>3.82</v>
+        <v>3.5</v>
       </c>
       <c r="H17" t="n">
-        <v>102.36</v>
+        <v>101.08</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="K17" t="n">
-        <v>6.36</v>
+        <v>6.17</v>
       </c>
       <c r="L17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="M17" t="n">
-        <v>58.91</v>
+        <v>58.33</v>
       </c>
       <c r="N17" t="n">
-        <v>0.64</v>
+        <v>0.58</v>
       </c>
       <c r="O17" t="n">
-        <v>2.55</v>
+        <v>2.67</v>
       </c>
       <c r="P17" t="n">
-        <v>12.73</v>
+        <v>12</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.18</v>
+        <v>10.5</v>
       </c>
       <c r="R17" t="n">
-        <v>7.27</v>
+        <v>7.17</v>
       </c>
       <c r="S17" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="T17" t="n">
-        <v>1.73</v>
+        <v>2</v>
       </c>
       <c r="U17" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="V17" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>56</v>
+        <v>55.92</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.73</v>
+        <v>17.67</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.64</v>
+        <v>11.33</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.09</v>
+        <v>6.33</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.64</v>
+        <v>21.33</v>
       </c>
       <c r="AD17" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.82</v>
+        <v>1.67</v>
       </c>
       <c r="AF17" t="n">
         <v>0.27</v>
@@ -7591,64 +7595,64 @@
         <v>2.45</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.45</v>
+        <v>10.48</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.59</v>
+        <v>2.78</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.36</v>
+        <v>0.48</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="BL17" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.55</v>
+        <v>0.57</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.14</v>
+        <v>1.26</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.73</v>
+        <v>4.78</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.68</v>
+        <v>5.65</v>
       </c>
       <c r="BR17" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS17" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT17" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BU17" t="n">
-        <v>13.64</v>
+        <v>17.39</v>
       </c>
       <c r="BV17" t="n">
-        <v>4.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BW17" t="n">
-        <v>4.55</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="BX17" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="CA17" t="n">
         <v>3.64</v>
@@ -7675,7 +7679,7 @@
         <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="CJ17" t="n">
         <v>1.6</v>
@@ -7684,7 +7688,7 @@
         <v>1.37</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM17" t="n">
         <v>2.84</v>
@@ -7717,7 +7721,7 @@
         <v>2.39</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CX17" t="n">
         <v>1.46</v>
@@ -7741,79 +7745,79 @@
         <v>2.77</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.14</v>
+        <v>0.17</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.46</v>
+        <v>1.39</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.23</v>
+        <v>3.09</v>
       </c>
       <c r="DH17" t="n">
-        <v>100.54</v>
+        <v>99.95999999999999</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.37</v>
+        <v>2.26</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.64</v>
+        <v>5.57</v>
       </c>
       <c r="DL17" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="DM17" t="n">
+        <v>50</v>
+      </c>
+      <c r="DN17" t="n">
         <v>0.78</v>
       </c>
-      <c r="DM17" t="n">
-        <v>49.91</v>
-      </c>
-      <c r="DN17" t="n">
-        <v>0.82</v>
-      </c>
       <c r="DO17" t="n">
-        <v>2.37</v>
+        <v>2.44</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.64</v>
+        <v>12.26</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.77</v>
+        <v>10.91</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.32</v>
+        <v>7.26</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.22</v>
+        <v>0.26</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.41</v>
+        <v>54.44</v>
       </c>
       <c r="DW17" t="n">
         <v>0.13</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.82</v>
+        <v>15.87</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.37</v>
+        <v>10.26</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.45</v>
+        <v>5.61</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.18</v>
+        <v>21.04</v>
       </c>
       <c r="EB17" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.13</v>
+        <v>2.04</v>
       </c>
     </row>
     <row r="18">
@@ -7823,10 +7827,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D18" t="n">
         <v>11</v>
@@ -7835,82 +7839,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G18" t="n">
-        <v>1.64</v>
+        <v>1.83</v>
       </c>
       <c r="H18" t="n">
-        <v>91.27</v>
+        <v>91.33</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="J18" t="n">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="K18" t="n">
-        <v>4.45</v>
+        <v>4.58</v>
       </c>
       <c r="L18" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="M18" t="n">
-        <v>38.09</v>
+        <v>39.92</v>
       </c>
       <c r="N18" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O18" t="n">
-        <v>2.82</v>
+        <v>2.75</v>
       </c>
       <c r="P18" t="n">
-        <v>14.91</v>
+        <v>15</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.18</v>
+        <v>14.08</v>
       </c>
       <c r="R18" t="n">
-        <v>6.55</v>
+        <v>6.67</v>
       </c>
       <c r="S18" t="n">
-        <v>1.27</v>
+        <v>1.42</v>
       </c>
       <c r="T18" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="U18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="V18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>55.27</v>
+        <v>55.25</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.18</v>
+        <v>13.75</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.550000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.64</v>
+        <v>4.92</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.45</v>
+        <v>21.17</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AF18" t="n">
         <v>0.09</v>
@@ -7994,70 +7998,70 @@
         <v>3.64</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.77</v>
+        <v>9.83</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.59</v>
+        <v>0.61</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.41</v>
+        <v>0.52</v>
       </c>
       <c r="BL18" t="n">
         <v>0.91</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="BO18" t="n">
-        <v>1</v>
+        <v>1.13</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.64</v>
+        <v>4.65</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.14</v>
+        <v>5.17</v>
       </c>
       <c r="BR18" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS18" t="n">
-        <v>81.81999999999999</v>
+        <v>82.61</v>
       </c>
       <c r="BT18" t="n">
-        <v>54.55</v>
+        <v>56.52</v>
       </c>
       <c r="BU18" t="n">
-        <v>22.73</v>
+        <v>26.09</v>
       </c>
       <c r="BV18" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>72.73</v>
+        <v>73.91</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.86</v>
+        <v>2.83</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.51</v>
+        <v>3.5</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.59</v>
+        <v>3.58</v>
       </c>
       <c r="CC18" t="n">
         <v>3.72</v>
@@ -8102,22 +8106,22 @@
         <v>1.76</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CU18" t="n">
         <v>1.48</v>
       </c>
       <c r="CV18" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CW18" t="n">
         <v>1.68</v>
@@ -8138,10 +8142,10 @@
         <v>1.26</v>
       </c>
       <c r="DC18" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.01</v>
+        <v>3.03</v>
       </c>
       <c r="DE18" t="n">
         <v>0.04</v>
@@ -8150,25 +8154,25 @@
         <v>1.96</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="DH18" t="n">
-        <v>88</v>
+        <v>88.17</v>
       </c>
       <c r="DI18" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.32</v>
+        <v>3.31</v>
       </c>
       <c r="DK18" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.27</v>
+        <v>0.3</v>
       </c>
       <c r="DM18" t="n">
-        <v>35.14</v>
+        <v>36.22</v>
       </c>
       <c r="DN18" t="n">
         <v>1.18</v>
@@ -8177,10 +8181,10 @@
         <v>2.13</v>
       </c>
       <c r="DP18" t="n">
-        <v>13.78</v>
+        <v>13.87</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.72</v>
+        <v>13.69</v>
       </c>
       <c r="DR18" t="n">
         <v>7.78</v>
@@ -8195,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>56.09</v>
+        <v>56.04</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.13</v>
+        <v>12.48</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.050000000000001</v>
+        <v>8.220000000000001</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.1</v>
+        <v>4.26</v>
       </c>
       <c r="EA18" t="n">
-        <v>21.27</v>
+        <v>21.13</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="19">
@@ -8226,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D19" t="n">
         <v>12</v>
       </c>
       <c r="E19" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="F19" t="n">
-        <v>2.1</v>
+        <v>2.09</v>
       </c>
       <c r="G19" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H19" t="n">
-        <v>103.1</v>
+        <v>105.82</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.6</v>
+        <v>2.55</v>
       </c>
       <c r="K19" t="n">
-        <v>5.8</v>
+        <v>5.64</v>
       </c>
       <c r="L19" t="n">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="M19" t="n">
-        <v>50.4</v>
+        <v>52.09</v>
       </c>
       <c r="N19" t="n">
-        <v>0.5</v>
+        <v>0.45</v>
       </c>
       <c r="O19" t="n">
-        <v>2.3</v>
+        <v>2.18</v>
       </c>
       <c r="P19" t="n">
-        <v>13.6</v>
+        <v>13.82</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.6</v>
+        <v>12.09</v>
       </c>
       <c r="R19" t="n">
-        <v>5.5</v>
+        <v>5.64</v>
       </c>
       <c r="S19" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="T19" t="n">
-        <v>1.4</v>
+        <v>1.73</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.09</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>44.5</v>
+        <v>44.82</v>
       </c>
       <c r="Y19" t="n">
-        <v>0.1</v>
+        <v>0.09</v>
       </c>
       <c r="Z19" t="n">
-        <v>13.7</v>
+        <v>14.45</v>
       </c>
       <c r="AA19" t="n">
         <v>9</v>
       </c>
       <c r="AB19" t="n">
-        <v>4.7</v>
+        <v>5.45</v>
       </c>
       <c r="AC19" t="n">
-        <v>21</v>
+        <v>21.64</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.56</v>
+        <v>1.68</v>
       </c>
       <c r="AE19" t="n">
-        <v>2.5</v>
+        <v>2.45</v>
       </c>
       <c r="AF19" t="n">
         <v>0.17</v>
@@ -8397,70 +8401,70 @@
         <v>2.33</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.68</v>
+        <v>9.52</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.05</v>
+        <v>2.3</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.32</v>
+        <v>0.39</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.45</v>
+        <v>0.48</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.73</v>
+        <v>0.83</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.55</v>
+        <v>0.61</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.27</v>
+        <v>1.43</v>
       </c>
       <c r="BO19" t="n">
-        <v>0.77</v>
+        <v>0.87</v>
       </c>
       <c r="BP19" t="n">
-        <v>4</v>
+        <v>3.91</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.64</v>
+        <v>5.57</v>
       </c>
       <c r="BR19" t="n">
-        <v>90.91</v>
+        <v>91.3</v>
       </c>
       <c r="BS19" t="n">
-        <v>59.09</v>
+        <v>60.87</v>
       </c>
       <c r="BT19" t="n">
-        <v>45.45</v>
+        <v>47.83</v>
       </c>
       <c r="BU19" t="n">
-        <v>9.09</v>
+        <v>13.04</v>
       </c>
       <c r="BV19" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BW19" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="BX19" t="n">
-        <v>40.91</v>
+        <v>43.48</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.23</v>
+        <v>2.2</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CA19" t="n">
         <v>3.39</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.52</v>
+        <v>3.53</v>
       </c>
       <c r="CC19" t="n">
         <v>2.67</v>
@@ -8472,7 +8476,7 @@
         <v>1.36</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="CG19" t="n">
         <v>2.95</v>
@@ -8505,25 +8509,25 @@
         <v>1.82</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.03</v>
+        <v>3.02</v>
       </c>
       <c r="CR19" t="n">
         <v>1.38</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.79</v>
+        <v>2.78</v>
       </c>
       <c r="CT19" t="n">
-        <v>3.17</v>
+        <v>3.19</v>
       </c>
       <c r="CU19" t="n">
         <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CX19" t="n">
         <v>1.5</v>
@@ -8544,82 +8548,82 @@
         <v>1.88</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="DG19" t="n">
         <v>2.91</v>
       </c>
       <c r="DH19" t="n">
-        <v>105.13</v>
+        <v>106.35</v>
       </c>
       <c r="DI19" t="n">
         <v>0.09</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.09</v>
+        <v>5.05</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.36</v>
+        <v>0.39</v>
       </c>
       <c r="DM19" t="n">
-        <v>47.55</v>
+        <v>48.48</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.73</v>
+        <v>0.7</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.18</v>
+        <v>2.13</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.64</v>
+        <v>13.74</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.37</v>
+        <v>12.13</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.82</v>
+        <v>5.87</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.18</v>
+        <v>0.22</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>43.64</v>
+        <v>43.83</v>
       </c>
       <c r="DW19" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>13</v>
+        <v>13.39</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.550000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.45</v>
+        <v>4.82</v>
       </c>
       <c r="EA19" t="n">
-        <v>22.09</v>
+        <v>22.35</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -2735,25 +2735,25 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.75</v>
+        <v>48.83</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.25</v>
+        <v>13.17</v>
       </c>
       <c r="BB5" t="n">
         <v>9.42</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="BD5" t="n">
         <v>22.17</v>
       </c>
       <c r="BE5" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BF5" t="n">
         <v>2</v>
@@ -2960,19 +2960,19 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>48.87</v>
+        <v>48.91</v>
       </c>
       <c r="DW5" t="n">
         <v>0.13</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.61</v>
+        <v>12.57</v>
       </c>
       <c r="DY5" t="n">
         <v>8.74</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.87</v>
+        <v>3.83</v>
       </c>
       <c r="EA5" t="n">
         <v>21.44</v>
@@ -4669,16 +4669,16 @@
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.27</v>
+        <v>57.18</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>17.09</v>
+        <v>17</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.36</v>
+        <v>11.27</v>
       </c>
       <c r="AB10" t="n">
         <v>5.73</v>
@@ -4687,7 +4687,7 @@
         <v>19.73</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AE10" t="n">
         <v>1.55</v>
@@ -4975,16 +4975,16 @@
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.87</v>
+        <v>55.82</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.83</v>
+        <v>14.78</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.35</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="DZ10" t="n">
         <v>5.48</v>
@@ -5153,7 +5153,7 @@
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.45</v>
+        <v>47.55</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
@@ -5378,7 +5378,7 @@
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.48</v>
+        <v>48.53</v>
       </c>
       <c r="DW11" t="n">
         <v>0.13</v>
@@ -5965,13 +5965,13 @@
         <v>0.09</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.55</v>
+        <v>11.64</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.64</v>
+        <v>7.82</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.91</v>
+        <v>3.82</v>
       </c>
       <c r="BD13" t="n">
         <v>20</v>
@@ -6190,13 +6190,13 @@
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.57</v>
+        <v>13.61</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.609999999999999</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="EA13" t="n">
         <v>21.91</v>
@@ -7490,7 +7490,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>55.92</v>
+        <v>55.83</v>
       </c>
       <c r="Y17" t="n">
         <v>0.17</v>
@@ -7796,7 +7796,7 @@
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.44</v>
+        <v>54.39</v>
       </c>
       <c r="DW17" t="n">
         <v>0.13</v>
@@ -7899,10 +7899,10 @@
         <v>0.17</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.75</v>
+        <v>13.67</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.83</v>
+        <v>8.75</v>
       </c>
       <c r="AB18" t="n">
         <v>4.92</v>
@@ -8205,10 +8205,10 @@
         <v>0.17</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.48</v>
+        <v>12.44</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.220000000000001</v>
+        <v>8.18</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.26</v>
@@ -8302,19 +8302,19 @@
         <v>0.09</v>
       </c>
       <c r="Z19" t="n">
-        <v>14.45</v>
+        <v>14.36</v>
       </c>
       <c r="AA19" t="n">
         <v>9</v>
       </c>
       <c r="AB19" t="n">
-        <v>5.45</v>
+        <v>5.36</v>
       </c>
       <c r="AC19" t="n">
         <v>21.64</v>
       </c>
       <c r="AD19" t="n">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="AE19" t="n">
         <v>2.45</v>
@@ -8608,19 +8608,19 @@
         <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.39</v>
+        <v>13.35</v>
       </c>
       <c r="DY19" t="n">
         <v>8.57</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.82</v>
+        <v>4.78</v>
       </c>
       <c r="EA19" t="n">
         <v>22.35</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="EC19" t="n">
         <v>2.39</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D2" t="n">
         <v>12</v>
       </c>
       <c r="E2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F2" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G2" t="n">
-        <v>4.27</v>
+        <v>4.08</v>
       </c>
       <c r="H2" t="n">
-        <v>102.36</v>
+        <v>103.67</v>
       </c>
       <c r="I2" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J2" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="K2" t="n">
-        <v>6.55</v>
+        <v>6.75</v>
       </c>
       <c r="L2" t="n">
-        <v>0.18</v>
+        <v>0.33</v>
       </c>
       <c r="M2" t="n">
-        <v>49.55</v>
+        <v>50.17</v>
       </c>
       <c r="N2" t="n">
-        <v>0.82</v>
+        <v>0.75</v>
       </c>
       <c r="O2" t="n">
-        <v>2.27</v>
+        <v>2.58</v>
       </c>
       <c r="P2" t="n">
-        <v>13.18</v>
+        <v>13.5</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.82</v>
+        <v>13.75</v>
       </c>
       <c r="R2" t="n">
-        <v>7.73</v>
+        <v>7.67</v>
       </c>
       <c r="S2" t="n">
-        <v>1.27</v>
+        <v>1.25</v>
       </c>
       <c r="T2" t="n">
-        <v>2</v>
+        <v>1.83</v>
       </c>
       <c r="U2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="V2" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>55.36</v>
+        <v>54.33</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>14.73</v>
+        <v>15.33</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.09</v>
+        <v>10.5</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.64</v>
+        <v>4.83</v>
       </c>
       <c r="AC2" t="n">
-        <v>23</v>
+        <v>22.75</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,64 +1550,64 @@
         <v>2.33</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.52</v>
+        <v>10.58</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BP2" t="n">
-        <v>3.96</v>
+        <v>4.12</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.52</v>
+        <v>6.38</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS2" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT2" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BV2" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX2" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.11</v>
+        <v>2.16</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.21</v>
+        <v>2.26</v>
       </c>
       <c r="CA2" t="n">
         <v>3.56</v>
@@ -1631,10 +1631,10 @@
         <v>3.21</v>
       </c>
       <c r="CH2" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.57</v>
@@ -1646,7 +1646,7 @@
         <v>1.74</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.81</v>
+        <v>2.8</v>
       </c>
       <c r="CN2" t="n">
         <v>2.17</v>
@@ -1658,16 +1658,16 @@
         <v>1.68</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.62</v>
+        <v>2.63</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.16</v>
+        <v>3.19</v>
       </c>
       <c r="CU2" t="n">
         <v>1.54</v>
@@ -1700,79 +1700,79 @@
         <v>2.74</v>
       </c>
       <c r="DE2" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="DG2" t="n">
-        <v>4.04</v>
+        <v>3.96</v>
       </c>
       <c r="DH2" t="n">
-        <v>102.52</v>
+        <v>103.17</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.26</v>
+        <v>2.21</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.3</v>
+        <v>6.42</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.35</v>
+        <v>0.42</v>
       </c>
       <c r="DM2" t="n">
-        <v>50.83</v>
+        <v>51.08</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.26</v>
+        <v>2.42</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.61</v>
+        <v>13.75</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.83</v>
+        <v>13.79</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.26</v>
+        <v>7.25</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>52.13</v>
+        <v>51.75</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>13.96</v>
+        <v>14.29</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.74</v>
+        <v>9.960000000000001</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.22</v>
+        <v>4.33</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.91</v>
+        <v>23.75</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.13</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C3" t="n">
         <v>12</v>
       </c>
       <c r="D3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E3" t="n">
         <v>0.08</v>
@@ -1872,139 +1872,139 @@
         <v>3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="AI3" t="n">
-        <v>83.81999999999999</v>
+        <v>83</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK3" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.82</v>
+        <v>5.58</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AN3" t="n">
-        <v>39.09</v>
+        <v>39.25</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.91</v>
+        <v>2.67</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.82</v>
+        <v>12.58</v>
       </c>
       <c r="AR3" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.359999999999999</v>
+        <v>9.17</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.55</v>
+        <v>44.58</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>12</v>
+        <v>11.83</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.449999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BD3" t="n">
-        <v>23.18</v>
+        <v>23.33</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="BF3" t="n">
-        <v>3.09</v>
+        <v>2.92</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.48</v>
+        <v>11.54</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BO3" t="n">
         <v>1.17</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.57</v>
+        <v>5.71</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.91</v>
+        <v>5.83</v>
       </c>
       <c r="BR3" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS3" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT3" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BU3" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV3" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX3" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY3" t="n">
         <v>2.2</v>
@@ -2013,64 +2013,64 @@
         <v>2.34</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.6</v>
+        <v>3.58</v>
       </c>
       <c r="CB3" t="n">
         <v>3.67</v>
       </c>
       <c r="CC3" t="n">
-        <v>3.01</v>
+        <v>3.02</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="CH3" t="n">
         <v>1.51</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ3" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK3" t="n">
         <v>1.33</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CM3" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CO3" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CQ3" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="CR3" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="CS3" t="n">
         <v>2.61</v>
       </c>
-      <c r="CR3" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="CS3" t="n">
-        <v>2.62</v>
-      </c>
       <c r="CT3" t="n">
-        <v>3.24</v>
+        <v>3.25</v>
       </c>
       <c r="CU3" t="n">
         <v>1.52</v>
@@ -2085,13 +2085,13 @@
         <v>1.45</v>
       </c>
       <c r="CY3" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CZ3" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="DA3" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="DB3" t="n">
         <v>1.22</v>
@@ -2103,79 +2103,79 @@
         <v>2.73</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.09</v>
+        <v>2.04</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.31</v>
+        <v>93.45999999999999</v>
       </c>
       <c r="DI3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="DJ3" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.65</v>
+        <v>5.54</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.96</v>
+        <v>46.71</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.78</v>
+        <v>2.67</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.7</v>
+        <v>13.54</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.56</v>
+        <v>9.58</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.69</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU3" t="n">
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.92</v>
+        <v>45.88</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.31</v>
+        <v>14.12</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.82</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.48</v>
+        <v>4.42</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.21</v>
+        <v>22.33</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="EC3" t="n">
-        <v>3.04</v>
+        <v>2.96</v>
       </c>
     </row>
     <row r="4">
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" t="n">
         <v>12</v>
       </c>
       <c r="D4" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E4" t="n">
         <v>0.33</v>
@@ -2275,139 +2275,139 @@
         <v>2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.09</v>
+        <v>2.5</v>
       </c>
       <c r="AI4" t="n">
-        <v>89.27</v>
+        <v>89.42</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AL4" t="n">
-        <v>4.73</v>
+        <v>5</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN4" t="n">
-        <v>36.73</v>
+        <v>37.33</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.27</v>
+        <v>0.33</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.64</v>
+        <v>11.75</v>
       </c>
       <c r="AR4" t="n">
-        <v>10.91</v>
+        <v>11.5</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.17</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX4" t="n">
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>50.82</v>
+        <v>50.83</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.45</v>
+        <v>12.83</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.09</v>
+        <v>8.25</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.36</v>
+        <v>4.58</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.82</v>
+        <v>17.67</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.7</v>
+        <v>10.62</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.87</v>
+        <v>0.92</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL4" t="n">
         <v>0.96</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.17</v>
+        <v>5.04</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.52</v>
+        <v>5.58</v>
       </c>
       <c r="BR4" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS4" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BT4" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU4" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BV4" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX4" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY4" t="n">
         <v>1.86</v>
@@ -2416,22 +2416,22 @@
         <v>1.9</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.67</v>
+        <v>3.66</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.09</v>
+        <v>3.08</v>
       </c>
       <c r="CE4" t="n">
         <v>1.31</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="CG4" t="n">
         <v>3.2</v>
@@ -2452,7 +2452,7 @@
         <v>1.77</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN4" t="n">
         <v>2.07</v>
@@ -2461,22 +2461,22 @@
         <v>1.18</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
       </c>
       <c r="CS4" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="CT4" t="n">
         <v>3.28</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CV4" t="n">
         <v>2.42</v>
@@ -2488,7 +2488,7 @@
         <v>1.47</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.58</v>
@@ -2497,55 +2497,55 @@
         <v>2.11</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.35</v>
+        <v>2.54</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.39</v>
+        <v>88.5</v>
       </c>
       <c r="DI4" t="n">
         <v>0.05</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.78</v>
+        <v>1.83</v>
       </c>
       <c r="DK4" t="n">
-        <v>5</v>
+        <v>5.12</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.05</v>
+        <v>42.12</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.26</v>
+        <v>11.34</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.61</v>
+        <v>11.88</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.44</v>
+        <v>8.210000000000001</v>
       </c>
       <c r="DS4" t="n">
         <v>0.08</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>49.96</v>
+        <v>50</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.78</v>
+        <v>13.92</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.43</v>
+        <v>8.5</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.35</v>
+        <v>5.42</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.26</v>
+        <v>17.21</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
     </row>
     <row r="5">
@@ -2588,67 +2588,67 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C5" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D5" t="n">
         <v>12</v>
       </c>
       <c r="E5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="G5" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="H5" t="n">
-        <v>85.45</v>
+        <v>86.17</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>0.08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="K5" t="n">
-        <v>5.09</v>
+        <v>4.75</v>
       </c>
       <c r="L5" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M5" t="n">
-        <v>43.27</v>
+        <v>42.58</v>
       </c>
       <c r="N5" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="O5" t="n">
-        <v>2.09</v>
+        <v>2</v>
       </c>
       <c r="P5" t="n">
-        <v>10.45</v>
+        <v>10.83</v>
       </c>
       <c r="Q5" t="n">
-        <v>13.09</v>
+        <v>13.08</v>
       </c>
       <c r="R5" t="n">
-        <v>7.18</v>
+        <v>7.17</v>
       </c>
       <c r="S5" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="T5" t="n">
-        <v>1.45</v>
+        <v>1.58</v>
       </c>
       <c r="U5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -2657,22 +2657,22 @@
         <v>49</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="Z5" t="n">
-        <v>11.91</v>
+        <v>12.5</v>
       </c>
       <c r="AA5" t="n">
-        <v>8</v>
+        <v>8.33</v>
       </c>
       <c r="AB5" t="n">
-        <v>3.91</v>
+        <v>4.17</v>
       </c>
       <c r="AC5" t="n">
-        <v>20.64</v>
+        <v>20</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="AE5" t="n">
         <v>2</v>
@@ -2759,70 +2759,70 @@
         <v>2</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="BH5" t="n">
-        <v>11.04</v>
+        <v>10.96</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.13</v>
+        <v>3.17</v>
       </c>
       <c r="BJ5" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="BK5" t="n">
         <v>0.83</v>
       </c>
-      <c r="BK5" t="n">
-        <v>0.87</v>
-      </c>
       <c r="BL5" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.91</v>
+        <v>4.79</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.09</v>
+        <v>6.12</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS5" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BT5" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BU5" t="n">
-        <v>34.78</v>
+        <v>37.5</v>
       </c>
       <c r="BV5" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX5" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.54</v>
+        <v>2.57</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CC5" t="n">
         <v>3.78</v>
@@ -2840,10 +2840,10 @@
         <v>3.23</v>
       </c>
       <c r="CH5" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.59</v>
@@ -2876,7 +2876,7 @@
         <v>2.58</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU5" t="n">
         <v>1.54</v>
@@ -2906,49 +2906,49 @@
         <v>1.73</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.76</v>
+        <v>2.77</v>
       </c>
       <c r="DE5" t="n">
         <v>0.08</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.96</v>
+        <v>2.83</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.22</v>
+        <v>91.34</v>
       </c>
       <c r="DI5" t="n">
-        <v>0.09</v>
+        <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.22</v>
+        <v>2.25</v>
       </c>
       <c r="DK5" t="n">
-        <v>5.04</v>
+        <v>4.88</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.39</v>
+        <v>0.38</v>
       </c>
       <c r="DM5" t="n">
-        <v>44.82</v>
+        <v>44.42</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.71</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="DP5" t="n">
-        <v>10.91</v>
+        <v>11.08</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.39</v>
+        <v>12.42</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.09</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS5" t="n">
         <v>0.04</v>
@@ -2960,25 +2960,25 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>48.91</v>
+        <v>48.92</v>
       </c>
       <c r="DW5" t="n">
-        <v>0.13</v>
+        <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.57</v>
+        <v>12.84</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.74</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.83</v>
+        <v>3.96</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.44</v>
+        <v>21.08</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="EC5" t="n">
         <v>2</v>
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C7" t="n">
         <v>11</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E7" t="n">
         <v>0.18</v>
@@ -3490,133 +3490,133 @@
         <v>1.92</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AI7" t="n">
-        <v>96.42</v>
+        <v>95.77</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.58</v>
+        <v>2.54</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.08</v>
+        <v>6.15</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AN7" t="n">
-        <v>47</v>
+        <v>47.15</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP7" t="n">
         <v>3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.25</v>
+        <v>10.77</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.83</v>
+        <v>14.92</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.17</v>
+        <v>7.23</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.92</v>
+        <v>1.85</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.92</v>
+        <v>53.38</v>
       </c>
       <c r="AZ7" t="n">
         <v>0.08</v>
       </c>
       <c r="BA7" t="n">
-        <v>14.75</v>
+        <v>14.15</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.5</v>
+        <v>9.08</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.25</v>
+        <v>5.08</v>
       </c>
       <c r="BD7" t="n">
-        <v>21.67</v>
+        <v>22.08</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.5</v>
+        <v>2.46</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.48</v>
+        <v>10.54</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.91</v>
+        <v>2.88</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BL7" t="n">
         <v>0.96</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.13</v>
+        <v>5.17</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.65</v>
+        <v>4.71</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS7" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT7" t="n">
-        <v>56.52</v>
+        <v>54.17</v>
       </c>
       <c r="BU7" t="n">
-        <v>39.13</v>
+        <v>37.5</v>
       </c>
       <c r="BV7" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX7" t="n">
-        <v>52.17</v>
+        <v>54.17</v>
       </c>
       <c r="BY7" t="n">
         <v>1.91</v>
@@ -3625,46 +3625,46 @@
         <v>1.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.46</v>
+        <v>3.47</v>
       </c>
       <c r="CB7" t="n">
         <v>3.75</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.58</v>
+        <v>2.55</v>
       </c>
       <c r="CE7" t="n">
         <v>1.25</v>
       </c>
       <c r="CF7" t="n">
-        <v>2.34</v>
+        <v>2.35</v>
       </c>
       <c r="CG7" t="n">
         <v>3.15</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.5</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="CL7" t="n">
         <v>1.62</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN7" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO7" t="n">
         <v>1.15</v>
@@ -3703,28 +3703,28 @@
         <v>2.6</v>
       </c>
       <c r="DA7" t="n">
-        <v>2.16</v>
+        <v>2.17</v>
       </c>
       <c r="DB7" t="n">
         <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DE7" t="n">
         <v>0.13</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.65</v>
+        <v>2.71</v>
       </c>
       <c r="DH7" t="n">
-        <v>99.22</v>
+        <v>98.75</v>
       </c>
       <c r="DI7" t="n">
         <v>0.17</v>
@@ -3733,58 +3733,58 @@
         <v>2.04</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.08</v>
+        <v>6.12</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="DM7" t="n">
-        <v>51.74</v>
+        <v>51.62</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.52</v>
+        <v>10.79</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.3</v>
+        <v>14.37</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.83</v>
+        <v>6.87</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.7</v>
+        <v>54.37</v>
       </c>
       <c r="DW7" t="n">
         <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.39</v>
+        <v>15.04</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.26</v>
+        <v>10</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.13</v>
+        <v>5.04</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.96</v>
+        <v>23.12</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="EC7" t="n">
         <v>2</v>
@@ -3797,10 +3797,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D8" t="n">
         <v>11</v>
@@ -3809,49 +3809,49 @@
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="H8" t="n">
-        <v>92.67</v>
+        <v>93.84999999999999</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.17</v>
+        <v>-0.15</v>
       </c>
       <c r="J8" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>4.46</v>
       </c>
       <c r="L8" t="n">
-        <v>0.17</v>
+        <v>0.38</v>
       </c>
       <c r="M8" t="n">
-        <v>51.75</v>
+        <v>51.54</v>
       </c>
       <c r="N8" t="n">
-        <v>1.33</v>
+        <v>1.23</v>
       </c>
       <c r="O8" t="n">
-        <v>1.58</v>
+        <v>2.15</v>
       </c>
       <c r="P8" t="n">
-        <v>12.5</v>
+        <v>11.92</v>
       </c>
       <c r="Q8" t="n">
-        <v>11.33</v>
+        <v>11.46</v>
       </c>
       <c r="R8" t="n">
-        <v>6.17</v>
+        <v>6.31</v>
       </c>
       <c r="S8" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="T8" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -3863,28 +3863,28 @@
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>51.33</v>
+        <v>51.62</v>
       </c>
       <c r="Y8" t="n">
         <v>0.08</v>
       </c>
       <c r="Z8" t="n">
-        <v>12.17</v>
+        <v>12.77</v>
       </c>
       <c r="AA8" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
       <c r="AB8" t="n">
-        <v>3.58</v>
+        <v>4</v>
       </c>
       <c r="AC8" t="n">
-        <v>21.92</v>
+        <v>21.62</v>
       </c>
       <c r="AD8" t="n">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="AE8" t="n">
-        <v>2.83</v>
+        <v>2.69</v>
       </c>
       <c r="AF8" t="n">
         <v>0.09</v>
@@ -3968,70 +3968,70 @@
         <v>2.27</v>
       </c>
       <c r="BG8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BH8" t="n">
+        <v>8.92</v>
+      </c>
+      <c r="BI8" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BJ8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="BK8" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="BQ8" t="n">
+        <v>5</v>
+      </c>
+      <c r="BR8" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="BS8" t="n">
+        <v>70.83</v>
+      </c>
+      <c r="BT8" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="BU8" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BV8" t="n">
+        <v>8.33</v>
+      </c>
+      <c r="BW8" t="n">
+        <v>4.17</v>
+      </c>
+      <c r="BX8" t="n">
+        <v>58.33</v>
+      </c>
+      <c r="BY8" t="n">
         <v>2.35</v>
       </c>
-      <c r="BH8" t="n">
-        <v>8.74</v>
-      </c>
-      <c r="BI8" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="BJ8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="BK8" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BL8" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="BM8" t="n">
-        <v>0.65</v>
-      </c>
-      <c r="BN8" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="BO8" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="BP8" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="BQ8" t="n">
-        <v>5.04</v>
-      </c>
-      <c r="BR8" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="BS8" t="n">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="BT8" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="BU8" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BV8" t="n">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="BW8" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="BX8" t="n">
-        <v>56.52</v>
-      </c>
-      <c r="BY8" t="n">
-        <v>2.36</v>
-      </c>
       <c r="BZ8" t="n">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.76</v>
+        <v>3.75</v>
       </c>
       <c r="CC8" t="n">
         <v>3.45</v>
@@ -4043,16 +4043,16 @@
         <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.17</v>
+        <v>3.16</v>
       </c>
       <c r="CH8" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="CI8" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CJ8" t="n">
         <v>1.58</v>
@@ -4061,7 +4061,7 @@
         <v>1.41</v>
       </c>
       <c r="CL8" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="CM8" t="n">
         <v>2.64</v>
@@ -4076,16 +4076,16 @@
         <v>1.66</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CR8" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="CS8" t="n">
         <v>2.58</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CU8" t="n">
         <v>1.53</v>
@@ -4097,13 +4097,13 @@
         <v>1.6</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="CY8" t="n">
         <v>1.74</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.49</v>
+        <v>2.51</v>
       </c>
       <c r="DA8" t="n">
         <v>2.08</v>
@@ -4121,43 +4121,43 @@
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.57</v>
+        <v>2.5</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.22</v>
+        <v>93.84</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.05</v>
+        <v>-0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.79</v>
+        <v>2.71</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.22</v>
+        <v>4.46</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.17</v>
+        <v>0.29</v>
       </c>
       <c r="DM8" t="n">
-        <v>47.04</v>
+        <v>47.13</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.26</v>
+        <v>1.21</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.61</v>
+        <v>1.92</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.61</v>
+        <v>12.29</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.74</v>
+        <v>11.79</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.83</v>
+        <v>7.84</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.52</v>
+        <v>48.79</v>
       </c>
       <c r="DW8" t="n">
         <v>0.17</v>
       </c>
       <c r="DX8" t="n">
-        <v>12.96</v>
+        <v>13.25</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.09</v>
+        <v>9.17</v>
       </c>
       <c r="DZ8" t="n">
-        <v>3.87</v>
+        <v>4.08</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.65</v>
+        <v>20.54</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.43</v>
+        <v>1.46</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>0.36</v>
+        <v>0.33</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="H9" t="n">
-        <v>86.36</v>
+        <v>84.25</v>
       </c>
       <c r="I9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="J9" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="K9" t="n">
-        <v>4.55</v>
+        <v>4.5</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>33</v>
+        <v>32.08</v>
       </c>
       <c r="N9" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="O9" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="P9" t="n">
-        <v>10.64</v>
+        <v>10.33</v>
       </c>
       <c r="Q9" t="n">
-        <v>15.18</v>
+        <v>14.75</v>
       </c>
       <c r="R9" t="n">
-        <v>8.09</v>
+        <v>8.5</v>
       </c>
       <c r="S9" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="T9" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>45.18</v>
+        <v>44.67</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z9" t="n">
-        <v>10.27</v>
+        <v>9.92</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.91</v>
+        <v>6.75</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.27</v>
+        <v>19.33</v>
       </c>
       <c r="AD9" t="n">
-        <v>1.13</v>
+        <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,64 +4371,64 @@
         <v>2.58</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.83</v>
+        <v>3.75</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.22</v>
+        <v>1.17</v>
       </c>
       <c r="BM9" t="n">
         <v>0.96</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.17</v>
+        <v>4.21</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.3</v>
+        <v>5.25</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS9" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT9" t="n">
-        <v>73.91</v>
+        <v>70.83</v>
       </c>
       <c r="BU9" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BV9" t="n">
-        <v>34.78</v>
+        <v>33.33</v>
       </c>
       <c r="BW9" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BX9" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY9" t="n">
-        <v>2.99</v>
+        <v>3.15</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.42</v>
+        <v>3.54</v>
       </c>
       <c r="CA9" t="n">
         <v>3.77</v>
@@ -4449,151 +4449,151 @@
         <v>2.37</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="CJ9" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CO9" t="n">
         <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.5</v>
+        <v>2.53</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="CT9" t="n">
-        <v>3.33</v>
+        <v>3.32</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.45</v>
+        <v>2.43</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CX9" t="n">
         <v>1.47</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ9" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="DA9" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DB9" t="n">
         <v>1.2</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.58</v>
+        <v>2.61</v>
       </c>
       <c r="DE9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.91</v>
+        <v>80.08</v>
       </c>
       <c r="DI9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.3</v>
+        <v>4.29</v>
       </c>
       <c r="DL9" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.87</v>
+        <v>33.38</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="DP9" t="n">
-        <v>12.17</v>
+        <v>11.96</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.43</v>
+        <v>13.29</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.52</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DS9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT9" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU9" t="n">
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.39</v>
+        <v>46.08</v>
       </c>
       <c r="DW9" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.13</v>
+        <v>10.92</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.22</v>
+        <v>7.12</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.91</v>
+        <v>3.8</v>
       </c>
       <c r="EA9" t="n">
-        <v>21.04</v>
+        <v>21</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
     </row>
     <row r="10">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C10" t="n">
         <v>11</v>
       </c>
       <c r="D10" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E10" t="n">
         <v>0.18</v>
@@ -4693,139 +4693,139 @@
         <v>1.55</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AI10" t="n">
-        <v>100.67</v>
+        <v>98.62</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.75</v>
+        <v>4.62</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN10" t="n">
-        <v>45.17</v>
+        <v>44.69</v>
       </c>
       <c r="AO10" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AP10" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="AQ10" t="n">
-        <v>13.33</v>
+        <v>13.31</v>
       </c>
       <c r="AR10" t="n">
-        <v>13.5</v>
+        <v>13.85</v>
       </c>
       <c r="AS10" t="n">
-        <v>6.33</v>
+        <v>6.54</v>
       </c>
       <c r="AT10" t="n">
-        <v>1.42</v>
+        <v>1.31</v>
       </c>
       <c r="AU10" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="AX10" t="n">
         <v>0</v>
       </c>
       <c r="AY10" t="n">
-        <v>54.58</v>
+        <v>54.77</v>
       </c>
       <c r="AZ10" t="n">
         <v>0.08</v>
       </c>
       <c r="BA10" t="n">
-        <v>12.75</v>
+        <v>12.23</v>
       </c>
       <c r="BB10" t="n">
-        <v>7.5</v>
+        <v>7.31</v>
       </c>
       <c r="BC10" t="n">
-        <v>5.25</v>
+        <v>4.92</v>
       </c>
       <c r="BD10" t="n">
-        <v>19.25</v>
+        <v>19.31</v>
       </c>
       <c r="BE10" t="n">
-        <v>1.5</v>
+        <v>1.45</v>
       </c>
       <c r="BF10" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="BG10" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.57</v>
+        <v>9.67</v>
       </c>
       <c r="BI10" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.3</v>
+        <v>4.46</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.26</v>
+        <v>5.17</v>
       </c>
       <c r="BR10" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS10" t="n">
-        <v>86.95999999999999</v>
+        <v>83.33</v>
       </c>
       <c r="BT10" t="n">
-        <v>78.26000000000001</v>
+        <v>75</v>
       </c>
       <c r="BU10" t="n">
-        <v>43.48</v>
+        <v>41.67</v>
       </c>
       <c r="BV10" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>60.87</v>
+        <v>58.33</v>
       </c>
       <c r="BY10" t="n">
         <v>1.78</v>
@@ -4837,13 +4837,13 @@
         <v>3.7</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.83</v>
+        <v>3.82</v>
       </c>
       <c r="CC10" t="n">
         <v>2.35</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CE10" t="n">
         <v>1.31</v>
@@ -4852,10 +4852,10 @@
         <v>2.45</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.25</v>
+        <v>3.24</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CI10" t="n">
         <v>2.28</v>
@@ -4864,13 +4864,13 @@
         <v>1.58</v>
       </c>
       <c r="CK10" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CL10" t="n">
         <v>1.7</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.91</v>
+        <v>2.89</v>
       </c>
       <c r="CN10" t="n">
         <v>2.17</v>
@@ -4882,7 +4882,7 @@
         <v>1.66</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4891,7 +4891,7 @@
         <v>2.52</v>
       </c>
       <c r="CT10" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CU10" t="n">
         <v>1.56</v>
@@ -4921,82 +4921,82 @@
         <v>1.68</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.65</v>
+        <v>2.66</v>
       </c>
       <c r="DE10" t="n">
+        <v>0.16</v>
+      </c>
+      <c r="DF10" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="DG10" t="n">
+        <v>3</v>
+      </c>
+      <c r="DH10" t="n">
+        <v>104.42</v>
+      </c>
+      <c r="DI10" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DJ10" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DK10" t="n">
+        <v>5.71</v>
+      </c>
+      <c r="DL10" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="DM10" t="n">
+        <v>50.46</v>
+      </c>
+      <c r="DN10" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="DO10" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="DP10" t="n">
+        <v>13.37</v>
+      </c>
+      <c r="DQ10" t="n">
+        <v>13.71</v>
+      </c>
+      <c r="DR10" t="n">
+        <v>6.17</v>
+      </c>
+      <c r="DS10" t="n">
         <v>0.17</v>
       </c>
-      <c r="DF10" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="DG10" t="n">
-        <v>3.09</v>
-      </c>
-      <c r="DH10" t="n">
-        <v>105.74</v>
-      </c>
-      <c r="DI10" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DJ10" t="n">
-        <v>1.96</v>
-      </c>
-      <c r="DK10" t="n">
-        <v>5.83</v>
-      </c>
-      <c r="DL10" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="DM10" t="n">
-        <v>50.96</v>
-      </c>
-      <c r="DN10" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="DO10" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="DP10" t="n">
-        <v>13.39</v>
-      </c>
-      <c r="DQ10" t="n">
-        <v>13.52</v>
-      </c>
-      <c r="DR10" t="n">
-        <v>6.04</v>
-      </c>
-      <c r="DS10" t="n">
-        <v>0.13</v>
-      </c>
       <c r="DT10" t="n">
-        <v>0.13</v>
+        <v>0.17</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.82</v>
+        <v>55.87</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.78</v>
+        <v>14.42</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.300000000000001</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.48</v>
+        <v>5.29</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.48</v>
+        <v>19.5</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.69</v>
+        <v>1.65</v>
       </c>
       <c r="EC10" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
     </row>
     <row r="11">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C12" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D12" t="n">
         <v>12</v>
@@ -5421,82 +5421,82 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G12" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="H12" t="n">
-        <v>88.81999999999999</v>
+        <v>88.25</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="K12" t="n">
-        <v>5.64</v>
+        <v>5.58</v>
       </c>
       <c r="L12" t="n">
-        <v>0.55</v>
+        <v>0.58</v>
       </c>
       <c r="M12" t="n">
-        <v>42.55</v>
+        <v>42.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="O12" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="P12" t="n">
-        <v>12.55</v>
+        <v>13</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.55</v>
+        <v>14.67</v>
       </c>
       <c r="R12" t="n">
-        <v>7.55</v>
+        <v>7.25</v>
       </c>
       <c r="S12" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="T12" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="U12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V12" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.73</v>
+        <v>52.75</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.73</v>
+        <v>12.5</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.550000000000001</v>
+        <v>8.42</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.18</v>
+        <v>4.08</v>
       </c>
       <c r="AC12" t="n">
-        <v>20.09</v>
+        <v>19.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AF12" t="n">
         <v>0.08</v>
@@ -5580,34 +5580,34 @@
         <v>3.5</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.43</v>
+        <v>10.5</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.57</v>
+        <v>0.54</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.39</v>
+        <v>4.46</v>
       </c>
       <c r="BQ12" t="n">
         <v>6</v>
@@ -5616,28 +5616,28 @@
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT12" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BV12" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX12" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.23</v>
+        <v>2.32</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.29</v>
+        <v>2.37</v>
       </c>
       <c r="CA12" t="n">
         <v>3.58</v>
@@ -5658,10 +5658,10 @@
         <v>2.53</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CI12" t="n">
         <v>2.27</v>
@@ -5685,7 +5685,7 @@
         <v>1.2</v>
       </c>
       <c r="CP12" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CQ12" t="n">
         <v>2.7</v>
@@ -5733,76 +5733,76 @@
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.39</v>
+        <v>85.25</v>
       </c>
       <c r="DI12" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.87</v>
+        <v>2.83</v>
       </c>
       <c r="DK12" t="n">
         <v>4.83</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.35</v>
+        <v>0.38</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.7</v>
+        <v>38.84</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="DO12" t="n">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.09</v>
+        <v>14.25</v>
       </c>
       <c r="DQ12" t="n">
-        <v>13.91</v>
+        <v>14</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.57</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="DS12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT12" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU12" t="n">
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.35</v>
+        <v>51.42</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.13</v>
+        <v>12.04</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.35</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.74</v>
+        <v>19.62</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.32</v>
+        <v>1.3</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.74</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="13">
@@ -5812,94 +5812,94 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D13" t="n">
         <v>11</v>
       </c>
       <c r="E13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="F13" t="n">
-        <v>1.58</v>
+        <v>1.46</v>
       </c>
       <c r="G13" t="n">
-        <v>2.08</v>
+        <v>1.92</v>
       </c>
       <c r="H13" t="n">
-        <v>101.5</v>
+        <v>100</v>
       </c>
       <c r="I13" t="n">
         <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.83</v>
+        <v>2.62</v>
       </c>
       <c r="K13" t="n">
-        <v>5.25</v>
+        <v>5.08</v>
       </c>
       <c r="L13" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M13" t="n">
-        <v>47.92</v>
+        <v>47.85</v>
       </c>
       <c r="N13" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="O13" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="P13" t="n">
-        <v>11.75</v>
+        <v>11.69</v>
       </c>
       <c r="Q13" t="n">
-        <v>13.58</v>
+        <v>14.38</v>
       </c>
       <c r="R13" t="n">
-        <v>8.5</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="S13" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T13" t="n">
-        <v>2.17</v>
+        <v>2.08</v>
       </c>
       <c r="U13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V13" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>48.17</v>
+        <v>48.15</v>
       </c>
       <c r="Y13" t="n">
         <v>0.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>15.42</v>
+        <v>15</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.5</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="AB13" t="n">
-        <v>5.92</v>
+        <v>5.62</v>
       </c>
       <c r="AC13" t="n">
-        <v>23.67</v>
+        <v>23.69</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.74</v>
+        <v>1.69</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="AF13" t="n">
         <v>0.09</v>
@@ -5983,70 +5983,70 @@
         <v>2.64</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.74</v>
+        <v>9.539999999999999</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.13</v>
+        <v>3.12</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.65</v>
+        <v>4.58</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.52</v>
+        <v>4.38</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS13" t="n">
-        <v>78.26000000000001</v>
+        <v>79.17</v>
       </c>
       <c r="BT13" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU13" t="n">
-        <v>52.17</v>
+        <v>50</v>
       </c>
       <c r="BV13" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY13" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="BZ13" t="n">
-        <v>2.47</v>
+        <v>2.55</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.64</v>
+        <v>3.65</v>
       </c>
       <c r="CC13" t="n">
         <v>3.02</v>
@@ -6058,7 +6058,7 @@
         <v>1.31</v>
       </c>
       <c r="CF13" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="CG13" t="n">
         <v>3.17</v>
@@ -6076,13 +6076,13 @@
         <v>1.37</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CN13" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CO13" t="n">
         <v>1.19</v>
@@ -6091,13 +6091,13 @@
         <v>1.68</v>
       </c>
       <c r="CQ13" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CR13" t="n">
         <v>1.37</v>
       </c>
       <c r="CS13" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="CT13" t="n">
         <v>3.25</v>
@@ -6106,7 +6106,7 @@
         <v>1.53</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CW13" t="n">
         <v>1.58</v>
@@ -6115,13 +6115,13 @@
         <v>1.49</v>
       </c>
       <c r="CY13" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CZ13" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DA13" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="DB13" t="n">
         <v>1.21</v>
@@ -6130,82 +6130,82 @@
         <v>1.71</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.57</v>
+        <v>1.5</v>
       </c>
       <c r="DG13" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="DH13" t="n">
-        <v>94.95999999999999</v>
+        <v>94.42</v>
       </c>
       <c r="DI13" t="n">
         <v>0.17</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.83</v>
+        <v>2.71</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.82</v>
+        <v>4.75</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.39</v>
+        <v>0.37</v>
       </c>
       <c r="DM13" t="n">
-        <v>42.18</v>
+        <v>42.38</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.22</v>
+        <v>1.16</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.3</v>
+        <v>12.25</v>
       </c>
       <c r="DQ13" t="n">
-        <v>13.82</v>
+        <v>14.25</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.050000000000001</v>
+        <v>9.09</v>
       </c>
       <c r="DS13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU13" t="n">
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.74</v>
+        <v>46.79</v>
       </c>
       <c r="DW13" t="n">
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.61</v>
+        <v>13.46</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.699999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.92</v>
+        <v>4.8</v>
       </c>
       <c r="EA13" t="n">
-        <v>21.91</v>
+        <v>22</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.7</v>
+        <v>2.59</v>
       </c>
     </row>
     <row r="14">
@@ -7424,13 +7424,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C17" t="n">
         <v>12</v>
       </c>
       <c r="D17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E17" t="n">
         <v>0.08</v>
@@ -7514,139 +7514,139 @@
         <v>1.67</v>
       </c>
       <c r="AF17" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AG17" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AH17" t="n">
-        <v>2.64</v>
+        <v>2.5</v>
       </c>
       <c r="AI17" t="n">
-        <v>98.73</v>
+        <v>100.42</v>
       </c>
       <c r="AJ17" t="n">
-        <v>-0.09</v>
+        <v>-0.08</v>
       </c>
       <c r="AK17" t="n">
-        <v>2.55</v>
+        <v>2.5</v>
       </c>
       <c r="AL17" t="n">
-        <v>4.91</v>
+        <v>4.67</v>
       </c>
       <c r="AM17" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="AN17" t="n">
-        <v>40.91</v>
+        <v>41.25</v>
       </c>
       <c r="AO17" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP17" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AQ17" t="n">
-        <v>12.55</v>
+        <v>13.42</v>
       </c>
       <c r="AR17" t="n">
-        <v>11.36</v>
+        <v>11.33</v>
       </c>
       <c r="AS17" t="n">
-        <v>7.36</v>
+        <v>7.25</v>
       </c>
       <c r="AT17" t="n">
-        <v>0.82</v>
+        <v>0.83</v>
       </c>
       <c r="AU17" t="n">
-        <v>1.27</v>
+        <v>1.33</v>
       </c>
       <c r="AV17" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AW17" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="AX17" t="n">
         <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>52.82</v>
+        <v>52.75</v>
       </c>
       <c r="AZ17" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA17" t="n">
-        <v>13.91</v>
+        <v>14.08</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.09</v>
+        <v>9.17</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.82</v>
+        <v>4.92</v>
       </c>
       <c r="BD17" t="n">
-        <v>20.73</v>
+        <v>20.17</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BF17" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.48</v>
+        <v>10.25</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="BL17" t="n">
         <v>0.96</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.65</v>
+        <v>5.46</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS17" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT17" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU17" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX17" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY17" t="n">
         <v>1.92</v>
@@ -7655,22 +7655,22 @@
         <v>2</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CB17" t="n">
         <v>3.74</v>
       </c>
       <c r="CC17" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CD17" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="CE17" t="n">
         <v>1.31</v>
       </c>
       <c r="CF17" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG17" t="n">
         <v>3.24</v>
@@ -7682,19 +7682,19 @@
         <v>2.26</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="CK17" t="n">
         <v>1.37</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CN17" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="CO17" t="n">
         <v>1.2</v>
@@ -7703,7 +7703,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.65</v>
+        <v>2.64</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
@@ -7718,7 +7718,7 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="CW17" t="n">
         <v>1.61</v>
@@ -7727,13 +7727,13 @@
         <v>1.46</v>
       </c>
       <c r="CY17" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ17" t="n">
-        <v>2.58</v>
+        <v>2.57</v>
       </c>
       <c r="DA17" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB17" t="n">
         <v>1.22</v>
@@ -7745,73 +7745,73 @@
         <v>2.77</v>
       </c>
       <c r="DE17" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.39</v>
+        <v>1.42</v>
       </c>
       <c r="DG17" t="n">
-        <v>3.09</v>
+        <v>3</v>
       </c>
       <c r="DH17" t="n">
-        <v>99.95999999999999</v>
+        <v>100.75</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.57</v>
+        <v>5.42</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.74</v>
+        <v>0.7</v>
       </c>
       <c r="DM17" t="n">
-        <v>50</v>
+        <v>49.79</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.26</v>
+        <v>12.71</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.91</v>
+        <v>10.92</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.26</v>
+        <v>7.21</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.26</v>
+        <v>0.29</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.39</v>
+        <v>54.29</v>
       </c>
       <c r="DW17" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.87</v>
+        <v>15.88</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.26</v>
+        <v>10.25</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.61</v>
+        <v>5.62</v>
       </c>
       <c r="EA17" t="n">
-        <v>21.04</v>
+        <v>20.75</v>
       </c>
       <c r="EB17" t="n">
         <v>1.76</v>
@@ -8230,13 +8230,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C19" t="n">
         <v>11</v>
       </c>
       <c r="D19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E19" t="n">
         <v>0.18</v>
@@ -8320,139 +8320,139 @@
         <v>2.45</v>
       </c>
       <c r="AF19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG19" t="n">
-        <v>1.42</v>
+        <v>1.54</v>
       </c>
       <c r="AH19" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AI19" t="n">
-        <v>106.83</v>
+        <v>108.15</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK19" t="n">
-        <v>2.33</v>
+        <v>2.46</v>
       </c>
       <c r="AL19" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="AM19" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AN19" t="n">
-        <v>45.17</v>
+        <v>46.31</v>
       </c>
       <c r="AO19" t="n">
         <v>0.92</v>
       </c>
       <c r="AP19" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AQ19" t="n">
-        <v>13.67</v>
+        <v>13.38</v>
       </c>
       <c r="AR19" t="n">
-        <v>12.17</v>
+        <v>11.77</v>
       </c>
       <c r="AS19" t="n">
-        <v>6.08</v>
+        <v>6.15</v>
       </c>
       <c r="AT19" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="AU19" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AV19" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AW19" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AX19" t="n">
         <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>42.92</v>
+        <v>44.31</v>
       </c>
       <c r="AZ19" t="n">
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.42</v>
+        <v>12.69</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.17</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="BC19" t="n">
-        <v>4.25</v>
+        <v>4.23</v>
       </c>
       <c r="BD19" t="n">
-        <v>23</v>
+        <v>23.46</v>
       </c>
       <c r="BE19" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="BF19" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="BG19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BH19" t="n">
+        <v>9.5</v>
+      </c>
+      <c r="BI19" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="BJ19" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="BK19" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="BL19" t="n">
+        <v>0.79</v>
+      </c>
+      <c r="BM19" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="BN19" t="n">
         <v>1.42</v>
       </c>
-      <c r="BF19" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="BG19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BH19" t="n">
-        <v>9.52</v>
-      </c>
-      <c r="BI19" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="BJ19" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="BK19" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BL19" t="n">
-        <v>0.83</v>
-      </c>
-      <c r="BM19" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="BN19" t="n">
-        <v>1.43</v>
-      </c>
       <c r="BO19" t="n">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.91</v>
+        <v>3.96</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.57</v>
+        <v>5.5</v>
       </c>
       <c r="BR19" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS19" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BT19" t="n">
-        <v>47.83</v>
+        <v>45.83</v>
       </c>
       <c r="BU19" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BV19" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BW19" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX19" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY19" t="n">
         <v>2.2</v>
@@ -8461,31 +8461,31 @@
         <v>2.24</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.39</v>
+        <v>3.41</v>
       </c>
       <c r="CB19" t="n">
-        <v>3.53</v>
+        <v>3.55</v>
       </c>
       <c r="CC19" t="n">
-        <v>2.67</v>
+        <v>2.59</v>
       </c>
       <c r="CD19" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="CE19" t="n">
         <v>1.36</v>
       </c>
       <c r="CF19" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CG19" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="CH19" t="n">
         <v>1.43</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.14</v>
+        <v>2.13</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.67</v>
@@ -8494,10 +8494,10 @@
         <v>1.43</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="CM19" t="n">
-        <v>2.63</v>
+        <v>2.62</v>
       </c>
       <c r="CN19" t="n">
         <v>2.02</v>
@@ -8512,10 +8512,10 @@
         <v>3.02</v>
       </c>
       <c r="CR19" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CT19" t="n">
         <v>3.19</v>
@@ -8524,106 +8524,106 @@
         <v>1.47</v>
       </c>
       <c r="CV19" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
       <c r="CW19" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CX19" t="n">
         <v>1.5</v>
       </c>
       <c r="CY19" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.49</v>
+        <v>2.48</v>
       </c>
       <c r="DA19" t="n">
-        <v>2.02</v>
+        <v>2.01</v>
       </c>
       <c r="DB19" t="n">
         <v>1.27</v>
       </c>
       <c r="DC19" t="n">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.12</v>
+        <v>3.11</v>
       </c>
       <c r="DE19" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.91</v>
+        <v>2.87</v>
       </c>
       <c r="DH19" t="n">
-        <v>106.35</v>
+        <v>107.08</v>
       </c>
       <c r="DI19" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.05</v>
+        <v>5.04</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="DM19" t="n">
-        <v>48.48</v>
+        <v>48.96</v>
       </c>
       <c r="DN19" t="n">
         <v>0.7</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.74</v>
+        <v>13.58</v>
       </c>
       <c r="DQ19" t="n">
-        <v>12.13</v>
+        <v>11.92</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.87</v>
+        <v>5.92</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.22</v>
+        <v>0.21</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>43.83</v>
+        <v>44.54</v>
       </c>
       <c r="DW19" t="n">
         <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.35</v>
+        <v>13.46</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.57</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.78</v>
+        <v>4.75</v>
       </c>
       <c r="EA19" t="n">
-        <v>22.35</v>
+        <v>22.63</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.39</v>
+        <v>2.46</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C6" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D6" t="n">
         <v>11</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="G6" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="H6" t="n">
+        <v>94.92</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K6" t="n">
+        <v>4.31</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="M6" t="n">
+        <v>37</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1</v>
+      </c>
+      <c r="O6" t="n">
         <v>2.08</v>
       </c>
-      <c r="H6" t="n">
-        <v>92.83</v>
-      </c>
-      <c r="I6" t="n">
-        <v>0</v>
-      </c>
-      <c r="J6" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="K6" t="n">
-        <v>4.08</v>
-      </c>
-      <c r="L6" t="n">
-        <v>0.33</v>
-      </c>
-      <c r="M6" t="n">
-        <v>35.75</v>
-      </c>
-      <c r="N6" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="O6" t="n">
-        <v>2</v>
-      </c>
       <c r="P6" t="n">
-        <v>12</v>
+        <v>11.62</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.58</v>
+        <v>12.54</v>
       </c>
       <c r="R6" t="n">
-        <v>8.58</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="S6" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="T6" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="U6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="V6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>40.33</v>
+        <v>40.69</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.67</v>
+        <v>12.54</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.67</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.42</v>
+        <v>22.92</v>
       </c>
       <c r="AD6" t="n">
         <v>1.34</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="AF6" t="n">
         <v>0.18</v>
@@ -3162,70 +3162,70 @@
         <v>2.45</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.39</v>
+        <v>10.25</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.7</v>
+        <v>0.67</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.39</v>
+        <v>1.46</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.48</v>
+        <v>1.42</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.52</v>
+        <v>4.46</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.87</v>
+        <v>5.79</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS6" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT6" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BU6" t="n">
-        <v>30.43</v>
+        <v>29.17</v>
       </c>
       <c r="BV6" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>60.87</v>
+        <v>62.5</v>
       </c>
       <c r="BY6" t="n">
-        <v>3</v>
+        <v>2.95</v>
       </c>
       <c r="BZ6" t="n">
-        <v>3.1</v>
+        <v>3.07</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.59</v>
+        <v>3.57</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.71</v>
+        <v>3.69</v>
       </c>
       <c r="CC6" t="n">
         <v>4.15</v>
@@ -3234,13 +3234,13 @@
         <v>4.57</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.04</v>
+        <v>3.03</v>
       </c>
       <c r="CH6" t="n">
         <v>1.47</v>
@@ -3261,7 +3261,7 @@
         <v>2.73</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO6" t="n">
         <v>1.21</v>
@@ -3270,16 +3270,16 @@
         <v>1.76</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.8</v>
+        <v>2.81</v>
       </c>
       <c r="CR6" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CT6" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CU6" t="n">
         <v>1.5</v>
@@ -3306,85 +3306,85 @@
         <v>1.24</v>
       </c>
       <c r="DC6" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.91</v>
+        <v>2.93</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DF6" t="n">
         <v>1.83</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="DH6" t="n">
-        <v>98.13</v>
+        <v>99.04000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.83</v>
+        <v>2.79</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.43</v>
+        <v>4.54</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.3</v>
+        <v>0.33</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.17</v>
+        <v>41.62</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.83</v>
+        <v>0.79</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.13</v>
+        <v>2.17</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.39</v>
+        <v>12.17</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.87</v>
+        <v>12.83</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.130000000000001</v>
+        <v>8.08</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.13</v>
+        <v>44.16</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.3</v>
+        <v>0.29</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.66</v>
+        <v>12.59</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.699999999999999</v>
+        <v>8.67</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.96</v>
+        <v>3.92</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.7</v>
+        <v>22</v>
       </c>
       <c r="EB6" t="n">
         <v>1.38</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.35</v>
+        <v>2.33</v>
       </c>
     </row>
     <row r="7">
@@ -5006,10 +5006,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D11" t="n">
         <v>11</v>
@@ -5018,82 +5018,82 @@
         <v>0.08</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5</v>
+        <v>1.38</v>
       </c>
       <c r="G11" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="H11" t="n">
-        <v>96</v>
+        <v>95.31</v>
       </c>
       <c r="I11" t="n">
         <v>-0.08</v>
       </c>
       <c r="J11" t="n">
-        <v>2.42</v>
+        <v>2.23</v>
       </c>
       <c r="K11" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="L11" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="M11" t="n">
-        <v>44.75</v>
+        <v>44.46</v>
       </c>
       <c r="N11" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="O11" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="P11" t="n">
-        <v>12.42</v>
+        <v>12.08</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.25</v>
+        <v>10.46</v>
       </c>
       <c r="R11" t="n">
-        <v>8.92</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="S11" t="n">
         <v>1.08</v>
       </c>
       <c r="T11" t="n">
-        <v>0.92</v>
+        <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V11" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.42</v>
+        <v>49.85</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.08</v>
+        <v>13.15</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.25</v>
+        <v>8.31</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.83</v>
+        <v>4.85</v>
       </c>
       <c r="AC11" t="n">
-        <v>20</v>
+        <v>19.85</v>
       </c>
       <c r="AD11" t="n">
         <v>1.49</v>
       </c>
       <c r="AE11" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AF11" t="n">
         <v>0.09</v>
@@ -5177,70 +5177,70 @@
         <v>2.73</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.26</v>
+        <v>10.21</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.61</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.57</v>
+        <v>0.58</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.91</v>
+        <v>0.88</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.78</v>
+        <v>4.71</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.91</v>
+        <v>4.96</v>
       </c>
       <c r="BR11" t="n">
-        <v>86.95999999999999</v>
+        <v>87.5</v>
       </c>
       <c r="BS11" t="n">
-        <v>69.56999999999999</v>
+        <v>70.83</v>
       </c>
       <c r="BT11" t="n">
-        <v>47.83</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV11" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.699999999999999</v>
+        <v>8.33</v>
       </c>
       <c r="BX11" t="n">
-        <v>39.13</v>
+        <v>41.67</v>
       </c>
       <c r="BY11" t="n">
         <v>1.91</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.37</v>
+        <v>3.38</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CC11" t="n">
         <v>2.71</v>
@@ -5249,19 +5249,19 @@
         <v>3.02</v>
       </c>
       <c r="CE11" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="CF11" t="n">
         <v>2.31</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.08</v>
+        <v>3.09</v>
       </c>
       <c r="CH11" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.22</v>
+        <v>2.23</v>
       </c>
       <c r="CJ11" t="n">
         <v>1.49</v>
@@ -5273,13 +5273,13 @@
         <v>1.64</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN11" t="n">
         <v>2.07</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="CP11" t="n">
         <v>1.59</v>
@@ -5306,16 +5306,16 @@
         <v>1.6</v>
       </c>
       <c r="CX11" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CY11" t="n">
         <v>1.69</v>
       </c>
       <c r="CZ11" t="n">
-        <v>2.54</v>
+        <v>2.55</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.15</v>
+        <v>2.14</v>
       </c>
       <c r="DB11" t="n">
         <v>1.21</v>
@@ -5330,76 +5330,76 @@
         <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.74</v>
+        <v>1.66</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.31</v>
+        <v>2.29</v>
       </c>
       <c r="DH11" t="n">
-        <v>94.44</v>
+        <v>94.13</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.69</v>
+        <v>4.62</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.35</v>
+        <v>45.17</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.74</v>
+        <v>0.71</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.13</v>
+        <v>2.09</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.91</v>
+        <v>12.71</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.3</v>
+        <v>11.37</v>
       </c>
       <c r="DR11" t="n">
-        <v>9</v>
+        <v>8.75</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.53</v>
+        <v>48.8</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.39</v>
+        <v>12.46</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.92</v>
+        <v>7.96</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.61</v>
+        <v>20.5</v>
       </c>
       <c r="EB11" t="n">
         <v>1.43</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.35</v>
+        <v>2.25</v>
       </c>
     </row>
     <row r="12">
@@ -5824,7 +5824,7 @@
         <v>0.31</v>
       </c>
       <c r="F13" t="n">
-        <v>1.46</v>
+        <v>1.54</v>
       </c>
       <c r="G13" t="n">
         <v>1.92</v>
@@ -5836,7 +5836,7 @@
         <v>0.08</v>
       </c>
       <c r="J13" t="n">
-        <v>2.62</v>
+        <v>2.69</v>
       </c>
       <c r="K13" t="n">
         <v>5.08</v>
@@ -5884,10 +5884,10 @@
         <v>0.08</v>
       </c>
       <c r="Z13" t="n">
-        <v>15</v>
+        <v>15.08</v>
       </c>
       <c r="AA13" t="n">
-        <v>9.380000000000001</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="AB13" t="n">
         <v>5.62</v>
@@ -5899,7 +5899,7 @@
         <v>1.69</v>
       </c>
       <c r="AE13" t="n">
-        <v>2.54</v>
+        <v>2.62</v>
       </c>
       <c r="AF13" t="n">
         <v>0.09</v>
@@ -6136,7 +6136,7 @@
         <v>0.21</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="DG13" t="n">
         <v>2</v>
@@ -6148,7 +6148,7 @@
         <v>0.17</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.71</v>
+        <v>2.75</v>
       </c>
       <c r="DK13" t="n">
         <v>4.75</v>
@@ -6190,10 +6190,10 @@
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.46</v>
+        <v>13.5</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.67</v>
+        <v>8.710000000000001</v>
       </c>
       <c r="DZ13" t="n">
         <v>4.8</v>
@@ -6205,7 +6205,7 @@
         <v>1.5</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.59</v>
+        <v>2.63</v>
       </c>
     </row>
     <row r="14">
@@ -6215,13 +6215,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C14" t="n">
         <v>11</v>
       </c>
       <c r="D14" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E14" t="n">
         <v>0.27</v>
@@ -6308,136 +6308,136 @@
         <v>0.08</v>
       </c>
       <c r="AG14" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AH14" t="n">
-        <v>3.17</v>
+        <v>2.92</v>
       </c>
       <c r="AI14" t="n">
-        <v>91.25</v>
+        <v>90.31</v>
       </c>
       <c r="AJ14" t="n">
         <v>0</v>
       </c>
       <c r="AK14" t="n">
-        <v>2.25</v>
+        <v>2.38</v>
       </c>
       <c r="AL14" t="n">
-        <v>5.5</v>
+        <v>5.23</v>
       </c>
       <c r="AM14" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="AN14" t="n">
-        <v>42.17</v>
+        <v>40.69</v>
       </c>
       <c r="AO14" t="n">
         <v>0.92</v>
       </c>
       <c r="AP14" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AQ14" t="n">
-        <v>11.58</v>
+        <v>11.69</v>
       </c>
       <c r="AR14" t="n">
-        <v>9.25</v>
+        <v>9.23</v>
       </c>
       <c r="AS14" t="n">
+        <v>9.460000000000001</v>
+      </c>
+      <c r="AT14" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>48.62</v>
+      </c>
+      <c r="AZ14" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA14" t="n">
+        <v>12.08</v>
+      </c>
+      <c r="BB14" t="n">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="BC14" t="n">
+        <v>3.54</v>
+      </c>
+      <c r="BD14" t="n">
+        <v>18.69</v>
+      </c>
+      <c r="BE14" t="n">
+        <v>1.31</v>
+      </c>
+      <c r="BF14" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BG14" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BH14" t="n">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="BI14" t="n">
+        <v>3.38</v>
+      </c>
+      <c r="BJ14" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="BK14" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="BL14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BM14" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BN14" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="BO14" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="BP14" t="n">
+        <v>4.42</v>
+      </c>
+      <c r="BQ14" t="n">
+        <v>4.92</v>
+      </c>
+      <c r="BR14" t="n">
+        <v>91.67</v>
+      </c>
+      <c r="BS14" t="n">
+        <v>83.33</v>
+      </c>
+      <c r="BT14" t="n">
+        <v>70.83</v>
+      </c>
+      <c r="BU14" t="n">
+        <v>54.17</v>
+      </c>
+      <c r="BV14" t="n">
+        <v>29.17</v>
+      </c>
+      <c r="BW14" t="n">
         <v>8.33</v>
       </c>
-      <c r="AT14" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="AU14" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="AV14" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AW14" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="AX14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY14" t="n">
-        <v>49.58</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA14" t="n">
-        <v>12.42</v>
-      </c>
-      <c r="BB14" t="n">
-        <v>9.17</v>
-      </c>
-      <c r="BC14" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="BD14" t="n">
-        <v>19.25</v>
-      </c>
-      <c r="BE14" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="BF14" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="BG14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BH14" t="n">
-        <v>10.04</v>
-      </c>
-      <c r="BI14" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="BJ14" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="BK14" t="n">
-        <v>0.48</v>
-      </c>
-      <c r="BL14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BM14" t="n">
-        <v>0.91</v>
-      </c>
-      <c r="BN14" t="n">
-        <v>2.13</v>
-      </c>
-      <c r="BO14" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="BP14" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="BQ14" t="n">
-        <v>4.96</v>
-      </c>
-      <c r="BR14" t="n">
-        <v>91.3</v>
-      </c>
-      <c r="BS14" t="n">
-        <v>82.61</v>
-      </c>
-      <c r="BT14" t="n">
-        <v>69.56999999999999</v>
-      </c>
-      <c r="BU14" t="n">
-        <v>52.17</v>
-      </c>
-      <c r="BV14" t="n">
-        <v>30.43</v>
-      </c>
-      <c r="BW14" t="n">
-        <v>8.699999999999999</v>
-      </c>
       <c r="BX14" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BY14" t="n">
         <v>2.57</v>
@@ -6446,31 +6446,31 @@
         <v>2.82</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.71</v>
+        <v>3.74</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.87</v>
+        <v>3.89</v>
       </c>
       <c r="CC14" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="CD14" t="n">
-        <v>4.08</v>
+        <v>4.12</v>
       </c>
       <c r="CE14" t="n">
         <v>1.29</v>
       </c>
       <c r="CF14" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="CG14" t="n">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="CH14" t="n">
         <v>1.55</v>
       </c>
       <c r="CI14" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="CJ14" t="n">
         <v>1.54</v>
@@ -6479,7 +6479,7 @@
         <v>1.36</v>
       </c>
       <c r="CL14" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CM14" t="n">
         <v>2.85</v>
@@ -6488,19 +6488,19 @@
         <v>2.17</v>
       </c>
       <c r="CO14" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ14" t="n">
-        <v>2.47</v>
+        <v>2.45</v>
       </c>
       <c r="CR14" t="n">
         <v>1.35</v>
       </c>
       <c r="CS14" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CT14" t="n">
         <v>3.3</v>
@@ -6509,10 +6509,10 @@
         <v>1.58</v>
       </c>
       <c r="CV14" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="CW14" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="CX14" t="n">
         <v>1.46</v>
@@ -6524,43 +6524,43 @@
         <v>2.6</v>
       </c>
       <c r="DA14" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DB14" t="n">
         <v>1.2</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="DE14" t="n">
         <v>0.17</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.74</v>
+        <v>1.79</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.57</v>
+        <v>2.46</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.7</v>
+        <v>84.45999999999999</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.95</v>
+        <v>4.83</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.43</v>
+        <v>0.46</v>
       </c>
       <c r="DM14" t="n">
-        <v>42</v>
+        <v>41.21</v>
       </c>
       <c r="DN14" t="n">
         <v>1.04</v>
@@ -6572,43 +6572,43 @@
         <v>13.17</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.96</v>
+        <v>10.88</v>
       </c>
       <c r="DR14" t="n">
-        <v>8.609999999999999</v>
+        <v>9.210000000000001</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.65</v>
+        <v>47.21</v>
       </c>
       <c r="DW14" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.96</v>
+        <v>11.79</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.92</v>
+        <v>7.63</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.04</v>
+        <v>4.17</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.96</v>
+        <v>17.71</v>
       </c>
       <c r="EB14" t="n">
         <v>1.34</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
     </row>
     <row r="15">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C15" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D15" t="n">
         <v>12</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="H15" t="n">
+        <v>108.75</v>
+      </c>
+      <c r="I15" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="K15" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="L15" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="M15" t="n">
+        <v>55.83</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="O15" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="P15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>11.83</v>
+      </c>
+      <c r="R15" t="n">
+        <v>5.92</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="V15" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="W15" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" t="n">
+        <v>57.42</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>16.83</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>11.75</v>
+      </c>
+      <c r="AB15" t="n">
+        <v>5.08</v>
+      </c>
+      <c r="AC15" t="n">
+        <v>19.5</v>
+      </c>
+      <c r="AD15" t="n">
         <v>1.82</v>
       </c>
-      <c r="G15" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="H15" t="n">
-        <v>107.36</v>
-      </c>
-      <c r="I15" t="n">
-        <v>0</v>
-      </c>
-      <c r="J15" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="K15" t="n">
-        <v>5.55</v>
-      </c>
-      <c r="L15" t="n">
-        <v>0.36</v>
-      </c>
-      <c r="M15" t="n">
-        <v>55.82</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="O15" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="P15" t="n">
-        <v>12.36</v>
-      </c>
-      <c r="Q15" t="n">
-        <v>11.82</v>
-      </c>
-      <c r="R15" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="S15" t="n">
-        <v>2</v>
-      </c>
-      <c r="T15" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="U15" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="V15" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="W15" t="n">
-        <v>0</v>
-      </c>
-      <c r="X15" t="n">
-        <v>56.91</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>16.27</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>11.55</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>4.73</v>
-      </c>
-      <c r="AC15" t="n">
-        <v>19.27</v>
-      </c>
-      <c r="AD15" t="n">
-        <v>1.76</v>
-      </c>
       <c r="AE15" t="n">
-        <v>2.36</v>
+        <v>2.33</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,70 +6789,70 @@
         <v>2.83</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.17</v>
+        <v>10.08</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.39</v>
+        <v>3.42</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BL15" t="n">
         <v>0.96</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.91</v>
+        <v>0.96</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.61</v>
+        <v>4.58</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.96</v>
+        <v>4.92</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS15" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT15" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU15" t="n">
-        <v>30.43</v>
+        <v>33.33</v>
       </c>
       <c r="BV15" t="n">
-        <v>21.74</v>
+        <v>20.83</v>
       </c>
       <c r="BW15" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BX15" t="n">
-        <v>43.48</v>
+        <v>45.83</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.17</v>
+        <v>2.12</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.33</v>
+        <v>2.27</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.64</v>
+        <v>3.68</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.81</v>
+        <v>3.83</v>
       </c>
       <c r="CC15" t="n">
         <v>2.9</v>
@@ -6864,25 +6864,25 @@
         <v>1.27</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.37</v>
+        <v>3.4</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="CJ15" t="n">
-        <v>1.5</v>
+        <v>1.49</v>
       </c>
       <c r="CK15" t="n">
         <v>1.37</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM15" t="n">
         <v>2.84</v>
@@ -6891,19 +6891,19 @@
         <v>2.17</v>
       </c>
       <c r="CO15" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
       </c>
       <c r="CS15" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CT15" t="n">
         <v>3.38</v>
@@ -6921,97 +6921,97 @@
         <v>1.46</v>
       </c>
       <c r="CY15" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CZ15" t="n">
         <v>2.55</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.18</v>
+        <v>2.19</v>
       </c>
       <c r="DB15" t="n">
         <v>1.18</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.69</v>
+        <v>2.75</v>
       </c>
       <c r="DH15" t="n">
-        <v>93.7</v>
+        <v>94.95999999999999</v>
       </c>
       <c r="DI15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.3</v>
+        <v>5.33</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.47</v>
+        <v>0.45</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.35</v>
+        <v>46.75</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.87</v>
+        <v>0.83</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DP15" t="n">
-        <v>12.08</v>
+        <v>11.92</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.74</v>
+        <v>12.7</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.52</v>
+        <v>7.25</v>
       </c>
       <c r="DS15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT15" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU15" t="n">
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.17</v>
+        <v>55.5</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.61</v>
+        <v>16.88</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.22</v>
+        <v>11.34</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.39</v>
+        <v>5.54</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.83</v>
+        <v>18.96</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="16">
@@ -7021,13 +7021,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C16" t="n">
         <v>12</v>
       </c>
       <c r="D16" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -7111,139 +7111,139 @@
         <v>2.58</v>
       </c>
       <c r="AF16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG16" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="AH16" t="n">
-        <v>3.18</v>
+        <v>3.25</v>
       </c>
       <c r="AI16" t="n">
-        <v>93.64</v>
+        <v>94.42</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK16" t="n">
-        <v>2.91</v>
+        <v>2.83</v>
       </c>
       <c r="AL16" t="n">
-        <v>5.64</v>
+        <v>5.67</v>
       </c>
       <c r="AM16" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="AN16" t="n">
-        <v>48.64</v>
+        <v>48.42</v>
       </c>
       <c r="AO16" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP16" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="AQ16" t="n">
-        <v>12.82</v>
+        <v>12.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>13.73</v>
+        <v>13.5</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.91</v>
+        <v>8.17</v>
       </c>
       <c r="AT16" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AU16" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX16" t="n">
         <v>0</v>
       </c>
       <c r="AY16" t="n">
-        <v>49.36</v>
+        <v>49</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="BA16" t="n">
-        <v>11.73</v>
+        <v>11.17</v>
       </c>
       <c r="BB16" t="n">
-        <v>7.36</v>
+        <v>7.08</v>
       </c>
       <c r="BC16" t="n">
-        <v>4.36</v>
+        <v>4.08</v>
       </c>
       <c r="BD16" t="n">
-        <v>22.36</v>
+        <v>22.83</v>
       </c>
       <c r="BE16" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="BF16" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.779999999999999</v>
+        <v>9.75</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.39</v>
+        <v>0.42</v>
       </c>
       <c r="BL16" t="n">
         <v>1.04</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.65</v>
+        <v>0.62</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="BO16" t="n">
-        <v>1</v>
+        <v>1.04</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.3</v>
+        <v>4.25</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.48</v>
+        <v>5.5</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.65000000000001</v>
+        <v>95.83</v>
       </c>
       <c r="BS16" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT16" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU16" t="n">
-        <v>17.39</v>
+        <v>16.67</v>
       </c>
       <c r="BV16" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.35</v>
+        <v>4.17</v>
       </c>
       <c r="BX16" t="n">
-        <v>65.22</v>
+        <v>66.67</v>
       </c>
       <c r="BY16" t="n">
         <v>2.37</v>
@@ -7252,22 +7252,22 @@
         <v>2.43</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="CB16" t="n">
         <v>3.7</v>
       </c>
       <c r="CC16" t="n">
-        <v>3.21</v>
+        <v>3.23</v>
       </c>
       <c r="CD16" t="n">
-        <v>3.38</v>
+        <v>3.36</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CG16" t="n">
         <v>3.21</v>
@@ -7276,7 +7276,7 @@
         <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.26</v>
+        <v>2.27</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.59</v>
@@ -7300,7 +7300,7 @@
         <v>1.71</v>
       </c>
       <c r="CQ16" t="n">
-        <v>2.67</v>
+        <v>2.66</v>
       </c>
       <c r="CR16" t="n">
         <v>1.36</v>
@@ -7324,13 +7324,13 @@
         <v>1.45</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CZ16" t="n">
         <v>2.62</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DB16" t="n">
         <v>1.22</v>
@@ -7339,82 +7339,82 @@
         <v>1.72</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="DG16" t="n">
-        <v>3</v>
+        <v>3.04</v>
       </c>
       <c r="DH16" t="n">
-        <v>94.56999999999999</v>
+        <v>94.92</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.35</v>
+        <v>5.38</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.43</v>
+        <v>0.42</v>
       </c>
       <c r="DM16" t="n">
-        <v>46.39</v>
+        <v>46.38</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.78</v>
+        <v>0.75</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.35</v>
+        <v>2.34</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.78</v>
+        <v>11.66</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.83</v>
+        <v>13.71</v>
       </c>
       <c r="DR16" t="n">
-        <v>7.92</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DT16" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DU16" t="n">
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.82</v>
+        <v>49.62</v>
       </c>
       <c r="DW16" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.87</v>
+        <v>12.54</v>
       </c>
       <c r="DY16" t="n">
-        <v>8</v>
+        <v>7.83</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.87</v>
+        <v>4.7</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.61</v>
+        <v>20.92</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="17">
@@ -7580,16 +7580,16 @@
         <v>14.08</v>
       </c>
       <c r="BB17" t="n">
-        <v>9.17</v>
+        <v>9.25</v>
       </c>
       <c r="BC17" t="n">
-        <v>4.92</v>
+        <v>4.83</v>
       </c>
       <c r="BD17" t="n">
         <v>20.17</v>
       </c>
       <c r="BE17" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="BF17" t="n">
         <v>2.42</v>
@@ -7805,10 +7805,10 @@
         <v>15.88</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.25</v>
+        <v>10.29</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.62</v>
+        <v>5.58</v>
       </c>
       <c r="EA17" t="n">
         <v>20.75</v>
@@ -7827,13 +7827,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C18" t="n">
         <v>12</v>
       </c>
       <c r="D18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
@@ -7917,52 +7917,52 @@
         <v>2.33</v>
       </c>
       <c r="AF18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG18" t="n">
-        <v>2.18</v>
+        <v>2.08</v>
       </c>
       <c r="AH18" t="n">
-        <v>2.27</v>
+        <v>2.08</v>
       </c>
       <c r="AI18" t="n">
-        <v>84.73</v>
+        <v>86</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AK18" t="n">
-        <v>4</v>
+        <v>3.92</v>
       </c>
       <c r="AL18" t="n">
-        <v>3.73</v>
+        <v>3.42</v>
       </c>
       <c r="AM18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AN18" t="n">
-        <v>32.18</v>
+        <v>31.5</v>
       </c>
       <c r="AO18" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="AP18" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AQ18" t="n">
-        <v>12.64</v>
+        <v>12.58</v>
       </c>
       <c r="AR18" t="n">
-        <v>13.27</v>
+        <v>12.83</v>
       </c>
       <c r="AS18" t="n">
-        <v>9</v>
+        <v>9.08</v>
       </c>
       <c r="AT18" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="AU18" t="n">
-        <v>0.91</v>
+        <v>1</v>
       </c>
       <c r="AV18" t="n">
         <v>0</v>
@@ -7974,82 +7974,82 @@
         <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>56.91</v>
+        <v>56.75</v>
       </c>
       <c r="AZ18" t="n">
-        <v>0.18</v>
+        <v>0.25</v>
       </c>
       <c r="BA18" t="n">
-        <v>11.09</v>
+        <v>10.83</v>
       </c>
       <c r="BB18" t="n">
-        <v>7.55</v>
+        <v>7.33</v>
       </c>
       <c r="BC18" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="BD18" t="n">
-        <v>21.09</v>
+        <v>21.17</v>
       </c>
       <c r="BE18" t="n">
-        <v>1.19</v>
+        <v>1.16</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.64</v>
+        <v>3.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.83</v>
+        <v>9.710000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.61</v>
+        <v>0.58</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BL18" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.65</v>
+        <v>0.71</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="BO18" t="n">
-        <v>1.13</v>
+        <v>1.08</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.65</v>
+        <v>4.58</v>
       </c>
       <c r="BQ18" t="n">
-        <v>5.17</v>
+        <v>5.12</v>
       </c>
       <c r="BR18" t="n">
-        <v>91.3</v>
+        <v>91.67</v>
       </c>
       <c r="BS18" t="n">
-        <v>82.61</v>
+        <v>83.33</v>
       </c>
       <c r="BT18" t="n">
-        <v>56.52</v>
+        <v>58.33</v>
       </c>
       <c r="BU18" t="n">
-        <v>26.09</v>
+        <v>25</v>
       </c>
       <c r="BV18" t="n">
-        <v>13.04</v>
+        <v>12.5</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>73.91</v>
+        <v>75</v>
       </c>
       <c r="BY18" t="n">
         <v>2.66</v>
@@ -8058,28 +8058,28 @@
         <v>2.83</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.5</v>
+        <v>3.49</v>
       </c>
       <c r="CB18" t="n">
         <v>3.58</v>
       </c>
       <c r="CC18" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="CD18" t="n">
-        <v>3.9</v>
+        <v>3.81</v>
       </c>
       <c r="CE18" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="CF18" t="n">
-        <v>2.55</v>
+        <v>2.56</v>
       </c>
       <c r="CG18" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="CH18" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="CI18" t="n">
         <v>2.18</v>
@@ -8094,31 +8094,31 @@
         <v>1.86</v>
       </c>
       <c r="CM18" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CN18" t="n">
         <v>2.01</v>
       </c>
       <c r="CO18" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="CP18" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CU18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="CV18" t="n">
         <v>2.26</v>
@@ -8145,82 +8145,82 @@
         <v>1.84</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.03</v>
+        <v>3.05</v>
       </c>
       <c r="DE18" t="n">
         <v>0.04</v>
       </c>
       <c r="DF18" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DG18" t="n">
         <v>1.96</v>
       </c>
-      <c r="DG18" t="n">
+      <c r="DH18" t="n">
+        <v>88.66</v>
+      </c>
+      <c r="DI18" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="DJ18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="DK18" t="n">
+        <v>4</v>
+      </c>
+      <c r="DL18" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="DM18" t="n">
+        <v>35.71</v>
+      </c>
+      <c r="DN18" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="DO18" t="n">
         <v>2.04</v>
       </c>
-      <c r="DH18" t="n">
-        <v>88.17</v>
-      </c>
-      <c r="DI18" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="DJ18" t="n">
-        <v>3.31</v>
-      </c>
-      <c r="DK18" t="n">
-        <v>4.17</v>
-      </c>
-      <c r="DL18" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="DM18" t="n">
-        <v>36.22</v>
-      </c>
-      <c r="DN18" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="DO18" t="n">
-        <v>2.13</v>
-      </c>
       <c r="DP18" t="n">
-        <v>13.87</v>
+        <v>13.79</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.69</v>
+        <v>13.46</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.78</v>
+        <v>7.88</v>
       </c>
       <c r="DS18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DT18" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="DU18" t="n">
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>56.04</v>
+        <v>56</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.17</v>
+        <v>0.21</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.44</v>
+        <v>12.25</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.18</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.26</v>
+        <v>4.21</v>
       </c>
       <c r="EA18" t="n">
-        <v>21.13</v>
+        <v>21.17</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
     </row>
     <row r="19">
@@ -8383,10 +8383,10 @@
         <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>12.69</v>
+        <v>12.62</v>
       </c>
       <c r="BB19" t="n">
-        <v>8.460000000000001</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="BC19" t="n">
         <v>4.23</v>
@@ -8395,7 +8395,7 @@
         <v>23.46</v>
       </c>
       <c r="BE19" t="n">
-        <v>1.44</v>
+        <v>1.43</v>
       </c>
       <c r="BF19" t="n">
         <v>2.46</v>
@@ -8608,10 +8608,10 @@
         <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.46</v>
+        <v>13.42</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.710000000000001</v>
+        <v>8.66</v>
       </c>
       <c r="DZ19" t="n">
         <v>4.75</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,13 +1379,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C2" t="n">
         <v>12</v>
       </c>
       <c r="D2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E2" t="n">
         <v>0.17</v>
@@ -1472,136 +1472,136 @@
         <v>0</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="AH2" t="n">
-        <v>3.83</v>
+        <v>3.62</v>
       </c>
       <c r="AI2" t="n">
-        <v>102.67</v>
+        <v>102.46</v>
       </c>
       <c r="AJ2" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK2" t="n">
-        <v>2.42</v>
+        <v>2.38</v>
       </c>
       <c r="AL2" t="n">
-        <v>6.08</v>
+        <v>5.77</v>
       </c>
       <c r="AM2" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AN2" t="n">
         <v>52</v>
       </c>
       <c r="AO2" t="n">
-        <v>0.67</v>
+        <v>0.62</v>
       </c>
       <c r="AP2" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="AQ2" t="n">
-        <v>14</v>
+        <v>13.69</v>
       </c>
       <c r="AR2" t="n">
-        <v>13.83</v>
+        <v>13.31</v>
       </c>
       <c r="AS2" t="n">
-        <v>6.83</v>
+        <v>6.85</v>
       </c>
       <c r="AT2" t="n">
-        <v>1.5</v>
+        <v>1.46</v>
       </c>
       <c r="AU2" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AV2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AW2" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AX2" t="n">
         <v>0</v>
       </c>
       <c r="AY2" t="n">
-        <v>49.17</v>
+        <v>49.62</v>
       </c>
       <c r="AZ2" t="n">
         <v>0.08</v>
       </c>
       <c r="BA2" t="n">
-        <v>13.25</v>
+        <v>13.15</v>
       </c>
       <c r="BB2" t="n">
-        <v>9.42</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="BC2" t="n">
-        <v>3.83</v>
+        <v>3.77</v>
       </c>
       <c r="BD2" t="n">
-        <v>24.75</v>
+        <v>24.92</v>
       </c>
       <c r="BE2" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="BF2" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.58</v>
+        <v>10.6</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.62</v>
+        <v>1.56</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.38</v>
+        <v>6.32</v>
       </c>
       <c r="BR2" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS2" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BT2" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BU2" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BV2" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW2" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX2" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BY2" t="n">
         <v>2.16</v>
@@ -1616,64 +1616,64 @@
         <v>3.67</v>
       </c>
       <c r="CC2" t="n">
-        <v>3.06</v>
+        <v>3.13</v>
       </c>
       <c r="CD2" t="n">
-        <v>3.24</v>
+        <v>3.3</v>
       </c>
       <c r="CE2" t="n">
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG2" t="n">
-        <v>3.21</v>
+        <v>3.2</v>
       </c>
       <c r="CH2" t="n">
         <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ2" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CK2" t="n">
         <v>1.36</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.8</v>
+        <v>2.79</v>
       </c>
       <c r="CN2" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO2" t="n">
         <v>1.19</v>
       </c>
       <c r="CP2" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CQ2" t="n">
-        <v>2.63</v>
+        <v>2.65</v>
       </c>
       <c r="CR2" t="n">
         <v>1.38</v>
       </c>
       <c r="CS2" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.19</v>
+        <v>3.18</v>
       </c>
       <c r="CU2" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV2" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CW2" t="n">
         <v>1.6</v>
@@ -1685,10 +1685,10 @@
         <v>1.66</v>
       </c>
       <c r="CZ2" t="n">
-        <v>2.59</v>
+        <v>2.58</v>
       </c>
       <c r="DA2" t="n">
-        <v>2.19</v>
+        <v>2.18</v>
       </c>
       <c r="DB2" t="n">
         <v>1.22</v>
@@ -1697,79 +1697,79 @@
         <v>1.72</v>
       </c>
       <c r="DD2" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="DE2" t="n">
         <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.96</v>
+        <v>3.84</v>
       </c>
       <c r="DH2" t="n">
-        <v>103.17</v>
+        <v>103.04</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.42</v>
+        <v>6.24</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.08</v>
+        <v>51.12</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.75</v>
+        <v>13.6</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.79</v>
+        <v>13.52</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.25</v>
+        <v>7.24</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.75</v>
+        <v>51.88</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.29</v>
+        <v>14.2</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.960000000000001</v>
+        <v>9.92</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.33</v>
+        <v>4.28</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.75</v>
+        <v>23.88</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="EC2" t="n">
         <v>2.08</v>
@@ -2185,61 +2185,61 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D4" t="n">
         <v>12</v>
       </c>
       <c r="E4" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="F4" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="G4" t="n">
-        <v>2.58</v>
+        <v>2.38</v>
       </c>
       <c r="H4" t="n">
-        <v>87.58</v>
+        <v>89.77</v>
       </c>
       <c r="I4" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J4" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="K4" t="n">
-        <v>5.25</v>
+        <v>4.92</v>
       </c>
       <c r="L4" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="M4" t="n">
-        <v>46.92</v>
+        <v>47.23</v>
       </c>
       <c r="N4" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="O4" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="P4" t="n">
-        <v>10.92</v>
+        <v>11.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.25</v>
+        <v>12.31</v>
       </c>
       <c r="R4" t="n">
-        <v>8.25</v>
+        <v>8.15</v>
       </c>
       <c r="S4" t="n">
-        <v>0.75</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="T4" t="n">
-        <v>2.17</v>
+        <v>2.15</v>
       </c>
       <c r="U4" t="n">
         <v>0.08</v>
@@ -2251,7 +2251,7 @@
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>49.17</v>
+        <v>50.54</v>
       </c>
       <c r="Y4" t="n">
         <v>0.08</v>
@@ -2260,19 +2260,19 @@
         <v>15</v>
       </c>
       <c r="AA4" t="n">
-        <v>8.75</v>
+        <v>9</v>
       </c>
       <c r="AB4" t="n">
-        <v>6.25</v>
+        <v>6</v>
       </c>
       <c r="AC4" t="n">
-        <v>16.75</v>
+        <v>17.31</v>
       </c>
       <c r="AD4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="AE4" t="n">
-        <v>2</v>
+        <v>2.15</v>
       </c>
       <c r="AF4" t="n">
         <v>0.25</v>
@@ -2356,58 +2356,58 @@
         <v>1.42</v>
       </c>
       <c r="BG4" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.62</v>
+        <v>10.44</v>
       </c>
       <c r="BI4" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BP4" t="n">
         <v>5.04</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.58</v>
+        <v>5.4</v>
       </c>
       <c r="BR4" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS4" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BT4" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BU4" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BV4" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW4" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX4" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BY4" t="n">
         <v>1.86</v>
@@ -2416,10 +2416,10 @@
         <v>1.9</v>
       </c>
       <c r="CA4" t="n">
-        <v>3.66</v>
+        <v>3.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="CC4" t="n">
         <v>2.84</v>
@@ -2434,28 +2434,28 @@
         <v>2.41</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.2</v>
+        <v>3.19</v>
       </c>
       <c r="CH4" t="n">
         <v>1.52</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.57</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="CL4" t="n">
         <v>1.77</v>
       </c>
       <c r="CM4" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN4" t="n">
-        <v>2.07</v>
+        <v>2.08</v>
       </c>
       <c r="CO4" t="n">
         <v>1.18</v>
@@ -2494,58 +2494,58 @@
         <v>2.58</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.11</v>
+        <v>2.12</v>
       </c>
       <c r="DB4" t="n">
         <v>1.22</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="DD4" t="n">
         <v>2.73</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="DH4" t="n">
-        <v>88.5</v>
+        <v>89.59999999999999</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="DK4" t="n">
-        <v>5.12</v>
+        <v>4.96</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.12</v>
+        <v>42.48</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.54</v>
+        <v>0.64</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.34</v>
+        <v>11.4</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.88</v>
+        <v>11.92</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.210000000000001</v>
+        <v>8.16</v>
       </c>
       <c r="DS4" t="n">
         <v>0.08</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50</v>
+        <v>50.68</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.92</v>
+        <v>13.96</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.5</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.42</v>
+        <v>5.32</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.21</v>
+        <v>17.48</v>
       </c>
       <c r="EB4" t="n">
         <v>1.56</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
     </row>
     <row r="5">
@@ -2991,13 +2991,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C6" t="n">
         <v>13</v>
       </c>
       <c r="D6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
@@ -3081,52 +3081,52 @@
         <v>2.23</v>
       </c>
       <c r="AF6" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AG6" t="n">
-        <v>2.27</v>
+        <v>2.33</v>
       </c>
       <c r="AH6" t="n">
-        <v>2.55</v>
+        <v>2.58</v>
       </c>
       <c r="AI6" t="n">
-        <v>103.91</v>
+        <v>100.08</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>3.08</v>
       </c>
       <c r="AL6" t="n">
-        <v>4.82</v>
+        <v>4.83</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AN6" t="n">
-        <v>47.09</v>
+        <v>45.33</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.55</v>
+        <v>0.5</v>
       </c>
       <c r="AP6" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="AQ6" t="n">
-        <v>12.82</v>
+        <v>13.25</v>
       </c>
       <c r="AR6" t="n">
-        <v>13.18</v>
+        <v>12.83</v>
       </c>
       <c r="AS6" t="n">
-        <v>7.64</v>
+        <v>7.75</v>
       </c>
       <c r="AT6" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="AU6" t="n">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="AV6" t="n">
         <v>0</v>
@@ -3138,82 +3138,82 @@
         <v>0</v>
       </c>
       <c r="AY6" t="n">
-        <v>48.27</v>
+        <v>46.92</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.36</v>
+        <v>0.42</v>
       </c>
       <c r="BA6" t="n">
-        <v>12.64</v>
+        <v>12.08</v>
       </c>
       <c r="BB6" t="n">
-        <v>8.73</v>
+        <v>8.25</v>
       </c>
       <c r="BC6" t="n">
-        <v>3.91</v>
+        <v>3.83</v>
       </c>
       <c r="BD6" t="n">
-        <v>20.91</v>
+        <v>20</v>
       </c>
       <c r="BE6" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BF6" t="n">
-        <v>2.45</v>
+        <v>2.42</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.25</v>
+        <v>10.4</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.46</v>
+        <v>4.64</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.79</v>
+        <v>5.76</v>
       </c>
       <c r="BR6" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS6" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT6" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BU6" t="n">
-        <v>29.17</v>
+        <v>28</v>
       </c>
       <c r="BV6" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY6" t="n">
         <v>2.95</v>
@@ -3222,34 +3222,34 @@
         <v>3.07</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.57</v>
+        <v>3.61</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.69</v>
+        <v>3.73</v>
       </c>
       <c r="CC6" t="n">
-        <v>4.15</v>
+        <v>4.26</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.57</v>
+        <v>4.76</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="CG6" t="n">
-        <v>3.03</v>
+        <v>3.04</v>
       </c>
       <c r="CH6" t="n">
         <v>1.47</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CK6" t="n">
         <v>1.41</v>
@@ -3261,7 +3261,7 @@
         <v>2.73</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="CO6" t="n">
         <v>1.21</v>
@@ -3270,7 +3270,7 @@
         <v>1.76</v>
       </c>
       <c r="CQ6" t="n">
-        <v>2.81</v>
+        <v>2.79</v>
       </c>
       <c r="CR6" t="n">
         <v>1.38</v>
@@ -3285,10 +3285,10 @@
         <v>1.5</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CX6" t="n">
         <v>1.47</v>
@@ -3300,7 +3300,7 @@
         <v>2.56</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.08</v>
+        <v>2.09</v>
       </c>
       <c r="DB6" t="n">
         <v>1.24</v>
@@ -3315,43 +3315,43 @@
         <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="DH6" t="n">
-        <v>99.04000000000001</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.79</v>
+        <v>2.84</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.54</v>
+        <v>4.56</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="DM6" t="n">
-        <v>41.62</v>
+        <v>41</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.17</v>
+        <v>12.4</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.83</v>
+        <v>12.68</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.08</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DS6" t="n">
         <v>0.12</v>
@@ -3363,28 +3363,28 @@
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>44.16</v>
+        <v>43.68</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.29</v>
+        <v>0.32</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.59</v>
+        <v>12.32</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.67</v>
+        <v>8.44</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.92</v>
+        <v>3.88</v>
       </c>
       <c r="EA6" t="n">
-        <v>22</v>
+        <v>21.52</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="7">
@@ -3394,94 +3394,94 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D7" t="n">
         <v>13</v>
       </c>
       <c r="E7" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="G7" t="n">
-        <v>3.27</v>
+        <v>3.58</v>
       </c>
       <c r="H7" t="n">
-        <v>102.27</v>
+        <v>102.92</v>
       </c>
       <c r="I7" t="n">
         <v>0</v>
       </c>
       <c r="J7" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="K7" t="n">
-        <v>6.09</v>
+        <v>6.5</v>
       </c>
       <c r="L7" t="n">
-        <v>0.45</v>
+        <v>0.58</v>
       </c>
       <c r="M7" t="n">
-        <v>56.91</v>
+        <v>57.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O7" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="P7" t="n">
-        <v>10.82</v>
+        <v>10.17</v>
       </c>
       <c r="Q7" t="n">
-        <v>13.73</v>
+        <v>13.5</v>
       </c>
       <c r="R7" t="n">
-        <v>6.45</v>
+        <v>6.58</v>
       </c>
       <c r="S7" t="n">
-        <v>0.91</v>
+        <v>0.83</v>
       </c>
       <c r="T7" t="n">
-        <v>1.73</v>
+        <v>1.67</v>
       </c>
       <c r="U7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V7" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>55.55</v>
+        <v>55</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>16.09</v>
+        <v>16</v>
       </c>
       <c r="AA7" t="n">
-        <v>11.09</v>
+        <v>11.08</v>
       </c>
       <c r="AB7" t="n">
-        <v>5</v>
+        <v>4.92</v>
       </c>
       <c r="AC7" t="n">
-        <v>24.36</v>
+        <v>23.75</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.45</v>
+        <v>1.33</v>
       </c>
       <c r="AF7" t="n">
         <v>0.08</v>
@@ -3565,58 +3565,58 @@
         <v>2.46</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.54</v>
+        <v>10.76</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.88</v>
+        <v>2.8</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.5</v>
+        <v>0.48</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BL7" t="n">
         <v>0.96</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="BO7" t="n">
-        <v>1.17</v>
+        <v>1.12</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.17</v>
+        <v>5.12</v>
       </c>
       <c r="BQ7" t="n">
-        <v>4.71</v>
+        <v>5</v>
       </c>
       <c r="BR7" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS7" t="n">
-        <v>79.17</v>
+        <v>76</v>
       </c>
       <c r="BT7" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU7" t="n">
-        <v>37.5</v>
+        <v>36</v>
       </c>
       <c r="BV7" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW7" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX7" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BY7" t="n">
         <v>1.91</v>
@@ -3625,10 +3625,10 @@
         <v>1.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.47</v>
+        <v>3.48</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.75</v>
+        <v>3.77</v>
       </c>
       <c r="CC7" t="n">
         <v>2.19</v>
@@ -3643,13 +3643,13 @@
         <v>2.35</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CH7" t="n">
         <v>1.46</v>
       </c>
       <c r="CI7" t="n">
-        <v>2.24</v>
+        <v>2.25</v>
       </c>
       <c r="CJ7" t="n">
         <v>1.5</v>
@@ -3661,7 +3661,7 @@
         <v>1.62</v>
       </c>
       <c r="CM7" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="CN7" t="n">
         <v>2.08</v>
@@ -3673,7 +3673,7 @@
         <v>1.58</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.48</v>
+        <v>2.47</v>
       </c>
       <c r="CR7" t="n">
         <v>1.37</v>
@@ -3688,7 +3688,7 @@
         <v>1.53</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.41</v>
+        <v>2.43</v>
       </c>
       <c r="CW7" t="n">
         <v>1.61</v>
@@ -3709,52 +3709,52 @@
         <v>1.22</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.71</v>
+        <v>2.88</v>
       </c>
       <c r="DH7" t="n">
-        <v>98.75</v>
+        <v>99.2</v>
       </c>
       <c r="DI7" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ7" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.12</v>
+        <v>6.32</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.46</v>
+        <v>0.52</v>
       </c>
       <c r="DM7" t="n">
-        <v>51.62</v>
+        <v>52.12</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="DO7" t="n">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.79</v>
+        <v>10.48</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.37</v>
+        <v>14.24</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.87</v>
+        <v>6.92</v>
       </c>
       <c r="DS7" t="n">
         <v>0.12</v>
@@ -3766,7 +3766,7 @@
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.37</v>
+        <v>54.16</v>
       </c>
       <c r="DW7" t="n">
         <v>0.04</v>
@@ -3775,19 +3775,19 @@
         <v>15.04</v>
       </c>
       <c r="DY7" t="n">
-        <v>10</v>
+        <v>10.04</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
       <c r="EA7" t="n">
-        <v>23.12</v>
+        <v>22.88</v>
       </c>
       <c r="EB7" t="n">
         <v>1.68</v>
       </c>
       <c r="EC7" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="8">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C8" t="n">
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3887,139 +3887,139 @@
         <v>2.69</v>
       </c>
       <c r="AF8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AI8" t="n">
-        <v>93.81999999999999</v>
+        <v>93.5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.45</v>
+        <v>4.5</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AN8" t="n">
-        <v>41.91</v>
+        <v>42.67</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.73</v>
+        <v>12.42</v>
       </c>
       <c r="AR8" t="n">
-        <v>12.18</v>
+        <v>12</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.640000000000001</v>
+        <v>9.17</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.55</v>
+        <v>1.42</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="AV8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AW8" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AX8" t="n">
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.45</v>
+        <v>45.67</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="BA8" t="n">
-        <v>13.82</v>
+        <v>14.08</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.640000000000001</v>
+        <v>9.67</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.18</v>
+        <v>4.42</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.27</v>
+        <v>19.08</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.47</v>
+        <v>1.51</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BH8" t="n">
-        <v>8.92</v>
+        <v>8.880000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.33</v>
+        <v>0.32</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BP8" t="n">
         <v>3.88</v>
       </c>
       <c r="BQ8" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="BR8" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS8" t="n">
-        <v>70.83</v>
+        <v>68</v>
       </c>
       <c r="BT8" t="n">
-        <v>54.17</v>
+        <v>52</v>
       </c>
       <c r="BU8" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BV8" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW8" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX8" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BY8" t="n">
         <v>2.35</v>
@@ -4028,22 +4028,22 @@
         <v>2.4</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.62</v>
+        <v>3.61</v>
       </c>
       <c r="CB8" t="n">
+        <v>3.74</v>
+      </c>
+      <c r="CC8" t="n">
+        <v>3.41</v>
+      </c>
+      <c r="CD8" t="n">
         <v>3.75</v>
-      </c>
-      <c r="CC8" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="CD8" t="n">
-        <v>3.81</v>
       </c>
       <c r="CE8" t="n">
         <v>1.31</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG8" t="n">
         <v>3.16</v>
@@ -4067,13 +4067,13 @@
         <v>2.64</v>
       </c>
       <c r="CN8" t="n">
-        <v>2.04</v>
+        <v>2.03</v>
       </c>
       <c r="CO8" t="n">
         <v>1.19</v>
       </c>
       <c r="CP8" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="CQ8" t="n">
         <v>2.59</v>
@@ -4082,7 +4082,7 @@
         <v>1.36</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.58</v>
+        <v>2.59</v>
       </c>
       <c r="CT8" t="n">
         <v>3.23</v>
@@ -4097,67 +4097,67 @@
         <v>1.6</v>
       </c>
       <c r="CX8" t="n">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="CY8" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.51</v>
+        <v>2.5</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.08</v>
+        <v>2.07</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.84</v>
+        <v>93.68000000000001</v>
       </c>
       <c r="DI8" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.71</v>
+        <v>2.68</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM8" t="n">
-        <v>47.13</v>
+        <v>47.28</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.29</v>
+        <v>12.16</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.79</v>
+        <v>11.72</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.84</v>
+        <v>7.68</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.79</v>
+        <v>48.76</v>
       </c>
       <c r="DW8" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.25</v>
+        <v>13.4</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.17</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.08</v>
+        <v>4.2</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.54</v>
+        <v>20.4</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
     </row>
     <row r="9">
@@ -5409,13 +5409,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C12" t="n">
         <v>12</v>
       </c>
       <c r="D12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
@@ -5502,136 +5502,136 @@
         <v>0.08</v>
       </c>
       <c r="AG12" t="n">
-        <v>2.67</v>
+        <v>2.46</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AI12" t="n">
-        <v>82.25</v>
+        <v>79.62</v>
       </c>
       <c r="AJ12" t="n">
         <v>0.08</v>
       </c>
       <c r="AK12" t="n">
-        <v>3.75</v>
+        <v>3.62</v>
       </c>
       <c r="AL12" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="AM12" t="n">
-        <v>0.17</v>
+        <v>0.31</v>
       </c>
       <c r="AN12" t="n">
-        <v>35.17</v>
+        <v>34.69</v>
       </c>
       <c r="AO12" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="AQ12" t="n">
-        <v>15.5</v>
+        <v>15.46</v>
       </c>
       <c r="AR12" t="n">
-        <v>13.33</v>
+        <v>13.23</v>
       </c>
       <c r="AS12" t="n">
-        <v>9.5</v>
+        <v>9.92</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AV12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AW12" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AX12" t="n">
         <v>0</v>
       </c>
       <c r="AY12" t="n">
-        <v>50.08</v>
+        <v>48.77</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.25</v>
+        <v>0.31</v>
       </c>
       <c r="BA12" t="n">
-        <v>11.58</v>
+        <v>11.23</v>
       </c>
       <c r="BB12" t="n">
-        <v>8.17</v>
+        <v>8</v>
       </c>
       <c r="BC12" t="n">
-        <v>3.42</v>
+        <v>3.23</v>
       </c>
       <c r="BD12" t="n">
-        <v>19.42</v>
+        <v>19.15</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.23</v>
+        <v>1.19</v>
       </c>
       <c r="BF12" t="n">
-        <v>3.5</v>
+        <v>3.31</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.5</v>
+        <v>10.32</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.67</v>
+        <v>2.64</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.46</v>
+        <v>4.48</v>
       </c>
       <c r="BQ12" t="n">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT12" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BU12" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BV12" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW12" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX12" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BY12" t="n">
         <v>2.32</v>
@@ -5643,22 +5643,22 @@
         <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.62</v>
+        <v>3.64</v>
       </c>
       <c r="CC12" t="n">
-        <v>2.99</v>
+        <v>3.02</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="CE12" t="n">
         <v>1.33</v>
       </c>
       <c r="CF12" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.12</v>
+        <v>3.13</v>
       </c>
       <c r="CH12" t="n">
         <v>1.49</v>
@@ -5673,13 +5673,13 @@
         <v>1.36</v>
       </c>
       <c r="CL12" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="CM12" t="n">
-        <v>2.84</v>
+        <v>2.83</v>
       </c>
       <c r="CN12" t="n">
-        <v>2.17</v>
+        <v>2.18</v>
       </c>
       <c r="CO12" t="n">
         <v>1.2</v>
@@ -5712,13 +5712,13 @@
         <v>1.48</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ12" t="n">
         <v>2.54</v>
       </c>
       <c r="DA12" t="n">
-        <v>2.13</v>
+        <v>2.14</v>
       </c>
       <c r="DB12" t="n">
         <v>1.24</v>
@@ -5727,49 +5727,49 @@
         <v>1.79</v>
       </c>
       <c r="DD12" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="DE12" t="n">
         <v>0.04</v>
       </c>
       <c r="DF12" t="n">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="DG12" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="DH12" t="n">
-        <v>85.25</v>
+        <v>83.76000000000001</v>
       </c>
       <c r="DI12" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ12" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="DK12" t="n">
-        <v>4.83</v>
+        <v>4.84</v>
       </c>
       <c r="DL12" t="n">
-        <v>0.38</v>
+        <v>0.44</v>
       </c>
       <c r="DM12" t="n">
-        <v>38.84</v>
+        <v>38.44</v>
       </c>
       <c r="DN12" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="DO12" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="DP12" t="n">
-        <v>14.25</v>
+        <v>14.28</v>
       </c>
       <c r="DQ12" t="n">
-        <v>14</v>
+        <v>13.92</v>
       </c>
       <c r="DR12" t="n">
-        <v>8.380000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DS12" t="n">
         <v>0.16</v>
@@ -5781,28 +5781,28 @@
         <v>0</v>
       </c>
       <c r="DV12" t="n">
-        <v>51.42</v>
+        <v>50.68</v>
       </c>
       <c r="DW12" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DX12" t="n">
-        <v>12.04</v>
+        <v>11.84</v>
       </c>
       <c r="DY12" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DZ12" t="n">
-        <v>3.75</v>
+        <v>3.64</v>
       </c>
       <c r="EA12" t="n">
-        <v>19.62</v>
+        <v>19.48</v>
       </c>
       <c r="EB12" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="EC12" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
     </row>
     <row r="13">
@@ -6618,13 +6618,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C15" t="n">
         <v>12</v>
       </c>
       <c r="D15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
@@ -6711,49 +6711,49 @@
         <v>0</v>
       </c>
       <c r="AG15" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.58</v>
+        <v>2.77</v>
       </c>
       <c r="AI15" t="n">
-        <v>81.17</v>
+        <v>80.69</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AK15" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="AL15" t="n">
         <v>5.08</v>
       </c>
       <c r="AM15" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="AN15" t="n">
-        <v>37.67</v>
+        <v>37.62</v>
       </c>
       <c r="AO15" t="n">
         <v>1.08</v>
       </c>
       <c r="AP15" t="n">
-        <v>2.25</v>
+        <v>2.08</v>
       </c>
       <c r="AQ15" t="n">
-        <v>11.83</v>
+        <v>11.15</v>
       </c>
       <c r="AR15" t="n">
-        <v>13.58</v>
+        <v>12.85</v>
       </c>
       <c r="AS15" t="n">
-        <v>8.58</v>
+        <v>8.77</v>
       </c>
       <c r="AT15" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="AU15" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="AV15" t="n">
         <v>0.08</v>
@@ -6765,82 +6765,82 @@
         <v>0</v>
       </c>
       <c r="AY15" t="n">
-        <v>53.58</v>
+        <v>53.38</v>
       </c>
       <c r="AZ15" t="n">
         <v>0</v>
       </c>
       <c r="BA15" t="n">
-        <v>16.92</v>
+        <v>16.69</v>
       </c>
       <c r="BB15" t="n">
         <v>10.92</v>
       </c>
       <c r="BC15" t="n">
-        <v>6</v>
+        <v>5.77</v>
       </c>
       <c r="BD15" t="n">
-        <v>18.42</v>
+        <v>18.23</v>
       </c>
       <c r="BE15" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="BF15" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.08</v>
+        <v>10.32</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.42</v>
+        <v>3.32</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BL15" t="n">
         <v>0.96</v>
       </c>
       <c r="BM15" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN15" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.58</v>
+        <v>4.56</v>
       </c>
       <c r="BQ15" t="n">
-        <v>4.92</v>
+        <v>5.2</v>
       </c>
       <c r="BR15" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS15" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BT15" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BU15" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BV15" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BW15" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BX15" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BY15" t="n">
         <v>2.12</v>
@@ -6849,19 +6849,19 @@
         <v>2.27</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.68</v>
+        <v>3.69</v>
       </c>
       <c r="CB15" t="n">
-        <v>3.83</v>
+        <v>3.85</v>
       </c>
       <c r="CC15" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="CD15" t="n">
-        <v>3.12</v>
+        <v>3.18</v>
       </c>
       <c r="CE15" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="CF15" t="n">
         <v>2.28</v>
@@ -6885,7 +6885,7 @@
         <v>1.73</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.84</v>
+        <v>2.85</v>
       </c>
       <c r="CN15" t="n">
         <v>2.17</v>
@@ -6912,7 +6912,7 @@
         <v>1.62</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.63</v>
+        <v>2.64</v>
       </c>
       <c r="CW15" t="n">
         <v>1.52</v>
@@ -6930,55 +6930,55 @@
         <v>2.19</v>
       </c>
       <c r="DB15" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="DC15" t="n">
         <v>1.58</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.75</v>
+        <v>2.84</v>
       </c>
       <c r="DH15" t="n">
-        <v>94.95999999999999</v>
+        <v>94.16</v>
       </c>
       <c r="DI15" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.33</v>
+        <v>5.32</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.45</v>
+        <v>0.44</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.75</v>
+        <v>46.36</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.83</v>
+        <v>0.84</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.42</v>
+        <v>2.32</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.92</v>
+        <v>11.56</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.7</v>
+        <v>12.36</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.25</v>
+        <v>7.4</v>
       </c>
       <c r="DS15" t="n">
         <v>0.12</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.5</v>
+        <v>55.32</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.88</v>
+        <v>16.76</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.34</v>
+        <v>11.32</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.54</v>
+        <v>5.44</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.96</v>
+        <v>18.84</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="16">
@@ -7021,10 +7021,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C16" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D16" t="n">
         <v>12</v>
@@ -7033,49 +7033,49 @@
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="G16" t="n">
-        <v>2.83</v>
+        <v>2.77</v>
       </c>
       <c r="H16" t="n">
-        <v>95.42</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="I16" t="n">
         <v>0</v>
       </c>
       <c r="J16" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="K16" t="n">
-        <v>5.08</v>
+        <v>4.92</v>
       </c>
       <c r="L16" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M16" t="n">
-        <v>44.33</v>
+        <v>44</v>
       </c>
       <c r="N16" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O16" t="n">
-        <v>2.25</v>
+        <v>2.15</v>
       </c>
       <c r="P16" t="n">
-        <v>10.83</v>
+        <v>10.77</v>
       </c>
       <c r="Q16" t="n">
-        <v>13.92</v>
+        <v>13.54</v>
       </c>
       <c r="R16" t="n">
-        <v>7.92</v>
+        <v>8.23</v>
       </c>
       <c r="S16" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="T16" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="U16" t="n">
         <v>0.08</v>
@@ -7087,28 +7087,28 @@
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>50.25</v>
+        <v>50.38</v>
       </c>
       <c r="Y16" t="n">
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.92</v>
+        <v>13.54</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.58</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AB16" t="n">
-        <v>5.33</v>
+        <v>5.08</v>
       </c>
       <c r="AC16" t="n">
-        <v>19</v>
+        <v>18.69</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.57</v>
+        <v>1.53</v>
       </c>
       <c r="AE16" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AF16" t="n">
         <v>0.08</v>
@@ -7192,67 +7192,67 @@
         <v>2.58</v>
       </c>
       <c r="BG16" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="BH16" t="n">
-        <v>9.75</v>
+        <v>9.68</v>
       </c>
       <c r="BI16" t="n">
-        <v>2.71</v>
+        <v>2.64</v>
       </c>
       <c r="BJ16" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BK16" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="BL16" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BM16" t="n">
-        <v>0.62</v>
+        <v>0.64</v>
       </c>
       <c r="BN16" t="n">
-        <v>1.67</v>
+        <v>1.64</v>
       </c>
       <c r="BO16" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="BP16" t="n">
-        <v>4.25</v>
+        <v>4.24</v>
       </c>
       <c r="BQ16" t="n">
-        <v>5.5</v>
+        <v>5.44</v>
       </c>
       <c r="BR16" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS16" t="n">
-        <v>83.33</v>
+        <v>80</v>
       </c>
       <c r="BT16" t="n">
-        <v>58.33</v>
+        <v>56</v>
       </c>
       <c r="BU16" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BV16" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW16" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX16" t="n">
-        <v>66.67</v>
+        <v>64</v>
       </c>
       <c r="BY16" t="n">
-        <v>2.37</v>
+        <v>2.35</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CA16" t="n">
-        <v>3.56</v>
+        <v>3.55</v>
       </c>
       <c r="CB16" t="n">
         <v>3.7</v>
@@ -7264,19 +7264,19 @@
         <v>3.36</v>
       </c>
       <c r="CE16" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF16" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CG16" t="n">
-        <v>3.21</v>
+        <v>3.22</v>
       </c>
       <c r="CH16" t="n">
         <v>1.5</v>
       </c>
       <c r="CI16" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ16" t="n">
         <v>1.59</v>
@@ -7288,10 +7288,10 @@
         <v>1.74</v>
       </c>
       <c r="CM16" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CN16" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO16" t="n">
         <v>1.2</v>
@@ -7306,31 +7306,31 @@
         <v>1.36</v>
       </c>
       <c r="CS16" t="n">
-        <v>2.6</v>
+        <v>2.61</v>
       </c>
       <c r="CT16" t="n">
         <v>3.25</v>
       </c>
       <c r="CU16" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="CW16" t="n">
         <v>1.61</v>
       </c>
       <c r="CX16" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="CY16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="DA16" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB16" t="n">
         <v>1.22</v>
@@ -7339,49 +7339,49 @@
         <v>1.72</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.75</v>
+        <v>2.76</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
       </c>
       <c r="DF16" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="DG16" t="n">
-        <v>3.04</v>
+        <v>3</v>
       </c>
       <c r="DH16" t="n">
-        <v>94.92</v>
+        <v>95.52</v>
       </c>
       <c r="DI16" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ16" t="n">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="DK16" t="n">
-        <v>5.38</v>
+        <v>5.28</v>
       </c>
       <c r="DL16" t="n">
-        <v>0.42</v>
+        <v>0.4</v>
       </c>
       <c r="DM16" t="n">
-        <v>46.38</v>
+        <v>46.12</v>
       </c>
       <c r="DN16" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO16" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="DP16" t="n">
-        <v>11.66</v>
+        <v>11.6</v>
       </c>
       <c r="DQ16" t="n">
-        <v>13.71</v>
+        <v>13.52</v>
       </c>
       <c r="DR16" t="n">
-        <v>8.039999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="DS16" t="n">
         <v>0.12</v>
@@ -7393,28 +7393,28 @@
         <v>0</v>
       </c>
       <c r="DV16" t="n">
-        <v>49.62</v>
+        <v>49.72</v>
       </c>
       <c r="DW16" t="n">
         <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.54</v>
+        <v>12.4</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.83</v>
+        <v>7.8</v>
       </c>
       <c r="DZ16" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="EA16" t="n">
-        <v>20.92</v>
+        <v>20.68</v>
       </c>
       <c r="EB16" t="n">
-        <v>1.46</v>
+        <v>1.44</v>
       </c>
       <c r="EC16" t="n">
-        <v>2.58</v>
+        <v>2.52</v>
       </c>
     </row>
     <row r="17">
@@ -7424,10 +7424,10 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C17" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D17" t="n">
         <v>12</v>
@@ -7436,82 +7436,82 @@
         <v>0.08</v>
       </c>
       <c r="F17" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="G17" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="H17" t="n">
-        <v>101.08</v>
+        <v>103.23</v>
       </c>
       <c r="I17" t="n">
         <v>0</v>
       </c>
       <c r="J17" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="K17" t="n">
-        <v>6.17</v>
+        <v>6.38</v>
       </c>
       <c r="L17" t="n">
-        <v>0.58</v>
+        <v>0.77</v>
       </c>
       <c r="M17" t="n">
-        <v>58.33</v>
+        <v>59.23</v>
       </c>
       <c r="N17" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O17" t="n">
-        <v>2.67</v>
+        <v>3</v>
       </c>
       <c r="P17" t="n">
-        <v>12</v>
+        <v>11.85</v>
       </c>
       <c r="Q17" t="n">
-        <v>10.5</v>
+        <v>11.08</v>
       </c>
       <c r="R17" t="n">
-        <v>7.17</v>
+        <v>6.77</v>
       </c>
       <c r="S17" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="T17" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="U17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="V17" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>55.83</v>
+        <v>56.77</v>
       </c>
       <c r="Y17" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z17" t="n">
-        <v>17.67</v>
+        <v>17.69</v>
       </c>
       <c r="AA17" t="n">
-        <v>11.33</v>
+        <v>11.46</v>
       </c>
       <c r="AB17" t="n">
-        <v>6.33</v>
+        <v>6.23</v>
       </c>
       <c r="AC17" t="n">
-        <v>21.33</v>
+        <v>21.31</v>
       </c>
       <c r="AD17" t="n">
         <v>1.98</v>
       </c>
       <c r="AE17" t="n">
-        <v>1.67</v>
+        <v>1.62</v>
       </c>
       <c r="AF17" t="n">
         <v>0.25</v>
@@ -7595,70 +7595,70 @@
         <v>2.42</v>
       </c>
       <c r="BG17" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="BH17" t="n">
-        <v>10.25</v>
+        <v>10.4</v>
       </c>
       <c r="BI17" t="n">
-        <v>2.79</v>
+        <v>2.76</v>
       </c>
       <c r="BJ17" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BK17" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BL17" t="n">
         <v>0.96</v>
       </c>
       <c r="BM17" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BN17" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="BO17" t="n">
-        <v>1.25</v>
+        <v>1.2</v>
       </c>
       <c r="BP17" t="n">
-        <v>4.71</v>
+        <v>4.88</v>
       </c>
       <c r="BQ17" t="n">
-        <v>5.46</v>
+        <v>5.44</v>
       </c>
       <c r="BR17" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS17" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT17" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BU17" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BV17" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BW17" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX17" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY17" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="BZ17" t="n">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="CA17" t="n">
-        <v>3.63</v>
+        <v>3.66</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.74</v>
+        <v>3.78</v>
       </c>
       <c r="CC17" t="n">
         <v>2.24</v>
@@ -7679,19 +7679,19 @@
         <v>1.51</v>
       </c>
       <c r="CI17" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CJ17" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CK17" t="n">
         <v>1.37</v>
       </c>
       <c r="CL17" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="CM17" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="CN17" t="n">
         <v>2.14</v>
@@ -7703,7 +7703,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ17" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CR17" t="n">
         <v>1.36</v>
@@ -7718,10 +7718,10 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="CW17" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX17" t="n">
         <v>1.46</v>
@@ -7748,76 +7748,76 @@
         <v>0.16</v>
       </c>
       <c r="DF17" t="n">
-        <v>1.42</v>
+        <v>1.4</v>
       </c>
       <c r="DG17" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="DH17" t="n">
-        <v>100.75</v>
+        <v>101.88</v>
       </c>
       <c r="DI17" t="n">
         <v>-0.04</v>
       </c>
       <c r="DJ17" t="n">
-        <v>2.25</v>
+        <v>2.2</v>
       </c>
       <c r="DK17" t="n">
-        <v>5.42</v>
+        <v>5.56</v>
       </c>
       <c r="DL17" t="n">
-        <v>0.7</v>
+        <v>0.8</v>
       </c>
       <c r="DM17" t="n">
-        <v>49.79</v>
+        <v>50.6</v>
       </c>
       <c r="DN17" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="DO17" t="n">
-        <v>2.38</v>
+        <v>2.56</v>
       </c>
       <c r="DP17" t="n">
-        <v>12.71</v>
+        <v>12.6</v>
       </c>
       <c r="DQ17" t="n">
-        <v>10.92</v>
+        <v>11.2</v>
       </c>
       <c r="DR17" t="n">
-        <v>7.21</v>
+        <v>7</v>
       </c>
       <c r="DS17" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DT17" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DU17" t="n">
         <v>0</v>
       </c>
       <c r="DV17" t="n">
-        <v>54.29</v>
+        <v>54.84</v>
       </c>
       <c r="DW17" t="n">
         <v>0.12</v>
       </c>
       <c r="DX17" t="n">
-        <v>15.88</v>
+        <v>15.96</v>
       </c>
       <c r="DY17" t="n">
-        <v>10.29</v>
+        <v>10.4</v>
       </c>
       <c r="DZ17" t="n">
-        <v>5.58</v>
+        <v>5.56</v>
       </c>
       <c r="EA17" t="n">
-        <v>20.75</v>
+        <v>20.76</v>
       </c>
       <c r="EB17" t="n">
         <v>1.76</v>
       </c>
       <c r="EC17" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
     </row>
     <row r="18">
@@ -8230,94 +8230,94 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D19" t="n">
         <v>13</v>
       </c>
       <c r="E19" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F19" t="n">
-        <v>2.09</v>
+        <v>1.92</v>
       </c>
       <c r="G19" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="H19" t="n">
-        <v>105.82</v>
+        <v>106.58</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>2.55</v>
+        <v>2.33</v>
       </c>
       <c r="K19" t="n">
-        <v>5.64</v>
+        <v>5.92</v>
       </c>
       <c r="L19" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M19" t="n">
-        <v>52.09</v>
+        <v>52.83</v>
       </c>
       <c r="N19" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O19" t="n">
-        <v>2.18</v>
+        <v>2.42</v>
       </c>
       <c r="P19" t="n">
-        <v>13.82</v>
+        <v>13.25</v>
       </c>
       <c r="Q19" t="n">
-        <v>12.09</v>
+        <v>12.17</v>
       </c>
       <c r="R19" t="n">
-        <v>5.64</v>
+        <v>5.75</v>
       </c>
       <c r="S19" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="T19" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="V19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>44.83</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>15.17</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>9.58</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>5.58</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>21.67</v>
+      </c>
+      <c r="AD19" t="n">
         <v>1.73</v>
       </c>
-      <c r="U19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="V19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>44.82</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>14.36</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>9</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>21.64</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AE19" t="n">
-        <v>2.45</v>
+        <v>2.25</v>
       </c>
       <c r="AF19" t="n">
         <v>0.15</v>
@@ -8401,67 +8401,67 @@
         <v>2.46</v>
       </c>
       <c r="BG19" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="BH19" t="n">
-        <v>9.5</v>
+        <v>9.56</v>
       </c>
       <c r="BI19" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="BJ19" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="BK19" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="BL19" t="n">
-        <v>0.79</v>
+        <v>0.76</v>
       </c>
       <c r="BM19" t="n">
-        <v>0.62</v>
+        <v>0.6</v>
       </c>
       <c r="BN19" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="BO19" t="n">
         <v>0.88</v>
       </c>
       <c r="BP19" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="BQ19" t="n">
-        <v>5.5</v>
+        <v>5.48</v>
       </c>
       <c r="BR19" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS19" t="n">
-        <v>62.5</v>
+        <v>60</v>
       </c>
       <c r="BT19" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BU19" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BV19" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BW19" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX19" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BY19" t="n">
-        <v>2.2</v>
+        <v>2.17</v>
       </c>
       <c r="BZ19" t="n">
-        <v>2.24</v>
+        <v>2.21</v>
       </c>
       <c r="CA19" t="n">
-        <v>3.41</v>
+        <v>3.42</v>
       </c>
       <c r="CB19" t="n">
         <v>3.55</v>
@@ -8485,16 +8485,16 @@
         <v>1.43</v>
       </c>
       <c r="CI19" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="CJ19" t="n">
         <v>1.67</v>
       </c>
       <c r="CK19" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="CL19" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="CM19" t="n">
         <v>2.62</v>
@@ -8509,13 +8509,13 @@
         <v>1.82</v>
       </c>
       <c r="CQ19" t="n">
-        <v>3.02</v>
+        <v>3.03</v>
       </c>
       <c r="CR19" t="n">
         <v>1.37</v>
       </c>
       <c r="CS19" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="CT19" t="n">
         <v>3.19</v>
@@ -8536,7 +8536,7 @@
         <v>1.81</v>
       </c>
       <c r="CZ19" t="n">
-        <v>2.48</v>
+        <v>2.49</v>
       </c>
       <c r="DA19" t="n">
         <v>2.01</v>
@@ -8548,82 +8548,82 @@
         <v>1.87</v>
       </c>
       <c r="DD19" t="n">
-        <v>3.11</v>
+        <v>3.12</v>
       </c>
       <c r="DE19" t="n">
         <v>0.16</v>
       </c>
       <c r="DF19" t="n">
-        <v>1.79</v>
+        <v>1.72</v>
       </c>
       <c r="DG19" t="n">
-        <v>2.87</v>
+        <v>2.92</v>
       </c>
       <c r="DH19" t="n">
-        <v>107.08</v>
+        <v>107.4</v>
       </c>
       <c r="DI19" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ19" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="DK19" t="n">
-        <v>5.04</v>
+        <v>5.2</v>
       </c>
       <c r="DL19" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="DM19" t="n">
-        <v>48.96</v>
+        <v>49.44</v>
       </c>
       <c r="DN19" t="n">
-        <v>0.7</v>
+        <v>0.68</v>
       </c>
       <c r="DO19" t="n">
-        <v>2.16</v>
+        <v>2.28</v>
       </c>
       <c r="DP19" t="n">
-        <v>13.58</v>
+        <v>13.32</v>
       </c>
       <c r="DQ19" t="n">
-        <v>11.92</v>
+        <v>11.96</v>
       </c>
       <c r="DR19" t="n">
-        <v>5.92</v>
+        <v>5.96</v>
       </c>
       <c r="DS19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DT19" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DU19" t="n">
         <v>0</v>
       </c>
       <c r="DV19" t="n">
-        <v>44.54</v>
+        <v>44.56</v>
       </c>
       <c r="DW19" t="n">
         <v>0.04</v>
       </c>
       <c r="DX19" t="n">
-        <v>13.42</v>
+        <v>13.84</v>
       </c>
       <c r="DY19" t="n">
-        <v>8.66</v>
+        <v>8.960000000000001</v>
       </c>
       <c r="DZ19" t="n">
-        <v>4.75</v>
+        <v>4.88</v>
       </c>
       <c r="EA19" t="n">
-        <v>22.63</v>
+        <v>22.6</v>
       </c>
       <c r="EB19" t="n">
-        <v>1.54</v>
+        <v>1.57</v>
       </c>
       <c r="EC19" t="n">
-        <v>2.46</v>
+        <v>2.36</v>
       </c>
     </row>
   </sheetData>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="8.4" customWidth="1" min="76" max="76"/>
+    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -1782,25 +1782,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D3" t="n">
         <v>12</v>
       </c>
       <c r="E3" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="F3" t="n">
         <v>2</v>
       </c>
       <c r="G3" t="n">
-        <v>2.83</v>
+        <v>2.92</v>
       </c>
       <c r="H3" t="n">
-        <v>103.92</v>
+        <v>105.69</v>
       </c>
       <c r="I3" t="n">
         <v>0.08</v>
@@ -1809,34 +1809,34 @@
         <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>5.5</v>
+        <v>5.46</v>
       </c>
       <c r="L3" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="M3" t="n">
-        <v>54.17</v>
+        <v>53.46</v>
       </c>
       <c r="N3" t="n">
         <v>1</v>
       </c>
       <c r="O3" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="P3" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Q3" t="n">
-        <v>10.08</v>
+        <v>10.15</v>
       </c>
       <c r="R3" t="n">
-        <v>8.08</v>
+        <v>7.85</v>
       </c>
       <c r="S3" t="n">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="T3" t="n">
-        <v>1.5</v>
+        <v>1.62</v>
       </c>
       <c r="U3" t="n">
         <v>0.08</v>
@@ -1848,25 +1848,25 @@
         <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>47.17</v>
+        <v>47.92</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>16.42</v>
+        <v>16.46</v>
       </c>
       <c r="AA3" t="n">
-        <v>11.08</v>
+        <v>10.85</v>
       </c>
       <c r="AB3" t="n">
-        <v>5.33</v>
+        <v>5.62</v>
       </c>
       <c r="AC3" t="n">
-        <v>21.33</v>
+        <v>21.08</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="AE3" t="n">
         <v>3</v>
@@ -1953,70 +1953,70 @@
         <v>2.92</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.54</v>
+        <v>11.52</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.58</v>
+        <v>2.68</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.71</v>
+        <v>5.56</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.83</v>
+        <v>5.96</v>
       </c>
       <c r="BR3" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS3" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT3" t="n">
-        <v>45.83</v>
+        <v>48</v>
       </c>
       <c r="BU3" t="n">
-        <v>20.83</v>
+        <v>24</v>
       </c>
       <c r="BV3" t="n">
-        <v>16.67</v>
+        <v>20</v>
       </c>
       <c r="BW3" t="n">
-        <v>4.17</v>
+        <v>4</v>
       </c>
       <c r="BX3" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY3" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="BZ3" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="CA3" t="n">
-        <v>3.58</v>
+        <v>3.6</v>
       </c>
       <c r="CB3" t="n">
-        <v>3.67</v>
+        <v>3.68</v>
       </c>
       <c r="CC3" t="n">
         <v>3.02</v>
@@ -2049,10 +2049,10 @@
         <v>1.67</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.98</v>
+        <v>2.97</v>
       </c>
       <c r="CN3" t="n">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="CO3" t="n">
         <v>1.2</v>
@@ -2076,7 +2076,7 @@
         <v>1.52</v>
       </c>
       <c r="CV3" t="n">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="CW3" t="n">
         <v>1.6</v>
@@ -2094,25 +2094,25 @@
         <v>2.26</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DF3" t="n">
         <v>2.04</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="DH3" t="n">
-        <v>93.45999999999999</v>
+        <v>94.8</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
@@ -2121,28 +2121,28 @@
         <v>2.96</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.54</v>
+        <v>5.52</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.71</v>
+        <v>46.64</v>
       </c>
       <c r="DN3" t="n">
         <v>0.92</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.67</v>
+        <v>2.6</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.54</v>
+        <v>13.32</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.58</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.619999999999999</v>
+        <v>8.48</v>
       </c>
       <c r="DS3" t="n">
         <v>0.12</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>45.88</v>
+        <v>46.32</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.12</v>
+        <v>14.24</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.699999999999999</v>
+        <v>9.640000000000001</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.42</v>
+        <v>4.6</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.33</v>
+        <v>22.16</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="EC3" t="n">
         <v>2.96</v>
@@ -2230,7 +2230,7 @@
         <v>11.08</v>
       </c>
       <c r="Q4" t="n">
-        <v>12.31</v>
+        <v>12.23</v>
       </c>
       <c r="R4" t="n">
         <v>8.15</v>
@@ -2419,7 +2419,7 @@
         <v>3.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CC4" t="n">
         <v>2.84</v>
@@ -2476,7 +2476,7 @@
         <v>3.28</v>
       </c>
       <c r="CU4" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CV4" t="n">
         <v>2.42</v>
@@ -2542,7 +2542,7 @@
         <v>11.4</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.92</v>
+        <v>11.88</v>
       </c>
       <c r="DR4" t="n">
         <v>8.16</v>
@@ -2588,13 +2588,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C5" t="n">
         <v>12</v>
       </c>
       <c r="D5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E5" t="n">
         <v>0.08</v>
@@ -2678,52 +2678,52 @@
         <v>2</v>
       </c>
       <c r="AF5" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.08</v>
+        <v>1</v>
       </c>
       <c r="AH5" t="n">
-        <v>2.92</v>
+        <v>2.77</v>
       </c>
       <c r="AI5" t="n">
-        <v>96.5</v>
+        <v>96.23</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AK5" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="AL5" t="n">
         <v>5</v>
       </c>
       <c r="AM5" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AN5" t="n">
-        <v>46.25</v>
+        <v>45.23</v>
       </c>
       <c r="AO5" t="n">
-        <v>1</v>
+        <v>0.92</v>
       </c>
       <c r="AP5" t="n">
-        <v>2.08</v>
+        <v>2.23</v>
       </c>
       <c r="AQ5" t="n">
-        <v>11.33</v>
+        <v>11.23</v>
       </c>
       <c r="AR5" t="n">
-        <v>11.75</v>
+        <v>11.62</v>
       </c>
       <c r="AS5" t="n">
-        <v>8.92</v>
+        <v>8.85</v>
       </c>
       <c r="AT5" t="n">
-        <v>1.75</v>
+        <v>1.85</v>
       </c>
       <c r="AU5" t="n">
-        <v>1.33</v>
+        <v>1.46</v>
       </c>
       <c r="AV5" t="n">
         <v>0</v>
@@ -2735,82 +2735,82 @@
         <v>0</v>
       </c>
       <c r="AY5" t="n">
-        <v>48.83</v>
+        <v>49</v>
       </c>
       <c r="AZ5" t="n">
         <v>0.08</v>
       </c>
       <c r="BA5" t="n">
-        <v>13.17</v>
+        <v>13.08</v>
       </c>
       <c r="BB5" t="n">
-        <v>9.42</v>
+        <v>9.15</v>
       </c>
       <c r="BC5" t="n">
-        <v>3.75</v>
+        <v>3.92</v>
       </c>
       <c r="BD5" t="n">
-        <v>22.17</v>
+        <v>21.69</v>
       </c>
       <c r="BE5" t="n">
         <v>1.43</v>
       </c>
       <c r="BF5" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="BH5" t="n">
-        <v>10.96</v>
+        <v>11</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.17</v>
+        <v>3.28</v>
       </c>
       <c r="BJ5" t="n">
         <v>0.88</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.79</v>
+        <v>0.84</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.71</v>
+        <v>1.8</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.79</v>
+        <v>4.88</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.12</v>
+        <v>6.08</v>
       </c>
       <c r="BR5" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS5" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BT5" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BU5" t="n">
-        <v>37.5</v>
+        <v>40</v>
       </c>
       <c r="BV5" t="n">
-        <v>12.5</v>
+        <v>16</v>
       </c>
       <c r="BW5" t="n">
-        <v>4.17</v>
+        <v>8</v>
       </c>
       <c r="BX5" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BY5" t="n">
         <v>2.57</v>
@@ -2819,16 +2819,16 @@
         <v>2.61</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.65</v>
+        <v>3.64</v>
       </c>
       <c r="CB5" t="n">
         <v>3.72</v>
       </c>
       <c r="CC5" t="n">
-        <v>3.78</v>
+        <v>3.67</v>
       </c>
       <c r="CD5" t="n">
-        <v>4.09</v>
+        <v>3.96</v>
       </c>
       <c r="CE5" t="n">
         <v>1.32</v>
@@ -2837,13 +2837,13 @@
         <v>2.45</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.23</v>
+        <v>3.22</v>
       </c>
       <c r="CH5" t="n">
         <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CJ5" t="n">
         <v>1.59</v>
@@ -2855,10 +2855,10 @@
         <v>1.69</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.87</v>
+        <v>2.86</v>
       </c>
       <c r="CN5" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="CO5" t="n">
         <v>1.19</v>
@@ -2867,7 +2867,7 @@
         <v>1.69</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.68</v>
+        <v>2.67</v>
       </c>
       <c r="CR5" t="n">
         <v>1.36</v>
@@ -2876,13 +2876,13 @@
         <v>2.58</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.26</v>
+        <v>3.27</v>
       </c>
       <c r="CU5" t="n">
         <v>1.54</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="CW5" t="n">
         <v>1.61</v>
@@ -2906,46 +2906,46 @@
         <v>1.73</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.77</v>
+        <v>2.78</v>
       </c>
       <c r="DE5" t="n">
-        <v>0.08</v>
+        <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.83</v>
+        <v>2.76</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.34</v>
+        <v>91.40000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="DK5" t="n">
         <v>4.88</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.38</v>
+        <v>0.4</v>
       </c>
       <c r="DM5" t="n">
-        <v>44.42</v>
+        <v>43.96</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.71</v>
+        <v>0.68</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.08</v>
+        <v>11.04</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.42</v>
+        <v>12.32</v>
       </c>
       <c r="DR5" t="n">
         <v>8.039999999999999</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>48.92</v>
+        <v>49</v>
       </c>
       <c r="DW5" t="n">
         <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.84</v>
+        <v>12.8</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.880000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="DZ5" t="n">
-        <v>3.96</v>
+        <v>4.04</v>
       </c>
       <c r="EA5" t="n">
-        <v>21.08</v>
+        <v>20.88</v>
       </c>
       <c r="EB5" t="n">
         <v>1.41</v>
       </c>
       <c r="EC5" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
     </row>
     <row r="6">
@@ -3225,13 +3225,13 @@
         <v>3.61</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.73</v>
+        <v>3.72</v>
       </c>
       <c r="CC6" t="n">
         <v>4.26</v>
       </c>
       <c r="CD6" t="n">
-        <v>4.76</v>
+        <v>4.65</v>
       </c>
       <c r="CE6" t="n">
         <v>1.33</v>
@@ -3276,7 +3276,7 @@
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="CT6" t="n">
         <v>3.18</v>
@@ -3285,10 +3285,10 @@
         <v>1.5</v>
       </c>
       <c r="CV6" t="n">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="CW6" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="CX6" t="n">
         <v>1.47</v>
@@ -3911,7 +3911,7 @@
         <v>0.17</v>
       </c>
       <c r="AN8" t="n">
-        <v>42.67</v>
+        <v>42.75</v>
       </c>
       <c r="AO8" t="n">
         <v>1.17</v>
@@ -4037,7 +4037,7 @@
         <v>3.41</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.75</v>
+        <v>3.74</v>
       </c>
       <c r="CE8" t="n">
         <v>1.31</v>
@@ -4085,7 +4085,7 @@
         <v>2.59</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CU8" t="n">
         <v>1.53</v>
@@ -4103,19 +4103,19 @@
         <v>1.75</v>
       </c>
       <c r="CZ8" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="DA8" t="n">
         <v>2.07</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
@@ -4142,7 +4142,7 @@
         <v>0.28</v>
       </c>
       <c r="DM8" t="n">
-        <v>47.28</v>
+        <v>47.32</v>
       </c>
       <c r="DN8" t="n">
         <v>1.2</v>
@@ -4200,13 +4200,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" t="n">
         <v>12</v>
       </c>
       <c r="D9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E9" t="n">
         <v>0.33</v>
@@ -4293,100 +4293,100 @@
         <v>0</v>
       </c>
       <c r="AG9" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="AH9" t="n">
-        <v>2.08</v>
+        <v>2.15</v>
       </c>
       <c r="AI9" t="n">
-        <v>75.92</v>
+        <v>74.77</v>
       </c>
       <c r="AJ9" t="n">
         <v>0</v>
       </c>
       <c r="AK9" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="AL9" t="n">
-        <v>4.08</v>
+        <v>4.15</v>
       </c>
       <c r="AM9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="AN9" t="n">
-        <v>34.67</v>
+        <v>33.62</v>
       </c>
       <c r="AO9" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="AP9" t="n">
         <v>2</v>
       </c>
       <c r="AQ9" t="n">
-        <v>13.58</v>
+        <v>13.38</v>
       </c>
       <c r="AR9" t="n">
-        <v>11.83</v>
+        <v>11.69</v>
       </c>
       <c r="AS9" t="n">
-        <v>8.92</v>
+        <v>9</v>
       </c>
       <c r="AT9" t="n">
-        <v>2.42</v>
+        <v>2.31</v>
       </c>
       <c r="AU9" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="AV9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AW9" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AX9" t="n">
         <v>0</v>
       </c>
       <c r="AY9" t="n">
-        <v>47.5</v>
+        <v>46.85</v>
       </c>
       <c r="AZ9" t="n">
         <v>0</v>
       </c>
       <c r="BA9" t="n">
-        <v>11.92</v>
+        <v>12.08</v>
       </c>
       <c r="BB9" t="n">
-        <v>7.5</v>
+        <v>7.46</v>
       </c>
       <c r="BC9" t="n">
-        <v>4.42</v>
+        <v>4.62</v>
       </c>
       <c r="BD9" t="n">
-        <v>22.67</v>
+        <v>22.15</v>
       </c>
       <c r="BE9" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="BF9" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="BH9" t="n">
-        <v>10</v>
+        <v>10.48</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.75</v>
+        <v>3.72</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.75</v>
+        <v>0.72</v>
       </c>
       <c r="BK9" t="n">
         <v>0.88</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="BM9" t="n">
         <v>0.96</v>
@@ -4395,34 +4395,34 @@
         <v>2.12</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.21</v>
+        <v>4.28</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.25</v>
+        <v>5.64</v>
       </c>
       <c r="BR9" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS9" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT9" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BU9" t="n">
-        <v>45.83</v>
+        <v>44</v>
       </c>
       <c r="BV9" t="n">
-        <v>33.33</v>
+        <v>32</v>
       </c>
       <c r="BW9" t="n">
-        <v>20.83</v>
+        <v>20</v>
       </c>
       <c r="BX9" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY9" t="n">
         <v>3.15</v>
@@ -4431,16 +4431,16 @@
         <v>3.54</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.77</v>
+        <v>3.81</v>
       </c>
       <c r="CB9" t="n">
-        <v>3.98</v>
+        <v>4.05</v>
       </c>
       <c r="CC9" t="n">
-        <v>4.2</v>
+        <v>4.38</v>
       </c>
       <c r="CD9" t="n">
-        <v>4.95</v>
+        <v>5.24</v>
       </c>
       <c r="CE9" t="n">
         <v>1.29</v>
@@ -4449,61 +4449,61 @@
         <v>2.37</v>
       </c>
       <c r="CG9" t="n">
-        <v>3.34</v>
+        <v>3.36</v>
       </c>
       <c r="CH9" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.57</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="CM9" t="n">
-        <v>2.78</v>
+        <v>2.79</v>
       </c>
       <c r="CN9" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="CO9" t="n">
         <v>1.17</v>
       </c>
       <c r="CP9" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="CQ9" t="n">
-        <v>2.53</v>
+        <v>2.52</v>
       </c>
       <c r="CR9" t="n">
         <v>1.35</v>
       </c>
       <c r="CS9" t="n">
-        <v>2.49</v>
+        <v>2.47</v>
       </c>
       <c r="CT9" t="n">
         <v>3.32</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="CV9" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW9" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX9" t="n">
         <v>1.47</v>
       </c>
       <c r="CY9" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CZ9" t="n">
         <v>2.56</v>
@@ -4515,10 +4515,10 @@
         <v>1.2</v>
       </c>
       <c r="DC9" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="DD9" t="n">
-        <v>2.61</v>
+        <v>2.59</v>
       </c>
       <c r="DE9" t="n">
         <v>0.16</v>
@@ -4527,40 +4527,40 @@
         <v>1.16</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="DH9" t="n">
-        <v>80.08</v>
+        <v>79.31999999999999</v>
       </c>
       <c r="DI9" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.29</v>
+        <v>4.32</v>
       </c>
       <c r="DL9" t="n">
         <v>0.16</v>
       </c>
       <c r="DM9" t="n">
-        <v>33.38</v>
+        <v>32.88</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.96</v>
+        <v>11.92</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.29</v>
+        <v>13.16</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.710000000000001</v>
+        <v>8.76</v>
       </c>
       <c r="DS9" t="n">
         <v>0.12</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>46.08</v>
+        <v>45.8</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>10.92</v>
+        <v>11.04</v>
       </c>
       <c r="DY9" t="n">
         <v>7.12</v>
       </c>
       <c r="DZ9" t="n">
-        <v>3.8</v>
+        <v>3.92</v>
       </c>
       <c r="EA9" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="EB9" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="10">
@@ -4603,94 +4603,94 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D10" t="n">
         <v>13</v>
       </c>
       <c r="E10" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="F10" t="n">
-        <v>1.09</v>
+        <v>1.17</v>
       </c>
       <c r="G10" t="n">
-        <v>3.64</v>
+        <v>4.33</v>
       </c>
       <c r="H10" t="n">
-        <v>111.27</v>
+        <v>109.25</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="K10" t="n">
-        <v>7</v>
+        <v>7.83</v>
       </c>
       <c r="L10" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="M10" t="n">
-        <v>57.27</v>
+        <v>58.25</v>
       </c>
       <c r="N10" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="O10" t="n">
-        <v>3.36</v>
+        <v>3.42</v>
       </c>
       <c r="P10" t="n">
-        <v>13.45</v>
+        <v>13.25</v>
       </c>
       <c r="Q10" t="n">
-        <v>13.55</v>
+        <v>13.08</v>
       </c>
       <c r="R10" t="n">
-        <v>5.73</v>
+        <v>5.67</v>
       </c>
       <c r="S10" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="T10" t="n">
-        <v>1.55</v>
+        <v>1.5</v>
       </c>
       <c r="U10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="V10" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>57.18</v>
+        <v>57.5</v>
       </c>
       <c r="Y10" t="n">
         <v>0</v>
       </c>
       <c r="Z10" t="n">
-        <v>17</v>
+        <v>17.58</v>
       </c>
       <c r="AA10" t="n">
-        <v>11.27</v>
+        <v>11.58</v>
       </c>
       <c r="AB10" t="n">
-        <v>5.73</v>
+        <v>6</v>
       </c>
       <c r="AC10" t="n">
-        <v>19.73</v>
+        <v>19.92</v>
       </c>
       <c r="AD10" t="n">
-        <v>1.89</v>
+        <v>1.95</v>
       </c>
       <c r="AE10" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="AF10" t="n">
         <v>0.15</v>
@@ -4777,16 +4777,16 @@
         <v>3</v>
       </c>
       <c r="BH10" t="n">
-        <v>9.67</v>
+        <v>10.16</v>
       </c>
       <c r="BI10" t="n">
         <v>3</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.54</v>
+        <v>0.52</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BL10" t="n">
         <v>0.88</v>
@@ -4795,49 +4795,49 @@
         <v>0.88</v>
       </c>
       <c r="BN10" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>4.52</v>
+      </c>
+      <c r="BQ10" t="n">
+        <v>5.56</v>
+      </c>
+      <c r="BR10" t="n">
+        <v>92</v>
+      </c>
+      <c r="BS10" t="n">
+        <v>84</v>
+      </c>
+      <c r="BT10" t="n">
+        <v>76</v>
+      </c>
+      <c r="BU10" t="n">
+        <v>40</v>
+      </c>
+      <c r="BV10" t="n">
+        <v>8</v>
+      </c>
+      <c r="BW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="BX10" t="n">
+        <v>60</v>
+      </c>
+      <c r="BY10" t="n">
         <v>1.75</v>
       </c>
-      <c r="BO10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="BP10" t="n">
-        <v>4.46</v>
-      </c>
-      <c r="BQ10" t="n">
-        <v>5.17</v>
-      </c>
-      <c r="BR10" t="n">
-        <v>91.67</v>
-      </c>
-      <c r="BS10" t="n">
-        <v>83.33</v>
-      </c>
-      <c r="BT10" t="n">
-        <v>75</v>
-      </c>
-      <c r="BU10" t="n">
-        <v>41.67</v>
-      </c>
-      <c r="BV10" t="n">
-        <v>8.33</v>
-      </c>
-      <c r="BW10" t="n">
-        <v>0</v>
-      </c>
-      <c r="BX10" t="n">
-        <v>58.33</v>
-      </c>
-      <c r="BY10" t="n">
-        <v>1.78</v>
-      </c>
       <c r="BZ10" t="n">
-        <v>1.86</v>
+        <v>1.82</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.7</v>
+        <v>3.74</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.82</v>
+        <v>3.9</v>
       </c>
       <c r="CC10" t="n">
         <v>2.35</v>
@@ -4846,19 +4846,19 @@
         <v>2.43</v>
       </c>
       <c r="CE10" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF10" t="n">
-        <v>2.45</v>
+        <v>2.44</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="CH10" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.58</v>
@@ -4867,10 +4867,10 @@
         <v>1.35</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.89</v>
+        <v>2.9</v>
       </c>
       <c r="CN10" t="n">
         <v>2.17</v>
@@ -4879,61 +4879,61 @@
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.59</v>
+        <v>2.57</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
       </c>
       <c r="CS10" t="n">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="CT10" t="n">
         <v>3.31</v>
       </c>
       <c r="CU10" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="CV10" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW10" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="CX10" t="n">
         <v>1.47</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.56</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="DB10" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DC10" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="DE10" t="n">
         <v>0.16</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="DG10" t="n">
-        <v>3</v>
+        <v>3.36</v>
       </c>
       <c r="DH10" t="n">
-        <v>104.42</v>
+        <v>103.72</v>
       </c>
       <c r="DI10" t="n">
         <v>0.08</v>
@@ -4942,58 +4942,58 @@
         <v>1.92</v>
       </c>
       <c r="DK10" t="n">
-        <v>5.71</v>
+        <v>6.16</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM10" t="n">
-        <v>50.46</v>
+        <v>51.2</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.7</v>
+        <v>2.76</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.37</v>
+        <v>13.28</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.71</v>
+        <v>13.48</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.17</v>
+        <v>6.12</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>55.87</v>
+        <v>56.08</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.42</v>
+        <v>14.8</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.119999999999999</v>
+        <v>9.359999999999999</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.29</v>
+        <v>5.44</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="EB10" t="n">
-        <v>1.65</v>
+        <v>1.69</v>
       </c>
       <c r="EC10" t="n">
         <v>1.88</v>
@@ -5006,13 +5006,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C11" t="n">
         <v>13</v>
       </c>
       <c r="D11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E11" t="n">
         <v>0.08</v>
@@ -5096,139 +5096,139 @@
         <v>1.85</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG11" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AH11" t="n">
-        <v>1.91</v>
+        <v>1.83</v>
       </c>
       <c r="AI11" t="n">
-        <v>92.73</v>
+        <v>93.58</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AK11" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.27</v>
+        <v>4.58</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
       <c r="AN11" t="n">
-        <v>46</v>
+        <v>47.67</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.73</v>
+        <v>0.75</v>
       </c>
       <c r="AP11" t="n">
-        <v>1.82</v>
+        <v>2.25</v>
       </c>
       <c r="AQ11" t="n">
-        <v>13.45</v>
+        <v>13.08</v>
       </c>
       <c r="AR11" t="n">
-        <v>12.45</v>
+        <v>12.17</v>
       </c>
       <c r="AS11" t="n">
-        <v>9.09</v>
+        <v>8.75</v>
       </c>
       <c r="AT11" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="AU11" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.09</v>
+        <v>0.17</v>
       </c>
       <c r="AX11" t="n">
         <v>0</v>
       </c>
       <c r="AY11" t="n">
-        <v>47.55</v>
+        <v>48.5</v>
       </c>
       <c r="AZ11" t="n">
         <v>0</v>
       </c>
       <c r="BA11" t="n">
-        <v>11.64</v>
+        <v>11.92</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.55</v>
+        <v>7.75</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.09</v>
+        <v>4.17</v>
       </c>
       <c r="BD11" t="n">
-        <v>21.27</v>
+        <v>21.67</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.36</v>
+        <v>1.39</v>
       </c>
       <c r="BF11" t="n">
-        <v>2.73</v>
+        <v>2.67</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.21</v>
+        <v>10.28</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.67</v>
+        <v>0.64</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.58</v>
+        <v>0.6</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BM11" t="n">
         <v>0.88</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.71</v>
+        <v>4.8</v>
       </c>
       <c r="BQ11" t="n">
         <v>4.96</v>
       </c>
       <c r="BR11" t="n">
-        <v>87.5</v>
+        <v>88</v>
       </c>
       <c r="BS11" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BT11" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BU11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV11" t="n">
-        <v>16.67</v>
+        <v>16</v>
       </c>
       <c r="BW11" t="n">
-        <v>8.33</v>
+        <v>8</v>
       </c>
       <c r="BX11" t="n">
-        <v>41.67</v>
+        <v>44</v>
       </c>
       <c r="BY11" t="n">
         <v>1.91</v>
@@ -5240,19 +5240,19 @@
         <v>3.38</v>
       </c>
       <c r="CB11" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CC11" t="n">
-        <v>2.71</v>
+        <v>2.67</v>
       </c>
       <c r="CD11" t="n">
-        <v>3.02</v>
+        <v>2.97</v>
       </c>
       <c r="CE11" t="n">
         <v>1.26</v>
       </c>
       <c r="CF11" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CG11" t="n">
         <v>3.09</v>
@@ -5273,7 +5273,7 @@
         <v>1.64</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="CN11" t="n">
         <v>2.07</v>
@@ -5282,22 +5282,22 @@
         <v>1.14</v>
       </c>
       <c r="CP11" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CQ11" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CR11" t="n">
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.52</v>
+        <v>2.53</v>
       </c>
       <c r="CT11" t="n">
         <v>3.32</v>
       </c>
       <c r="CU11" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="CV11" t="n">
         <v>2.44</v>
@@ -5321,85 +5321,85 @@
         <v>1.21</v>
       </c>
       <c r="DC11" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.67</v>
+        <v>2.68</v>
       </c>
       <c r="DE11" t="n">
         <v>0.08</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.29</v>
+        <v>2.24</v>
       </c>
       <c r="DH11" t="n">
-        <v>94.13</v>
+        <v>94.48</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.62</v>
+        <v>4.76</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.21</v>
+        <v>0.32</v>
       </c>
       <c r="DM11" t="n">
-        <v>45.17</v>
+        <v>46</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.09</v>
+        <v>2.28</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.71</v>
+        <v>12.56</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.37</v>
+        <v>11.28</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.75</v>
+        <v>8.6</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.12</v>
+        <v>0.16</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>48.8</v>
+        <v>49.2</v>
       </c>
       <c r="DW11" t="n">
         <v>0.12</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.46</v>
+        <v>12.56</v>
       </c>
       <c r="DY11" t="n">
-        <v>7.96</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.5</v>
+        <v>4.52</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.5</v>
+        <v>20.72</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.25</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="12">
@@ -5643,13 +5643,13 @@
         <v>3.58</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CC12" t="n">
         <v>3.02</v>
       </c>
       <c r="CD12" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CE12" t="n">
         <v>1.33</v>
@@ -5724,7 +5724,7 @@
         <v>1.24</v>
       </c>
       <c r="DC12" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="DD12" t="n">
         <v>2.89</v>
@@ -5812,13 +5812,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C13" t="n">
         <v>13</v>
       </c>
       <c r="D13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E13" t="n">
         <v>0.31</v>
@@ -5902,139 +5902,139 @@
         <v>2.62</v>
       </c>
       <c r="AF13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AG13" t="n">
-        <v>1.55</v>
+        <v>1.75</v>
       </c>
       <c r="AH13" t="n">
-        <v>2.09</v>
+        <v>2.33</v>
       </c>
       <c r="AI13" t="n">
-        <v>87.81999999999999</v>
+        <v>86</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="AK13" t="n">
-        <v>2.82</v>
+        <v>2.92</v>
       </c>
       <c r="AL13" t="n">
-        <v>4.36</v>
+        <v>4.5</v>
       </c>
       <c r="AM13" t="n">
-        <v>0.45</v>
+        <v>0.5</v>
       </c>
       <c r="AN13" t="n">
-        <v>35.91</v>
+        <v>34.92</v>
       </c>
       <c r="AO13" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="AP13" t="n">
-        <v>2.27</v>
+        <v>2.17</v>
       </c>
       <c r="AQ13" t="n">
-        <v>12.91</v>
+        <v>12.25</v>
       </c>
       <c r="AR13" t="n">
-        <v>14.09</v>
+        <v>14</v>
       </c>
       <c r="AS13" t="n">
-        <v>9.640000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="AT13" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="AU13" t="n">
-        <v>1.18</v>
+        <v>1.25</v>
       </c>
       <c r="AV13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AW13" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="AX13" t="n">
         <v>0</v>
       </c>
       <c r="AY13" t="n">
-        <v>45.18</v>
+        <v>45</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="BA13" t="n">
-        <v>11.64</v>
+        <v>11.42</v>
       </c>
       <c r="BB13" t="n">
-        <v>7.82</v>
+        <v>7.75</v>
       </c>
       <c r="BC13" t="n">
-        <v>3.82</v>
+        <v>3.67</v>
       </c>
       <c r="BD13" t="n">
-        <v>20</v>
+        <v>20.08</v>
       </c>
       <c r="BE13" t="n">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="BF13" t="n">
-        <v>2.64</v>
+        <v>2.75</v>
       </c>
       <c r="BG13" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="BH13" t="n">
-        <v>9.539999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="BI13" t="n">
-        <v>3.12</v>
+        <v>3.2</v>
       </c>
       <c r="BJ13" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BK13" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL13" t="n">
-        <v>1.12</v>
+        <v>1.16</v>
       </c>
       <c r="BM13" t="n">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="BN13" t="n">
-        <v>1.88</v>
+        <v>1.92</v>
       </c>
       <c r="BO13" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="BP13" t="n">
-        <v>4.58</v>
+        <v>4.48</v>
       </c>
       <c r="BQ13" t="n">
-        <v>4.38</v>
+        <v>4.56</v>
       </c>
       <c r="BR13" t="n">
-        <v>95.83</v>
+        <v>96</v>
       </c>
       <c r="BS13" t="n">
-        <v>79.17</v>
+        <v>80</v>
       </c>
       <c r="BT13" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BU13" t="n">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="BV13" t="n">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="BW13" t="n">
         <v>0</v>
       </c>
       <c r="BX13" t="n">
-        <v>62.5</v>
+        <v>64</v>
       </c>
       <c r="BY13" t="n">
         <v>2.43</v>
@@ -6043,16 +6043,16 @@
         <v>2.55</v>
       </c>
       <c r="CA13" t="n">
-        <v>3.57</v>
+        <v>3.58</v>
       </c>
       <c r="CB13" t="n">
-        <v>3.65</v>
+        <v>3.66</v>
       </c>
       <c r="CC13" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="CD13" t="n">
-        <v>3.16</v>
+        <v>3.26</v>
       </c>
       <c r="CE13" t="n">
         <v>1.31</v>
@@ -6061,13 +6061,13 @@
         <v>2.44</v>
       </c>
       <c r="CG13" t="n">
-        <v>3.17</v>
+        <v>3.18</v>
       </c>
       <c r="CH13" t="n">
         <v>1.52</v>
       </c>
       <c r="CI13" t="n">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="CJ13" t="n">
         <v>1.56</v>
@@ -6076,10 +6076,10 @@
         <v>1.37</v>
       </c>
       <c r="CL13" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="CM13" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CN13" t="n">
         <v>2.15</v>
@@ -6106,7 +6106,7 @@
         <v>1.53</v>
       </c>
       <c r="CV13" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CW13" t="n">
         <v>1.58</v>
@@ -6127,52 +6127,52 @@
         <v>1.21</v>
       </c>
       <c r="DC13" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD13" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="DE13" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DF13" t="n">
-        <v>1.54</v>
+        <v>1.64</v>
       </c>
       <c r="DG13" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="DH13" t="n">
-        <v>94.42</v>
+        <v>93.28</v>
       </c>
       <c r="DI13" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DJ13" t="n">
-        <v>2.75</v>
+        <v>2.8</v>
       </c>
       <c r="DK13" t="n">
-        <v>4.75</v>
+        <v>4.8</v>
       </c>
       <c r="DL13" t="n">
-        <v>0.37</v>
+        <v>0.4</v>
       </c>
       <c r="DM13" t="n">
-        <v>42.38</v>
+        <v>41.64</v>
       </c>
       <c r="DN13" t="n">
-        <v>1.16</v>
+        <v>1.12</v>
       </c>
       <c r="DO13" t="n">
-        <v>2.33</v>
+        <v>2.28</v>
       </c>
       <c r="DP13" t="n">
-        <v>12.25</v>
+        <v>11.96</v>
       </c>
       <c r="DQ13" t="n">
-        <v>14.25</v>
+        <v>14.2</v>
       </c>
       <c r="DR13" t="n">
-        <v>9.09</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS13" t="n">
         <v>0.16</v>
@@ -6184,28 +6184,28 @@
         <v>0</v>
       </c>
       <c r="DV13" t="n">
-        <v>46.79</v>
+        <v>46.64</v>
       </c>
       <c r="DW13" t="n">
         <v>0.08</v>
       </c>
       <c r="DX13" t="n">
-        <v>13.5</v>
+        <v>13.32</v>
       </c>
       <c r="DY13" t="n">
-        <v>8.710000000000001</v>
+        <v>8.640000000000001</v>
       </c>
       <c r="DZ13" t="n">
-        <v>4.8</v>
+        <v>4.68</v>
       </c>
       <c r="EA13" t="n">
-        <v>22</v>
+        <v>21.96</v>
       </c>
       <c r="EB13" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="EC13" t="n">
-        <v>2.63</v>
+        <v>2.68</v>
       </c>
     </row>
     <row r="14">
@@ -6215,94 +6215,94 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D14" t="n">
         <v>13</v>
       </c>
       <c r="E14" t="n">
-        <v>0.27</v>
+        <v>0.25</v>
       </c>
       <c r="F14" t="n">
-        <v>2.18</v>
+        <v>2.17</v>
       </c>
       <c r="G14" t="n">
-        <v>1.91</v>
+        <v>2.08</v>
       </c>
       <c r="H14" t="n">
-        <v>77.55</v>
+        <v>80.25</v>
       </c>
       <c r="I14" t="n">
         <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>3.36</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>4.36</v>
+        <v>4.58</v>
       </c>
       <c r="L14" t="n">
-        <v>0.45</v>
+        <v>0.42</v>
       </c>
       <c r="M14" t="n">
-        <v>41.82</v>
+        <v>41.33</v>
       </c>
       <c r="N14" t="n">
-        <v>1.18</v>
+        <v>1.08</v>
       </c>
       <c r="O14" t="n">
-        <v>1.91</v>
+        <v>2</v>
       </c>
       <c r="P14" t="n">
-        <v>14.91</v>
+        <v>14.5</v>
       </c>
       <c r="Q14" t="n">
-        <v>12.82</v>
+        <v>12.42</v>
       </c>
       <c r="R14" t="n">
-        <v>8.91</v>
+        <v>8.58</v>
       </c>
       <c r="S14" t="n">
-        <v>1.64</v>
+        <v>1.75</v>
       </c>
       <c r="T14" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.17</v>
       </c>
       <c r="W14" t="n">
         <v>0</v>
       </c>
       <c r="X14" t="n">
-        <v>45.55</v>
+        <v>45.83</v>
       </c>
       <c r="Y14" t="n">
-        <v>0.18</v>
+        <v>0.17</v>
       </c>
       <c r="Z14" t="n">
-        <v>11.45</v>
+        <v>12.33</v>
       </c>
       <c r="AA14" t="n">
-        <v>6.55</v>
+        <v>7.33</v>
       </c>
       <c r="AB14" t="n">
-        <v>4.91</v>
+        <v>5</v>
       </c>
       <c r="AC14" t="n">
-        <v>16.55</v>
+        <v>16.92</v>
       </c>
       <c r="AD14" t="n">
-        <v>1.37</v>
+        <v>1.43</v>
       </c>
       <c r="AE14" t="n">
-        <v>3.18</v>
+        <v>3.08</v>
       </c>
       <c r="AF14" t="n">
         <v>0.08</v>
@@ -6386,70 +6386,70 @@
         <v>2.38</v>
       </c>
       <c r="BG14" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="BH14" t="n">
-        <v>9.960000000000001</v>
+        <v>10.04</v>
       </c>
       <c r="BI14" t="n">
-        <v>3.38</v>
+        <v>3.48</v>
       </c>
       <c r="BJ14" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BK14" t="n">
-        <v>0.5</v>
+        <v>0.6</v>
       </c>
       <c r="BL14" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="BM14" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN14" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="BO14" t="n">
-        <v>1.21</v>
+        <v>1.32</v>
       </c>
       <c r="BP14" t="n">
-        <v>4.42</v>
+        <v>4.52</v>
       </c>
       <c r="BQ14" t="n">
         <v>4.92</v>
       </c>
       <c r="BR14" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS14" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT14" t="n">
-        <v>70.83</v>
+        <v>72</v>
       </c>
       <c r="BU14" t="n">
-        <v>54.17</v>
+        <v>56</v>
       </c>
       <c r="BV14" t="n">
-        <v>29.17</v>
+        <v>32</v>
       </c>
       <c r="BW14" t="n">
-        <v>8.33</v>
+        <v>12</v>
       </c>
       <c r="BX14" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BY14" t="n">
-        <v>2.57</v>
+        <v>2.61</v>
       </c>
       <c r="BZ14" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="CA14" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CB14" t="n">
-        <v>3.89</v>
+        <v>3.88</v>
       </c>
       <c r="CC14" t="n">
         <v>3.82</v>
@@ -6482,16 +6482,16 @@
         <v>1.68</v>
       </c>
       <c r="CM14" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CN14" t="n">
-        <v>2.17</v>
+        <v>2.16</v>
       </c>
       <c r="CO14" t="n">
         <v>1.16</v>
       </c>
       <c r="CP14" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CQ14" t="n">
         <v>2.45</v>
@@ -6503,7 +6503,7 @@
         <v>2.47</v>
       </c>
       <c r="CT14" t="n">
-        <v>3.3</v>
+        <v>3.31</v>
       </c>
       <c r="CU14" t="n">
         <v>1.58</v>
@@ -6530,85 +6530,85 @@
         <v>1.2</v>
       </c>
       <c r="DC14" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="DD14" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DE14" t="n">
-        <v>0.17</v>
+        <v>0.16</v>
       </c>
       <c r="DF14" t="n">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="DG14" t="n">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="DH14" t="n">
-        <v>84.45999999999999</v>
+        <v>85.48</v>
       </c>
       <c r="DI14" t="n">
         <v>0</v>
       </c>
       <c r="DJ14" t="n">
-        <v>2.83</v>
+        <v>2.8</v>
       </c>
       <c r="DK14" t="n">
-        <v>4.83</v>
+        <v>4.92</v>
       </c>
       <c r="DL14" t="n">
-        <v>0.46</v>
+        <v>0.44</v>
       </c>
       <c r="DM14" t="n">
-        <v>41.21</v>
+        <v>41</v>
       </c>
       <c r="DN14" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="DO14" t="n">
-        <v>2.13</v>
+        <v>2.16</v>
       </c>
       <c r="DP14" t="n">
-        <v>13.17</v>
+        <v>13.04</v>
       </c>
       <c r="DQ14" t="n">
-        <v>10.88</v>
+        <v>10.76</v>
       </c>
       <c r="DR14" t="n">
-        <v>9.210000000000001</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="DS14" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DT14" t="n">
-        <v>0.08</v>
+        <v>0.16</v>
       </c>
       <c r="DU14" t="n">
         <v>0</v>
       </c>
       <c r="DV14" t="n">
-        <v>47.21</v>
+        <v>47.28</v>
       </c>
       <c r="DW14" t="n">
         <v>0.08</v>
       </c>
       <c r="DX14" t="n">
-        <v>11.79</v>
+        <v>12.2</v>
       </c>
       <c r="DY14" t="n">
-        <v>7.63</v>
+        <v>7.96</v>
       </c>
       <c r="DZ14" t="n">
-        <v>4.17</v>
+        <v>4.24</v>
       </c>
       <c r="EA14" t="n">
-        <v>17.71</v>
+        <v>17.84</v>
       </c>
       <c r="EB14" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="EC14" t="n">
-        <v>2.75</v>
+        <v>2.72</v>
       </c>
     </row>
     <row r="15">
@@ -7054,7 +7054,7 @@
         <v>0.38</v>
       </c>
       <c r="M16" t="n">
-        <v>44</v>
+        <v>44.08</v>
       </c>
       <c r="N16" t="n">
         <v>0.54</v>
@@ -7249,7 +7249,7 @@
         <v>2.35</v>
       </c>
       <c r="BZ16" t="n">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="CA16" t="n">
         <v>3.55</v>
@@ -7315,7 +7315,7 @@
         <v>1.52</v>
       </c>
       <c r="CV16" t="n">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="CW16" t="n">
         <v>1.61</v>
@@ -7327,7 +7327,7 @@
         <v>1.69</v>
       </c>
       <c r="CZ16" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="DA16" t="n">
         <v>2.15</v>
@@ -7339,7 +7339,7 @@
         <v>1.72</v>
       </c>
       <c r="DD16" t="n">
-        <v>2.76</v>
+        <v>2.75</v>
       </c>
       <c r="DE16" t="n">
         <v>0.04</v>
@@ -7366,7 +7366,7 @@
         <v>0.4</v>
       </c>
       <c r="DM16" t="n">
-        <v>46.12</v>
+        <v>46.16</v>
       </c>
       <c r="DN16" t="n">
         <v>0.72</v>
@@ -7457,7 +7457,7 @@
         <v>0.77</v>
       </c>
       <c r="M17" t="n">
-        <v>59.23</v>
+        <v>59.54</v>
       </c>
       <c r="N17" t="n">
         <v>0.54</v>
@@ -7652,13 +7652,13 @@
         <v>1.88</v>
       </c>
       <c r="BZ17" t="n">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="CA17" t="n">
         <v>3.66</v>
       </c>
       <c r="CB17" t="n">
-        <v>3.78</v>
+        <v>3.76</v>
       </c>
       <c r="CC17" t="n">
         <v>2.24</v>
@@ -7709,7 +7709,7 @@
         <v>1.36</v>
       </c>
       <c r="CS17" t="n">
-        <v>2.61</v>
+        <v>2.6</v>
       </c>
       <c r="CT17" t="n">
         <v>3.26</v>
@@ -7718,7 +7718,7 @@
         <v>1.53</v>
       </c>
       <c r="CV17" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="CW17" t="n">
         <v>1.62</v>
@@ -7769,7 +7769,7 @@
         <v>0.8</v>
       </c>
       <c r="DM17" t="n">
-        <v>50.6</v>
+        <v>50.76</v>
       </c>
       <c r="DN17" t="n">
         <v>0.72</v>
@@ -7827,10 +7827,10 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C18" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D18" t="n">
         <v>12</v>
@@ -7839,82 +7839,82 @@
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="G18" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="H18" t="n">
-        <v>91.33</v>
+        <v>90</v>
       </c>
       <c r="I18" t="n">
         <v>-0.08</v>
       </c>
       <c r="J18" t="n">
-        <v>2.67</v>
+        <v>2.62</v>
       </c>
       <c r="K18" t="n">
-        <v>4.58</v>
+        <v>4.54</v>
       </c>
       <c r="L18" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="M18" t="n">
-        <v>39.92</v>
+        <v>39</v>
       </c>
       <c r="N18" t="n">
-        <v>0.75</v>
+        <v>0.77</v>
       </c>
       <c r="O18" t="n">
-        <v>2.75</v>
+        <v>2.54</v>
       </c>
       <c r="P18" t="n">
-        <v>15</v>
+        <v>14.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>14.08</v>
+        <v>13.69</v>
       </c>
       <c r="R18" t="n">
-        <v>6.67</v>
+        <v>6.85</v>
       </c>
       <c r="S18" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="T18" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="U18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>55.25</v>
+        <v>54.15</v>
       </c>
       <c r="Y18" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.67</v>
+        <v>13.46</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.75</v>
+        <v>8.619999999999999</v>
       </c>
       <c r="AB18" t="n">
-        <v>4.92</v>
+        <v>4.85</v>
       </c>
       <c r="AC18" t="n">
-        <v>21.17</v>
+        <v>21.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="AE18" t="n">
-        <v>2.33</v>
+        <v>2.31</v>
       </c>
       <c r="AF18" t="n">
         <v>0.08</v>
@@ -7998,70 +7998,70 @@
         <v>3.5</v>
       </c>
       <c r="BG18" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BH18" t="n">
-        <v>9.710000000000001</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BI18" t="n">
-        <v>2.71</v>
+        <v>2.72</v>
       </c>
       <c r="BJ18" t="n">
-        <v>0.58</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="BK18" t="n">
-        <v>0.5</v>
+        <v>0.52</v>
       </c>
       <c r="BL18" t="n">
         <v>0.92</v>
       </c>
       <c r="BM18" t="n">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="BN18" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="BO18" t="n">
         <v>1.08</v>
       </c>
       <c r="BP18" t="n">
-        <v>4.58</v>
+        <v>4.68</v>
       </c>
       <c r="BQ18" t="n">
         <v>5.12</v>
       </c>
       <c r="BR18" t="n">
-        <v>91.67</v>
+        <v>92</v>
       </c>
       <c r="BS18" t="n">
-        <v>83.33</v>
+        <v>84</v>
       </c>
       <c r="BT18" t="n">
-        <v>58.33</v>
+        <v>60</v>
       </c>
       <c r="BU18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BV18" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BW18" t="n">
         <v>0</v>
       </c>
       <c r="BX18" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="BY18" t="n">
-        <v>2.66</v>
+        <v>2.67</v>
       </c>
       <c r="BZ18" t="n">
-        <v>2.83</v>
+        <v>2.84</v>
       </c>
       <c r="CA18" t="n">
-        <v>3.49</v>
+        <v>3.48</v>
       </c>
       <c r="CB18" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CC18" t="n">
         <v>3.65</v>
@@ -8091,7 +8091,7 @@
         <v>1.44</v>
       </c>
       <c r="CL18" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="CM18" t="n">
         <v>2.59</v>
@@ -8106,16 +8106,16 @@
         <v>1.77</v>
       </c>
       <c r="CQ18" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="CR18" t="n">
         <v>1.38</v>
       </c>
       <c r="CS18" t="n">
-        <v>2.78</v>
+        <v>2.77</v>
       </c>
       <c r="CT18" t="n">
-        <v>3.15</v>
+        <v>3.16</v>
       </c>
       <c r="CU18" t="n">
         <v>1.47</v>
@@ -8145,49 +8145,49 @@
         <v>1.84</v>
       </c>
       <c r="DD18" t="n">
-        <v>3.05</v>
+        <v>3.04</v>
       </c>
       <c r="DE18" t="n">
         <v>0.04</v>
       </c>
       <c r="DF18" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="DG18" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="DH18" t="n">
-        <v>88.66</v>
+        <v>88.08</v>
       </c>
       <c r="DI18" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ18" t="n">
-        <v>3.3</v>
+        <v>3.24</v>
       </c>
       <c r="DK18" t="n">
         <v>4</v>
       </c>
       <c r="DL18" t="n">
-        <v>0.29</v>
+        <v>0.28</v>
       </c>
       <c r="DM18" t="n">
-        <v>35.71</v>
+        <v>35.4</v>
       </c>
       <c r="DN18" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="DO18" t="n">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="DP18" t="n">
-        <v>13.79</v>
+        <v>13.6</v>
       </c>
       <c r="DQ18" t="n">
-        <v>13.46</v>
+        <v>13.28</v>
       </c>
       <c r="DR18" t="n">
-        <v>7.88</v>
+        <v>7.92</v>
       </c>
       <c r="DS18" t="n">
         <v>0.08</v>
@@ -8199,28 +8199,28 @@
         <v>0</v>
       </c>
       <c r="DV18" t="n">
-        <v>56</v>
+        <v>55.4</v>
       </c>
       <c r="DW18" t="n">
-        <v>0.21</v>
+        <v>0.2</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.25</v>
+        <v>12.2</v>
       </c>
       <c r="DY18" t="n">
-        <v>8.039999999999999</v>
+        <v>8</v>
       </c>
       <c r="DZ18" t="n">
-        <v>4.21</v>
+        <v>4.2</v>
       </c>
       <c r="EA18" t="n">
-        <v>21.17</v>
+        <v>21.28</v>
       </c>
       <c r="EB18" t="n">
         <v>1.33</v>
       </c>
       <c r="EC18" t="n">
-        <v>2.92</v>
+        <v>2.88</v>
       </c>
     </row>
     <row r="19">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -5162,16 +5162,16 @@
         <v>11.92</v>
       </c>
       <c r="BB11" t="n">
-        <v>7.75</v>
+        <v>7.67</v>
       </c>
       <c r="BC11" t="n">
-        <v>4.17</v>
+        <v>4.25</v>
       </c>
       <c r="BD11" t="n">
         <v>21.67</v>
       </c>
       <c r="BE11" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="BF11" t="n">
         <v>2.67</v>
@@ -5387,16 +5387,16 @@
         <v>12.56</v>
       </c>
       <c r="DY11" t="n">
-        <v>8.039999999999999</v>
+        <v>8</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.52</v>
+        <v>4.56</v>
       </c>
       <c r="EA11" t="n">
         <v>20.72</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="EC11" t="n">
         <v>2.24</v>
@@ -7093,10 +7093,10 @@
         <v>0</v>
       </c>
       <c r="Z16" t="n">
-        <v>13.54</v>
+        <v>13.62</v>
       </c>
       <c r="AA16" t="n">
-        <v>8.460000000000001</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AB16" t="n">
         <v>5.08</v>
@@ -7105,7 +7105,7 @@
         <v>18.69</v>
       </c>
       <c r="AD16" t="n">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="AE16" t="n">
         <v>2.46</v>
@@ -7399,10 +7399,10 @@
         <v>0.08</v>
       </c>
       <c r="DX16" t="n">
-        <v>12.4</v>
+        <v>12.44</v>
       </c>
       <c r="DY16" t="n">
-        <v>7.8</v>
+        <v>7.84</v>
       </c>
       <c r="DZ16" t="n">
         <v>4.6</v>
@@ -7899,10 +7899,10 @@
         <v>0.15</v>
       </c>
       <c r="Z18" t="n">
-        <v>13.46</v>
+        <v>13.38</v>
       </c>
       <c r="AA18" t="n">
-        <v>8.619999999999999</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="AB18" t="n">
         <v>4.85</v>
@@ -7911,7 +7911,7 @@
         <v>21.38</v>
       </c>
       <c r="AD18" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="AE18" t="n">
         <v>2.31</v>
@@ -8205,10 +8205,10 @@
         <v>0.2</v>
       </c>
       <c r="DX18" t="n">
-        <v>12.2</v>
+        <v>12.16</v>
       </c>
       <c r="DY18" t="n">
-        <v>8</v>
+        <v>7.96</v>
       </c>
       <c r="DZ18" t="n">
         <v>4.2</v>
@@ -8217,7 +8217,7 @@
         <v>21.28</v>
       </c>
       <c r="EB18" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="EC18" t="n">
         <v>2.88</v>

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -645,7 +645,7 @@
     <col width="9.6" customWidth="1" min="73" max="73"/>
     <col width="9.6" customWidth="1" min="74" max="74"/>
     <col width="9.6" customWidth="1" min="75" max="75"/>
-    <col width="7.199999999999999" customWidth="1" min="76" max="76"/>
+    <col width="8.4" customWidth="1" min="76" max="76"/>
     <col width="18" customWidth="1" min="77" max="77"/>
     <col width="27.6" customWidth="1" min="78" max="78"/>
     <col width="18" customWidth="1" min="79" max="79"/>
@@ -2185,13 +2185,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C4" t="n">
         <v>13</v>
       </c>
       <c r="D4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E4" t="n">
         <v>0.31</v>
@@ -2275,52 +2275,52 @@
         <v>2.15</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="AH4" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="AI4" t="n">
-        <v>89.42</v>
+        <v>89.31</v>
       </c>
       <c r="AJ4" t="n">
         <v>-0.08</v>
       </c>
       <c r="AK4" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AL4" t="n">
-        <v>5</v>
+        <v>4.69</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="AN4" t="n">
-        <v>37.33</v>
+        <v>37.69</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="AP4" t="n">
-        <v>2.5</v>
+        <v>2.31</v>
       </c>
       <c r="AQ4" t="n">
-        <v>11.75</v>
+        <v>11.62</v>
       </c>
       <c r="AR4" t="n">
-        <v>11.5</v>
+        <v>11.08</v>
       </c>
       <c r="AS4" t="n">
-        <v>8.17</v>
+        <v>8.380000000000001</v>
       </c>
       <c r="AT4" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AU4" t="n">
-        <v>1.58</v>
+        <v>1.54</v>
       </c>
       <c r="AV4" t="n">
         <v>0.08</v>
@@ -2332,82 +2332,82 @@
         <v>0</v>
       </c>
       <c r="AY4" t="n">
-        <v>50.83</v>
+        <v>50.23</v>
       </c>
       <c r="AZ4" t="n">
         <v>0.08</v>
       </c>
       <c r="BA4" t="n">
-        <v>12.83</v>
+        <v>12.62</v>
       </c>
       <c r="BB4" t="n">
-        <v>8.25</v>
+        <v>8.15</v>
       </c>
       <c r="BC4" t="n">
-        <v>4.58</v>
+        <v>4.46</v>
       </c>
       <c r="BD4" t="n">
-        <v>17.67</v>
+        <v>17.77</v>
       </c>
       <c r="BE4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BF4" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="BG4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BH4" t="n">
-        <v>10.44</v>
+        <v>10.38</v>
       </c>
       <c r="BI4" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.48</v>
+        <v>0.46</v>
       </c>
       <c r="BL4" t="n">
         <v>1</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BN4" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="BO4" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="BP4" t="n">
-        <v>5.04</v>
+        <v>5</v>
       </c>
       <c r="BQ4" t="n">
-        <v>5.4</v>
+        <v>5.38</v>
       </c>
       <c r="BR4" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS4" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT4" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BU4" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BV4" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW4" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX4" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BY4" t="n">
         <v>1.86</v>
@@ -2419,37 +2419,37 @@
         <v>3.65</v>
       </c>
       <c r="CB4" t="n">
-        <v>3.73</v>
+        <v>3.74</v>
       </c>
       <c r="CC4" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="CD4" t="n">
-        <v>3.08</v>
+        <v>3.06</v>
       </c>
       <c r="CE4" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF4" t="n">
-        <v>2.41</v>
+        <v>2.39</v>
       </c>
       <c r="CG4" t="n">
-        <v>3.19</v>
+        <v>3.21</v>
       </c>
       <c r="CH4" t="n">
         <v>1.52</v>
       </c>
       <c r="CI4" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CJ4" t="n">
         <v>1.57</v>
       </c>
       <c r="CK4" t="n">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="CL4" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="CM4" t="n">
         <v>2.7</v>
@@ -2461,10 +2461,10 @@
         <v>1.18</v>
       </c>
       <c r="CP4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CQ4" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="CR4" t="n">
         <v>1.36</v>
@@ -2479,7 +2479,7 @@
         <v>1.55</v>
       </c>
       <c r="CV4" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="CW4" t="n">
         <v>1.6</v>
@@ -2488,64 +2488,64 @@
         <v>1.47</v>
       </c>
       <c r="CY4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="CZ4" t="n">
         <v>2.58</v>
       </c>
       <c r="DA4" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="DB4" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="DC4" t="n">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="DD4" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.28</v>
+        <v>0.27</v>
       </c>
       <c r="DF4" t="n">
-        <v>1.24</v>
+        <v>1.2</v>
       </c>
       <c r="DG4" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="DH4" t="n">
-        <v>89.59999999999999</v>
+        <v>89.54000000000001</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="DJ4" t="n">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="DK4" t="n">
-        <v>4.96</v>
+        <v>4.81</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM4" t="n">
-        <v>42.48</v>
+        <v>42.46</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="DO4" t="n">
-        <v>2.52</v>
+        <v>2.43</v>
       </c>
       <c r="DP4" t="n">
-        <v>11.4</v>
+        <v>11.35</v>
       </c>
       <c r="DQ4" t="n">
-        <v>11.88</v>
+        <v>11.66</v>
       </c>
       <c r="DR4" t="n">
-        <v>8.16</v>
+        <v>8.26</v>
       </c>
       <c r="DS4" t="n">
         <v>0.08</v>
@@ -2557,28 +2557,28 @@
         <v>0</v>
       </c>
       <c r="DV4" t="n">
-        <v>50.68</v>
+        <v>50.38</v>
       </c>
       <c r="DW4" t="n">
         <v>0.08</v>
       </c>
       <c r="DX4" t="n">
-        <v>13.96</v>
+        <v>13.81</v>
       </c>
       <c r="DY4" t="n">
-        <v>8.640000000000001</v>
+        <v>8.57</v>
       </c>
       <c r="DZ4" t="n">
-        <v>5.32</v>
+        <v>5.23</v>
       </c>
       <c r="EA4" t="n">
-        <v>17.48</v>
+        <v>17.54</v>
       </c>
       <c r="EB4" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="EC4" t="n">
-        <v>1.8</v>
+        <v>1.76</v>
       </c>
     </row>
     <row r="5">
@@ -3394,13 +3394,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C7" t="n">
         <v>12</v>
       </c>
       <c r="D7" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E7" t="n">
         <v>0.17</v>
@@ -3484,139 +3484,139 @@
         <v>1.33</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="AH7" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="AI7" t="n">
-        <v>95.77</v>
+        <v>95.79000000000001</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AK7" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="AL7" t="n">
-        <v>6.15</v>
+        <v>6.14</v>
       </c>
       <c r="AM7" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AN7" t="n">
-        <v>47.15</v>
+        <v>47.71</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.62</v>
+        <v>0.57</v>
       </c>
       <c r="AP7" t="n">
         <v>3</v>
       </c>
       <c r="AQ7" t="n">
-        <v>10.77</v>
+        <v>10.86</v>
       </c>
       <c r="AR7" t="n">
-        <v>14.92</v>
+        <v>14.71</v>
       </c>
       <c r="AS7" t="n">
-        <v>7.23</v>
+        <v>7</v>
       </c>
       <c r="AT7" t="n">
-        <v>1.23</v>
+        <v>1.29</v>
       </c>
       <c r="AU7" t="n">
-        <v>1.85</v>
+        <v>1.71</v>
       </c>
       <c r="AV7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AX7" t="n">
         <v>0</v>
       </c>
       <c r="AY7" t="n">
-        <v>53.38</v>
+        <v>53.64</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="BA7" t="n">
-        <v>14.15</v>
+        <v>14.07</v>
       </c>
       <c r="BB7" t="n">
-        <v>9.08</v>
+        <v>9.07</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="BD7" t="n">
-        <v>22.08</v>
+        <v>21.71</v>
       </c>
       <c r="BE7" t="n">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="BF7" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="BG7" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="BH7" t="n">
-        <v>10.76</v>
+        <v>10.65</v>
       </c>
       <c r="BI7" t="n">
-        <v>2.8</v>
+        <v>2.77</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.48</v>
+        <v>0.5</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BL7" t="n">
         <v>0.96</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN7" t="n">
-        <v>1.68</v>
+        <v>1.65</v>
       </c>
       <c r="BO7" t="n">
         <v>1.12</v>
       </c>
       <c r="BP7" t="n">
-        <v>5.12</v>
+        <v>5.04</v>
       </c>
       <c r="BQ7" t="n">
         <v>5</v>
       </c>
       <c r="BR7" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS7" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BT7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BU7" t="n">
-        <v>36</v>
+        <v>34.62</v>
       </c>
       <c r="BV7" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX7" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BY7" t="n">
         <v>1.91</v>
@@ -3625,16 +3625,16 @@
         <v>1.94</v>
       </c>
       <c r="CA7" t="n">
-        <v>3.48</v>
+        <v>3.51</v>
       </c>
       <c r="CB7" t="n">
-        <v>3.77</v>
+        <v>3.78</v>
       </c>
       <c r="CC7" t="n">
-        <v>2.19</v>
+        <v>2.15</v>
       </c>
       <c r="CD7" t="n">
-        <v>2.55</v>
+        <v>2.49</v>
       </c>
       <c r="CE7" t="n">
         <v>1.25</v>
@@ -3643,10 +3643,10 @@
         <v>2.35</v>
       </c>
       <c r="CG7" t="n">
-        <v>3.16</v>
+        <v>3.17</v>
       </c>
       <c r="CH7" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="CI7" t="n">
         <v>2.25</v>
@@ -3658,7 +3658,7 @@
         <v>1.31</v>
       </c>
       <c r="CL7" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="CM7" t="n">
         <v>2.72</v>
@@ -3673,13 +3673,13 @@
         <v>1.58</v>
       </c>
       <c r="CQ7" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CR7" t="n">
         <v>1.37</v>
       </c>
       <c r="CS7" t="n">
-        <v>2.6</v>
+        <v>2.59</v>
       </c>
       <c r="CT7" t="n">
         <v>3.23</v>
@@ -3688,7 +3688,7 @@
         <v>1.53</v>
       </c>
       <c r="CV7" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW7" t="n">
         <v>1.61</v>
@@ -3712,19 +3712,19 @@
         <v>1.71</v>
       </c>
       <c r="DD7" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="DE7" t="n">
         <v>0.12</v>
       </c>
       <c r="DF7" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="DG7" t="n">
-        <v>2.88</v>
+        <v>2.89</v>
       </c>
       <c r="DH7" t="n">
-        <v>99.2</v>
+        <v>99.08</v>
       </c>
       <c r="DI7" t="n">
         <v>0.16</v>
@@ -3733,58 +3733,58 @@
         <v>1.96</v>
       </c>
       <c r="DK7" t="n">
-        <v>6.32</v>
+        <v>6.31</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DM7" t="n">
-        <v>52.12</v>
+        <v>52.23</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="DO7" t="n">
         <v>2.96</v>
       </c>
       <c r="DP7" t="n">
-        <v>10.48</v>
+        <v>10.54</v>
       </c>
       <c r="DQ7" t="n">
-        <v>14.24</v>
+        <v>14.15</v>
       </c>
       <c r="DR7" t="n">
-        <v>6.92</v>
+        <v>6.81</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT7" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU7" t="n">
         <v>0</v>
       </c>
       <c r="DV7" t="n">
-        <v>54.16</v>
+        <v>54.27</v>
       </c>
       <c r="DW7" t="n">
         <v>0.04</v>
       </c>
       <c r="DX7" t="n">
-        <v>15.04</v>
+        <v>14.96</v>
       </c>
       <c r="DY7" t="n">
-        <v>10.04</v>
+        <v>10</v>
       </c>
       <c r="DZ7" t="n">
-        <v>5</v>
+        <v>4.96</v>
       </c>
       <c r="EA7" t="n">
-        <v>22.88</v>
+        <v>22.65</v>
       </c>
       <c r="EB7" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="EC7" t="n">
         <v>1.92</v>
@@ -4200,61 +4200,61 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C9" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D9" t="n">
         <v>13</v>
       </c>
       <c r="E9" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="F9" t="n">
         <v>1</v>
       </c>
       <c r="G9" t="n">
-        <v>2.25</v>
+        <v>2.23</v>
       </c>
       <c r="H9" t="n">
-        <v>84.25</v>
+        <v>82.69</v>
       </c>
       <c r="I9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="J9" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="K9" t="n">
-        <v>4.5</v>
+        <v>4.31</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>32.08</v>
+        <v>33.69</v>
       </c>
       <c r="N9" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="O9" t="n">
-        <v>1.25</v>
+        <v>1.15</v>
       </c>
       <c r="P9" t="n">
-        <v>10.33</v>
+        <v>10.54</v>
       </c>
       <c r="Q9" t="n">
-        <v>14.75</v>
+        <v>14.54</v>
       </c>
       <c r="R9" t="n">
-        <v>8.5</v>
+        <v>8.69</v>
       </c>
       <c r="S9" t="n">
-        <v>2.17</v>
+        <v>2</v>
       </c>
       <c r="T9" t="n">
-        <v>1.42</v>
+        <v>1.46</v>
       </c>
       <c r="U9" t="n">
         <v>0</v>
@@ -4266,28 +4266,28 @@
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>44.67</v>
+        <v>44.54</v>
       </c>
       <c r="Y9" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="Z9" t="n">
-        <v>9.92</v>
+        <v>9.77</v>
       </c>
       <c r="AA9" t="n">
-        <v>6.75</v>
+        <v>6.54</v>
       </c>
       <c r="AB9" t="n">
-        <v>3.17</v>
+        <v>3.23</v>
       </c>
       <c r="AC9" t="n">
-        <v>19.33</v>
+        <v>19.23</v>
       </c>
       <c r="AD9" t="n">
         <v>1.09</v>
       </c>
       <c r="AE9" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AF9" t="n">
         <v>0</v>
@@ -4371,70 +4371,70 @@
         <v>2.46</v>
       </c>
       <c r="BG9" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="BH9" t="n">
-        <v>10.48</v>
+        <v>10.38</v>
       </c>
       <c r="BI9" t="n">
-        <v>3.72</v>
+        <v>3.65</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BL9" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.96</v>
+        <v>0.92</v>
       </c>
       <c r="BN9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="BP9" t="n">
-        <v>4.28</v>
+        <v>4.23</v>
       </c>
       <c r="BQ9" t="n">
-        <v>5.64</v>
+        <v>5.62</v>
       </c>
       <c r="BR9" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS9" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT9" t="n">
-        <v>72</v>
+        <v>69.23</v>
       </c>
       <c r="BU9" t="n">
-        <v>44</v>
+        <v>42.31</v>
       </c>
       <c r="BV9" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BW9" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BX9" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BY9" t="n">
-        <v>3.15</v>
+        <v>3.26</v>
       </c>
       <c r="BZ9" t="n">
-        <v>3.54</v>
+        <v>3.63</v>
       </c>
       <c r="CA9" t="n">
-        <v>3.81</v>
+        <v>3.82</v>
       </c>
       <c r="CB9" t="n">
-        <v>4.05</v>
+        <v>4.06</v>
       </c>
       <c r="CC9" t="n">
         <v>4.38</v>
@@ -4455,16 +4455,16 @@
         <v>1.55</v>
       </c>
       <c r="CI9" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CJ9" t="n">
         <v>1.57</v>
       </c>
       <c r="CK9" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="CM9" t="n">
         <v>2.79</v>
@@ -4527,40 +4527,40 @@
         <v>1.16</v>
       </c>
       <c r="DG9" t="n">
-        <v>2.2</v>
+        <v>2.19</v>
       </c>
       <c r="DH9" t="n">
-        <v>79.31999999999999</v>
+        <v>78.73</v>
       </c>
       <c r="DI9" t="n">
         <v>0.08</v>
       </c>
       <c r="DJ9" t="n">
-        <v>2.28</v>
+        <v>2.23</v>
       </c>
       <c r="DK9" t="n">
-        <v>4.32</v>
+        <v>4.23</v>
       </c>
       <c r="DL9" t="n">
         <v>0.16</v>
       </c>
       <c r="DM9" t="n">
-        <v>32.88</v>
+        <v>33.66</v>
       </c>
       <c r="DN9" t="n">
-        <v>1.04</v>
+        <v>1</v>
       </c>
       <c r="DO9" t="n">
-        <v>1.64</v>
+        <v>1.58</v>
       </c>
       <c r="DP9" t="n">
-        <v>11.92</v>
+        <v>11.96</v>
       </c>
       <c r="DQ9" t="n">
-        <v>13.16</v>
+        <v>13.12</v>
       </c>
       <c r="DR9" t="n">
-        <v>8.76</v>
+        <v>8.85</v>
       </c>
       <c r="DS9" t="n">
         <v>0.12</v>
@@ -4572,28 +4572,28 @@
         <v>0</v>
       </c>
       <c r="DV9" t="n">
-        <v>45.8</v>
+        <v>45.7</v>
       </c>
       <c r="DW9" t="n">
         <v>0.08</v>
       </c>
       <c r="DX9" t="n">
-        <v>11.04</v>
+        <v>10.92</v>
       </c>
       <c r="DY9" t="n">
-        <v>7.12</v>
+        <v>7</v>
       </c>
       <c r="DZ9" t="n">
         <v>3.92</v>
       </c>
       <c r="EA9" t="n">
-        <v>20.8</v>
+        <v>20.69</v>
       </c>
       <c r="EB9" t="n">
         <v>1.21</v>
       </c>
       <c r="EC9" t="n">
-        <v>2.12</v>
+        <v>2.08</v>
       </c>
     </row>
     <row r="10">
@@ -6618,10 +6618,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D15" t="n">
         <v>13</v>
@@ -6630,82 +6630,82 @@
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="G15" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>108.75</v>
+        <v>108.69</v>
       </c>
       <c r="I15" t="n">
         <v>0</v>
       </c>
       <c r="J15" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="K15" t="n">
-        <v>5.58</v>
+        <v>5.77</v>
       </c>
       <c r="L15" t="n">
-        <v>0.33</v>
+        <v>0.46</v>
       </c>
       <c r="M15" t="n">
-        <v>55.83</v>
+        <v>55.69</v>
       </c>
       <c r="N15" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="O15" t="n">
-        <v>2.58</v>
+        <v>2.69</v>
       </c>
       <c r="P15" t="n">
-        <v>12</v>
+        <v>11.62</v>
       </c>
       <c r="Q15" t="n">
-        <v>11.83</v>
+        <v>11.69</v>
       </c>
       <c r="R15" t="n">
-        <v>5.92</v>
+        <v>5.85</v>
       </c>
       <c r="S15" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="T15" t="n">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="U15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="V15" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>57.42</v>
+        <v>57.38</v>
       </c>
       <c r="Y15" t="n">
         <v>0.08</v>
       </c>
       <c r="Z15" t="n">
-        <v>16.83</v>
+        <v>16.85</v>
       </c>
       <c r="AA15" t="n">
-        <v>11.75</v>
+        <v>11.85</v>
       </c>
       <c r="AB15" t="n">
-        <v>5.08</v>
+        <v>5</v>
       </c>
       <c r="AC15" t="n">
-        <v>19.5</v>
+        <v>19.77</v>
       </c>
       <c r="AD15" t="n">
         <v>1.82</v>
       </c>
       <c r="AE15" t="n">
-        <v>2.33</v>
+        <v>2.38</v>
       </c>
       <c r="AF15" t="n">
         <v>0</v>
@@ -6789,19 +6789,19 @@
         <v>2.77</v>
       </c>
       <c r="BG15" t="n">
-        <v>3.32</v>
+        <v>3.27</v>
       </c>
       <c r="BH15" t="n">
-        <v>10.32</v>
+        <v>10.27</v>
       </c>
       <c r="BI15" t="n">
-        <v>3.32</v>
+        <v>3.27</v>
       </c>
       <c r="BJ15" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.54</v>
       </c>
       <c r="BK15" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BL15" t="n">
         <v>0.96</v>
@@ -6813,43 +6813,43 @@
         <v>1.88</v>
       </c>
       <c r="BO15" t="n">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="BP15" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="BQ15" t="n">
-        <v>5.2</v>
+        <v>5.19</v>
       </c>
       <c r="BR15" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS15" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT15" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BU15" t="n">
-        <v>32</v>
+        <v>30.77</v>
       </c>
       <c r="BV15" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW15" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BX15" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BY15" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="BZ15" t="n">
-        <v>2.27</v>
+        <v>2.28</v>
       </c>
       <c r="CA15" t="n">
-        <v>3.69</v>
+        <v>3.68</v>
       </c>
       <c r="CB15" t="n">
         <v>3.85</v>
@@ -6864,16 +6864,16 @@
         <v>1.26</v>
       </c>
       <c r="CF15" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CG15" t="n">
-        <v>3.4</v>
+        <v>3.41</v>
       </c>
       <c r="CH15" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CI15" t="n">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="CJ15" t="n">
         <v>1.49</v>
@@ -6882,10 +6882,10 @@
         <v>1.37</v>
       </c>
       <c r="CL15" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="CM15" t="n">
-        <v>2.85</v>
+        <v>2.84</v>
       </c>
       <c r="CN15" t="n">
         <v>2.17</v>
@@ -6894,10 +6894,10 @@
         <v>1.15</v>
       </c>
       <c r="CP15" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CQ15" t="n">
-        <v>2.36</v>
+        <v>2.35</v>
       </c>
       <c r="CR15" t="n">
         <v>1.34</v>
@@ -6912,7 +6912,7 @@
         <v>1.62</v>
       </c>
       <c r="CV15" t="n">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="CW15" t="n">
         <v>1.52</v>
@@ -6927,58 +6927,58 @@
         <v>2.55</v>
       </c>
       <c r="DA15" t="n">
-        <v>2.19</v>
+        <v>2.2</v>
       </c>
       <c r="DB15" t="n">
         <v>1.17</v>
       </c>
       <c r="DC15" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="DD15" t="n">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="DE15" t="n">
         <v>0</v>
       </c>
       <c r="DF15" t="n">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="DG15" t="n">
-        <v>2.84</v>
+        <v>2.88</v>
       </c>
       <c r="DH15" t="n">
-        <v>94.16</v>
+        <v>94.69</v>
       </c>
       <c r="DI15" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ15" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="DK15" t="n">
-        <v>5.32</v>
+        <v>5.43</v>
       </c>
       <c r="DL15" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="DM15" t="n">
-        <v>46.36</v>
+        <v>46.66</v>
       </c>
       <c r="DN15" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DO15" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="DP15" t="n">
-        <v>11.56</v>
+        <v>11.38</v>
       </c>
       <c r="DQ15" t="n">
-        <v>12.36</v>
+        <v>12.27</v>
       </c>
       <c r="DR15" t="n">
-        <v>7.4</v>
+        <v>7.31</v>
       </c>
       <c r="DS15" t="n">
         <v>0.12</v>
@@ -6990,28 +6990,28 @@
         <v>0</v>
       </c>
       <c r="DV15" t="n">
-        <v>55.32</v>
+        <v>55.38</v>
       </c>
       <c r="DW15" t="n">
         <v>0.04</v>
       </c>
       <c r="DX15" t="n">
-        <v>16.76</v>
+        <v>16.77</v>
       </c>
       <c r="DY15" t="n">
-        <v>11.32</v>
+        <v>11.38</v>
       </c>
       <c r="DZ15" t="n">
-        <v>5.44</v>
+        <v>5.38</v>
       </c>
       <c r="EA15" t="n">
-        <v>18.84</v>
+        <v>19</v>
       </c>
       <c r="EB15" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="EC15" t="n">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
     </row>
     <row r="16">

--- a/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
+++ b/data/teams/leagues/Averages_Germany_Bundesliga_2_2025-2026.xlsx
@@ -1379,94 +1379,94 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C2" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D2" t="n">
         <v>13</v>
       </c>
       <c r="E2" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="F2" t="n">
-        <v>1.17</v>
+        <v>1.08</v>
       </c>
       <c r="G2" t="n">
-        <v>4.08</v>
+        <v>4</v>
       </c>
       <c r="H2" t="n">
-        <v>103.67</v>
+        <v>101.46</v>
       </c>
       <c r="I2" t="n">
-        <v>0.17</v>
+        <v>0.23</v>
       </c>
       <c r="J2" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="K2" t="n">
-        <v>6.75</v>
+        <v>6.54</v>
       </c>
       <c r="L2" t="n">
-        <v>0.33</v>
+        <v>0.31</v>
       </c>
       <c r="M2" t="n">
-        <v>50.17</v>
+        <v>49.92</v>
       </c>
       <c r="N2" t="n">
-        <v>0.75</v>
+        <v>0.92</v>
       </c>
       <c r="O2" t="n">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="P2" t="n">
-        <v>13.5</v>
+        <v>13.54</v>
       </c>
       <c r="Q2" t="n">
-        <v>13.75</v>
+        <v>13.54</v>
       </c>
       <c r="R2" t="n">
-        <v>7.67</v>
+        <v>7.38</v>
       </c>
       <c r="S2" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="T2" t="n">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="U2" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0.33</v>
+        <v>0.38</v>
       </c>
       <c r="W2" t="n">
         <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>54.33</v>
+        <v>53.23</v>
       </c>
       <c r="Y2" t="n">
         <v>0.08</v>
       </c>
       <c r="Z2" t="n">
-        <v>15.33</v>
+        <v>16.15</v>
       </c>
       <c r="AA2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AB2" t="n">
-        <v>4.83</v>
+        <v>5.15</v>
       </c>
       <c r="AC2" t="n">
-        <v>22.75</v>
+        <v>22.46</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF2" t="n">
         <v>0</v>
@@ -1550,64 +1550,64 @@
         <v>2.31</v>
       </c>
       <c r="BG2" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="BH2" t="n">
-        <v>10.6</v>
+        <v>10.38</v>
       </c>
       <c r="BI2" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.52</v>
+        <v>0.54</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL2" t="n">
         <v>1.12</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.44</v>
+        <v>0.5</v>
       </c>
       <c r="BN2" t="n">
-        <v>1.56</v>
+        <v>1.62</v>
       </c>
       <c r="BO2" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BP2" t="n">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="BQ2" t="n">
-        <v>6.32</v>
+        <v>6.19</v>
       </c>
       <c r="BR2" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS2" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT2" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BU2" t="n">
-        <v>32</v>
+        <v>34.62</v>
       </c>
       <c r="BV2" t="n">
-        <v>12</v>
+        <v>11.54</v>
       </c>
       <c r="BW2" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX2" t="n">
-        <v>56</v>
+        <v>57.69</v>
       </c>
       <c r="BY2" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="BZ2" t="n">
-        <v>2.26</v>
+        <v>2.31</v>
       </c>
       <c r="CA2" t="n">
         <v>3.56</v>
@@ -1625,7 +1625,7 @@
         <v>1.31</v>
       </c>
       <c r="CF2" t="n">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="CG2" t="n">
         <v>3.2</v>
@@ -1634,7 +1634,7 @@
         <v>1.51</v>
       </c>
       <c r="CI2" t="n">
-        <v>2.31</v>
+        <v>2.3</v>
       </c>
       <c r="CJ2" t="n">
         <v>1.58</v>
@@ -1643,10 +1643,10 @@
         <v>1.36</v>
       </c>
       <c r="CL2" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="CM2" t="n">
-        <v>2.79</v>
+        <v>2.8</v>
       </c>
       <c r="CN2" t="n">
         <v>2.16</v>
@@ -1661,13 +1661,13 @@
         <v>2.65</v>
       </c>
       <c r="CR2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="CS2" t="n">
         <v>2.6</v>
       </c>
       <c r="CT2" t="n">
-        <v>3.18</v>
+        <v>3.2</v>
       </c>
       <c r="CU2" t="n">
         <v>1.53</v>
@@ -1703,76 +1703,76 @@
         <v>0.08</v>
       </c>
       <c r="DF2" t="n">
-        <v>1.48</v>
+        <v>1.43</v>
       </c>
       <c r="DG2" t="n">
-        <v>3.84</v>
+        <v>3.81</v>
       </c>
       <c r="DH2" t="n">
-        <v>103.04</v>
+        <v>101.96</v>
       </c>
       <c r="DI2" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="DJ2" t="n">
-        <v>2.2</v>
+        <v>2.23</v>
       </c>
       <c r="DK2" t="n">
-        <v>6.24</v>
+        <v>6.15</v>
       </c>
       <c r="DL2" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM2" t="n">
-        <v>51.12</v>
+        <v>50.96</v>
       </c>
       <c r="DN2" t="n">
-        <v>0.68</v>
+        <v>0.77</v>
       </c>
       <c r="DO2" t="n">
-        <v>2.36</v>
+        <v>2.31</v>
       </c>
       <c r="DP2" t="n">
-        <v>13.6</v>
+        <v>13.62</v>
       </c>
       <c r="DQ2" t="n">
-        <v>13.52</v>
+        <v>13.42</v>
       </c>
       <c r="DR2" t="n">
-        <v>7.24</v>
+        <v>7.12</v>
       </c>
       <c r="DS2" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DT2" t="n">
-        <v>0.28</v>
+        <v>0.31</v>
       </c>
       <c r="DU2" t="n">
         <v>0</v>
       </c>
       <c r="DV2" t="n">
-        <v>51.88</v>
+        <v>51.42</v>
       </c>
       <c r="DW2" t="n">
         <v>0.08</v>
       </c>
       <c r="DX2" t="n">
-        <v>14.2</v>
+        <v>14.65</v>
       </c>
       <c r="DY2" t="n">
-        <v>9.92</v>
+        <v>10.19</v>
       </c>
       <c r="DZ2" t="n">
-        <v>4.28</v>
+        <v>4.46</v>
       </c>
       <c r="EA2" t="n">
-        <v>23.88</v>
+        <v>23.69</v>
       </c>
       <c r="EB2" t="n">
-        <v>1.57</v>
+        <v>1.61</v>
       </c>
       <c r="EC2" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
     </row>
     <row r="3">
@@ -1782,13 +1782,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C3" t="n">
         <v>13</v>
       </c>
       <c r="D3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E3" t="n">
         <v>0.15</v>
@@ -1872,16 +1872,16 @@
         <v>3</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AG3" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>2.92</v>
+        <v>3.08</v>
       </c>
       <c r="AI3" t="n">
-        <v>83</v>
+        <v>84.31</v>
       </c>
       <c r="AJ3" t="n">
         <v>-0.08</v>
@@ -1890,121 +1890,121 @@
         <v>2.92</v>
       </c>
       <c r="AL3" t="n">
-        <v>5.58</v>
+        <v>5.62</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.5</v>
+        <v>0.46</v>
       </c>
       <c r="AN3" t="n">
-        <v>39.25</v>
+        <v>38.15</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.83</v>
+        <v>0.92</v>
       </c>
       <c r="AP3" t="n">
-        <v>2.67</v>
+        <v>2.54</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12.58</v>
+        <v>12.38</v>
       </c>
       <c r="AR3" t="n">
-        <v>9.08</v>
+        <v>9.31</v>
       </c>
       <c r="AS3" t="n">
-        <v>9.17</v>
+        <v>9.15</v>
       </c>
       <c r="AT3" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU3" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AX3" t="n">
         <v>0</v>
       </c>
       <c r="AY3" t="n">
-        <v>44.58</v>
+        <v>45.15</v>
       </c>
       <c r="AZ3" t="n">
         <v>0</v>
       </c>
       <c r="BA3" t="n">
-        <v>11.83</v>
+        <v>11.54</v>
       </c>
       <c r="BB3" t="n">
-        <v>8.33</v>
+        <v>8.15</v>
       </c>
       <c r="BC3" t="n">
-        <v>3.5</v>
+        <v>3.38</v>
       </c>
       <c r="BD3" t="n">
-        <v>23.33</v>
+        <v>22.77</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="BF3" t="n">
         <v>2.92</v>
       </c>
       <c r="BG3" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BH3" t="n">
-        <v>11.52</v>
+        <v>11.5</v>
       </c>
       <c r="BI3" t="n">
-        <v>2.68</v>
+        <v>2.65</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.92</v>
+        <v>0.88</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="BN3" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BO3" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="BP3" t="n">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="BQ3" t="n">
-        <v>5.96</v>
+        <v>6</v>
       </c>
       <c r="BR3" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS3" t="n">
-        <v>80</v>
+        <v>80.77</v>
       </c>
       <c r="BT3" t="n">
-        <v>48</v>
+        <v>46.15</v>
       </c>
       <c r="BU3" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV3" t="n">
-        <v>20</v>
+        <v>19.23</v>
       </c>
       <c r="BW3" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX3" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BY3" t="n">
         <v>2.16</v>
@@ -2022,34 +2022,34 @@
         <v>3.02</v>
       </c>
       <c r="CD3" t="n">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="CE3" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="CF3" t="n">
-        <v>2.39</v>
+        <v>2.38</v>
       </c>
       <c r="CG3" t="n">
-        <v>3.23</v>
+        <v>3.24</v>
       </c>
       <c r="CH3" t="n">
         <v>1.51</v>
       </c>
       <c r="CI3" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="CJ3" t="n">
         <v>1.57</v>
       </c>
       <c r="CK3" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CL3" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="CM3" t="n">
-        <v>2.97</v>
+        <v>2.96</v>
       </c>
       <c r="CN3" t="n">
         <v>2.25</v>
@@ -2058,10 +2058,10 @@
         <v>1.2</v>
       </c>
       <c r="CP3" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="CQ3" t="n">
-        <v>2.62</v>
+        <v>2.61</v>
       </c>
       <c r="CR3" t="n">
         <v>1.36</v>
@@ -2070,7 +2070,7 @@
         <v>2.61</v>
       </c>
       <c r="CT3" t="n">
-        <v>3.25</v>
+        <v>3.26</v>
       </c>
       <c r="CU3" t="n">
         <v>1.52</v>
@@ -2094,25 +2094,25 @@
         <v>2.26</v>
       </c>
       <c r="DB3" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC3" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD3" t="n">
-        <v>2.72</v>
+        <v>2.73</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF3" t="n">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="DG3" t="n">
-        <v>2.92</v>
+        <v>3</v>
       </c>
       <c r="DH3" t="n">
-        <v>94.8</v>
+        <v>95</v>
       </c>
       <c r="DI3" t="n">
         <v>0</v>
@@ -2121,28 +2121,28 @@
         <v>2.96</v>
       </c>
       <c r="DK3" t="n">
-        <v>5.52</v>
+        <v>5.54</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="DM3" t="n">
-        <v>46.64</v>
+        <v>45.8</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.92</v>
+        <v>0.96</v>
       </c>
       <c r="DO3" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="DP3" t="n">
-        <v>13.32</v>
+        <v>13.19</v>
       </c>
       <c r="DQ3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.73</v>
       </c>
       <c r="DR3" t="n">
-        <v>8.48</v>
+        <v>8.5</v>
       </c>
       <c r="DS3" t="n">
         <v>0.12</v>
@@ -2154,25 +2154,25 @@
         <v>0</v>
       </c>
       <c r="DV3" t="n">
-        <v>46.32</v>
+        <v>46.54</v>
       </c>
       <c r="DW3" t="n">
         <v>0</v>
       </c>
       <c r="DX3" t="n">
-        <v>14.24</v>
+        <v>14</v>
       </c>
       <c r="DY3" t="n">
-        <v>9.640000000000001</v>
+        <v>9.5</v>
       </c>
       <c r="DZ3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="EA3" t="n">
-        <v>22.16</v>
+        <v>21.92</v>
       </c>
       <c r="EB3" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="EC3" t="n">
         <v>2.96</v>
@@ -2588,10 +2588,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" t="n">
         <v>13</v>
@@ -2600,49 +2600,49 @@
         <v>0.08</v>
       </c>
       <c r="F5" t="n">
-        <v>1.83</v>
+        <v>1.69</v>
       </c>
       <c r="G5" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="H5" t="n">
-        <v>86.17</v>
+        <v>85.84999999999999</v>
       </c>
       <c r="I5" t="n">
         <v>0.08</v>
       </c>
       <c r="J5" t="n">
-        <v>2.33</v>
+        <v>2.23</v>
       </c>
       <c r="K5" t="n">
-        <v>4.75</v>
+        <v>4.77</v>
       </c>
       <c r="L5" t="n">
-        <v>0.42</v>
+        <v>0.54</v>
       </c>
       <c r="M5" t="n">
-        <v>42.58</v>
+        <v>41.85</v>
       </c>
       <c r="N5" t="n">
-        <v>0.42</v>
+        <v>0.46</v>
       </c>
       <c r="O5" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="P5" t="n">
-        <v>10.83</v>
+        <v>10.23</v>
       </c>
       <c r="Q5" t="n">
         <v>13.08</v>
       </c>
       <c r="R5" t="n">
-        <v>7.17</v>
+        <v>7</v>
       </c>
       <c r="S5" t="n">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="T5" t="n">
-        <v>1.58</v>
+        <v>1.92</v>
       </c>
       <c r="U5" t="n">
         <v>0.08</v>
@@ -2654,28 +2654,28 @@
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>49</v>
+        <v>48.69</v>
       </c>
       <c r="Y5" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="Z5" t="n">
-        <v>12.5</v>
+        <v>12.92</v>
       </c>
       <c r="AA5" t="n">
-        <v>8.33</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="AB5" t="n">
-        <v>4.17</v>
+        <v>4.46</v>
       </c>
       <c r="AC5" t="n">
-        <v>20</v>
+        <v>19.92</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.39</v>
+        <v>1.43</v>
       </c>
       <c r="AE5" t="n">
-        <v>2</v>
+        <v>1.92</v>
       </c>
       <c r="AF5" t="n">
         <v>0.15</v>
@@ -2759,70 +2759,70 @@
         <v>1.85</v>
       </c>
       <c r="BG5" t="n">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="BH5" t="n">
-        <v>11</v>
+        <v>10.92</v>
       </c>
       <c r="BI5" t="n">
-        <v>3.28</v>
+        <v>3.38</v>
       </c>
       <c r="BJ5" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="BK5" t="n">
         <v>0.88</v>
       </c>
-      <c r="BK5" t="n">
+      <c r="BL5" t="n">
         <v>0.92</v>
       </c>
-      <c r="BL5" t="n">
-        <v>0.84</v>
-      </c>
       <c r="BM5" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BN5" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="BO5" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="BP5" t="n">
-        <v>4.88</v>
+        <v>4.92</v>
       </c>
       <c r="BQ5" t="n">
-        <v>6.08</v>
+        <v>5.96</v>
       </c>
       <c r="BR5" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS5" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BT5" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BU5" t="n">
-        <v>40</v>
+        <v>42.31</v>
       </c>
       <c r="BV5" t="n">
-        <v>16</v>
+        <v>19.23</v>
       </c>
       <c r="BW5" t="n">
-        <v>8</v>
+        <v>11.54</v>
       </c>
       <c r="BX5" t="n">
-        <v>80</v>
+        <v>76.92</v>
       </c>
       <c r="BY5" t="n">
-        <v>2.57</v>
+        <v>2.53</v>
       </c>
       <c r="BZ5" t="n">
-        <v>2.61</v>
+        <v>2.58</v>
       </c>
       <c r="CA5" t="n">
-        <v>3.64</v>
+        <v>3.63</v>
       </c>
       <c r="CB5" t="n">
-        <v>3.72</v>
+        <v>3.7</v>
       </c>
       <c r="CC5" t="n">
         <v>3.67</v>
@@ -2834,28 +2834,28 @@
         <v>1.32</v>
       </c>
       <c r="CF5" t="n">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="CG5" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="CH5" t="n">
         <v>1.5</v>
       </c>
       <c r="CI5" t="n">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="CJ5" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="CK5" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="CL5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM5" t="n">
-        <v>2.86</v>
+        <v>2.85</v>
       </c>
       <c r="CN5" t="n">
         <v>2.17</v>
@@ -2864,28 +2864,28 @@
         <v>1.19</v>
       </c>
       <c r="CP5" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CQ5" t="n">
-        <v>2.67</v>
+        <v>2.69</v>
       </c>
       <c r="CR5" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="CS5" t="n">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="CT5" t="n">
-        <v>3.27</v>
+        <v>3.24</v>
       </c>
       <c r="CU5" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="CV5" t="n">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="CW5" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="CX5" t="n">
         <v>1.46</v>
@@ -2900,55 +2900,55 @@
         <v>2.2</v>
       </c>
       <c r="DB5" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="DC5" t="n">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="DD5" t="n">
-        <v>2.78</v>
+        <v>2.81</v>
       </c>
       <c r="DE5" t="n">
         <v>0.12</v>
       </c>
       <c r="DF5" t="n">
-        <v>1.4</v>
+        <v>1.34</v>
       </c>
       <c r="DG5" t="n">
-        <v>2.76</v>
+        <v>2.73</v>
       </c>
       <c r="DH5" t="n">
-        <v>91.40000000000001</v>
+        <v>91.04000000000001</v>
       </c>
       <c r="DI5" t="n">
         <v>0.12</v>
       </c>
       <c r="DJ5" t="n">
-        <v>2.16</v>
+        <v>2.11</v>
       </c>
       <c r="DK5" t="n">
         <v>4.88</v>
       </c>
       <c r="DL5" t="n">
-        <v>0.4</v>
+        <v>0.46</v>
       </c>
       <c r="DM5" t="n">
-        <v>43.96</v>
+        <v>43.54</v>
       </c>
       <c r="DN5" t="n">
-        <v>0.68</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO5" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="DP5" t="n">
-        <v>11.04</v>
+        <v>10.73</v>
       </c>
       <c r="DQ5" t="n">
-        <v>12.32</v>
+        <v>12.35</v>
       </c>
       <c r="DR5" t="n">
-        <v>8.039999999999999</v>
+        <v>7.93</v>
       </c>
       <c r="DS5" t="n">
         <v>0.04</v>
@@ -2960,28 +2960,28 @@
         <v>0</v>
       </c>
       <c r="DV5" t="n">
-        <v>49</v>
+        <v>48.84</v>
       </c>
       <c r="DW5" t="n">
         <v>0.16</v>
       </c>
       <c r="DX5" t="n">
-        <v>12.8</v>
+        <v>13</v>
       </c>
       <c r="DY5" t="n">
-        <v>8.76</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="DZ5" t="n">
-        <v>4.04</v>
+        <v>4.19</v>
       </c>
       <c r="EA5" t="n">
-        <v>20.88</v>
+        <v>20.81</v>
       </c>
       <c r="EB5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="EC5" t="n">
-        <v>1.92</v>
+        <v>1.89</v>
       </c>
     </row>
     <row r="6">
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C6" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D6" t="n">
         <v>12</v>
@@ -3003,82 +3003,82 @@
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="G6" t="n">
-        <v>2.23</v>
+        <v>2.29</v>
       </c>
       <c r="H6" t="n">
-        <v>94.92</v>
+        <v>95.70999999999999</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="K6" t="n">
-        <v>4.31</v>
+        <v>4.29</v>
       </c>
       <c r="L6" t="n">
-        <v>0.38</v>
+        <v>0.36</v>
       </c>
       <c r="M6" t="n">
-        <v>37</v>
+        <v>38.21</v>
       </c>
       <c r="N6" t="n">
         <v>1</v>
       </c>
       <c r="O6" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="P6" t="n">
-        <v>11.62</v>
+        <v>11.5</v>
       </c>
       <c r="Q6" t="n">
-        <v>12.54</v>
+        <v>12.64</v>
       </c>
       <c r="R6" t="n">
-        <v>8.460000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S6" t="n">
-        <v>1.77</v>
+        <v>1.64</v>
       </c>
       <c r="T6" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="U6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="V6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>40.69</v>
+        <v>41.43</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="Z6" t="n">
-        <v>12.54</v>
+        <v>12.79</v>
       </c>
       <c r="AA6" t="n">
-        <v>8.619999999999999</v>
+        <v>8.789999999999999</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.92</v>
+        <v>4</v>
       </c>
       <c r="AC6" t="n">
-        <v>22.92</v>
+        <v>22.43</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="AE6" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AF6" t="n">
         <v>0.17</v>
@@ -3162,70 +3162,70 @@
         <v>2.42</v>
       </c>
       <c r="BG6" t="n">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="BH6" t="n">
-        <v>10.4</v>
+        <v>10.35</v>
       </c>
       <c r="BI6" t="n">
-        <v>2.84</v>
+        <v>2.77</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.64</v>
+        <v>0.62</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="BN6" t="n">
-        <v>1.48</v>
+        <v>1.46</v>
       </c>
       <c r="BO6" t="n">
-        <v>1.36</v>
+        <v>1.31</v>
       </c>
       <c r="BP6" t="n">
-        <v>4.64</v>
+        <v>4.54</v>
       </c>
       <c r="BQ6" t="n">
-        <v>5.76</v>
+        <v>5.81</v>
       </c>
       <c r="BR6" t="n">
-        <v>96</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="BS6" t="n">
-        <v>84</v>
+        <v>80.77</v>
       </c>
       <c r="BT6" t="n">
-        <v>60</v>
+        <v>57.69</v>
       </c>
       <c r="BU6" t="n">
-        <v>28</v>
+        <v>26.92</v>
       </c>
       <c r="BV6" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW6" t="n">
         <v>0</v>
       </c>
       <c r="BX6" t="n">
-        <v>64</v>
+        <v>61.54</v>
       </c>
       <c r="BY6" t="n">
-        <v>2.95</v>
+        <v>2.96</v>
       </c>
       <c r="BZ6" t="n">
         <v>3.07</v>
       </c>
       <c r="CA6" t="n">
-        <v>3.61</v>
+        <v>3.59</v>
       </c>
       <c r="CB6" t="n">
-        <v>3.72</v>
+        <v>3.71</v>
       </c>
       <c r="CC6" t="n">
         <v>4.26</v>
@@ -3234,10 +3234,10 @@
         <v>4.65</v>
       </c>
       <c r="CE6" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="CF6" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CG6" t="n">
         <v>3.04</v>
@@ -3246,10 +3246,10 @@
         <v>1.47</v>
       </c>
       <c r="CI6" t="n">
-        <v>2.15</v>
+        <v>2.16</v>
       </c>
       <c r="CJ6" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="CK6" t="n">
         <v>1.41</v>
@@ -3258,10 +3258,10 @@
         <v>1.78</v>
       </c>
       <c r="CM6" t="n">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="CN6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="CO6" t="n">
         <v>1.21</v>
@@ -3276,7 +3276,7 @@
         <v>1.38</v>
       </c>
       <c r="CS6" t="n">
-        <v>2.69</v>
+        <v>2.7</v>
       </c>
       <c r="CT6" t="n">
         <v>3.18</v>
@@ -3300,7 +3300,7 @@
         <v>2.56</v>
       </c>
       <c r="DA6" t="n">
-        <v>2.09</v>
+        <v>2.08</v>
       </c>
       <c r="DB6" t="n">
         <v>1.24</v>
@@ -3309,82 +3309,82 @@
         <v>1.8</v>
       </c>
       <c r="DD6" t="n">
-        <v>2.93</v>
+        <v>2.94</v>
       </c>
       <c r="DE6" t="n">
         <v>0.08</v>
       </c>
       <c r="DF6" t="n">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="DG6" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="DH6" t="n">
-        <v>97.40000000000001</v>
+        <v>97.73</v>
       </c>
       <c r="DI6" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ6" t="n">
-        <v>2.84</v>
+        <v>2.81</v>
       </c>
       <c r="DK6" t="n">
-        <v>4.56</v>
+        <v>4.54</v>
       </c>
       <c r="DL6" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DM6" t="n">
-        <v>41</v>
+        <v>41.5</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="DO6" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="DP6" t="n">
-        <v>12.4</v>
+        <v>12.31</v>
       </c>
       <c r="DQ6" t="n">
-        <v>12.68</v>
+        <v>12.73</v>
       </c>
       <c r="DR6" t="n">
-        <v>8.119999999999999</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DS6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DT6" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DU6" t="n">
         <v>0</v>
       </c>
       <c r="DV6" t="n">
-        <v>43.68</v>
+        <v>43.96</v>
       </c>
       <c r="DW6" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="DX6" t="n">
-        <v>12.32</v>
+        <v>12.46</v>
       </c>
       <c r="DY6" t="n">
-        <v>8.44</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="DZ6" t="n">
-        <v>3.88</v>
+        <v>3.92</v>
       </c>
       <c r="EA6" t="n">
-        <v>21.52</v>
+        <v>21.31</v>
       </c>
       <c r="EB6" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="EC6" t="n">
-        <v>2.32</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="7">
@@ -3797,13 +3797,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C8" t="n">
         <v>13</v>
       </c>
       <c r="D8" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
@@ -3890,49 +3890,49 @@
         <v>0.08</v>
       </c>
       <c r="AG8" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AH8" t="n">
-        <v>2.67</v>
+        <v>2.77</v>
       </c>
       <c r="AI8" t="n">
-        <v>93.5</v>
+        <v>92.08</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="AK8" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="AL8" t="n">
-        <v>4.5</v>
+        <v>4.54</v>
       </c>
       <c r="AM8" t="n">
-        <v>0.17</v>
+        <v>0.15</v>
       </c>
       <c r="AN8" t="n">
-        <v>42.75</v>
+        <v>43.31</v>
       </c>
       <c r="AO8" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="AP8" t="n">
-        <v>1.75</v>
+        <v>1.69</v>
       </c>
       <c r="AQ8" t="n">
-        <v>12.42</v>
+        <v>12.85</v>
       </c>
       <c r="AR8" t="n">
-        <v>12</v>
+        <v>11.85</v>
       </c>
       <c r="AS8" t="n">
-        <v>9.17</v>
+        <v>8.77</v>
       </c>
       <c r="AT8" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="AU8" t="n">
-        <v>0.92</v>
+        <v>0.85</v>
       </c>
       <c r="AV8" t="n">
         <v>0.08</v>
@@ -3944,82 +3944,82 @@
         <v>0</v>
       </c>
       <c r="AY8" t="n">
-        <v>45.67</v>
+        <v>45.92</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.25</v>
+        <v>0.23</v>
       </c>
       <c r="BA8" t="n">
-        <v>14.08</v>
+        <v>13.69</v>
       </c>
       <c r="BB8" t="n">
-        <v>9.67</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="BC8" t="n">
-        <v>4.42</v>
+        <v>4.23</v>
       </c>
       <c r="BD8" t="n">
-        <v>19.08</v>
+        <v>19.69</v>
       </c>
       <c r="BE8" t="n">
-        <v>1.51</v>
+        <v>1.48</v>
       </c>
       <c r="BF8" t="n">
-        <v>2.25</v>
+        <v>2.31</v>
       </c>
       <c r="BG8" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="BH8" t="n">
         <v>8.880000000000001</v>
       </c>
       <c r="BI8" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.44</v>
+        <v>0.42</v>
       </c>
       <c r="BL8" t="n">
         <v>0.88</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.68</v>
+        <v>0.65</v>
       </c>
       <c r="BN8" t="n">
-        <v>1.56</v>
+        <v>1.54</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.76</v>
+        <v>0.73</v>
       </c>
       <c r="BP8" t="n">
-        <v>3.88</v>
+        <v>3.81</v>
       </c>
       <c r="BQ8" t="n">
-        <v>4.96</v>
+        <v>5.04</v>
       </c>
       <c r="BR8" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS8" t="n">
-        <v>68</v>
+        <v>65.38</v>
       </c>
       <c r="BT8" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BU8" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BV8" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW8" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX8" t="n">
-        <v>56</v>
+        <v>53.85</v>
       </c>
       <c r="BY8" t="n">
         <v>2.35</v>
@@ -4028,25 +4028,25 @@
         <v>2.4</v>
       </c>
       <c r="CA8" t="n">
-        <v>3.61</v>
+        <v>3.6</v>
       </c>
       <c r="CB8" t="n">
-        <v>3.74</v>
+        <v>3.73</v>
       </c>
       <c r="CC8" t="n">
-        <v>3.41</v>
+        <v>3.31</v>
       </c>
       <c r="CD8" t="n">
-        <v>3.74</v>
+        <v>3.63</v>
       </c>
       <c r="CE8" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CF8" t="n">
-        <v>2.47</v>
+        <v>2.48</v>
       </c>
       <c r="CG8" t="n">
-        <v>3.16</v>
+        <v>3.15</v>
       </c>
       <c r="CH8" t="n">
         <v>1.5</v>
@@ -4064,7 +4064,7 @@
         <v>1.77</v>
       </c>
       <c r="CM8" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="CN8" t="n">
         <v>2.03</v>
@@ -4076,22 +4076,22 @@
         <v>1.67</v>
       </c>
       <c r="CQ8" t="n">
-        <v>2.59</v>
+        <v>2.6</v>
       </c>
       <c r="CR8" t="n">
         <v>1.36</v>
       </c>
       <c r="CS8" t="n">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="CT8" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="CU8" t="n">
         <v>1.53</v>
       </c>
       <c r="CV8" t="n">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="CW8" t="n">
         <v>1.6</v>
@@ -4106,58 +4106,58 @@
         <v>2.51</v>
       </c>
       <c r="DA8" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="DB8" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="DC8" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="DD8" t="n">
-        <v>2.71</v>
+        <v>2.73</v>
       </c>
       <c r="DE8" t="n">
         <v>0.04</v>
       </c>
       <c r="DF8" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="DG8" t="n">
-        <v>2.48</v>
+        <v>2.54</v>
       </c>
       <c r="DH8" t="n">
-        <v>93.68000000000001</v>
+        <v>92.95999999999999</v>
       </c>
       <c r="DI8" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="DJ8" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="DK8" t="n">
-        <v>4.48</v>
+        <v>4.5</v>
       </c>
       <c r="DL8" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="DM8" t="n">
-        <v>47.32</v>
+        <v>47.42</v>
       </c>
       <c r="DN8" t="n">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="DO8" t="n">
-        <v>1.96</v>
+        <v>1.92</v>
       </c>
       <c r="DP8" t="n">
-        <v>12.16</v>
+        <v>12.38</v>
       </c>
       <c r="DQ8" t="n">
-        <v>11.72</v>
+        <v>11.66</v>
       </c>
       <c r="DR8" t="n">
-        <v>7.68</v>
+        <v>7.54</v>
       </c>
       <c r="DS8" t="n">
         <v>0.04</v>
@@ -4169,28 +4169,28 @@
         <v>0</v>
       </c>
       <c r="DV8" t="n">
-        <v>48.76</v>
+        <v>48.77</v>
       </c>
       <c r="DW8" t="n">
         <v>0.16</v>
       </c>
       <c r="DX8" t="n">
-        <v>13.4</v>
+        <v>13.23</v>
       </c>
       <c r="DY8" t="n">
-        <v>9.199999999999999</v>
+        <v>9.119999999999999</v>
       </c>
       <c r="DZ8" t="n">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="EA8" t="n">
-        <v>20.4</v>
+        <v>20.65</v>
       </c>
       <c r="EB8" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="EC8" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
     </row>
     <row r="9">
@@ -4603,13 +4603,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C10" t="n">
         <v>12</v>
       </c>
       <c r="D10" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" t="n">
         <v>0.17</v>
@@ -4693,139 +4693,139 @@
         <v>1.58</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AG10" t="n">
-        <v>1.54</v>
+        <v>1.5</v>
       </c>
       <c r="AH10" t="n">
-        <v>2.46</v>
+        <v>2.43</v>
       </c>
       <c r="AI10" t="n">
-        <v>98.62</v>
+        <v>101</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AK10" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="AL10" t="n">
-        <v>4.62</v>
+        <v>4.43</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.31</v>
+        <v>0.29</v>
       </c>
       <c r="AN10" t="n">
-        <v>44.69</v>
+        <v>46.5</v>
       </c>
       <c r="AO10" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="AP10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AQ10" t="n">
+        <v>13.14</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>13.86</v>
+      </c>
+      <c r="AS10" t="n">
+        <v>6.57</v>
+      </c>
+      <c r="AT10" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU10" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>55.43</v>
+      </c>
+      <c r="AZ10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="BA10" t="n">
+        <v>12.07</v>
+      </c>
+      <c r="BB10" t="n">
+        <v>7.07</v>
+      </c>
+      <c r="BC10" t="n">
+        <v>5</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>20.07</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="BF10" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="BG10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BH10" t="n">
+        <v>10</v>
+      </c>
+      <c r="BI10" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="BJ10" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="BK10" t="n">
         <v>0.6899999999999999</v>
       </c>
-      <c r="AP10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>13.31</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>13.85</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>6.54</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>1.31</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>0.23</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>54.77</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>12.23</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>7.31</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>4.92</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>19.31</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BH10" t="n">
-        <v>10.16</v>
-      </c>
-      <c r="BI10" t="n">
-        <v>3</v>
-      </c>
-      <c r="BJ10" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="BK10" t="n">
-        <v>0.72</v>
-      </c>
       <c r="BL10" t="n">
-        <v>0.88</v>
+        <v>0.85</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.88</v>
+        <v>0.92</v>
       </c>
       <c r="BN10" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="BO10" t="n">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="BP10" t="n">
-        <v>4.52</v>
+        <v>4.42</v>
       </c>
       <c r="BQ10" t="n">
-        <v>5.56</v>
+        <v>5.5</v>
       </c>
       <c r="BR10" t="n">
-        <v>92</v>
+        <v>92.31</v>
       </c>
       <c r="BS10" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT10" t="n">
-        <v>76</v>
+        <v>76.92</v>
       </c>
       <c r="BU10" t="n">
-        <v>40</v>
+        <v>42.31</v>
       </c>
       <c r="BV10" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BW10" t="n">
         <v>0</v>
       </c>
       <c r="BX10" t="n">
-        <v>60</v>
+        <v>61.54</v>
       </c>
       <c r="BY10" t="n">
         <v>1.75</v>
@@ -4834,16 +4834,16 @@
         <v>1.82</v>
       </c>
       <c r="CA10" t="n">
-        <v>3.74</v>
+        <v>3.72</v>
       </c>
       <c r="CB10" t="n">
-        <v>3.9</v>
+        <v>3.89</v>
       </c>
       <c r="CC10" t="n">
-        <v>2.35</v>
+        <v>2.41</v>
       </c>
       <c r="CD10" t="n">
-        <v>2.43</v>
+        <v>2.51</v>
       </c>
       <c r="CE10" t="n">
         <v>1.3</v>
@@ -4852,13 +4852,13 @@
         <v>2.44</v>
       </c>
       <c r="CG10" t="n">
-        <v>3.26</v>
+        <v>3.25</v>
       </c>
       <c r="CH10" t="n">
         <v>1.54</v>
       </c>
       <c r="CI10" t="n">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="CJ10" t="n">
         <v>1.58</v>
@@ -4867,10 +4867,10 @@
         <v>1.35</v>
       </c>
       <c r="CL10" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="CM10" t="n">
-        <v>2.9</v>
+        <v>2.89</v>
       </c>
       <c r="CN10" t="n">
         <v>2.17</v>
@@ -4879,10 +4879,10 @@
         <v>1.18</v>
       </c>
       <c r="CP10" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="CQ10" t="n">
-        <v>2.57</v>
+        <v>2.58</v>
       </c>
       <c r="CR10" t="n">
         <v>1.35</v>
@@ -4906,13 +4906,13 @@
         <v>1.47</v>
       </c>
       <c r="CY10" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="CZ10" t="n">
         <v>2.56</v>
       </c>
       <c r="DA10" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="DB10" t="n">
         <v>1.2</v>
@@ -4921,19 +4921,19 @@
         <v>1.67</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.64</v>
+        <v>2.63</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DF10" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="DG10" t="n">
-        <v>3.36</v>
+        <v>3.31</v>
       </c>
       <c r="DH10" t="n">
-        <v>103.72</v>
+        <v>104.81</v>
       </c>
       <c r="DI10" t="n">
         <v>0.08</v>
@@ -4942,55 +4942,55 @@
         <v>1.92</v>
       </c>
       <c r="DK10" t="n">
-        <v>6.16</v>
+        <v>6</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.4</v>
+        <v>0.39</v>
       </c>
       <c r="DM10" t="n">
-        <v>51.2</v>
+        <v>51.92</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.5600000000000001</v>
+        <v>0.58</v>
       </c>
       <c r="DO10" t="n">
-        <v>2.76</v>
+        <v>2.66</v>
       </c>
       <c r="DP10" t="n">
-        <v>13.28</v>
+        <v>13.19</v>
       </c>
       <c r="DQ10" t="n">
-        <v>13.48</v>
+        <v>13.5</v>
       </c>
       <c r="DR10" t="n">
-        <v>6.12</v>
+        <v>6.15</v>
       </c>
       <c r="DS10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DT10" t="n">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="DU10" t="n">
         <v>0</v>
       </c>
       <c r="DV10" t="n">
-        <v>56.08</v>
+        <v>56.39</v>
       </c>
       <c r="DW10" t="n">
         <v>0.04</v>
       </c>
       <c r="DX10" t="n">
-        <v>14.8</v>
+        <v>14.61</v>
       </c>
       <c r="DY10" t="n">
-        <v>9.359999999999999</v>
+        <v>9.15</v>
       </c>
       <c r="DZ10" t="n">
-        <v>5.44</v>
+        <v>5.46</v>
       </c>
       <c r="EA10" t="n">
-        <v>19.6</v>
+        <v>20</v>
       </c>
       <c r="EB10" t="n">
         <v>1.69</v>
@@ -5006,94 +5006,94 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D11" t="n">
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F11" t="n">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="G11" t="n">
-        <v>2.62</v>
+        <v>2.57</v>
       </c>
       <c r="H11" t="n">
-        <v>95.31</v>
+        <v>96.70999999999999</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.08</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>2.23</v>
+        <v>2.21</v>
       </c>
       <c r="K11" t="n">
-        <v>4.92</v>
+        <v>4.93</v>
       </c>
       <c r="L11" t="n">
-        <v>0.38</v>
+        <v>0.43</v>
       </c>
       <c r="M11" t="n">
-        <v>44.46</v>
+        <v>43.64</v>
       </c>
       <c r="N11" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.64</v>
       </c>
       <c r="O11" t="n">
-        <v>2.31</v>
+        <v>2.36</v>
       </c>
       <c r="P11" t="n">
-        <v>12.08</v>
+        <v>11.71</v>
       </c>
       <c r="Q11" t="n">
-        <v>10.46</v>
+        <v>10.57</v>
       </c>
       <c r="R11" t="n">
-        <v>8.460000000000001</v>
+        <v>8.289999999999999</v>
       </c>
       <c r="S11" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="T11" t="n">
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="V11" t="n">
-        <v>0.15</v>
+        <v>0.21</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>49.85</v>
+        <v>49.71</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.23</v>
+        <v>0.21</v>
       </c>
       <c r="Z11" t="n">
-        <v>13.15</v>
+        <v>13</v>
       </c>
       <c r="AA11" t="n">
-        <v>8.31</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AB11" t="n">
-        <v>4.85</v>
+        <v>4.64</v>
       </c>
       <c r="AC11" t="n">
-        <v>19.85</v>
+        <v>19.64</v>
       </c>
       <c r="AD11" t="n">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="AE11" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="AF11" t="n">
         <v>0.08</v>
@@ -5177,67 +5177,67 @@
         <v>2.67</v>
       </c>
       <c r="BG11" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BH11" t="n">
-        <v>10.28</v>
+        <v>10.31</v>
       </c>
       <c r="BI11" t="n">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="BJ11" t="n">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.6</v>
+        <v>0.58</v>
       </c>
       <c r="BL11" t="n">
-        <v>0.52</v>
+        <v>0.5</v>
       </c>
       <c r="BM11" t="n">
         <v>0.88</v>
       </c>
       <c r="BN11" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="BO11" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="BP11" t="n">
-        <v>4.8</v>
+        <v>4.77</v>
       </c>
       <c r="BQ11" t="n">
-        <v>4.96</v>
+        <v>5.04</v>
       </c>
       <c r="BR11" t="n">
-        <v>88</v>
+        <v>88.45999999999999</v>
       </c>
       <c r="BS11" t="n">
-        <v>72</v>
+        <v>73.08</v>
       </c>
       <c r="BT11" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="BU11" t="n">
-        <v>24</v>
+        <v>23.08</v>
       </c>
       <c r="BV11" t="n">
-        <v>16</v>
+        <v>15.38</v>
       </c>
       <c r="BW11" t="n">
-        <v>8</v>
+        <v>7.69</v>
       </c>
       <c r="BX11" t="n">
-        <v>44</v>
+        <v>46.15</v>
       </c>
       <c r="BY11" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="BZ11" t="n">
-        <v>2.1</v>
+        <v>2.11</v>
       </c>
       <c r="CA11" t="n">
-        <v>3.38</v>
+        <v>3.39</v>
       </c>
       <c r="CB11" t="n">
         <v>3.73</v>
@@ -5255,25 +5255,25 @@
         <v>2.32</v>
       </c>
       <c r="CG11" t="n">
-        <v>3.09</v>
+        <v>3.1</v>
       </c>
       <c r="CH11" t="n">
         <v>1.46</v>
       </c>
       <c r="CI11" t="n">
-        <v>2.23</v>
+        <v>2.24</v>
       </c>
       <c r="CJ11" t="n">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="CK11" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="CL11" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="CM11" t="n">
-        <v>2.7</v>
+        <v>2.71</v>
       </c>
       <c r="CN11" t="n">
         <v>2.07</v>
@@ -5291,7 +5291,7 @@
         <v>1.35</v>
       </c>
       <c r="CS11" t="n">
-        <v>2.53</v>
+        <v>2.54</v>
       </c>
       <c r="CT11" t="n">
         <v>3.32</v>
@@ -5324,82 +5324,82 @@
         <v>1.69</v>
       </c>
       <c r="DD11" t="n">
-        <v>2.68</v>
+        <v>2.69</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="DF11" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="DG11" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
       <c r="DH11" t="n">
-        <v>94.48</v>
+        <v>95.27</v>
       </c>
       <c r="DI11" t="n">
         <v>0.04</v>
       </c>
       <c r="DJ11" t="n">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="DK11" t="n">
-        <v>4.76</v>
+        <v>4.77</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.32</v>
+        <v>0.35</v>
       </c>
       <c r="DM11" t="n">
-        <v>46</v>
+        <v>45.5</v>
       </c>
       <c r="DN11" t="n">
-        <v>0.72</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="DO11" t="n">
-        <v>2.28</v>
+        <v>2.31</v>
       </c>
       <c r="DP11" t="n">
-        <v>12.56</v>
+        <v>12.34</v>
       </c>
       <c r="DQ11" t="n">
-        <v>11.28</v>
+        <v>11.31</v>
       </c>
       <c r="DR11" t="n">
-        <v>8.6</v>
+        <v>8.5</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.16</v>
+        <v>0.19</v>
       </c>
       <c r="DU11" t="n">
         <v>0</v>
       </c>
       <c r="DV11" t="n">
-        <v>49.2</v>
+        <v>49.15</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.12</v>
+        <v>0.11</v>
       </c>
       <c r="DX11" t="n">
-        <v>12.56</v>
+        <v>12.5</v>
       </c>
       <c r="DY11" t="n">
-        <v>8</v>
+        <v>8.039999999999999</v>
       </c>
       <c r="DZ11" t="n">
-        <v>4.56</v>
+        <v>4.46</v>
       </c>
       <c r="EA11" t="n">
-        <v>20.72</v>
+        <v>20.58</v>
       </c>
       <c r="EB11" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="EC11" t="n">
-        <v>2.24</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="12">
@@ -5409,10 +5409,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D12" t="n">
         <v>13</v>
@@ -5421,49 +5421,49 @@
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="G12" t="n">
-        <v>3.25</v>
+        <v>3.54</v>
       </c>
       <c r="H12" t="n">
-        <v>88.25</v>
+        <v>90.23</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="K12" t="n">
-        <v>5.58</v>
+        <v>5.69</v>
       </c>
       <c r="L12" t="n">
-        <v>0.58</v>
+        <v>0.54</v>
       </c>
       <c r="M12" t="n">
-        <v>42.5</v>
+        <v>44.77</v>
       </c>
       <c r="N12" t="n">
-        <v>0.75</v>
+        <v>0.85</v>
       </c>
       <c r="O12" t="n">
-        <v>2.33</v>
+        <v>2.15</v>
       </c>
       <c r="P12" t="n">
-        <v>13</v>
+        <v>13.23</v>
       </c>
       <c r="Q12" t="n">
-        <v>14.67</v>
+        <v>14.54</v>
       </c>
       <c r="R12" t="n">
-        <v>7.25</v>
+        <v>7</v>
       </c>
       <c r="S12" t="n">
-        <v>1.08</v>
+        <v>1.23</v>
       </c>
       <c r="T12" t="n">
-        <v>1.17</v>
+        <v>1.23</v>
       </c>
       <c r="U12" t="n">
         <v>0.08</v>
@@ -5475,28 +5475,28 @@
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>52.75</v>
+        <v>53.46</v>
       </c>
       <c r="Y12" t="n">
         <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>12.5</v>
+        <v>13.15</v>
       </c>
       <c r="AA12" t="n">
-        <v>8.42</v>
+        <v>8.85</v>
       </c>
       <c r="AB12" t="n">
-        <v>4.08</v>
+        <v>4.31</v>
       </c>
       <c r="AC12" t="n">
-        <v>19.83</v>
+        <v>20.31</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="AE12" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="AF12" t="n">
         <v>0.08</v>
@@ -5580,70 +5580,70 @@
         <v>3.31</v>
       </c>
       <c r="BG12" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="BH12" t="n">
-        <v>10.32</v>
+        <v>10.23</v>
       </c>
       <c r="BI12" t="n">
-        <v>2.64</v>
+        <v>2.73</v>
       </c>
       <c r="BJ12" t="n">
-        <v>0.68</v>
+        <v>0.73</v>
       </c>
       <c r="BK12" t="n">
-        <v>0.52</v>
+        <v>0.58</v>
       </c>
       <c r="BL12" t="n">
-        <v>0.84</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="BM12" t="n">
-        <v>0.6</v>
+        <v>0.62</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="BO12" t="n">
-        <v>1.2</v>
+        <v>1.31</v>
       </c>
       <c r="BP12" t="n">
-        <v>4.48</v>
+        <v>4.35</v>
       </c>
       <c r="BQ12" t="n">
-        <v>5.8</v>
+        <v>5.85</v>
       </c>
       <c r="BR12" t="n">
         <v>100</v>
       </c>
       <c r="BS12" t="n">
-        <v>84</v>
+        <v>84.62</v>
       </c>
       <c r="BT12" t="n">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BU12" t="n">
-        <v>20</v>
+        <v>23.08</v>
       </c>
       <c r="BV12" t="n">
-        <v>8</v>
+        <v>11.54</v>
       </c>
       <c r="BW12" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="BX12" t="n">
-        <v>64</v>
+        <v>65.38</v>
       </c>
       <c r="BY12" t="n">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="BZ12" t="n">
-        <v>2.37</v>
+        <v>2.38</v>
       </c>
       <c r="CA12" t="n">
-        <v>3.58</v>
+        <v>3.57</v>
       </c>
       <c r="CB12" t="n">
-        <v>3.63</v>
+        <v>3.62</v>
       </c>
       <c r="CC12" t="n">
         <v>3.02</v>
@@ -5658,7 +5658,7 @@
         <v>2.52</v>
       </c>
       <c r="CG12" t="n">
-        <v>3.13</v>
+        <v>3.14</v>
       </c>
       <c r="CH12" t="n">
         <v>1.49</v>
@@ -5688,22 +5688,22 @@
         <v>1.72</v>
       </c>
       <c r="CQ